--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Among Us code\TheOtherUs\TheOtherUs-Edited-Lite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47093854-56BC-4972-8E3E-10AC161FB888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FEB7DDE-C8E2-4DFB-A244-78015297004C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="645" windowWidth="25620" windowHeight="15555" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="645" windowWidth="25620" windowHeight="15555" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Options" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3393" uniqueCount="3070">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3395" uniqueCount="3072">
   <si>
     <t>English</t>
   </si>
@@ -10834,6 +10834,14 @@
   </si>
   <si>
     <t>复活前摇</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PelicanWin</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹈鹕胜利！</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -21342,7 +21350,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
@@ -21992,121 +22000,129 @@
     </row>
     <row r="69" spans="1:15" ht="24.95" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>2989</v>
+        <v>3070</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>3005</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="24.95" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>3004</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="24.95" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>3003</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="24.95" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>3019</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="24.95" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>3018</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="24.95" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>3002</v>
+        <v>3018</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="24.95" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>3017</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="24.95" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>3016</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="24.95" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>3001</v>
+        <v>3016</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="24.95" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>3015</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="24.95" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>3013</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="24.95" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="81" spans="1:15" ht="24.95" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>3020</v>
+        <v>3000</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>3021</v>
+        <v>3014</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="24.95" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>3022</v>
+        <v>3020</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>3023</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="83" spans="1:15" ht="24.95" customHeight="1">
       <c r="A83" s="1" t="s">
+        <v>3022</v>
+      </c>
+      <c r="O83" s="1" t="s">
+        <v>3023</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A84" s="1" t="s">
         <v>3024</v>
       </c>
-      <c r="O83" s="1" t="s">
+      <c r="O84" s="1" t="s">
         <v>3025</v>
       </c>
     </row>

--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Among Us code\TheOtherUs\TheOtherUs-Edited-Lite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFDE31FA-73A3-46B0-AE74-5F5B72BA9100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739FD9A4-D374-44CC-9D74-6ACE9E106AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2355" yWindow="525" windowWidth="25755" windowHeight="15555" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4907,9 +4907,6 @@
     <t>executionerPromotesToLawyer</t>
   </si>
   <si>
-    <t>目标死亡后变为</t>
-  </si>
-  <si>
     <t>pavlovsownerAndJackalAsWell</t>
   </si>
   <si>
@@ -4954,9 +4951,6 @@
   </si>
   <si>
     <t>juggernautReducedkillEach</t>
-  </si>
-  <si>
-    <t>目标职业变更时可以晋升为律师</t>
   </si>
   <si>
     <t>每次击杀后减少的cd</t>
@@ -10883,6 +10877,14 @@
   </si>
   <si>
     <t>Team</t>
+  </si>
+  <si>
+    <t>目标被招募时可以晋升为律师</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标死亡后变为</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -11562,7 +11564,7 @@
     </row>
     <row r="4" spans="1:17" ht="24.95" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>2572</v>
+        <v>2570</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>20</v>
@@ -11617,24 +11619,24 @@
     </row>
     <row r="9" spans="1:17" ht="24.75" customHeight="1">
       <c r="A9" s="2" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>2464</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>2465</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>2466</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>2467</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="24.75" customHeight="1">
       <c r="A10" s="2" t="s">
+        <v>2567</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>2568</v>
+      </c>
+      <c r="O10" s="3" t="s">
         <v>2569</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>2570</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>2571</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="24.95" customHeight="1">
@@ -11650,156 +11652,156 @@
     </row>
     <row r="13" spans="1:17" ht="24.95" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>2443</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="24.95" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>2457</v>
+        <v>2455</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>2444</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="24.95" customHeight="1">
       <c r="A15" s="2" t="s">
+        <v>2452</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>2453</v>
+      </c>
+      <c r="O15" s="3" t="s">
         <v>2454</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>2455</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>2456</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="24.95" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>2461</v>
+        <v>2459</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>2452</v>
+        <v>2450</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>2450</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="24.95" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>2989</v>
+        <v>2987</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>2453</v>
+        <v>2451</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>2449</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="24.95" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>2459</v>
+        <v>2457</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="24.95" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>2451</v>
+        <v>2449</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>2464</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="24.95" customHeight="1">
       <c r="A20" s="2" t="s">
+        <v>2522</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>2523</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>2524</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>2525</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>2526</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="24.95" customHeight="1">
       <c r="A21" s="2" t="s">
+        <v>2470</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>2471</v>
+      </c>
+      <c r="O21" s="3" t="s">
         <v>2472</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>2473</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>2474</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="24.95" customHeight="1">
       <c r="A22" s="2" t="s">
+        <v>2768</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>2770</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>2772</v>
-      </c>
       <c r="O22" s="3" t="s">
-        <v>2771</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="24.95" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>2564</v>
+        <v>2562</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>2773</v>
+        <v>2771</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>2565</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="24.95" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>2445</v>
+        <v>2443</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>2446</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="24.95" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>2447</v>
+        <v>2445</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="24.95" customHeight="1">
       <c r="A26" s="2" t="s">
+        <v>2466</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>2468</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>2470</v>
-      </c>
       <c r="O26" s="3" t="s">
-        <v>2469</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="24.95" customHeight="1">
@@ -11829,7 +11831,7 @@
     </row>
     <row r="30" spans="1:15" ht="24.95" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>2988</v>
+        <v>2986</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>42</v>
@@ -11840,7 +11842,7 @@
     </row>
     <row r="31" spans="1:15" ht="24.95" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>44</v>
@@ -11854,7 +11856,7 @@
         <v>99</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>100</v>
@@ -11865,7 +11867,7 @@
         <v>101</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>102</v>
@@ -11876,10 +11878,10 @@
         <v>103</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="24.95" customHeight="1">
@@ -11887,7 +11889,7 @@
         <v>104</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>105</v>
@@ -11895,13 +11897,13 @@
     </row>
     <row r="36" spans="1:15" ht="24.95" customHeight="1">
       <c r="A36" s="2" t="s">
+        <v>2894</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>2895</v>
+      </c>
+      <c r="O36" s="3" t="s">
         <v>2896</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>2897</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>2898</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="24.95" customHeight="1">
@@ -11909,7 +11911,7 @@
         <v>97</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="O37" s="3" t="s">
         <v>98</v>
@@ -11942,21 +11944,21 @@
     </row>
     <row r="41" spans="1:15" ht="24.95" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>52</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>2568</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="24.95" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>54</v>
@@ -11964,7 +11966,7 @@
     </row>
     <row r="43" spans="1:15" ht="24.95" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>55</v>
@@ -11975,7 +11977,7 @@
     </row>
     <row r="44" spans="1:15" ht="24.95" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>57</v>
@@ -11986,13 +11988,13 @@
     </row>
     <row r="45" spans="1:15" ht="24.95" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>2943</v>
+        <v>2941</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>2887</v>
+        <v>2885</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>2888</v>
+        <v>2886</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="24.95" customHeight="1">
@@ -12001,7 +12003,7 @@
     </row>
     <row r="47" spans="1:15" ht="24.95" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>2327</v>
+        <v>2325</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>59</v>
@@ -12012,7 +12014,7 @@
     </row>
     <row r="48" spans="1:15" ht="24.95" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>2326</v>
+        <v>2324</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>60</v>
@@ -12023,7 +12025,7 @@
     </row>
     <row r="49" spans="1:15" ht="24.95" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>2324</v>
+        <v>2322</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>61</v>
@@ -12034,7 +12036,7 @@
     </row>
     <row r="50" spans="1:15" ht="24.95" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>2325</v>
+        <v>2323</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>62</v>
@@ -12052,7 +12054,7 @@
         <v>63</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>2774</v>
+        <v>2772</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>64</v>
@@ -12082,33 +12084,33 @@
     </row>
     <row r="55" spans="1:15" ht="24.95" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>2566</v>
+        <v>2564</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>2567</v>
+        <v>2565</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>2573</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="24.95" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>2579</v>
+        <v>2577</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>2580</v>
+        <v>2578</v>
       </c>
       <c r="C56" s="3"/>
       <c r="O56" s="3" t="s">
-        <v>2581</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="24.95" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>3053</v>
+        <v>3051</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>3053</v>
+        <v>3051</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>1154</v>
@@ -12116,10 +12118,10 @@
     </row>
     <row r="58" spans="1:15" ht="24.95" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>3076</v>
+        <v>3074</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>3073</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="24.95" customHeight="1">
@@ -12158,7 +12160,7 @@
         <v>74</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="24.95" customHeight="1">
@@ -12169,7 +12171,7 @@
         <v>76</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="24.95" customHeight="1">
@@ -12213,7 +12215,7 @@
         <v>87</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="24.95" customHeight="1">
@@ -12271,24 +12273,24 @@
     </row>
     <row r="74" spans="1:15" ht="24.95" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="24.95" customHeight="1">
       <c r="A75" s="2" t="s">
+        <v>2878</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>2880</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>2882</v>
-      </c>
       <c r="O75" s="2" t="s">
-        <v>2881</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="24.95" customHeight="1">
@@ -12315,18 +12317,18 @@
     </row>
     <row r="78" spans="1:15" ht="24.95" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>3068</v>
+        <v>3066</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>3071</v>
+        <v>3069</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="24.95" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>3069</v>
+        <v>3067</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>3070</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="24.95" customHeight="1">
@@ -12538,7 +12540,7 @@
         <v>171</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>2540</v>
+        <v>2538</v>
       </c>
       <c r="O99" s="2" t="s">
         <v>172</v>
@@ -12546,24 +12548,24 @@
     </row>
     <row r="100" spans="1:15" ht="24.95" customHeight="1">
       <c r="A100" s="2" t="s">
-        <v>2536</v>
+        <v>2534</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>2539</v>
+        <v>2537</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>2778</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="101" spans="1:15" ht="24.95" customHeight="1">
       <c r="A101" s="2" t="s">
-        <v>2537</v>
+        <v>2535</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>2538</v>
+        <v>2536</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>2779</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="102" spans="1:15" ht="24.95" customHeight="1">
@@ -12615,42 +12617,42 @@
     </row>
     <row r="107" spans="1:15" ht="24.95" customHeight="1">
       <c r="A107" s="2" t="s">
-        <v>3058</v>
+        <v>3056</v>
       </c>
       <c r="O107" s="2" t="s">
-        <v>3063</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="108" spans="1:15" ht="24.95" customHeight="1">
       <c r="A108" s="2" t="s">
-        <v>3059</v>
+        <v>3057</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>3064</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="109" spans="1:15" ht="24.95" customHeight="1">
       <c r="A109" s="2" t="s">
-        <v>3060</v>
+        <v>3058</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>3065</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="110" spans="1:15" ht="24.95" customHeight="1">
       <c r="A110" s="2" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>3066</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="111" spans="1:15" ht="24.95" customHeight="1">
       <c r="A111" s="2" t="s">
-        <v>3062</v>
+        <v>3060</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>3067</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="112" spans="1:15" ht="24.95" customHeight="1">
@@ -12691,13 +12693,13 @@
     </row>
     <row r="116" spans="1:15" ht="24.95" customHeight="1">
       <c r="A116" s="2" t="s">
+        <v>3041</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>3042</v>
+      </c>
+      <c r="O116" s="2" t="s">
         <v>3043</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>3044</v>
-      </c>
-      <c r="O116" s="2" t="s">
-        <v>3045</v>
       </c>
     </row>
     <row r="117" spans="1:15" ht="24.95" customHeight="1">
@@ -12741,7 +12743,7 @@
         <v>204</v>
       </c>
       <c r="O120" s="2" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="121" spans="1:15" ht="24.95" customHeight="1">
@@ -12768,13 +12770,13 @@
     </row>
     <row r="123" spans="1:15" ht="24.95" customHeight="1">
       <c r="A123" s="2" t="s">
-        <v>2475</v>
+        <v>2473</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>211</v>
       </c>
       <c r="O123" s="2" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="124" spans="1:15" ht="24.95" customHeight="1">
@@ -12801,18 +12803,18 @@
     </row>
     <row r="126" spans="1:15" ht="24.95" customHeight="1">
       <c r="A126" s="2" t="s">
-        <v>2588</v>
+        <v>2586</v>
       </c>
       <c r="O126" s="2" t="s">
-        <v>2589</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="127" spans="1:15" ht="24.95" customHeight="1">
       <c r="A127" s="2" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="O127" s="3" t="s">
-        <v>2574</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="128" spans="1:15" ht="24.95" customHeight="1">
@@ -12872,7 +12874,7 @@
     </row>
     <row r="133" spans="1:15" ht="24.95" customHeight="1">
       <c r="A133" s="2" t="s">
-        <v>2527</v>
+        <v>2525</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>233</v>
@@ -12883,10 +12885,10 @@
     </row>
     <row r="134" spans="1:15" ht="24.95" customHeight="1">
       <c r="A134" s="2" t="s">
-        <v>2562</v>
+        <v>2560</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>2563</v>
+        <v>2561</v>
       </c>
       <c r="O134" s="2" t="s">
         <v>235</v>
@@ -12944,7 +12946,7 @@
         <v>248</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="O140" s="3" t="s">
         <v>249</v>
@@ -12955,7 +12957,7 @@
         <v>250</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="O141" s="2" t="s">
         <v>251</v>
@@ -12963,10 +12965,10 @@
     </row>
     <row r="142" spans="1:15" ht="24.95" customHeight="1">
       <c r="A142" s="2" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="O142" s="2" t="s">
         <v>253</v>
@@ -12977,10 +12979,10 @@
         <v>252</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="O143" s="2" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="144" spans="1:15" ht="24.95" customHeight="1">
@@ -12988,7 +12990,7 @@
         <v>254</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="O144" s="2" t="s">
         <v>255</v>
@@ -12999,7 +13001,7 @@
         <v>256</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="O145" s="2" t="s">
         <v>257</v>
@@ -13010,7 +13012,7 @@
         <v>258</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="O146" s="2" t="s">
         <v>259</v>
@@ -13021,7 +13023,7 @@
         <v>260</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="O147" s="2" t="s">
         <v>261</v>
@@ -13032,7 +13034,7 @@
         <v>262</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="O148" s="2" t="s">
         <v>263</v>
@@ -13043,18 +13045,18 @@
     </row>
     <row r="150" spans="1:15" ht="24.95" customHeight="1">
       <c r="A150" s="2" t="s">
+        <v>2937</v>
+      </c>
+      <c r="O150" s="2" t="s">
         <v>2939</v>
-      </c>
-      <c r="O150" s="2" t="s">
-        <v>2941</v>
       </c>
     </row>
     <row r="151" spans="1:15" ht="24.95" customHeight="1">
       <c r="A151" s="2" t="s">
+        <v>2938</v>
+      </c>
+      <c r="O151" s="2" t="s">
         <v>2940</v>
-      </c>
-      <c r="O151" s="2" t="s">
-        <v>2942</v>
       </c>
     </row>
     <row r="152" spans="1:15" ht="24.95" customHeight="1">
@@ -13109,7 +13111,7 @@
         <v>274</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="O157" s="2" t="s">
         <v>275</v>
@@ -13164,7 +13166,7 @@
         <v>287</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="O162" s="2" t="s">
         <v>288</v>
@@ -13172,10 +13174,10 @@
     </row>
     <row r="163" spans="1:15" ht="24.95" customHeight="1">
       <c r="A163" s="2" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="O163" s="2" t="s">
         <v>289</v>
@@ -13186,7 +13188,7 @@
         <v>290</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="O164" s="2" t="s">
         <v>291</v>
@@ -13208,7 +13210,7 @@
         <v>294</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="O166" s="2" t="s">
         <v>295</v>
@@ -13233,7 +13235,7 @@
         <v>299</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>2486</v>
+        <v>2484</v>
       </c>
       <c r="O169" s="2" t="s">
         <v>300</v>
@@ -13244,24 +13246,24 @@
     </row>
     <row r="171" spans="1:15" ht="24.95" customHeight="1">
       <c r="A171" s="2" t="s">
-        <v>2483</v>
+        <v>2481</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>301</v>
       </c>
       <c r="O171" s="2" t="s">
-        <v>2482</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="172" spans="1:15" ht="24.95" customHeight="1">
       <c r="A172" s="2" t="s">
-        <v>2586</v>
+        <v>2584</v>
       </c>
       <c r="B172" s="2" t="s">
+        <v>2583</v>
+      </c>
+      <c r="O172" s="2" t="s">
         <v>2585</v>
-      </c>
-      <c r="O172" s="2" t="s">
-        <v>2587</v>
       </c>
     </row>
     <row r="173" spans="1:15" ht="24.95" customHeight="1">
@@ -13360,7 +13362,7 @@
         <v>327</v>
       </c>
       <c r="O181" s="2" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="182" spans="1:15" ht="24.95" customHeight="1">
@@ -13390,26 +13392,26 @@
     </row>
     <row r="185" spans="1:15" ht="24.95" customHeight="1">
       <c r="A185" s="2" t="s">
-        <v>3050</v>
+        <v>3048</v>
       </c>
       <c r="O185" s="2" t="s">
-        <v>3072</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="186" spans="1:15" ht="24.95" customHeight="1">
       <c r="A186" s="2" t="s">
-        <v>3051</v>
+        <v>3049</v>
       </c>
       <c r="O186" s="2" t="s">
-        <v>3074</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="187" spans="1:15" ht="24.95" customHeight="1">
       <c r="A187" s="2" t="s">
-        <v>3052</v>
+        <v>3050</v>
       </c>
       <c r="O187" s="2" t="s">
-        <v>3075</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="188" spans="1:15" ht="24.95" customHeight="1">
@@ -13417,24 +13419,24 @@
     </row>
     <row r="189" spans="1:15" ht="24.95" customHeight="1">
       <c r="A189" s="2" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>1815</v>
+      </c>
+      <c r="O189" s="2" t="s">
         <v>1816</v>
-      </c>
-      <c r="B189" s="2" t="s">
-        <v>1817</v>
-      </c>
-      <c r="O189" s="2" t="s">
-        <v>1818</v>
       </c>
     </row>
     <row r="190" spans="1:15" ht="24.95" customHeight="1">
       <c r="A190" s="2" t="s">
-        <v>2560</v>
+        <v>2558</v>
       </c>
       <c r="B190" s="2" t="s">
+        <v>2557</v>
+      </c>
+      <c r="O190" s="2" t="s">
         <v>2559</v>
-      </c>
-      <c r="O190" s="2" t="s">
-        <v>2561</v>
       </c>
     </row>
     <row r="191" spans="1:15" ht="24.95" customHeight="1">
@@ -13445,7 +13447,7 @@
         <v>334</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="O192" s="2" t="s">
         <v>335</v>
@@ -13456,7 +13458,7 @@
         <v>336</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="O193" s="2" t="s">
         <v>337</v>
@@ -13467,7 +13469,7 @@
         <v>338</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="O194" s="2" t="s">
         <v>339</v>
@@ -13478,7 +13480,7 @@
         <v>340</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="O195" s="2" t="s">
         <v>341</v>
@@ -13489,32 +13491,32 @@
         <v>342</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="O196" s="2" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="197" spans="1:15" ht="24.95" customHeight="1">
       <c r="A197" s="2" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="O197" s="2" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="198" spans="1:15" ht="24.95" customHeight="1">
       <c r="A198" s="2" t="s">
+        <v>2319</v>
+      </c>
+      <c r="B198" s="2" t="s">
         <v>2321</v>
       </c>
-      <c r="B198" s="2" t="s">
-        <v>2323</v>
-      </c>
       <c r="O198" s="2" t="s">
-        <v>2322</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="199" spans="1:15" ht="24.95" customHeight="1">
@@ -13522,7 +13524,7 @@
         <v>343</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="O199" s="2" t="s">
         <v>344</v>
@@ -13533,7 +13535,7 @@
         <v>345</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="O200" s="2" t="s">
         <v>346</v>
@@ -13544,7 +13546,7 @@
         <v>347</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="O201" s="2" t="s">
         <v>348</v>
@@ -13555,7 +13557,7 @@
         <v>349</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="O202" s="2" t="s">
         <v>350</v>
@@ -13577,7 +13579,7 @@
         <v>353</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="O204" s="2" t="s">
         <v>354</v>
@@ -13588,7 +13590,7 @@
         <v>355</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="O205" s="2" t="s">
         <v>356</v>
@@ -14404,24 +14406,24 @@
     </row>
     <row r="288" spans="1:15" ht="24.95" customHeight="1">
       <c r="A288" s="2" t="s">
-        <v>2502</v>
+        <v>2500</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="O288" s="2" t="s">
-        <v>2503</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="289" spans="1:15" ht="24.95" customHeight="1">
       <c r="A289" s="2" t="s">
-        <v>2505</v>
+        <v>2503</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>2510</v>
+        <v>2508</v>
       </c>
       <c r="O289" s="2" t="s">
-        <v>2506</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="290" spans="1:15" ht="24.95" customHeight="1">
@@ -14598,35 +14600,35 @@
     </row>
     <row r="310" spans="1:15" ht="24.95" customHeight="1">
       <c r="A310" s="2" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="O310" s="2" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="311" spans="1:15" ht="24.95" customHeight="1">
       <c r="A311" s="2" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
       <c r="O311" s="2" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="312" spans="1:15" ht="24.95" customHeight="1">
       <c r="A312" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>1828</v>
+      </c>
+      <c r="O312" s="2" t="s">
         <v>1829</v>
-      </c>
-      <c r="B312" s="2" t="s">
-        <v>1830</v>
-      </c>
-      <c r="O312" s="2" t="s">
-        <v>1831</v>
       </c>
     </row>
     <row r="313" spans="1:15" ht="24.95" customHeight="1">
@@ -14764,7 +14766,7 @@
         <v>628</v>
       </c>
       <c r="O329" s="3" t="s">
-        <v>2794</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="330" spans="1:15" ht="24.95" customHeight="1">
@@ -14835,13 +14837,13 @@
     </row>
     <row r="337" spans="1:15" ht="24.95" customHeight="1">
       <c r="A337" s="2" t="s">
-        <v>2501</v>
+        <v>2499</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="O337" s="2" t="s">
-        <v>2504</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="338" spans="1:15" ht="24.95" customHeight="1">
@@ -14852,7 +14854,7 @@
         <v>648</v>
       </c>
       <c r="O338" s="2" t="s">
-        <v>2937</v>
+        <v>2935</v>
       </c>
     </row>
     <row r="339" spans="1:15" ht="24.95" customHeight="1">
@@ -14945,7 +14947,7 @@
     </row>
     <row r="349" spans="1:15" ht="24.95" customHeight="1">
       <c r="A349" s="2" t="s">
-        <v>2608</v>
+        <v>2606</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>670</v>
@@ -14956,7 +14958,7 @@
     </row>
     <row r="350" spans="1:15" ht="24.95" customHeight="1">
       <c r="A350" s="2" t="s">
-        <v>2607</v>
+        <v>2605</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>672</v>
@@ -15089,7 +15091,7 @@
         <v>702</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="O364" s="2" t="s">
         <v>703</v>
@@ -15100,7 +15102,7 @@
         <v>704</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="O365" s="2" t="s">
         <v>705</v>
@@ -15111,7 +15113,7 @@
         <v>706</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="O366" s="2" t="s">
         <v>707</v>
@@ -15122,7 +15124,7 @@
         <v>708</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="O367" s="2" t="s">
         <v>709</v>
@@ -15133,7 +15135,7 @@
         <v>710</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="O368" s="2" t="s">
         <v>711</v>
@@ -15144,7 +15146,7 @@
         <v>712</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="O369" s="2" t="s">
         <v>713</v>
@@ -15155,7 +15157,7 @@
         <v>714</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="O370" s="2" t="s">
         <v>715</v>
@@ -15166,7 +15168,7 @@
         <v>716</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="O371" s="2" t="s">
         <v>717</v>
@@ -15174,35 +15176,35 @@
     </row>
     <row r="373" spans="1:15" ht="24.95" customHeight="1">
       <c r="A373" s="2" t="s">
-        <v>2312</v>
+        <v>2310</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>2319</v>
+        <v>2317</v>
       </c>
       <c r="O373" s="3" t="s">
-        <v>2317</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="374" spans="1:15" ht="24.95" customHeight="1">
       <c r="A374" s="2" t="s">
-        <v>2313</v>
+        <v>2311</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>2320</v>
+        <v>2318</v>
       </c>
       <c r="O374" s="2" t="s">
-        <v>2316</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="375" spans="1:15" ht="24.95" customHeight="1">
       <c r="A375" s="2" t="s">
-        <v>2314</v>
+        <v>2312</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
       <c r="O375" s="2" t="s">
-        <v>2315</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="376" spans="1:15" ht="24.95" customHeight="1">
@@ -15210,62 +15212,62 @@
     </row>
     <row r="377" spans="1:15" ht="24.95" customHeight="1">
       <c r="A377" s="2" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="B377" s="2" t="s">
+        <v>2620</v>
+      </c>
+      <c r="O377" s="2" t="s">
         <v>2622</v>
-      </c>
-      <c r="O377" s="2" t="s">
-        <v>2624</v>
       </c>
     </row>
     <row r="378" spans="1:15" ht="24.95" customHeight="1">
       <c r="A378" s="2" t="s">
-        <v>2628</v>
+        <v>2626</v>
       </c>
       <c r="B378" s="2" t="s">
+        <v>2619</v>
+      </c>
+      <c r="O378" s="2" t="s">
         <v>2621</v>
-      </c>
-      <c r="O378" s="2" t="s">
-        <v>2623</v>
       </c>
     </row>
     <row r="379" spans="1:15" ht="24.95" customHeight="1">
       <c r="A379" s="2" t="s">
-        <v>2619</v>
+        <v>2617</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>2620</v>
+        <v>2618</v>
       </c>
       <c r="O379" s="2" t="s">
-        <v>2625</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="380" spans="1:15" ht="24.95" customHeight="1">
       <c r="A380" s="2" t="s">
-        <v>2618</v>
+        <v>2616</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>2616</v>
+        <v>2614</v>
       </c>
       <c r="O380" s="2" t="s">
-        <v>2617</v>
+        <v>2615</v>
       </c>
     </row>
     <row r="381" spans="1:15" ht="24.95" customHeight="1">
       <c r="A381" s="2" t="s">
-        <v>2626</v>
+        <v>2624</v>
       </c>
       <c r="O381" s="2" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="382" spans="1:15" ht="24.95" customHeight="1">
       <c r="A382" s="2" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="O382" s="2" t="s">
-        <v>2631</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="383" spans="1:15" ht="24.95" customHeight="1">
@@ -15273,10 +15275,10 @@
     </row>
     <row r="384" spans="1:15" ht="24.95" customHeight="1">
       <c r="A384" s="2" t="s">
-        <v>2305</v>
+        <v>2303</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>2304</v>
+        <v>2302</v>
       </c>
       <c r="O384" s="2" t="s">
         <v>772</v>
@@ -15284,21 +15286,21 @@
     </row>
     <row r="385" spans="1:15" ht="24.95" customHeight="1">
       <c r="A385" s="2" t="s">
-        <v>3056</v>
+        <v>3054</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="O385" s="2" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="386" spans="1:15" ht="24.95" customHeight="1">
       <c r="A386" s="2" t="s">
-        <v>3055</v>
+        <v>3053</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="O386" s="2" t="s">
         <v>781</v>
@@ -15309,37 +15311,37 @@
     </row>
     <row r="388" spans="1:15" ht="24.95" customHeight="1">
       <c r="A388" s="2" t="s">
+        <v>2903</v>
+      </c>
+      <c r="B388" s="2" t="s">
+        <v>2904</v>
+      </c>
+      <c r="O388" s="2" t="s">
         <v>2905</v>
-      </c>
-      <c r="B388" s="2" t="s">
-        <v>2906</v>
-      </c>
-      <c r="O388" s="2" t="s">
-        <v>2907</v>
       </c>
     </row>
     <row r="389" spans="1:15" ht="24.95" customHeight="1">
       <c r="A389" s="2" t="s">
-        <v>3027</v>
+        <v>3025</v>
       </c>
       <c r="O389" s="2" t="s">
-        <v>3028</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="390" spans="1:15" ht="24.95" customHeight="1">
       <c r="A390" s="2" t="s">
+        <v>3038</v>
+      </c>
+      <c r="O390" s="2" t="s">
         <v>3040</v>
-      </c>
-      <c r="O390" s="2" t="s">
-        <v>3042</v>
       </c>
     </row>
     <row r="391" spans="1:15" ht="24.95" customHeight="1">
       <c r="A391" s="2" t="s">
+        <v>3037</v>
+      </c>
+      <c r="O391" s="3" t="s">
         <v>3039</v>
-      </c>
-      <c r="O391" s="3" t="s">
-        <v>3041</v>
       </c>
     </row>
     <row r="392" spans="1:15" ht="24.95" customHeight="1">
@@ -15364,7 +15366,7 @@
         <v>722</v>
       </c>
       <c r="O394" s="2" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="395" spans="1:15" ht="24.95" customHeight="1">
@@ -15372,84 +15374,84 @@
     </row>
     <row r="396" spans="1:15" ht="24.95" customHeight="1">
       <c r="A396" s="2" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="O396" s="2" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="397" spans="1:15" ht="24.95" customHeight="1">
       <c r="A397" s="2" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="O397" s="2" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="398" spans="1:15" ht="24.95" customHeight="1">
       <c r="A398" s="2" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="O398" s="2" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="399" spans="1:15" ht="24.95" customHeight="1">
       <c r="A399" s="2" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="O399" s="2" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="400" spans="1:15" ht="24.95" customHeight="1">
       <c r="A400" s="2" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="O400" s="2" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="401" spans="1:15" ht="24.95" customHeight="1">
       <c r="A401" s="2" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="O401" s="2" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="402" spans="1:15" ht="24.95" customHeight="1">
       <c r="A402" s="2" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="O402" s="2" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="403" spans="1:15" ht="24.95" customHeight="1">
       <c r="A403" s="2" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="O403" s="2" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="404" spans="1:15" ht="24.95" customHeight="1">
@@ -15485,7 +15487,7 @@
         <v>729</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>2427</v>
+        <v>2425</v>
       </c>
       <c r="O408" s="2" t="s">
         <v>730</v>
@@ -15496,18 +15498,18 @@
         <v>731</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>2428</v>
+        <v>2426</v>
       </c>
       <c r="O409" s="2" t="s">
-        <v>2884</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="410" spans="1:15" ht="24.95" customHeight="1">
       <c r="A410" s="2" t="s">
-        <v>2886</v>
+        <v>2884</v>
       </c>
       <c r="O410" s="2" t="s">
-        <v>2885</v>
+        <v>2883</v>
       </c>
     </row>
     <row r="411" spans="1:15" ht="24.95" customHeight="1">
@@ -15584,10 +15586,10 @@
         <v>746</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="O418" s="2" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="419" spans="1:15" ht="24.95" customHeight="1">
@@ -15614,18 +15616,18 @@
     </row>
     <row r="421" spans="1:15" ht="24.95" customHeight="1">
       <c r="A421" s="2" t="s">
+        <v>2421</v>
+      </c>
+      <c r="B421" s="2" t="s">
+        <v>2422</v>
+      </c>
+      <c r="O421" s="2" t="s">
         <v>2423</v>
-      </c>
-      <c r="B421" s="2" t="s">
-        <v>2424</v>
-      </c>
-      <c r="O421" s="2" t="s">
-        <v>2425</v>
       </c>
     </row>
     <row r="422" spans="1:15" ht="24.95" customHeight="1">
       <c r="A422" s="2" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>753</v>
@@ -15658,7 +15660,7 @@
     </row>
     <row r="425" spans="1:15" ht="24.95" customHeight="1">
       <c r="A425" s="2" t="s">
-        <v>2421</v>
+        <v>2419</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>761</v>
@@ -15683,15 +15685,15 @@
     </row>
     <row r="428" spans="1:15" ht="24.95" customHeight="1">
       <c r="A428" s="2" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="O428" s="2" t="s">
-        <v>2328</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="429" spans="1:15" ht="24.95" customHeight="1">
       <c r="A429" s="2" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="O429" s="2" t="s">
         <v>798</v>
@@ -15699,66 +15701,66 @@
     </row>
     <row r="430" spans="1:15" ht="24.95" customHeight="1">
       <c r="A430" s="2" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="O430" s="2" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="431" spans="1:15" ht="24.95" customHeight="1">
       <c r="A431" s="2" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="O431" s="2" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="432" spans="1:15" ht="24.95" customHeight="1">
       <c r="A432" s="2" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="O432" s="2" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="433" spans="1:15" ht="24.95" customHeight="1">
       <c r="A433" s="2" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="O433" s="2" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="434" spans="1:15" ht="24.95" customHeight="1">
       <c r="A434" s="2" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="O434" s="2" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="435" spans="1:15" ht="24.95" customHeight="1">
       <c r="A435" s="2" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="O435" s="2" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="436" spans="1:15" ht="24.95" customHeight="1">
       <c r="A436" s="2" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="O436" s="2" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="437" spans="1:15" ht="24.95" customHeight="1">
       <c r="A437" s="2" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="O437" s="2" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="438" spans="1:15" ht="24.95" customHeight="1">
@@ -15766,10 +15768,10 @@
     </row>
     <row r="439" spans="1:15" ht="24.95" customHeight="1">
       <c r="A439" s="2" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="O439" s="2" t="s">
         <v>798</v>
@@ -15777,18 +15779,18 @@
     </row>
     <row r="440" spans="1:15" ht="24.95" customHeight="1">
       <c r="A440" s="2" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>738</v>
       </c>
       <c r="O440" s="2" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="441" spans="1:15" ht="24.95" customHeight="1">
       <c r="A441" s="2" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>739</v>
@@ -15799,13 +15801,13 @@
     </row>
     <row r="442" spans="1:15" ht="24.95" customHeight="1">
       <c r="A442" s="2" t="s">
+        <v>2299</v>
+      </c>
+      <c r="B442" s="2" t="s">
+        <v>2300</v>
+      </c>
+      <c r="O442" s="2" t="s">
         <v>2301</v>
-      </c>
-      <c r="B442" s="2" t="s">
-        <v>2302</v>
-      </c>
-      <c r="O442" s="2" t="s">
-        <v>2303</v>
       </c>
     </row>
     <row r="443" spans="1:15" ht="24.95" customHeight="1">
@@ -15849,7 +15851,7 @@
     </row>
     <row r="448" spans="1:15" ht="24.95" customHeight="1">
       <c r="A448" s="2" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="O448" s="2" t="s">
         <v>798</v>
@@ -15857,10 +15859,10 @@
     </row>
     <row r="449" spans="1:15" ht="24.95" customHeight="1">
       <c r="A449" s="2" t="s">
+        <v>1632</v>
+      </c>
+      <c r="O449" s="2" t="s">
         <v>1633</v>
-      </c>
-      <c r="O449" s="2" t="s">
-        <v>1635</v>
       </c>
     </row>
     <row r="450" spans="1:15" ht="24.95" customHeight="1">
@@ -15868,18 +15870,18 @@
     </row>
     <row r="451" spans="1:15" ht="24.95" customHeight="1">
       <c r="A451" s="2" t="s">
+        <v>3010</v>
+      </c>
+      <c r="O451" s="2" t="s">
         <v>3012</v>
-      </c>
-      <c r="O451" s="2" t="s">
-        <v>3014</v>
       </c>
     </row>
     <row r="452" spans="1:15" ht="24.95" customHeight="1">
       <c r="A452" s="2" t="s">
+        <v>3011</v>
+      </c>
+      <c r="O452" s="2" t="s">
         <v>3013</v>
-      </c>
-      <c r="O452" s="2" t="s">
-        <v>3015</v>
       </c>
     </row>
     <row r="453" spans="1:15" ht="24.95" customHeight="1">
@@ -15981,18 +15983,18 @@
         <v>1617</v>
       </c>
       <c r="O464" s="2" t="s">
-        <v>1634</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="465" spans="1:15" ht="24.95" customHeight="1">
       <c r="A465" s="2" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="O465" s="2" t="s">
-        <v>1618</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="466" spans="1:15" ht="24.95" customHeight="1">
@@ -16000,21 +16002,21 @@
     </row>
     <row r="467" spans="1:15" ht="24.95" customHeight="1">
       <c r="A467" s="2" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="O467" s="2" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="468" spans="1:15" ht="24.95" customHeight="1">
       <c r="A468" s="2" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="O468" s="2" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="469" spans="1:15" ht="24.95" customHeight="1">
@@ -16022,62 +16024,62 @@
         <v>785</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="O469" s="2" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="470" spans="1:15" ht="24.95" customHeight="1">
       <c r="A470" s="2" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="O470" s="2" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="471" spans="1:15" ht="24.95" customHeight="1">
       <c r="A471" s="2" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="O471" s="2" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="472" spans="1:15" ht="24.95" customHeight="1">
       <c r="A472" s="2" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="O472" s="2" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="473" spans="1:15" ht="24.95" customHeight="1">
       <c r="A473" s="2" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="O473" s="2" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="474" spans="1:15" ht="24.95" customHeight="1">
       <c r="A474" s="2" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="O474" s="2" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="475" spans="1:15" ht="24.95" customHeight="1">
@@ -16085,34 +16087,34 @@
     </row>
     <row r="476" spans="1:15" ht="24.95" customHeight="1">
       <c r="A476" s="2" t="s">
-        <v>2930</v>
+        <v>2928</v>
       </c>
       <c r="O476" s="2" t="s">
-        <v>2935</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="477" spans="1:15" ht="24.95" customHeight="1">
       <c r="A477" s="2" t="s">
+        <v>2929</v>
+      </c>
+      <c r="O477" s="2" t="s">
         <v>2931</v>
-      </c>
-      <c r="O477" s="2" t="s">
-        <v>2933</v>
       </c>
     </row>
     <row r="478" spans="1:15" ht="24.95" customHeight="1">
       <c r="A478" s="2" t="s">
+        <v>2930</v>
+      </c>
+      <c r="O478" s="3" t="s">
         <v>2932</v>
-      </c>
-      <c r="O478" s="3" t="s">
-        <v>2934</v>
       </c>
     </row>
     <row r="479" spans="1:15" ht="24.95" customHeight="1">
       <c r="A479" s="2" t="s">
-        <v>2999</v>
+        <v>2997</v>
       </c>
       <c r="O479" s="3" t="s">
-        <v>3026</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="480" spans="1:15" ht="24.95" customHeight="1">
@@ -16120,26 +16122,26 @@
     </row>
     <row r="481" spans="1:15" ht="24.95" customHeight="1">
       <c r="A481" s="2" t="s">
-        <v>2499</v>
+        <v>2497</v>
       </c>
       <c r="O481" s="3" t="s">
-        <v>2500</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="482" spans="1:15" ht="24.95" customHeight="1">
       <c r="A482" s="2" t="s">
-        <v>2489</v>
+        <v>2487</v>
       </c>
       <c r="O482" s="2" t="s">
-        <v>2487</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="483" spans="1:15" ht="24.95" customHeight="1">
       <c r="A483" s="2" t="s">
-        <v>2490</v>
+        <v>2488</v>
       </c>
       <c r="O483" s="2" t="s">
-        <v>2488</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="484" spans="1:15" ht="24.95" customHeight="1">
@@ -16150,10 +16152,10 @@
         <v>1615</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="O485" s="2" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="486" spans="1:15" ht="24.95" customHeight="1">
@@ -16161,18 +16163,18 @@
         <v>1616</v>
       </c>
       <c r="O486" s="2" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="487" spans="1:15" ht="24.95" customHeight="1">
       <c r="A487" s="2" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="O487" s="2" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="488" spans="1:15" ht="24.95" customHeight="1">
@@ -16180,10 +16182,10 @@
         <v>941</v>
       </c>
       <c r="B488" s="2" t="s">
+        <v>2432</v>
+      </c>
+      <c r="O488" s="2" t="s">
         <v>2434</v>
-      </c>
-      <c r="O488" s="2" t="s">
-        <v>2436</v>
       </c>
     </row>
     <row r="489" spans="1:15" ht="24.95" customHeight="1">
@@ -16191,7 +16193,7 @@
         <v>942</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
       <c r="O489" s="2" t="s">
         <v>943</v>
@@ -16202,10 +16204,10 @@
         <v>944</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="O490" s="2" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="491" spans="1:15" ht="24.95" customHeight="1">
@@ -16224,7 +16226,7 @@
         <v>972</v>
       </c>
       <c r="O493" s="2" t="s">
-        <v>2878</v>
+        <v>2876</v>
       </c>
     </row>
     <row r="494" spans="1:15" ht="24.95" customHeight="1">
@@ -16248,7 +16250,7 @@
         <v>977</v>
       </c>
       <c r="O496" s="2" t="s">
-        <v>2533</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="497" spans="1:15" ht="24.95" customHeight="1">
@@ -16270,18 +16272,18 @@
         <v>800</v>
       </c>
       <c r="O499" s="2" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="500" spans="1:15" ht="24.95" customHeight="1">
       <c r="A500" s="2" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="O500" s="2" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="501" spans="1:15" ht="24.95" customHeight="1">
@@ -16297,24 +16299,24 @@
     </row>
     <row r="502" spans="1:15" ht="24.95" customHeight="1">
       <c r="A502" s="2" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>804</v>
       </c>
       <c r="O502" s="3" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="504" spans="1:15" ht="24.95" customHeight="1">
       <c r="A504" s="2" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B504" s="2" t="s">
+        <v>2907</v>
+      </c>
+      <c r="O504" s="3" t="s">
         <v>2908</v>
-      </c>
-      <c r="B504" s="2" t="s">
-        <v>2909</v>
-      </c>
-      <c r="O504" s="3" t="s">
-        <v>2910</v>
       </c>
     </row>
     <row r="505" spans="1:15" ht="24.95" customHeight="1">
@@ -16402,10 +16404,10 @@
     </row>
     <row r="514" spans="1:15" ht="24.95" customHeight="1">
       <c r="A514" s="2" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="O514" s="2" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="515" spans="1:15" ht="24.95" customHeight="1">
@@ -16418,10 +16420,10 @@
     </row>
     <row r="516" spans="1:15" ht="24.95" customHeight="1">
       <c r="A516" s="2" t="s">
-        <v>2311</v>
+        <v>2309</v>
       </c>
       <c r="O516" s="2" t="s">
-        <v>2485</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="517" spans="1:15" ht="24.95" customHeight="1">
@@ -16432,7 +16434,7 @@
         <v>828</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="O518" s="2" t="s">
         <v>829</v>
@@ -16482,18 +16484,18 @@
         <v>837</v>
       </c>
       <c r="O523" s="2" t="s">
-        <v>2484</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="524" spans="1:15" ht="24.95" customHeight="1">
       <c r="A524" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B524" s="2" t="s">
         <v>1682</v>
       </c>
-      <c r="B524" s="2" t="s">
-        <v>1684</v>
-      </c>
       <c r="O524" s="2" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="525" spans="1:15" ht="24.95" customHeight="1">
@@ -16606,10 +16608,10 @@
         <v>864</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="O536" s="2" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="537" spans="1:15" ht="24.95" customHeight="1">
@@ -16719,7 +16721,7 @@
     </row>
     <row r="548" spans="1:15" ht="24.95" customHeight="1">
       <c r="A548" s="2" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>892</v>
@@ -16730,10 +16732,10 @@
     </row>
     <row r="549" spans="1:15" ht="24.95" customHeight="1">
       <c r="A549" s="2" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="O549" s="2" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="550" spans="1:15" ht="24.95" customHeight="1">
@@ -16774,7 +16776,7 @@
         <v>903</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
       <c r="O553" s="2" t="s">
         <v>904</v>
@@ -16840,7 +16842,7 @@
     </row>
     <row r="560" spans="1:15" ht="24.95" customHeight="1">
       <c r="A560" s="2" t="s">
-        <v>2306</v>
+        <v>2304</v>
       </c>
       <c r="B560" s="2" t="s">
         <v>936</v>
@@ -16857,7 +16859,7 @@
         <v>921</v>
       </c>
       <c r="O561" s="2" t="s">
-        <v>2307</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="562" spans="1:15" ht="24.95" customHeight="1">
@@ -16884,7 +16886,7 @@
     </row>
     <row r="564" spans="1:15" ht="24.95" customHeight="1">
       <c r="A564" s="2" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>929</v>
@@ -16898,7 +16900,7 @@
         <v>931</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>2308</v>
+        <v>2306</v>
       </c>
       <c r="O565" s="2" t="s">
         <v>932</v>
@@ -16931,7 +16933,7 @@
         <v>939</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>2309</v>
+        <v>2307</v>
       </c>
       <c r="O568" s="2" t="s">
         <v>940</v>
@@ -16978,7 +16980,7 @@
     </row>
     <row r="574" spans="1:15" ht="24.95" customHeight="1">
       <c r="A574" s="2" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="B574" s="2" t="s">
         <v>954</v>
@@ -16989,7 +16991,7 @@
     </row>
     <row r="575" spans="1:15" ht="24.95" customHeight="1">
       <c r="A575" s="2" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="B575" s="2" t="s">
         <v>956</v>
@@ -17318,7 +17320,7 @@
         <v>1047</v>
       </c>
       <c r="O608" s="2" t="s">
-        <v>2310</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="609" spans="1:15" ht="24.95" customHeight="1">
@@ -17384,7 +17386,7 @@
         <v>1062</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="O615" s="2" t="s">
         <v>1063</v>
@@ -17395,7 +17397,7 @@
         <v>1064</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="O616" s="2" t="s">
         <v>1065</v>
@@ -17406,7 +17408,7 @@
         <v>1066</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
       <c r="O617" s="2" t="s">
         <v>1067</v>
@@ -17417,7 +17419,7 @@
         <v>1068</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
       <c r="O618" s="2" t="s">
         <v>1069</v>
@@ -17428,21 +17430,21 @@
         <v>1070</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="O619" s="2" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="620" spans="1:15" ht="24.95" customHeight="1">
       <c r="A620" s="2" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
       <c r="O620" s="2" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="621" spans="1:15" ht="24.95" customHeight="1">
@@ -17450,10 +17452,10 @@
         <v>1071</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="O621" s="2" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="622" spans="1:15" ht="24.95" customHeight="1">
@@ -17461,10 +17463,10 @@
         <v>1072</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="O622" s="2" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="623" spans="1:15" ht="24.95" customHeight="1">
@@ -17472,46 +17474,46 @@
     </row>
     <row r="624" spans="1:15" ht="24.95" customHeight="1">
       <c r="A624" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="O624" s="2" t="s">
-        <v>1857</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="625" spans="1:15" ht="24.95" customHeight="1">
       <c r="A625" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B625" s="2" t="s">
         <v>1851</v>
       </c>
-      <c r="B625" s="2" t="s">
+      <c r="O625" s="2" t="s">
         <v>1853</v>
-      </c>
-      <c r="O625" s="2" t="s">
-        <v>1855</v>
       </c>
     </row>
     <row r="626" spans="1:15" ht="24.95" customHeight="1">
       <c r="A626" s="2" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B626" s="2" t="s">
         <v>1852</v>
       </c>
-      <c r="B626" s="2" t="s">
+      <c r="O626" s="2" t="s">
         <v>1854</v>
-      </c>
-      <c r="O626" s="2" t="s">
-        <v>1856</v>
       </c>
     </row>
     <row r="627" spans="1:15" ht="24.95" customHeight="1">
       <c r="A627" s="2" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B627" s="2" t="s">
+        <v>1857</v>
+      </c>
+      <c r="O627" s="2" t="s">
         <v>1858</v>
-      </c>
-      <c r="B627" s="2" t="s">
-        <v>1859</v>
-      </c>
-      <c r="O627" s="2" t="s">
-        <v>1860</v>
       </c>
     </row>
     <row r="628" spans="1:15" ht="24.95" customHeight="1">
@@ -17525,7 +17527,7 @@
         <v>1074</v>
       </c>
       <c r="O629" s="2" t="s">
-        <v>3057</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="630" spans="1:15" ht="24.95" customHeight="1">
@@ -17762,7 +17764,7 @@
     </row>
     <row r="654" spans="1:15" ht="24.95" customHeight="1">
       <c r="A654" s="2" t="s">
-        <v>2481</v>
+        <v>2479</v>
       </c>
       <c r="B654" s="2" t="s">
         <v>602</v>
@@ -17820,18 +17822,18 @@
     </row>
     <row r="661" spans="1:15" ht="24.95" customHeight="1">
       <c r="A661" s="2" t="s">
+        <v>2544</v>
+      </c>
+      <c r="O661" s="2" t="s">
         <v>2546</v>
-      </c>
-      <c r="O661" s="2" t="s">
-        <v>2548</v>
       </c>
     </row>
     <row r="662" spans="1:15" ht="24.95" customHeight="1">
       <c r="A662" s="2" t="s">
+        <v>2545</v>
+      </c>
+      <c r="O662" s="2" t="s">
         <v>2547</v>
-      </c>
-      <c r="O662" s="2" t="s">
-        <v>2549</v>
       </c>
     </row>
     <row r="663" spans="1:15" ht="24.95" customHeight="1">
@@ -17897,7 +17899,7 @@
         <v>1152</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="O669" s="2" t="s">
         <v>1153</v>
@@ -17905,7 +17907,7 @@
     </row>
     <row r="670" spans="1:15" ht="24.95" customHeight="1">
       <c r="A670" s="2" t="s">
-        <v>3054</v>
+        <v>3052</v>
       </c>
       <c r="B670" s="2" t="s">
         <v>1155</v>
@@ -17933,7 +17935,7 @@
         <v>1162</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="O673" s="2" t="s">
         <v>1163</v>
@@ -17958,18 +17960,18 @@
     </row>
     <row r="677" spans="1:15" ht="24.95" customHeight="1">
       <c r="A677" s="2" t="s">
+        <v>3014</v>
+      </c>
+      <c r="O677" s="2" t="s">
         <v>3016</v>
-      </c>
-      <c r="O677" s="2" t="s">
-        <v>3018</v>
       </c>
     </row>
     <row r="678" spans="1:15" ht="24.95" customHeight="1">
       <c r="A678" s="2" t="s">
+        <v>3015</v>
+      </c>
+      <c r="O678" s="2" t="s">
         <v>3017</v>
-      </c>
-      <c r="O678" s="2" t="s">
-        <v>3019</v>
       </c>
     </row>
     <row r="679" spans="1:15" ht="24.95" customHeight="1">
@@ -18146,10 +18148,10 @@
     </row>
     <row r="700" spans="1:15" ht="33">
       <c r="A700" s="2" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
       <c r="O700" s="3" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="701" spans="1:15" ht="24.95" customHeight="1">
@@ -18160,7 +18162,7 @@
         <v>1208</v>
       </c>
       <c r="O702" s="2" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="703" spans="1:15" ht="24.95" customHeight="1">
@@ -18235,7 +18237,7 @@
         <v>1224</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="O712" s="2" t="s">
         <v>1225</v>
@@ -18260,7 +18262,7 @@
         <v>1227</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="O716" s="2" t="s">
         <v>1228</v>
@@ -21459,13 +21461,13 @@
     </row>
     <row r="2" spans="1:17" ht="24.95" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>2513</v>
+        <v>2511</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1253</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>3036</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="54">
@@ -21473,10 +21475,10 @@
         <v>1254</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3037</v>
+        <v>3035</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>2776</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="24.95" customHeight="1">
@@ -21531,7 +21533,7 @@
         <v>1268</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>2790</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="54">
@@ -21539,10 +21541,10 @@
         <v>1269</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>3038</v>
+        <v>3036</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>2791</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="36">
@@ -21553,7 +21555,7 @@
         <v>1271</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>2775</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="409.5">
@@ -21561,43 +21563,43 @@
         <v>1272</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2793</v>
+        <v>2791</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>2792</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="45" customHeight="1"/>
     <row r="13" spans="1:17" ht="45" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>2508</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="45" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>2575</v>
+        <v>2573</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>2576</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="45" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>2511</v>
+        <v>2509</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="45" customHeight="1">
       <c r="A16" s="1" t="s">
+        <v>2510</v>
+      </c>
+      <c r="O16" s="1" t="s">
         <v>2512</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>2514</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="24.95" customHeight="1">
@@ -21734,101 +21736,101 @@
     </row>
     <row r="34" spans="1:15" ht="18">
       <c r="A34" s="1" t="s">
-        <v>2590</v>
+        <v>2588</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>2602</v>
+        <v>2600</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>2601</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="24.95" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>2591</v>
+        <v>2589</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>2603</v>
+        <v>2601</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>2600</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="24.95" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>2592</v>
+        <v>2590</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>2604</v>
+        <v>2602</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>2599</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="24.95" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>2593</v>
+        <v>2591</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>2605</v>
+        <v>2603</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>2598</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="36">
       <c r="A38" s="1" t="s">
-        <v>2594</v>
+        <v>2592</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>2606</v>
+        <v>2604</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>2597</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="24.95" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>2595</v>
+        <v>2593</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>2596</v>
+        <v>2594</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>2422</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="24.95" customHeight="1">
       <c r="A41" s="1" t="s">
+        <v>2514</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>2516</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>2518</v>
-      </c>
       <c r="O41" s="1" t="s">
-        <v>2517</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="24.95" customHeight="1">
       <c r="A42" s="1" t="s">
+        <v>2580</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>2581</v>
+      </c>
+      <c r="O42" s="1" t="s">
         <v>2582</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>2583</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>2584</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="24.95" customHeight="1">
       <c r="A44" s="1" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>1728</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>1730</v>
-      </c>
       <c r="O44" s="1" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="24.95" customHeight="1">
@@ -21869,7 +21871,7 @@
         <v>1316</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
       <c r="O49" s="1" t="s">
         <v>1317</v>
@@ -21877,24 +21879,24 @@
     </row>
     <row r="50" spans="1:15" ht="24.95" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="24.95" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>2528</v>
+        <v>2526</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>2532</v>
+        <v>2530</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>2531</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="24.95" customHeight="1">
@@ -21910,263 +21912,263 @@
     </row>
     <row r="53" spans="1:15" ht="24.95" customHeight="1">
       <c r="A53" s="1" t="s">
+        <v>2921</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>2923</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>2925</v>
-      </c>
       <c r="O53" s="1" t="s">
-        <v>2922</v>
+        <v>2920</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="24.95" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>2926</v>
+        <v>2924</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>2927</v>
+        <v>2925</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>3009</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="24.95" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>2924</v>
+        <v>2922</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>2925</v>
+        <v>2923</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>2929</v>
+        <v>2927</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="24.95" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>2777</v>
+        <v>2775</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>2780</v>
+        <v>2778</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>2781</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="24.95" customHeight="1">
       <c r="A58" s="1" t="s">
+        <v>2548</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>2549</v>
+      </c>
+      <c r="O58" s="1" t="s">
         <v>2550</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>2551</v>
-      </c>
-      <c r="O58" s="1" t="s">
-        <v>2552</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="24.95" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>2555</v>
+        <v>2553</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>2553</v>
+        <v>2551</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>2554</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="24.95" customHeight="1">
       <c r="A60" s="1" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>2555</v>
+      </c>
+      <c r="O60" s="1" t="s">
         <v>2556</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>2557</v>
-      </c>
-      <c r="O60" s="1" t="s">
-        <v>2558</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="24.95" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>2944</v>
+        <v>2942</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="24.95" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>2945</v>
+        <v>2943</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>2973</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="24.95" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>2946</v>
+        <v>2944</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="24.95" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>2947</v>
+        <v>2945</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>2971</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="24.95" customHeight="1">
       <c r="A66" s="1" t="s">
-        <v>2948</v>
+        <v>2946</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>2970</v>
+        <v>2968</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="24.95" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>2949</v>
+        <v>2947</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>2969</v>
+        <v>2967</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="24.95" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>2950</v>
+        <v>2948</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>2968</v>
+        <v>2966</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="24.95" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>3029</v>
+        <v>3027</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>3030</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="24.95" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>2951</v>
+        <v>2949</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>2967</v>
+        <v>2965</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="24.95" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>2952</v>
+        <v>2950</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>2966</v>
+        <v>2964</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="24.95" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>2953</v>
+        <v>2951</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>2965</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="24.95" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>2954</v>
+        <v>2952</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>2981</v>
+        <v>2979</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="24.95" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>2955</v>
+        <v>2953</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>2980</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="24.95" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>2956</v>
+        <v>2954</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>2964</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="24.95" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>2957</v>
+        <v>2955</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>2979</v>
+        <v>2977</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="24.95" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>2958</v>
+        <v>2956</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>2978</v>
+        <v>2976</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="24.95" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>2959</v>
+        <v>2957</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>2963</v>
+        <v>2961</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="24.95" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>2960</v>
+        <v>2958</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>2977</v>
+        <v>2975</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="24.95" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>2961</v>
+        <v>2959</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>2975</v>
+        <v>2973</v>
       </c>
     </row>
     <row r="81" spans="1:15" ht="24.95" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>2962</v>
+        <v>2960</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="24.95" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>2982</v>
+        <v>2980</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
     </row>
     <row r="83" spans="1:15" ht="24.95" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>2984</v>
+        <v>2982</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>2985</v>
+        <v>2983</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="24.95" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>2986</v>
+        <v>2984</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
     </row>
   </sheetData>
@@ -22258,7 +22260,7 @@
         <v>1322</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>3031</v>
+        <v>3029</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="16.5">
@@ -22269,7 +22271,7 @@
         <v>1324</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>3032</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="16.5">
@@ -22280,7 +22282,7 @@
         <v>1326</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>3033</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="16.5">
@@ -22291,7 +22293,7 @@
         <v>1328</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="16.5">
@@ -22302,7 +22304,7 @@
         <v>1330</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>3034</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="16.5">
@@ -22313,7 +22315,7 @@
         <v>1332</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>3035</v>
+        <v>3033</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="16.5">
@@ -22574,7 +22576,7 @@
         <v>1402</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>1403</v>
@@ -22651,7 +22653,7 @@
         <v>1422</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="O38" s="7" t="s">
         <v>1423</v>
@@ -22670,24 +22672,24 @@
     </row>
     <row r="40" spans="1:15" ht="18" customHeight="1">
       <c r="A40" s="7" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="O40" s="7" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="18" customHeight="1">
       <c r="A41" s="7" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>1804</v>
+      </c>
+      <c r="O41" s="7" t="s">
         <v>1805</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>1806</v>
-      </c>
-      <c r="O41" s="7" t="s">
-        <v>1807</v>
       </c>
     </row>
   </sheetData>
@@ -22796,7 +22798,7 @@
     </row>
     <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>2523</v>
+        <v>2521</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>1433</v>
@@ -22832,21 +22834,21 @@
         <v>1441</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>2877</v>
+        <v>2875</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>2876</v>
+        <v>2874</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>1451</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1">
@@ -23063,7 +23065,7 @@
     </row>
     <row r="28" spans="1:15" ht="20.100000000000001" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>2789</v>
+        <v>2787</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>1500</v>
@@ -23074,7 +23076,7 @@
     </row>
     <row r="29" spans="1:15" ht="20.100000000000001" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>3024</v>
+        <v>3022</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>1502</v>
@@ -23107,7 +23109,7 @@
     </row>
     <row r="32" spans="1:15" ht="20.100000000000001" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>2522</v>
+        <v>2520</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>1510</v>
@@ -23421,7 +23423,7 @@
         <v>1446</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>2478</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="20.100000000000001" customHeight="1">
@@ -23509,7 +23511,7 @@
         <v>1446</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>2479</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="69" spans="1:17" ht="20.100000000000001" customHeight="1">
@@ -23696,79 +23698,79 @@
     </row>
     <row r="85" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A85" s="2" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>1714</v>
+      </c>
+      <c r="O85" s="2" t="s">
         <v>1715</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>1716</v>
-      </c>
-      <c r="O85" s="2" t="s">
-        <v>1717</v>
       </c>
     </row>
     <row r="86" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A86" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="O86" s="2" t="s">
         <v>1825</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>1826</v>
-      </c>
-      <c r="O86" s="2" t="s">
-        <v>1827</v>
       </c>
     </row>
     <row r="87" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A87" s="2" t="s">
+        <v>2296</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>2298</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>2300</v>
-      </c>
       <c r="O87" s="2" t="s">
-        <v>2299</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="88" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>2497</v>
+        <v>2495</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>2492</v>
+        <v>2490</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>2498</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="89" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A89" s="2" t="s">
+        <v>2517</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>2518</v>
+      </c>
+      <c r="O89" s="2" t="s">
         <v>2519</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>2520</v>
-      </c>
-      <c r="O89" s="2" t="s">
-        <v>2521</v>
       </c>
     </row>
     <row r="90" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A90" s="2" t="s">
+        <v>2607</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>2608</v>
+      </c>
+      <c r="O90" s="2" t="s">
         <v>2609</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>2610</v>
-      </c>
-      <c r="O90" s="2" t="s">
-        <v>2611</v>
       </c>
     </row>
     <row r="91" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A91" s="2" t="s">
+        <v>2914</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>2915</v>
+      </c>
+      <c r="O91" s="2" t="s">
         <v>2916</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>2917</v>
-      </c>
-      <c r="O91" s="2" t="s">
-        <v>2918</v>
       </c>
     </row>
   </sheetData>
@@ -23791,2931 +23793,2931 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15" customHeight="1">
       <c r="B1" s="7" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>1868</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>1869</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>1870</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>1871</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>1872</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>1873</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>1874</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>1875</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>1876</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>1877</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>1878</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>1879</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>1880</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>1881</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>1882</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>1883</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24.95" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>2638</v>
+        <v>2636</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="24.95" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="24.95" customHeight="1"/>
     <row r="5" spans="1:17">
       <c r="A5" s="7" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="7" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="7" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>2639</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="7" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="7" t="s">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="7" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="7" t="s">
-        <v>2995</v>
+        <v>2993</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="O13" s="7" t="s">
         <v>2994</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>2996</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="7" t="s">
-        <v>2997</v>
+        <v>2995</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="7" t="s">
-        <v>2998</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="7" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="7" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="7" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>2640</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="7" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="7" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>2769</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="7" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="7" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="7" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>2641</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="7" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="7" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="O29" s="7" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="7" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="O30" s="7" t="s">
-        <v>2644</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="7" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
       <c r="O31" s="7" t="s">
-        <v>2645</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="7" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="7" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="O34" s="7" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="7" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="O35" s="7" t="s">
-        <v>2646</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="37" spans="1:15">
       <c r="A37" s="7" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="O37" s="7" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="7" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="O38" s="7" t="s">
-        <v>2637</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="39" spans="1:15">
       <c r="A39" s="7" t="s">
+        <v>1819</v>
+      </c>
+      <c r="O39" s="7" t="s">
         <v>1821</v>
-      </c>
-      <c r="O39" s="7" t="s">
-        <v>1823</v>
       </c>
     </row>
     <row r="41" spans="1:15">
       <c r="A41" s="7" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="O41" s="7" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="42" spans="1:15">
       <c r="A42" s="7" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="O42" s="7" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="43" spans="1:15">
       <c r="A43" s="7" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="O43" s="7" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="45" spans="1:15">
       <c r="A45" s="7" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="O45" s="7" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="46" spans="1:15">
       <c r="A46" s="7" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="O46" s="7" t="s">
-        <v>2647</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="47" spans="1:15">
       <c r="A47" s="7" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="O47" s="7" t="s">
-        <v>2648</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="49" spans="1:15">
       <c r="A49" s="7" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
       <c r="O49" s="7" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="50" spans="1:15">
       <c r="A50" s="7" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
       <c r="O50" s="7" t="s">
-        <v>2649</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="51" spans="1:15">
       <c r="A51" s="7" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
       <c r="O51" s="7" t="s">
-        <v>2768</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="53" spans="1:15">
       <c r="A53" s="7" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
       <c r="O53" s="7" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="54" spans="1:15">
       <c r="A54" s="7" t="s">
-        <v>1932</v>
+        <v>1930</v>
       </c>
       <c r="O54" s="7" t="s">
-        <v>2650</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="55" spans="1:15">
       <c r="A55" s="7" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="O55" s="7" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="57" spans="1:15">
       <c r="A57" s="7" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="O57" s="7" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="58" spans="1:15">
       <c r="A58" s="7" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="O58" s="7" t="s">
-        <v>2651</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="59" spans="1:15">
       <c r="A59" s="7" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="O59" s="7" t="s">
-        <v>2652</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="61" spans="1:15">
       <c r="A61" s="7" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="O61" s="7" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="62" spans="1:15">
       <c r="A62" s="7" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="O62" s="7" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="63" spans="1:15">
       <c r="A63" s="7" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
       <c r="O63" s="7" t="s">
-        <v>2653</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="65" spans="1:15">
       <c r="A65" s="7" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="O65" s="7" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="7" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="O66" s="7" t="s">
-        <v>2636</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="67" spans="1:15">
       <c r="A67" s="7" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="O67" s="7" t="s">
-        <v>2654</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="69" spans="1:15">
       <c r="A69" s="7" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="O69" s="7" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="70" spans="1:15">
       <c r="A70" s="7" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="O70" s="7" t="s">
-        <v>2655</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="71" spans="1:15">
       <c r="A71" s="7" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
       <c r="O71" s="7" t="s">
-        <v>2656</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="73" spans="1:15">
       <c r="A73" s="7" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>2657</v>
+        <v>2655</v>
       </c>
       <c r="O73" s="7" t="s">
-        <v>2658</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="74" spans="1:15">
       <c r="A74" s="7" t="s">
+        <v>1950</v>
+      </c>
+      <c r="O74" s="7" t="s">
         <v>1952</v>
-      </c>
-      <c r="O74" s="7" t="s">
-        <v>1954</v>
       </c>
     </row>
     <row r="75" spans="1:15">
       <c r="A75" s="7" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="O75" s="7" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="77" spans="1:15">
       <c r="A77" s="7" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="O77" s="7" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="78" spans="1:15">
       <c r="A78" s="7" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="O78" s="7" t="s">
-        <v>2659</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="79" spans="1:15">
       <c r="A79" s="7" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="O79" s="7" t="s">
-        <v>2660</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="81" spans="1:15">
       <c r="A81" s="7" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="O81" s="7" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="82" spans="1:15">
       <c r="A82" s="7" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="O82" s="7" t="s">
-        <v>2661</v>
+        <v>2659</v>
       </c>
     </row>
     <row r="83" spans="1:15">
       <c r="A83" s="7" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="O83" s="7" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="85" spans="1:15">
       <c r="A85" s="7" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="O85" s="7" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="86" spans="1:15">
       <c r="A86" s="7" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="O86" s="7" t="s">
-        <v>2662</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="87" spans="1:15">
       <c r="A87" s="7" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="O87" s="7" t="s">
-        <v>2663</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="89" spans="1:15">
       <c r="A89" s="7" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="O89" s="7" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="90" spans="1:15">
       <c r="A90" s="7" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="O90" s="7" t="s">
-        <v>2664</v>
+        <v>2662</v>
       </c>
     </row>
     <row r="91" spans="1:15">
       <c r="A91" s="7" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="O91" s="7" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="93" spans="1:15">
       <c r="A93" s="7" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>1971</v>
+      </c>
+      <c r="O93" s="7" t="s">
         <v>1972</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>1973</v>
-      </c>
-      <c r="O93" s="7" t="s">
-        <v>1974</v>
       </c>
     </row>
     <row r="94" spans="1:15">
       <c r="A94" s="7" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="O94" s="7" t="s">
-        <v>2666</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="95" spans="1:15">
       <c r="A95" s="7" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="O95" s="7" t="s">
-        <v>2667</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="97" spans="1:15">
       <c r="A97" s="7" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>2668</v>
+        <v>2666</v>
       </c>
       <c r="O97" s="7" t="s">
-        <v>2669</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="98" spans="1:15">
       <c r="A98" s="7" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="O98" s="7" t="s">
-        <v>2635</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="99" spans="1:15">
       <c r="A99" s="7" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="O99" s="7" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="101" spans="1:15">
       <c r="A101" s="7" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
       <c r="O101" s="7" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="102" spans="1:15">
       <c r="A102" s="7" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="O102" s="7" t="s">
-        <v>2671</v>
+        <v>2669</v>
       </c>
     </row>
     <row r="103" spans="1:15">
       <c r="A103" s="7" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="O103" s="7" t="s">
-        <v>2672</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="105" spans="1:15">
       <c r="A105" s="7" t="s">
-        <v>2612</v>
+        <v>2610</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>2612</v>
+        <v>2610</v>
       </c>
       <c r="O105" s="7" t="s">
-        <v>2613</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="106" spans="1:15">
       <c r="A106" s="7" t="s">
-        <v>2614</v>
+        <v>2612</v>
       </c>
       <c r="O106" s="7" t="s">
-        <v>2633</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="107" spans="1:15">
       <c r="A107" s="7" t="s">
-        <v>2615</v>
+        <v>2613</v>
       </c>
       <c r="O107" s="7" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="109" spans="1:15">
       <c r="A109" s="7" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="O109" s="7" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="110" spans="1:15">
       <c r="A110" s="7" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="O110" s="7" t="s">
-        <v>2673</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="111" spans="1:15">
       <c r="A111" s="7" t="s">
+        <v>1710</v>
+      </c>
+      <c r="O111" s="7" t="s">
         <v>1712</v>
-      </c>
-      <c r="O111" s="7" t="s">
-        <v>1714</v>
       </c>
     </row>
     <row r="113" spans="1:15">
       <c r="A113" s="7" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="O113" s="7" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="114" spans="1:15">
       <c r="A114" s="7" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="O114" s="7" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="115" spans="1:15">
       <c r="A115" s="7" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="O115" s="7" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="117" spans="1:15">
       <c r="A117" s="7" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="O117" s="7" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="118" spans="1:15">
       <c r="A118" s="7" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="O118" s="7" t="s">
-        <v>2674</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="119" spans="1:15">
       <c r="A119" s="7" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="O119" s="7" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="121" spans="1:15">
       <c r="A121" s="7" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="O121" s="7" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="122" spans="1:15">
       <c r="A122" s="7" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="O122" s="7" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="123" spans="1:15">
       <c r="A123" s="7" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="O123" s="7" t="s">
-        <v>2676</v>
+        <v>2674</v>
       </c>
     </row>
     <row r="125" spans="1:15">
       <c r="A125" s="7" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="O125" s="7" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="126" spans="1:15">
       <c r="A126" s="7" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="O126" s="7" t="s">
-        <v>2677</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="127" spans="1:15">
       <c r="A127" s="7" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="O127" s="7" t="s">
-        <v>2678</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="129" spans="1:15">
       <c r="A129" s="7" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="O129" s="7" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="130" spans="1:15">
       <c r="A130" s="7" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="O130" s="7" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="131" spans="1:15">
       <c r="A131" s="7" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="O131" s="7" t="s">
-        <v>2680</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="133" spans="1:15">
       <c r="A133" s="7" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="O133" s="7" t="s">
-        <v>2681</v>
+        <v>2679</v>
       </c>
     </row>
     <row r="134" spans="1:15">
       <c r="A134" s="7" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="O134" s="7" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="135" spans="1:15">
       <c r="A135" s="7" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="O135" s="7" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="137" spans="1:15">
       <c r="A137" s="7" t="s">
-        <v>2913</v>
+        <v>2911</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>2912</v>
+        <v>2910</v>
       </c>
       <c r="O137" s="7" t="s">
-        <v>2911</v>
+        <v>2909</v>
       </c>
     </row>
     <row r="138" spans="1:15">
       <c r="A138" s="7" t="s">
-        <v>2914</v>
+        <v>2912</v>
       </c>
       <c r="O138" s="7" t="s">
-        <v>2919</v>
+        <v>2917</v>
       </c>
     </row>
     <row r="139" spans="1:15">
       <c r="A139" s="7" t="s">
-        <v>2915</v>
+        <v>2913</v>
       </c>
       <c r="O139" s="7" t="s">
-        <v>2920</v>
+        <v>2918</v>
       </c>
     </row>
     <row r="141" spans="1:15">
       <c r="A141" s="7" t="s">
-        <v>2492</v>
+        <v>2490</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>2491</v>
+        <v>2489</v>
       </c>
       <c r="O141" s="7" t="s">
-        <v>2495</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="142" spans="1:15">
       <c r="A142" s="7" t="s">
-        <v>2493</v>
+        <v>2491</v>
       </c>
       <c r="O142" s="7" t="s">
-        <v>2496</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="143" spans="1:15">
       <c r="A143" s="7" t="s">
-        <v>2494</v>
+        <v>2492</v>
       </c>
       <c r="O143" s="7" t="s">
-        <v>2682</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="145" spans="1:15">
       <c r="A145" s="7" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="O145" s="7" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="146" spans="1:15">
       <c r="A146" s="7" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="O146" s="7" t="s">
-        <v>2683</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="147" spans="1:15">
       <c r="A147" s="7" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="O147" s="7" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="149" spans="1:15">
       <c r="A149" s="7" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="O149" s="7" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="150" spans="1:15">
       <c r="A150" s="7" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="O150" s="7" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="151" spans="1:15">
       <c r="A151" s="7" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="O151" s="7" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="153" spans="1:15">
       <c r="A153" s="7" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="O153" s="7" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="154" spans="1:15">
       <c r="A154" s="7" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="O154" s="7" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="155" spans="1:15">
       <c r="A155" s="7" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="O155" s="7" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="157" spans="1:15">
       <c r="A157" s="7" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="O157" s="7" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="158" spans="1:15">
       <c r="A158" s="7" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="O158" s="7" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="159" spans="1:15">
       <c r="A159" s="7" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="O159" s="7" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="161" spans="1:15">
       <c r="A161" s="7" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="O161" s="7" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="162" spans="1:15">
       <c r="A162" s="7" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="O162" s="7" t="s">
-        <v>2685</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="163" spans="1:15">
       <c r="A163" s="7" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="O163" s="7" t="s">
-        <v>2685</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="165" spans="1:15">
       <c r="A165" s="7" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="O165" s="7" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="166" spans="1:15">
       <c r="A166" s="7" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="O166" s="7" t="s">
-        <v>2687</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="167" spans="1:15">
       <c r="A167" s="7" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="O167" s="7" t="s">
-        <v>2688</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="169" spans="1:15">
       <c r="A169" s="7" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="O169" s="7" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="170" spans="1:15">
       <c r="A170" s="7" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
       <c r="O170" s="7" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="171" spans="1:15">
       <c r="A171" s="7" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="O171" s="7" t="s">
-        <v>2689</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="173" spans="1:15">
       <c r="A173" s="7" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="O173" s="7" t="s">
-        <v>2690</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="174" spans="1:15">
       <c r="A174" s="7" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="O174" s="7" t="s">
-        <v>2691</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="175" spans="1:15">
       <c r="A175" s="7" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="O175" s="7" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="177" spans="1:15">
       <c r="A177" s="7" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="O177" s="7" t="s">
-        <v>2692</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="178" spans="1:15">
       <c r="A178" s="7" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="O178" s="7" t="s">
-        <v>2693</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="179" spans="1:15">
       <c r="A179" s="7" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="O179" s="7" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="181" spans="1:15">
       <c r="A181" s="7" t="s">
-        <v>3020</v>
+        <v>3018</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>3020</v>
+        <v>3018</v>
       </c>
       <c r="O181" s="7" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="182" spans="1:15">
       <c r="A182" s="7" t="s">
-        <v>3022</v>
+        <v>3020</v>
       </c>
       <c r="O182" s="7" t="s">
-        <v>3047</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="183" spans="1:15">
       <c r="A183" s="7" t="s">
+        <v>3019</v>
+      </c>
+      <c r="O183" s="7" t="s">
         <v>3021</v>
-      </c>
-      <c r="O183" s="7" t="s">
-        <v>3023</v>
       </c>
     </row>
     <row r="185" spans="1:15">
       <c r="A185" s="7" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="O185" s="7" t="s">
-        <v>2694</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="186" spans="1:15">
       <c r="A186" s="7" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="O186" s="7" t="s">
-        <v>2695</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="187" spans="1:15">
       <c r="A187" s="7" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
       <c r="O187" s="7" t="s">
-        <v>2696</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="189" spans="1:15">
       <c r="A189" s="7" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="O189" s="7" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="190" spans="1:15">
       <c r="A190" s="7" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="O190" s="7" t="s">
-        <v>2697</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="191" spans="1:15">
       <c r="A191" s="7" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="O191" s="7" t="s">
-        <v>2698</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="193" spans="1:15">
       <c r="A193" s="7" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="O193" s="7" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="194" spans="1:15">
       <c r="A194" s="7" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="O194" s="7" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="195" spans="1:15">
       <c r="A195" s="7" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
       <c r="O195" s="7" t="s">
-        <v>2699</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="197" spans="1:15">
       <c r="A197" s="7" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="O197" s="7" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="198" spans="1:15">
       <c r="A198" s="7" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="O198" s="7" t="s">
-        <v>2700</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="199" spans="1:15">
       <c r="A199" s="7" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
       <c r="O199" s="7" t="s">
-        <v>2701</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="201" spans="1:15">
       <c r="A201" s="7" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
       <c r="O201" s="7" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="202" spans="1:15">
       <c r="A202" s="7" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
       <c r="O202" s="7" t="s">
-        <v>2702</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="203" spans="1:15">
       <c r="A203" s="7" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="O203" s="7" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="205" spans="1:15">
       <c r="A205" s="7" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
       <c r="O205" s="7" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="206" spans="1:15">
       <c r="A206" s="7" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
       <c r="O206" s="7" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="207" spans="1:15">
       <c r="A207" s="7" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
       <c r="O207" s="7" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="209" spans="1:15">
       <c r="A209" s="7" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
       <c r="O209" s="7" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="210" spans="1:15">
       <c r="A210" s="7" t="s">
-        <v>2074</v>
+        <v>2072</v>
       </c>
       <c r="O210" s="7" t="s">
-        <v>2703</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="211" spans="1:15">
       <c r="A211" s="7" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
       <c r="O211" s="7" t="s">
-        <v>2704</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="213" spans="1:15">
       <c r="A213" s="7" t="s">
-        <v>2076</v>
+        <v>2074</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>2076</v>
+        <v>2074</v>
       </c>
       <c r="O213" s="7" t="s">
-        <v>2705</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="214" spans="1:15">
       <c r="A214" s="7" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="O214" s="7" t="s">
-        <v>2706</v>
+        <v>2704</v>
       </c>
     </row>
     <row r="215" spans="1:15">
       <c r="A215" s="7" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="O215" s="7" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="217" spans="1:15">
       <c r="A217" s="7" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
       <c r="O217" s="7" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="218" spans="1:15">
       <c r="A218" s="7" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
       <c r="O218" s="7" t="s">
-        <v>2707</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="219" spans="1:15">
       <c r="A219" s="7" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="O219" s="7" t="s">
-        <v>2708</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="221" spans="1:15">
       <c r="A221" s="7" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="O221" s="7" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="222" spans="1:15">
       <c r="A222" s="7" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
       <c r="O222" s="7" t="s">
-        <v>2709</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="223" spans="1:15">
       <c r="A223" s="7" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
       <c r="O223" s="7" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="225" spans="1:15">
       <c r="A225" s="7" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="O225" s="7" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="226" spans="1:15">
       <c r="A226" s="7" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="O226" s="7" t="s">
-        <v>2710</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="227" spans="1:15">
       <c r="A227" s="7" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="O227" s="7" t="s">
-        <v>2710</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="229" spans="1:15">
       <c r="A229" s="7" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="B229" s="7" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="O229" s="7" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="230" spans="1:15">
       <c r="A230" s="7" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
       <c r="O230" s="7" t="s">
-        <v>2711</v>
+        <v>2709</v>
       </c>
     </row>
     <row r="231" spans="1:15">
       <c r="A231" s="7" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
       <c r="O231" s="7" t="s">
-        <v>2653</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="233" spans="1:15">
       <c r="A233" s="7" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="B233" s="7" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
       <c r="O233" s="7" t="s">
-        <v>2712</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="234" spans="1:15">
       <c r="A234" s="7" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
       <c r="O234" s="7" t="s">
-        <v>2713</v>
+        <v>2711</v>
       </c>
     </row>
     <row r="235" spans="1:15">
       <c r="A235" s="7" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
       <c r="O235" s="7" t="s">
-        <v>2714</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="237" spans="1:15">
       <c r="A237" s="7" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="B237" s="7" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
       <c r="O237" s="7" t="s">
-        <v>2715</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="238" spans="1:15">
       <c r="A238" s="7" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="O238" s="7" t="s">
-        <v>2104</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="239" spans="1:15">
       <c r="A239" s="7" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="O239" s="7" t="s">
-        <v>2716</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="241" spans="1:15">
       <c r="A241" s="7" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="B241" s="7" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="O241" s="7" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="242" spans="1:15">
       <c r="A242" s="7" t="s">
-        <v>2717</v>
+        <v>2715</v>
       </c>
       <c r="O242" s="7" t="s">
-        <v>2718</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="243" spans="1:15">
       <c r="A243" s="7" t="s">
-        <v>2719</v>
+        <v>2717</v>
       </c>
       <c r="O243" s="7" t="s">
-        <v>2720</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="245" spans="1:15">
       <c r="A245" s="7" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="B245" s="7" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="O245" s="7" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="246" spans="1:15">
       <c r="A246" s="7" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="O246" s="7" t="s">
-        <v>2110</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="247" spans="1:15">
       <c r="A247" s="7" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="O247" s="7" t="s">
-        <v>2721</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="249" spans="1:15">
       <c r="A249" s="7" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="B249" s="7" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="O249" s="7" t="s">
-        <v>2113</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="250" spans="1:15">
       <c r="A250" s="7" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
       <c r="O250" s="7" t="s">
-        <v>2722</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="251" spans="1:15">
       <c r="A251" s="7" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="O251" s="7" t="s">
-        <v>2723</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="253" spans="1:15">
       <c r="A253" s="7" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
       <c r="B253" s="7" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
       <c r="O253" s="7" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="254" spans="1:15">
       <c r="A254" s="7" t="s">
-        <v>2118</v>
+        <v>2116</v>
       </c>
       <c r="O254" s="7" t="s">
-        <v>2724</v>
+        <v>2722</v>
       </c>
     </row>
     <row r="255" spans="1:15">
       <c r="A255" s="7" t="s">
-        <v>2119</v>
+        <v>2117</v>
       </c>
       <c r="O255" s="7" t="s">
-        <v>2120</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="257" spans="1:15">
       <c r="A257" s="7" t="s">
-        <v>2121</v>
+        <v>2119</v>
       </c>
       <c r="B257" s="7" t="s">
-        <v>2121</v>
+        <v>2119</v>
       </c>
       <c r="O257" s="7" t="s">
-        <v>2122</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="258" spans="1:15">
       <c r="A258" s="7" t="s">
-        <v>2123</v>
+        <v>2121</v>
       </c>
       <c r="O258" s="7" t="s">
-        <v>2725</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="259" spans="1:15">
       <c r="A259" s="7" t="s">
-        <v>2124</v>
+        <v>2122</v>
       </c>
       <c r="O259" s="7" t="s">
-        <v>2726</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="261" spans="1:15">
       <c r="A261" s="7" t="s">
-        <v>2125</v>
+        <v>2123</v>
       </c>
       <c r="B261" s="7" t="s">
-        <v>2125</v>
+        <v>2123</v>
       </c>
       <c r="O261" s="7" t="s">
-        <v>2126</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="262" spans="1:15">
       <c r="A262" s="7" t="s">
-        <v>2127</v>
+        <v>2125</v>
       </c>
       <c r="O262" s="7" t="s">
-        <v>2727</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="263" spans="1:15">
       <c r="A263" s="7" t="s">
-        <v>2128</v>
+        <v>2126</v>
       </c>
       <c r="O263" s="7" t="s">
-        <v>2129</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="265" spans="1:15">
       <c r="A265" s="7" t="s">
-        <v>2130</v>
+        <v>2128</v>
       </c>
       <c r="B265" s="7" t="s">
-        <v>2130</v>
+        <v>2128</v>
       </c>
       <c r="O265" s="7" t="s">
-        <v>2131</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="266" spans="1:15">
       <c r="A266" s="7" t="s">
-        <v>2132</v>
+        <v>2130</v>
       </c>
       <c r="O266" s="7" t="s">
-        <v>2728</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="267" spans="1:15">
       <c r="A267" s="7" t="s">
-        <v>2133</v>
+        <v>2131</v>
       </c>
       <c r="O267" s="7" t="s">
-        <v>2729</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="269" spans="1:15">
       <c r="A269" s="7" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="B269" s="7" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="O269" s="7" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="270" spans="1:15">
       <c r="A270" s="7" t="s">
-        <v>2136</v>
+        <v>2134</v>
       </c>
       <c r="O270" s="7" t="s">
-        <v>2730</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="271" spans="1:15">
       <c r="A271" s="7" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="O271" s="7" t="s">
-        <v>2138</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="273" spans="1:15">
       <c r="A273" s="7" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="B273" s="7" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="O273" s="7" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="274" spans="1:15">
       <c r="A274" s="7" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="O274" s="7" t="s">
-        <v>2142</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="275" spans="1:15">
       <c r="A275" s="7" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="O275" s="7" t="s">
-        <v>2731</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="277" spans="1:15">
       <c r="A277" s="7" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="B277" s="7" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="O277" s="7" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="278" spans="1:15">
       <c r="A278" s="7" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="O278" s="7" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="279" spans="1:15">
       <c r="A279" s="7" t="s">
-        <v>2148</v>
+        <v>2146</v>
       </c>
       <c r="O279" s="7" t="s">
-        <v>2732</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="281" spans="1:15">
       <c r="A281" s="7" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
       <c r="B281" s="7" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
       <c r="O281" s="7" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="282" spans="1:15">
       <c r="A282" s="7" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
       <c r="O282" s="7" t="s">
-        <v>2733</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="283" spans="1:15">
       <c r="A283" s="7" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
       <c r="O283" s="7" t="s">
-        <v>2734</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="285" spans="1:15">
       <c r="A285" s="7" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
       <c r="B285" s="7" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
       <c r="O285" s="7" t="s">
-        <v>2154</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="286" spans="1:15">
       <c r="A286" s="7" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="O286" s="7" t="s">
-        <v>2155</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="287" spans="1:15">
       <c r="A287" s="7" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="O287" s="7" t="s">
-        <v>2735</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="289" spans="1:15">
       <c r="A289" s="7" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B289" s="7" t="s">
+        <v>1840</v>
+      </c>
+      <c r="O289" s="7" t="s">
         <v>1841</v>
-      </c>
-      <c r="B289" s="7" t="s">
-        <v>1842</v>
-      </c>
-      <c r="O289" s="7" t="s">
-        <v>1843</v>
       </c>
     </row>
     <row r="290" spans="1:15">
       <c r="A290" s="7" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="O290" s="7" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="291" spans="1:15">
       <c r="A291" s="7" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="O291" s="7" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="293" spans="1:15">
       <c r="A293" s="7" t="s">
-        <v>2541</v>
+        <v>2539</v>
       </c>
       <c r="B293" s="7" t="s">
-        <v>2541</v>
+        <v>2539</v>
       </c>
       <c r="O293" s="7" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="294" spans="1:15">
       <c r="A294" s="7" t="s">
-        <v>2542</v>
+        <v>2540</v>
       </c>
       <c r="O294" s="7" t="s">
-        <v>2634</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="295" spans="1:15">
       <c r="A295" s="7" t="s">
+        <v>2541</v>
+      </c>
+      <c r="O295" s="7" t="s">
         <v>2543</v>
-      </c>
-      <c r="O295" s="7" t="s">
-        <v>2545</v>
       </c>
     </row>
     <row r="297" spans="1:15">
       <c r="A297" s="7" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
       <c r="B297" s="7" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
       <c r="O297" s="7" t="s">
-        <v>2157</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="298" spans="1:15">
       <c r="A298" s="7" t="s">
-        <v>2158</v>
+        <v>2156</v>
       </c>
       <c r="O298" s="7" t="s">
-        <v>2736</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="299" spans="1:15">
       <c r="A299" s="7" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="O299" s="7" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="301" spans="1:15">
       <c r="A301" s="7" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>2737</v>
+        <v>2735</v>
       </c>
       <c r="O301" s="7" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="302" spans="1:15">
       <c r="A302" s="7" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="O302" s="7" t="s">
-        <v>2738</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="303" spans="1:15">
       <c r="A303" s="7" t="s">
-        <v>2164</v>
+        <v>2162</v>
       </c>
       <c r="O303" s="7" t="s">
-        <v>2739</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="305" spans="1:15">
       <c r="A305" s="7" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="B305" s="7" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="O305" s="7" t="s">
-        <v>2166</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="306" spans="1:15">
       <c r="A306" s="7" t="s">
-        <v>2167</v>
+        <v>2165</v>
       </c>
       <c r="O306" s="7" t="s">
-        <v>2168</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="307" spans="1:15">
       <c r="A307" s="7" t="s">
-        <v>2169</v>
+        <v>2167</v>
       </c>
       <c r="O307" s="7" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="309" spans="1:15">
       <c r="A309" s="7" t="s">
-        <v>3002</v>
+        <v>3000</v>
       </c>
       <c r="B309" s="7" t="s">
+        <v>2999</v>
+      </c>
+      <c r="O309" s="7" t="s">
         <v>3001</v>
-      </c>
-      <c r="O309" s="7" t="s">
-        <v>3003</v>
       </c>
     </row>
     <row r="310" spans="1:15">
       <c r="A310" s="7" t="s">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="O310" s="7" t="s">
-        <v>3006</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="311" spans="1:15">
       <c r="A311" s="7" t="s">
-        <v>3011</v>
+        <v>3009</v>
       </c>
       <c r="O311" s="7" t="s">
-        <v>3005</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="313" spans="1:15">
       <c r="A313" s="7" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="B313" s="7" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="O313" s="7" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="314" spans="1:15">
       <c r="A314" s="7" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="O314" s="7" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="315" spans="1:15">
       <c r="A315" s="7" t="s">
-        <v>2175</v>
+        <v>2173</v>
       </c>
       <c r="O315" s="7" t="s">
-        <v>2740</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="317" spans="1:15">
       <c r="A317" s="7" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="B317" s="7" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="O317" s="7" t="s">
-        <v>2177</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="318" spans="1:15">
       <c r="A318" s="7" t="s">
-        <v>2178</v>
+        <v>2176</v>
       </c>
       <c r="O318" s="7" t="s">
-        <v>2788</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="319" spans="1:15">
       <c r="A319" s="7" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="O319" s="7" t="s">
-        <v>2788</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="321" spans="1:15">
       <c r="A321" s="7" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
       <c r="B321" s="7" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
       <c r="O321" s="7" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="322" spans="1:15">
       <c r="A322" s="7" t="s">
-        <v>2182</v>
+        <v>2180</v>
       </c>
       <c r="O322" s="7" t="s">
-        <v>2741</v>
+        <v>2739</v>
       </c>
     </row>
     <row r="323" spans="1:15">
       <c r="A323" s="7" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="O323" s="7" t="s">
-        <v>2184</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="325" spans="1:15">
       <c r="A325" s="7" t="s">
-        <v>2185</v>
+        <v>2183</v>
       </c>
       <c r="B325" s="7" t="s">
-        <v>2185</v>
+        <v>2183</v>
       </c>
       <c r="O325" s="7" t="s">
-        <v>2186</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="326" spans="1:15">
       <c r="A326" s="7" t="s">
-        <v>2187</v>
+        <v>2185</v>
       </c>
       <c r="O326" s="7" t="s">
-        <v>2742</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="327" spans="1:15">
       <c r="A327" s="7" t="s">
-        <v>2188</v>
+        <v>2186</v>
       </c>
       <c r="O327" s="7" t="s">
-        <v>2743</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="329" spans="1:15">
       <c r="A329" s="7" t="s">
-        <v>2189</v>
+        <v>2187</v>
       </c>
       <c r="B329" s="7" t="s">
-        <v>2189</v>
+        <v>2187</v>
       </c>
       <c r="O329" s="7" t="s">
-        <v>2190</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="330" spans="1:15">
       <c r="A330" s="7" t="s">
-        <v>2191</v>
+        <v>2189</v>
       </c>
       <c r="O330" s="7" t="s">
-        <v>2192</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="331" spans="1:15">
       <c r="A331" s="7" t="s">
-        <v>2193</v>
+        <v>2191</v>
       </c>
       <c r="O331" s="7" t="s">
-        <v>2194</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="333" spans="1:15">
       <c r="A333" s="7" t="s">
-        <v>2195</v>
+        <v>2193</v>
       </c>
       <c r="B333" s="7" t="s">
-        <v>2195</v>
+        <v>2193</v>
       </c>
       <c r="O333" s="7" t="s">
-        <v>2196</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="334" spans="1:15">
       <c r="A334" s="7" t="s">
-        <v>2197</v>
+        <v>2195</v>
       </c>
       <c r="O334" s="7" t="s">
-        <v>2744</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="335" spans="1:15">
       <c r="A335" s="7" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="O335" s="7" t="s">
-        <v>2199</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="337" spans="1:15">
       <c r="A337" s="7" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="B337" s="7" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="O337" s="7" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="338" spans="1:15">
       <c r="A338" s="7" t="s">
-        <v>2202</v>
+        <v>2200</v>
       </c>
       <c r="O338" s="7" t="s">
-        <v>2203</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="339" spans="1:15">
       <c r="A339" s="7" t="s">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="O339" s="7" t="s">
-        <v>2745</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="341" spans="1:15">
       <c r="A341" s="7" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="B341" s="7" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="O341" s="7" t="s">
-        <v>2206</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="342" spans="1:15">
       <c r="A342" s="7" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
       <c r="O342" s="7" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="343" spans="1:15">
       <c r="A343" s="7" t="s">
-        <v>2209</v>
+        <v>2207</v>
       </c>
       <c r="O343" s="7" t="s">
-        <v>2746</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="345" spans="1:15">
       <c r="A345" s="7" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
       <c r="B345" s="7" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
       <c r="O345" s="7" t="s">
-        <v>2211</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="346" spans="1:15">
       <c r="A346" s="7" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
       <c r="O346" s="7" t="s">
-        <v>2747</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="347" spans="1:15">
       <c r="A347" s="7" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
       <c r="O347" s="7" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="349" spans="1:15">
       <c r="A349" s="7" t="s">
-        <v>2215</v>
+        <v>2213</v>
       </c>
       <c r="B349" s="7" t="s">
-        <v>2215</v>
+        <v>2213</v>
       </c>
       <c r="O349" s="7" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="350" spans="1:15">
       <c r="A350" s="7" t="s">
-        <v>2217</v>
+        <v>2215</v>
       </c>
       <c r="O350" s="7" t="s">
-        <v>2218</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="351" spans="1:15">
       <c r="A351" s="7" t="s">
-        <v>2219</v>
+        <v>2217</v>
       </c>
       <c r="O351" s="7" t="s">
-        <v>2218</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="353" spans="1:15">
       <c r="A353" s="7" t="s">
-        <v>2220</v>
+        <v>2218</v>
       </c>
       <c r="B353" s="7" t="s">
-        <v>2220</v>
+        <v>2218</v>
       </c>
       <c r="O353" s="7" t="s">
-        <v>2221</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="354" spans="1:15">
       <c r="A354" s="7" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
       <c r="O354" s="7" t="s">
-        <v>2223</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="355" spans="1:15">
       <c r="A355" s="7" t="s">
-        <v>2224</v>
+        <v>2222</v>
       </c>
       <c r="O355" s="7" t="s">
-        <v>2748</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="357" spans="1:15">
       <c r="A357" s="7" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
       <c r="B357" s="7" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
       <c r="O357" s="7" t="s">
-        <v>2226</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="358" spans="1:15">
       <c r="A358" s="7" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
       <c r="O358" s="7" t="s">
-        <v>2749</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="359" spans="1:15">
       <c r="A359" s="7" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
       <c r="O359" s="7" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="361" spans="1:15">
       <c r="A361" s="7" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
       <c r="B361" s="7" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
       <c r="O361" s="7" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="362" spans="1:15">
       <c r="A362" s="7" t="s">
-        <v>2232</v>
+        <v>2230</v>
       </c>
       <c r="O362" s="7" t="s">
-        <v>2233</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="363" spans="1:15">
       <c r="A363" s="7" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="O363" s="7" t="s">
-        <v>2750</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="365" spans="1:15">
       <c r="A365" s="7" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="B365" s="7" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="O365" s="7" t="s">
-        <v>2236</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="366" spans="1:15">
       <c r="A366" s="7" t="s">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="O366" s="7" t="s">
-        <v>2751</v>
+        <v>2749</v>
       </c>
     </row>
     <row r="367" spans="1:15">
       <c r="A367" s="7" t="s">
-        <v>2238</v>
+        <v>2236</v>
       </c>
       <c r="O367" s="7" t="s">
-        <v>2752</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="369" spans="1:15">
       <c r="A369" s="7" t="s">
-        <v>2239</v>
+        <v>2237</v>
       </c>
       <c r="B369" s="7" t="s">
-        <v>2239</v>
+        <v>2237</v>
       </c>
       <c r="O369" s="7" t="s">
-        <v>2240</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="370" spans="1:15">
       <c r="A370" s="7" t="s">
-        <v>2241</v>
+        <v>2239</v>
       </c>
       <c r="O370" s="7" t="s">
-        <v>2242</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="371" spans="1:15">
       <c r="A371" s="7" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="O371" s="7" t="s">
-        <v>2753</v>
+        <v>2751</v>
       </c>
     </row>
     <row r="373" spans="1:15">
       <c r="A373" s="7" t="s">
-        <v>2244</v>
+        <v>2242</v>
       </c>
       <c r="B373" s="7" t="s">
-        <v>2244</v>
+        <v>2242</v>
       </c>
       <c r="O373" s="7" t="s">
-        <v>2245</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="374" spans="1:15">
       <c r="A374" s="7" t="s">
-        <v>2246</v>
+        <v>2244</v>
       </c>
       <c r="O374" s="7" t="s">
-        <v>2754</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="375" spans="1:15">
       <c r="A375" s="7" t="s">
-        <v>2247</v>
+        <v>2245</v>
       </c>
       <c r="O375" s="7" t="s">
-        <v>2248</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="377" spans="1:15">
       <c r="A377" s="7" t="s">
-        <v>2249</v>
+        <v>2247</v>
       </c>
       <c r="B377" s="7" t="s">
-        <v>2249</v>
+        <v>2247</v>
       </c>
       <c r="O377" s="7" t="s">
-        <v>2250</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="378" spans="1:15">
       <c r="A378" s="7" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
       <c r="O378" s="7" t="s">
-        <v>2755</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="379" spans="1:15">
       <c r="A379" s="7" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
       <c r="O379" s="7" t="s">
-        <v>2756</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="381" spans="1:15">
       <c r="A381" s="7" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="B381" s="7" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="O381" s="7" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="382" spans="1:15">
       <c r="A382" s="7" t="s">
-        <v>2254</v>
+        <v>2252</v>
       </c>
       <c r="O382" s="7" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="383" spans="1:15">
       <c r="A383" s="7" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="O383" s="7" t="s">
-        <v>2757</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="385" spans="1:15">
       <c r="A385" s="7" t="s">
-        <v>2257</v>
+        <v>2255</v>
       </c>
       <c r="B385" s="7" t="s">
-        <v>2257</v>
+        <v>2255</v>
       </c>
       <c r="O385" s="7" t="s">
-        <v>2258</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="386" spans="1:15">
       <c r="A386" s="7" t="s">
-        <v>2259</v>
+        <v>2257</v>
       </c>
       <c r="O386" s="7" t="s">
-        <v>2260</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="387" spans="1:15">
       <c r="A387" s="7" t="s">
-        <v>2261</v>
+        <v>2259</v>
       </c>
       <c r="O387" s="7" t="s">
-        <v>2758</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="389" spans="1:15">
       <c r="A389" s="7" t="s">
-        <v>2262</v>
+        <v>2260</v>
       </c>
       <c r="B389" s="7" t="s">
-        <v>2262</v>
+        <v>2260</v>
       </c>
       <c r="O389" s="7" t="s">
-        <v>2263</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="390" spans="1:15">
       <c r="A390" s="7" t="s">
-        <v>2264</v>
+        <v>2262</v>
       </c>
       <c r="O390" s="7" t="s">
-        <v>2759</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="391" spans="1:15">
       <c r="A391" s="7" t="s">
-        <v>2265</v>
+        <v>2263</v>
       </c>
       <c r="O391" s="7" t="s">
-        <v>2760</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="393" spans="1:15">
       <c r="A393" s="7" t="s">
-        <v>2266</v>
+        <v>2264</v>
       </c>
       <c r="B393" s="7" t="s">
-        <v>2266</v>
+        <v>2264</v>
       </c>
       <c r="O393" s="7" t="s">
-        <v>2267</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="394" spans="1:15">
       <c r="A394" s="7" t="s">
-        <v>2268</v>
+        <v>2266</v>
       </c>
       <c r="O394" s="7" t="s">
-        <v>2269</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="395" spans="1:15">
       <c r="A395" s="7" t="s">
-        <v>2270</v>
+        <v>2268</v>
       </c>
       <c r="O395" s="7" t="s">
-        <v>2271</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="397" spans="1:15">
       <c r="A397" s="7" t="s">
-        <v>2272</v>
+        <v>2270</v>
       </c>
       <c r="B397" s="7" t="s">
-        <v>2761</v>
+        <v>2759</v>
       </c>
       <c r="O397" s="7" t="s">
-        <v>2273</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="398" spans="1:15">
       <c r="A398" s="7" t="s">
-        <v>2274</v>
+        <v>2272</v>
       </c>
       <c r="O398" s="7" t="s">
-        <v>2762</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="399" spans="1:15">
       <c r="A399" s="7" t="s">
-        <v>2275</v>
+        <v>2273</v>
       </c>
       <c r="O399" s="7" t="s">
-        <v>2762</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="401" spans="1:15">
       <c r="A401" s="7" t="s">
-        <v>2276</v>
+        <v>2274</v>
       </c>
       <c r="B401" s="7" t="s">
-        <v>2276</v>
+        <v>2274</v>
       </c>
       <c r="O401" s="7" t="s">
-        <v>2277</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="402" spans="1:15">
       <c r="A402" s="7" t="s">
-        <v>2278</v>
+        <v>2276</v>
       </c>
       <c r="O402" s="7" t="s">
-        <v>2763</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="403" spans="1:15">
       <c r="A403" s="7" t="s">
-        <v>2279</v>
+        <v>2277</v>
       </c>
       <c r="O403" s="7" t="s">
-        <v>2280</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="405" spans="1:15">
       <c r="A405" s="7" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="B405" s="7" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="O405" s="7" t="s">
-        <v>2282</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="406" spans="1:15">
       <c r="A406" s="7" t="s">
-        <v>2283</v>
+        <v>2281</v>
       </c>
       <c r="O406" s="7" t="s">
-        <v>2284</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="407" spans="1:15">
       <c r="A407" s="7" t="s">
-        <v>2285</v>
+        <v>2283</v>
       </c>
       <c r="O407" s="7" t="s">
-        <v>2286</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="409" spans="1:15">
       <c r="A409" s="7" t="s">
-        <v>2889</v>
+        <v>2887</v>
       </c>
       <c r="B409" s="7" t="s">
-        <v>2889</v>
+        <v>2887</v>
       </c>
       <c r="O409" s="7" t="s">
-        <v>2892</v>
+        <v>2890</v>
       </c>
     </row>
     <row r="410" spans="1:15">
       <c r="A410" s="7" t="s">
-        <v>2890</v>
+        <v>2888</v>
       </c>
       <c r="O410" s="7" t="s">
-        <v>2893</v>
+        <v>2891</v>
       </c>
     </row>
     <row r="411" spans="1:15">
       <c r="A411" s="7" t="s">
+        <v>2889</v>
+      </c>
+      <c r="O411" s="7" t="s">
         <v>2891</v>
-      </c>
-      <c r="O411" s="7" t="s">
-        <v>2893</v>
       </c>
     </row>
     <row r="413" spans="1:15">
       <c r="A413" s="7" t="s">
-        <v>2899</v>
+        <v>2897</v>
       </c>
       <c r="B413" s="7" t="s">
-        <v>2899</v>
+        <v>2897</v>
       </c>
       <c r="O413" s="7" t="s">
-        <v>2902</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="414" spans="1:15">
       <c r="A414" s="7" t="s">
-        <v>2900</v>
+        <v>2898</v>
       </c>
       <c r="O414" s="7" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="415" spans="1:15">
       <c r="A415" s="7" t="s">
+        <v>2899</v>
+      </c>
+      <c r="O415" s="7" t="s">
         <v>2901</v>
-      </c>
-      <c r="O415" s="7" t="s">
-        <v>2903</v>
       </c>
     </row>
     <row r="417" spans="1:15">
       <c r="A417" s="7" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
       <c r="B417" s="7" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
       <c r="O417" s="7" t="s">
-        <v>2288</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="418" spans="1:15">
       <c r="A418" s="7" t="s">
-        <v>2289</v>
+        <v>2287</v>
       </c>
       <c r="O418" s="7" t="s">
-        <v>2764</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="419" spans="1:15">
       <c r="A419" s="7" t="s">
-        <v>2290</v>
+        <v>2288</v>
       </c>
       <c r="O419" s="7" t="s">
-        <v>2764</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="421" spans="1:15">
       <c r="A421" s="7" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
       <c r="B421" s="7" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
       <c r="O421" s="7" t="s">
-        <v>2292</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="422" spans="1:15">
       <c r="A422" s="7" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
       <c r="O422" s="7" t="s">
-        <v>2765</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="423" spans="1:15">
       <c r="A423" s="7" t="s">
-        <v>2294</v>
+        <v>2292</v>
       </c>
       <c r="O423" s="7" t="s">
-        <v>2765</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="425" spans="1:15">
       <c r="A425" s="7" t="s">
-        <v>2295</v>
+        <v>2293</v>
       </c>
       <c r="B425" s="7" t="s">
-        <v>2295</v>
+        <v>2293</v>
       </c>
       <c r="O425" s="7" t="s">
-        <v>2292</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="426" spans="1:15">
       <c r="A426" s="7" t="s">
-        <v>2296</v>
+        <v>2294</v>
       </c>
       <c r="O426" s="7" t="s">
-        <v>2766</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="427" spans="1:15">
       <c r="A427" s="7" t="s">
-        <v>2297</v>
+        <v>2295</v>
       </c>
       <c r="O427" s="7" t="s">
-        <v>2766</v>
+        <v>2764</v>
       </c>
     </row>
   </sheetData>
@@ -26741,884 +26743,884 @@
   <sheetData>
     <row r="1" spans="1:17" ht="20.100000000000001" customHeight="1">
       <c r="B1" s="9" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>1868</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>1869</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>1870</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>1871</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>1872</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>1873</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>1874</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>1875</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>1876</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>1877</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="N1" s="9" t="s">
         <v>1878</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>1879</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>1880</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="Q1" s="8" t="s">
         <v>1881</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>1882</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>1883</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="60" customHeight="1">
       <c r="A2" s="8" t="s">
-        <v>2333</v>
+        <v>2331</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>2797</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="60" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>3008</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="60" customHeight="1">
       <c r="A4" s="8" t="s">
-        <v>2335</v>
+        <v>2333</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>2799</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="60" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>2336</v>
+        <v>2334</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>2800</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="60" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>2337</v>
+        <v>2335</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="60" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>2787</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="60" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>2338</v>
+        <v>2336</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>2786</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="60" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>2339</v>
+        <v>2337</v>
       </c>
       <c r="O9" s="9" t="s">
-        <v>2329</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="60" customHeight="1">
       <c r="A10" s="8" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>2330</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="60" customHeight="1">
       <c r="A11" s="8" t="s">
-        <v>2341</v>
+        <v>2339</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>2801</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="60" customHeight="1">
       <c r="A12" s="8" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>2802</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="60" customHeight="1">
       <c r="A13" s="8" t="s">
-        <v>2343</v>
+        <v>2341</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>2785</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="60" customHeight="1">
       <c r="A14" s="8" t="s">
-        <v>2344</v>
+        <v>2342</v>
       </c>
       <c r="O14" s="9" t="s">
-        <v>2784</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="60" customHeight="1">
       <c r="A15" s="8" t="s">
-        <v>2345</v>
+        <v>2343</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>2803</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="60" customHeight="1">
       <c r="A16" s="8" t="s">
-        <v>2346</v>
+        <v>2344</v>
       </c>
       <c r="O16" s="9" t="s">
-        <v>2804</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="60" customHeight="1">
       <c r="A17" s="8" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>2805</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="60" customHeight="1">
       <c r="A18" s="8" t="s">
-        <v>2348</v>
+        <v>2346</v>
       </c>
       <c r="O18" s="9" t="s">
-        <v>2806</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="60" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>2343</v>
+        <v>2341</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>2807</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="60" customHeight="1">
       <c r="A20" s="8" t="s">
-        <v>2349</v>
+        <v>2347</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>2808</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="60" customHeight="1">
       <c r="A21" s="8" t="s">
-        <v>2350</v>
+        <v>2348</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>2331</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="60" customHeight="1">
       <c r="A22" s="8" t="s">
-        <v>2351</v>
+        <v>2349</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>2938</v>
+        <v>2936</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="60" customHeight="1">
       <c r="A23" s="8" t="s">
-        <v>2352</v>
+        <v>2350</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>2809</v>
+        <v>2807</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="60" customHeight="1">
       <c r="A24" s="8" t="s">
-        <v>2353</v>
+        <v>2351</v>
       </c>
       <c r="O24" s="9" t="s">
-        <v>2810</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="60" customHeight="1">
       <c r="A25" s="8" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>2811</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="60" customHeight="1">
       <c r="A26" s="8" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
       <c r="O26" s="9" t="s">
-        <v>2812</v>
+        <v>2810</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="60" customHeight="1">
       <c r="A28" s="8" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="O28" s="9" t="s">
-        <v>2813</v>
+        <v>2811</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="60" customHeight="1">
       <c r="A29" s="8" t="s">
-        <v>2535</v>
+        <v>2533</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>2534</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="60" customHeight="1">
       <c r="A30" s="8" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="O30" s="9" t="s">
-        <v>2814</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="60" customHeight="1">
       <c r="A31" s="8" t="s">
-        <v>2354</v>
+        <v>2352</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>2815</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="60" customHeight="1">
       <c r="A32" s="8" t="s">
-        <v>2355</v>
+        <v>2353</v>
       </c>
       <c r="O32" s="9" t="s">
-        <v>2332</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="60" customHeight="1">
       <c r="A33" s="8" t="s">
-        <v>2356</v>
+        <v>2354</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>2816</v>
+        <v>2814</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="60" customHeight="1">
       <c r="A34" s="8" t="s">
-        <v>2357</v>
+        <v>2355</v>
       </c>
       <c r="O34" s="9" t="s">
-        <v>2817</v>
+        <v>2815</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="60" customHeight="1">
       <c r="A35" s="8" t="s">
-        <v>2358</v>
+        <v>2356</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>2818</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="60" customHeight="1">
       <c r="A36" s="8" t="s">
-        <v>2359</v>
+        <v>2357</v>
       </c>
       <c r="O36" s="9" t="s">
-        <v>2819</v>
+        <v>2817</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="60" customHeight="1">
       <c r="A37" s="8" t="s">
-        <v>2360</v>
+        <v>2358</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>2820</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="60" customHeight="1">
       <c r="A38" s="8" t="s">
-        <v>2361</v>
+        <v>2359</v>
       </c>
       <c r="O38" s="9" t="s">
-        <v>2821</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="60" customHeight="1">
       <c r="A39" s="8" t="s">
-        <v>2362</v>
+        <v>2360</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>2822</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="60" customHeight="1">
       <c r="A40" s="8" t="s">
-        <v>2363</v>
+        <v>2361</v>
       </c>
       <c r="O40" s="9" t="s">
-        <v>2823</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="60" customHeight="1">
       <c r="A41" s="8" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>3000</v>
+        <v>2998</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="60" customHeight="1">
       <c r="A42" s="8" t="s">
-        <v>2365</v>
+        <v>2363</v>
       </c>
       <c r="O42" s="9" t="s">
-        <v>2824</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="60" customHeight="1">
       <c r="A43" s="8" t="s">
-        <v>2366</v>
+        <v>2364</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>2825</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="60" customHeight="1">
       <c r="A44" s="8" t="s">
-        <v>2367</v>
+        <v>2365</v>
       </c>
       <c r="O44" s="9" t="s">
-        <v>2826</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="60" customHeight="1">
       <c r="A45" s="8" t="s">
-        <v>3025</v>
+        <v>3023</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>3048</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="60" customHeight="1">
       <c r="A46" s="8" t="s">
-        <v>2368</v>
+        <v>2366</v>
       </c>
       <c r="O46" s="9" t="s">
-        <v>2827</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="60" customHeight="1">
       <c r="A47" s="8" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>2828</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="60" customHeight="1">
       <c r="A48" s="8" t="s">
-        <v>2928</v>
+        <v>2926</v>
       </c>
       <c r="O48" s="9" t="s">
-        <v>2936</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="60" customHeight="1">
       <c r="A50" s="8" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
       <c r="O50" s="9" t="s">
-        <v>2829</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="60" customHeight="1">
       <c r="A51" s="8" t="s">
-        <v>2371</v>
+        <v>2369</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>2830</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="60" customHeight="1">
       <c r="A52" s="8" t="s">
-        <v>2372</v>
+        <v>2370</v>
       </c>
       <c r="O52" s="9" t="s">
-        <v>2783</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="60" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>2373</v>
+        <v>2371</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>2831</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="60" customHeight="1">
       <c r="A54" s="8" t="s">
-        <v>2374</v>
+        <v>2372</v>
       </c>
       <c r="O54" s="9" t="s">
-        <v>2832</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="60" customHeight="1">
       <c r="A55" s="8" t="s">
-        <v>2375</v>
+        <v>2373</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>2782</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="60" customHeight="1">
       <c r="A56" s="8" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="O56" s="9" t="s">
-        <v>2833</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="60" customHeight="1">
       <c r="A57" s="8" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>2834</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="60" customHeight="1">
       <c r="A58" s="8" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="O58" s="9" t="s">
-        <v>2835</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="60" customHeight="1">
       <c r="A59" s="8" t="s">
-        <v>2379</v>
+        <v>2377</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>2836</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="60" customHeight="1">
       <c r="A60" s="8" t="s">
-        <v>2380</v>
+        <v>2378</v>
       </c>
       <c r="O60" s="9" t="s">
-        <v>2837</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="60" customHeight="1">
       <c r="A61" s="8" t="s">
-        <v>2381</v>
+        <v>2379</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>2838</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="60" customHeight="1">
       <c r="A62" s="8" t="s">
-        <v>2382</v>
+        <v>2380</v>
       </c>
       <c r="O62" s="9" t="s">
-        <v>2839</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="60" customHeight="1">
       <c r="A63" s="8" t="s">
-        <v>2874</v>
+        <v>2872</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>2840</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="60" customHeight="1">
       <c r="A64" s="8" t="s">
-        <v>2383</v>
+        <v>2381</v>
       </c>
       <c r="O64" s="9" t="s">
-        <v>2841</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="60" customHeight="1">
       <c r="A65" s="8" t="s">
-        <v>2384</v>
+        <v>2382</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>2879</v>
+        <v>2877</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="60" customHeight="1">
       <c r="A66" s="8" t="s">
-        <v>2385</v>
+        <v>2383</v>
       </c>
       <c r="O66" s="9" t="s">
-        <v>2842</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="60" customHeight="1">
       <c r="A67" s="8" t="s">
-        <v>2386</v>
+        <v>2384</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>2843</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="60" customHeight="1">
       <c r="A68" s="8" t="s">
-        <v>2387</v>
+        <v>2385</v>
       </c>
       <c r="O68" s="9" t="s">
-        <v>2844</v>
+        <v>2842</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="60" customHeight="1">
       <c r="A69" s="8" t="s">
-        <v>2388</v>
+        <v>2386</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>2845</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="60" customHeight="1">
       <c r="A70" s="8" t="s">
-        <v>2389</v>
+        <v>2387</v>
       </c>
       <c r="O70" s="9" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="60" customHeight="1">
       <c r="A71" s="8" t="s">
-        <v>2390</v>
+        <v>2388</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>2846</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="60" customHeight="1">
       <c r="A72" s="8" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
       <c r="O72" s="9" t="s">
-        <v>2847</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="60" customHeight="1">
       <c r="A73" s="8" t="s">
-        <v>2392</v>
+        <v>2390</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>2848</v>
+        <v>2846</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="60" customHeight="1">
       <c r="A74" s="8" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="O74" s="9" t="s">
-        <v>2849</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="60" customHeight="1">
       <c r="A75" s="8" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>2883</v>
+        <v>2881</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="60" customHeight="1">
       <c r="A76" s="8" t="s">
-        <v>2578</v>
+        <v>2576</v>
       </c>
       <c r="O76" s="9" t="s">
-        <v>2577</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="60" customHeight="1">
       <c r="A78" s="8" t="s">
-        <v>2394</v>
+        <v>2392</v>
       </c>
       <c r="O78" s="9" t="s">
-        <v>2850</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="60" customHeight="1">
       <c r="A79" s="8" t="s">
-        <v>2334</v>
+        <v>2332</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>2798</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="60" customHeight="1">
       <c r="A80" s="8" t="s">
-        <v>2395</v>
+        <v>2393</v>
       </c>
       <c r="O80" s="9" t="s">
-        <v>2795</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="81" spans="1:15" ht="60" customHeight="1">
       <c r="A81" s="8" t="s">
-        <v>2396</v>
+        <v>2394</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>2851</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="60" customHeight="1">
       <c r="A82" s="8" t="s">
-        <v>2397</v>
+        <v>2395</v>
       </c>
       <c r="O82" s="9" t="s">
-        <v>2852</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="83" spans="1:15" ht="60" customHeight="1">
       <c r="A83" s="8" t="s">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>3049</v>
+        <v>3047</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="60" customHeight="1">
       <c r="A84" s="8" t="s">
-        <v>2398</v>
+        <v>2396</v>
       </c>
       <c r="O84" s="9" t="s">
-        <v>2853</v>
+        <v>2851</v>
       </c>
     </row>
     <row r="85" spans="1:15" ht="60" customHeight="1">
       <c r="A85" s="8" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>2854</v>
+        <v>2852</v>
       </c>
     </row>
     <row r="86" spans="1:15" ht="60" customHeight="1">
       <c r="A86" s="8" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
       <c r="O86" s="9" t="s">
-        <v>2855</v>
+        <v>2853</v>
       </c>
     </row>
     <row r="87" spans="1:15" ht="60" customHeight="1">
       <c r="A87" s="8" t="s">
-        <v>2401</v>
+        <v>2399</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>2856</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="60" customHeight="1">
       <c r="A88" s="8" t="s">
-        <v>2402</v>
+        <v>2400</v>
       </c>
       <c r="O88" s="9" t="s">
-        <v>2857</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="60" customHeight="1">
       <c r="A89" s="8" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>2858</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="90" spans="1:15" ht="60" customHeight="1">
       <c r="A90" s="8" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="O90" s="9" t="s">
-        <v>2859</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="60" customHeight="1">
       <c r="A91" s="8" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>2860</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="92" spans="1:15" ht="60" customHeight="1">
       <c r="A92" s="8" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="O92" s="9" t="s">
-        <v>2861</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="93" spans="1:15" ht="60" customHeight="1">
       <c r="A93" s="8" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>2796</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="94" spans="1:15" ht="60" customHeight="1">
       <c r="A94" s="8" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
       <c r="O94" s="9" t="s">
-        <v>2862</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="95" spans="1:15" ht="60" customHeight="1">
       <c r="A95" s="8" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>2863</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="96" spans="1:15" ht="60" customHeight="1">
       <c r="A96" s="8" t="s">
-        <v>2410</v>
+        <v>2408</v>
       </c>
       <c r="O96" s="9" t="s">
-        <v>2864</v>
+        <v>2862</v>
       </c>
     </row>
     <row r="97" spans="1:15" ht="60" customHeight="1">
       <c r="A97" s="8" t="s">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>2865</v>
+        <v>2863</v>
       </c>
     </row>
     <row r="98" spans="1:15" ht="60" customHeight="1">
       <c r="A98" s="8" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
       <c r="O98" s="9" t="s">
-        <v>2866</v>
+        <v>2864</v>
       </c>
     </row>
     <row r="99" spans="1:15" ht="60" customHeight="1">
       <c r="A99" s="8" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>2867</v>
+        <v>2865</v>
       </c>
     </row>
     <row r="100" spans="1:15" ht="60" customHeight="1">
       <c r="A100" s="8" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
       <c r="O100" s="9" t="s">
-        <v>2868</v>
+        <v>2866</v>
       </c>
     </row>
     <row r="101" spans="1:15" ht="60" customHeight="1">
       <c r="A101" s="8" t="s">
-        <v>2415</v>
+        <v>2413</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>2869</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="102" spans="1:15" ht="60" customHeight="1">
       <c r="A102" s="8" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
       <c r="O102" s="9" t="s">
-        <v>2870</v>
+        <v>2868</v>
       </c>
     </row>
     <row r="103" spans="1:15" ht="60" customHeight="1">
       <c r="A103" s="8" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>2871</v>
+        <v>2869</v>
       </c>
     </row>
     <row r="104" spans="1:15" ht="60" customHeight="1">
       <c r="A104" s="8" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="O104" s="9" t="s">
-        <v>2872</v>
+        <v>2870</v>
       </c>
     </row>
     <row r="105" spans="1:15" ht="60" customHeight="1">
       <c r="A105" s="8" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>2873</v>
+        <v>2871</v>
       </c>
     </row>
     <row r="106" spans="1:15" ht="60" customHeight="1">
       <c r="A106" s="8" t="s">
-        <v>2420</v>
+        <v>2418</v>
       </c>
       <c r="O106" s="9" t="s">
-        <v>2875</v>
+        <v>2873</v>
       </c>
     </row>
     <row r="107" spans="1:15" ht="60" customHeight="1">
       <c r="A107" s="8" t="s">
-        <v>2894</v>
+        <v>2892</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>2895</v>
+        <v>2893</v>
       </c>
     </row>
     <row r="108" spans="1:15" ht="60" customHeight="1">
       <c r="A108" s="8" t="s">
-        <v>2904</v>
+        <v>2902</v>
       </c>
       <c r="O108" s="9" t="s">
-        <v>2921</v>
+        <v>2919</v>
       </c>
     </row>
   </sheetData>

--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Among Us code\TheOtherUs\TheOtherUs-Edited-Lite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739FD9A4-D374-44CC-9D74-6ACE9E106AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23AC7112-6429-42F6-B861-98C2AE3D8BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2355" yWindow="525" windowWidth="25755" windowHeight="15555" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Options" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Role Description" sheetId="11" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Options!$O$1:$O$1430</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Options!$O$1:$O$1438</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3393" uniqueCount="3077">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3426" uniqueCount="3107">
   <si>
     <t>English</t>
   </si>
@@ -10234,10 +10234,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SpecterButton</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Revive</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -10552,9 +10548,6 @@
   </si>
   <si>
     <t>WolfLord</t>
-  </si>
-  <si>
-    <t>WolfLord</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -10884,6 +10877,135 @@
   </si>
   <si>
     <t>目标死亡后变为</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>redemptorRevelation</t>
+  </si>
+  <si>
+    <t>redemptorRevelationCooldown</t>
+  </si>
+  <si>
+    <t>redemptorPrayer</t>
+  </si>
+  <si>
+    <t>redemptorPrayerCooldown</t>
+  </si>
+  <si>
+    <t>redemptorPrayerDuration</t>
+  </si>
+  <si>
+    <t>启示</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>启示冷却</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>祈祷</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>祈祷冷却</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>祈祷持续时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RedemptorIntroDesc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RedemptorShortDesc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>牧师</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>redemptorReviveDuration</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通复活持续时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReviveButton</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>redemptorRevelationDuration</t>
+  </si>
+  <si>
+    <t>箭头持续时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RedemptorRevelation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Revelation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 启示</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prayer</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>恶者亦可称王</t>
+  </si>
+  <si>
+    <t>在会议中强制击杀一人</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>给予重生的机会</t>
+  </si>
+  <si>
+    <t>为亡灵祈祷吧</t>
+  </si>
+  <si>
+    <t>GrenadierFullDesc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以使用技能闪瞎附近的非红狼玩家，被闪到的玩家名称会变黑。
+队友按照房间设置也可以得知哪些玩家被影响。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Redemptor</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RedemptorFullDesc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">牧师可以寻找尸体并复活该玩家，且复活时会向所有坏人通知复活位置。
+该玩家复活后，所有坏人会有箭头指向该玩家。
+牧师拥有三个技能（房主可以禁用前两个技能）：
+启示：使用后会随机指向场上的一个尸体，没有尸体则没有箭头。
+祈祷：需要在尸体旁使用，祈祷需要持续一定的时间，且会向所有坏人
+通知牧师的位置，祈祷完成后会将该尸体所属的玩家复活。
+如果祈祷被打断则复活失败！每回合只能使用一次。
+殉道：需要在尸体旁使用：使用技能后会自杀，技能持续时间(一般很短)
+结束后完成后会将该尸体所属的玩家复活。
+复活过程中如果进入会议则复活失败！
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RedemptorPrayer</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -11483,7 +11605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1727"/>
+  <dimension ref="A1:Q1735"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40.375" style="2" customWidth="1"/>
@@ -11696,7 +11818,7 @@
     </row>
     <row r="17" spans="1:15" ht="24.95" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>2451</v>
@@ -11707,7 +11829,7 @@
     </row>
     <row r="18" spans="1:15" ht="24.95" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>2457</v>
@@ -11831,7 +11953,7 @@
     </row>
     <row r="30" spans="1:15" ht="24.95" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>42</v>
@@ -11988,7 +12110,7 @@
     </row>
     <row r="45" spans="1:15" ht="24.95" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>2885</v>
@@ -12107,10 +12229,10 @@
     </row>
     <row r="57" spans="1:15" ht="24.95" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>3051</v>
+        <v>3049</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>3051</v>
+        <v>3049</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>1154</v>
@@ -12118,10 +12240,10 @@
     </row>
     <row r="58" spans="1:15" ht="24.95" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>3074</v>
+        <v>3072</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>3071</v>
+        <v>3069</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="24.95" customHeight="1">
@@ -12317,18 +12439,18 @@
     </row>
     <row r="78" spans="1:15" ht="24.95" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>3066</v>
+        <v>3064</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>3069</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="24.95" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>3067</v>
+        <v>3065</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>3068</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="24.95" customHeight="1">
@@ -12617,42 +12739,42 @@
     </row>
     <row r="107" spans="1:15" ht="24.95" customHeight="1">
       <c r="A107" s="2" t="s">
-        <v>3056</v>
+        <v>3054</v>
       </c>
       <c r="O107" s="2" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="108" spans="1:15" ht="24.95" customHeight="1">
       <c r="A108" s="2" t="s">
-        <v>3057</v>
+        <v>3055</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>3062</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="109" spans="1:15" ht="24.95" customHeight="1">
       <c r="A109" s="2" t="s">
-        <v>3058</v>
+        <v>3056</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>3063</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="110" spans="1:15" ht="24.95" customHeight="1">
       <c r="A110" s="2" t="s">
-        <v>3059</v>
+        <v>3057</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>3064</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="111" spans="1:15" ht="24.95" customHeight="1">
       <c r="A111" s="2" t="s">
-        <v>3060</v>
+        <v>3058</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>3065</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="112" spans="1:15" ht="24.95" customHeight="1">
@@ -12693,13 +12815,13 @@
     </row>
     <row r="116" spans="1:15" ht="24.95" customHeight="1">
       <c r="A116" s="2" t="s">
+        <v>3039</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>3040</v>
+      </c>
+      <c r="O116" s="2" t="s">
         <v>3041</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>3042</v>
-      </c>
-      <c r="O116" s="2" t="s">
-        <v>3043</v>
       </c>
     </row>
     <row r="117" spans="1:15" ht="24.95" customHeight="1">
@@ -13045,18 +13167,18 @@
     </row>
     <row r="150" spans="1:15" ht="24.95" customHeight="1">
       <c r="A150" s="2" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="O150" s="2" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="151" spans="1:15" ht="24.95" customHeight="1">
       <c r="A151" s="2" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="O151" s="2" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
     </row>
     <row r="152" spans="1:15" ht="24.95" customHeight="1">
@@ -13392,26 +13514,26 @@
     </row>
     <row r="185" spans="1:15" ht="24.95" customHeight="1">
       <c r="A185" s="2" t="s">
-        <v>3048</v>
+        <v>3046</v>
       </c>
       <c r="O185" s="2" t="s">
-        <v>3070</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="186" spans="1:15" ht="24.95" customHeight="1">
       <c r="A186" s="2" t="s">
-        <v>3049</v>
+        <v>3047</v>
       </c>
       <c r="O186" s="2" t="s">
-        <v>3072</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="187" spans="1:15" ht="24.95" customHeight="1">
       <c r="A187" s="2" t="s">
-        <v>3050</v>
+        <v>3048</v>
       </c>
       <c r="O187" s="2" t="s">
-        <v>3073</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="188" spans="1:15" ht="24.95" customHeight="1">
@@ -14854,7 +14976,7 @@
         <v>648</v>
       </c>
       <c r="O338" s="2" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="339" spans="1:15" ht="24.95" customHeight="1">
@@ -15286,7 +15408,7 @@
     </row>
     <row r="385" spans="1:15" ht="24.95" customHeight="1">
       <c r="A385" s="2" t="s">
-        <v>3054</v>
+        <v>3052</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>1652</v>
@@ -15297,7 +15419,7 @@
     </row>
     <row r="386" spans="1:15" ht="24.95" customHeight="1">
       <c r="A386" s="2" t="s">
-        <v>3053</v>
+        <v>3051</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>1678</v>
@@ -15322,26 +15444,26 @@
     </row>
     <row r="389" spans="1:15" ht="24.95" customHeight="1">
       <c r="A389" s="2" t="s">
-        <v>3025</v>
+        <v>3023</v>
       </c>
       <c r="O389" s="2" t="s">
-        <v>3026</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="390" spans="1:15" ht="24.95" customHeight="1">
       <c r="A390" s="2" t="s">
+        <v>3036</v>
+      </c>
+      <c r="O390" s="2" t="s">
         <v>3038</v>
-      </c>
-      <c r="O390" s="2" t="s">
-        <v>3040</v>
       </c>
     </row>
     <row r="391" spans="1:15" ht="24.95" customHeight="1">
       <c r="A391" s="2" t="s">
+        <v>3035</v>
+      </c>
+      <c r="O391" s="3" t="s">
         <v>3037</v>
-      </c>
-      <c r="O391" s="3" t="s">
-        <v>3039</v>
       </c>
     </row>
     <row r="392" spans="1:15" ht="24.95" customHeight="1">
@@ -15870,18 +15992,18 @@
     </row>
     <row r="451" spans="1:15" ht="24.95" customHeight="1">
       <c r="A451" s="2" t="s">
+        <v>3008</v>
+      </c>
+      <c r="O451" s="2" t="s">
         <v>3010</v>
-      </c>
-      <c r="O451" s="2" t="s">
-        <v>3012</v>
       </c>
     </row>
     <row r="452" spans="1:15" ht="24.95" customHeight="1">
       <c r="A452" s="2" t="s">
+        <v>3009</v>
+      </c>
+      <c r="O452" s="2" t="s">
         <v>3011</v>
-      </c>
-      <c r="O452" s="2" t="s">
-        <v>3013</v>
       </c>
     </row>
     <row r="453" spans="1:15" ht="24.95" customHeight="1">
@@ -15983,7 +16105,7 @@
         <v>1617</v>
       </c>
       <c r="O464" s="2" t="s">
-        <v>3075</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="465" spans="1:15" ht="24.95" customHeight="1">
@@ -15994,7 +16116,7 @@
         <v>1812</v>
       </c>
       <c r="O465" s="2" t="s">
-        <v>3076</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="466" spans="1:15" ht="24.95" customHeight="1">
@@ -16087,34 +16209,34 @@
     </row>
     <row r="476" spans="1:15" ht="24.95" customHeight="1">
       <c r="A476" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="O476" s="2" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
     </row>
     <row r="477" spans="1:15" ht="24.95" customHeight="1">
       <c r="A477" s="2" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="O477" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="478" spans="1:15" ht="24.95" customHeight="1">
       <c r="A478" s="2" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="O478" s="3" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="479" spans="1:15" ht="24.95" customHeight="1">
       <c r="A479" s="2" t="s">
-        <v>2997</v>
+        <v>2995</v>
       </c>
       <c r="O479" s="3" t="s">
-        <v>3024</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="480" spans="1:15" ht="24.95" customHeight="1">
@@ -17527,7 +17649,7 @@
         <v>1074</v>
       </c>
       <c r="O629" s="2" t="s">
-        <v>3055</v>
+        <v>3053</v>
       </c>
     </row>
     <row r="630" spans="1:15" ht="24.95" customHeight="1">
@@ -17907,7 +18029,7 @@
     </row>
     <row r="670" spans="1:15" ht="24.95" customHeight="1">
       <c r="A670" s="2" t="s">
-        <v>3052</v>
+        <v>3050</v>
       </c>
       <c r="B670" s="2" t="s">
         <v>1155</v>
@@ -17932,71 +18054,72 @@
     </row>
     <row r="673" spans="1:15" ht="24.95" customHeight="1">
       <c r="A673" s="2" t="s">
-        <v>1162</v>
-      </c>
-      <c r="B673" s="2" t="s">
-        <v>1775</v>
+        <v>3075</v>
       </c>
       <c r="O673" s="2" t="s">
-        <v>1163</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="674" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O674" s="2"/>
+      <c r="A674" s="2" t="s">
+        <v>3076</v>
+      </c>
+      <c r="O674" s="2" t="s">
+        <v>3081</v>
+      </c>
     </row>
     <row r="675" spans="1:15" ht="24.95" customHeight="1">
       <c r="A675" s="2" t="s">
-        <v>1164</v>
-      </c>
-      <c r="B675" s="2" t="s">
-        <v>1165</v>
+        <v>3091</v>
       </c>
       <c r="O675" s="2" t="s">
-        <v>1166</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="676" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O676" s="2"/>
+      <c r="A676" s="2" t="s">
+        <v>3077</v>
+      </c>
+      <c r="O676" s="2" t="s">
+        <v>3082</v>
+      </c>
     </row>
     <row r="677" spans="1:15" ht="24.95" customHeight="1">
       <c r="A677" s="2" t="s">
-        <v>3014</v>
+        <v>3078</v>
       </c>
       <c r="O677" s="2" t="s">
-        <v>3016</v>
+        <v>3083</v>
       </c>
     </row>
     <row r="678" spans="1:15" ht="24.95" customHeight="1">
       <c r="A678" s="2" t="s">
-        <v>3015</v>
+        <v>3079</v>
       </c>
       <c r="O678" s="2" t="s">
-        <v>3017</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="679" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O679" s="2"/>
+      <c r="A679" s="2" t="s">
+        <v>3088</v>
+      </c>
+      <c r="O679" s="2" t="s">
+        <v>3089</v>
+      </c>
     </row>
     <row r="680" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A680" s="2" t="s">
-        <v>1167</v>
-      </c>
-      <c r="B680" s="2" t="s">
-        <v>1168</v>
-      </c>
-      <c r="O680" s="2" t="s">
-        <v>1169</v>
-      </c>
+      <c r="O680" s="2"/>
     </row>
     <row r="681" spans="1:15" ht="24.95" customHeight="1">
       <c r="A681" s="2" t="s">
-        <v>1170</v>
+        <v>1162</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>1171</v>
+        <v>1775</v>
       </c>
       <c r="O681" s="2" t="s">
-        <v>1172</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="682" spans="1:15" ht="24.95" customHeight="1">
@@ -18004,13 +18127,13 @@
     </row>
     <row r="683" spans="1:15" ht="24.95" customHeight="1">
       <c r="A683" s="2" t="s">
-        <v>1173</v>
+        <v>1164</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1174</v>
+        <v>1165</v>
       </c>
       <c r="O683" s="2" t="s">
-        <v>1175</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="684" spans="1:15" ht="24.95" customHeight="1">
@@ -18018,140 +18141,137 @@
     </row>
     <row r="685" spans="1:15" ht="24.95" customHeight="1">
       <c r="A685" s="2" t="s">
-        <v>1176</v>
+        <v>3012</v>
       </c>
       <c r="O685" s="2" t="s">
-        <v>1177</v>
+        <v>3014</v>
       </c>
     </row>
     <row r="686" spans="1:15" ht="24.95" customHeight="1">
       <c r="A686" s="2" t="s">
-        <v>1178</v>
-      </c>
-      <c r="B686" s="2" t="s">
-        <v>1179</v>
+        <v>3013</v>
       </c>
       <c r="O686" s="2" t="s">
-        <v>1180</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="687" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A687" s="2" t="s">
-        <v>1181</v>
-      </c>
-      <c r="B687" s="2" t="s">
-        <v>1182</v>
-      </c>
-      <c r="O687" s="2" t="s">
-        <v>1183</v>
-      </c>
+      <c r="O687" s="2"/>
     </row>
     <row r="688" spans="1:15" ht="24.95" customHeight="1">
       <c r="A688" s="2" t="s">
-        <v>1184</v>
+        <v>1167</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>1185</v>
+        <v>1168</v>
       </c>
       <c r="O688" s="2" t="s">
-        <v>1186</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="689" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O689" s="2"/>
+      <c r="A689" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B689" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="O689" s="2" t="s">
+        <v>1172</v>
+      </c>
     </row>
     <row r="690" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A690" s="2" t="s">
-        <v>1187</v>
-      </c>
-      <c r="B690" s="2" t="s">
-        <v>1188</v>
-      </c>
-      <c r="O690" s="2" t="s">
-        <v>1189</v>
-      </c>
+      <c r="O690" s="2"/>
     </row>
     <row r="691" spans="1:15" ht="24.95" customHeight="1">
       <c r="A691" s="2" t="s">
-        <v>1190</v>
+        <v>1173</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1191</v>
+        <v>1174</v>
       </c>
       <c r="O691" s="2" t="s">
-        <v>1192</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="692" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A692" s="2" t="s">
-        <v>1193</v>
-      </c>
-      <c r="B692" s="2" t="s">
-        <v>1194</v>
-      </c>
-      <c r="O692" s="2" t="s">
-        <v>1195</v>
-      </c>
+      <c r="O692" s="2"/>
     </row>
     <row r="693" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O693" s="2"/>
+      <c r="A693" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="O693" s="2" t="s">
+        <v>1177</v>
+      </c>
     </row>
     <row r="694" spans="1:15" ht="24.95" customHeight="1">
       <c r="A694" s="2" t="s">
-        <v>1196</v>
+        <v>1178</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>1197</v>
+        <v>1179</v>
       </c>
       <c r="O694" s="2" t="s">
-        <v>1198</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="695" spans="1:15" ht="24.95" customHeight="1">
       <c r="A695" s="2" t="s">
-        <v>1199</v>
+        <v>1181</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>1200</v>
+        <v>1182</v>
       </c>
       <c r="O695" s="2" t="s">
-        <v>1201</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="696" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O696" s="2"/>
+      <c r="A696" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B696" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="O696" s="2" t="s">
+        <v>1186</v>
+      </c>
     </row>
     <row r="697" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A697" s="2" t="s">
-        <v>1202</v>
-      </c>
-      <c r="B697" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="O697" s="2" t="s">
-        <v>1204</v>
-      </c>
+      <c r="O697" s="2"/>
     </row>
     <row r="698" spans="1:15" ht="24.95" customHeight="1">
       <c r="A698" s="2" t="s">
-        <v>1205</v>
+        <v>1187</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="O698" s="2" t="s">
-        <v>1207</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="699" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O699" s="2"/>
-    </row>
-    <row r="700" spans="1:15" ht="33">
+      <c r="A699" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B699" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="O699" s="2" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="700" spans="1:15" ht="24.95" customHeight="1">
       <c r="A700" s="2" t="s">
-        <v>2989</v>
-      </c>
-      <c r="O700" s="3" t="s">
-        <v>2990</v>
+        <v>1193</v>
+      </c>
+      <c r="B700" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="O700" s="2" t="s">
+        <v>1195</v>
       </c>
     </row>
     <row r="701" spans="1:15" ht="24.95" customHeight="1">
@@ -18159,74 +18279,71 @@
     </row>
     <row r="702" spans="1:15" ht="24.95" customHeight="1">
       <c r="A702" s="2" t="s">
-        <v>1208</v>
+        <v>1196</v>
+      </c>
+      <c r="B702" s="2" t="s">
+        <v>1197</v>
       </c>
       <c r="O702" s="2" t="s">
-        <v>1787</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="703" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O703" s="2"/>
+      <c r="A703" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B703" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="O703" s="2" t="s">
+        <v>1201</v>
+      </c>
     </row>
     <row r="704" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A704" s="2" t="s">
-        <v>1209</v>
-      </c>
-      <c r="B704" s="2" t="s">
-        <v>1210</v>
-      </c>
-      <c r="O704" s="2" t="s">
-        <v>1211</v>
-      </c>
+      <c r="O704" s="2"/>
     </row>
     <row r="705" spans="1:15" ht="24.95" customHeight="1">
       <c r="A705" s="2" t="s">
-        <v>1212</v>
+        <v>1202</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>1213</v>
+        <v>1203</v>
       </c>
       <c r="O705" s="2" t="s">
-        <v>1214</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="706" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O706" s="2"/>
+      <c r="A706" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B706" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="O706" s="2" t="s">
+        <v>1207</v>
+      </c>
     </row>
     <row r="707" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A707" s="2" t="s">
-        <v>1215</v>
-      </c>
-      <c r="B707" s="2" t="s">
-        <v>1216</v>
-      </c>
-      <c r="O707" s="2" t="s">
-        <v>1217</v>
-      </c>
-    </row>
-    <row r="708" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O708" s="2"/>
+      <c r="O707" s="2"/>
+    </row>
+    <row r="708" spans="1:15" ht="33">
+      <c r="A708" s="2" t="s">
+        <v>2988</v>
+      </c>
+      <c r="O708" s="3" t="s">
+        <v>2989</v>
+      </c>
     </row>
     <row r="709" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A709" s="2" t="s">
-        <v>1218</v>
-      </c>
-      <c r="B709" s="2" t="s">
-        <v>1219</v>
-      </c>
-      <c r="O709" s="2" t="s">
-        <v>1220</v>
-      </c>
+      <c r="O709" s="2"/>
     </row>
     <row r="710" spans="1:15" ht="24.95" customHeight="1">
       <c r="A710" s="2" t="s">
-        <v>1221</v>
-      </c>
-      <c r="B710" s="2" t="s">
-        <v>1222</v>
+        <v>1208</v>
       </c>
       <c r="O710" s="2" t="s">
-        <v>1223</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="711" spans="1:15" ht="24.95" customHeight="1">
@@ -18234,88 +18351,88 @@
     </row>
     <row r="712" spans="1:15" ht="24.95" customHeight="1">
       <c r="A712" s="2" t="s">
-        <v>1224</v>
+        <v>1209</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>1777</v>
+        <v>1210</v>
       </c>
       <c r="O712" s="2" t="s">
-        <v>1225</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="713" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O713" s="2"/>
+      <c r="A713" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B713" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="O713" s="2" t="s">
+        <v>1214</v>
+      </c>
     </row>
     <row r="714" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A714" s="2" t="s">
-        <v>1226</v>
-      </c>
-      <c r="O714" s="2" t="s">
-        <v>827</v>
-      </c>
+      <c r="O714" s="2"/>
     </row>
     <row r="715" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O715" s="2"/>
+      <c r="A715" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B715" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="O715" s="2" t="s">
+        <v>1217</v>
+      </c>
     </row>
     <row r="716" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A716" s="2" t="s">
-        <v>1227</v>
-      </c>
-      <c r="B716" s="2" t="s">
-        <v>1776</v>
-      </c>
-      <c r="O716" s="2" t="s">
-        <v>1228</v>
-      </c>
+      <c r="O716" s="2"/>
     </row>
     <row r="717" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O717" s="2"/>
+      <c r="A717" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B717" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="O717" s="2" t="s">
+        <v>1220</v>
+      </c>
     </row>
     <row r="718" spans="1:15" ht="24.95" customHeight="1">
       <c r="A718" s="2" t="s">
-        <v>1229</v>
+        <v>1221</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1230</v>
+        <v>1222</v>
       </c>
       <c r="O718" s="2" t="s">
-        <v>1231</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="719" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A719" s="2" t="s">
-        <v>1232</v>
-      </c>
-      <c r="B719" s="2" t="s">
-        <v>1233</v>
-      </c>
-      <c r="O719" s="2" t="s">
-        <v>1234</v>
-      </c>
+      <c r="O719" s="2"/>
     </row>
     <row r="720" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O720" s="2"/>
+      <c r="A720" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B720" s="2" t="s">
+        <v>1777</v>
+      </c>
+      <c r="O720" s="2" t="s">
+        <v>1225</v>
+      </c>
     </row>
     <row r="721" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A721" s="2" t="s">
-        <v>1235</v>
-      </c>
-      <c r="B721" s="2" t="s">
-        <v>1236</v>
-      </c>
-      <c r="O721" s="2" t="s">
-        <v>1237</v>
-      </c>
+      <c r="O721" s="2"/>
     </row>
     <row r="722" spans="1:15" ht="24.95" customHeight="1">
       <c r="A722" s="2" t="s">
-        <v>1238</v>
-      </c>
-      <c r="B722" s="2" t="s">
-        <v>1239</v>
+        <v>1226</v>
       </c>
       <c r="O722" s="2" t="s">
-        <v>1240</v>
+        <v>827</v>
       </c>
     </row>
     <row r="723" spans="1:15" ht="24.95" customHeight="1">
@@ -18323,46 +18440,38 @@
     </row>
     <row r="724" spans="1:15" ht="24.95" customHeight="1">
       <c r="A724" s="2" t="s">
-        <v>1241</v>
+        <v>1227</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>1242</v>
+        <v>1776</v>
       </c>
       <c r="O724" s="2" t="s">
-        <v>1243</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="725" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A725" s="2" t="s">
-        <v>1244</v>
-      </c>
-      <c r="B725" s="2" t="s">
-        <v>1245</v>
-      </c>
-      <c r="O725" s="2" t="s">
-        <v>1246</v>
-      </c>
+      <c r="O725" s="2"/>
     </row>
     <row r="726" spans="1:15" ht="24.95" customHeight="1">
       <c r="A726" s="2" t="s">
-        <v>1247</v>
+        <v>1229</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>1248</v>
+        <v>1230</v>
       </c>
       <c r="O726" s="2" t="s">
-        <v>1249</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="727" spans="1:15" ht="24.95" customHeight="1">
       <c r="A727" s="2" t="s">
-        <v>1250</v>
+        <v>1232</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>1251</v>
+        <v>1233</v>
       </c>
       <c r="O727" s="2" t="s">
-        <v>1252</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="728" spans="1:15" ht="24.95" customHeight="1">
@@ -18370,84 +18479,132 @@
     </row>
     <row r="729" spans="1:15" ht="24.95" customHeight="1">
       <c r="A729" s="2" t="s">
-        <v>1608</v>
+        <v>1235</v>
+      </c>
+      <c r="B729" s="2" t="s">
+        <v>1236</v>
       </c>
       <c r="O729" s="2" t="s">
-        <v>1610</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="730" spans="1:15" ht="24.95" customHeight="1">
       <c r="A730" s="2" t="s">
-        <v>1609</v>
-      </c>
-      <c r="O730" s="3" t="s">
-        <v>1611</v>
+        <v>1238</v>
+      </c>
+      <c r="B730" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="O730" s="2" t="s">
+        <v>1240</v>
       </c>
     </row>
     <row r="731" spans="1:15" ht="24.95" customHeight="1">
       <c r="O731" s="2"/>
     </row>
     <row r="732" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O732" s="2"/>
+      <c r="A732" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B732" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="O732" s="2" t="s">
+        <v>1243</v>
+      </c>
     </row>
     <row r="733" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O733" s="2"/>
+      <c r="A733" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B733" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="O733" s="2" t="s">
+        <v>1246</v>
+      </c>
     </row>
     <row r="734" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O734" s="2"/>
+      <c r="A734" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B734" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="O734" s="2" t="s">
+        <v>1249</v>
+      </c>
     </row>
     <row r="735" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O735" s="2"/>
+      <c r="A735" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B735" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="O735" s="2" t="s">
+        <v>1252</v>
+      </c>
     </row>
     <row r="736" spans="1:15" ht="24.95" customHeight="1">
       <c r="O736" s="2"/>
     </row>
-    <row r="737" spans="15:15" ht="24.95" customHeight="1">
-      <c r="O737" s="2"/>
-    </row>
-    <row r="738" spans="15:15" ht="24.95" customHeight="1">
-      <c r="O738" s="2"/>
-    </row>
-    <row r="739" spans="15:15" ht="24.95" customHeight="1">
+    <row r="737" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A737" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="O737" s="2" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="738" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A738" s="2" t="s">
+        <v>1609</v>
+      </c>
+      <c r="O738" s="3" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="739" spans="1:15" ht="24.95" customHeight="1">
       <c r="O739" s="2"/>
     </row>
-    <row r="740" spans="15:15" ht="24.95" customHeight="1">
+    <row r="740" spans="1:15" ht="24.95" customHeight="1">
       <c r="O740" s="2"/>
     </row>
-    <row r="741" spans="15:15" ht="24.95" customHeight="1">
+    <row r="741" spans="1:15" ht="24.95" customHeight="1">
       <c r="O741" s="2"/>
     </row>
-    <row r="742" spans="15:15" ht="24.95" customHeight="1">
+    <row r="742" spans="1:15" ht="24.95" customHeight="1">
       <c r="O742" s="2"/>
     </row>
-    <row r="743" spans="15:15" ht="24.95" customHeight="1">
+    <row r="743" spans="1:15" ht="24.95" customHeight="1">
       <c r="O743" s="2"/>
     </row>
-    <row r="744" spans="15:15" ht="24.95" customHeight="1">
+    <row r="744" spans="1:15" ht="24.95" customHeight="1">
       <c r="O744" s="2"/>
     </row>
-    <row r="745" spans="15:15" ht="24.95" customHeight="1">
+    <row r="745" spans="1:15" ht="24.95" customHeight="1">
       <c r="O745" s="2"/>
     </row>
-    <row r="746" spans="15:15" ht="24.95" customHeight="1">
+    <row r="746" spans="1:15" ht="24.95" customHeight="1">
       <c r="O746" s="2"/>
     </row>
-    <row r="747" spans="15:15" ht="24.95" customHeight="1">
+    <row r="747" spans="1:15" ht="24.95" customHeight="1">
       <c r="O747" s="2"/>
     </row>
-    <row r="748" spans="15:15" ht="24.95" customHeight="1">
+    <row r="748" spans="1:15" ht="24.95" customHeight="1">
       <c r="O748" s="2"/>
     </row>
-    <row r="749" spans="15:15" ht="24.95" customHeight="1">
+    <row r="749" spans="1:15" ht="24.95" customHeight="1">
       <c r="O749" s="2"/>
     </row>
-    <row r="750" spans="15:15" ht="24.95" customHeight="1">
+    <row r="750" spans="1:15" ht="24.95" customHeight="1">
       <c r="O750" s="2"/>
     </row>
-    <row r="751" spans="15:15" ht="24.95" customHeight="1">
+    <row r="751" spans="1:15" ht="24.95" customHeight="1">
       <c r="O751" s="2"/>
     </row>
-    <row r="752" spans="15:15" ht="24.95" customHeight="1">
+    <row r="752" spans="1:15" ht="24.95" customHeight="1">
       <c r="O752" s="2"/>
     </row>
     <row r="753" spans="15:15" ht="24.95" customHeight="1">
@@ -18675,6 +18832,9 @@
     <row r="827" spans="15:15" ht="24.95" customHeight="1">
       <c r="O827" s="2"/>
     </row>
+    <row r="828" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O828" s="2"/>
+    </row>
     <row r="829" spans="15:15" ht="24.95" customHeight="1">
       <c r="O829" s="2"/>
     </row>
@@ -18696,9 +18856,6 @@
     <row r="835" spans="15:15" ht="24.95" customHeight="1">
       <c r="O835" s="2"/>
     </row>
-    <row r="836" spans="15:15" ht="24.95" customHeight="1">
-      <c r="O836" s="2"/>
-    </row>
     <row r="837" spans="15:15" ht="24.95" customHeight="1">
       <c r="O837" s="2"/>
     </row>
@@ -19855,20 +20012,7 @@
       <c r="O1221" s="2"/>
     </row>
     <row r="1222" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A1222" s="5"/>
-      <c r="B1222" s="5"/>
-      <c r="D1222" s="5"/>
-      <c r="E1222" s="5"/>
-      <c r="F1222" s="5"/>
-      <c r="G1222" s="5"/>
-      <c r="H1222" s="5"/>
-      <c r="I1222" s="5"/>
-      <c r="J1222" s="5"/>
-      <c r="K1222" s="5"/>
-      <c r="L1222" s="5"/>
-      <c r="M1222" s="5"/>
-      <c r="N1222" s="5"/>
-      <c r="O1222" s="6"/>
+      <c r="O1222" s="2"/>
     </row>
     <row r="1223" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1223" s="2"/>
@@ -19892,7 +20036,20 @@
       <c r="O1229" s="2"/>
     </row>
     <row r="1230" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O1230" s="2"/>
+      <c r="A1230" s="5"/>
+      <c r="B1230" s="5"/>
+      <c r="D1230" s="5"/>
+      <c r="E1230" s="5"/>
+      <c r="F1230" s="5"/>
+      <c r="G1230" s="5"/>
+      <c r="H1230" s="5"/>
+      <c r="I1230" s="5"/>
+      <c r="J1230" s="5"/>
+      <c r="K1230" s="5"/>
+      <c r="L1230" s="5"/>
+      <c r="M1230" s="5"/>
+      <c r="N1230" s="5"/>
+      <c r="O1230" s="6"/>
     </row>
     <row r="1231" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1231" s="2"/>
@@ -21385,8 +21542,32 @@
     <row r="1727" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1727" s="2"/>
     </row>
+    <row r="1728" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1728" s="2"/>
+    </row>
+    <row r="1729" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1729" s="2"/>
+    </row>
+    <row r="1730" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1730" s="2"/>
+    </row>
+    <row r="1731" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1731" s="2"/>
+    </row>
+    <row r="1732" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1732" s="2"/>
+    </row>
+    <row r="1733" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1733" s="2"/>
+    </row>
+    <row r="1734" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1734" s="2"/>
+    </row>
+    <row r="1735" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1735" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="O1:O1430" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="O1:O1438" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -21467,7 +21648,7 @@
         <v>1253</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>3034</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="54">
@@ -21475,7 +21656,7 @@
         <v>1254</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3035</v>
+        <v>3033</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>2774</v>
@@ -21541,7 +21722,7 @@
         <v>1269</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>3036</v>
+        <v>3034</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>2789</v>
@@ -21912,35 +22093,35 @@
     </row>
     <row r="53" spans="1:15" ht="24.95" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="24.95" customHeight="1">
       <c r="A54" s="1" t="s">
+        <v>2923</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>2924</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>2925</v>
-      </c>
       <c r="O54" s="1" t="s">
-        <v>3007</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="24.95" customHeight="1">
       <c r="A55" s="1" t="s">
+        <v>2921</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>2922</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>2923</v>
-      </c>
       <c r="O55" s="1" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="24.95" customHeight="1">
@@ -21989,186 +22170,186 @@
     </row>
     <row r="62" spans="1:15" ht="24.95" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="24.95" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="24.95" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="24.95" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="24.95" customHeight="1">
       <c r="A66" s="1" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="24.95" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="24.95" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="24.95" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>3027</v>
+        <v>3025</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>3028</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="24.95" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="24.95" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="24.95" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="24.95" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="24.95" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="24.95" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="24.95" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="24.95" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="24.95" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="24.95" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="24.95" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="81" spans="1:15" ht="24.95" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="24.95" customHeight="1">
       <c r="A82" s="1" t="s">
+        <v>2979</v>
+      </c>
+      <c r="O82" s="1" t="s">
         <v>2980</v>
-      </c>
-      <c r="O82" s="1" t="s">
-        <v>2981</v>
       </c>
     </row>
     <row r="83" spans="1:15" ht="24.95" customHeight="1">
       <c r="A83" s="1" t="s">
+        <v>2981</v>
+      </c>
+      <c r="O83" s="1" t="s">
         <v>2982</v>
-      </c>
-      <c r="O83" s="1" t="s">
-        <v>2983</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="24.95" customHeight="1">
       <c r="A84" s="1" t="s">
+        <v>2983</v>
+      </c>
+      <c r="O84" s="1" t="s">
         <v>2984</v>
-      </c>
-      <c r="O84" s="1" t="s">
-        <v>2985</v>
       </c>
     </row>
   </sheetData>
@@ -22260,7 +22441,7 @@
         <v>1322</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>3029</v>
+        <v>3027</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="16.5">
@@ -22271,7 +22452,7 @@
         <v>1324</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>3030</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="16.5">
@@ -22282,7 +22463,7 @@
         <v>1326</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>3031</v>
+        <v>3029</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="16.5">
@@ -22304,7 +22485,7 @@
         <v>1330</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>3032</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="16.5">
@@ -22315,7 +22496,7 @@
         <v>1332</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>3033</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="16.5">
@@ -22701,7 +22882,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:S91"/>
+  <dimension ref="A1:S93"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21.5" style="2" customWidth="1"/>
@@ -23076,7 +23257,7 @@
     </row>
     <row r="29" spans="1:15" ht="20.100000000000001" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>3022</v>
+        <v>3020</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>1502</v>
@@ -23764,13 +23945,35 @@
     </row>
     <row r="91" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A91" s="2" t="s">
+        <v>3090</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>2914</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="O91" s="2" t="s">
         <v>2915</v>
       </c>
-      <c r="O91" s="2" t="s">
-        <v>2916</v>
+    </row>
+    <row r="92" spans="1:19" ht="20.100000000000001" customHeight="1">
+      <c r="A92" s="2" t="s">
+        <v>3093</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>3094</v>
+      </c>
+      <c r="O92" s="2" t="s">
+        <v>3095</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" ht="20.100000000000001" customHeight="1">
+      <c r="A93" s="2" t="s">
+        <v>3106</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>3096</v>
+      </c>
+      <c r="O93" s="2" t="s">
+        <v>3082</v>
       </c>
     </row>
   </sheetData>
@@ -23781,7 +23984,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:Q427"/>
+  <dimension ref="A1:Q431"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="27.875" style="7" customWidth="1"/>
@@ -23920,23 +24123,29 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="7" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>2991</v>
+      </c>
+      <c r="O13" s="7" t="s">
         <v>2992</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>2994</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="7" t="s">
-        <v>2995</v>
+        <v>2993</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>3097</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="7" t="s">
-        <v>2996</v>
+        <v>2994</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>3098</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -24765,7 +24974,7 @@
         <v>2912</v>
       </c>
       <c r="O138" s="7" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="139" spans="1:15">
@@ -24773,7 +24982,7 @@
         <v>2913</v>
       </c>
       <c r="O139" s="7" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
     </row>
     <row r="141" spans="1:15">
@@ -25048,29 +25257,29 @@
     </row>
     <row r="181" spans="1:15">
       <c r="A181" s="7" t="s">
-        <v>3018</v>
+        <v>3016</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>3018</v>
+        <v>3016</v>
       </c>
       <c r="O181" s="7" t="s">
-        <v>3044</v>
+        <v>3042</v>
       </c>
     </row>
     <row r="182" spans="1:15">
       <c r="A182" s="7" t="s">
-        <v>3020</v>
+        <v>3018</v>
       </c>
       <c r="O182" s="7" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="183" spans="1:15">
       <c r="A183" s="7" t="s">
+        <v>3017</v>
+      </c>
+      <c r="O183" s="7" t="s">
         <v>3019</v>
-      </c>
-      <c r="O183" s="7" t="s">
-        <v>3021</v>
       </c>
     </row>
     <row r="185" spans="1:15">
@@ -25831,874 +26040,874 @@
     </row>
     <row r="297" spans="1:15">
       <c r="A297" s="7" t="s">
-        <v>2154</v>
+        <v>3103</v>
       </c>
       <c r="B297" s="7" t="s">
-        <v>2154</v>
+        <v>3103</v>
       </c>
       <c r="O297" s="7" t="s">
-        <v>2155</v>
+        <v>3087</v>
       </c>
     </row>
     <row r="298" spans="1:15">
       <c r="A298" s="7" t="s">
-        <v>2156</v>
+        <v>3085</v>
       </c>
       <c r="O298" s="7" t="s">
-        <v>2734</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="299" spans="1:15">
       <c r="A299" s="7" t="s">
-        <v>2157</v>
+        <v>3086</v>
       </c>
       <c r="O299" s="7" t="s">
-        <v>2158</v>
+        <v>3099</v>
       </c>
     </row>
     <row r="301" spans="1:15">
       <c r="A301" s="7" t="s">
-        <v>2159</v>
+        <v>2154</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>2735</v>
+        <v>2154</v>
       </c>
       <c r="O301" s="7" t="s">
-        <v>2160</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="302" spans="1:15">
       <c r="A302" s="7" t="s">
-        <v>2161</v>
+        <v>2156</v>
       </c>
       <c r="O302" s="7" t="s">
-        <v>2736</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="303" spans="1:15">
       <c r="A303" s="7" t="s">
-        <v>2162</v>
+        <v>2157</v>
       </c>
       <c r="O303" s="7" t="s">
-        <v>2737</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="305" spans="1:15">
       <c r="A305" s="7" t="s">
-        <v>2163</v>
+        <v>2159</v>
       </c>
       <c r="B305" s="7" t="s">
-        <v>2163</v>
+        <v>2735</v>
       </c>
       <c r="O305" s="7" t="s">
-        <v>2164</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="306" spans="1:15">
       <c r="A306" s="7" t="s">
-        <v>2165</v>
+        <v>2161</v>
       </c>
       <c r="O306" s="7" t="s">
-        <v>2166</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="307" spans="1:15">
       <c r="A307" s="7" t="s">
-        <v>2167</v>
+        <v>2162</v>
       </c>
       <c r="O307" s="7" t="s">
-        <v>2168</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="309" spans="1:15">
       <c r="A309" s="7" t="s">
-        <v>3000</v>
+        <v>2163</v>
       </c>
       <c r="B309" s="7" t="s">
-        <v>2999</v>
+        <v>2163</v>
       </c>
       <c r="O309" s="7" t="s">
-        <v>3001</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="310" spans="1:15">
       <c r="A310" s="7" t="s">
-        <v>3008</v>
+        <v>2165</v>
       </c>
       <c r="O310" s="7" t="s">
-        <v>3004</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="311" spans="1:15">
       <c r="A311" s="7" t="s">
-        <v>3009</v>
+        <v>2167</v>
       </c>
       <c r="O311" s="7" t="s">
-        <v>3003</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="313" spans="1:15">
       <c r="A313" s="7" t="s">
-        <v>2169</v>
+        <v>2998</v>
       </c>
       <c r="B313" s="7" t="s">
-        <v>2169</v>
+        <v>2997</v>
       </c>
       <c r="O313" s="7" t="s">
-        <v>2170</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="314" spans="1:15">
       <c r="A314" s="7" t="s">
-        <v>2171</v>
+        <v>3006</v>
       </c>
       <c r="O314" s="7" t="s">
-        <v>2172</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="315" spans="1:15">
       <c r="A315" s="7" t="s">
-        <v>2173</v>
+        <v>3007</v>
       </c>
       <c r="O315" s="7" t="s">
-        <v>2738</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="317" spans="1:15">
       <c r="A317" s="7" t="s">
-        <v>2174</v>
+        <v>2169</v>
       </c>
       <c r="B317" s="7" t="s">
-        <v>2174</v>
+        <v>2169</v>
       </c>
       <c r="O317" s="7" t="s">
-        <v>2175</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="318" spans="1:15">
       <c r="A318" s="7" t="s">
-        <v>2176</v>
+        <v>2171</v>
       </c>
       <c r="O318" s="7" t="s">
-        <v>2786</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="319" spans="1:15">
       <c r="A319" s="7" t="s">
-        <v>2177</v>
+        <v>2173</v>
       </c>
       <c r="O319" s="7" t="s">
-        <v>2786</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="321" spans="1:15">
       <c r="A321" s="7" t="s">
-        <v>2178</v>
+        <v>2174</v>
       </c>
       <c r="B321" s="7" t="s">
-        <v>2178</v>
+        <v>2174</v>
       </c>
       <c r="O321" s="7" t="s">
-        <v>2179</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="322" spans="1:15">
       <c r="A322" s="7" t="s">
-        <v>2180</v>
+        <v>2176</v>
       </c>
       <c r="O322" s="7" t="s">
-        <v>2739</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="323" spans="1:15">
       <c r="A323" s="7" t="s">
-        <v>2181</v>
+        <v>2177</v>
       </c>
       <c r="O323" s="7" t="s">
-        <v>2182</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="325" spans="1:15">
       <c r="A325" s="7" t="s">
-        <v>2183</v>
+        <v>2178</v>
       </c>
       <c r="B325" s="7" t="s">
-        <v>2183</v>
+        <v>2178</v>
       </c>
       <c r="O325" s="7" t="s">
-        <v>2184</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="326" spans="1:15">
       <c r="A326" s="7" t="s">
-        <v>2185</v>
+        <v>2180</v>
       </c>
       <c r="O326" s="7" t="s">
-        <v>2740</v>
+        <v>2739</v>
       </c>
     </row>
     <row r="327" spans="1:15">
       <c r="A327" s="7" t="s">
-        <v>2186</v>
+        <v>2181</v>
       </c>
       <c r="O327" s="7" t="s">
-        <v>2741</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="329" spans="1:15">
       <c r="A329" s="7" t="s">
-        <v>2187</v>
+        <v>2183</v>
       </c>
       <c r="B329" s="7" t="s">
-        <v>2187</v>
+        <v>2183</v>
       </c>
       <c r="O329" s="7" t="s">
-        <v>2188</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="330" spans="1:15">
       <c r="A330" s="7" t="s">
-        <v>2189</v>
+        <v>2185</v>
       </c>
       <c r="O330" s="7" t="s">
-        <v>2190</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="331" spans="1:15">
       <c r="A331" s="7" t="s">
-        <v>2191</v>
+        <v>2186</v>
       </c>
       <c r="O331" s="7" t="s">
-        <v>2192</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="333" spans="1:15">
       <c r="A333" s="7" t="s">
-        <v>2193</v>
+        <v>2187</v>
       </c>
       <c r="B333" s="7" t="s">
-        <v>2193</v>
+        <v>2187</v>
       </c>
       <c r="O333" s="7" t="s">
-        <v>2194</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="334" spans="1:15">
       <c r="A334" s="7" t="s">
-        <v>2195</v>
+        <v>2189</v>
       </c>
       <c r="O334" s="7" t="s">
-        <v>2742</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="335" spans="1:15">
       <c r="A335" s="7" t="s">
-        <v>2196</v>
+        <v>2191</v>
       </c>
       <c r="O335" s="7" t="s">
-        <v>2197</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="337" spans="1:15">
       <c r="A337" s="7" t="s">
-        <v>2198</v>
+        <v>2193</v>
       </c>
       <c r="B337" s="7" t="s">
-        <v>2198</v>
+        <v>2193</v>
       </c>
       <c r="O337" s="7" t="s">
-        <v>2199</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="338" spans="1:15">
       <c r="A338" s="7" t="s">
-        <v>2200</v>
+        <v>2195</v>
       </c>
       <c r="O338" s="7" t="s">
-        <v>2201</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="339" spans="1:15">
       <c r="A339" s="7" t="s">
-        <v>2202</v>
+        <v>2196</v>
       </c>
       <c r="O339" s="7" t="s">
-        <v>2743</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="341" spans="1:15">
       <c r="A341" s="7" t="s">
-        <v>2203</v>
+        <v>2198</v>
       </c>
       <c r="B341" s="7" t="s">
-        <v>2203</v>
+        <v>2198</v>
       </c>
       <c r="O341" s="7" t="s">
-        <v>2204</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="342" spans="1:15">
       <c r="A342" s="7" t="s">
-        <v>2205</v>
+        <v>2200</v>
       </c>
       <c r="O342" s="7" t="s">
-        <v>2206</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="343" spans="1:15">
       <c r="A343" s="7" t="s">
-        <v>2207</v>
+        <v>2202</v>
       </c>
       <c r="O343" s="7" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="345" spans="1:15">
       <c r="A345" s="7" t="s">
-        <v>2208</v>
+        <v>2203</v>
       </c>
       <c r="B345" s="7" t="s">
-        <v>2208</v>
+        <v>2203</v>
       </c>
       <c r="O345" s="7" t="s">
-        <v>2209</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="346" spans="1:15">
       <c r="A346" s="7" t="s">
-        <v>2210</v>
+        <v>2205</v>
       </c>
       <c r="O346" s="7" t="s">
-        <v>2745</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="347" spans="1:15">
       <c r="A347" s="7" t="s">
-        <v>2211</v>
+        <v>2207</v>
       </c>
       <c r="O347" s="7" t="s">
-        <v>2212</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="349" spans="1:15">
       <c r="A349" s="7" t="s">
-        <v>2213</v>
+        <v>2208</v>
       </c>
       <c r="B349" s="7" t="s">
-        <v>2213</v>
+        <v>2208</v>
       </c>
       <c r="O349" s="7" t="s">
-        <v>2214</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="350" spans="1:15">
       <c r="A350" s="7" t="s">
-        <v>2215</v>
+        <v>2210</v>
       </c>
       <c r="O350" s="7" t="s">
-        <v>2216</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="351" spans="1:15">
       <c r="A351" s="7" t="s">
-        <v>2217</v>
+        <v>2211</v>
       </c>
       <c r="O351" s="7" t="s">
-        <v>2216</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="353" spans="1:15">
       <c r="A353" s="7" t="s">
-        <v>2218</v>
+        <v>2213</v>
       </c>
       <c r="B353" s="7" t="s">
-        <v>2218</v>
+        <v>2213</v>
       </c>
       <c r="O353" s="7" t="s">
-        <v>2219</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="354" spans="1:15">
       <c r="A354" s="7" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
       <c r="O354" s="7" t="s">
-        <v>2221</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="355" spans="1:15">
       <c r="A355" s="7" t="s">
-        <v>2222</v>
+        <v>2217</v>
       </c>
       <c r="O355" s="7" t="s">
-        <v>2746</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="357" spans="1:15">
       <c r="A357" s="7" t="s">
-        <v>2223</v>
+        <v>2218</v>
       </c>
       <c r="B357" s="7" t="s">
-        <v>2223</v>
+        <v>2218</v>
       </c>
       <c r="O357" s="7" t="s">
-        <v>2224</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="358" spans="1:15">
       <c r="A358" s="7" t="s">
-        <v>2225</v>
+        <v>2220</v>
       </c>
       <c r="O358" s="7" t="s">
-        <v>2747</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="359" spans="1:15">
       <c r="A359" s="7" t="s">
-        <v>2226</v>
+        <v>2222</v>
       </c>
       <c r="O359" s="7" t="s">
-        <v>2227</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="361" spans="1:15">
       <c r="A361" s="7" t="s">
-        <v>2228</v>
+        <v>2223</v>
       </c>
       <c r="B361" s="7" t="s">
-        <v>2229</v>
+        <v>2223</v>
       </c>
       <c r="O361" s="7" t="s">
-        <v>2229</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="362" spans="1:15">
       <c r="A362" s="7" t="s">
-        <v>2230</v>
+        <v>2225</v>
       </c>
       <c r="O362" s="7" t="s">
-        <v>2231</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="363" spans="1:15">
       <c r="A363" s="7" t="s">
-        <v>2232</v>
+        <v>2226</v>
       </c>
       <c r="O363" s="7" t="s">
-        <v>2748</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="365" spans="1:15">
       <c r="A365" s="7" t="s">
-        <v>2233</v>
+        <v>2228</v>
       </c>
       <c r="B365" s="7" t="s">
-        <v>2233</v>
+        <v>2229</v>
       </c>
       <c r="O365" s="7" t="s">
-        <v>2234</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="366" spans="1:15">
       <c r="A366" s="7" t="s">
-        <v>2235</v>
+        <v>2230</v>
       </c>
       <c r="O366" s="7" t="s">
-        <v>2749</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="367" spans="1:15">
       <c r="A367" s="7" t="s">
-        <v>2236</v>
+        <v>2232</v>
       </c>
       <c r="O367" s="7" t="s">
-        <v>2750</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="369" spans="1:15">
       <c r="A369" s="7" t="s">
-        <v>2237</v>
+        <v>2233</v>
       </c>
       <c r="B369" s="7" t="s">
-        <v>2237</v>
+        <v>2233</v>
       </c>
       <c r="O369" s="7" t="s">
-        <v>2238</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="370" spans="1:15">
       <c r="A370" s="7" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="O370" s="7" t="s">
-        <v>2240</v>
+        <v>2749</v>
       </c>
     </row>
     <row r="371" spans="1:15">
       <c r="A371" s="7" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="O371" s="7" t="s">
-        <v>2751</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="373" spans="1:15">
       <c r="A373" s="7" t="s">
-        <v>2242</v>
+        <v>2237</v>
       </c>
       <c r="B373" s="7" t="s">
-        <v>2242</v>
+        <v>2237</v>
       </c>
       <c r="O373" s="7" t="s">
-        <v>2243</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="374" spans="1:15">
       <c r="A374" s="7" t="s">
-        <v>2244</v>
+        <v>2239</v>
       </c>
       <c r="O374" s="7" t="s">
-        <v>2752</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="375" spans="1:15">
       <c r="A375" s="7" t="s">
-        <v>2245</v>
+        <v>2241</v>
       </c>
       <c r="O375" s="7" t="s">
-        <v>2246</v>
+        <v>2751</v>
       </c>
     </row>
     <row r="377" spans="1:15">
       <c r="A377" s="7" t="s">
-        <v>2247</v>
+        <v>2242</v>
       </c>
       <c r="B377" s="7" t="s">
-        <v>2247</v>
+        <v>2242</v>
       </c>
       <c r="O377" s="7" t="s">
-        <v>2248</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="378" spans="1:15">
       <c r="A378" s="7" t="s">
-        <v>2249</v>
+        <v>2244</v>
       </c>
       <c r="O378" s="7" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="379" spans="1:15">
       <c r="A379" s="7" t="s">
-        <v>2250</v>
+        <v>2245</v>
       </c>
       <c r="O379" s="7" t="s">
-        <v>2754</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="381" spans="1:15">
       <c r="A381" s="7" t="s">
-        <v>1836</v>
+        <v>2247</v>
       </c>
       <c r="B381" s="7" t="s">
-        <v>1836</v>
+        <v>2247</v>
       </c>
       <c r="O381" s="7" t="s">
-        <v>2251</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="382" spans="1:15">
       <c r="A382" s="7" t="s">
-        <v>2252</v>
+        <v>2249</v>
       </c>
       <c r="O382" s="7" t="s">
-        <v>2253</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="383" spans="1:15">
       <c r="A383" s="7" t="s">
-        <v>2254</v>
+        <v>2250</v>
       </c>
       <c r="O383" s="7" t="s">
-        <v>2755</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="385" spans="1:15">
       <c r="A385" s="7" t="s">
-        <v>2255</v>
+        <v>1836</v>
       </c>
       <c r="B385" s="7" t="s">
-        <v>2255</v>
+        <v>1836</v>
       </c>
       <c r="O385" s="7" t="s">
-        <v>2256</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="386" spans="1:15">
       <c r="A386" s="7" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
       <c r="O386" s="7" t="s">
-        <v>2258</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="387" spans="1:15">
       <c r="A387" s="7" t="s">
-        <v>2259</v>
+        <v>2254</v>
       </c>
       <c r="O387" s="7" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="389" spans="1:15">
       <c r="A389" s="7" t="s">
-        <v>2260</v>
+        <v>2255</v>
       </c>
       <c r="B389" s="7" t="s">
-        <v>2260</v>
+        <v>2255</v>
       </c>
       <c r="O389" s="7" t="s">
-        <v>2261</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="390" spans="1:15">
       <c r="A390" s="7" t="s">
-        <v>2262</v>
+        <v>2257</v>
       </c>
       <c r="O390" s="7" t="s">
-        <v>2757</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="391" spans="1:15">
       <c r="A391" s="7" t="s">
-        <v>2263</v>
+        <v>2259</v>
       </c>
       <c r="O391" s="7" t="s">
-        <v>2758</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="393" spans="1:15">
       <c r="A393" s="7" t="s">
-        <v>2264</v>
+        <v>2260</v>
       </c>
       <c r="B393" s="7" t="s">
-        <v>2264</v>
+        <v>2260</v>
       </c>
       <c r="O393" s="7" t="s">
-        <v>2265</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="394" spans="1:15">
       <c r="A394" s="7" t="s">
-        <v>2266</v>
+        <v>2262</v>
       </c>
       <c r="O394" s="7" t="s">
-        <v>2267</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="395" spans="1:15">
       <c r="A395" s="7" t="s">
-        <v>2268</v>
+        <v>2263</v>
       </c>
       <c r="O395" s="7" t="s">
-        <v>2269</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="397" spans="1:15">
       <c r="A397" s="7" t="s">
-        <v>2270</v>
+        <v>2264</v>
       </c>
       <c r="B397" s="7" t="s">
-        <v>2759</v>
+        <v>2264</v>
       </c>
       <c r="O397" s="7" t="s">
-        <v>2271</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="398" spans="1:15">
       <c r="A398" s="7" t="s">
-        <v>2272</v>
+        <v>2266</v>
       </c>
       <c r="O398" s="7" t="s">
-        <v>2760</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="399" spans="1:15">
       <c r="A399" s="7" t="s">
-        <v>2273</v>
+        <v>2268</v>
       </c>
       <c r="O399" s="7" t="s">
-        <v>2760</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="401" spans="1:15">
       <c r="A401" s="7" t="s">
-        <v>2274</v>
+        <v>2270</v>
       </c>
       <c r="B401" s="7" t="s">
-        <v>2274</v>
+        <v>2759</v>
       </c>
       <c r="O401" s="7" t="s">
-        <v>2275</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="402" spans="1:15">
       <c r="A402" s="7" t="s">
-        <v>2276</v>
+        <v>2272</v>
       </c>
       <c r="O402" s="7" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="403" spans="1:15">
       <c r="A403" s="7" t="s">
-        <v>2277</v>
+        <v>2273</v>
       </c>
       <c r="O403" s="7" t="s">
-        <v>2278</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="405" spans="1:15">
       <c r="A405" s="7" t="s">
-        <v>2279</v>
+        <v>2274</v>
       </c>
       <c r="B405" s="7" t="s">
-        <v>2279</v>
+        <v>2274</v>
       </c>
       <c r="O405" s="7" t="s">
-        <v>2280</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="406" spans="1:15">
       <c r="A406" s="7" t="s">
-        <v>2281</v>
+        <v>2276</v>
       </c>
       <c r="O406" s="7" t="s">
-        <v>2282</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="407" spans="1:15">
       <c r="A407" s="7" t="s">
-        <v>2283</v>
+        <v>2277</v>
       </c>
       <c r="O407" s="7" t="s">
-        <v>2284</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="409" spans="1:15">
       <c r="A409" s="7" t="s">
-        <v>2887</v>
+        <v>2279</v>
       </c>
       <c r="B409" s="7" t="s">
-        <v>2887</v>
+        <v>2279</v>
       </c>
       <c r="O409" s="7" t="s">
-        <v>2890</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="410" spans="1:15">
       <c r="A410" s="7" t="s">
-        <v>2888</v>
+        <v>2281</v>
       </c>
       <c r="O410" s="7" t="s">
-        <v>2891</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="411" spans="1:15">
       <c r="A411" s="7" t="s">
-        <v>2889</v>
+        <v>2283</v>
       </c>
       <c r="O411" s="7" t="s">
-        <v>2891</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="413" spans="1:15">
       <c r="A413" s="7" t="s">
-        <v>2897</v>
+        <v>2887</v>
       </c>
       <c r="B413" s="7" t="s">
-        <v>2897</v>
+        <v>2887</v>
       </c>
       <c r="O413" s="7" t="s">
-        <v>2900</v>
+        <v>2890</v>
       </c>
     </row>
     <row r="414" spans="1:15">
       <c r="A414" s="7" t="s">
-        <v>2898</v>
+        <v>2888</v>
       </c>
       <c r="O414" s="7" t="s">
-        <v>2901</v>
+        <v>2891</v>
       </c>
     </row>
     <row r="415" spans="1:15">
       <c r="A415" s="7" t="s">
-        <v>2899</v>
+        <v>2889</v>
       </c>
       <c r="O415" s="7" t="s">
-        <v>2901</v>
+        <v>2891</v>
       </c>
     </row>
     <row r="417" spans="1:15">
       <c r="A417" s="7" t="s">
-        <v>2285</v>
+        <v>2897</v>
       </c>
       <c r="B417" s="7" t="s">
-        <v>2285</v>
+        <v>2897</v>
       </c>
       <c r="O417" s="7" t="s">
-        <v>2286</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="418" spans="1:15">
       <c r="A418" s="7" t="s">
-        <v>2287</v>
+        <v>2898</v>
       </c>
       <c r="O418" s="7" t="s">
-        <v>2762</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="419" spans="1:15">
       <c r="A419" s="7" t="s">
-        <v>2288</v>
+        <v>2899</v>
       </c>
       <c r="O419" s="7" t="s">
-        <v>2762</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="421" spans="1:15">
       <c r="A421" s="7" t="s">
-        <v>2289</v>
+        <v>2285</v>
       </c>
       <c r="B421" s="7" t="s">
-        <v>2289</v>
+        <v>2285</v>
       </c>
       <c r="O421" s="7" t="s">
-        <v>2290</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="422" spans="1:15">
       <c r="A422" s="7" t="s">
-        <v>2291</v>
+        <v>2287</v>
       </c>
       <c r="O422" s="7" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="423" spans="1:15">
       <c r="A423" s="7" t="s">
-        <v>2292</v>
+        <v>2288</v>
       </c>
       <c r="O423" s="7" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="425" spans="1:15">
       <c r="A425" s="7" t="s">
-        <v>2293</v>
+        <v>2289</v>
       </c>
       <c r="B425" s="7" t="s">
-        <v>2293</v>
+        <v>2289</v>
       </c>
       <c r="O425" s="7" t="s">
         <v>2290</v>
@@ -26706,17 +26915,44 @@
     </row>
     <row r="426" spans="1:15">
       <c r="A426" s="7" t="s">
-        <v>2294</v>
+        <v>2291</v>
       </c>
       <c r="O426" s="7" t="s">
-        <v>2764</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="427" spans="1:15">
       <c r="A427" s="7" t="s">
+        <v>2292</v>
+      </c>
+      <c r="O427" s="7" t="s">
+        <v>2763</v>
+      </c>
+    </row>
+    <row r="429" spans="1:15">
+      <c r="A429" s="7" t="s">
+        <v>2293</v>
+      </c>
+      <c r="B429" s="7" t="s">
+        <v>2293</v>
+      </c>
+      <c r="O429" s="7" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="430" spans="1:15">
+      <c r="A430" s="7" t="s">
+        <v>2294</v>
+      </c>
+      <c r="O430" s="7" t="s">
+        <v>2764</v>
+      </c>
+    </row>
+    <row r="431" spans="1:15">
+      <c r="A431" s="7" t="s">
         <v>2295</v>
       </c>
-      <c r="O427" s="7" t="s">
+      <c r="O431" s="7" t="s">
         <v>2764</v>
       </c>
     </row>
@@ -26729,7 +26965,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:Q108"/>
+  <dimension ref="A1:Q110"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="60" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.625" style="8" customWidth="1"/>
@@ -26801,10 +27037,10 @@
     </row>
     <row r="3" spans="1:17" ht="60" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>3005</v>
+        <v>3003</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>3006</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="60" customHeight="1">
@@ -26828,7 +27064,7 @@
         <v>2335</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="60" customHeight="1">
@@ -26956,7 +27192,7 @@
         <v>2349</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="60" customHeight="1">
@@ -26991,636 +27227,652 @@
         <v>2810</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="60" customHeight="1">
-      <c r="A28" s="8" t="s">
-        <v>1719</v>
-      </c>
-      <c r="O28" s="9" t="s">
-        <v>2811</v>
+    <row r="27" spans="1:15" ht="60" customHeight="1">
+      <c r="A27" s="8" t="s">
+        <v>3101</v>
+      </c>
+      <c r="O27" s="9" t="s">
+        <v>3102</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="60" customHeight="1">
       <c r="A29" s="8" t="s">
-        <v>2533</v>
+        <v>1719</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>2532</v>
+        <v>2811</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="60" customHeight="1">
       <c r="A30" s="8" t="s">
-        <v>1718</v>
+        <v>2533</v>
       </c>
       <c r="O30" s="9" t="s">
-        <v>2812</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="60" customHeight="1">
       <c r="A31" s="8" t="s">
-        <v>2352</v>
+        <v>1718</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="60" customHeight="1">
       <c r="A32" s="8" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="O32" s="9" t="s">
-        <v>2330</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="60" customHeight="1">
       <c r="A33" s="8" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>2814</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="60" customHeight="1">
       <c r="A34" s="8" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="O34" s="9" t="s">
-        <v>2815</v>
+        <v>2814</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="60" customHeight="1">
       <c r="A35" s="8" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>2816</v>
+        <v>2815</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="60" customHeight="1">
       <c r="A36" s="8" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="O36" s="9" t="s">
-        <v>2817</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="60" customHeight="1">
       <c r="A37" s="8" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>2818</v>
+        <v>2817</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="60" customHeight="1">
       <c r="A38" s="8" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="O38" s="9" t="s">
-        <v>2819</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="60" customHeight="1">
       <c r="A39" s="8" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="60" customHeight="1">
       <c r="A40" s="8" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="O40" s="9" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="60" customHeight="1">
       <c r="A41" s="8" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>2998</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="60" customHeight="1">
       <c r="A42" s="8" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="O42" s="9" t="s">
-        <v>2822</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="60" customHeight="1">
       <c r="A43" s="8" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>2823</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="60" customHeight="1">
       <c r="A44" s="8" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="O44" s="9" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="60" customHeight="1">
       <c r="A45" s="8" t="s">
-        <v>3023</v>
+        <v>2365</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>3046</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="60" customHeight="1">
       <c r="A46" s="8" t="s">
-        <v>2366</v>
+        <v>3021</v>
       </c>
       <c r="O46" s="9" t="s">
-        <v>2825</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="60" customHeight="1">
       <c r="A47" s="8" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>2826</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="60" customHeight="1">
       <c r="A48" s="8" t="s">
-        <v>2926</v>
+        <v>2367</v>
       </c>
       <c r="O48" s="9" t="s">
-        <v>2934</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" ht="60" customHeight="1">
-      <c r="A50" s="8" t="s">
-        <v>2368</v>
-      </c>
-      <c r="O50" s="9" t="s">
-        <v>2827</v>
+        <v>2826</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="60" customHeight="1">
+      <c r="A49" s="8" t="s">
+        <v>2925</v>
+      </c>
+      <c r="O49" s="9" t="s">
+        <v>2933</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="60" customHeight="1">
       <c r="A51" s="8" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="60" customHeight="1">
       <c r="A52" s="8" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="O52" s="9" t="s">
-        <v>2781</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="60" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>2829</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="60" customHeight="1">
       <c r="A54" s="8" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="O54" s="9" t="s">
-        <v>2830</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="60" customHeight="1">
       <c r="A55" s="8" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>2780</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="60" customHeight="1">
       <c r="A56" s="8" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="O56" s="9" t="s">
-        <v>2831</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="60" customHeight="1">
       <c r="A57" s="8" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>2832</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="60" customHeight="1">
       <c r="A58" s="8" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="O58" s="9" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="60" customHeight="1">
       <c r="A59" s="8" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="60" customHeight="1">
       <c r="A60" s="8" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="O60" s="9" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="60" customHeight="1">
       <c r="A61" s="8" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="60" customHeight="1">
       <c r="A62" s="8" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="O62" s="9" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="60" customHeight="1">
       <c r="A63" s="8" t="s">
-        <v>2872</v>
+        <v>2380</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="60" customHeight="1">
       <c r="A64" s="8" t="s">
-        <v>2381</v>
+        <v>2872</v>
       </c>
       <c r="O64" s="9" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="60" customHeight="1">
       <c r="A65" s="8" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>2877</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="60" customHeight="1">
       <c r="A66" s="8" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="O66" s="9" t="s">
-        <v>2840</v>
+        <v>2877</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="60" customHeight="1">
       <c r="A67" s="8" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="60" customHeight="1">
       <c r="A68" s="8" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="O68" s="9" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="60" customHeight="1">
       <c r="A69" s="8" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="60" customHeight="1">
       <c r="A70" s="8" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="O70" s="9" t="s">
-        <v>1725</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="60" customHeight="1">
       <c r="A71" s="8" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>2844</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="60" customHeight="1">
       <c r="A72" s="8" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="O72" s="9" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="60" customHeight="1">
       <c r="A73" s="8" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="60" customHeight="1">
       <c r="A74" s="8" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="O74" s="9" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="60" customHeight="1">
       <c r="A75" s="8" t="s">
-        <v>1859</v>
+        <v>2391</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>2881</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="60" customHeight="1">
       <c r="A76" s="8" t="s">
+        <v>1859</v>
+      </c>
+      <c r="O76" s="9" t="s">
+        <v>2881</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" ht="60" customHeight="1">
+      <c r="A77" s="8" t="s">
         <v>2576</v>
       </c>
-      <c r="O76" s="9" t="s">
+      <c r="O77" s="9" t="s">
         <v>2575</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="60" customHeight="1">
       <c r="A78" s="8" t="s">
-        <v>2392</v>
+        <v>3104</v>
       </c>
       <c r="O78" s="9" t="s">
-        <v>2848</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" ht="60" customHeight="1">
-      <c r="A79" s="8" t="s">
-        <v>2332</v>
-      </c>
-      <c r="O79" s="9" t="s">
-        <v>2796</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="60" customHeight="1">
       <c r="A80" s="8" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="O80" s="9" t="s">
-        <v>2793</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="81" spans="1:15" ht="60" customHeight="1">
       <c r="A81" s="8" t="s">
-        <v>2394</v>
+        <v>2332</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>2849</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="60" customHeight="1">
       <c r="A82" s="8" t="s">
-        <v>2395</v>
+        <v>2393</v>
       </c>
       <c r="O82" s="9" t="s">
-        <v>2850</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="83" spans="1:15" ht="60" customHeight="1">
       <c r="A83" s="8" t="s">
-        <v>3002</v>
+        <v>2394</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>3047</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="60" customHeight="1">
       <c r="A84" s="8" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="O84" s="9" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="85" spans="1:15" ht="60" customHeight="1">
       <c r="A85" s="8" t="s">
-        <v>2397</v>
+        <v>3000</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>2852</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="86" spans="1:15" ht="60" customHeight="1">
       <c r="A86" s="8" t="s">
-        <v>2398</v>
+        <v>2396</v>
       </c>
       <c r="O86" s="9" t="s">
-        <v>2853</v>
+        <v>2851</v>
       </c>
     </row>
     <row r="87" spans="1:15" ht="60" customHeight="1">
       <c r="A87" s="8" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>2854</v>
+        <v>2852</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="60" customHeight="1">
       <c r="A88" s="8" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
       <c r="O88" s="9" t="s">
-        <v>2855</v>
+        <v>2853</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="60" customHeight="1">
       <c r="A89" s="8" t="s">
-        <v>2401</v>
+        <v>2399</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>2856</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="90" spans="1:15" ht="60" customHeight="1">
       <c r="A90" s="8" t="s">
-        <v>2402</v>
+        <v>2400</v>
       </c>
       <c r="O90" s="9" t="s">
-        <v>2857</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="60" customHeight="1">
       <c r="A91" s="8" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>2858</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="92" spans="1:15" ht="60" customHeight="1">
       <c r="A92" s="8" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="O92" s="9" t="s">
-        <v>2859</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="93" spans="1:15" ht="60" customHeight="1">
       <c r="A93" s="8" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>2794</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="94" spans="1:15" ht="60" customHeight="1">
       <c r="A94" s="8" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="O94" s="9" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="95" spans="1:15" ht="60" customHeight="1">
       <c r="A95" s="8" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>2861</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="96" spans="1:15" ht="60" customHeight="1">
       <c r="A96" s="8" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
       <c r="O96" s="9" t="s">
-        <v>2862</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="97" spans="1:15" ht="60" customHeight="1">
       <c r="A97" s="8" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>2863</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="98" spans="1:15" ht="60" customHeight="1">
       <c r="A98" s="8" t="s">
-        <v>2410</v>
+        <v>2408</v>
       </c>
       <c r="O98" s="9" t="s">
-        <v>2864</v>
+        <v>2862</v>
       </c>
     </row>
     <row r="99" spans="1:15" ht="60" customHeight="1">
       <c r="A99" s="8" t="s">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>2865</v>
+        <v>2863</v>
       </c>
     </row>
     <row r="100" spans="1:15" ht="60" customHeight="1">
       <c r="A100" s="8" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
       <c r="O100" s="9" t="s">
-        <v>2866</v>
+        <v>2864</v>
       </c>
     </row>
     <row r="101" spans="1:15" ht="60" customHeight="1">
       <c r="A101" s="8" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>2867</v>
+        <v>2865</v>
       </c>
     </row>
     <row r="102" spans="1:15" ht="60" customHeight="1">
       <c r="A102" s="8" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
       <c r="O102" s="9" t="s">
-        <v>2868</v>
+        <v>2866</v>
       </c>
     </row>
     <row r="103" spans="1:15" ht="60" customHeight="1">
       <c r="A103" s="8" t="s">
-        <v>2415</v>
+        <v>2413</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>2869</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="104" spans="1:15" ht="60" customHeight="1">
       <c r="A104" s="8" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
       <c r="O104" s="9" t="s">
-        <v>2870</v>
+        <v>2868</v>
       </c>
     </row>
     <row r="105" spans="1:15" ht="60" customHeight="1">
       <c r="A105" s="8" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>2871</v>
+        <v>2869</v>
       </c>
     </row>
     <row r="106" spans="1:15" ht="60" customHeight="1">
       <c r="A106" s="8" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="O106" s="9" t="s">
-        <v>2873</v>
+        <v>2870</v>
       </c>
     </row>
     <row r="107" spans="1:15" ht="60" customHeight="1">
       <c r="A107" s="8" t="s">
-        <v>2892</v>
+        <v>2417</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>2893</v>
+        <v>2871</v>
       </c>
     </row>
     <row r="108" spans="1:15" ht="60" customHeight="1">
       <c r="A108" s="8" t="s">
+        <v>2418</v>
+      </c>
+      <c r="O108" s="9" t="s">
+        <v>2873</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" ht="60" customHeight="1">
+      <c r="A109" s="8" t="s">
+        <v>2892</v>
+      </c>
+      <c r="O109" s="9" t="s">
+        <v>2893</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" ht="60" customHeight="1">
+      <c r="A110" s="8" t="s">
         <v>2902</v>
       </c>
-      <c r="O108" s="9" t="s">
-        <v>2919</v>
+      <c r="O110" s="9" t="s">
+        <v>2918</v>
       </c>
     </row>
   </sheetData>

--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Among Us code\TheOtherUs\TheOtherUs-Edited-Lite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23AC7112-6429-42F6-B861-98C2AE3D8BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B876DC-F490-49BB-83EE-D7F8ABD74804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2355" yWindow="525" windowWidth="25755" windowHeight="15555" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Options" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3426" uniqueCount="3107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3429" uniqueCount="3110">
   <si>
     <t>English</t>
   </si>
@@ -10191,10 +10191,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SpecterOptions</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Specter (Ghost)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -10601,12 +10597,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>在会议中可以揭示身份，获得一次在会议中击杀玩家的机会。 
-揭示身份后无法再使用赌怪能力，
-同时，如果使用赌怪能力则本轮会议无法揭示身份。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>没有适合的杀手目标 {0}</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -10928,10 +10918,6 @@
   </si>
   <si>
     <t>redemptorReviveDuration</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通复活持续时间</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -11006,6 +10992,33 @@
   </si>
   <si>
     <t>RedemptorPrayer</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpecterOption</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RedemptorRevive</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>殉道</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>会议后重置保护目标</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>殉道复活持续时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>在会议中可以揭示身份，获得一次在会议中击杀玩家的机会。且无法被猜测
+狼之主揭示身份后无法再使用赌怪能力，
+同时，如果狼之主使用赌怪能力则本轮会议无法揭示身份。
+（猎杀和赌怪一次会议只能用一个能力）</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -11818,7 +11831,7 @@
     </row>
     <row r="17" spans="1:15" ht="24.95" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>2451</v>
@@ -11829,7 +11842,7 @@
     </row>
     <row r="18" spans="1:15" ht="24.95" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>2457</v>
@@ -11953,7 +11966,7 @@
     </row>
     <row r="30" spans="1:15" ht="24.95" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>42</v>
@@ -12110,7 +12123,7 @@
     </row>
     <row r="45" spans="1:15" ht="24.95" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>2885</v>
@@ -12229,10 +12242,10 @@
     </row>
     <row r="57" spans="1:15" ht="24.95" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>3049</v>
+        <v>3047</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>3049</v>
+        <v>3047</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>1154</v>
@@ -12240,10 +12253,10 @@
     </row>
     <row r="58" spans="1:15" ht="24.95" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>3072</v>
+        <v>3070</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>3069</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="24.95" customHeight="1">
@@ -12439,18 +12452,18 @@
     </row>
     <row r="78" spans="1:15" ht="24.95" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>3064</v>
+        <v>3062</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>3067</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="24.95" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>3065</v>
+        <v>3063</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>3066</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="24.95" customHeight="1">
@@ -12739,42 +12752,42 @@
     </row>
     <row r="107" spans="1:15" ht="24.95" customHeight="1">
       <c r="A107" s="2" t="s">
-        <v>3054</v>
+        <v>3052</v>
       </c>
       <c r="O107" s="2" t="s">
-        <v>3059</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="108" spans="1:15" ht="24.95" customHeight="1">
       <c r="A108" s="2" t="s">
-        <v>3055</v>
+        <v>3053</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>3060</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="109" spans="1:15" ht="24.95" customHeight="1">
       <c r="A109" s="2" t="s">
-        <v>3056</v>
+        <v>3054</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="110" spans="1:15" ht="24.95" customHeight="1">
       <c r="A110" s="2" t="s">
-        <v>3057</v>
+        <v>3055</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>3062</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="111" spans="1:15" ht="24.95" customHeight="1">
       <c r="A111" s="2" t="s">
-        <v>3058</v>
+        <v>3056</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>3063</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="112" spans="1:15" ht="24.95" customHeight="1">
@@ -12815,13 +12828,13 @@
     </row>
     <row r="116" spans="1:15" ht="24.95" customHeight="1">
       <c r="A116" s="2" t="s">
+        <v>3037</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>3038</v>
+      </c>
+      <c r="O116" s="2" t="s">
         <v>3039</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>3040</v>
-      </c>
-      <c r="O116" s="2" t="s">
-        <v>3041</v>
       </c>
     </row>
     <row r="117" spans="1:15" ht="24.95" customHeight="1">
@@ -13167,18 +13180,18 @@
     </row>
     <row r="150" spans="1:15" ht="24.95" customHeight="1">
       <c r="A150" s="2" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="O150" s="2" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="151" spans="1:15" ht="24.95" customHeight="1">
       <c r="A151" s="2" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="O151" s="2" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="152" spans="1:15" ht="24.95" customHeight="1">
@@ -13514,26 +13527,26 @@
     </row>
     <row r="185" spans="1:15" ht="24.95" customHeight="1">
       <c r="A185" s="2" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="O185" s="2" t="s">
-        <v>3068</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="186" spans="1:15" ht="24.95" customHeight="1">
       <c r="A186" s="2" t="s">
-        <v>3047</v>
+        <v>3045</v>
       </c>
       <c r="O186" s="2" t="s">
-        <v>3070</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="187" spans="1:15" ht="24.95" customHeight="1">
       <c r="A187" s="2" t="s">
-        <v>3048</v>
+        <v>3046</v>
       </c>
       <c r="O187" s="2" t="s">
-        <v>3071</v>
+        <v>3069</v>
       </c>
     </row>
     <row r="188" spans="1:15" ht="24.95" customHeight="1">
@@ -14976,7 +14989,7 @@
         <v>648</v>
       </c>
       <c r="O338" s="2" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="339" spans="1:15" ht="24.95" customHeight="1">
@@ -15408,7 +15421,7 @@
     </row>
     <row r="385" spans="1:15" ht="24.95" customHeight="1">
       <c r="A385" s="2" t="s">
-        <v>3052</v>
+        <v>3050</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>1652</v>
@@ -15419,7 +15432,7 @@
     </row>
     <row r="386" spans="1:15" ht="24.95" customHeight="1">
       <c r="A386" s="2" t="s">
-        <v>3051</v>
+        <v>3049</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>1678</v>
@@ -15433,37 +15446,37 @@
     </row>
     <row r="388" spans="1:15" ht="24.95" customHeight="1">
       <c r="A388" s="2" t="s">
+        <v>3104</v>
+      </c>
+      <c r="B388" s="2" t="s">
         <v>2903</v>
       </c>
-      <c r="B388" s="2" t="s">
+      <c r="O388" s="2" t="s">
         <v>2904</v>
-      </c>
-      <c r="O388" s="2" t="s">
-        <v>2905</v>
       </c>
     </row>
     <row r="389" spans="1:15" ht="24.95" customHeight="1">
       <c r="A389" s="2" t="s">
-        <v>3023</v>
+        <v>3021</v>
       </c>
       <c r="O389" s="2" t="s">
-        <v>3024</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="390" spans="1:15" ht="24.95" customHeight="1">
       <c r="A390" s="2" t="s">
+        <v>3034</v>
+      </c>
+      <c r="O390" s="2" t="s">
         <v>3036</v>
-      </c>
-      <c r="O390" s="2" t="s">
-        <v>3038</v>
       </c>
     </row>
     <row r="391" spans="1:15" ht="24.95" customHeight="1">
       <c r="A391" s="2" t="s">
+        <v>3033</v>
+      </c>
+      <c r="O391" s="3" t="s">
         <v>3035</v>
-      </c>
-      <c r="O391" s="3" t="s">
-        <v>3037</v>
       </c>
     </row>
     <row r="392" spans="1:15" ht="24.95" customHeight="1">
@@ -15992,18 +16005,18 @@
     </row>
     <row r="451" spans="1:15" ht="24.95" customHeight="1">
       <c r="A451" s="2" t="s">
+        <v>3006</v>
+      </c>
+      <c r="O451" s="2" t="s">
         <v>3008</v>
-      </c>
-      <c r="O451" s="2" t="s">
-        <v>3010</v>
       </c>
     </row>
     <row r="452" spans="1:15" ht="24.95" customHeight="1">
       <c r="A452" s="2" t="s">
+        <v>3007</v>
+      </c>
+      <c r="O452" s="2" t="s">
         <v>3009</v>
-      </c>
-      <c r="O452" s="2" t="s">
-        <v>3011</v>
       </c>
     </row>
     <row r="453" spans="1:15" ht="24.95" customHeight="1">
@@ -16105,7 +16118,7 @@
         <v>1617</v>
       </c>
       <c r="O464" s="2" t="s">
-        <v>3073</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="465" spans="1:15" ht="24.95" customHeight="1">
@@ -16116,7 +16129,7 @@
         <v>1812</v>
       </c>
       <c r="O465" s="2" t="s">
-        <v>3074</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="466" spans="1:15" ht="24.95" customHeight="1">
@@ -16209,34 +16222,34 @@
     </row>
     <row r="476" spans="1:15" ht="24.95" customHeight="1">
       <c r="A476" s="2" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="O476" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="477" spans="1:15" ht="24.95" customHeight="1">
       <c r="A477" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="O477" s="2" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
     </row>
     <row r="478" spans="1:15" ht="24.95" customHeight="1">
       <c r="A478" s="2" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="O478" s="3" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="479" spans="1:15" ht="24.95" customHeight="1">
       <c r="A479" s="2" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="O479" s="3" t="s">
-        <v>3022</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="480" spans="1:15" ht="24.95" customHeight="1">
@@ -16432,13 +16445,13 @@
     </row>
     <row r="504" spans="1:15" ht="24.95" customHeight="1">
       <c r="A504" s="2" t="s">
+        <v>2905</v>
+      </c>
+      <c r="B504" s="2" t="s">
         <v>2906</v>
       </c>
-      <c r="B504" s="2" t="s">
+      <c r="O504" s="3" t="s">
         <v>2907</v>
-      </c>
-      <c r="O504" s="3" t="s">
-        <v>2908</v>
       </c>
     </row>
     <row r="505" spans="1:15" ht="24.95" customHeight="1">
@@ -17649,7 +17662,7 @@
         <v>1074</v>
       </c>
       <c r="O629" s="2" t="s">
-        <v>3053</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="630" spans="1:15" ht="24.95" customHeight="1">
@@ -17917,7 +17930,7 @@
         <v>924</v>
       </c>
       <c r="O657" s="2" t="s">
-        <v>925</v>
+        <v>3107</v>
       </c>
     </row>
     <row r="658" spans="1:15" ht="24.95" customHeight="1">
@@ -18029,7 +18042,7 @@
     </row>
     <row r="670" spans="1:15" ht="24.95" customHeight="1">
       <c r="A670" s="2" t="s">
-        <v>3050</v>
+        <v>3048</v>
       </c>
       <c r="B670" s="2" t="s">
         <v>1155</v>
@@ -18054,58 +18067,58 @@
     </row>
     <row r="673" spans="1:15" ht="24.95" customHeight="1">
       <c r="A673" s="2" t="s">
-        <v>3075</v>
+        <v>3073</v>
       </c>
       <c r="O673" s="2" t="s">
-        <v>3080</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="674" spans="1:15" ht="24.95" customHeight="1">
       <c r="A674" s="2" t="s">
-        <v>3076</v>
+        <v>3074</v>
       </c>
       <c r="O674" s="2" t="s">
-        <v>3081</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="675" spans="1:15" ht="24.95" customHeight="1">
       <c r="A675" s="2" t="s">
-        <v>3091</v>
+        <v>3088</v>
       </c>
       <c r="O675" s="2" t="s">
-        <v>3092</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="676" spans="1:15" ht="24.95" customHeight="1">
       <c r="A676" s="2" t="s">
-        <v>3077</v>
+        <v>3075</v>
       </c>
       <c r="O676" s="2" t="s">
-        <v>3082</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="677" spans="1:15" ht="24.95" customHeight="1">
       <c r="A677" s="2" t="s">
-        <v>3078</v>
+        <v>3076</v>
       </c>
       <c r="O677" s="2" t="s">
-        <v>3083</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="678" spans="1:15" ht="24.95" customHeight="1">
       <c r="A678" s="2" t="s">
-        <v>3079</v>
+        <v>3077</v>
       </c>
       <c r="O678" s="2" t="s">
-        <v>3084</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="679" spans="1:15" ht="24.95" customHeight="1">
       <c r="A679" s="2" t="s">
-        <v>3088</v>
+        <v>3086</v>
       </c>
       <c r="O679" s="2" t="s">
-        <v>3089</v>
+        <v>3108</v>
       </c>
     </row>
     <row r="680" spans="1:15" ht="24.95" customHeight="1">
@@ -18141,18 +18154,18 @@
     </row>
     <row r="685" spans="1:15" ht="24.95" customHeight="1">
       <c r="A685" s="2" t="s">
+        <v>3010</v>
+      </c>
+      <c r="O685" s="2" t="s">
         <v>3012</v>
-      </c>
-      <c r="O685" s="2" t="s">
-        <v>3014</v>
       </c>
     </row>
     <row r="686" spans="1:15" ht="24.95" customHeight="1">
       <c r="A686" s="2" t="s">
+        <v>3011</v>
+      </c>
+      <c r="O686" s="2" t="s">
         <v>3013</v>
-      </c>
-      <c r="O686" s="2" t="s">
-        <v>3015</v>
       </c>
     </row>
     <row r="687" spans="1:15" ht="24.95" customHeight="1">
@@ -18329,10 +18342,10 @@
     </row>
     <row r="708" spans="1:15" ht="33">
       <c r="A708" s="2" t="s">
+        <v>2987</v>
+      </c>
+      <c r="O708" s="3" t="s">
         <v>2988</v>
-      </c>
-      <c r="O708" s="3" t="s">
-        <v>2989</v>
       </c>
     </row>
     <row r="709" spans="1:15" ht="24.95" customHeight="1">
@@ -21648,7 +21661,7 @@
         <v>1253</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>3032</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="54">
@@ -21656,7 +21669,7 @@
         <v>1254</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3033</v>
+        <v>3031</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>2774</v>
@@ -21722,7 +21735,7 @@
         <v>1269</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>3034</v>
+        <v>3032</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>2789</v>
@@ -22093,35 +22106,35 @@
     </row>
     <row r="53" spans="1:15" ht="24.95" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="24.95" customHeight="1">
       <c r="A54" s="1" t="s">
+        <v>2922</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>2923</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>2924</v>
-      </c>
       <c r="O54" s="1" t="s">
-        <v>3005</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="24.95" customHeight="1">
       <c r="A55" s="1" t="s">
+        <v>2920</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>2921</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>2922</v>
-      </c>
       <c r="O55" s="1" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="24.95" customHeight="1">
@@ -22170,186 +22183,186 @@
     </row>
     <row r="62" spans="1:15" ht="24.95" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="24.95" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="24.95" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="24.95" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="24.95" customHeight="1">
       <c r="A66" s="1" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="24.95" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="24.95" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="24.95" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>3025</v>
+        <v>3023</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>3026</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="24.95" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="24.95" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="24.95" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="24.95" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="24.95" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="24.95" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="24.95" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="24.95" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="24.95" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="24.95" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="24.95" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="81" spans="1:15" ht="24.95" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="24.95" customHeight="1">
       <c r="A82" s="1" t="s">
+        <v>2978</v>
+      </c>
+      <c r="O82" s="1" t="s">
         <v>2979</v>
-      </c>
-      <c r="O82" s="1" t="s">
-        <v>2980</v>
       </c>
     </row>
     <row r="83" spans="1:15" ht="24.95" customHeight="1">
       <c r="A83" s="1" t="s">
+        <v>2980</v>
+      </c>
+      <c r="O83" s="1" t="s">
         <v>2981</v>
-      </c>
-      <c r="O83" s="1" t="s">
-        <v>2982</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="24.95" customHeight="1">
       <c r="A84" s="1" t="s">
+        <v>2982</v>
+      </c>
+      <c r="O84" s="1" t="s">
         <v>2983</v>
-      </c>
-      <c r="O84" s="1" t="s">
-        <v>2984</v>
       </c>
     </row>
   </sheetData>
@@ -22441,7 +22454,7 @@
         <v>1322</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>3027</v>
+        <v>3025</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="16.5">
@@ -22452,7 +22465,7 @@
         <v>1324</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>3028</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="16.5">
@@ -22463,7 +22476,7 @@
         <v>1326</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>3029</v>
+        <v>3027</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="16.5">
@@ -22485,7 +22498,7 @@
         <v>1330</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>3030</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="16.5">
@@ -22496,7 +22509,7 @@
         <v>1332</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>3031</v>
+        <v>3029</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="16.5">
@@ -22882,7 +22895,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:S93"/>
+  <dimension ref="A1:S94"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21.5" style="2" customWidth="1"/>
@@ -23257,7 +23270,7 @@
     </row>
     <row r="29" spans="1:15" ht="20.100000000000001" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>3020</v>
+        <v>3018</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>1502</v>
@@ -23945,35 +23958,46 @@
     </row>
     <row r="91" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A91" s="2" t="s">
-        <v>3090</v>
+        <v>3087</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>2913</v>
+      </c>
+      <c r="O91" s="2" t="s">
         <v>2914</v>
-      </c>
-      <c r="O91" s="2" t="s">
-        <v>2915</v>
       </c>
     </row>
     <row r="92" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A92" s="2" t="s">
-        <v>3093</v>
+        <v>3090</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>3094</v>
+        <v>3091</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>3095</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="93" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A93" s="2" t="s">
+        <v>3103</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>3093</v>
+      </c>
+      <c r="O93" s="2" t="s">
+        <v>3080</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" ht="20.100000000000001" customHeight="1">
+      <c r="A94" s="2" t="s">
+        <v>3105</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>2913</v>
+      </c>
+      <c r="O94" s="2" t="s">
         <v>3106</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>3096</v>
-      </c>
-      <c r="O93" s="2" t="s">
-        <v>3082</v>
       </c>
     </row>
   </sheetData>
@@ -24123,29 +24147,29 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="7" t="s">
+        <v>2990</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>2990</v>
+      </c>
+      <c r="O13" s="7" t="s">
         <v>2991</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>2991</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>2992</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="7" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>3097</v>
+        <v>3094</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="7" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>3098</v>
+        <v>3095</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -24960,29 +24984,29 @@
     </row>
     <row r="137" spans="1:15">
       <c r="A137" s="7" t="s">
-        <v>2911</v>
+        <v>2910</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>2910</v>
+        <v>2909</v>
       </c>
       <c r="O137" s="7" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
     </row>
     <row r="138" spans="1:15">
       <c r="A138" s="7" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="O138" s="7" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="139" spans="1:15">
       <c r="A139" s="7" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="O139" s="7" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="141" spans="1:15">
@@ -25257,29 +25281,29 @@
     </row>
     <row r="181" spans="1:15">
       <c r="A181" s="7" t="s">
-        <v>3016</v>
+        <v>3014</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>3016</v>
+        <v>3014</v>
       </c>
       <c r="O181" s="7" t="s">
-        <v>3042</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="182" spans="1:15">
       <c r="A182" s="7" t="s">
-        <v>3018</v>
+        <v>3016</v>
       </c>
       <c r="O182" s="7" t="s">
-        <v>3043</v>
+        <v>3041</v>
       </c>
     </row>
     <row r="183" spans="1:15">
       <c r="A183" s="7" t="s">
+        <v>3015</v>
+      </c>
+      <c r="O183" s="7" t="s">
         <v>3017</v>
-      </c>
-      <c r="O183" s="7" t="s">
-        <v>3019</v>
       </c>
     </row>
     <row r="185" spans="1:15">
@@ -26040,29 +26064,29 @@
     </row>
     <row r="297" spans="1:15">
       <c r="A297" s="7" t="s">
-        <v>3103</v>
+        <v>3100</v>
       </c>
       <c r="B297" s="7" t="s">
-        <v>3103</v>
+        <v>3100</v>
       </c>
       <c r="O297" s="7" t="s">
-        <v>3087</v>
+        <v>3085</v>
       </c>
     </row>
     <row r="298" spans="1:15">
       <c r="A298" s="7" t="s">
-        <v>3085</v>
+        <v>3083</v>
       </c>
       <c r="O298" s="7" t="s">
-        <v>3100</v>
+        <v>3097</v>
       </c>
     </row>
     <row r="299" spans="1:15">
       <c r="A299" s="7" t="s">
-        <v>3086</v>
+        <v>3084</v>
       </c>
       <c r="O299" s="7" t="s">
-        <v>3099</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="301" spans="1:15">
@@ -26148,29 +26172,29 @@
     </row>
     <row r="313" spans="1:15">
       <c r="A313" s="7" t="s">
+        <v>2997</v>
+      </c>
+      <c r="B313" s="7" t="s">
+        <v>2996</v>
+      </c>
+      <c r="O313" s="7" t="s">
         <v>2998</v>
-      </c>
-      <c r="B313" s="7" t="s">
-        <v>2997</v>
-      </c>
-      <c r="O313" s="7" t="s">
-        <v>2999</v>
       </c>
     </row>
     <row r="314" spans="1:15">
       <c r="A314" s="7" t="s">
-        <v>3006</v>
+        <v>3004</v>
       </c>
       <c r="O314" s="7" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="315" spans="1:15">
       <c r="A315" s="7" t="s">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="O315" s="7" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="317" spans="1:15">
@@ -27037,10 +27061,10 @@
     </row>
     <row r="3" spans="1:17" ht="60" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>3004</v>
+        <v>3109</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="60" customHeight="1">
@@ -27064,7 +27088,7 @@
         <v>2335</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="60" customHeight="1">
@@ -27192,7 +27216,7 @@
         <v>2349</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="60" customHeight="1">
@@ -27229,10 +27253,10 @@
     </row>
     <row r="27" spans="1:15" ht="60" customHeight="1">
       <c r="A27" s="8" t="s">
-        <v>3101</v>
+        <v>3098</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>3102</v>
+        <v>3099</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="60" customHeight="1">
@@ -27344,7 +27368,7 @@
         <v>2362</v>
       </c>
       <c r="O42" s="9" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="60" customHeight="1">
@@ -27373,10 +27397,10 @@
     </row>
     <row r="46" spans="1:15" ht="60" customHeight="1">
       <c r="A46" s="8" t="s">
-        <v>3021</v>
+        <v>3019</v>
       </c>
       <c r="O46" s="9" t="s">
-        <v>3044</v>
+        <v>3042</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="60" customHeight="1">
@@ -27397,10 +27421,10 @@
     </row>
     <row r="49" spans="1:15" ht="60" customHeight="1">
       <c r="A49" s="8" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="60" customHeight="1">
@@ -27621,10 +27645,10 @@
     </row>
     <row r="78" spans="1:15" ht="60" customHeight="1">
       <c r="A78" s="8" t="s">
-        <v>3104</v>
+        <v>3101</v>
       </c>
       <c r="O78" s="9" t="s">
-        <v>3105</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="60" customHeight="1">
@@ -27669,10 +27693,10 @@
     </row>
     <row r="85" spans="1:15" ht="60" customHeight="1">
       <c r="A85" s="8" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="86" spans="1:15" ht="60" customHeight="1">
@@ -27872,7 +27896,7 @@
         <v>2902</v>
       </c>
       <c r="O110" s="9" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
     </row>
   </sheetData>

--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Among Us code\TheOtherUs\TheOtherUs-Edited-Lite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F615EB9-F6C2-4805-8408-97D2D6C144A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE317E71-21C5-45B0-95D6-630F11371A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2745" yWindow="645" windowWidth="25755" windowHeight="15555" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2745" yWindow="645" windowWidth="25755" windowHeight="15555" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Options" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Role Description" sheetId="11" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Options!$O$1:$O$1447</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Options!$O$1:$O$1450</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3515" uniqueCount="3193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3519" uniqueCount="3197">
   <si>
     <t>English</t>
   </si>
@@ -7415,10 +7415,6 @@
   </si>
   <si>
     <t>Tunneler</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>管道工程师</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -11352,6 +11348,25 @@
   </si>
   <si>
     <t>存活时查验类信息会被反转</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>modifierAutoJoin</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>在伪装者人数占优时自动加入</t>
+  </si>
+  <si>
+    <t>modifierTunnelerNoTask</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>隧道工</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>未完成任务也可以使用管道</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -11962,7 +11977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1744"/>
+  <dimension ref="A1:Q1747"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40.375" style="2" customWidth="1"/>
@@ -12043,7 +12058,7 @@
     </row>
     <row r="4" spans="1:17" ht="24.95" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>2565</v>
+        <v>2564</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>20</v>
@@ -12098,24 +12113,24 @@
     </row>
     <row r="9" spans="1:17" ht="24.75" customHeight="1">
       <c r="A9" s="2" t="s">
+        <v>2457</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>2458</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="O9" s="3" t="s">
         <v>2459</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>2460</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="24.75" customHeight="1">
       <c r="A10" s="2" t="s">
+        <v>2561</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>2562</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="O10" s="3" t="s">
         <v>2563</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>2564</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="24.95" customHeight="1">
@@ -12131,156 +12146,156 @@
     </row>
     <row r="13" spans="1:17" ht="24.95" customHeight="1">
       <c r="A13" s="2" t="s">
+        <v>2434</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>2450</v>
+      </c>
+      <c r="O13" s="3" t="s">
         <v>2435</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>2451</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>2436</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="24.95" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="24.95" customHeight="1">
       <c r="A15" s="2" t="s">
+        <v>2446</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>2447</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="O15" s="3" t="s">
         <v>2448</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>2449</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="24.95" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="24.95" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="24.95" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="24.95" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="24.95" customHeight="1">
       <c r="A20" s="2" t="s">
+        <v>2516</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>2517</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="O20" s="3" t="s">
         <v>2518</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>2519</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="24.95" customHeight="1">
       <c r="A21" s="2" t="s">
+        <v>2464</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>2465</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="O21" s="3" t="s">
         <v>2466</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>2467</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="24.95" customHeight="1">
       <c r="A22" s="2" t="s">
+        <v>2762</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>2764</v>
+      </c>
+      <c r="O22" s="3" t="s">
         <v>2763</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>2765</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>2764</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="24.95" customHeight="1">
       <c r="A23" s="2" t="s">
+        <v>2556</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>2765</v>
+      </c>
+      <c r="O23" s="3" t="s">
         <v>2557</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>2766</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>2558</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="24.95" customHeight="1">
       <c r="A24" s="2" t="s">
+        <v>2437</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>2452</v>
+      </c>
+      <c r="O24" s="3" t="s">
         <v>2438</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>2453</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>2439</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="24.95" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>2454</v>
+      </c>
+      <c r="O25" s="3" t="s">
         <v>2455</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>2456</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="24.95" customHeight="1">
       <c r="A26" s="2" t="s">
+        <v>2460</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>2462</v>
+      </c>
+      <c r="O26" s="3" t="s">
         <v>2461</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>2463</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>2462</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="24.95" customHeight="1">
@@ -12310,7 +12325,7 @@
     </row>
     <row r="30" spans="1:15" ht="24.95" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>42</v>
@@ -12376,13 +12391,13 @@
     </row>
     <row r="36" spans="1:15" ht="24.95" customHeight="1">
       <c r="A36" s="2" t="s">
+        <v>2888</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>2889</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="O36" s="3" t="s">
         <v>2890</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>2891</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="24.95" customHeight="1">
@@ -12429,7 +12444,7 @@
         <v>52</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="24.95" customHeight="1">
@@ -12456,7 +12471,7 @@
     </row>
     <row r="44" spans="1:15" ht="24.95" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>57</v>
@@ -12467,13 +12482,13 @@
     </row>
     <row r="45" spans="1:15" ht="24.95" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>2879</v>
+      </c>
+      <c r="O45" s="3" t="s">
         <v>2880</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>2881</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="24.95" customHeight="1">
@@ -12482,7 +12497,7 @@
     </row>
     <row r="47" spans="1:15" ht="24.95" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>59</v>
@@ -12493,7 +12508,7 @@
     </row>
     <row r="48" spans="1:15" ht="24.95" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>60</v>
@@ -12504,7 +12519,7 @@
     </row>
     <row r="49" spans="1:15" ht="24.95" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>61</v>
@@ -12515,7 +12530,7 @@
     </row>
     <row r="50" spans="1:15" ht="24.95" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>62</v>
@@ -12533,7 +12548,7 @@
         <v>63</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>2767</v>
+        <v>2766</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>64</v>
@@ -12563,33 +12578,33 @@
     </row>
     <row r="55" spans="1:15" ht="24.95" customHeight="1">
       <c r="A55" s="2" t="s">
+        <v>2558</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>2559</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>2560</v>
-      </c>
       <c r="O55" s="3" t="s">
-        <v>2566</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="24.95" customHeight="1">
       <c r="A56" s="2" t="s">
+        <v>2571</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>2572</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>2573</v>
       </c>
       <c r="C56" s="3"/>
       <c r="O56" s="3" t="s">
-        <v>2574</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="24.95" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>1153</v>
@@ -12597,10 +12612,10 @@
     </row>
     <row r="58" spans="1:15" ht="24.95" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="24.95" customHeight="1">
@@ -12746,13 +12761,13 @@
     </row>
     <row r="75" spans="1:15" ht="24.95" customHeight="1">
       <c r="A75" s="2" t="s">
+        <v>2872</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>2874</v>
+      </c>
+      <c r="O75" s="2" t="s">
         <v>2873</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>2875</v>
-      </c>
-      <c r="O75" s="2" t="s">
-        <v>2874</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="24.95" customHeight="1">
@@ -12779,18 +12794,18 @@
     </row>
     <row r="78" spans="1:15" ht="24.95" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="24.95" customHeight="1">
       <c r="A79" s="2" t="s">
+        <v>3057</v>
+      </c>
+      <c r="O79" s="2" t="s">
         <v>3058</v>
-      </c>
-      <c r="O79" s="2" t="s">
-        <v>3059</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="24.95" customHeight="1">
@@ -13002,7 +13017,7 @@
         <v>170</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="O99" s="2" t="s">
         <v>171</v>
@@ -13010,24 +13025,24 @@
     </row>
     <row r="100" spans="1:15" ht="24.95" customHeight="1">
       <c r="A100" s="2" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>2771</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="101" spans="1:15" ht="24.95" customHeight="1">
       <c r="A101" s="2" t="s">
+        <v>2529</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>2530</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>2531</v>
-      </c>
       <c r="O101" s="2" t="s">
-        <v>2772</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="102" spans="1:15" ht="24.95" customHeight="1">
@@ -13079,79 +13094,79 @@
     </row>
     <row r="107" spans="1:15" ht="24.95" customHeight="1">
       <c r="A107" s="2" t="s">
+        <v>3139</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>3140</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>3141</v>
-      </c>
       <c r="O107" s="2" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="108" spans="1:15" ht="24.95" customHeight="1">
       <c r="A108" s="2" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="109" spans="1:15" ht="24.95" customHeight="1">
       <c r="A109" s="2" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="110" spans="1:15" ht="24.95" customHeight="1">
       <c r="A110" s="2" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
     </row>
     <row r="111" spans="1:15" ht="24.95" customHeight="1">
       <c r="A111" s="2" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="112" spans="1:15" ht="24.95" customHeight="1">
       <c r="A112" s="2" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="O112" s="2" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
     </row>
     <row r="113" spans="1:15" ht="24.95" customHeight="1">
       <c r="A113" s="2" t="s">
+        <v>3172</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>3173</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="O113" s="2" t="s">
         <v>3174</v>
-      </c>
-      <c r="O113" s="2" t="s">
-        <v>3175</v>
       </c>
     </row>
     <row r="114" spans="1:15" ht="24.95" customHeight="1">
@@ -13159,42 +13174,42 @@
     </row>
     <row r="115" spans="1:15" ht="24.95" customHeight="1">
       <c r="A115" s="2" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="O115" s="2" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="116" spans="1:15" ht="24.95" customHeight="1">
       <c r="A116" s="2" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="O116" s="2" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="117" spans="1:15" ht="24.95" customHeight="1">
       <c r="A117" s="2" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="O117" s="2" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
     </row>
     <row r="118" spans="1:15" ht="24.95" customHeight="1">
       <c r="A118" s="2" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="O118" s="2" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="119" spans="1:15" ht="24.95" customHeight="1">
       <c r="A119" s="2" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="O119" s="2" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="120" spans="1:15" ht="24.95" customHeight="1">
@@ -13235,13 +13250,13 @@
     </row>
     <row r="124" spans="1:15" ht="24.95" customHeight="1">
       <c r="A124" s="2" t="s">
+        <v>3031</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>3032</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="O124" s="2" t="s">
         <v>3033</v>
-      </c>
-      <c r="O124" s="2" t="s">
-        <v>3034</v>
       </c>
     </row>
     <row r="125" spans="1:15" ht="24.95" customHeight="1">
@@ -13285,7 +13300,7 @@
         <v>203</v>
       </c>
       <c r="O128" s="2" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="129" spans="1:15" ht="24.95" customHeight="1">
@@ -13312,13 +13327,13 @@
     </row>
     <row r="131" spans="1:15" ht="24.95" customHeight="1">
       <c r="A131" s="2" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>210</v>
       </c>
       <c r="O131" s="2" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="132" spans="1:15" ht="24.95" customHeight="1">
@@ -13345,10 +13360,10 @@
     </row>
     <row r="134" spans="1:15" ht="24.95" customHeight="1">
       <c r="A134" s="2" t="s">
+        <v>2580</v>
+      </c>
+      <c r="O134" s="2" t="s">
         <v>2581</v>
-      </c>
-      <c r="O134" s="2" t="s">
-        <v>2582</v>
       </c>
     </row>
     <row r="135" spans="1:15" ht="24.95" customHeight="1">
@@ -13356,7 +13371,7 @@
         <v>1792</v>
       </c>
       <c r="O135" s="3" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="136" spans="1:15" ht="24.95" customHeight="1">
@@ -13416,7 +13431,7 @@
     </row>
     <row r="141" spans="1:15" ht="24.95" customHeight="1">
       <c r="A141" s="2" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>232</v>
@@ -13427,10 +13442,10 @@
     </row>
     <row r="142" spans="1:15" ht="24.95" customHeight="1">
       <c r="A142" s="2" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B142" s="2" t="s">
         <v>2555</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>2556</v>
       </c>
       <c r="O142" s="2" t="s">
         <v>234</v>
@@ -13587,18 +13602,18 @@
     </row>
     <row r="158" spans="1:15" ht="24.95" customHeight="1">
       <c r="A158" s="2" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="O158" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="159" spans="1:15" ht="24.95" customHeight="1">
       <c r="A159" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="O159" s="2" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
     </row>
     <row r="160" spans="1:15" ht="24.95" customHeight="1">
@@ -13777,7 +13792,7 @@
         <v>298</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="O177" s="2" t="s">
         <v>299</v>
@@ -13788,24 +13803,24 @@
     </row>
     <row r="179" spans="1:15" ht="24.95" customHeight="1">
       <c r="A179" s="2" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>300</v>
       </c>
       <c r="O179" s="2" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="180" spans="1:15" ht="24.95" customHeight="1">
       <c r="A180" s="2" t="s">
+        <v>2578</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>2577</v>
+      </c>
+      <c r="O180" s="2" t="s">
         <v>2579</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>2578</v>
-      </c>
-      <c r="O180" s="2" t="s">
-        <v>2580</v>
       </c>
     </row>
     <row r="181" spans="1:15" ht="24.95" customHeight="1">
@@ -13934,26 +13949,26 @@
     </row>
     <row r="193" spans="1:15" ht="24.95" customHeight="1">
       <c r="A193" s="2" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="O193" s="2" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="194" spans="1:15" ht="24.95" customHeight="1">
       <c r="A194" s="2" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="O194" s="2" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="195" spans="1:15" ht="24.95" customHeight="1">
       <c r="A195" s="2" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="O195" s="2" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="196" spans="1:15" ht="24.95" customHeight="1">
@@ -13972,13 +13987,13 @@
     </row>
     <row r="198" spans="1:15" ht="24.95" customHeight="1">
       <c r="A198" s="2" t="s">
+        <v>2552</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>2551</v>
+      </c>
+      <c r="O198" s="2" t="s">
         <v>2553</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>2552</v>
-      </c>
-      <c r="O198" s="2" t="s">
-        <v>2554</v>
       </c>
     </row>
     <row r="199" spans="1:15" ht="24.95" customHeight="1">
@@ -14052,13 +14067,13 @@
     </row>
     <row r="206" spans="1:15" ht="24.95" customHeight="1">
       <c r="A206" s="2" t="s">
+        <v>2313</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>2315</v>
+      </c>
+      <c r="O206" s="2" t="s">
         <v>2314</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>2316</v>
-      </c>
-      <c r="O206" s="2" t="s">
-        <v>2315</v>
       </c>
     </row>
     <row r="207" spans="1:15" ht="24.95" customHeight="1">
@@ -14948,24 +14963,24 @@
     </row>
     <row r="296" spans="1:15" ht="24.95" customHeight="1">
       <c r="A296" s="2" t="s">
+        <v>2494</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>2501</v>
+      </c>
+      <c r="O296" s="2" t="s">
         <v>2495</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>2502</v>
-      </c>
-      <c r="O296" s="2" t="s">
-        <v>2496</v>
       </c>
     </row>
     <row r="297" spans="1:15" ht="24.95" customHeight="1">
       <c r="A297" s="2" t="s">
+        <v>2497</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>2502</v>
+      </c>
+      <c r="O297" s="2" t="s">
         <v>2498</v>
-      </c>
-      <c r="B297" s="2" t="s">
-        <v>2503</v>
-      </c>
-      <c r="O297" s="2" t="s">
-        <v>2499</v>
       </c>
     </row>
     <row r="298" spans="1:15" ht="24.95" customHeight="1">
@@ -15308,7 +15323,7 @@
         <v>627</v>
       </c>
       <c r="O337" s="3" t="s">
-        <v>2787</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="338" spans="1:15" ht="24.95" customHeight="1">
@@ -15379,13 +15394,13 @@
     </row>
     <row r="345" spans="1:15" ht="24.95" customHeight="1">
       <c r="A345" s="2" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="O345" s="2" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="346" spans="1:15" ht="24.95" customHeight="1">
@@ -15396,7 +15411,7 @@
         <v>647</v>
       </c>
       <c r="O346" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
     </row>
     <row r="347" spans="1:15" ht="24.95" customHeight="1">
@@ -15489,7 +15504,7 @@
     </row>
     <row r="357" spans="1:15" ht="24.95" customHeight="1">
       <c r="A357" s="2" t="s">
-        <v>2601</v>
+        <v>2600</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>669</v>
@@ -15500,7 +15515,7 @@
     </row>
     <row r="358" spans="1:15" ht="24.95" customHeight="1">
       <c r="A358" s="2" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>671</v>
@@ -15718,35 +15733,35 @@
     </row>
     <row r="381" spans="1:15" ht="24.95" customHeight="1">
       <c r="A381" s="2" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="O381" s="3" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="382" spans="1:15" ht="24.95" customHeight="1">
       <c r="A382" s="2" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="O382" s="2" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="383" spans="1:15" ht="24.95" customHeight="1">
       <c r="A383" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="B383" s="2" t="s">
+        <v>2310</v>
+      </c>
+      <c r="O383" s="2" t="s">
         <v>2307</v>
-      </c>
-      <c r="B383" s="2" t="s">
-        <v>2311</v>
-      </c>
-      <c r="O383" s="2" t="s">
-        <v>2308</v>
       </c>
     </row>
     <row r="384" spans="1:15" ht="24.95" customHeight="1">
@@ -15754,62 +15769,62 @@
     </row>
     <row r="385" spans="1:15" ht="24.95" customHeight="1">
       <c r="A385" s="2" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="O385" s="2" t="s">
-        <v>2617</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="386" spans="1:15" ht="24.95" customHeight="1">
       <c r="A386" s="2" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>2614</v>
+        <v>2613</v>
       </c>
       <c r="O386" s="2" t="s">
-        <v>2616</v>
+        <v>2615</v>
       </c>
     </row>
     <row r="387" spans="1:15" ht="24.95" customHeight="1">
       <c r="A387" s="2" t="s">
+        <v>2611</v>
+      </c>
+      <c r="B387" s="2" t="s">
         <v>2612</v>
       </c>
-      <c r="B387" s="2" t="s">
-        <v>2613</v>
-      </c>
       <c r="O387" s="2" t="s">
-        <v>2618</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="388" spans="1:15" ht="24.95" customHeight="1">
       <c r="A388" s="2" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="B388" s="2" t="s">
+        <v>2608</v>
+      </c>
+      <c r="O388" s="2" t="s">
         <v>2609</v>
-      </c>
-      <c r="O388" s="2" t="s">
-        <v>2610</v>
       </c>
     </row>
     <row r="389" spans="1:15" ht="24.95" customHeight="1">
       <c r="A389" s="2" t="s">
-        <v>2619</v>
+        <v>2618</v>
       </c>
       <c r="O389" s="2" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="390" spans="1:15" ht="24.95" customHeight="1">
       <c r="A390" s="2" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="O390" s="2" t="s">
-        <v>2624</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="391" spans="1:15" ht="24.95" customHeight="1">
@@ -15817,10 +15832,10 @@
     </row>
     <row r="392" spans="1:15" ht="24.95" customHeight="1">
       <c r="A392" s="2" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="O392" s="2" t="s">
         <v>771</v>
@@ -15828,7 +15843,7 @@
     </row>
     <row r="393" spans="1:15" ht="24.95" customHeight="1">
       <c r="A393" s="2" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>1647</v>
@@ -15839,7 +15854,7 @@
     </row>
     <row r="394" spans="1:15" ht="24.95" customHeight="1">
       <c r="A394" s="2" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>1673</v>
@@ -15853,37 +15868,37 @@
     </row>
     <row r="396" spans="1:15" ht="24.95" customHeight="1">
       <c r="A396" s="2" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="B396" s="2" t="s">
+        <v>2897</v>
+      </c>
+      <c r="O396" s="2" t="s">
         <v>2898</v>
-      </c>
-      <c r="O396" s="2" t="s">
-        <v>2899</v>
       </c>
     </row>
     <row r="397" spans="1:15" ht="24.95" customHeight="1">
       <c r="A397" s="2" t="s">
+        <v>3015</v>
+      </c>
+      <c r="O397" s="2" t="s">
         <v>3016</v>
-      </c>
-      <c r="O397" s="2" t="s">
-        <v>3017</v>
       </c>
     </row>
     <row r="398" spans="1:15" ht="24.95" customHeight="1">
       <c r="A398" s="2" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="O398" s="2" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="399" spans="1:15" ht="24.95" customHeight="1">
       <c r="A399" s="2" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="O399" s="3" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
     </row>
     <row r="400" spans="1:15" ht="24.95" customHeight="1">
@@ -16029,7 +16044,7 @@
         <v>728</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="O416" s="2" t="s">
         <v>729</v>
@@ -16040,18 +16055,18 @@
         <v>730</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="O417" s="2" t="s">
-        <v>2877</v>
+        <v>2876</v>
       </c>
     </row>
     <row r="418" spans="1:15" ht="24.95" customHeight="1">
       <c r="A418" s="2" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
       <c r="O418" s="2" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
     </row>
     <row r="419" spans="1:15" ht="24.95" customHeight="1">
@@ -16158,13 +16173,13 @@
     </row>
     <row r="429" spans="1:15" ht="24.95" customHeight="1">
       <c r="A429" s="2" t="s">
+        <v>2415</v>
+      </c>
+      <c r="B429" s="2" t="s">
         <v>2416</v>
       </c>
-      <c r="B429" s="2" t="s">
+      <c r="O429" s="2" t="s">
         <v>2417</v>
-      </c>
-      <c r="O429" s="2" t="s">
-        <v>2418</v>
       </c>
     </row>
     <row r="430" spans="1:15" ht="24.95" customHeight="1">
@@ -16202,7 +16217,7 @@
     </row>
     <row r="433" spans="1:15" ht="24.95" customHeight="1">
       <c r="A433" s="2" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>760</v>
@@ -16230,7 +16245,7 @@
         <v>1613</v>
       </c>
       <c r="O436" s="2" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="437" spans="1:15" ht="24.95" customHeight="1">
@@ -16343,13 +16358,13 @@
     </row>
     <row r="450" spans="1:15" ht="24.95" customHeight="1">
       <c r="A450" s="2" t="s">
+        <v>2293</v>
+      </c>
+      <c r="B450" s="2" t="s">
         <v>2294</v>
       </c>
-      <c r="B450" s="2" t="s">
+      <c r="O450" s="2" t="s">
         <v>2295</v>
-      </c>
-      <c r="O450" s="2" t="s">
-        <v>2296</v>
       </c>
     </row>
     <row r="451" spans="1:15" ht="24.95" customHeight="1">
@@ -16412,18 +16427,18 @@
     </row>
     <row r="459" spans="1:15" ht="24.95" customHeight="1">
       <c r="A459" s="2" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="O459" s="2" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="460" spans="1:15" ht="24.95" customHeight="1">
       <c r="A460" s="2" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="O460" s="2" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="461" spans="1:15" ht="24.95" customHeight="1">
@@ -16525,7 +16540,7 @@
         <v>1612</v>
       </c>
       <c r="O472" s="2" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="473" spans="1:15" ht="24.95" customHeight="1">
@@ -16536,7 +16551,7 @@
         <v>1807</v>
       </c>
       <c r="O473" s="2" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="474" spans="1:15" ht="24.95" customHeight="1">
@@ -16629,34 +16644,34 @@
     </row>
     <row r="484" spans="1:15" ht="24.95" customHeight="1">
       <c r="A484" s="2" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="O484" s="2" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="485" spans="1:15" ht="24.95" customHeight="1">
       <c r="A485" s="2" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="O485" s="2" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="486" spans="1:15" ht="24.95" customHeight="1">
       <c r="A486" s="2" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="O486" s="3" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="487" spans="1:15" ht="24.95" customHeight="1">
       <c r="A487" s="2" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="O487" s="3" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
     </row>
     <row r="488" spans="1:15" ht="24.95" customHeight="1">
@@ -16664,26 +16679,26 @@
     </row>
     <row r="489" spans="1:15" ht="24.95" customHeight="1">
       <c r="A489" s="2" t="s">
+        <v>2491</v>
+      </c>
+      <c r="O489" s="3" t="s">
         <v>2492</v>
-      </c>
-      <c r="O489" s="3" t="s">
-        <v>2493</v>
       </c>
     </row>
     <row r="490" spans="1:15" ht="24.95" customHeight="1">
       <c r="A490" s="2" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="O490" s="2" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="491" spans="1:15" ht="24.95" customHeight="1">
       <c r="A491" s="2" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="O491" s="2" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="492" spans="1:15" ht="24.95" customHeight="1">
@@ -16705,7 +16720,7 @@
         <v>1611</v>
       </c>
       <c r="O494" s="2" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="495" spans="1:15" ht="24.95" customHeight="1">
@@ -16713,7 +16728,7 @@
         <v>1639</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="O495" s="2" t="s">
         <v>1806</v>
@@ -16724,10 +16739,10 @@
         <v>940</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="O496" s="2" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="497" spans="1:15" ht="24.95" customHeight="1">
@@ -16735,7 +16750,7 @@
         <v>941</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="O497" s="2" t="s">
         <v>942</v>
@@ -16746,10 +16761,10 @@
         <v>943</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="O498" s="2" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="499" spans="1:15" ht="24.95" customHeight="1">
@@ -16768,7 +16783,7 @@
         <v>971</v>
       </c>
       <c r="O501" s="2" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
     </row>
     <row r="502" spans="1:15" ht="24.95" customHeight="1">
@@ -16792,7 +16807,7 @@
         <v>976</v>
       </c>
       <c r="O504" s="2" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="505" spans="1:15" ht="24.95" customHeight="1">
@@ -16852,13 +16867,13 @@
     </row>
     <row r="512" spans="1:15" ht="24.95" customHeight="1">
       <c r="A512" s="2" t="s">
+        <v>2899</v>
+      </c>
+      <c r="B512" s="2" t="s">
         <v>2900</v>
       </c>
-      <c r="B512" s="2" t="s">
+      <c r="O512" s="3" t="s">
         <v>2901</v>
-      </c>
-      <c r="O512" s="3" t="s">
-        <v>2902</v>
       </c>
     </row>
     <row r="513" spans="1:15" ht="24.95" customHeight="1">
@@ -16946,10 +16961,10 @@
     </row>
     <row r="522" spans="1:15" ht="24.95" customHeight="1">
       <c r="A522" s="2" t="s">
+        <v>2430</v>
+      </c>
+      <c r="O522" s="2" t="s">
         <v>2431</v>
-      </c>
-      <c r="O522" s="2" t="s">
-        <v>2432</v>
       </c>
     </row>
     <row r="523" spans="1:15" ht="24.95" customHeight="1">
@@ -16962,10 +16977,10 @@
     </row>
     <row r="524" spans="1:15" ht="24.95" customHeight="1">
       <c r="A524" s="2" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="O524" s="2" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="525" spans="1:15" ht="24.95" customHeight="1">
@@ -17026,7 +17041,7 @@
         <v>836</v>
       </c>
       <c r="O531" s="2" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="532" spans="1:15" ht="24.95" customHeight="1">
@@ -17384,7 +17399,7 @@
     </row>
     <row r="568" spans="1:15" ht="24.95" customHeight="1">
       <c r="A568" s="2" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>935</v>
@@ -17401,7 +17416,7 @@
         <v>920</v>
       </c>
       <c r="O569" s="2" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="570" spans="1:15" ht="24.95" customHeight="1">
@@ -17442,7 +17457,7 @@
         <v>930</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="O573" s="2" t="s">
         <v>931</v>
@@ -17475,7 +17490,7 @@
         <v>938</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="O576" s="2" t="s">
         <v>939</v>
@@ -17862,7 +17877,7 @@
         <v>1046</v>
       </c>
       <c r="O616" s="2" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="617" spans="1:15" ht="24.95" customHeight="1">
@@ -18069,7 +18084,7 @@
         <v>1073</v>
       </c>
       <c r="O637" s="2" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="638" spans="1:15" ht="24.95" customHeight="1">
@@ -18306,7 +18321,7 @@
     </row>
     <row r="662" spans="1:15" ht="24.95" customHeight="1">
       <c r="A662" s="2" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="B662" s="2" t="s">
         <v>601</v>
@@ -18337,7 +18352,7 @@
         <v>923</v>
       </c>
       <c r="O665" s="2" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="666" spans="1:15" ht="24.95" customHeight="1">
@@ -18364,18 +18379,18 @@
     </row>
     <row r="669" spans="1:15" ht="24.95" customHeight="1">
       <c r="A669" s="2" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="O669" s="2" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="670" spans="1:15" ht="24.95" customHeight="1">
       <c r="A670" s="2" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="O670" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="671" spans="1:15" ht="24.95" customHeight="1">
@@ -18449,7 +18464,7 @@
     </row>
     <row r="678" spans="1:15" ht="24.95" customHeight="1">
       <c r="A678" s="2" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="B678" s="2" t="s">
         <v>1154</v>
@@ -18474,58 +18489,58 @@
     </row>
     <row r="681" spans="1:15" ht="24.95" customHeight="1">
       <c r="A681" s="2" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="O681" s="2" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="682" spans="1:15" ht="24.95" customHeight="1">
       <c r="A682" s="2" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="O682" s="2" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="683" spans="1:15" ht="24.95" customHeight="1">
       <c r="A683" s="2" t="s">
+        <v>3082</v>
+      </c>
+      <c r="O683" s="2" t="s">
         <v>3083</v>
-      </c>
-      <c r="O683" s="2" t="s">
-        <v>3084</v>
       </c>
     </row>
     <row r="684" spans="1:15" ht="24.95" customHeight="1">
       <c r="A684" s="2" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="O684" s="2" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="685" spans="1:15" ht="24.95" customHeight="1">
       <c r="A685" s="2" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="O685" s="2" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="686" spans="1:15" ht="24.95" customHeight="1">
       <c r="A686" s="2" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="O686" s="2" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="687" spans="1:15" ht="24.95" customHeight="1">
       <c r="A687" s="2" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="O687" s="2" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="688" spans="1:15" ht="24.95" customHeight="1">
@@ -18561,26 +18576,26 @@
     </row>
     <row r="693" spans="1:15" ht="24.95" customHeight="1">
       <c r="A693" s="2" t="s">
+        <v>3190</v>
+      </c>
+      <c r="O693" s="2" t="s">
         <v>3191</v>
-      </c>
-      <c r="O693" s="2" t="s">
-        <v>3192</v>
       </c>
     </row>
     <row r="694" spans="1:15" ht="24.95" customHeight="1">
       <c r="A694" s="2" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="O694" s="2" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="695" spans="1:15" ht="24.95" customHeight="1">
       <c r="A695" s="2" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="O695" s="2" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="696" spans="1:15" ht="24.95" customHeight="1">
@@ -18757,10 +18772,10 @@
     </row>
     <row r="717" spans="1:15" ht="33">
       <c r="A717" s="2" t="s">
+        <v>2981</v>
+      </c>
+      <c r="O717" s="3" t="s">
         <v>2982</v>
-      </c>
-      <c r="O717" s="3" t="s">
-        <v>2983</v>
       </c>
     </row>
     <row r="718" spans="1:15" ht="24.95" customHeight="1">
@@ -18857,10 +18872,10 @@
     </row>
     <row r="731" spans="1:15" ht="24.95" customHeight="1">
       <c r="A731" s="2" t="s">
-        <v>1225</v>
+        <v>3194</v>
       </c>
       <c r="O731" s="2" t="s">
-        <v>826</v>
+        <v>3196</v>
       </c>
     </row>
     <row r="732" spans="1:15" ht="24.95" customHeight="1">
@@ -18868,13 +18883,10 @@
     </row>
     <row r="733" spans="1:15" ht="24.95" customHeight="1">
       <c r="A733" s="2" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B733" s="2" t="s">
-        <v>1771</v>
+        <v>1225</v>
       </c>
       <c r="O733" s="2" t="s">
-        <v>1227</v>
+        <v>826</v>
       </c>
     </row>
     <row r="734" spans="1:15" ht="24.95" customHeight="1">
@@ -18882,24 +18894,21 @@
     </row>
     <row r="735" spans="1:15" ht="24.95" customHeight="1">
       <c r="A735" s="2" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B735" s="2" t="s">
-        <v>1229</v>
+        <v>3192</v>
       </c>
       <c r="O735" s="2" t="s">
-        <v>1230</v>
+        <v>3193</v>
       </c>
     </row>
     <row r="736" spans="1:15" ht="24.95" customHeight="1">
       <c r="A736" s="2" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="B736" s="2" t="s">
-        <v>1232</v>
+        <v>1771</v>
       </c>
       <c r="O736" s="2" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="737" spans="1:15" ht="24.95" customHeight="1">
@@ -18907,24 +18916,24 @@
     </row>
     <row r="738" spans="1:15" ht="24.95" customHeight="1">
       <c r="A738" s="2" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="O738" s="2" t="s">
-        <v>1236</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="739" spans="1:15" ht="24.95" customHeight="1">
       <c r="A739" s="2" t="s">
-        <v>1237</v>
+        <v>1231</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>1238</v>
+        <v>1232</v>
       </c>
       <c r="O739" s="2" t="s">
-        <v>1239</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="740" spans="1:15" ht="24.95" customHeight="1">
@@ -18932,75 +18941,91 @@
     </row>
     <row r="741" spans="1:15" ht="24.95" customHeight="1">
       <c r="A741" s="2" t="s">
-        <v>1240</v>
+        <v>1234</v>
       </c>
       <c r="B741" s="2" t="s">
-        <v>1241</v>
+        <v>1235</v>
       </c>
       <c r="O741" s="2" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="742" spans="1:15" ht="24.95" customHeight="1">
       <c r="A742" s="2" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>1244</v>
+        <v>1238</v>
       </c>
       <c r="O742" s="2" t="s">
-        <v>1245</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="743" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A743" s="2" t="s">
-        <v>1246</v>
-      </c>
-      <c r="B743" s="2" t="s">
-        <v>1247</v>
-      </c>
-      <c r="O743" s="2" t="s">
-        <v>1248</v>
-      </c>
+      <c r="O743" s="2"/>
     </row>
     <row r="744" spans="1:15" ht="24.95" customHeight="1">
       <c r="A744" s="2" t="s">
-        <v>1249</v>
+        <v>1240</v>
       </c>
       <c r="B744" s="2" t="s">
-        <v>1250</v>
+        <v>1241</v>
       </c>
       <c r="O744" s="2" t="s">
-        <v>1251</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="745" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O745" s="2"/>
+      <c r="A745" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B745" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="O745" s="2" t="s">
+        <v>1245</v>
+      </c>
     </row>
     <row r="746" spans="1:15" ht="24.95" customHeight="1">
       <c r="A746" s="2" t="s">
-        <v>1603</v>
+        <v>1246</v>
+      </c>
+      <c r="B746" s="2" t="s">
+        <v>1247</v>
       </c>
       <c r="O746" s="2" t="s">
-        <v>1605</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="747" spans="1:15" ht="24.95" customHeight="1">
       <c r="A747" s="2" t="s">
-        <v>1604</v>
-      </c>
-      <c r="O747" s="3" t="s">
-        <v>1606</v>
+        <v>1249</v>
+      </c>
+      <c r="B747" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="O747" s="2" t="s">
+        <v>1251</v>
       </c>
     </row>
     <row r="748" spans="1:15" ht="24.95" customHeight="1">
       <c r="O748" s="2"/>
     </row>
     <row r="749" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O749" s="2"/>
+      <c r="A749" s="2" t="s">
+        <v>1603</v>
+      </c>
+      <c r="O749" s="2" t="s">
+        <v>1605</v>
+      </c>
     </row>
     <row r="750" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O750" s="2"/>
+      <c r="A750" s="2" t="s">
+        <v>1604</v>
+      </c>
+      <c r="O750" s="3" t="s">
+        <v>1606</v>
+      </c>
     </row>
     <row r="751" spans="1:15" ht="24.95" customHeight="1">
       <c r="O751" s="2"/>
@@ -19284,15 +19309,15 @@
     <row r="844" spans="15:15" ht="24.95" customHeight="1">
       <c r="O844" s="2"/>
     </row>
+    <row r="845" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O845" s="2"/>
+    </row>
     <row r="846" spans="15:15" ht="24.95" customHeight="1">
       <c r="O846" s="2"/>
     </row>
     <row r="847" spans="15:15" ht="24.95" customHeight="1">
       <c r="O847" s="2"/>
     </row>
-    <row r="848" spans="15:15" ht="24.95" customHeight="1">
-      <c r="O848" s="2"/>
-    </row>
     <row r="849" spans="15:15" ht="24.95" customHeight="1">
       <c r="O849" s="2"/>
     </row>
@@ -20464,20 +20489,7 @@
       <c r="O1238" s="2"/>
     </row>
     <row r="1239" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A1239" s="5"/>
-      <c r="B1239" s="5"/>
-      <c r="D1239" s="5"/>
-      <c r="E1239" s="5"/>
-      <c r="F1239" s="5"/>
-      <c r="G1239" s="5"/>
-      <c r="H1239" s="5"/>
-      <c r="I1239" s="5"/>
-      <c r="J1239" s="5"/>
-      <c r="K1239" s="5"/>
-      <c r="L1239" s="5"/>
-      <c r="M1239" s="5"/>
-      <c r="N1239" s="5"/>
-      <c r="O1239" s="6"/>
+      <c r="O1239" s="2"/>
     </row>
     <row r="1240" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1240" s="2"/>
@@ -20486,7 +20498,20 @@
       <c r="O1241" s="2"/>
     </row>
     <row r="1242" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O1242" s="2"/>
+      <c r="A1242" s="5"/>
+      <c r="B1242" s="5"/>
+      <c r="D1242" s="5"/>
+      <c r="E1242" s="5"/>
+      <c r="F1242" s="5"/>
+      <c r="G1242" s="5"/>
+      <c r="H1242" s="5"/>
+      <c r="I1242" s="5"/>
+      <c r="J1242" s="5"/>
+      <c r="K1242" s="5"/>
+      <c r="L1242" s="5"/>
+      <c r="M1242" s="5"/>
+      <c r="N1242" s="5"/>
+      <c r="O1242" s="6"/>
     </row>
     <row r="1243" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1243" s="2"/>
@@ -21994,8 +22019,17 @@
     <row r="1744" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1744" s="2"/>
     </row>
+    <row r="1745" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1745" s="2"/>
+    </row>
+    <row r="1746" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1746" s="2"/>
+    </row>
+    <row r="1747" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1747" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="O1:O1447" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="O1:O1450" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -22070,13 +22104,13 @@
     </row>
     <row r="2" spans="1:17" ht="24.95" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1252</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="54">
@@ -22084,10 +22118,10 @@
         <v>1253</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>2769</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="24.95" customHeight="1">
@@ -22142,7 +22176,7 @@
         <v>1267</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="54">
@@ -22150,10 +22184,10 @@
         <v>1268</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="36">
@@ -22164,7 +22198,7 @@
         <v>1270</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>2768</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="409.5">
@@ -22172,43 +22206,43 @@
         <v>1271</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2786</v>
+        <v>2785</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>2785</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="45" customHeight="1"/>
     <row r="13" spans="1:17" ht="45" customHeight="1">
       <c r="A13" s="1" t="s">
+        <v>2499</v>
+      </c>
+      <c r="O13" s="1" t="s">
         <v>2500</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>2501</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="45" customHeight="1">
       <c r="A14" s="1" t="s">
+        <v>2567</v>
+      </c>
+      <c r="O14" s="1" t="s">
         <v>2568</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>2569</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="45" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="45" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="24.95" customHeight="1">
@@ -22258,7 +22292,7 @@
     <row r="23" spans="1:15" s="2" customFormat="1" ht="24.95" customHeight="1"/>
     <row r="24" spans="1:15" s="2" customFormat="1" ht="24.95" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>106</v>
@@ -22272,18 +22306,18 @@
     </row>
     <row r="25" spans="1:15" ht="24.95" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="24.95" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>1283</v>
@@ -22360,90 +22394,90 @@
     </row>
     <row r="35" spans="1:15" ht="18">
       <c r="A35" s="1" t="s">
-        <v>2583</v>
+        <v>2582</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>2594</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="24.95" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>2596</v>
+        <v>2595</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>2593</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="24.95" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>2597</v>
+        <v>2596</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>2592</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="24.95" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>2586</v>
+        <v>2585</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>2598</v>
+        <v>2597</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>2591</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="36">
       <c r="A39" s="1" t="s">
-        <v>2587</v>
+        <v>2586</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>2599</v>
+        <v>2598</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>2590</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="24.95" customHeight="1">
       <c r="A40" s="1" t="s">
+        <v>2587</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>2588</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>2589</v>
-      </c>
       <c r="O40" s="1" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="24.95" customHeight="1">
       <c r="A42" s="1" t="s">
+        <v>2508</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>2510</v>
+      </c>
+      <c r="O42" s="1" t="s">
         <v>2509</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>2511</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>2510</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="24.95" customHeight="1">
       <c r="A43" s="1" t="s">
+        <v>2574</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>2575</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="O43" s="1" t="s">
         <v>2576</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>2577</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="24.95" customHeight="1">
@@ -22495,7 +22529,7 @@
         <v>1311</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="O50" s="1" t="s">
         <v>1312</v>
@@ -22503,24 +22537,24 @@
     </row>
     <row r="51" spans="1:15" ht="24.95" customHeight="1">
       <c r="A51" s="1" t="s">
+        <v>2468</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>2521</v>
+      </c>
+      <c r="O51" s="1" t="s">
         <v>2469</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>2522</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>2470</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="24.95" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="24.95" customHeight="1">
@@ -22536,453 +22570,453 @@
     </row>
     <row r="54" spans="1:15" ht="24.95" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="24.95" customHeight="1">
       <c r="A55" s="1" t="s">
+        <v>2916</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>2917</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>2918</v>
-      </c>
       <c r="O55" s="1" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="24.95" customHeight="1">
       <c r="A56" s="1" t="s">
+        <v>2914</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>2915</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>2916</v>
-      </c>
       <c r="O56" s="1" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="24.95" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>2770</v>
+        <v>2769</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>2772</v>
+      </c>
+      <c r="O57" s="1" t="s">
         <v>2773</v>
-      </c>
-      <c r="O57" s="1" t="s">
-        <v>2774</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="24.95" customHeight="1">
       <c r="A59" s="1" t="s">
+        <v>2542</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>2543</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="O59" s="1" t="s">
         <v>2544</v>
-      </c>
-      <c r="O59" s="1" t="s">
-        <v>2545</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="24.95" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>2545</v>
+      </c>
+      <c r="O60" s="1" t="s">
         <v>2546</v>
-      </c>
-      <c r="O60" s="1" t="s">
-        <v>2547</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="24.95" customHeight="1">
       <c r="A61" s="1" t="s">
+        <v>2548</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>2549</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="O61" s="1" t="s">
         <v>2550</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>2551</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="24.95" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="24.95" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="24.95" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="24.95" customHeight="1">
       <c r="A66" s="1" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="24.95" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="24.95" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="24.95" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="24.95" customHeight="1">
       <c r="A70" s="1" t="s">
+        <v>3017</v>
+      </c>
+      <c r="O70" s="1" t="s">
         <v>3018</v>
-      </c>
-      <c r="O70" s="1" t="s">
-        <v>3019</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="24.95" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="24.95" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="24.95" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="24.95" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="24.95" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="24.95" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="24.95" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="24.95" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="24.95" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="24.95" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
     </row>
     <row r="81" spans="1:15" ht="24.95" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="24.95" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
     </row>
     <row r="83" spans="1:15" ht="24.95" customHeight="1">
       <c r="A83" s="1" t="s">
+        <v>2972</v>
+      </c>
+      <c r="O83" s="1" t="s">
         <v>2973</v>
-      </c>
-      <c r="O83" s="1" t="s">
-        <v>2974</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="24.95" customHeight="1">
       <c r="A84" s="1" t="s">
+        <v>2974</v>
+      </c>
+      <c r="O84" s="1" t="s">
         <v>2975</v>
-      </c>
-      <c r="O84" s="1" t="s">
-        <v>2976</v>
       </c>
     </row>
     <row r="85" spans="1:15" ht="24.95" customHeight="1">
       <c r="A85" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="O85" s="1" t="s">
         <v>2977</v>
-      </c>
-      <c r="O85" s="1" t="s">
-        <v>2978</v>
       </c>
     </row>
     <row r="87" spans="1:15" ht="24.95" customHeight="1">
       <c r="A87" s="1" t="s">
+        <v>3164</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>3163</v>
+      </c>
+      <c r="O87" s="1" t="s">
         <v>3165</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>3164</v>
-      </c>
-      <c r="O87" s="1" t="s">
-        <v>3166</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="24.95" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="C88" s="1" t="s">
+        <v>3123</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>3124</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="E88" s="1" t="s">
         <v>3125</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="F88" s="1" t="s">
         <v>3126</v>
       </c>
-      <c r="F88" s="1" t="s">
+      <c r="G88" s="1" t="s">
         <v>3127</v>
       </c>
-      <c r="G88" s="1" t="s">
+      <c r="H88" s="1" t="s">
         <v>3128</v>
       </c>
-      <c r="H88" s="1" t="s">
+      <c r="I88" s="1" t="s">
         <v>3129</v>
       </c>
-      <c r="I88" s="1" t="s">
+      <c r="J88" s="1" t="s">
         <v>3130</v>
       </c>
-      <c r="J88" s="1" t="s">
+      <c r="K88" s="1" t="s">
         <v>3131</v>
       </c>
-      <c r="K88" s="1" t="s">
+      <c r="L88" s="1" t="s">
         <v>3132</v>
       </c>
-      <c r="L88" s="1" t="s">
+      <c r="M88" s="1" t="s">
         <v>3133</v>
       </c>
-      <c r="M88" s="1" t="s">
+      <c r="N88" s="1" t="s">
         <v>3134</v>
       </c>
-      <c r="N88" s="1" t="s">
-        <v>3135</v>
-      </c>
       <c r="O88" s="1" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="24.95" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="C89" s="1" t="s">
+        <v>3111</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>3112</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="E89" s="1" t="s">
         <v>3113</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="F89" s="1" t="s">
         <v>3114</v>
       </c>
-      <c r="F89" s="1" t="s">
+      <c r="G89" s="1" t="s">
         <v>3115</v>
       </c>
-      <c r="G89" s="1" t="s">
+      <c r="H89" s="1" t="s">
         <v>3116</v>
       </c>
-      <c r="H89" s="1" t="s">
+      <c r="I89" s="1" t="s">
         <v>3117</v>
       </c>
-      <c r="I89" s="1" t="s">
+      <c r="J89" s="1" t="s">
         <v>3118</v>
       </c>
-      <c r="J89" s="1" t="s">
+      <c r="K89" s="1" t="s">
         <v>3119</v>
       </c>
-      <c r="K89" s="1" t="s">
+      <c r="L89" s="1" t="s">
         <v>3120</v>
       </c>
-      <c r="L89" s="1" t="s">
+      <c r="M89" s="1" t="s">
         <v>3121</v>
       </c>
-      <c r="M89" s="1" t="s">
+      <c r="N89" s="1" t="s">
         <v>3122</v>
       </c>
-      <c r="N89" s="1" t="s">
-        <v>3123</v>
-      </c>
       <c r="O89" s="1" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="90" spans="1:15" ht="24.95" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="24.95" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
     </row>
     <row r="92" spans="1:15" ht="24.95" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="93" spans="1:15" ht="24.95" customHeight="1">
       <c r="A93" s="1" t="s">
+        <v>3156</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>3157</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="O93" s="1" t="s">
         <v>3158</v>
-      </c>
-      <c r="O93" s="1" t="s">
-        <v>3159</v>
       </c>
     </row>
     <row r="94" spans="1:15" ht="24.95" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
     </row>
     <row r="95" spans="1:15" ht="24.95" customHeight="1">
       <c r="A95" s="1" t="s">
+        <v>3168</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>3169</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>3170</v>
-      </c>
       <c r="O95" s="1" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
     </row>
     <row r="96" spans="1:15" ht="24.95" customHeight="1">
       <c r="A96" s="1" t="s">
+        <v>3175</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>3176</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>3177</v>
-      </c>
       <c r="O96" s="1" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="97" spans="1:15" ht="24.95" customHeight="1">
       <c r="A97" s="10" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="O97" s="1" t="s">
         <v>1853</v>
@@ -22990,24 +23024,24 @@
     </row>
     <row r="98" spans="1:15" ht="24.95" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="B98" s="1" t="s">
+        <v>3182</v>
+      </c>
+      <c r="O98" s="1" t="s">
         <v>3183</v>
-      </c>
-      <c r="O98" s="1" t="s">
-        <v>3184</v>
       </c>
     </row>
     <row r="99" spans="1:15" ht="24.95" customHeight="1">
       <c r="A99" s="1" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="B99" s="1" t="s">
+        <v>3178</v>
+      </c>
+      <c r="O99" s="1" t="s">
         <v>3179</v>
-      </c>
-      <c r="O99" s="1" t="s">
-        <v>3180</v>
       </c>
     </row>
   </sheetData>
@@ -23099,7 +23133,7 @@
         <v>1317</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="16.5">
@@ -23110,7 +23144,7 @@
         <v>1319</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="16.5">
@@ -23121,7 +23155,7 @@
         <v>1321</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="16.5">
@@ -23143,7 +23177,7 @@
         <v>1325</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="16.5">
@@ -23154,7 +23188,7 @@
         <v>1327</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="16.5">
@@ -23637,7 +23671,7 @@
     </row>
     <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>1428</v>
@@ -23673,21 +23707,21 @@
         <v>1436</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>2870</v>
+        <v>2869</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>2869</v>
+        <v>2868</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>1446</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1">
@@ -23904,7 +23938,7 @@
     </row>
     <row r="28" spans="1:15" ht="20.100000000000001" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>1495</v>
@@ -23915,7 +23949,7 @@
     </row>
     <row r="29" spans="1:15" ht="20.100000000000001" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>1497</v>
@@ -23948,7 +23982,7 @@
     </row>
     <row r="32" spans="1:15" ht="20.100000000000001" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>1505</v>
@@ -24262,7 +24296,7 @@
         <v>1441</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="20.100000000000001" customHeight="1">
@@ -24350,7 +24384,7 @@
         <v>1441</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="69" spans="1:17" ht="20.100000000000001" customHeight="1">
@@ -24559,90 +24593,90 @@
     </row>
     <row r="87" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A87" s="2" t="s">
+        <v>2290</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>2292</v>
+      </c>
+      <c r="O87" s="2" t="s">
         <v>2291</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>2293</v>
-      </c>
-      <c r="O87" s="2" t="s">
-        <v>2292</v>
       </c>
     </row>
     <row r="88" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A88" s="2" t="s">
+        <v>2489</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>2484</v>
+      </c>
+      <c r="O88" s="2" t="s">
         <v>2490</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>2485</v>
-      </c>
-      <c r="O88" s="2" t="s">
-        <v>2491</v>
       </c>
     </row>
     <row r="89" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A89" s="2" t="s">
+        <v>2511</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>2512</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="O89" s="2" t="s">
         <v>2513</v>
-      </c>
-      <c r="O89" s="2" t="s">
-        <v>2514</v>
       </c>
     </row>
     <row r="90" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A90" s="2" t="s">
+        <v>2601</v>
+      </c>
+      <c r="B90" s="2" t="s">
         <v>2602</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="O90" s="2" t="s">
         <v>2603</v>
-      </c>
-      <c r="O90" s="2" t="s">
-        <v>2604</v>
       </c>
     </row>
     <row r="91" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A91" s="2" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>2907</v>
+      </c>
+      <c r="O91" s="2" t="s">
         <v>2908</v>
-      </c>
-      <c r="O91" s="2" t="s">
-        <v>2909</v>
       </c>
     </row>
     <row r="92" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A92" s="2" t="s">
+        <v>3084</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>3085</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="O92" s="2" t="s">
         <v>3086</v>
-      </c>
-      <c r="O92" s="2" t="s">
-        <v>3087</v>
       </c>
     </row>
     <row r="93" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A93" s="2" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="94" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A94" s="2" t="s">
+        <v>3099</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>2907</v>
+      </c>
+      <c r="O94" s="2" t="s">
         <v>3100</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>2908</v>
-      </c>
-      <c r="O94" s="2" t="s">
-        <v>3101</v>
       </c>
     </row>
   </sheetData>
@@ -24715,7 +24749,7 @@
     </row>
     <row r="2" spans="1:17" ht="24.95" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>2631</v>
+        <v>2630</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>1650</v>
@@ -24760,7 +24794,7 @@
         <v>1881</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>2632</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -24792,29 +24826,29 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="7" t="s">
+        <v>2984</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>2984</v>
+      </c>
+      <c r="O13" s="7" t="s">
         <v>2985</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>2985</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>2986</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="7" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="7" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -24841,7 +24875,7 @@
         <v>1892</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="21" spans="1:15">
@@ -24860,7 +24894,7 @@
         <v>1895</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="23" spans="1:15">
@@ -24887,7 +24921,7 @@
         <v>1899</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="27" spans="1:15">
@@ -24895,7 +24929,7 @@
         <v>1900</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>2635</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="29" spans="1:15">
@@ -24906,7 +24940,7 @@
         <v>1901</v>
       </c>
       <c r="O29" s="7" t="s">
-        <v>2636</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="30" spans="1:15">
@@ -24914,7 +24948,7 @@
         <v>1902</v>
       </c>
       <c r="O30" s="7" t="s">
-        <v>2637</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="31" spans="1:15">
@@ -24922,7 +24956,7 @@
         <v>1903</v>
       </c>
       <c r="O31" s="7" t="s">
-        <v>2638</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="33" spans="1:15">
@@ -24949,7 +24983,7 @@
         <v>1908</v>
       </c>
       <c r="O35" s="7" t="s">
-        <v>2639</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="37" spans="1:15">
@@ -24968,7 +25002,7 @@
         <v>1813</v>
       </c>
       <c r="O38" s="7" t="s">
-        <v>2630</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="39" spans="1:15">
@@ -25022,7 +25056,7 @@
         <v>1917</v>
       </c>
       <c r="O46" s="7" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="47" spans="1:15">
@@ -25030,7 +25064,7 @@
         <v>1918</v>
       </c>
       <c r="O47" s="7" t="s">
-        <v>2641</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="49" spans="1:15">
@@ -25049,7 +25083,7 @@
         <v>1921</v>
       </c>
       <c r="O50" s="7" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="51" spans="1:15">
@@ -25057,7 +25091,7 @@
         <v>1922</v>
       </c>
       <c r="O51" s="7" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="53" spans="1:15">
@@ -25076,7 +25110,7 @@
         <v>1925</v>
       </c>
       <c r="O54" s="7" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="55" spans="1:15">
@@ -25103,7 +25137,7 @@
         <v>1930</v>
       </c>
       <c r="O58" s="7" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="59" spans="1:15">
@@ -25111,7 +25145,7 @@
         <v>1931</v>
       </c>
       <c r="O59" s="7" t="s">
-        <v>2645</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="61" spans="1:15">
@@ -25130,7 +25164,7 @@
         <v>1934</v>
       </c>
       <c r="O62" s="7" t="s">
-        <v>2760</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="63" spans="1:15">
@@ -25138,7 +25172,7 @@
         <v>1935</v>
       </c>
       <c r="O63" s="7" t="s">
-        <v>2646</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="65" spans="1:15">
@@ -25157,7 +25191,7 @@
         <v>1938</v>
       </c>
       <c r="O66" s="7" t="s">
-        <v>2629</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="67" spans="1:15">
@@ -25165,7 +25199,7 @@
         <v>1939</v>
       </c>
       <c r="O67" s="7" t="s">
-        <v>2647</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="69" spans="1:15">
@@ -25184,7 +25218,7 @@
         <v>1942</v>
       </c>
       <c r="O70" s="7" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="71" spans="1:15">
@@ -25192,7 +25226,7 @@
         <v>1943</v>
       </c>
       <c r="O71" s="7" t="s">
-        <v>2649</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="73" spans="1:15">
@@ -25200,10 +25234,10 @@
         <v>1944</v>
       </c>
       <c r="B73" s="7" t="s">
+        <v>2649</v>
+      </c>
+      <c r="O73" s="7" t="s">
         <v>2650</v>
-      </c>
-      <c r="O73" s="7" t="s">
-        <v>2651</v>
       </c>
     </row>
     <row r="74" spans="1:15">
@@ -25238,7 +25272,7 @@
         <v>1950</v>
       </c>
       <c r="O78" s="7" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="79" spans="1:15">
@@ -25246,7 +25280,7 @@
         <v>1951</v>
       </c>
       <c r="O79" s="7" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="81" spans="1:15">
@@ -25265,7 +25299,7 @@
         <v>1954</v>
       </c>
       <c r="O82" s="7" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="83" spans="1:15">
@@ -25292,7 +25326,7 @@
         <v>1959</v>
       </c>
       <c r="O86" s="7" t="s">
-        <v>2655</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="87" spans="1:15">
@@ -25300,7 +25334,7 @@
         <v>1960</v>
       </c>
       <c r="O87" s="7" t="s">
-        <v>2656</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="89" spans="1:15">
@@ -25319,7 +25353,7 @@
         <v>1963</v>
       </c>
       <c r="O90" s="7" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="91" spans="1:15">
@@ -25327,7 +25361,7 @@
         <v>1964</v>
       </c>
       <c r="O91" s="7" t="s">
-        <v>2658</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="93" spans="1:15">
@@ -25346,7 +25380,7 @@
         <v>1968</v>
       </c>
       <c r="O94" s="7" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="95" spans="1:15">
@@ -25354,7 +25388,7 @@
         <v>1969</v>
       </c>
       <c r="O95" s="7" t="s">
-        <v>2660</v>
+        <v>2659</v>
       </c>
     </row>
     <row r="97" spans="1:15">
@@ -25362,10 +25396,10 @@
         <v>1970</v>
       </c>
       <c r="B97" s="7" t="s">
+        <v>2660</v>
+      </c>
+      <c r="O97" s="7" t="s">
         <v>2661</v>
-      </c>
-      <c r="O97" s="7" t="s">
-        <v>2662</v>
       </c>
     </row>
     <row r="98" spans="1:15">
@@ -25373,7 +25407,7 @@
         <v>1702</v>
       </c>
       <c r="O98" s="7" t="s">
-        <v>2628</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="99" spans="1:15">
@@ -25381,7 +25415,7 @@
         <v>1704</v>
       </c>
       <c r="O99" s="7" t="s">
-        <v>2663</v>
+        <v>2662</v>
       </c>
     </row>
     <row r="101" spans="1:15">
@@ -25400,7 +25434,7 @@
         <v>1858</v>
       </c>
       <c r="O102" s="7" t="s">
-        <v>2664</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="103" spans="1:15">
@@ -25408,34 +25442,34 @@
         <v>1859</v>
       </c>
       <c r="O103" s="7" t="s">
-        <v>2665</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="105" spans="1:15">
       <c r="A105" s="7" t="s">
+        <v>2604</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>2604</v>
+      </c>
+      <c r="O105" s="7" t="s">
         <v>2605</v>
-      </c>
-      <c r="B105" s="7" t="s">
-        <v>2605</v>
-      </c>
-      <c r="O105" s="7" t="s">
-        <v>2606</v>
       </c>
     </row>
     <row r="106" spans="1:15">
       <c r="A106" s="7" t="s">
-        <v>2607</v>
+        <v>2606</v>
       </c>
       <c r="O106" s="7" t="s">
-        <v>2626</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="107" spans="1:15">
       <c r="A107" s="7" t="s">
-        <v>2608</v>
+        <v>2607</v>
       </c>
       <c r="O107" s="7" t="s">
-        <v>2625</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="109" spans="1:15">
@@ -25454,7 +25488,7 @@
         <v>1703</v>
       </c>
       <c r="O110" s="7" t="s">
-        <v>2666</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="111" spans="1:15">
@@ -25508,7 +25542,7 @@
         <v>1979</v>
       </c>
       <c r="O118" s="7" t="s">
-        <v>2667</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="119" spans="1:15">
@@ -25535,7 +25569,7 @@
         <v>1984</v>
       </c>
       <c r="O122" s="7" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="123" spans="1:15">
@@ -25543,7 +25577,7 @@
         <v>1985</v>
       </c>
       <c r="O123" s="7" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="125" spans="1:15">
@@ -25562,7 +25596,7 @@
         <v>1988</v>
       </c>
       <c r="O126" s="7" t="s">
-        <v>2670</v>
+        <v>2669</v>
       </c>
     </row>
     <row r="127" spans="1:15">
@@ -25570,7 +25604,7 @@
         <v>1989</v>
       </c>
       <c r="O127" s="7" t="s">
-        <v>2671</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="129" spans="1:15">
@@ -25589,7 +25623,7 @@
         <v>1992</v>
       </c>
       <c r="O130" s="7" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="131" spans="1:15">
@@ -25597,7 +25631,7 @@
         <v>1993</v>
       </c>
       <c r="O131" s="7" t="s">
-        <v>2673</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="133" spans="1:15">
@@ -25608,7 +25642,7 @@
         <v>1994</v>
       </c>
       <c r="O133" s="7" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="134" spans="1:15">
@@ -25629,56 +25663,56 @@
     </row>
     <row r="137" spans="1:15">
       <c r="A137" s="7" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="O137" s="7" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
     </row>
     <row r="138" spans="1:15">
       <c r="A138" s="7" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="O138" s="7" t="s">
-        <v>2910</v>
+        <v>2909</v>
       </c>
     </row>
     <row r="139" spans="1:15">
       <c r="A139" s="7" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
       <c r="O139" s="7" t="s">
-        <v>2911</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="141" spans="1:15">
       <c r="A141" s="7" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="O141" s="7" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="142" spans="1:15">
       <c r="A142" s="7" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="O142" s="7" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="143" spans="1:15">
       <c r="A143" s="7" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="O143" s="7" t="s">
-        <v>2675</v>
+        <v>2674</v>
       </c>
     </row>
     <row r="145" spans="1:15">
@@ -25697,7 +25731,7 @@
         <v>2000</v>
       </c>
       <c r="O146" s="7" t="s">
-        <v>2676</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="147" spans="1:15">
@@ -25797,7 +25831,7 @@
         <v>2019</v>
       </c>
       <c r="O161" s="7" t="s">
-        <v>2677</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="162" spans="1:15">
@@ -25805,7 +25839,7 @@
         <v>2020</v>
       </c>
       <c r="O162" s="7" t="s">
-        <v>2678</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="163" spans="1:15">
@@ -25813,7 +25847,7 @@
         <v>2021</v>
       </c>
       <c r="O163" s="7" t="s">
-        <v>2678</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="165" spans="1:15">
@@ -25824,7 +25858,7 @@
         <v>2022</v>
       </c>
       <c r="O165" s="7" t="s">
-        <v>2679</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="166" spans="1:15">
@@ -25832,7 +25866,7 @@
         <v>2023</v>
       </c>
       <c r="O166" s="7" t="s">
-        <v>2680</v>
+        <v>2679</v>
       </c>
     </row>
     <row r="167" spans="1:15">
@@ -25840,7 +25874,7 @@
         <v>2024</v>
       </c>
       <c r="O167" s="7" t="s">
-        <v>2681</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="169" spans="1:15">
@@ -25867,7 +25901,7 @@
         <v>2029</v>
       </c>
       <c r="O171" s="7" t="s">
-        <v>2682</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="173" spans="1:15">
@@ -25878,7 +25912,7 @@
         <v>2030</v>
       </c>
       <c r="O173" s="7" t="s">
-        <v>2683</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="174" spans="1:15">
@@ -25886,7 +25920,7 @@
         <v>2031</v>
       </c>
       <c r="O174" s="7" t="s">
-        <v>2684</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="175" spans="1:15">
@@ -25905,7 +25939,7 @@
         <v>2034</v>
       </c>
       <c r="O177" s="7" t="s">
-        <v>2685</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="178" spans="1:15">
@@ -25913,7 +25947,7 @@
         <v>2035</v>
       </c>
       <c r="O178" s="7" t="s">
-        <v>2686</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="179" spans="1:15">
@@ -25926,29 +25960,29 @@
     </row>
     <row r="181" spans="1:15">
       <c r="A181" s="7" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="O181" s="7" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="182" spans="1:15">
       <c r="A182" s="7" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="O182" s="7" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
     </row>
     <row r="183" spans="1:15">
       <c r="A183" s="7" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="O183" s="7" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="185" spans="1:15">
@@ -25959,7 +25993,7 @@
         <v>2038</v>
       </c>
       <c r="O185" s="7" t="s">
-        <v>2687</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="186" spans="1:15">
@@ -25967,7 +26001,7 @@
         <v>2039</v>
       </c>
       <c r="O186" s="7" t="s">
-        <v>2688</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="187" spans="1:15">
@@ -25975,7 +26009,7 @@
         <v>2040</v>
       </c>
       <c r="O187" s="7" t="s">
-        <v>2689</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="189" spans="1:15">
@@ -25994,7 +26028,7 @@
         <v>2043</v>
       </c>
       <c r="O190" s="7" t="s">
-        <v>2690</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="191" spans="1:15">
@@ -26002,7 +26036,7 @@
         <v>2044</v>
       </c>
       <c r="O191" s="7" t="s">
-        <v>2691</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="193" spans="1:15">
@@ -26029,7 +26063,7 @@
         <v>2049</v>
       </c>
       <c r="O195" s="7" t="s">
-        <v>2692</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="197" spans="1:15">
@@ -26048,7 +26082,7 @@
         <v>2052</v>
       </c>
       <c r="O198" s="7" t="s">
-        <v>2693</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="199" spans="1:15">
@@ -26056,7 +26090,7 @@
         <v>2053</v>
       </c>
       <c r="O199" s="7" t="s">
-        <v>2694</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="201" spans="1:15">
@@ -26075,7 +26109,7 @@
         <v>2056</v>
       </c>
       <c r="O202" s="7" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="203" spans="1:15">
@@ -26129,7 +26163,7 @@
         <v>2067</v>
       </c>
       <c r="O210" s="7" t="s">
-        <v>2696</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="211" spans="1:15">
@@ -26137,7 +26171,7 @@
         <v>2068</v>
       </c>
       <c r="O211" s="7" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="213" spans="1:15">
@@ -26148,7 +26182,7 @@
         <v>2069</v>
       </c>
       <c r="O213" s="7" t="s">
-        <v>2698</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="214" spans="1:15">
@@ -26156,7 +26190,7 @@
         <v>2070</v>
       </c>
       <c r="O214" s="7" t="s">
-        <v>2699</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="215" spans="1:15">
@@ -26183,7 +26217,7 @@
         <v>2075</v>
       </c>
       <c r="O218" s="7" t="s">
-        <v>2700</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="219" spans="1:15">
@@ -26191,7 +26225,7 @@
         <v>2076</v>
       </c>
       <c r="O219" s="7" t="s">
-        <v>2701</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="221" spans="1:15">
@@ -26210,7 +26244,7 @@
         <v>2079</v>
       </c>
       <c r="O222" s="7" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="223" spans="1:15">
@@ -26237,7 +26271,7 @@
         <v>2084</v>
       </c>
       <c r="O226" s="7" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="227" spans="1:15">
@@ -26245,7 +26279,7 @@
         <v>2085</v>
       </c>
       <c r="O227" s="7" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="229" spans="1:15">
@@ -26264,7 +26298,7 @@
         <v>2088</v>
       </c>
       <c r="O230" s="7" t="s">
-        <v>2704</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="231" spans="1:15">
@@ -26272,7 +26306,7 @@
         <v>2089</v>
       </c>
       <c r="O231" s="7" t="s">
-        <v>2646</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="233" spans="1:15">
@@ -26283,7 +26317,7 @@
         <v>2091</v>
       </c>
       <c r="O233" s="7" t="s">
-        <v>2705</v>
+        <v>2704</v>
       </c>
     </row>
     <row r="234" spans="1:15">
@@ -26291,7 +26325,7 @@
         <v>2092</v>
       </c>
       <c r="O234" s="7" t="s">
-        <v>2706</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="235" spans="1:15">
@@ -26299,7 +26333,7 @@
         <v>2093</v>
       </c>
       <c r="O235" s="7" t="s">
-        <v>2707</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="237" spans="1:15">
@@ -26310,7 +26344,7 @@
         <v>2095</v>
       </c>
       <c r="O237" s="7" t="s">
-        <v>2708</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="238" spans="1:15">
@@ -26326,7 +26360,7 @@
         <v>2098</v>
       </c>
       <c r="O239" s="7" t="s">
-        <v>2709</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="241" spans="1:15">
@@ -26342,18 +26376,18 @@
     </row>
     <row r="242" spans="1:15">
       <c r="A242" s="7" t="s">
+        <v>2709</v>
+      </c>
+      <c r="O242" s="7" t="s">
         <v>2710</v>
-      </c>
-      <c r="O242" s="7" t="s">
-        <v>2711</v>
       </c>
     </row>
     <row r="243" spans="1:15">
       <c r="A243" s="7" t="s">
+        <v>2711</v>
+      </c>
+      <c r="O243" s="7" t="s">
         <v>2712</v>
-      </c>
-      <c r="O243" s="7" t="s">
-        <v>2713</v>
       </c>
     </row>
     <row r="245" spans="1:15">
@@ -26380,7 +26414,7 @@
         <v>2104</v>
       </c>
       <c r="O247" s="7" t="s">
-        <v>2714</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="249" spans="1:15">
@@ -26399,7 +26433,7 @@
         <v>2107</v>
       </c>
       <c r="O250" s="7" t="s">
-        <v>2715</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="251" spans="1:15">
@@ -26407,7 +26441,7 @@
         <v>2108</v>
       </c>
       <c r="O251" s="7" t="s">
-        <v>2716</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="253" spans="1:15">
@@ -26426,7 +26460,7 @@
         <v>2111</v>
       </c>
       <c r="O254" s="7" t="s">
-        <v>2717</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="255" spans="1:15">
@@ -26453,7 +26487,7 @@
         <v>2116</v>
       </c>
       <c r="O258" s="7" t="s">
-        <v>2718</v>
+        <v>2717</v>
       </c>
     </row>
     <row r="259" spans="1:15">
@@ -26461,7 +26495,7 @@
         <v>2117</v>
       </c>
       <c r="O259" s="7" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="261" spans="1:15">
@@ -26480,7 +26514,7 @@
         <v>2120</v>
       </c>
       <c r="O262" s="7" t="s">
-        <v>2720</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="263" spans="1:15">
@@ -26507,7 +26541,7 @@
         <v>2125</v>
       </c>
       <c r="O266" s="7" t="s">
-        <v>2721</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="267" spans="1:15">
@@ -26515,7 +26549,7 @@
         <v>2126</v>
       </c>
       <c r="O267" s="7" t="s">
-        <v>2722</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="269" spans="1:15">
@@ -26534,7 +26568,7 @@
         <v>2129</v>
       </c>
       <c r="O270" s="7" t="s">
-        <v>2723</v>
+        <v>2722</v>
       </c>
     </row>
     <row r="271" spans="1:15">
@@ -26569,7 +26603,7 @@
         <v>2136</v>
       </c>
       <c r="O275" s="7" t="s">
-        <v>2724</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="277" spans="1:15">
@@ -26596,7 +26630,7 @@
         <v>2141</v>
       </c>
       <c r="O279" s="7" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="281" spans="1:15">
@@ -26615,7 +26649,7 @@
         <v>2144</v>
       </c>
       <c r="O282" s="7" t="s">
-        <v>2726</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="283" spans="1:15">
@@ -26623,7 +26657,7 @@
         <v>2145</v>
       </c>
       <c r="O283" s="7" t="s">
-        <v>2727</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="285" spans="1:15">
@@ -26650,7 +26684,7 @@
         <v>1839</v>
       </c>
       <c r="O287" s="7" t="s">
-        <v>2728</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="289" spans="1:15">
@@ -26682,56 +26716,56 @@
     </row>
     <row r="293" spans="1:15">
       <c r="A293" s="7" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="B293" s="7" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="O293" s="7" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="294" spans="1:15">
       <c r="A294" s="7" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="O294" s="7" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
     </row>
     <row r="295" spans="1:15">
       <c r="A295" s="7" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="O295" s="7" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="297" spans="1:15">
       <c r="A297" s="7" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="B297" s="7" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="O297" s="7" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="298" spans="1:15">
       <c r="A298" s="7" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="O298" s="7" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
     </row>
     <row r="299" spans="1:15">
       <c r="A299" s="7" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="O299" s="7" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="301" spans="1:15">
@@ -26750,7 +26784,7 @@
         <v>2151</v>
       </c>
       <c r="O302" s="7" t="s">
-        <v>2729</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="303" spans="1:15">
@@ -26766,7 +26800,7 @@
         <v>2154</v>
       </c>
       <c r="B305" s="7" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
       <c r="O305" s="7" t="s">
         <v>2155</v>
@@ -26777,7 +26811,7 @@
         <v>2156</v>
       </c>
       <c r="O306" s="7" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="307" spans="1:15">
@@ -26785,7 +26819,7 @@
         <v>2157</v>
       </c>
       <c r="O307" s="7" t="s">
-        <v>2732</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="309" spans="1:15">
@@ -26817,29 +26851,29 @@
     </row>
     <row r="313" spans="1:15">
       <c r="A313" s="7" t="s">
+        <v>2991</v>
+      </c>
+      <c r="B313" s="7" t="s">
+        <v>2990</v>
+      </c>
+      <c r="O313" s="7" t="s">
         <v>2992</v>
-      </c>
-      <c r="B313" s="7" t="s">
-        <v>2991</v>
-      </c>
-      <c r="O313" s="7" t="s">
-        <v>2993</v>
       </c>
     </row>
     <row r="314" spans="1:15">
       <c r="A314" s="7" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="O314" s="7" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
     </row>
     <row r="315" spans="1:15">
       <c r="A315" s="7" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="O315" s="7" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
     </row>
     <row r="317" spans="1:15">
@@ -26866,7 +26900,7 @@
         <v>2168</v>
       </c>
       <c r="O319" s="7" t="s">
-        <v>2733</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="321" spans="1:15">
@@ -26885,7 +26919,7 @@
         <v>2171</v>
       </c>
       <c r="O322" s="7" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="323" spans="1:15">
@@ -26893,7 +26927,7 @@
         <v>2172</v>
       </c>
       <c r="O323" s="7" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="325" spans="1:15">
@@ -26912,7 +26946,7 @@
         <v>2175</v>
       </c>
       <c r="O326" s="7" t="s">
-        <v>2734</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="327" spans="1:15">
@@ -26939,7 +26973,7 @@
         <v>2180</v>
       </c>
       <c r="O330" s="7" t="s">
-        <v>2735</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="331" spans="1:15">
@@ -26947,7 +26981,7 @@
         <v>2181</v>
       </c>
       <c r="O331" s="7" t="s">
-        <v>2736</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="333" spans="1:15">
@@ -26993,7 +27027,7 @@
         <v>2190</v>
       </c>
       <c r="O338" s="7" t="s">
-        <v>2737</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="339" spans="1:15">
@@ -27028,7 +27062,7 @@
         <v>2197</v>
       </c>
       <c r="O343" s="7" t="s">
-        <v>2738</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="345" spans="1:15">
@@ -27055,7 +27089,7 @@
         <v>2202</v>
       </c>
       <c r="O347" s="7" t="s">
-        <v>2739</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="349" spans="1:15">
@@ -27074,7 +27108,7 @@
         <v>2205</v>
       </c>
       <c r="O350" s="7" t="s">
-        <v>2740</v>
+        <v>2739</v>
       </c>
     </row>
     <row r="351" spans="1:15">
@@ -27136,7 +27170,7 @@
         <v>2217</v>
       </c>
       <c r="O359" s="7" t="s">
-        <v>2741</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="361" spans="1:15">
@@ -27155,7 +27189,7 @@
         <v>2220</v>
       </c>
       <c r="O362" s="7" t="s">
-        <v>2742</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="363" spans="1:15">
@@ -27190,7 +27224,7 @@
         <v>2227</v>
       </c>
       <c r="O367" s="7" t="s">
-        <v>2743</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="369" spans="1:15">
@@ -27209,7 +27243,7 @@
         <v>2230</v>
       </c>
       <c r="O370" s="7" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="371" spans="1:15">
@@ -27217,7 +27251,7 @@
         <v>2231</v>
       </c>
       <c r="O371" s="7" t="s">
-        <v>2745</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="373" spans="1:15">
@@ -27244,7 +27278,7 @@
         <v>2236</v>
       </c>
       <c r="O375" s="7" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="377" spans="1:15">
@@ -27263,7 +27297,7 @@
         <v>2239</v>
       </c>
       <c r="O378" s="7" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="379" spans="1:15">
@@ -27290,7 +27324,7 @@
         <v>2244</v>
       </c>
       <c r="O382" s="7" t="s">
-        <v>2748</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="383" spans="1:15">
@@ -27298,7 +27332,7 @@
         <v>2245</v>
       </c>
       <c r="O383" s="7" t="s">
-        <v>2749</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="385" spans="1:15">
@@ -27325,7 +27359,7 @@
         <v>2249</v>
       </c>
       <c r="O387" s="7" t="s">
-        <v>2750</v>
+        <v>2749</v>
       </c>
     </row>
     <row r="389" spans="1:15">
@@ -27352,7 +27386,7 @@
         <v>2254</v>
       </c>
       <c r="O391" s="7" t="s">
-        <v>2751</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="393" spans="1:15">
@@ -27371,7 +27405,7 @@
         <v>2257</v>
       </c>
       <c r="O394" s="7" t="s">
-        <v>2752</v>
+        <v>2751</v>
       </c>
     </row>
     <row r="395" spans="1:15">
@@ -27379,7 +27413,7 @@
         <v>2258</v>
       </c>
       <c r="O395" s="7" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="397" spans="1:15">
@@ -27390,239 +27424,239 @@
         <v>2259</v>
       </c>
       <c r="O397" s="7" t="s">
-        <v>2260</v>
+        <v>3195</v>
       </c>
     </row>
     <row r="398" spans="1:15">
       <c r="A398" s="7" t="s">
+        <v>2260</v>
+      </c>
+      <c r="O398" s="7" t="s">
         <v>2261</v>
-      </c>
-      <c r="O398" s="7" t="s">
-        <v>2262</v>
       </c>
     </row>
     <row r="399" spans="1:15">
       <c r="A399" s="7" t="s">
+        <v>2262</v>
+      </c>
+      <c r="O399" s="7" t="s">
         <v>2263</v>
-      </c>
-      <c r="O399" s="7" t="s">
-        <v>2264</v>
       </c>
     </row>
     <row r="401" spans="1:15">
       <c r="A401" s="7" t="s">
+        <v>2264</v>
+      </c>
+      <c r="B401" s="7" t="s">
+        <v>2753</v>
+      </c>
+      <c r="O401" s="7" t="s">
         <v>2265</v>
-      </c>
-      <c r="B401" s="7" t="s">
-        <v>2754</v>
-      </c>
-      <c r="O401" s="7" t="s">
-        <v>2266</v>
       </c>
     </row>
     <row r="402" spans="1:15">
       <c r="A402" s="7" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="O402" s="7" t="s">
-        <v>2755</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="403" spans="1:15">
       <c r="A403" s="7" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="O403" s="7" t="s">
-        <v>2755</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="405" spans="1:15">
       <c r="A405" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="B405" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="O405" s="7" t="s">
         <v>2269</v>
-      </c>
-      <c r="B405" s="7" t="s">
-        <v>2269</v>
-      </c>
-      <c r="O405" s="7" t="s">
-        <v>2270</v>
       </c>
     </row>
     <row r="406" spans="1:15">
       <c r="A406" s="7" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="O406" s="7" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="407" spans="1:15">
       <c r="A407" s="7" t="s">
+        <v>2271</v>
+      </c>
+      <c r="O407" s="7" t="s">
         <v>2272</v>
-      </c>
-      <c r="O407" s="7" t="s">
-        <v>2273</v>
       </c>
     </row>
     <row r="409" spans="1:15">
       <c r="A409" s="7" t="s">
+        <v>2273</v>
+      </c>
+      <c r="B409" s="7" t="s">
+        <v>2273</v>
+      </c>
+      <c r="O409" s="7" t="s">
         <v>2274</v>
-      </c>
-      <c r="B409" s="7" t="s">
-        <v>2274</v>
-      </c>
-      <c r="O409" s="7" t="s">
-        <v>2275</v>
       </c>
     </row>
     <row r="410" spans="1:15">
       <c r="A410" s="7" t="s">
+        <v>2275</v>
+      </c>
+      <c r="O410" s="7" t="s">
         <v>2276</v>
-      </c>
-      <c r="O410" s="7" t="s">
-        <v>2277</v>
       </c>
     </row>
     <row r="411" spans="1:15">
       <c r="A411" s="7" t="s">
+        <v>2277</v>
+      </c>
+      <c r="O411" s="7" t="s">
         <v>2278</v>
-      </c>
-      <c r="O411" s="7" t="s">
-        <v>2279</v>
       </c>
     </row>
     <row r="413" spans="1:15">
       <c r="A413" s="7" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="B413" s="7" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="O413" s="7" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
     </row>
     <row r="414" spans="1:15">
       <c r="A414" s="7" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
       <c r="O414" s="7" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
     </row>
     <row r="415" spans="1:15">
       <c r="A415" s="7" t="s">
-        <v>2884</v>
+        <v>2883</v>
       </c>
       <c r="O415" s="7" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
     </row>
     <row r="417" spans="1:15">
       <c r="A417" s="7" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="B417" s="7" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="O417" s="7" t="s">
-        <v>2895</v>
+        <v>2894</v>
       </c>
     </row>
     <row r="418" spans="1:15">
       <c r="A418" s="7" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="O418" s="7" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="419" spans="1:15">
       <c r="A419" s="7" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
       <c r="O419" s="7" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="421" spans="1:15">
       <c r="A421" s="7" t="s">
+        <v>2279</v>
+      </c>
+      <c r="B421" s="7" t="s">
+        <v>2279</v>
+      </c>
+      <c r="O421" s="7" t="s">
         <v>2280</v>
-      </c>
-      <c r="B421" s="7" t="s">
-        <v>2280</v>
-      </c>
-      <c r="O421" s="7" t="s">
-        <v>2281</v>
       </c>
     </row>
     <row r="422" spans="1:15">
       <c r="A422" s="7" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="O422" s="7" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="423" spans="1:15">
       <c r="A423" s="7" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="O423" s="7" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="425" spans="1:15">
       <c r="A425" s="7" t="s">
+        <v>2283</v>
+      </c>
+      <c r="B425" s="7" t="s">
+        <v>2283</v>
+      </c>
+      <c r="O425" s="7" t="s">
         <v>2284</v>
-      </c>
-      <c r="B425" s="7" t="s">
-        <v>2284</v>
-      </c>
-      <c r="O425" s="7" t="s">
-        <v>2285</v>
       </c>
     </row>
     <row r="426" spans="1:15">
       <c r="A426" s="7" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="O426" s="7" t="s">
-        <v>2758</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="427" spans="1:15">
       <c r="A427" s="7" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="O427" s="7" t="s">
-        <v>2758</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="429" spans="1:15">
       <c r="A429" s="7" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="B429" s="7" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="O429" s="7" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="430" spans="1:15">
       <c r="A430" s="7" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="O430" s="7" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="431" spans="1:15">
       <c r="A431" s="7" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="O431" s="7" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
     </row>
   </sheetData>
@@ -27698,42 +27732,42 @@
     </row>
     <row r="2" spans="1:17" ht="60" customHeight="1">
       <c r="A2" s="8" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="60" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="60" customHeight="1">
       <c r="A4" s="8" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>2792</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="60" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="60" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="60" customHeight="1">
@@ -27741,143 +27775,143 @@
         <v>1817</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="60" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>2779</v>
+        <v>2778</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="60" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="O9" s="9" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="60" customHeight="1">
       <c r="A10" s="8" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="60" customHeight="1">
       <c r="A11" s="8" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>2794</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="60" customHeight="1">
       <c r="A12" s="8" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>2795</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="60" customHeight="1">
       <c r="A13" s="8" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="60" customHeight="1">
       <c r="A14" s="8" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="O14" s="9" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="60" customHeight="1">
       <c r="A15" s="8" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>2796</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="60" customHeight="1">
       <c r="A16" s="8" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="O16" s="9" t="s">
-        <v>2797</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="60" customHeight="1">
       <c r="A17" s="8" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>2798</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="60" customHeight="1">
       <c r="A18" s="8" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="O18" s="9" t="s">
-        <v>2799</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="60" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="60" customHeight="1">
       <c r="A20" s="8" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>2801</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="60" customHeight="1">
       <c r="A21" s="8" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="60" customHeight="1">
       <c r="A22" s="8" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="60" customHeight="1">
       <c r="A23" s="8" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>2802</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="60" customHeight="1">
       <c r="A24" s="8" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="O24" s="9" t="s">
-        <v>2803</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="60" customHeight="1">
@@ -27885,7 +27919,7 @@
         <v>1856</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>2804</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="60" customHeight="1">
@@ -27893,15 +27927,15 @@
         <v>1857</v>
       </c>
       <c r="O26" s="9" t="s">
-        <v>2805</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="60" customHeight="1">
       <c r="A27" s="8" t="s">
+        <v>3092</v>
+      </c>
+      <c r="O27" s="9" t="s">
         <v>3093</v>
-      </c>
-      <c r="O27" s="9" t="s">
-        <v>3094</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="60" customHeight="1">
@@ -27909,15 +27943,15 @@
         <v>1714</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>2806</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="60" customHeight="1">
       <c r="A30" s="8" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="O30" s="9" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="60" customHeight="1">
@@ -27925,316 +27959,316 @@
         <v>1713</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>2807</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="60" customHeight="1">
       <c r="A32" s="8" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="O32" s="9" t="s">
-        <v>2808</v>
+        <v>2807</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="60" customHeight="1">
       <c r="A33" s="8" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="60" customHeight="1">
       <c r="A34" s="8" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="O34" s="9" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="60" customHeight="1">
       <c r="A35" s="8" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>2810</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="60" customHeight="1">
       <c r="A36" s="8" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="O36" s="9" t="s">
-        <v>2811</v>
+        <v>2810</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="60" customHeight="1">
       <c r="A37" s="8" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="60" customHeight="1">
       <c r="A38" s="8" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="O38" s="9" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="60" customHeight="1">
       <c r="A39" s="8" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>2814</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="60" customHeight="1">
       <c r="A40" s="8" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="O40" s="9" t="s">
-        <v>2815</v>
+        <v>2814</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="60" customHeight="1">
       <c r="A41" s="8" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>2816</v>
+        <v>2815</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="60" customHeight="1">
       <c r="A42" s="8" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="O42" s="9" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="60" customHeight="1">
       <c r="A43" s="8" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>2817</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="60" customHeight="1">
       <c r="A44" s="8" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="O44" s="9" t="s">
-        <v>2818</v>
+        <v>2817</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="60" customHeight="1">
       <c r="A45" s="8" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>2819</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="60" customHeight="1">
       <c r="A46" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="O46" s="9" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="60" customHeight="1">
       <c r="A47" s="8" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="60" customHeight="1">
       <c r="A48" s="8" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="O48" s="9" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="60" customHeight="1">
       <c r="A49" s="8" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="60" customHeight="1">
       <c r="A51" s="8" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="60" customHeight="1">
       <c r="A52" s="8" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="O52" s="9" t="s">
-        <v>2823</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="60" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="60" customHeight="1">
       <c r="A54" s="8" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="O54" s="9" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="60" customHeight="1">
       <c r="A55" s="8" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="60" customHeight="1">
       <c r="A56" s="8" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="O56" s="9" t="s">
-        <v>2775</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="60" customHeight="1">
       <c r="A57" s="8" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>2826</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="60" customHeight="1">
       <c r="A58" s="8" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="O58" s="9" t="s">
-        <v>2827</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="60" customHeight="1">
       <c r="A59" s="8" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="60" customHeight="1">
       <c r="A60" s="8" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="O60" s="9" t="s">
-        <v>2829</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="60" customHeight="1">
       <c r="A61" s="8" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>2830</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="60" customHeight="1">
       <c r="A62" s="8" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="O62" s="9" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="60" customHeight="1">
       <c r="A63" s="8" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>2832</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="60" customHeight="1">
       <c r="A64" s="8" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="O64" s="9" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="60" customHeight="1">
       <c r="A65" s="8" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="60" customHeight="1">
       <c r="A66" s="8" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="O66" s="9" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="60" customHeight="1">
       <c r="A67" s="8" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="60" customHeight="1">
       <c r="A68" s="8" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="O68" s="9" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="60" customHeight="1">
       <c r="A69" s="8" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="60" customHeight="1">
       <c r="A70" s="8" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="O70" s="9" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="60" customHeight="1">
       <c r="A71" s="8" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>1720</v>
@@ -28242,34 +28276,34 @@
     </row>
     <row r="72" spans="1:15" ht="60" customHeight="1">
       <c r="A72" s="8" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="O72" s="9" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="60" customHeight="1">
       <c r="A73" s="8" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="60" customHeight="1">
       <c r="A74" s="8" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="O74" s="9" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="60" customHeight="1">
       <c r="A75" s="8" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="60" customHeight="1">
@@ -28277,271 +28311,271 @@
         <v>1854</v>
       </c>
       <c r="O76" s="9" t="s">
-        <v>2876</v>
+        <v>2875</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="60" customHeight="1">
       <c r="A77" s="8" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="60" customHeight="1">
       <c r="A78" s="8" t="s">
+        <v>3095</v>
+      </c>
+      <c r="O78" s="9" t="s">
         <v>3096</v>
-      </c>
-      <c r="O78" s="9" t="s">
-        <v>3097</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="60" customHeight="1">
       <c r="A80" s="8" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="O80" s="9" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
     </row>
     <row r="81" spans="1:15" ht="60" customHeight="1">
       <c r="A81" s="8" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>2791</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="60" customHeight="1">
       <c r="A82" s="8" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="O82" s="9" t="s">
-        <v>2788</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="83" spans="1:15" ht="60" customHeight="1">
       <c r="A83" s="8" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="60" customHeight="1">
       <c r="A84" s="8" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="O84" s="9" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="85" spans="1:15" ht="60" customHeight="1">
       <c r="A85" s="8" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="86" spans="1:15" ht="60" customHeight="1">
       <c r="A86" s="8" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="O86" s="9" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="87" spans="1:15" ht="60" customHeight="1">
       <c r="A87" s="8" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="60" customHeight="1">
       <c r="A88" s="8" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="O88" s="9" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="60" customHeight="1">
       <c r="A89" s="8" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="90" spans="1:15" ht="60" customHeight="1">
       <c r="A90" s="8" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="O90" s="9" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="60" customHeight="1">
       <c r="A91" s="8" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="92" spans="1:15" ht="60" customHeight="1">
       <c r="A92" s="8" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="O92" s="9" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
     </row>
     <row r="93" spans="1:15" ht="60" customHeight="1">
       <c r="A93" s="8" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
     </row>
     <row r="94" spans="1:15" ht="60" customHeight="1">
       <c r="A94" s="8" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="O94" s="9" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
     </row>
     <row r="95" spans="1:15" ht="60" customHeight="1">
       <c r="A95" s="8" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>2789</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="96" spans="1:15" ht="60" customHeight="1">
       <c r="A96" s="8" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="O96" s="9" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="97" spans="1:15" ht="60" customHeight="1">
       <c r="A97" s="8" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="98" spans="1:15" ht="60" customHeight="1">
       <c r="A98" s="8" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="O98" s="9" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="99" spans="1:15" ht="60" customHeight="1">
       <c r="A99" s="8" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="100" spans="1:15" ht="60" customHeight="1">
       <c r="A100" s="8" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="O100" s="9" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="101" spans="1:15" ht="60" customHeight="1">
       <c r="A101" s="8" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="102" spans="1:15" ht="60" customHeight="1">
       <c r="A102" s="8" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="O102" s="9" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="103" spans="1:15" ht="60" customHeight="1">
       <c r="A103" s="8" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="104" spans="1:15" ht="60" customHeight="1">
       <c r="A104" s="8" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="O104" s="9" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
     </row>
     <row r="105" spans="1:15" ht="60" customHeight="1">
       <c r="A105" s="8" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
     </row>
     <row r="106" spans="1:15" ht="60" customHeight="1">
       <c r="A106" s="8" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="O106" s="9" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
     </row>
     <row r="107" spans="1:15" ht="60" customHeight="1">
       <c r="A107" s="8" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
     </row>
     <row r="108" spans="1:15" ht="60" customHeight="1">
       <c r="A108" s="8" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="O108" s="9" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="109" spans="1:15" ht="60" customHeight="1">
       <c r="A109" s="8" t="s">
+        <v>2886</v>
+      </c>
+      <c r="O109" s="9" t="s">
         <v>2887</v>
-      </c>
-      <c r="O109" s="9" t="s">
-        <v>2888</v>
       </c>
     </row>
     <row r="110" spans="1:15" ht="60" customHeight="1">
       <c r="A110" s="8" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="O110" s="9" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
     </row>
   </sheetData>

--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Among Us code\TheOtherUs\TheOtherUs-Edited-Lite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A120D4AD-88FA-4307-996C-3709205F0BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830F0ABE-4B9F-4CE7-8B98-00975C740F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="1200" windowWidth="25755" windowHeight="14910" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="720" yWindow="1200" windowWidth="25755" windowHeight="14910" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Options" sheetId="3" r:id="rId1"/>
@@ -5002,14 +5002,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> (隐身)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>JackalIsSwooperInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>pursuerEnableBlanks</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -11316,14 +11308,6 @@
   </si>
   <si>
     <t>寻找主人喵</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BandLeaderInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(乐队成员)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -11452,9 +11436,81 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>乐队主唱需要寻找三位乐队成员，招募不会影响玩家的职业与阵营。
-每次进入会议时会进行判断是否能成立乐队。成立需要三位成员同属与
-一个类型（三位需同属与船员、红狼或中立）。
+    <t>欢迎游玩&lt;color=#ff351f&gt;&lt;size=120%&gt;我们的超多职业&lt;/size&gt;&lt;/color&gt; ！
+游戏指令【指令和内容中间需要空格】：
+/r [职业名称] ：获取该职业的介绍
+/m ：游戏内使用，获取自己已有职业的介绍
+如需查看其它指令请输入：/cmd</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏中指令：
+/end ：强制游戏结束
+/mt 召集/结束会议
+/kill [玩家名称] ：强制击杀玩家
+/revive [玩家名称] ： 强制复活玩家
+/say [内容] : 向所有玩家发送房主消息</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>killCooldown</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>schrodingersCatTeamChanges</t>
+  </si>
+  <si>
+    <t>schrodingersCatMaxChangeCount</t>
+  </si>
+  <si>
+    <t>schrodingersCatIsGuessable</t>
+  </si>
+  <si>
+    <t>可以连续变更阵营</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以变更阵营的次数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以被赌怪猜测而死</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>schrodingersCatCanKill</t>
+  </si>
+  <si>
+    <t>非船员阵营时允许击杀玩家</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>thiefCanKill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">身份窃贼可以击杀 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief Can Kill </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SchrodingersCatFullDesc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>薛定谔的猫被其他玩家击杀后，可以加入对方阵营。
+以下职业功能将按照房间设置决定：
+薛定谔的猫不允许被赌怪猜测；
+非船员阵营的猫会获得击杀技能；
+允许猫被击杀多次且加入对方阵营。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>乐队主唱需要寻找三位乐队成员，招募不会影响玩家的职业与阵营。标记
+在成立之前不会向队员完全显示。每次进入会议时会进行判断是否能成立乐队。
+成立需要三位成员同属与一个类型（三位需同属与船员、红狼或中立）。
 在乐队成立之前，乐队主唱可以在会议外踢出成员，且游戏结束时仍然未成立
 乐队则无法胜利。乐队成立后固定胜利条件和成员，无法变更(除非主唱消失)
 乐队成立后，乐队的胜利条件变更为：
@@ -11465,63 +11521,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>欢迎游玩&lt;color=#ff351f&gt;&lt;size=120%&gt;我们的超多职业&lt;/size&gt;&lt;/color&gt; ！
-游戏指令【指令和内容中间需要空格】：
-/r [职业名称] ：获取该职业的介绍
-/m ：游戏内使用，获取自己已有职业的介绍
-如需查看其它指令请输入：/cmd</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>游戏中指令：
-/end ：强制游戏结束
-/mt 召集/结束会议
-/kill [玩家名称] ：强制击杀玩家
-/revive [玩家名称] ： 强制复活玩家
-/say [内容] : 向所有玩家发送房主消息</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>killCooldown</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>schrodingersCatTeamChanges</t>
-  </si>
-  <si>
-    <t>schrodingersCatMaxChangeCount</t>
-  </si>
-  <si>
-    <t>schrodingersCatIsGuessable</t>
-  </si>
-  <si>
-    <t>可以连续变更阵营</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以变更阵营的次数</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以被赌怪猜测而死</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>schrodingersCatCanKill</t>
-  </si>
-  <si>
-    <t>非船员阵营时允许击杀玩家</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>thiefCanKill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">身份窃贼可以击杀 </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief Can Kill </t>
+    <t>JackalIsSwooperInfo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> (隐身)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -12202,7 +12206,7 @@
     </row>
     <row r="4" spans="1:17" ht="24.95" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>2552</v>
+        <v>2550</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>20</v>
@@ -12257,24 +12261,24 @@
     </row>
     <row r="9" spans="1:17" ht="24.75" customHeight="1">
       <c r="A9" s="2" t="s">
+        <v>2446</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>2447</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>2448</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>2449</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>2450</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="24.75" customHeight="1">
       <c r="A10" s="2" t="s">
+        <v>2547</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>2548</v>
+      </c>
+      <c r="O10" s="3" t="s">
         <v>2549</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>2550</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>2551</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="24.95" customHeight="1">
@@ -12290,156 +12294,156 @@
     </row>
     <row r="13" spans="1:17" ht="24.95" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>2425</v>
+        <v>2423</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="24.95" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>2424</v>
+        <v>2422</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>2427</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="24.95" customHeight="1">
       <c r="A15" s="2" t="s">
+        <v>2435</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>2436</v>
+      </c>
+      <c r="O15" s="3" t="s">
         <v>2437</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>2438</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>2439</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="24.95" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>2444</v>
+        <v>2442</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="24.95" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>2966</v>
+        <v>2964</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="24.95" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>2967</v>
+        <v>2965</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="24.95" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>2454</v>
+        <v>2452</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>2447</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="24.95" customHeight="1">
       <c r="A20" s="2" t="s">
+        <v>2503</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>2504</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>2505</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>2506</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>2507</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="24.95" customHeight="1">
       <c r="A21" s="2" t="s">
+        <v>2453</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>2454</v>
+      </c>
+      <c r="O21" s="3" t="s">
         <v>2455</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>2456</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>2457</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="24.95" customHeight="1">
       <c r="A22" s="2" t="s">
+        <v>2748</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>2750</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>2752</v>
-      </c>
       <c r="O22" s="3" t="s">
-        <v>2751</v>
+        <v>2749</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="24.95" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>2753</v>
+        <v>2751</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>2545</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="24.95" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>2428</v>
+        <v>2426</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>2443</v>
+        <v>2441</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="24.95" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>2445</v>
+        <v>2443</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>2446</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="24.95" customHeight="1">
       <c r="A26" s="2" t="s">
+        <v>2449</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>2451</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>2453</v>
-      </c>
       <c r="O26" s="3" t="s">
-        <v>2452</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="24.95" customHeight="1">
@@ -12469,7 +12473,7 @@
     </row>
     <row r="30" spans="1:15" ht="24.95" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>2965</v>
+        <v>2963</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>42</v>
@@ -12480,7 +12484,7 @@
     </row>
     <row r="31" spans="1:15" ht="24.95" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>44</v>
@@ -12494,7 +12498,7 @@
         <v>99</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>100</v>
@@ -12505,7 +12509,7 @@
         <v>101</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>102</v>
@@ -12516,10 +12520,10 @@
         <v>103</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="24.95" customHeight="1">
@@ -12527,7 +12531,7 @@
         <v>104</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>105</v>
@@ -12535,13 +12539,13 @@
     </row>
     <row r="36" spans="1:15" ht="24.95" customHeight="1">
       <c r="A36" s="2" t="s">
+        <v>2873</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>2874</v>
+      </c>
+      <c r="O36" s="3" t="s">
         <v>2875</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>2876</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>2877</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="24.95" customHeight="1">
@@ -12549,7 +12553,7 @@
         <v>97</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="O37" s="3" t="s">
         <v>98</v>
@@ -12582,21 +12586,21 @@
     </row>
     <row r="41" spans="1:15" ht="24.95" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>52</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>2548</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="24.95" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>54</v>
@@ -12604,7 +12608,7 @@
     </row>
     <row r="43" spans="1:15" ht="24.95" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>55</v>
@@ -12615,7 +12619,7 @@
     </row>
     <row r="44" spans="1:15" ht="24.95" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>57</v>
@@ -12626,13 +12630,13 @@
     </row>
     <row r="45" spans="1:15" ht="24.95" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>2920</v>
+        <v>2918</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>2866</v>
+        <v>2864</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>2867</v>
+        <v>2865</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="24.95" customHeight="1">
@@ -12641,7 +12645,7 @@
     </row>
     <row r="47" spans="1:15" ht="24.95" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>2310</v>
+        <v>2308</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>59</v>
@@ -12652,7 +12656,7 @@
     </row>
     <row r="48" spans="1:15" ht="24.95" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>2309</v>
+        <v>2307</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>60</v>
@@ -12663,7 +12667,7 @@
     </row>
     <row r="49" spans="1:15" ht="24.95" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>2307</v>
+        <v>2305</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>61</v>
@@ -12674,7 +12678,7 @@
     </row>
     <row r="50" spans="1:15" ht="24.95" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>2308</v>
+        <v>2306</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>62</v>
@@ -12692,7 +12696,7 @@
         <v>63</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>2754</v>
+        <v>2752</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>64</v>
@@ -12722,33 +12726,33 @@
     </row>
     <row r="55" spans="1:15" ht="24.95" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>2546</v>
+        <v>2544</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>2547</v>
+        <v>2545</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>2553</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="24.95" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>2559</v>
+        <v>2557</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>2560</v>
+        <v>2558</v>
       </c>
       <c r="C56" s="3"/>
       <c r="O56" s="3" t="s">
-        <v>2561</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="24.95" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>3028</v>
+        <v>3026</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>3028</v>
+        <v>3026</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>1150</v>
@@ -12756,10 +12760,10 @@
     </row>
     <row r="58" spans="1:15" ht="24.95" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>3051</v>
+        <v>3049</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>3048</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="24.95" customHeight="1">
@@ -12798,7 +12802,7 @@
         <v>74</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="24.95" customHeight="1">
@@ -12809,7 +12813,7 @@
         <v>76</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="24.95" customHeight="1">
@@ -12853,7 +12857,7 @@
         <v>87</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="24.95" customHeight="1">
@@ -12894,24 +12898,24 @@
     </row>
     <row r="74" spans="1:15" ht="24.95" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="24.95" customHeight="1">
       <c r="A75" s="2" t="s">
+        <v>2857</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>2859</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>2861</v>
-      </c>
       <c r="O75" s="2" t="s">
-        <v>2860</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="24.95" customHeight="1">
@@ -12938,18 +12942,18 @@
     </row>
     <row r="78" spans="1:15" ht="24.95" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>3043</v>
+        <v>3041</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="24.95" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>3044</v>
+        <v>3042</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="24.95" customHeight="1">
@@ -13161,7 +13165,7 @@
         <v>170</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="O99" s="2" t="s">
         <v>171</v>
@@ -13169,24 +13173,24 @@
     </row>
     <row r="100" spans="1:15" ht="24.95" customHeight="1">
       <c r="A100" s="2" t="s">
-        <v>2517</v>
+        <v>2515</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>2520</v>
+        <v>2518</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>2758</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="101" spans="1:15" ht="24.95" customHeight="1">
       <c r="A101" s="2" t="s">
-        <v>2518</v>
+        <v>2516</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>2519</v>
+        <v>2517</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>2759</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="102" spans="1:15" ht="24.95" customHeight="1">
@@ -13238,79 +13242,79 @@
     </row>
     <row r="107" spans="1:15" ht="24.95" customHeight="1">
       <c r="A107" s="2" t="s">
-        <v>3125</v>
+        <v>3123</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>3126</v>
+        <v>3124</v>
       </c>
       <c r="O107" s="2" t="s">
-        <v>3131</v>
+        <v>3129</v>
       </c>
     </row>
     <row r="108" spans="1:15" ht="24.95" customHeight="1">
       <c r="A108" s="2" t="s">
-        <v>3141</v>
+        <v>3139</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>3124</v>
+        <v>3122</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>3132</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="109" spans="1:15" ht="24.95" customHeight="1">
       <c r="A109" s="2" t="s">
-        <v>3140</v>
+        <v>3138</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>3127</v>
+        <v>3125</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>3133</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="110" spans="1:15" ht="24.95" customHeight="1">
       <c r="A110" s="2" t="s">
-        <v>3139</v>
+        <v>3137</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>3128</v>
+        <v>3126</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>3134</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="111" spans="1:15" ht="24.95" customHeight="1">
       <c r="A111" s="2" t="s">
-        <v>3138</v>
+        <v>3136</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>3129</v>
+        <v>3127</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>3136</v>
+        <v>3134</v>
       </c>
     </row>
     <row r="112" spans="1:15" ht="24.95" customHeight="1">
       <c r="A112" s="2" t="s">
-        <v>3137</v>
+        <v>3135</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>3130</v>
+        <v>3128</v>
       </c>
       <c r="O112" s="2" t="s">
-        <v>3135</v>
+        <v>3133</v>
       </c>
     </row>
     <row r="113" spans="1:15" ht="24.95" customHeight="1">
       <c r="A113" s="2" t="s">
+        <v>3156</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>3157</v>
+      </c>
+      <c r="O113" s="2" t="s">
         <v>3158</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>3159</v>
-      </c>
-      <c r="O113" s="2" t="s">
-        <v>3160</v>
       </c>
     </row>
     <row r="114" spans="1:15" ht="24.95" customHeight="1">
@@ -13318,42 +13322,42 @@
     </row>
     <row r="115" spans="1:15" ht="24.95" customHeight="1">
       <c r="A115" s="2" t="s">
-        <v>3033</v>
+        <v>3031</v>
       </c>
       <c r="O115" s="2" t="s">
-        <v>3038</v>
+        <v>3036</v>
       </c>
     </row>
     <row r="116" spans="1:15" ht="24.95" customHeight="1">
       <c r="A116" s="2" t="s">
-        <v>3034</v>
+        <v>3032</v>
       </c>
       <c r="O116" s="2" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="117" spans="1:15" ht="24.95" customHeight="1">
       <c r="A117" s="2" t="s">
-        <v>3035</v>
+        <v>3033</v>
       </c>
       <c r="O117" s="2" t="s">
-        <v>3040</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="118" spans="1:15" ht="24.95" customHeight="1">
       <c r="A118" s="2" t="s">
-        <v>3036</v>
+        <v>3034</v>
       </c>
       <c r="O118" s="2" t="s">
-        <v>3041</v>
+        <v>3039</v>
       </c>
     </row>
     <row r="119" spans="1:15" ht="24.95" customHeight="1">
       <c r="A119" s="2" t="s">
-        <v>3037</v>
+        <v>3035</v>
       </c>
       <c r="O119" s="2" t="s">
-        <v>3042</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="120" spans="1:15" ht="24.95" customHeight="1">
@@ -13394,13 +13398,13 @@
     </row>
     <row r="124" spans="1:15" ht="24.95" customHeight="1">
       <c r="A124" s="2" t="s">
+        <v>3016</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>3017</v>
+      </c>
+      <c r="O124" s="2" t="s">
         <v>3018</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>3019</v>
-      </c>
-      <c r="O124" s="2" t="s">
-        <v>3020</v>
       </c>
     </row>
     <row r="125" spans="1:15" ht="24.95" customHeight="1">
@@ -13444,7 +13448,7 @@
         <v>203</v>
       </c>
       <c r="O128" s="2" t="s">
-        <v>2423</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="129" spans="1:15" ht="24.95" customHeight="1">
@@ -13471,13 +13475,13 @@
     </row>
     <row r="131" spans="1:15" ht="24.95" customHeight="1">
       <c r="A131" s="2" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>210</v>
       </c>
       <c r="O131" s="2" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="132" spans="1:15" ht="24.95" customHeight="1">
@@ -13504,18 +13508,18 @@
     </row>
     <row r="134" spans="1:15" ht="24.95" customHeight="1">
       <c r="A134" s="2" t="s">
-        <v>2568</v>
+        <v>2566</v>
       </c>
       <c r="O134" s="2" t="s">
-        <v>2569</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="135" spans="1:15" ht="24.95" customHeight="1">
       <c r="A135" s="2" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="O135" s="3" t="s">
-        <v>2554</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="136" spans="1:15" ht="24.95" customHeight="1">
@@ -13575,7 +13579,7 @@
     </row>
     <row r="141" spans="1:15" ht="24.95" customHeight="1">
       <c r="A141" s="2" t="s">
-        <v>2508</v>
+        <v>2506</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>232</v>
@@ -13586,10 +13590,10 @@
     </row>
     <row r="142" spans="1:15" ht="24.95" customHeight="1">
       <c r="A142" s="2" t="s">
-        <v>2542</v>
+        <v>2540</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>2543</v>
+        <v>2541</v>
       </c>
       <c r="O142" s="2" t="s">
         <v>234</v>
@@ -13647,7 +13651,7 @@
         <v>247</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="O148" s="3" t="s">
         <v>248</v>
@@ -13658,7 +13662,7 @@
         <v>249</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="O149" s="2" t="s">
         <v>250</v>
@@ -13666,10 +13670,10 @@
     </row>
     <row r="150" spans="1:15" ht="24.95" customHeight="1">
       <c r="A150" s="2" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="O150" s="2" t="s">
         <v>252</v>
@@ -13680,10 +13684,10 @@
         <v>251</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="O151" s="2" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="152" spans="1:15" ht="24.95" customHeight="1">
@@ -13691,7 +13695,7 @@
         <v>253</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="O152" s="2" t="s">
         <v>254</v>
@@ -13702,7 +13706,7 @@
         <v>255</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="O153" s="2" t="s">
         <v>256</v>
@@ -13713,7 +13717,7 @@
         <v>257</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="O154" s="2" t="s">
         <v>258</v>
@@ -13724,7 +13728,7 @@
         <v>259</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="O155" s="2" t="s">
         <v>260</v>
@@ -13735,7 +13739,7 @@
         <v>261</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="O156" s="2" t="s">
         <v>262</v>
@@ -13746,18 +13750,18 @@
     </row>
     <row r="158" spans="1:15" ht="24.95" customHeight="1">
       <c r="A158" s="2" t="s">
+        <v>2914</v>
+      </c>
+      <c r="O158" s="2" t="s">
         <v>2916</v>
-      </c>
-      <c r="O158" s="2" t="s">
-        <v>2918</v>
       </c>
     </row>
     <row r="159" spans="1:15" ht="24.95" customHeight="1">
       <c r="A159" s="2" t="s">
+        <v>2915</v>
+      </c>
+      <c r="O159" s="2" t="s">
         <v>2917</v>
-      </c>
-      <c r="O159" s="2" t="s">
-        <v>2919</v>
       </c>
     </row>
     <row r="160" spans="1:15" ht="24.95" customHeight="1">
@@ -13812,7 +13816,7 @@
         <v>273</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="O165" s="2" t="s">
         <v>274</v>
@@ -13867,7 +13871,7 @@
         <v>286</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="O170" s="2" t="s">
         <v>287</v>
@@ -13875,10 +13879,10 @@
     </row>
     <row r="171" spans="1:15" ht="24.95" customHeight="1">
       <c r="A171" s="2" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="O171" s="2" t="s">
         <v>288</v>
@@ -13889,7 +13893,7 @@
         <v>289</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="O172" s="2" t="s">
         <v>290</v>
@@ -13911,7 +13915,7 @@
         <v>293</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="O174" s="2" t="s">
         <v>294</v>
@@ -13936,7 +13940,7 @@
         <v>298</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>2469</v>
+        <v>2467</v>
       </c>
       <c r="O177" s="2" t="s">
         <v>299</v>
@@ -13947,24 +13951,24 @@
     </row>
     <row r="179" spans="1:15" ht="24.95" customHeight="1">
       <c r="A179" s="2" t="s">
-        <v>2466</v>
+        <v>2464</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>300</v>
       </c>
       <c r="O179" s="2" t="s">
-        <v>2465</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="180" spans="1:15" ht="24.95" customHeight="1">
       <c r="A180" s="2" t="s">
-        <v>2566</v>
+        <v>2564</v>
       </c>
       <c r="B180" s="2" t="s">
+        <v>2563</v>
+      </c>
+      <c r="O180" s="2" t="s">
         <v>2565</v>
-      </c>
-      <c r="O180" s="2" t="s">
-        <v>2567</v>
       </c>
     </row>
     <row r="181" spans="1:15" ht="24.95" customHeight="1">
@@ -14063,7 +14067,7 @@
         <v>326</v>
       </c>
       <c r="O189" s="2" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="190" spans="1:15" ht="24.95" customHeight="1">
@@ -14093,26 +14097,26 @@
     </row>
     <row r="193" spans="1:15" ht="24.95" customHeight="1">
       <c r="A193" s="2" t="s">
-        <v>3025</v>
+        <v>3023</v>
       </c>
       <c r="O193" s="2" t="s">
-        <v>3047</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="194" spans="1:15" ht="24.95" customHeight="1">
       <c r="A194" s="2" t="s">
-        <v>3026</v>
+        <v>3024</v>
       </c>
       <c r="O194" s="2" t="s">
-        <v>3049</v>
+        <v>3047</v>
       </c>
     </row>
     <row r="195" spans="1:15" ht="24.95" customHeight="1">
       <c r="A195" s="2" t="s">
-        <v>3027</v>
+        <v>3025</v>
       </c>
       <c r="O195" s="2" t="s">
-        <v>3050</v>
+        <v>3048</v>
       </c>
     </row>
     <row r="196" spans="1:15" ht="24.95" customHeight="1">
@@ -14120,24 +14124,24 @@
     </row>
     <row r="197" spans="1:15" ht="24.95" customHeight="1">
       <c r="A197" s="2" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>1799</v>
+      </c>
+      <c r="O197" s="2" t="s">
         <v>1800</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>1801</v>
-      </c>
-      <c r="O197" s="2" t="s">
-        <v>1802</v>
       </c>
     </row>
     <row r="198" spans="1:15" ht="24.95" customHeight="1">
       <c r="A198" s="2" t="s">
-        <v>2540</v>
+        <v>2538</v>
       </c>
       <c r="B198" s="2" t="s">
+        <v>2537</v>
+      </c>
+      <c r="O198" s="2" t="s">
         <v>2539</v>
-      </c>
-      <c r="O198" s="2" t="s">
-        <v>2541</v>
       </c>
     </row>
     <row r="199" spans="1:15" ht="24.95" customHeight="1">
@@ -14148,7 +14152,7 @@
         <v>333</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="O200" s="2" t="s">
         <v>334</v>
@@ -14159,7 +14163,7 @@
         <v>335</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="O201" s="2" t="s">
         <v>336</v>
@@ -14170,7 +14174,7 @@
         <v>337</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="O202" s="2" t="s">
         <v>338</v>
@@ -14181,7 +14185,7 @@
         <v>339</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="O203" s="2" t="s">
         <v>340</v>
@@ -14192,10 +14196,10 @@
         <v>341</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="O204" s="2" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="205" spans="1:15" ht="24.95" customHeight="1">
@@ -14203,7 +14207,7 @@
         <v>1634</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="O205" s="2" t="s">
         <v>1635</v>
@@ -14211,13 +14215,13 @@
     </row>
     <row r="206" spans="1:15" ht="24.95" customHeight="1">
       <c r="A206" s="2" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B206" s="2" t="s">
         <v>2304</v>
       </c>
-      <c r="B206" s="2" t="s">
-        <v>2306</v>
-      </c>
       <c r="O206" s="2" t="s">
-        <v>2305</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="207" spans="1:15" ht="24.95" customHeight="1">
@@ -14225,7 +14229,7 @@
         <v>342</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="O207" s="2" t="s">
         <v>343</v>
@@ -14236,7 +14240,7 @@
         <v>344</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="O208" s="2" t="s">
         <v>345</v>
@@ -14247,7 +14251,7 @@
         <v>346</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="O209" s="2" t="s">
         <v>347</v>
@@ -14258,7 +14262,7 @@
         <v>348</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="O210" s="2" t="s">
         <v>349</v>
@@ -14280,7 +14284,7 @@
         <v>352</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="O212" s="2" t="s">
         <v>353</v>
@@ -14291,7 +14295,7 @@
         <v>354</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="O213" s="2" t="s">
         <v>355</v>
@@ -15107,24 +15111,24 @@
     </row>
     <row r="296" spans="1:15" ht="24.95" customHeight="1">
       <c r="A296" s="2" t="s">
-        <v>2485</v>
+        <v>2483</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>2491</v>
+        <v>2489</v>
       </c>
       <c r="O296" s="2" t="s">
-        <v>2486</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="297" spans="1:15" ht="24.95" customHeight="1">
       <c r="A297" s="2" t="s">
-        <v>2488</v>
+        <v>2486</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>2492</v>
+        <v>2490</v>
       </c>
       <c r="O297" s="2" t="s">
-        <v>2489</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="298" spans="1:15" ht="24.95" customHeight="1">
@@ -15301,35 +15305,35 @@
     </row>
     <row r="318" spans="1:15" ht="24.95" customHeight="1">
       <c r="A318" s="2" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="O318" s="2" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="319" spans="1:15" ht="24.95" customHeight="1">
       <c r="A319" s="2" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="O319" s="2" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="320" spans="1:15" ht="24.95" customHeight="1">
       <c r="A320" s="2" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>1812</v>
+      </c>
+      <c r="O320" s="2" t="s">
         <v>1813</v>
-      </c>
-      <c r="B320" s="2" t="s">
-        <v>1814</v>
-      </c>
-      <c r="O320" s="2" t="s">
-        <v>1815</v>
       </c>
     </row>
     <row r="321" spans="1:15" ht="24.95" customHeight="1">
@@ -15467,7 +15471,7 @@
         <v>627</v>
       </c>
       <c r="O337" s="3" t="s">
-        <v>2773</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="338" spans="1:15" ht="24.95" customHeight="1">
@@ -15538,13 +15542,13 @@
     </row>
     <row r="345" spans="1:15" ht="24.95" customHeight="1">
       <c r="A345" s="2" t="s">
-        <v>2484</v>
+        <v>2482</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>2491</v>
+        <v>2489</v>
       </c>
       <c r="O345" s="2" t="s">
-        <v>2487</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="346" spans="1:15" ht="24.95" customHeight="1">
@@ -15555,7 +15559,7 @@
         <v>647</v>
       </c>
       <c r="O346" s="2" t="s">
-        <v>2914</v>
+        <v>2912</v>
       </c>
     </row>
     <row r="347" spans="1:15" ht="24.95" customHeight="1">
@@ -15648,7 +15652,7 @@
     </row>
     <row r="357" spans="1:15" ht="24.95" customHeight="1">
       <c r="A357" s="2" t="s">
-        <v>2588</v>
+        <v>2586</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>669</v>
@@ -15659,7 +15663,7 @@
     </row>
     <row r="358" spans="1:15" ht="24.95" customHeight="1">
       <c r="A358" s="2" t="s">
-        <v>2587</v>
+        <v>2585</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>671</v>
@@ -15792,7 +15796,7 @@
         <v>701</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="O372" s="2" t="s">
         <v>702</v>
@@ -15803,7 +15807,7 @@
         <v>703</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="O373" s="2" t="s">
         <v>704</v>
@@ -15814,7 +15818,7 @@
         <v>705</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="O374" s="2" t="s">
         <v>706</v>
@@ -15825,7 +15829,7 @@
         <v>707</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="O375" s="2" t="s">
         <v>708</v>
@@ -15836,7 +15840,7 @@
         <v>709</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="O376" s="2" t="s">
         <v>710</v>
@@ -15847,7 +15851,7 @@
         <v>711</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="O377" s="2" t="s">
         <v>712</v>
@@ -15858,7 +15862,7 @@
         <v>713</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="O378" s="2" t="s">
         <v>714</v>
@@ -15869,7 +15873,7 @@
         <v>715</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="O379" s="2" t="s">
         <v>716</v>
@@ -15877,35 +15881,35 @@
     </row>
     <row r="381" spans="1:15" ht="24.95" customHeight="1">
       <c r="A381" s="2" t="s">
-        <v>2295</v>
+        <v>2293</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>2302</v>
+        <v>2300</v>
       </c>
       <c r="O381" s="3" t="s">
-        <v>2300</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="382" spans="1:15" ht="24.95" customHeight="1">
       <c r="A382" s="2" t="s">
-        <v>2296</v>
+        <v>2294</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>2303</v>
+        <v>2301</v>
       </c>
       <c r="O382" s="2" t="s">
-        <v>2299</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="383" spans="1:15" ht="24.95" customHeight="1">
       <c r="A383" s="2" t="s">
-        <v>2297</v>
+        <v>2295</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>2301</v>
+        <v>2299</v>
       </c>
       <c r="O383" s="2" t="s">
-        <v>2298</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="384" spans="1:15" ht="24.95" customHeight="1">
@@ -15913,62 +15917,62 @@
     </row>
     <row r="385" spans="1:15" ht="24.95" customHeight="1">
       <c r="A385" s="2" t="s">
-        <v>2609</v>
+        <v>2607</v>
       </c>
       <c r="B385" s="2" t="s">
+        <v>2600</v>
+      </c>
+      <c r="O385" s="2" t="s">
         <v>2602</v>
-      </c>
-      <c r="O385" s="2" t="s">
-        <v>2604</v>
       </c>
     </row>
     <row r="386" spans="1:15" ht="24.95" customHeight="1">
       <c r="A386" s="2" t="s">
-        <v>2608</v>
+        <v>2606</v>
       </c>
       <c r="B386" s="2" t="s">
+        <v>2599</v>
+      </c>
+      <c r="O386" s="2" t="s">
         <v>2601</v>
-      </c>
-      <c r="O386" s="2" t="s">
-        <v>2603</v>
       </c>
     </row>
     <row r="387" spans="1:15" ht="24.95" customHeight="1">
       <c r="A387" s="2" t="s">
-        <v>2599</v>
+        <v>2597</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>2600</v>
+        <v>2598</v>
       </c>
       <c r="O387" s="2" t="s">
-        <v>2605</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="388" spans="1:15" ht="24.95" customHeight="1">
       <c r="A388" s="2" t="s">
-        <v>2598</v>
+        <v>2596</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>2596</v>
+        <v>2594</v>
       </c>
       <c r="O388" s="2" t="s">
-        <v>2597</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="389" spans="1:15" ht="24.95" customHeight="1">
       <c r="A389" s="2" t="s">
-        <v>2606</v>
+        <v>2604</v>
       </c>
       <c r="O389" s="2" t="s">
-        <v>2610</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="390" spans="1:15" ht="24.95" customHeight="1">
       <c r="A390" s="2" t="s">
-        <v>2607</v>
+        <v>2605</v>
       </c>
       <c r="O390" s="2" t="s">
-        <v>2611</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="391" spans="1:15" ht="24.95" customHeight="1">
@@ -15976,10 +15980,10 @@
     </row>
     <row r="392" spans="1:15" ht="24.95" customHeight="1">
       <c r="A392" s="2" t="s">
-        <v>2288</v>
+        <v>2286</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
       <c r="O392" s="2" t="s">
         <v>768</v>
@@ -15987,21 +15991,21 @@
     </row>
     <row r="393" spans="1:15" ht="24.95" customHeight="1">
       <c r="A393" s="2" t="s">
-        <v>3031</v>
+        <v>3029</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>1641</v>
       </c>
       <c r="O393" s="2" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="394" spans="1:15" ht="24.95" customHeight="1">
       <c r="A394" s="2" t="s">
-        <v>3030</v>
+        <v>3028</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="O394" s="2" t="s">
         <v>777</v>
@@ -16009,7 +16013,7 @@
     </row>
     <row r="395" spans="1:15" ht="24.95" customHeight="1">
       <c r="A395" s="2" t="s">
-        <v>3223</v>
+        <v>3218</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>1639</v>
@@ -16023,37 +16027,37 @@
     </row>
     <row r="397" spans="1:15" ht="24.95" customHeight="1">
       <c r="A397" s="2" t="s">
-        <v>3085</v>
+        <v>3083</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>2884</v>
+        <v>2882</v>
       </c>
       <c r="O397" s="2" t="s">
-        <v>2885</v>
+        <v>2883</v>
       </c>
     </row>
     <row r="398" spans="1:15" ht="24.95" customHeight="1">
       <c r="A398" s="2" t="s">
-        <v>3002</v>
+        <v>3000</v>
       </c>
       <c r="O398" s="2" t="s">
-        <v>3003</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="399" spans="1:15" ht="24.95" customHeight="1">
       <c r="A399" s="2" t="s">
+        <v>3013</v>
+      </c>
+      <c r="O399" s="2" t="s">
         <v>3015</v>
-      </c>
-      <c r="O399" s="2" t="s">
-        <v>3017</v>
       </c>
     </row>
     <row r="400" spans="1:15" ht="24.95" customHeight="1">
       <c r="A400" s="2" t="s">
+        <v>3012</v>
+      </c>
+      <c r="O400" s="3" t="s">
         <v>3014</v>
-      </c>
-      <c r="O400" s="3" t="s">
-        <v>3016</v>
       </c>
     </row>
     <row r="401" spans="1:15" ht="24.95" customHeight="1">
@@ -16078,7 +16082,7 @@
         <v>721</v>
       </c>
       <c r="O403" s="2" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="404" spans="1:15" ht="24.95" customHeight="1">
@@ -16086,84 +16090,84 @@
     </row>
     <row r="405" spans="1:15" ht="24.95" customHeight="1">
       <c r="A405" s="2" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="O405" s="2" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="406" spans="1:15" ht="24.95" customHeight="1">
       <c r="A406" s="2" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="O406" s="2" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="407" spans="1:15" ht="24.95" customHeight="1">
       <c r="A407" s="2" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="O407" s="2" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="408" spans="1:15" ht="24.95" customHeight="1">
       <c r="A408" s="2" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="O408" s="2" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="409" spans="1:15" ht="24.95" customHeight="1">
       <c r="A409" s="2" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="O409" s="2" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="410" spans="1:15" ht="24.95" customHeight="1">
       <c r="A410" s="2" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="O410" s="2" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="411" spans="1:15" ht="24.95" customHeight="1">
       <c r="A411" s="2" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="O411" s="2" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="412" spans="1:15" ht="24.95" customHeight="1">
       <c r="A412" s="2" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="O412" s="2" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="413" spans="1:15" ht="24.95" customHeight="1">
@@ -16199,7 +16203,7 @@
         <v>728</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>2410</v>
+        <v>2408</v>
       </c>
       <c r="O417" s="2" t="s">
         <v>729</v>
@@ -16210,18 +16214,18 @@
         <v>730</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="O418" s="2" t="s">
-        <v>2863</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="419" spans="1:15" ht="24.95" customHeight="1">
       <c r="A419" s="2" t="s">
-        <v>2865</v>
+        <v>2863</v>
       </c>
       <c r="O419" s="2" t="s">
-        <v>2864</v>
+        <v>2862</v>
       </c>
     </row>
     <row r="420" spans="1:15" ht="24.95" customHeight="1">
@@ -16290,7 +16294,7 @@
         <v>1640</v>
       </c>
       <c r="O426" s="2" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="427" spans="1:15" ht="24.95" customHeight="1">
@@ -16317,18 +16321,18 @@
     </row>
     <row r="429" spans="1:15" ht="24.95" customHeight="1">
       <c r="A429" s="2" t="s">
+        <v>2404</v>
+      </c>
+      <c r="B429" s="2" t="s">
+        <v>2405</v>
+      </c>
+      <c r="O429" s="2" t="s">
         <v>2406</v>
-      </c>
-      <c r="B429" s="2" t="s">
-        <v>2407</v>
-      </c>
-      <c r="O429" s="2" t="s">
-        <v>2408</v>
       </c>
     </row>
     <row r="430" spans="1:15" ht="24.95" customHeight="1">
       <c r="A430" s="2" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>749</v>
@@ -16361,7 +16365,7 @@
     </row>
     <row r="433" spans="1:15" ht="24.95" customHeight="1">
       <c r="A433" s="2" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>757</v>
@@ -16389,7 +16393,7 @@
         <v>1610</v>
       </c>
       <c r="O436" s="2" t="s">
-        <v>2311</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="437" spans="1:15" ht="24.95" customHeight="1">
@@ -16483,13 +16487,13 @@
     </row>
     <row r="448" spans="1:15" ht="24.95" customHeight="1">
       <c r="A448" s="2" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B448" s="2" t="s">
+        <v>2283</v>
+      </c>
+      <c r="O448" s="2" t="s">
         <v>2284</v>
-      </c>
-      <c r="B448" s="2" t="s">
-        <v>2285</v>
-      </c>
-      <c r="O448" s="2" t="s">
-        <v>2286</v>
       </c>
     </row>
     <row r="449" spans="1:15" ht="24.95" customHeight="1">
@@ -16544,18 +16548,18 @@
     </row>
     <row r="456" spans="1:15" ht="24.95" customHeight="1">
       <c r="A456" s="2" t="s">
+        <v>2985</v>
+      </c>
+      <c r="O456" s="2" t="s">
         <v>2987</v>
-      </c>
-      <c r="O456" s="2" t="s">
-        <v>2989</v>
       </c>
     </row>
     <row r="457" spans="1:15" ht="24.95" customHeight="1">
       <c r="A457" s="2" t="s">
+        <v>2986</v>
+      </c>
+      <c r="O457" s="2" t="s">
         <v>2988</v>
-      </c>
-      <c r="O457" s="2" t="s">
-        <v>2990</v>
       </c>
     </row>
     <row r="458" spans="1:15" ht="24.95" customHeight="1">
@@ -16657,18 +16661,18 @@
         <v>1609</v>
       </c>
       <c r="O469" s="2" t="s">
-        <v>3052</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="470" spans="1:15" ht="24.95" customHeight="1">
       <c r="A470" s="2" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="O470" s="2" t="s">
-        <v>3053</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="471" spans="1:15" ht="24.95" customHeight="1">
@@ -16676,21 +16680,21 @@
     </row>
     <row r="472" spans="1:15" ht="24.95" customHeight="1">
       <c r="A472" s="2" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="O472" s="2" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="473" spans="1:15" ht="24.95" customHeight="1">
       <c r="A473" s="2" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="O473" s="2" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="474" spans="1:15" ht="24.95" customHeight="1">
@@ -16698,62 +16702,62 @@
         <v>781</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="O474" s="2" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="475" spans="1:15" ht="24.95" customHeight="1">
       <c r="A475" s="2" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="O475" s="2" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="476" spans="1:15" ht="24.95" customHeight="1">
       <c r="A476" s="2" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="O476" s="2" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="477" spans="1:15" ht="24.95" customHeight="1">
       <c r="A477" s="2" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="O477" s="2" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="478" spans="1:15" ht="24.95" customHeight="1">
       <c r="A478" s="2" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="O478" s="2" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="479" spans="1:15" ht="24.95" customHeight="1">
       <c r="A479" s="2" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="O479" s="2" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="480" spans="1:15" ht="24.95" customHeight="1">
@@ -16761,50 +16765,50 @@
     </row>
     <row r="481" spans="1:15" ht="24.95" customHeight="1">
       <c r="A481" s="2" t="s">
-        <v>2907</v>
+        <v>2905</v>
       </c>
       <c r="O481" s="2" t="s">
-        <v>2912</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="482" spans="1:15" ht="24.95" customHeight="1">
       <c r="A482" s="2" t="s">
+        <v>2906</v>
+      </c>
+      <c r="O482" s="2" t="s">
         <v>2908</v>
-      </c>
-      <c r="O482" s="2" t="s">
-        <v>2910</v>
       </c>
     </row>
     <row r="483" spans="1:15" ht="24.95" customHeight="1">
       <c r="A483" s="2" t="s">
+        <v>2907</v>
+      </c>
+      <c r="O483" s="3" t="s">
         <v>2909</v>
-      </c>
-      <c r="O483" s="3" t="s">
-        <v>2911</v>
       </c>
     </row>
     <row r="484" spans="1:15" ht="24.95" customHeight="1">
       <c r="A484" s="2" t="s">
-        <v>2975</v>
+        <v>2973</v>
       </c>
       <c r="O484" s="3" t="s">
-        <v>3001</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="486" spans="1:15" ht="24.95" customHeight="1">
       <c r="A486" s="2" t="s">
-        <v>3207</v>
+        <v>3203</v>
       </c>
       <c r="O486" s="3" t="s">
-        <v>3210</v>
+        <v>3206</v>
       </c>
     </row>
     <row r="487" spans="1:15" ht="24.95" customHeight="1">
       <c r="A487" s="2" t="s">
-        <v>3208</v>
+        <v>3204</v>
       </c>
       <c r="O487" s="3" t="s">
-        <v>3209</v>
+        <v>3205</v>
       </c>
     </row>
     <row r="488" spans="1:15" ht="24.95" customHeight="1">
@@ -16812,26 +16816,26 @@
     </row>
     <row r="489" spans="1:15" ht="24.95" customHeight="1">
       <c r="A489" s="2" t="s">
-        <v>2482</v>
+        <v>2480</v>
       </c>
       <c r="O489" s="3" t="s">
-        <v>2483</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="490" spans="1:15" ht="24.95" customHeight="1">
       <c r="A490" s="2" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
       <c r="O490" s="2" t="s">
-        <v>2470</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="491" spans="1:15" ht="24.95" customHeight="1">
       <c r="A491" s="2" t="s">
-        <v>2473</v>
+        <v>2471</v>
       </c>
       <c r="O491" s="2" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="492" spans="1:15" ht="24.95" customHeight="1">
@@ -16842,7 +16846,7 @@
         <v>1607</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="O493" s="2" t="s">
         <v>1632</v>
@@ -16853,7 +16857,7 @@
         <v>1608</v>
       </c>
       <c r="O494" s="2" t="s">
-        <v>2415</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="495" spans="1:15" ht="24.95" customHeight="1">
@@ -16861,10 +16865,10 @@
         <v>1633</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
       <c r="O495" s="2" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="496" spans="1:15" ht="24.95" customHeight="1">
@@ -16872,10 +16876,10 @@
         <v>937</v>
       </c>
       <c r="B496" s="2" t="s">
+        <v>2415</v>
+      </c>
+      <c r="O496" s="2" t="s">
         <v>2417</v>
-      </c>
-      <c r="O496" s="2" t="s">
-        <v>2419</v>
       </c>
     </row>
     <row r="497" spans="1:15" ht="24.95" customHeight="1">
@@ -16883,7 +16887,7 @@
         <v>938</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>2420</v>
+        <v>2418</v>
       </c>
       <c r="O497" s="2" t="s">
         <v>939</v>
@@ -16894,10 +16898,10 @@
         <v>940</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="O498" s="2" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="499" spans="1:15" ht="24.95" customHeight="1">
@@ -16916,7 +16920,7 @@
         <v>968</v>
       </c>
       <c r="O501" s="2" t="s">
-        <v>2857</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="502" spans="1:15" ht="24.95" customHeight="1">
@@ -16940,7 +16944,7 @@
         <v>973</v>
       </c>
       <c r="O504" s="2" t="s">
-        <v>2514</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="505" spans="1:15" ht="24.95" customHeight="1">
@@ -16956,13 +16960,13 @@
     </row>
     <row r="507" spans="1:15" ht="24.95" customHeight="1">
       <c r="A507" s="2" t="s">
-        <v>3232</v>
+        <v>3227</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>3234</v>
+        <v>3229</v>
       </c>
       <c r="O507" s="2" t="s">
-        <v>3233</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="508" spans="1:15" ht="24.95" customHeight="1">
@@ -17000,45 +17004,45 @@
     </row>
     <row r="512" spans="1:15" ht="24.95" customHeight="1">
       <c r="A512" s="2" t="s">
-        <v>3226</v>
+        <v>3221</v>
       </c>
       <c r="O512" s="3" t="s">
-        <v>3229</v>
+        <v>3224</v>
       </c>
     </row>
     <row r="513" spans="1:15" ht="24.95" customHeight="1">
       <c r="A513" s="2" t="s">
-        <v>3230</v>
+        <v>3225</v>
       </c>
       <c r="O513" s="3" t="s">
-        <v>3231</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="514" spans="1:15" ht="24.95" customHeight="1">
       <c r="A514" s="2" t="s">
-        <v>3224</v>
+        <v>3219</v>
       </c>
       <c r="O514" s="3" t="s">
-        <v>3227</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="515" spans="1:15" ht="24.95" customHeight="1">
       <c r="A515" s="2" t="s">
-        <v>3225</v>
+        <v>3220</v>
       </c>
       <c r="O515" s="3" t="s">
-        <v>3228</v>
+        <v>3223</v>
       </c>
     </row>
     <row r="518" spans="1:15" ht="24.95" customHeight="1">
       <c r="A518" s="2" t="s">
+        <v>2884</v>
+      </c>
+      <c r="B518" s="2" t="s">
+        <v>2885</v>
+      </c>
+      <c r="O518" s="3" t="s">
         <v>2886</v>
-      </c>
-      <c r="B518" s="2" t="s">
-        <v>2887</v>
-      </c>
-      <c r="O518" s="3" t="s">
-        <v>2888</v>
       </c>
     </row>
     <row r="519" spans="1:15" ht="24.95" customHeight="1">
@@ -17126,10 +17130,10 @@
     </row>
     <row r="528" spans="1:15" ht="24.95" customHeight="1">
       <c r="A528" s="2" t="s">
-        <v>2421</v>
+        <v>2419</v>
       </c>
       <c r="O528" s="2" t="s">
-        <v>2422</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="529" spans="1:15" ht="24.95" customHeight="1">
@@ -17142,10 +17146,10 @@
     </row>
     <row r="530" spans="1:15" ht="24.95" customHeight="1">
       <c r="A530" s="2" t="s">
-        <v>2294</v>
+        <v>2292</v>
       </c>
       <c r="O530" s="2" t="s">
-        <v>2468</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="531" spans="1:15" ht="24.95" customHeight="1">
@@ -17156,7 +17160,7 @@
         <v>824</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="O532" s="2" t="s">
         <v>825</v>
@@ -17206,18 +17210,18 @@
         <v>833</v>
       </c>
       <c r="O537" s="2" t="s">
-        <v>2467</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="538" spans="1:15" ht="24.95" customHeight="1">
       <c r="A538" s="2" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B538" s="2" t="s">
         <v>1668</v>
       </c>
-      <c r="B538" s="2" t="s">
-        <v>1670</v>
-      </c>
       <c r="O538" s="2" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="539" spans="1:15" ht="24.95" customHeight="1">
@@ -17330,10 +17334,10 @@
         <v>860</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="O550" s="2" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="551" spans="1:15" ht="24.95" customHeight="1">
@@ -17443,7 +17447,7 @@
     </row>
     <row r="562" spans="1:15" ht="24.95" customHeight="1">
       <c r="A562" s="2" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="B562" s="2" t="s">
         <v>888</v>
@@ -17454,10 +17458,10 @@
     </row>
     <row r="563" spans="1:15" ht="24.95" customHeight="1">
       <c r="A563" s="2" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="O563" s="2" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="564" spans="1:15" ht="24.95" customHeight="1">
@@ -17498,7 +17502,7 @@
         <v>899</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
       <c r="O567" s="2" t="s">
         <v>900</v>
@@ -17564,7 +17568,7 @@
     </row>
     <row r="574" spans="1:15" ht="24.95" customHeight="1">
       <c r="A574" s="2" t="s">
-        <v>2289</v>
+        <v>2287</v>
       </c>
       <c r="B574" s="2" t="s">
         <v>932</v>
@@ -17581,7 +17585,7 @@
         <v>917</v>
       </c>
       <c r="O575" s="2" t="s">
-        <v>2290</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="576" spans="1:15" ht="24.95" customHeight="1">
@@ -17608,7 +17612,7 @@
     </row>
     <row r="578" spans="1:15" ht="24.95" customHeight="1">
       <c r="A578" s="2" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>925</v>
@@ -17622,7 +17626,7 @@
         <v>927</v>
       </c>
       <c r="B579" s="3" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
       <c r="O579" s="2" t="s">
         <v>928</v>
@@ -17655,7 +17659,7 @@
         <v>935</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>2292</v>
+        <v>2290</v>
       </c>
       <c r="O582" s="2" t="s">
         <v>936</v>
@@ -17702,7 +17706,7 @@
     </row>
     <row r="588" spans="1:15" ht="24.95" customHeight="1">
       <c r="A588" s="2" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="B588" s="2" t="s">
         <v>950</v>
@@ -17713,7 +17717,7 @@
     </row>
     <row r="589" spans="1:15" ht="24.95" customHeight="1">
       <c r="A589" s="2" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="B589" s="2" t="s">
         <v>952</v>
@@ -18042,7 +18046,7 @@
         <v>1043</v>
       </c>
       <c r="O622" s="2" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="623" spans="1:15" ht="24.95" customHeight="1">
@@ -18108,7 +18112,7 @@
         <v>1058</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="O629" s="2" t="s">
         <v>1059</v>
@@ -18119,7 +18123,7 @@
         <v>1060</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="O630" s="2" t="s">
         <v>1061</v>
@@ -18130,7 +18134,7 @@
         <v>1062</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="O631" s="2" t="s">
         <v>1063</v>
@@ -18141,7 +18145,7 @@
         <v>1064</v>
       </c>
       <c r="B632" s="2" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="O632" s="2" t="s">
         <v>1065</v>
@@ -18152,21 +18156,21 @@
         <v>1066</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="O633" s="2" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="634" spans="1:15" ht="24.95" customHeight="1">
       <c r="A634" s="2" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="O634" s="2" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="635" spans="1:15" ht="24.95" customHeight="1">
@@ -18174,10 +18178,10 @@
         <v>1067</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="O635" s="2" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="636" spans="1:15" ht="24.95" customHeight="1">
@@ -18185,10 +18189,10 @@
         <v>1068</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="O636" s="2" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="637" spans="1:15" ht="24.95" customHeight="1">
@@ -18196,46 +18200,46 @@
     </row>
     <row r="638" spans="1:15" ht="24.95" customHeight="1">
       <c r="A638" s="2" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="O638" s="2" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="639" spans="1:15" ht="24.95" customHeight="1">
       <c r="A639" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B639" s="2" t="s">
         <v>1835</v>
       </c>
-      <c r="B639" s="2" t="s">
+      <c r="O639" s="2" t="s">
         <v>1837</v>
-      </c>
-      <c r="O639" s="2" t="s">
-        <v>1839</v>
       </c>
     </row>
     <row r="640" spans="1:15" ht="24.95" customHeight="1">
       <c r="A640" s="2" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B640" s="2" t="s">
         <v>1836</v>
       </c>
-      <c r="B640" s="2" t="s">
+      <c r="O640" s="2" t="s">
         <v>1838</v>
-      </c>
-      <c r="O640" s="2" t="s">
-        <v>1840</v>
       </c>
     </row>
     <row r="641" spans="1:15" ht="24.95" customHeight="1">
       <c r="A641" s="2" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B641" s="2" t="s">
+        <v>1841</v>
+      </c>
+      <c r="O641" s="2" t="s">
         <v>1842</v>
-      </c>
-      <c r="B641" s="2" t="s">
-        <v>1843</v>
-      </c>
-      <c r="O641" s="2" t="s">
-        <v>1844</v>
       </c>
     </row>
     <row r="642" spans="1:15" ht="24.95" customHeight="1">
@@ -18249,7 +18253,7 @@
         <v>1070</v>
       </c>
       <c r="O643" s="2" t="s">
-        <v>3032</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="644" spans="1:15" ht="24.95" customHeight="1">
@@ -18486,7 +18490,7 @@
     </row>
     <row r="668" spans="1:15" ht="24.95" customHeight="1">
       <c r="A668" s="2" t="s">
-        <v>2464</v>
+        <v>2462</v>
       </c>
       <c r="B668" s="2" t="s">
         <v>601</v>
@@ -18517,7 +18521,7 @@
         <v>920</v>
       </c>
       <c r="O671" s="2" t="s">
-        <v>3088</v>
+        <v>3086</v>
       </c>
     </row>
     <row r="672" spans="1:15" ht="24.95" customHeight="1">
@@ -18544,18 +18548,18 @@
     </row>
     <row r="675" spans="1:15" ht="24.95" customHeight="1">
       <c r="A675" s="2" t="s">
+        <v>2525</v>
+      </c>
+      <c r="O675" s="2" t="s">
         <v>2527</v>
-      </c>
-      <c r="O675" s="2" t="s">
-        <v>2529</v>
       </c>
     </row>
     <row r="676" spans="1:15" ht="24.95" customHeight="1">
       <c r="A676" s="2" t="s">
+        <v>2526</v>
+      </c>
+      <c r="O676" s="2" t="s">
         <v>2528</v>
-      </c>
-      <c r="O676" s="2" t="s">
-        <v>2530</v>
       </c>
     </row>
     <row r="677" spans="1:15" ht="24.95" customHeight="1">
@@ -18621,7 +18625,7 @@
         <v>1148</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="O683" s="2" t="s">
         <v>1149</v>
@@ -18629,7 +18633,7 @@
     </row>
     <row r="684" spans="1:15" ht="24.95" customHeight="1">
       <c r="A684" s="2" t="s">
-        <v>3029</v>
+        <v>3027</v>
       </c>
       <c r="B684" s="2" t="s">
         <v>1151</v>
@@ -18654,58 +18658,58 @@
     </row>
     <row r="687" spans="1:15" ht="24.95" customHeight="1">
       <c r="A687" s="2" t="s">
-        <v>3054</v>
+        <v>3052</v>
       </c>
       <c r="O687" s="2" t="s">
-        <v>3059</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="688" spans="1:15" ht="24.95" customHeight="1">
       <c r="A688" s="2" t="s">
-        <v>3055</v>
+        <v>3053</v>
       </c>
       <c r="O688" s="2" t="s">
-        <v>3060</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="689" spans="1:15" ht="24.95" customHeight="1">
       <c r="A689" s="2" t="s">
-        <v>3069</v>
+        <v>3067</v>
       </c>
       <c r="O689" s="2" t="s">
-        <v>3070</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="690" spans="1:15" ht="24.95" customHeight="1">
       <c r="A690" s="2" t="s">
-        <v>3056</v>
+        <v>3054</v>
       </c>
       <c r="O690" s="2" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="691" spans="1:15" ht="24.95" customHeight="1">
       <c r="A691" s="2" t="s">
-        <v>3057</v>
+        <v>3055</v>
       </c>
       <c r="O691" s="2" t="s">
-        <v>3062</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="692" spans="1:15" ht="24.95" customHeight="1">
       <c r="A692" s="2" t="s">
-        <v>3058</v>
+        <v>3056</v>
       </c>
       <c r="O692" s="2" t="s">
-        <v>3063</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="693" spans="1:15" ht="24.95" customHeight="1">
       <c r="A693" s="2" t="s">
-        <v>3067</v>
+        <v>3065</v>
       </c>
       <c r="O693" s="2" t="s">
-        <v>3089</v>
+        <v>3087</v>
       </c>
     </row>
     <row r="694" spans="1:15" ht="24.95" customHeight="1">
@@ -18716,7 +18720,7 @@
         <v>1158</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="O695" s="2" t="s">
         <v>1159</v>
@@ -18741,26 +18745,26 @@
     </row>
     <row r="699" spans="1:15" ht="24.95" customHeight="1">
       <c r="A699" s="2" t="s">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="O699" s="2" t="s">
-        <v>3177</v>
+        <v>3175</v>
       </c>
     </row>
     <row r="700" spans="1:15" ht="24.95" customHeight="1">
       <c r="A700" s="2" t="s">
+        <v>2989</v>
+      </c>
+      <c r="O700" s="2" t="s">
         <v>2991</v>
-      </c>
-      <c r="O700" s="2" t="s">
-        <v>2993</v>
       </c>
     </row>
     <row r="701" spans="1:15" ht="24.95" customHeight="1">
       <c r="A701" s="2" t="s">
+        <v>2990</v>
+      </c>
+      <c r="O701" s="2" t="s">
         <v>2992</v>
-      </c>
-      <c r="O701" s="2" t="s">
-        <v>2994</v>
       </c>
     </row>
     <row r="702" spans="1:15" ht="24.95" customHeight="1">
@@ -18937,10 +18941,10 @@
     </row>
     <row r="723" spans="1:15" ht="33">
       <c r="A723" s="2" t="s">
-        <v>2968</v>
+        <v>2966</v>
       </c>
       <c r="O723" s="3" t="s">
-        <v>2969</v>
+        <v>2967</v>
       </c>
     </row>
     <row r="724" spans="1:15" ht="24.95" customHeight="1">
@@ -18951,7 +18955,7 @@
         <v>1204</v>
       </c>
       <c r="O725" s="2" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="726" spans="1:15" ht="24.95" customHeight="1">
@@ -19026,7 +19030,7 @@
         <v>1220</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="O735" s="2" t="s">
         <v>1221</v>
@@ -19037,10 +19041,10 @@
     </row>
     <row r="737" spans="1:15" ht="24.95" customHeight="1">
       <c r="A737" s="2" t="s">
+        <v>3178</v>
+      </c>
+      <c r="O737" s="2" t="s">
         <v>3180</v>
-      </c>
-      <c r="O737" s="2" t="s">
-        <v>3182</v>
       </c>
     </row>
     <row r="738" spans="1:15" ht="24.95" customHeight="1">
@@ -19059,10 +19063,10 @@
     </row>
     <row r="741" spans="1:15" ht="24.95" customHeight="1">
       <c r="A741" s="2" t="s">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="O741" s="2" t="s">
-        <v>3179</v>
+        <v>3177</v>
       </c>
     </row>
     <row r="742" spans="1:15" ht="24.95" customHeight="1">
@@ -19070,7 +19074,7 @@
         <v>1223</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="O742" s="2" t="s">
         <v>1224</v>
@@ -22269,13 +22273,13 @@
     </row>
     <row r="2" spans="1:17" ht="24.95" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>2495</v>
+        <v>2493</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1249</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>3011</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="54">
@@ -22283,10 +22287,10 @@
         <v>1250</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>2756</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="24.95" customHeight="1">
@@ -22341,7 +22345,7 @@
         <v>1264</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>2770</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="54">
@@ -22349,10 +22353,10 @@
         <v>1265</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>3013</v>
+        <v>3011</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>2771</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="36">
@@ -22363,7 +22367,7 @@
         <v>1267</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>2755</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="409.5">
@@ -22371,43 +22375,43 @@
         <v>1268</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2772</v>
+        <v>2770</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>3197</v>
+        <v>3193</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="45" customHeight="1"/>
     <row r="13" spans="1:17" ht="45" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>2490</v>
+        <v>2488</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>3221</v>
+        <v>3216</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="45" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>2555</v>
+        <v>2553</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>2556</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="45" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>2493</v>
+        <v>2491</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>3222</v>
+        <v>3217</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="45" customHeight="1">
       <c r="A16" s="1" t="s">
+        <v>2492</v>
+      </c>
+      <c r="O16" s="1" t="s">
         <v>2494</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>2496</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="24.95" customHeight="1">
@@ -22457,7 +22461,7 @@
     <row r="23" spans="1:15" s="2" customFormat="1" ht="24.95" customHeight="1"/>
     <row r="24" spans="1:15" s="2" customFormat="1" ht="24.95" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>3094</v>
+        <v>3092</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>106</v>
@@ -22471,18 +22475,18 @@
     </row>
     <row r="25" spans="1:15" ht="24.95" customHeight="1">
       <c r="A25" s="1" t="s">
+        <v>3088</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>3091</v>
+      </c>
+      <c r="O25" s="1" t="s">
         <v>3090</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>3093</v>
-      </c>
-      <c r="O25" s="1" t="s">
-        <v>3092</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="24.95" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>3091</v>
+        <v>3089</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>1280</v>
@@ -22559,101 +22563,101 @@
     </row>
     <row r="35" spans="1:15" ht="18">
       <c r="A35" s="1" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>2582</v>
+        <v>2580</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>2581</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="24.95" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>2571</v>
+        <v>2569</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>2583</v>
+        <v>2581</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>2580</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="24.95" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>2572</v>
+        <v>2570</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>2584</v>
+        <v>2582</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>2579</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="24.95" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>2573</v>
+        <v>2571</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>2585</v>
+        <v>2583</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>2578</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="36">
       <c r="A39" s="1" t="s">
-        <v>2574</v>
+        <v>2572</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>2586</v>
+        <v>2584</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>2577</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="24.95" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>2575</v>
+        <v>2573</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>2576</v>
+        <v>2574</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="24.95" customHeight="1">
       <c r="A42" s="1" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>2497</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>2499</v>
-      </c>
       <c r="O42" s="1" t="s">
-        <v>2498</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="24.95" customHeight="1">
       <c r="A43" s="1" t="s">
+        <v>2560</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>2561</v>
+      </c>
+      <c r="O43" s="1" t="s">
         <v>2562</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>2563</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>2564</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="24.95" customHeight="1">
       <c r="A45" s="1" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>1714</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>1716</v>
-      </c>
       <c r="O45" s="1" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="24.95" customHeight="1">
@@ -22694,7 +22698,7 @@
         <v>1308</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>2511</v>
+        <v>2509</v>
       </c>
       <c r="O50" s="1" t="s">
         <v>1309</v>
@@ -22702,24 +22706,24 @@
     </row>
     <row r="51" spans="1:15" ht="24.95" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>2459</v>
+        <v>2457</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>2510</v>
+        <v>2508</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="24.95" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>2513</v>
+        <v>2511</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>2512</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="24.95" customHeight="1">
@@ -22735,534 +22739,534 @@
     </row>
     <row r="54" spans="1:15" ht="24.95" customHeight="1">
       <c r="A54" s="1" t="s">
+        <v>2898</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>2900</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>2902</v>
-      </c>
       <c r="O54" s="1" t="s">
-        <v>2899</v>
+        <v>2897</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="24.95" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>2904</v>
+        <v>2902</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>2984</v>
+        <v>2982</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="24.95" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>2901</v>
+        <v>2899</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>2902</v>
+        <v>2900</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>2906</v>
+        <v>2904</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="24.95" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>2757</v>
+        <v>2755</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>2760</v>
+        <v>2758</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>2761</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="24.95" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>3216</v>
+        <v>3212</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>3218</v>
+        <v>3214</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="24.95" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>3217</v>
+        <v>3213</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>3219</v>
+        <v>3215</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="24.95" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>3193</v>
+        <v>3189</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>3192</v>
+        <v>3188</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="24.95" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>3196</v>
+        <v>3192</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>3211</v>
+        <v>3207</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="24.95" customHeight="1">
       <c r="A64" s="1" t="s">
+        <v>2529</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>2530</v>
+      </c>
+      <c r="O64" s="1" t="s">
         <v>2531</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>2532</v>
-      </c>
-      <c r="O64" s="1" t="s">
-        <v>2533</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="24.95" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>2535</v>
+        <v>2533</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>2534</v>
+        <v>2532</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>3213</v>
+        <v>3209</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="24.95" customHeight="1">
       <c r="A66" s="1" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>2535</v>
+      </c>
+      <c r="O66" s="1" t="s">
         <v>2536</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>2537</v>
-      </c>
-      <c r="O66" s="1" t="s">
-        <v>2538</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="24.95" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>2921</v>
+        <v>2919</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>2951</v>
+        <v>2949</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="24.95" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>2922</v>
+        <v>2920</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>2950</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="24.95" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>3203</v>
+        <v>3199</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>3205</v>
+        <v>3201</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="24.95" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>3204</v>
+        <v>3200</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>3206</v>
+        <v>3202</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="24.95" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>2923</v>
+        <v>2921</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>2949</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="24.95" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>2924</v>
+        <v>2922</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>2948</v>
+        <v>2946</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="24.95" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>2925</v>
+        <v>2923</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>2947</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="24.95" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>2926</v>
+        <v>2924</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>2946</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="24.95" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>2927</v>
+        <v>2925</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>2945</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="24.95" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>3005</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="24.95" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>2928</v>
+        <v>2926</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>2944</v>
+        <v>2942</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="24.95" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>2929</v>
+        <v>2927</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>2943</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="24.95" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>2930</v>
+        <v>2928</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>2942</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="81" spans="1:15" ht="24.95" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>2931</v>
+        <v>2929</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>2958</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="24.95" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>2932</v>
+        <v>2930</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>2957</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="83" spans="1:15" ht="24.95" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>2933</v>
+        <v>2931</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>2941</v>
+        <v>2939</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="24.95" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>2934</v>
+        <v>2932</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>2956</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="85" spans="1:15" ht="24.95" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>2935</v>
+        <v>2933</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>2955</v>
+        <v>2953</v>
       </c>
     </row>
     <row r="86" spans="1:15" ht="24.95" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>2936</v>
+        <v>2934</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>2940</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="87" spans="1:15" ht="24.95" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>2937</v>
+        <v>2935</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>2954</v>
+        <v>2952</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="24.95" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>2938</v>
+        <v>2936</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>2952</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="24.95" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>2939</v>
+        <v>2937</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>2953</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="90" spans="1:15" ht="24.95" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>2959</v>
+        <v>2957</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>2960</v>
+        <v>2958</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="24.95" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>2961</v>
+        <v>2959</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>2962</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="92" spans="1:15" ht="24.95" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>2963</v>
+        <v>2961</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>2964</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="93" spans="1:15" ht="24.95" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>3195</v>
+        <v>3191</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>3194</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="95" spans="1:15" ht="24.95" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>3150</v>
+        <v>3148</v>
       </c>
       <c r="B95" s="1" t="s">
+        <v>3147</v>
+      </c>
+      <c r="O95" s="1" t="s">
         <v>3149</v>
-      </c>
-      <c r="O95" s="1" t="s">
-        <v>3151</v>
       </c>
     </row>
     <row r="96" spans="1:15" ht="24.95" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>3170</v>
+        <v>3168</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>3095</v>
+        <v>3093</v>
       </c>
       <c r="C96" s="1" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>3108</v>
+      </c>
+      <c r="E96" s="1" t="s">
         <v>3109</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="F96" s="1" t="s">
         <v>3110</v>
       </c>
-      <c r="E96" s="1" t="s">
+      <c r="G96" s="1" t="s">
         <v>3111</v>
       </c>
-      <c r="F96" s="1" t="s">
+      <c r="H96" s="1" t="s">
         <v>3112</v>
       </c>
-      <c r="G96" s="1" t="s">
+      <c r="I96" s="1" t="s">
         <v>3113</v>
       </c>
-      <c r="H96" s="1" t="s">
+      <c r="J96" s="1" t="s">
         <v>3114</v>
       </c>
-      <c r="I96" s="1" t="s">
+      <c r="K96" s="1" t="s">
         <v>3115</v>
       </c>
-      <c r="J96" s="1" t="s">
+      <c r="L96" s="1" t="s">
         <v>3116</v>
       </c>
-      <c r="K96" s="1" t="s">
+      <c r="M96" s="1" t="s">
         <v>3117</v>
       </c>
-      <c r="L96" s="1" t="s">
+      <c r="N96" s="1" t="s">
         <v>3118</v>
       </c>
-      <c r="M96" s="1" t="s">
-        <v>3119</v>
-      </c>
-      <c r="N96" s="1" t="s">
-        <v>3120</v>
-      </c>
       <c r="O96" s="1" t="s">
-        <v>3148</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="97" spans="1:15" ht="24.95" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>3121</v>
+        <v>3119</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>3147</v>
+        <v>3145</v>
       </c>
       <c r="C97" s="1" t="s">
+        <v>3095</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>3096</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>3097</v>
       </c>
-      <c r="D97" s="1" t="s">
+      <c r="F97" s="1" t="s">
         <v>3098</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="G97" s="1" t="s">
         <v>3099</v>
       </c>
-      <c r="F97" s="1" t="s">
+      <c r="H97" s="1" t="s">
         <v>3100</v>
       </c>
-      <c r="G97" s="1" t="s">
+      <c r="I97" s="1" t="s">
         <v>3101</v>
       </c>
-      <c r="H97" s="1" t="s">
+      <c r="J97" s="1" t="s">
         <v>3102</v>
       </c>
-      <c r="I97" s="1" t="s">
+      <c r="K97" s="1" t="s">
         <v>3103</v>
       </c>
-      <c r="J97" s="1" t="s">
+      <c r="L97" s="1" t="s">
         <v>3104</v>
       </c>
-      <c r="K97" s="1" t="s">
+      <c r="M97" s="1" t="s">
         <v>3105</v>
       </c>
-      <c r="L97" s="1" t="s">
+      <c r="N97" s="1" t="s">
         <v>3106</v>
       </c>
-      <c r="M97" s="1" t="s">
-        <v>3107</v>
-      </c>
-      <c r="N97" s="1" t="s">
-        <v>3108</v>
-      </c>
       <c r="O97" s="1" t="s">
-        <v>3146</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="98" spans="1:15" ht="24.95" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>3122</v>
+        <v>3120</v>
       </c>
       <c r="B98" s="1" t="s">
+        <v>3170</v>
+      </c>
+      <c r="O98" s="1" t="s">
         <v>3172</v>
-      </c>
-      <c r="O98" s="1" t="s">
-        <v>3174</v>
       </c>
     </row>
     <row r="99" spans="1:15" ht="24.95" customHeight="1">
       <c r="A99" s="1" t="s">
+        <v>3169</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>3171</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="O99" s="1" t="s">
         <v>3173</v>
-      </c>
-      <c r="O99" s="1" t="s">
-        <v>3175</v>
       </c>
     </row>
     <row r="100" spans="1:15" ht="24.95" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="101" spans="1:15" ht="24.95" customHeight="1">
       <c r="A101" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>3141</v>
+      </c>
+      <c r="O101" s="1" t="s">
         <v>3142</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>3143</v>
-      </c>
-      <c r="O101" s="1" t="s">
-        <v>3144</v>
       </c>
     </row>
     <row r="102" spans="1:15" ht="24.95" customHeight="1">
       <c r="A102" s="1" t="s">
-        <v>3153</v>
+        <v>3151</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>3152</v>
+        <v>3150</v>
       </c>
       <c r="O102" s="1" t="s">
-        <v>3156</v>
+        <v>3154</v>
       </c>
     </row>
     <row r="103" spans="1:15" ht="24.95" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>3154</v>
+        <v>3152</v>
       </c>
       <c r="B103" s="1" t="s">
+        <v>3153</v>
+      </c>
+      <c r="O103" s="1" t="s">
         <v>3155</v>
-      </c>
-      <c r="O103" s="1" t="s">
-        <v>3157</v>
       </c>
     </row>
     <row r="104" spans="1:15" ht="24.95" customHeight="1">
       <c r="A104" s="1" t="s">
-        <v>3161</v>
+        <v>3159</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>3162</v>
+        <v>3160</v>
       </c>
       <c r="O104" s="1" t="s">
-        <v>2548</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="105" spans="1:15" ht="24.95" customHeight="1">
       <c r="A105" s="1" t="s">
-        <v>3167</v>
+        <v>3165</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>3163</v>
+        <v>3161</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="106" spans="1:15" ht="24.95" customHeight="1">
       <c r="A106" s="1" t="s">
+        <v>3164</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>3166</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>3168</v>
-      </c>
       <c r="O106" s="1" t="s">
-        <v>3169</v>
+        <v>3167</v>
       </c>
     </row>
     <row r="107" spans="1:15" ht="24.95" customHeight="1">
       <c r="A107" s="1" t="s">
-        <v>3142</v>
+        <v>3140</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>3164</v>
+        <v>3162</v>
       </c>
       <c r="O107" s="1" t="s">
-        <v>3165</v>
+        <v>3163</v>
       </c>
     </row>
   </sheetData>
@@ -23354,7 +23358,7 @@
         <v>1314</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>3006</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="16.5">
@@ -23365,7 +23369,7 @@
         <v>1316</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>3007</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="16.5">
@@ -23376,7 +23380,7 @@
         <v>1318</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>3008</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="16.5">
@@ -23387,7 +23391,7 @@
         <v>1320</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="16.5">
@@ -23398,7 +23402,7 @@
         <v>1322</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>3009</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="16.5">
@@ -23409,7 +23413,7 @@
         <v>1324</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>3010</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="16.5">
@@ -23670,7 +23674,7 @@
         <v>1394</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>1395</v>
@@ -23747,7 +23751,7 @@
         <v>1414</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
       <c r="O38" s="7" t="s">
         <v>1415</v>
@@ -23766,24 +23770,24 @@
     </row>
     <row r="40" spans="1:15" ht="18" customHeight="1">
       <c r="A40" s="7" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
       <c r="O40" s="7" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="18" customHeight="1">
       <c r="A41" s="7" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>1790</v>
+      </c>
+      <c r="O41" s="7" t="s">
         <v>1791</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>1792</v>
-      </c>
-      <c r="O41" s="7" t="s">
-        <v>1793</v>
       </c>
     </row>
   </sheetData>
@@ -23892,7 +23896,7 @@
     </row>
     <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>2504</v>
+        <v>2502</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>1425</v>
@@ -23928,21 +23932,21 @@
         <v>1433</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>2856</v>
+        <v>2854</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>2855</v>
+        <v>2853</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>1443</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1">
@@ -24159,7 +24163,7 @@
     </row>
     <row r="28" spans="1:15" ht="20.100000000000001" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>2769</v>
+        <v>2767</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>1492</v>
@@ -24170,7 +24174,7 @@
     </row>
     <row r="29" spans="1:15" ht="20.100000000000001" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>2999</v>
+        <v>2997</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>1494</v>
@@ -24203,7 +24207,7 @@
     </row>
     <row r="32" spans="1:15" ht="20.100000000000001" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>2503</v>
+        <v>2501</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>1502</v>
@@ -24517,7 +24521,7 @@
         <v>1438</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>2461</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="20.100000000000001" customHeight="1">
@@ -24605,7 +24609,7 @@
         <v>1438</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="69" spans="1:17" ht="20.100000000000001" customHeight="1">
@@ -24792,112 +24796,112 @@
     </row>
     <row r="85" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A85" s="2" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>1700</v>
+      </c>
+      <c r="O85" s="2" t="s">
         <v>1701</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>1702</v>
-      </c>
-      <c r="O85" s="2" t="s">
-        <v>1703</v>
       </c>
     </row>
     <row r="86" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A86" s="2" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>1808</v>
+      </c>
+      <c r="O86" s="2" t="s">
         <v>1809</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>1810</v>
-      </c>
-      <c r="O86" s="2" t="s">
-        <v>1811</v>
       </c>
     </row>
     <row r="87" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A87" s="2" t="s">
+        <v>2279</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>2281</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>2283</v>
-      </c>
       <c r="O87" s="2" t="s">
-        <v>2282</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="88" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>2475</v>
+        <v>2473</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>2481</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="89" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A89" s="2" t="s">
+        <v>2498</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>2499</v>
+      </c>
+      <c r="O89" s="2" t="s">
         <v>2500</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>2501</v>
-      </c>
-      <c r="O89" s="2" t="s">
-        <v>2502</v>
       </c>
     </row>
     <row r="90" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A90" s="2" t="s">
+        <v>2587</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>2588</v>
+      </c>
+      <c r="O90" s="2" t="s">
         <v>2589</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>2590</v>
-      </c>
-      <c r="O90" s="2" t="s">
-        <v>2591</v>
       </c>
     </row>
     <row r="91" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A91" s="2" t="s">
-        <v>3068</v>
+        <v>3066</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>2894</v>
+        <v>2892</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>2895</v>
+        <v>2893</v>
       </c>
     </row>
     <row r="92" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A92" s="2" t="s">
+        <v>3069</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>3070</v>
+      </c>
+      <c r="O92" s="2" t="s">
         <v>3071</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>3072</v>
-      </c>
-      <c r="O92" s="2" t="s">
-        <v>3073</v>
       </c>
     </row>
     <row r="93" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A93" s="2" t="s">
-        <v>3084</v>
+        <v>3082</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>3074</v>
+        <v>3072</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="94" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A94" s="2" t="s">
-        <v>3086</v>
+        <v>3084</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>2894</v>
+        <v>2892</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>3087</v>
+        <v>3085</v>
       </c>
     </row>
   </sheetData>
@@ -24908,7 +24912,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:Q440"/>
+  <dimension ref="A1:Q439"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="27.875" style="7" customWidth="1"/>
@@ -24920,57 +24924,57 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15" customHeight="1">
       <c r="B1" s="7" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>1852</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>1853</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>1854</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>1855</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>1856</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>1857</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>1858</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>1859</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>1860</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>1861</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>1862</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>1863</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>1864</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>1865</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>1866</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>1867</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24.95" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>2618</v>
+        <v>2616</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>1643</v>
@@ -24981,31 +24985,31 @@
     </row>
     <row r="3" spans="1:17" ht="24.95" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>1646</v>
+        <v>3233</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>1642</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>1645</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="24.95" customHeight="1">
-      <c r="A4" s="7" t="s">
-        <v>3190</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>3191</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="24.95" customHeight="1"/>
+        <v>3234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="24.95" customHeight="1"/>
+    <row r="5" spans="1:17">
+      <c r="A5" s="7" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>1866</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>1867</v>
+      </c>
+    </row>
     <row r="6" spans="1:17">
       <c r="A6" s="7" t="s">
         <v>1868</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>1868</v>
-      </c>
       <c r="O6" s="7" t="s">
         <v>1869</v>
       </c>
@@ -25015,24 +25019,24 @@
         <v>1870</v>
       </c>
       <c r="O7" s="7" t="s">
+        <v>2617</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="7" t="s">
         <v>1871</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
-      <c r="A8" s="7" t="s">
+      <c r="B9" s="7" t="s">
+        <v>1871</v>
+      </c>
+      <c r="O9" s="7" t="s">
         <v>1872</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>2619</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="7" t="s">
         <v>1873</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>1873</v>
-      </c>
       <c r="O10" s="7" t="s">
         <v>1874</v>
       </c>
@@ -25045,48 +25049,48 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
-      <c r="A12" s="7" t="s">
-        <v>1877</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>1878</v>
+    <row r="13" spans="1:17">
+      <c r="A13" s="7" t="s">
+        <v>2969</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>2969</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>2970</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="7" t="s">
         <v>2971</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>2971</v>
-      </c>
       <c r="O14" s="7" t="s">
-        <v>2972</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="7" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>3075</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17">
-      <c r="A16" s="7" t="s">
-        <v>2974</v>
-      </c>
-      <c r="O16" s="7" t="s">
-        <v>3076</v>
+        <v>3074</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="7" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>1877</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>1878</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="7" t="s">
         <v>1879</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>1879</v>
-      </c>
       <c r="O18" s="7" t="s">
         <v>1880</v>
       </c>
@@ -25096,105 +25100,105 @@
         <v>1881</v>
       </c>
       <c r="O19" s="7" t="s">
+        <v>2618</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="7" t="s">
         <v>1882</v>
       </c>
-    </row>
-    <row r="20" spans="1:15">
-      <c r="A20" s="7" t="s">
+      <c r="B21" s="7" t="s">
+        <v>1882</v>
+      </c>
+      <c r="O21" s="7" t="s">
         <v>1883</v>
-      </c>
-      <c r="O20" s="7" t="s">
-        <v>2620</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="7" t="s">
         <v>1884</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>1884</v>
-      </c>
       <c r="O22" s="7" t="s">
-        <v>1885</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="7" t="s">
+        <v>1885</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="7" t="s">
         <v>1886</v>
       </c>
-      <c r="O23" s="7" t="s">
-        <v>2749</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="A24" s="7" t="s">
+      <c r="B25" s="7" t="s">
+        <v>1886</v>
+      </c>
+      <c r="O25" s="7" t="s">
         <v>1887</v>
-      </c>
-      <c r="O24" s="7" t="s">
-        <v>1708</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="7" t="s">
         <v>1888</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>1888</v>
-      </c>
       <c r="O26" s="7" t="s">
-        <v>1889</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="7" t="s">
+        <v>1889</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>2620</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="7" t="s">
         <v>1890</v>
       </c>
-      <c r="O27" s="7" t="s">
+      <c r="B29" s="7" t="s">
+        <v>1890</v>
+      </c>
+      <c r="O29" s="7" t="s">
         <v>2621</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
-      <c r="A28" s="7" t="s">
-        <v>1891</v>
-      </c>
-      <c r="O28" s="7" t="s">
-        <v>2622</v>
       </c>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="7" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="O30" s="7" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="7" t="s">
+        <v>1892</v>
+      </c>
+      <c r="O31" s="7" t="s">
+        <v>2623</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" s="7" t="s">
         <v>1893</v>
       </c>
-      <c r="O31" s="7" t="s">
-        <v>2624</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
-      <c r="A32" s="7" t="s">
+      <c r="B33" s="7" t="s">
+        <v>1893</v>
+      </c>
+      <c r="O33" s="7" t="s">
         <v>1894</v>
-      </c>
-      <c r="O32" s="7" t="s">
-        <v>2625</v>
       </c>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="7" t="s">
         <v>1895</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>1895</v>
-      </c>
       <c r="O34" s="7" t="s">
         <v>1896</v>
       </c>
@@ -25204,51 +25208,51 @@
         <v>1897</v>
       </c>
       <c r="O35" s="7" t="s">
-        <v>1898</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15">
-      <c r="A36" s="7" t="s">
-        <v>1899</v>
-      </c>
-      <c r="O36" s="7" t="s">
-        <v>2626</v>
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" s="7" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>1801</v>
+      </c>
+      <c r="O37" s="7" t="s">
+        <v>1804</v>
       </c>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="7" t="s">
-        <v>1803</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="O38" s="7" t="s">
-        <v>1806</v>
+        <v>2615</v>
       </c>
     </row>
     <row r="39" spans="1:15">
       <c r="A39" s="7" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="O39" s="7" t="s">
-        <v>2617</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15">
-      <c r="A40" s="7" t="s">
         <v>1805</v>
       </c>
-      <c r="O40" s="7" t="s">
-        <v>1807</v>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" s="7" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>1898</v>
+      </c>
+      <c r="O41" s="7" t="s">
+        <v>1899</v>
       </c>
     </row>
     <row r="42" spans="1:15">
       <c r="A42" s="7" t="s">
         <v>1900</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>1900</v>
-      </c>
       <c r="O42" s="7" t="s">
         <v>1901</v>
       </c>
@@ -25261,11 +25265,14 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="44" spans="1:15">
-      <c r="A44" s="7" t="s">
+    <row r="45" spans="1:15">
+      <c r="A45" s="7" t="s">
         <v>1904</v>
       </c>
-      <c r="O44" s="7" t="s">
+      <c r="B45" s="7" t="s">
+        <v>1904</v>
+      </c>
+      <c r="O45" s="7" t="s">
         <v>1905</v>
       </c>
     </row>
@@ -25273,80 +25280,80 @@
       <c r="A46" s="7" t="s">
         <v>1906</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>1906</v>
-      </c>
       <c r="O46" s="7" t="s">
-        <v>1907</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="47" spans="1:15">
       <c r="A47" s="7" t="s">
+        <v>1907</v>
+      </c>
+      <c r="O47" s="7" t="s">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" s="7" t="s">
         <v>1908</v>
       </c>
-      <c r="O47" s="7" t="s">
-        <v>2627</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15">
-      <c r="A48" s="7" t="s">
+      <c r="B49" s="7" t="s">
+        <v>1908</v>
+      </c>
+      <c r="O49" s="7" t="s">
         <v>1909</v>
-      </c>
-      <c r="O48" s="7" t="s">
-        <v>2628</v>
       </c>
     </row>
     <row r="50" spans="1:15">
       <c r="A50" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>1910</v>
-      </c>
       <c r="O50" s="7" t="s">
-        <v>1911</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="51" spans="1:15">
       <c r="A51" s="7" t="s">
+        <v>1911</v>
+      </c>
+      <c r="O51" s="7" t="s">
+        <v>2746</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" s="7" t="s">
         <v>1912</v>
       </c>
-      <c r="O51" s="7" t="s">
-        <v>2629</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15">
-      <c r="A52" s="7" t="s">
+      <c r="B53" s="7" t="s">
+        <v>1912</v>
+      </c>
+      <c r="O53" s="7" t="s">
         <v>1913</v>
-      </c>
-      <c r="O52" s="7" t="s">
-        <v>2748</v>
       </c>
     </row>
     <row r="54" spans="1:15">
       <c r="A54" s="7" t="s">
         <v>1914</v>
       </c>
-      <c r="B54" s="7" t="s">
-        <v>1914</v>
-      </c>
       <c r="O54" s="7" t="s">
-        <v>1915</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="55" spans="1:15">
       <c r="A55" s="7" t="s">
+        <v>1915</v>
+      </c>
+      <c r="O55" s="7" t="s">
         <v>1916</v>
       </c>
-      <c r="O55" s="7" t="s">
-        <v>2630</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15">
-      <c r="A56" s="7" t="s">
+    </row>
+    <row r="57" spans="1:15">
+      <c r="A57" s="7" t="s">
         <v>1917</v>
       </c>
-      <c r="O56" s="7" t="s">
+      <c r="B57" s="7" t="s">
+        <v>1917</v>
+      </c>
+      <c r="O57" s="7" t="s">
         <v>1918</v>
       </c>
     </row>
@@ -25354,134 +25361,134 @@
       <c r="A58" s="7" t="s">
         <v>1919</v>
       </c>
-      <c r="B58" s="7" t="s">
-        <v>1919</v>
-      </c>
       <c r="O58" s="7" t="s">
-        <v>1920</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="59" spans="1:15">
       <c r="A59" s="7" t="s">
+        <v>1920</v>
+      </c>
+      <c r="O59" s="7" t="s">
+        <v>2630</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" s="7" t="s">
         <v>1921</v>
       </c>
-      <c r="O59" s="7" t="s">
-        <v>2631</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15">
-      <c r="A60" s="7" t="s">
+      <c r="B61" s="7" t="s">
+        <v>1921</v>
+      </c>
+      <c r="O61" s="7" t="s">
         <v>1922</v>
-      </c>
-      <c r="O60" s="7" t="s">
-        <v>2632</v>
       </c>
     </row>
     <row r="62" spans="1:15">
       <c r="A62" s="7" t="s">
         <v>1923</v>
       </c>
-      <c r="B62" s="7" t="s">
-        <v>1923</v>
-      </c>
       <c r="O62" s="7" t="s">
-        <v>1924</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="63" spans="1:15">
       <c r="A63" s="7" t="s">
+        <v>1924</v>
+      </c>
+      <c r="O63" s="7" t="s">
+        <v>2631</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65" s="7" t="s">
         <v>1925</v>
       </c>
-      <c r="O63" s="7" t="s">
-        <v>2747</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15">
-      <c r="A64" s="7" t="s">
+      <c r="B65" s="7" t="s">
+        <v>1925</v>
+      </c>
+      <c r="O65" s="7" t="s">
         <v>1926</v>
-      </c>
-      <c r="O64" s="7" t="s">
-        <v>2633</v>
       </c>
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="7" t="s">
         <v>1927</v>
       </c>
-      <c r="B66" s="7" t="s">
-        <v>1927</v>
-      </c>
       <c r="O66" s="7" t="s">
-        <v>1928</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="67" spans="1:15">
       <c r="A67" s="7" t="s">
+        <v>1928</v>
+      </c>
+      <c r="O67" s="7" t="s">
+        <v>2632</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69" s="7" t="s">
         <v>1929</v>
       </c>
-      <c r="O67" s="7" t="s">
-        <v>2616</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15">
-      <c r="A68" s="7" t="s">
+      <c r="B69" s="7" t="s">
+        <v>1929</v>
+      </c>
+      <c r="O69" s="7" t="s">
         <v>1930</v>
-      </c>
-      <c r="O68" s="7" t="s">
-        <v>2634</v>
       </c>
     </row>
     <row r="70" spans="1:15">
       <c r="A70" s="7" t="s">
         <v>1931</v>
       </c>
-      <c r="B70" s="7" t="s">
-        <v>1931</v>
-      </c>
       <c r="O70" s="7" t="s">
-        <v>1932</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="71" spans="1:15">
       <c r="A71" s="7" t="s">
+        <v>1932</v>
+      </c>
+      <c r="O71" s="7" t="s">
+        <v>2634</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
+      <c r="A73" s="7" t="s">
         <v>1933</v>
       </c>
-      <c r="O71" s="7" t="s">
+      <c r="B73" s="7" t="s">
         <v>2635</v>
       </c>
-    </row>
-    <row r="72" spans="1:15">
-      <c r="A72" s="7" t="s">
-        <v>1934</v>
-      </c>
-      <c r="O72" s="7" t="s">
+      <c r="O73" s="7" t="s">
         <v>2636</v>
       </c>
     </row>
     <row r="74" spans="1:15">
       <c r="A74" s="7" t="s">
-        <v>1935</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>2637</v>
+        <v>1934</v>
       </c>
       <c r="O74" s="7" t="s">
-        <v>2638</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="75" spans="1:15">
       <c r="A75" s="7" t="s">
+        <v>1935</v>
+      </c>
+      <c r="O75" s="7" t="s">
         <v>1936</v>
       </c>
-      <c r="O75" s="7" t="s">
-        <v>1938</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15">
-      <c r="A76" s="7" t="s">
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77" s="7" t="s">
         <v>1937</v>
       </c>
-      <c r="O76" s="7" t="s">
+      <c r="B77" s="7" t="s">
+        <v>1937</v>
+      </c>
+      <c r="O77" s="7" t="s">
         <v>1938</v>
       </c>
     </row>
@@ -25489,53 +25496,53 @@
       <c r="A78" s="7" t="s">
         <v>1939</v>
       </c>
-      <c r="B78" s="7" t="s">
-        <v>1939</v>
-      </c>
       <c r="O78" s="7" t="s">
-        <v>1940</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="79" spans="1:15">
       <c r="A79" s="7" t="s">
+        <v>1940</v>
+      </c>
+      <c r="O79" s="7" t="s">
+        <v>2638</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
+      <c r="A81" s="7" t="s">
         <v>1941</v>
       </c>
-      <c r="O79" s="7" t="s">
-        <v>2639</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15">
-      <c r="A80" s="7" t="s">
+      <c r="B81" s="7" t="s">
+        <v>1941</v>
+      </c>
+      <c r="O81" s="7" t="s">
         <v>1942</v>
-      </c>
-      <c r="O80" s="7" t="s">
-        <v>2640</v>
       </c>
     </row>
     <row r="82" spans="1:15">
       <c r="A82" s="7" t="s">
         <v>1943</v>
       </c>
-      <c r="B82" s="7" t="s">
-        <v>1943</v>
-      </c>
       <c r="O82" s="7" t="s">
-        <v>1944</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="83" spans="1:15">
       <c r="A83" s="7" t="s">
+        <v>1944</v>
+      </c>
+      <c r="O83" s="7" t="s">
         <v>1945</v>
       </c>
-      <c r="O83" s="7" t="s">
-        <v>2641</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15">
-      <c r="A84" s="7" t="s">
+    </row>
+    <row r="85" spans="1:15">
+      <c r="A85" s="7" t="s">
         <v>1946</v>
       </c>
-      <c r="O84" s="7" t="s">
+      <c r="B85" s="7" t="s">
+        <v>1946</v>
+      </c>
+      <c r="O85" s="7" t="s">
         <v>1947</v>
       </c>
     </row>
@@ -25543,92 +25550,89 @@
       <c r="A86" s="7" t="s">
         <v>1948</v>
       </c>
-      <c r="B86" s="7" t="s">
-        <v>1948</v>
-      </c>
       <c r="O86" s="7" t="s">
-        <v>1949</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="87" spans="1:15">
       <c r="A87" s="7" t="s">
+        <v>1949</v>
+      </c>
+      <c r="O87" s="7" t="s">
+        <v>2641</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15">
+      <c r="A89" s="7" t="s">
         <v>1950</v>
       </c>
-      <c r="O87" s="7" t="s">
-        <v>2642</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15">
-      <c r="A88" s="7" t="s">
+      <c r="B89" s="7" t="s">
+        <v>1950</v>
+      </c>
+      <c r="O89" s="7" t="s">
         <v>1951</v>
-      </c>
-      <c r="O88" s="7" t="s">
-        <v>2643</v>
       </c>
     </row>
     <row r="90" spans="1:15">
       <c r="A90" s="7" t="s">
         <v>1952</v>
       </c>
-      <c r="B90" s="7" t="s">
-        <v>1952</v>
-      </c>
       <c r="O90" s="7" t="s">
-        <v>1953</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="91" spans="1:15">
       <c r="A91" s="7" t="s">
+        <v>1953</v>
+      </c>
+      <c r="O91" s="7" t="s">
+        <v>2643</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15">
+      <c r="A93" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="O91" s="7" t="s">
-        <v>2644</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15">
-      <c r="A92" s="7" t="s">
+      <c r="B93" s="7" t="s">
         <v>1955</v>
       </c>
-      <c r="O92" s="7" t="s">
-        <v>2645</v>
+      <c r="O93" s="7" t="s">
+        <v>1956</v>
       </c>
     </row>
     <row r="94" spans="1:15">
       <c r="A94" s="7" t="s">
-        <v>1956</v>
-      </c>
-      <c r="B94" s="7" t="s">
         <v>1957</v>
       </c>
       <c r="O94" s="7" t="s">
-        <v>1958</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="95" spans="1:15">
       <c r="A95" s="7" t="s">
+        <v>1958</v>
+      </c>
+      <c r="O95" s="7" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15">
+      <c r="A97" s="7" t="s">
         <v>1959</v>
       </c>
-      <c r="O95" s="7" t="s">
+      <c r="B97" s="7" t="s">
         <v>2646</v>
       </c>
-    </row>
-    <row r="96" spans="1:15">
-      <c r="A96" s="7" t="s">
-        <v>1960</v>
-      </c>
-      <c r="O96" s="7" t="s">
+      <c r="O97" s="7" t="s">
         <v>2647</v>
       </c>
     </row>
     <row r="98" spans="1:15">
       <c r="A98" s="7" t="s">
-        <v>1961</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>2648</v>
+        <v>1693</v>
       </c>
       <c r="O98" s="7" t="s">
-        <v>2649</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="99" spans="1:15">
@@ -25636,80 +25640,80 @@
         <v>1695</v>
       </c>
       <c r="O99" s="7" t="s">
-        <v>2615</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15">
-      <c r="A100" s="7" t="s">
-        <v>1697</v>
-      </c>
-      <c r="O100" s="7" t="s">
-        <v>2650</v>
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15">
+      <c r="A101" s="7" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>1844</v>
+      </c>
+      <c r="O101" s="7" t="s">
+        <v>1849</v>
       </c>
     </row>
     <row r="102" spans="1:15">
       <c r="A102" s="7" t="s">
-        <v>1846</v>
-      </c>
-      <c r="B102" s="7" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="O102" s="7" t="s">
-        <v>1851</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="103" spans="1:15">
       <c r="A103" s="7" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="O103" s="7" t="s">
-        <v>2651</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15">
-      <c r="A104" s="7" t="s">
-        <v>1850</v>
-      </c>
-      <c r="O104" s="7" t="s">
-        <v>2652</v>
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15">
+      <c r="A105" s="7" t="s">
+        <v>2590</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>2590</v>
+      </c>
+      <c r="O105" s="7" t="s">
+        <v>2591</v>
       </c>
     </row>
     <row r="106" spans="1:15">
       <c r="A106" s="7" t="s">
         <v>2592</v>
       </c>
-      <c r="B106" s="7" t="s">
-        <v>2592</v>
-      </c>
       <c r="O106" s="7" t="s">
-        <v>2593</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="107" spans="1:15">
       <c r="A107" s="7" t="s">
-        <v>2594</v>
+        <v>2593</v>
       </c>
       <c r="O107" s="7" t="s">
-        <v>2613</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15">
-      <c r="A108" s="7" t="s">
-        <v>2595</v>
-      </c>
-      <c r="O108" s="7" t="s">
-        <v>2612</v>
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15">
+      <c r="A109" s="7" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>1692</v>
+      </c>
+      <c r="O109" s="7" t="s">
+        <v>1697</v>
       </c>
     </row>
     <row r="110" spans="1:15">
       <c r="A110" s="7" t="s">
         <v>1694</v>
       </c>
-      <c r="B110" s="7" t="s">
-        <v>1694</v>
-      </c>
       <c r="O110" s="7" t="s">
-        <v>1699</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="111" spans="1:15">
@@ -25717,24 +25721,24 @@
         <v>1696</v>
       </c>
       <c r="O111" s="7" t="s">
-        <v>2653</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15">
-      <c r="A112" s="7" t="s">
         <v>1698</v>
       </c>
-      <c r="O112" s="7" t="s">
-        <v>1700</v>
+    </row>
+    <row r="113" spans="1:15">
+      <c r="A113" s="7" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>1960</v>
+      </c>
+      <c r="O113" s="7" t="s">
+        <v>1961</v>
       </c>
     </row>
     <row r="114" spans="1:15">
       <c r="A114" s="7" t="s">
         <v>1962</v>
       </c>
-      <c r="B114" s="7" t="s">
-        <v>1962</v>
-      </c>
       <c r="O114" s="7" t="s">
         <v>1963</v>
       </c>
@@ -25747,11 +25751,14 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="116" spans="1:15">
-      <c r="A116" s="7" t="s">
+    <row r="117" spans="1:15">
+      <c r="A117" s="7" t="s">
         <v>1966</v>
       </c>
-      <c r="O116" s="7" t="s">
+      <c r="B117" s="7" t="s">
+        <v>1966</v>
+      </c>
+      <c r="O117" s="7" t="s">
         <v>1967</v>
       </c>
     </row>
@@ -25759,26 +25766,26 @@
       <c r="A118" s="7" t="s">
         <v>1968</v>
       </c>
-      <c r="B118" s="7" t="s">
-        <v>1968</v>
-      </c>
       <c r="O118" s="7" t="s">
-        <v>1969</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="119" spans="1:15">
       <c r="A119" s="7" t="s">
+        <v>1969</v>
+      </c>
+      <c r="O119" s="7" t="s">
         <v>1970</v>
       </c>
-      <c r="O119" s="7" t="s">
-        <v>2654</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15">
-      <c r="A120" s="7" t="s">
+    </row>
+    <row r="121" spans="1:15">
+      <c r="A121" s="7" t="s">
         <v>1971</v>
       </c>
-      <c r="O120" s="7" t="s">
+      <c r="B121" s="7" t="s">
+        <v>1971</v>
+      </c>
+      <c r="O121" s="7" t="s">
         <v>1972</v>
       </c>
     </row>
@@ -25786,92 +25793,89 @@
       <c r="A122" s="7" t="s">
         <v>1973</v>
       </c>
-      <c r="B122" s="7" t="s">
-        <v>1973</v>
-      </c>
       <c r="O122" s="7" t="s">
-        <v>1974</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="123" spans="1:15">
       <c r="A123" s="7" t="s">
+        <v>1974</v>
+      </c>
+      <c r="O123" s="7" t="s">
+        <v>2654</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15">
+      <c r="A125" s="7" t="s">
         <v>1975</v>
       </c>
-      <c r="O123" s="7" t="s">
-        <v>2655</v>
-      </c>
-    </row>
-    <row r="124" spans="1:15">
-      <c r="A124" s="7" t="s">
+      <c r="B125" s="7" t="s">
+        <v>1975</v>
+      </c>
+      <c r="O125" s="7" t="s">
         <v>1976</v>
-      </c>
-      <c r="O124" s="7" t="s">
-        <v>2656</v>
       </c>
     </row>
     <row r="126" spans="1:15">
       <c r="A126" s="7" t="s">
         <v>1977</v>
       </c>
-      <c r="B126" s="7" t="s">
-        <v>1977</v>
-      </c>
       <c r="O126" s="7" t="s">
-        <v>1978</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="127" spans="1:15">
       <c r="A127" s="7" t="s">
+        <v>1978</v>
+      </c>
+      <c r="O127" s="7" t="s">
+        <v>2656</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15">
+      <c r="A129" s="7" t="s">
         <v>1979</v>
       </c>
-      <c r="O127" s="7" t="s">
-        <v>2657</v>
-      </c>
-    </row>
-    <row r="128" spans="1:15">
-      <c r="A128" s="7" t="s">
+      <c r="B129" s="7" t="s">
+        <v>1979</v>
+      </c>
+      <c r="O129" s="7" t="s">
         <v>1980</v>
-      </c>
-      <c r="O128" s="7" t="s">
-        <v>2658</v>
       </c>
     </row>
     <row r="130" spans="1:15">
       <c r="A130" s="7" t="s">
         <v>1981</v>
       </c>
-      <c r="B130" s="7" t="s">
-        <v>1981</v>
-      </c>
       <c r="O130" s="7" t="s">
-        <v>1982</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="131" spans="1:15">
       <c r="A131" s="7" t="s">
+        <v>1982</v>
+      </c>
+      <c r="O131" s="7" t="s">
+        <v>2658</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15">
+      <c r="A133" s="7" t="s">
         <v>1983</v>
       </c>
-      <c r="O131" s="7" t="s">
+      <c r="B133" s="7" t="s">
+        <v>1983</v>
+      </c>
+      <c r="O133" s="7" t="s">
         <v>2659</v>
-      </c>
-    </row>
-    <row r="132" spans="1:15">
-      <c r="A132" s="7" t="s">
-        <v>1984</v>
-      </c>
-      <c r="O132" s="7" t="s">
-        <v>2660</v>
       </c>
     </row>
     <row r="134" spans="1:15">
       <c r="A134" s="7" t="s">
+        <v>1984</v>
+      </c>
+      <c r="O134" s="7" t="s">
         <v>1985</v>
-      </c>
-      <c r="B134" s="7" t="s">
-        <v>1985</v>
-      </c>
-      <c r="O134" s="7" t="s">
-        <v>2661</v>
       </c>
     </row>
     <row r="135" spans="1:15">
@@ -25879,122 +25883,125 @@
         <v>1986</v>
       </c>
       <c r="O135" s="7" t="s">
-        <v>1987</v>
-      </c>
-    </row>
-    <row r="136" spans="1:15">
-      <c r="A136" s="7" t="s">
-        <v>1988</v>
-      </c>
-      <c r="O136" s="7" t="s">
-        <v>1987</v>
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15">
+      <c r="A137" s="7" t="s">
+        <v>2889</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>2888</v>
+      </c>
+      <c r="O137" s="7" t="s">
+        <v>2887</v>
       </c>
     </row>
     <row r="138" spans="1:15">
       <c r="A138" s="7" t="s">
-        <v>2891</v>
-      </c>
-      <c r="B138" s="7" t="s">
         <v>2890</v>
       </c>
       <c r="O138" s="7" t="s">
-        <v>2889</v>
+        <v>2894</v>
       </c>
     </row>
     <row r="139" spans="1:15">
       <c r="A139" s="7" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="O139" s="7" t="s">
-        <v>2896</v>
-      </c>
-    </row>
-    <row r="140" spans="1:15">
-      <c r="A140" s="7" t="s">
-        <v>2893</v>
-      </c>
-      <c r="O140" s="7" t="s">
-        <v>2897</v>
+        <v>2895</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15">
+      <c r="A141" s="7" t="s">
+        <v>3195</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>3194</v>
+      </c>
+      <c r="O141" s="7" t="s">
+        <v>3196</v>
       </c>
     </row>
     <row r="142" spans="1:15">
       <c r="A142" s="7" t="s">
-        <v>3199</v>
-      </c>
-      <c r="B142" s="7" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="O142" s="7" t="s">
-        <v>3200</v>
+        <v>3207</v>
       </c>
     </row>
     <row r="143" spans="1:15">
       <c r="A143" s="7" t="s">
-        <v>3201</v>
+        <v>3198</v>
       </c>
       <c r="O143" s="7" t="s">
-        <v>3211</v>
-      </c>
-    </row>
-    <row r="144" spans="1:15">
-      <c r="A144" s="7" t="s">
-        <v>3202</v>
-      </c>
-      <c r="O144" s="7" t="s">
-        <v>3214</v>
+        <v>3210</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15">
+      <c r="A145" s="7" t="s">
+        <v>2473</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>2472</v>
+      </c>
+      <c r="O145" s="7" t="s">
+        <v>2476</v>
       </c>
     </row>
     <row r="146" spans="1:15">
       <c r="A146" s="7" t="s">
-        <v>2475</v>
-      </c>
-      <c r="B146" s="7" t="s">
         <v>2474</v>
       </c>
       <c r="O146" s="7" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="147" spans="1:15">
       <c r="A147" s="7" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="O147" s="7" t="s">
-        <v>2479</v>
-      </c>
-    </row>
-    <row r="148" spans="1:15">
-      <c r="A148" s="7" t="s">
-        <v>2477</v>
-      </c>
-      <c r="O148" s="7" t="s">
-        <v>2662</v>
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15">
+      <c r="A149" s="7" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>1987</v>
+      </c>
+      <c r="O149" s="7" t="s">
+        <v>1988</v>
       </c>
     </row>
     <row r="150" spans="1:15">
       <c r="A150" s="7" t="s">
         <v>1989</v>
       </c>
-      <c r="B150" s="7" t="s">
-        <v>1989</v>
-      </c>
       <c r="O150" s="7" t="s">
-        <v>1990</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="151" spans="1:15">
       <c r="A151" s="7" t="s">
+        <v>1990</v>
+      </c>
+      <c r="O151" s="7" t="s">
         <v>1991</v>
       </c>
-      <c r="O151" s="7" t="s">
-        <v>2663</v>
-      </c>
-    </row>
-    <row r="152" spans="1:15">
-      <c r="A152" s="7" t="s">
+    </row>
+    <row r="153" spans="1:15">
+      <c r="A153" s="7" t="s">
         <v>1992</v>
       </c>
-      <c r="O152" s="7" t="s">
+      <c r="B153" s="7" t="s">
+        <v>1992</v>
+      </c>
+      <c r="O153" s="7" t="s">
         <v>1993</v>
       </c>
     </row>
@@ -26002,9 +26009,6 @@
       <c r="A154" s="7" t="s">
         <v>1994</v>
       </c>
-      <c r="B154" s="7" t="s">
-        <v>1994</v>
-      </c>
       <c r="O154" s="7" t="s">
         <v>1995</v>
       </c>
@@ -26014,24 +26018,24 @@
         <v>1996</v>
       </c>
       <c r="O155" s="7" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15">
+      <c r="A157" s="7" t="s">
         <v>1997</v>
       </c>
-    </row>
-    <row r="156" spans="1:15">
-      <c r="A156" s="7" t="s">
+      <c r="B157" s="7" t="s">
+        <v>1702</v>
+      </c>
+      <c r="O157" s="7" t="s">
         <v>1998</v>
-      </c>
-      <c r="O156" s="7" t="s">
-        <v>1997</v>
       </c>
     </row>
     <row r="158" spans="1:15">
       <c r="A158" s="7" t="s">
         <v>1999</v>
       </c>
-      <c r="B158" s="7" t="s">
-        <v>1704</v>
-      </c>
       <c r="O158" s="7" t="s">
         <v>2000</v>
       </c>
@@ -26044,11 +26048,14 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="160" spans="1:15">
-      <c r="A160" s="7" t="s">
+    <row r="161" spans="1:15">
+      <c r="A161" s="7" t="s">
         <v>2003</v>
       </c>
-      <c r="O160" s="7" t="s">
+      <c r="B161" s="7" t="s">
+        <v>1703</v>
+      </c>
+      <c r="O161" s="7" t="s">
         <v>2004</v>
       </c>
     </row>
@@ -26056,9 +26063,6 @@
       <c r="A162" s="7" t="s">
         <v>2005</v>
       </c>
-      <c r="B162" s="7" t="s">
-        <v>1705</v>
-      </c>
       <c r="O162" s="7" t="s">
         <v>2006</v>
       </c>
@@ -26068,78 +26072,78 @@
         <v>2007</v>
       </c>
       <c r="O163" s="7" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15">
+      <c r="A165" s="7" t="s">
         <v>2008</v>
       </c>
-    </row>
-    <row r="164" spans="1:15">
-      <c r="A164" s="7" t="s">
-        <v>2009</v>
-      </c>
-      <c r="O164" s="7" t="s">
+      <c r="B165" s="7" t="s">
         <v>2008</v>
+      </c>
+      <c r="O165" s="7" t="s">
+        <v>2662</v>
       </c>
     </row>
     <row r="166" spans="1:15">
       <c r="A166" s="7" t="s">
-        <v>2010</v>
-      </c>
-      <c r="B166" s="7" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="O166" s="7" t="s">
-        <v>2664</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="167" spans="1:15">
       <c r="A167" s="7" t="s">
+        <v>2010</v>
+      </c>
+      <c r="O167" s="7" t="s">
+        <v>2663</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15">
+      <c r="A169" s="7" t="s">
         <v>2011</v>
       </c>
-      <c r="O167" s="7" t="s">
-        <v>2665</v>
-      </c>
-    </row>
-    <row r="168" spans="1:15">
-      <c r="A168" s="7" t="s">
-        <v>2012</v>
-      </c>
-      <c r="O168" s="7" t="s">
-        <v>2665</v>
+      <c r="B169" s="7" t="s">
+        <v>2011</v>
+      </c>
+      <c r="O169" s="7" t="s">
+        <v>2664</v>
       </c>
     </row>
     <row r="170" spans="1:15">
       <c r="A170" s="7" t="s">
-        <v>2013</v>
-      </c>
-      <c r="B170" s="7" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="O170" s="7" t="s">
-        <v>2666</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="171" spans="1:15">
       <c r="A171" s="7" t="s">
+        <v>2013</v>
+      </c>
+      <c r="O171" s="7" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15">
+      <c r="A173" s="7" t="s">
         <v>2014</v>
       </c>
-      <c r="O171" s="7" t="s">
-        <v>2667</v>
-      </c>
-    </row>
-    <row r="172" spans="1:15">
-      <c r="A172" s="7" t="s">
+      <c r="B173" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="O173" s="7" t="s">
         <v>2015</v>
-      </c>
-      <c r="O172" s="7" t="s">
-        <v>2668</v>
       </c>
     </row>
     <row r="174" spans="1:15">
       <c r="A174" s="7" t="s">
         <v>2016</v>
       </c>
-      <c r="B174" s="7" t="s">
-        <v>2016</v>
-      </c>
       <c r="O174" s="7" t="s">
         <v>2017</v>
       </c>
@@ -26149,186 +26153,186 @@
         <v>2018</v>
       </c>
       <c r="O175" s="7" t="s">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="176" spans="1:15">
-      <c r="A176" s="7" t="s">
-        <v>2020</v>
-      </c>
-      <c r="O176" s="7" t="s">
-        <v>2669</v>
+        <v>2667</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15">
+      <c r="A177" s="7" t="s">
+        <v>3185</v>
+      </c>
+      <c r="B177" s="7" t="s">
+        <v>3181</v>
+      </c>
+      <c r="O177" s="7" t="s">
+        <v>3182</v>
       </c>
     </row>
     <row r="178" spans="1:15">
       <c r="A178" s="7" t="s">
+        <v>3184</v>
+      </c>
+      <c r="O178" s="7" t="s">
         <v>3187</v>
-      </c>
-      <c r="B178" s="7" t="s">
-        <v>3183</v>
-      </c>
-      <c r="O178" s="7" t="s">
-        <v>3184</v>
       </c>
     </row>
     <row r="179" spans="1:15">
       <c r="A179" s="7" t="s">
+        <v>3183</v>
+      </c>
+      <c r="O179" s="7" t="s">
         <v>3186</v>
       </c>
-      <c r="O179" s="7" t="s">
-        <v>3189</v>
-      </c>
-    </row>
-    <row r="180" spans="1:15">
-      <c r="A180" s="7" t="s">
-        <v>3185</v>
-      </c>
-      <c r="O180" s="7" t="s">
-        <v>3188</v>
+    </row>
+    <row r="181" spans="1:15">
+      <c r="A181" s="7" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B181" s="7" t="s">
+        <v>2019</v>
+      </c>
+      <c r="O181" s="7" t="s">
+        <v>2668</v>
       </c>
     </row>
     <row r="182" spans="1:15">
       <c r="A182" s="7" t="s">
-        <v>2021</v>
-      </c>
-      <c r="B182" s="7" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="O182" s="7" t="s">
-        <v>2670</v>
+        <v>2669</v>
       </c>
     </row>
     <row r="183" spans="1:15">
       <c r="A183" s="7" t="s">
+        <v>2021</v>
+      </c>
+      <c r="O183" s="7" t="s">
         <v>2022</v>
       </c>
-      <c r="O183" s="7" t="s">
-        <v>2671</v>
-      </c>
-    </row>
-    <row r="184" spans="1:15">
-      <c r="A184" s="7" t="s">
+    </row>
+    <row r="185" spans="1:15">
+      <c r="A185" s="7" t="s">
         <v>2023</v>
       </c>
-      <c r="O184" s="7" t="s">
-        <v>2024</v>
+      <c r="B185" s="7" t="s">
+        <v>2023</v>
+      </c>
+      <c r="O185" s="7" t="s">
+        <v>2670</v>
       </c>
     </row>
     <row r="186" spans="1:15">
       <c r="A186" s="7" t="s">
-        <v>2025</v>
-      </c>
-      <c r="B186" s="7" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="O186" s="7" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="187" spans="1:15">
       <c r="A187" s="7" t="s">
+        <v>2025</v>
+      </c>
+      <c r="O187" s="7" t="s">
         <v>2026</v>
       </c>
-      <c r="O187" s="7" t="s">
-        <v>2673</v>
-      </c>
-    </row>
-    <row r="188" spans="1:15">
-      <c r="A188" s="7" t="s">
-        <v>2027</v>
-      </c>
-      <c r="O188" s="7" t="s">
-        <v>2028</v>
+    </row>
+    <row r="189" spans="1:15">
+      <c r="A189" s="7" t="s">
+        <v>2993</v>
+      </c>
+      <c r="B189" s="7" t="s">
+        <v>2993</v>
+      </c>
+      <c r="O189" s="7" t="s">
+        <v>3019</v>
       </c>
     </row>
     <row r="190" spans="1:15">
       <c r="A190" s="7" t="s">
         <v>2995</v>
       </c>
-      <c r="B190" s="7" t="s">
-        <v>2995</v>
-      </c>
       <c r="O190" s="7" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="191" spans="1:15">
       <c r="A191" s="7" t="s">
-        <v>2997</v>
+        <v>2994</v>
       </c>
       <c r="O191" s="7" t="s">
-        <v>3022</v>
-      </c>
-    </row>
-    <row r="192" spans="1:15">
-      <c r="A192" s="7" t="s">
         <v>2996</v>
       </c>
-      <c r="O192" s="7" t="s">
-        <v>2998</v>
+    </row>
+    <row r="193" spans="1:15">
+      <c r="A193" s="7" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B193" s="7" t="s">
+        <v>2027</v>
+      </c>
+      <c r="O193" s="7" t="s">
+        <v>2672</v>
       </c>
     </row>
     <row r="194" spans="1:15">
       <c r="A194" s="7" t="s">
-        <v>2029</v>
-      </c>
-      <c r="B194" s="7" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="O194" s="7" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="195" spans="1:15">
       <c r="A195" s="7" t="s">
+        <v>2029</v>
+      </c>
+      <c r="O195" s="7" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15">
+      <c r="A197" s="7" t="s">
         <v>2030</v>
       </c>
-      <c r="O195" s="7" t="s">
-        <v>2675</v>
-      </c>
-    </row>
-    <row r="196" spans="1:15">
-      <c r="A196" s="7" t="s">
+      <c r="B197" s="7" t="s">
+        <v>2030</v>
+      </c>
+      <c r="O197" s="7" t="s">
         <v>2031</v>
-      </c>
-      <c r="O196" s="7" t="s">
-        <v>2676</v>
       </c>
     </row>
     <row r="198" spans="1:15">
       <c r="A198" s="7" t="s">
         <v>2032</v>
       </c>
-      <c r="B198" s="7" t="s">
-        <v>2032</v>
-      </c>
       <c r="O198" s="7" t="s">
-        <v>2033</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="199" spans="1:15">
       <c r="A199" s="7" t="s">
+        <v>2033</v>
+      </c>
+      <c r="O199" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15">
+      <c r="A201" s="7" t="s">
         <v>2034</v>
       </c>
-      <c r="O199" s="7" t="s">
-        <v>2677</v>
-      </c>
-    </row>
-    <row r="200" spans="1:15">
-      <c r="A200" s="7" t="s">
+      <c r="B201" s="7" t="s">
+        <v>2034</v>
+      </c>
+      <c r="O201" s="7" t="s">
         <v>2035</v>
-      </c>
-      <c r="O200" s="7" t="s">
-        <v>2678</v>
       </c>
     </row>
     <row r="202" spans="1:15">
       <c r="A202" s="7" t="s">
         <v>2036</v>
       </c>
-      <c r="B202" s="7" t="s">
-        <v>2036</v>
-      </c>
       <c r="O202" s="7" t="s">
         <v>2037</v>
       </c>
@@ -26338,68 +26342,71 @@
         <v>2038</v>
       </c>
       <c r="O203" s="7" t="s">
+        <v>2677</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15">
+      <c r="A205" s="7" t="s">
         <v>2039</v>
       </c>
-    </row>
-    <row r="204" spans="1:15">
-      <c r="A204" s="7" t="s">
+      <c r="B205" s="7" t="s">
+        <v>2039</v>
+      </c>
+      <c r="O205" s="7" t="s">
         <v>2040</v>
-      </c>
-      <c r="O204" s="7" t="s">
-        <v>2679</v>
       </c>
     </row>
     <row r="206" spans="1:15">
       <c r="A206" s="7" t="s">
         <v>2041</v>
       </c>
-      <c r="B206" s="7" t="s">
-        <v>2041</v>
-      </c>
       <c r="O206" s="7" t="s">
-        <v>2042</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="207" spans="1:15">
       <c r="A207" s="7" t="s">
+        <v>2042</v>
+      </c>
+      <c r="O207" s="7" t="s">
+        <v>2679</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15">
+      <c r="A209" s="7" t="s">
         <v>2043</v>
       </c>
-      <c r="O207" s="7" t="s">
-        <v>2680</v>
-      </c>
-    </row>
-    <row r="208" spans="1:15">
-      <c r="A208" s="7" t="s">
+      <c r="B209" s="7" t="s">
+        <v>2043</v>
+      </c>
+      <c r="O209" s="7" t="s">
         <v>2044</v>
-      </c>
-      <c r="O208" s="7" t="s">
-        <v>2681</v>
       </c>
     </row>
     <row r="210" spans="1:15">
       <c r="A210" s="7" t="s">
         <v>2045</v>
       </c>
-      <c r="B210" s="7" t="s">
-        <v>2045</v>
-      </c>
       <c r="O210" s="7" t="s">
-        <v>2046</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="211" spans="1:15">
       <c r="A211" s="7" t="s">
+        <v>2046</v>
+      </c>
+      <c r="O211" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="O211" s="7" t="s">
-        <v>2682</v>
-      </c>
-    </row>
-    <row r="212" spans="1:15">
-      <c r="A212" s="7" t="s">
+    </row>
+    <row r="213" spans="1:15">
+      <c r="A213" s="7" t="s">
         <v>2048</v>
       </c>
-      <c r="O212" s="7" t="s">
+      <c r="B213" s="7" t="s">
+        <v>2048</v>
+      </c>
+      <c r="O213" s="7" t="s">
         <v>2049</v>
       </c>
     </row>
@@ -26407,9 +26414,6 @@
       <c r="A214" s="7" t="s">
         <v>2050</v>
       </c>
-      <c r="B214" s="7" t="s">
-        <v>2050</v>
-      </c>
       <c r="O214" s="7" t="s">
         <v>2051</v>
       </c>
@@ -26422,11 +26426,14 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="216" spans="1:15">
-      <c r="A216" s="7" t="s">
+    <row r="217" spans="1:15">
+      <c r="A217" s="7" t="s">
         <v>2054</v>
       </c>
-      <c r="O216" s="7" t="s">
+      <c r="B217" s="7" t="s">
+        <v>2054</v>
+      </c>
+      <c r="O217" s="7" t="s">
         <v>2055</v>
       </c>
     </row>
@@ -26434,53 +26441,53 @@
       <c r="A218" s="7" t="s">
         <v>2056</v>
       </c>
-      <c r="B218" s="7" t="s">
-        <v>2056</v>
-      </c>
       <c r="O218" s="7" t="s">
-        <v>2057</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="219" spans="1:15">
       <c r="A219" s="7" t="s">
+        <v>2057</v>
+      </c>
+      <c r="O219" s="7" t="s">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15">
+      <c r="A221" s="7" t="s">
         <v>2058</v>
       </c>
-      <c r="O219" s="7" t="s">
+      <c r="B221" s="7" t="s">
+        <v>2058</v>
+      </c>
+      <c r="O221" s="7" t="s">
         <v>2683</v>
-      </c>
-    </row>
-    <row r="220" spans="1:15">
-      <c r="A220" s="7" t="s">
-        <v>2059</v>
-      </c>
-      <c r="O220" s="7" t="s">
-        <v>2684</v>
       </c>
     </row>
     <row r="222" spans="1:15">
       <c r="A222" s="7" t="s">
-        <v>2060</v>
-      </c>
-      <c r="B222" s="7" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="O222" s="7" t="s">
-        <v>2685</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="223" spans="1:15">
       <c r="A223" s="7" t="s">
+        <v>2060</v>
+      </c>
+      <c r="O223" s="7" t="s">
         <v>2061</v>
       </c>
-      <c r="O223" s="7" t="s">
-        <v>2686</v>
-      </c>
-    </row>
-    <row r="224" spans="1:15">
-      <c r="A224" s="7" t="s">
+    </row>
+    <row r="225" spans="1:15">
+      <c r="A225" s="7" t="s">
         <v>2062</v>
       </c>
-      <c r="O224" s="7" t="s">
+      <c r="B225" s="7" t="s">
+        <v>2062</v>
+      </c>
+      <c r="O225" s="7" t="s">
         <v>2063</v>
       </c>
     </row>
@@ -26488,53 +26495,53 @@
       <c r="A226" s="7" t="s">
         <v>2064</v>
       </c>
-      <c r="B226" s="7" t="s">
-        <v>2064</v>
-      </c>
       <c r="O226" s="7" t="s">
-        <v>2065</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="227" spans="1:15">
       <c r="A227" s="7" t="s">
+        <v>2065</v>
+      </c>
+      <c r="O227" s="7" t="s">
+        <v>2686</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15">
+      <c r="A229" s="7" t="s">
         <v>2066</v>
       </c>
-      <c r="O227" s="7" t="s">
-        <v>2687</v>
-      </c>
-    </row>
-    <row r="228" spans="1:15">
-      <c r="A228" s="7" t="s">
+      <c r="B229" s="7" t="s">
+        <v>2066</v>
+      </c>
+      <c r="O229" s="7" t="s">
         <v>2067</v>
-      </c>
-      <c r="O228" s="7" t="s">
-        <v>2688</v>
       </c>
     </row>
     <row r="230" spans="1:15">
       <c r="A230" s="7" t="s">
         <v>2068</v>
       </c>
-      <c r="B230" s="7" t="s">
-        <v>2068</v>
-      </c>
       <c r="O230" s="7" t="s">
-        <v>2069</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="231" spans="1:15">
       <c r="A231" s="7" t="s">
+        <v>2069</v>
+      </c>
+      <c r="O231" s="7" t="s">
         <v>2070</v>
       </c>
-      <c r="O231" s="7" t="s">
-        <v>2689</v>
-      </c>
-    </row>
-    <row r="232" spans="1:15">
-      <c r="A232" s="7" t="s">
+    </row>
+    <row r="233" spans="1:15">
+      <c r="A233" s="7" t="s">
         <v>2071</v>
       </c>
-      <c r="O232" s="7" t="s">
+      <c r="B233" s="7" t="s">
+        <v>2071</v>
+      </c>
+      <c r="O233" s="7" t="s">
         <v>2072</v>
       </c>
     </row>
@@ -26542,92 +26549,89 @@
       <c r="A234" s="7" t="s">
         <v>2073</v>
       </c>
-      <c r="B234" s="7" t="s">
-        <v>2073</v>
-      </c>
       <c r="O234" s="7" t="s">
-        <v>2074</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="235" spans="1:15">
       <c r="A235" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="O235" s="7" t="s">
+        <v>2688</v>
+      </c>
+    </row>
+    <row r="237" spans="1:15">
+      <c r="A237" s="7" t="s">
         <v>2075</v>
       </c>
-      <c r="O235" s="7" t="s">
-        <v>2690</v>
-      </c>
-    </row>
-    <row r="236" spans="1:15">
-      <c r="A236" s="7" t="s">
+      <c r="B237" s="7" t="s">
+        <v>2075</v>
+      </c>
+      <c r="O237" s="7" t="s">
         <v>2076</v>
-      </c>
-      <c r="O236" s="7" t="s">
-        <v>2690</v>
       </c>
     </row>
     <row r="238" spans="1:15">
       <c r="A238" s="7" t="s">
         <v>2077</v>
       </c>
-      <c r="B238" s="7" t="s">
-        <v>2077</v>
-      </c>
       <c r="O238" s="7" t="s">
-        <v>2078</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="239" spans="1:15">
       <c r="A239" s="7" t="s">
+        <v>2078</v>
+      </c>
+      <c r="O239" s="7" t="s">
+        <v>2631</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15">
+      <c r="A241" s="7" t="s">
         <v>2079</v>
       </c>
-      <c r="O239" s="7" t="s">
-        <v>2691</v>
-      </c>
-    </row>
-    <row r="240" spans="1:15">
-      <c r="A240" s="7" t="s">
+      <c r="B241" s="7" t="s">
         <v>2080</v>
       </c>
-      <c r="O240" s="7" t="s">
-        <v>2633</v>
+      <c r="O241" s="7" t="s">
+        <v>2690</v>
       </c>
     </row>
     <row r="242" spans="1:15">
       <c r="A242" s="7" t="s">
         <v>2081</v>
       </c>
-      <c r="B242" s="7" t="s">
-        <v>2082</v>
-      </c>
       <c r="O242" s="7" t="s">
-        <v>2692</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="243" spans="1:15">
       <c r="A243" s="7" t="s">
+        <v>2082</v>
+      </c>
+      <c r="O243" s="7" t="s">
+        <v>2692</v>
+      </c>
+    </row>
+    <row r="245" spans="1:15">
+      <c r="A245" s="7" t="s">
         <v>2083</v>
       </c>
-      <c r="O243" s="7" t="s">
+      <c r="B245" s="7" t="s">
+        <v>2084</v>
+      </c>
+      <c r="O245" s="7" t="s">
         <v>2693</v>
-      </c>
-    </row>
-    <row r="244" spans="1:15">
-      <c r="A244" s="7" t="s">
-        <v>2084</v>
-      </c>
-      <c r="O244" s="7" t="s">
-        <v>2694</v>
       </c>
     </row>
     <row r="246" spans="1:15">
       <c r="A246" s="7" t="s">
         <v>2085</v>
       </c>
-      <c r="B246" s="7" t="s">
+      <c r="O246" s="7" t="s">
         <v>2086</v>
-      </c>
-      <c r="O246" s="7" t="s">
-        <v>2695</v>
       </c>
     </row>
     <row r="247" spans="1:15">
@@ -26635,26 +26639,26 @@
         <v>2087</v>
       </c>
       <c r="O247" s="7" t="s">
+        <v>2694</v>
+      </c>
+    </row>
+    <row r="249" spans="1:15">
+      <c r="A249" s="7" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B249" s="7" t="s">
+        <v>1674</v>
+      </c>
+      <c r="O249" s="7" t="s">
         <v>2088</v>
-      </c>
-    </row>
-    <row r="248" spans="1:15">
-      <c r="A248" s="7" t="s">
-        <v>2089</v>
-      </c>
-      <c r="O248" s="7" t="s">
-        <v>2696</v>
       </c>
     </row>
     <row r="250" spans="1:15">
       <c r="A250" s="7" t="s">
-        <v>1676</v>
-      </c>
-      <c r="B250" s="7" t="s">
-        <v>1676</v>
+        <v>2695</v>
       </c>
       <c r="O250" s="7" t="s">
-        <v>2090</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="251" spans="1:15">
@@ -26665,21 +26669,21 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="252" spans="1:15">
-      <c r="A252" s="7" t="s">
-        <v>2699</v>
-      </c>
-      <c r="O252" s="7" t="s">
-        <v>2700</v>
+    <row r="253" spans="1:15">
+      <c r="A253" s="7" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B253" s="7" t="s">
+        <v>2089</v>
+      </c>
+      <c r="O253" s="7" t="s">
+        <v>2090</v>
       </c>
     </row>
     <row r="254" spans="1:15">
       <c r="A254" s="7" t="s">
         <v>2091</v>
       </c>
-      <c r="B254" s="7" t="s">
-        <v>2091</v>
-      </c>
       <c r="O254" s="7" t="s">
         <v>2092</v>
       </c>
@@ -26689,68 +26693,71 @@
         <v>2093</v>
       </c>
       <c r="O255" s="7" t="s">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="257" spans="1:15">
+      <c r="A257" s="7" t="s">
         <v>2094</v>
       </c>
-    </row>
-    <row r="256" spans="1:15">
-      <c r="A256" s="7" t="s">
+      <c r="B257" s="7" t="s">
+        <v>2094</v>
+      </c>
+      <c r="O257" s="7" t="s">
         <v>2095</v>
-      </c>
-      <c r="O256" s="7" t="s">
-        <v>2701</v>
       </c>
     </row>
     <row r="258" spans="1:15">
       <c r="A258" s="7" t="s">
         <v>2096</v>
       </c>
-      <c r="B258" s="7" t="s">
-        <v>2096</v>
-      </c>
       <c r="O258" s="7" t="s">
-        <v>2097</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="259" spans="1:15">
       <c r="A259" s="7" t="s">
+        <v>2097</v>
+      </c>
+      <c r="O259" s="7" t="s">
+        <v>2701</v>
+      </c>
+    </row>
+    <row r="261" spans="1:15">
+      <c r="A261" s="7" t="s">
         <v>2098</v>
       </c>
-      <c r="O259" s="7" t="s">
-        <v>2702</v>
-      </c>
-    </row>
-    <row r="260" spans="1:15">
-      <c r="A260" s="7" t="s">
+      <c r="B261" s="7" t="s">
+        <v>2098</v>
+      </c>
+      <c r="O261" s="7" t="s">
         <v>2099</v>
-      </c>
-      <c r="O260" s="7" t="s">
-        <v>2703</v>
       </c>
     </row>
     <row r="262" spans="1:15">
       <c r="A262" s="7" t="s">
         <v>2100</v>
       </c>
-      <c r="B262" s="7" t="s">
-        <v>2100</v>
-      </c>
       <c r="O262" s="7" t="s">
-        <v>2101</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="263" spans="1:15">
       <c r="A263" s="7" t="s">
+        <v>2101</v>
+      </c>
+      <c r="O263" s="7" t="s">
         <v>2102</v>
       </c>
-      <c r="O263" s="7" t="s">
-        <v>2704</v>
-      </c>
-    </row>
-    <row r="264" spans="1:15">
-      <c r="A264" s="7" t="s">
+    </row>
+    <row r="265" spans="1:15">
+      <c r="A265" s="7" t="s">
         <v>2103</v>
       </c>
-      <c r="O264" s="7" t="s">
+      <c r="B265" s="7" t="s">
+        <v>2103</v>
+      </c>
+      <c r="O265" s="7" t="s">
         <v>2104</v>
       </c>
     </row>
@@ -26758,53 +26765,53 @@
       <c r="A266" s="7" t="s">
         <v>2105</v>
       </c>
-      <c r="B266" s="7" t="s">
-        <v>2105</v>
-      </c>
       <c r="O266" s="7" t="s">
-        <v>2106</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="267" spans="1:15">
       <c r="A267" s="7" t="s">
+        <v>2106</v>
+      </c>
+      <c r="O267" s="7" t="s">
+        <v>2704</v>
+      </c>
+    </row>
+    <row r="269" spans="1:15">
+      <c r="A269" s="7" t="s">
         <v>2107</v>
       </c>
-      <c r="O267" s="7" t="s">
-        <v>2705</v>
-      </c>
-    </row>
-    <row r="268" spans="1:15">
-      <c r="A268" s="7" t="s">
+      <c r="B269" s="7" t="s">
+        <v>2107</v>
+      </c>
+      <c r="O269" s="7" t="s">
         <v>2108</v>
-      </c>
-      <c r="O268" s="7" t="s">
-        <v>2706</v>
       </c>
     </row>
     <row r="270" spans="1:15">
       <c r="A270" s="7" t="s">
         <v>2109</v>
       </c>
-      <c r="B270" s="7" t="s">
-        <v>2109</v>
-      </c>
       <c r="O270" s="7" t="s">
-        <v>2110</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="271" spans="1:15">
       <c r="A271" s="7" t="s">
+        <v>2110</v>
+      </c>
+      <c r="O271" s="7" t="s">
         <v>2111</v>
       </c>
-      <c r="O271" s="7" t="s">
-        <v>2707</v>
-      </c>
-    </row>
-    <row r="272" spans="1:15">
-      <c r="A272" s="7" t="s">
+    </row>
+    <row r="273" spans="1:15">
+      <c r="A273" s="7" t="s">
         <v>2112</v>
       </c>
-      <c r="O272" s="7" t="s">
+      <c r="B273" s="7" t="s">
+        <v>2112</v>
+      </c>
+      <c r="O273" s="7" t="s">
         <v>2113</v>
       </c>
     </row>
@@ -26812,53 +26819,53 @@
       <c r="A274" s="7" t="s">
         <v>2114</v>
       </c>
-      <c r="B274" s="7" t="s">
-        <v>2114</v>
-      </c>
       <c r="O274" s="7" t="s">
-        <v>2115</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="275" spans="1:15">
       <c r="A275" s="7" t="s">
+        <v>2115</v>
+      </c>
+      <c r="O275" s="7" t="s">
+        <v>2707</v>
+      </c>
+    </row>
+    <row r="277" spans="1:15">
+      <c r="A277" s="7" t="s">
         <v>2116</v>
       </c>
-      <c r="O275" s="7" t="s">
-        <v>2708</v>
-      </c>
-    </row>
-    <row r="276" spans="1:15">
-      <c r="A276" s="7" t="s">
+      <c r="B277" s="7" t="s">
+        <v>2116</v>
+      </c>
+      <c r="O277" s="7" t="s">
         <v>2117</v>
-      </c>
-      <c r="O276" s="7" t="s">
-        <v>2709</v>
       </c>
     </row>
     <row r="278" spans="1:15">
       <c r="A278" s="7" t="s">
         <v>2118</v>
       </c>
-      <c r="B278" s="7" t="s">
-        <v>2118</v>
-      </c>
       <c r="O278" s="7" t="s">
-        <v>2119</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="279" spans="1:15">
       <c r="A279" s="7" t="s">
+        <v>2119</v>
+      </c>
+      <c r="O279" s="7" t="s">
         <v>2120</v>
       </c>
-      <c r="O279" s="7" t="s">
-        <v>2710</v>
-      </c>
-    </row>
-    <row r="280" spans="1:15">
-      <c r="A280" s="7" t="s">
+    </row>
+    <row r="281" spans="1:15">
+      <c r="A281" s="7" t="s">
         <v>2121</v>
       </c>
-      <c r="O280" s="7" t="s">
+      <c r="B281" s="7" t="s">
+        <v>2121</v>
+      </c>
+      <c r="O281" s="7" t="s">
         <v>2122</v>
       </c>
     </row>
@@ -26866,9 +26873,6 @@
       <c r="A282" s="7" t="s">
         <v>2123</v>
       </c>
-      <c r="B282" s="7" t="s">
-        <v>2123</v>
-      </c>
       <c r="O282" s="7" t="s">
         <v>2124</v>
       </c>
@@ -26878,24 +26882,24 @@
         <v>2125</v>
       </c>
       <c r="O283" s="7" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="285" spans="1:15">
+      <c r="A285" s="7" t="s">
         <v>2126</v>
       </c>
-    </row>
-    <row r="284" spans="1:15">
-      <c r="A284" s="7" t="s">
+      <c r="B285" s="7" t="s">
+        <v>2126</v>
+      </c>
+      <c r="O285" s="7" t="s">
         <v>2127</v>
-      </c>
-      <c r="O284" s="7" t="s">
-        <v>2711</v>
       </c>
     </row>
     <row r="286" spans="1:15">
       <c r="A286" s="7" t="s">
         <v>2128</v>
       </c>
-      <c r="B286" s="7" t="s">
-        <v>2128</v>
-      </c>
       <c r="O286" s="7" t="s">
         <v>2129</v>
       </c>
@@ -26905,53 +26909,53 @@
         <v>2130</v>
       </c>
       <c r="O287" s="7" t="s">
+        <v>2710</v>
+      </c>
+    </row>
+    <row r="289" spans="1:15">
+      <c r="A289" s="7" t="s">
         <v>2131</v>
       </c>
-    </row>
-    <row r="288" spans="1:15">
-      <c r="A288" s="7" t="s">
+      <c r="B289" s="7" t="s">
+        <v>2131</v>
+      </c>
+      <c r="O289" s="7" t="s">
         <v>2132</v>
-      </c>
-      <c r="O288" s="7" t="s">
-        <v>2712</v>
       </c>
     </row>
     <row r="290" spans="1:15">
       <c r="A290" s="7" t="s">
         <v>2133</v>
       </c>
-      <c r="B290" s="7" t="s">
-        <v>2133</v>
-      </c>
       <c r="O290" s="7" t="s">
-        <v>2134</v>
+        <v>2711</v>
       </c>
     </row>
     <row r="291" spans="1:15">
       <c r="A291" s="7" t="s">
+        <v>2134</v>
+      </c>
+      <c r="O291" s="7" t="s">
+        <v>2712</v>
+      </c>
+    </row>
+    <row r="293" spans="1:15">
+      <c r="A293" s="7" t="s">
         <v>2135</v>
       </c>
-      <c r="O291" s="7" t="s">
-        <v>2713</v>
-      </c>
-    </row>
-    <row r="292" spans="1:15">
-      <c r="A292" s="7" t="s">
+      <c r="B293" s="7" t="s">
+        <v>2135</v>
+      </c>
+      <c r="O293" s="7" t="s">
         <v>2136</v>
-      </c>
-      <c r="O292" s="7" t="s">
-        <v>2714</v>
       </c>
     </row>
     <row r="294" spans="1:15">
       <c r="A294" s="7" t="s">
+        <v>1826</v>
+      </c>
+      <c r="O294" s="7" t="s">
         <v>2137</v>
-      </c>
-      <c r="B294" s="7" t="s">
-        <v>2137</v>
-      </c>
-      <c r="O294" s="7" t="s">
-        <v>2138</v>
       </c>
     </row>
     <row r="295" spans="1:15">
@@ -26959,26 +26963,26 @@
         <v>1828</v>
       </c>
       <c r="O295" s="7" t="s">
-        <v>2139</v>
-      </c>
-    </row>
-    <row r="296" spans="1:15">
-      <c r="A296" s="7" t="s">
-        <v>1830</v>
-      </c>
-      <c r="O296" s="7" t="s">
-        <v>2715</v>
+        <v>2713</v>
+      </c>
+    </row>
+    <row r="297" spans="1:15">
+      <c r="A297" s="7" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B297" s="7" t="s">
+        <v>1824</v>
+      </c>
+      <c r="O297" s="7" t="s">
+        <v>1825</v>
       </c>
     </row>
     <row r="298" spans="1:15">
       <c r="A298" s="7" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B298" s="7" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="O298" s="7" t="s">
-        <v>1827</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="299" spans="1:15">
@@ -26986,95 +26990,98 @@
         <v>1829</v>
       </c>
       <c r="O299" s="7" t="s">
-        <v>1833</v>
-      </c>
-    </row>
-    <row r="300" spans="1:15">
-      <c r="A300" s="7" t="s">
-        <v>1831</v>
-      </c>
-      <c r="O300" s="7" t="s">
-        <v>1832</v>
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="301" spans="1:15">
+      <c r="A301" s="7" t="s">
+        <v>2520</v>
+      </c>
+      <c r="B301" s="7" t="s">
+        <v>2520</v>
+      </c>
+      <c r="O301" s="7" t="s">
+        <v>2523</v>
       </c>
     </row>
     <row r="302" spans="1:15">
       <c r="A302" s="7" t="s">
-        <v>2522</v>
-      </c>
-      <c r="B302" s="7" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="O302" s="7" t="s">
-        <v>2525</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="303" spans="1:15">
       <c r="A303" s="7" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="O303" s="7" t="s">
-        <v>2614</v>
-      </c>
-    </row>
-    <row r="304" spans="1:15">
-      <c r="A304" s="7" t="s">
         <v>2524</v>
       </c>
-      <c r="O304" s="7" t="s">
-        <v>2526</v>
+    </row>
+    <row r="305" spans="1:15">
+      <c r="A305" s="7" t="s">
+        <v>3079</v>
+      </c>
+      <c r="B305" s="7" t="s">
+        <v>3079</v>
+      </c>
+      <c r="O305" s="7" t="s">
+        <v>3064</v>
       </c>
     </row>
     <row r="306" spans="1:15">
       <c r="A306" s="7" t="s">
-        <v>3081</v>
-      </c>
-      <c r="B306" s="7" t="s">
-        <v>3081</v>
+        <v>3062</v>
       </c>
       <c r="O306" s="7" t="s">
-        <v>3066</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="307" spans="1:15">
       <c r="A307" s="7" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="O307" s="7" t="s">
-        <v>3078</v>
-      </c>
-    </row>
-    <row r="308" spans="1:15">
-      <c r="A308" s="7" t="s">
-        <v>3065</v>
-      </c>
-      <c r="O308" s="7" t="s">
-        <v>3077</v>
+        <v>3075</v>
+      </c>
+    </row>
+    <row r="309" spans="1:15">
+      <c r="A309" s="7" t="s">
+        <v>2138</v>
+      </c>
+      <c r="B309" s="7" t="s">
+        <v>2138</v>
+      </c>
+      <c r="O309" s="7" t="s">
+        <v>2139</v>
       </c>
     </row>
     <row r="310" spans="1:15">
       <c r="A310" s="7" t="s">
         <v>2140</v>
       </c>
-      <c r="B310" s="7" t="s">
-        <v>2140</v>
-      </c>
       <c r="O310" s="7" t="s">
-        <v>2141</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="311" spans="1:15">
       <c r="A311" s="7" t="s">
+        <v>2141</v>
+      </c>
+      <c r="O311" s="7" t="s">
         <v>2142</v>
       </c>
-      <c r="O311" s="7" t="s">
-        <v>2716</v>
-      </c>
-    </row>
-    <row r="312" spans="1:15">
-      <c r="A312" s="7" t="s">
+    </row>
+    <row r="313" spans="1:15">
+      <c r="A313" s="7" t="s">
         <v>2143</v>
       </c>
-      <c r="O312" s="7" t="s">
+      <c r="B313" s="7" t="s">
+        <v>2715</v>
+      </c>
+      <c r="O313" s="7" t="s">
         <v>2144</v>
       </c>
     </row>
@@ -27082,36 +27089,33 @@
       <c r="A314" s="7" t="s">
         <v>2145</v>
       </c>
-      <c r="B314" s="7" t="s">
-        <v>2717</v>
-      </c>
       <c r="O314" s="7" t="s">
-        <v>2146</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="315" spans="1:15">
       <c r="A315" s="7" t="s">
+        <v>2146</v>
+      </c>
+      <c r="O315" s="7" t="s">
+        <v>2717</v>
+      </c>
+    </row>
+    <row r="317" spans="1:15">
+      <c r="A317" s="7" t="s">
         <v>2147</v>
       </c>
-      <c r="O315" s="7" t="s">
-        <v>2718</v>
-      </c>
-    </row>
-    <row r="316" spans="1:15">
-      <c r="A316" s="7" t="s">
+      <c r="B317" s="7" t="s">
+        <v>2147</v>
+      </c>
+      <c r="O317" s="7" t="s">
         <v>2148</v>
-      </c>
-      <c r="O316" s="7" t="s">
-        <v>2719</v>
       </c>
     </row>
     <row r="318" spans="1:15">
       <c r="A318" s="7" t="s">
         <v>2149</v>
       </c>
-      <c r="B318" s="7" t="s">
-        <v>2149</v>
-      </c>
       <c r="O318" s="7" t="s">
         <v>2150</v>
       </c>
@@ -27124,48 +27128,48 @@
         <v>2152</v>
       </c>
     </row>
-    <row r="320" spans="1:15">
-      <c r="A320" s="7" t="s">
-        <v>2153</v>
-      </c>
-      <c r="O320" s="7" t="s">
-        <v>2154</v>
+    <row r="321" spans="1:15">
+      <c r="A321" s="7" t="s">
+        <v>2976</v>
+      </c>
+      <c r="B321" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="O321" s="7" t="s">
+        <v>2977</v>
       </c>
     </row>
     <row r="322" spans="1:15">
       <c r="A322" s="7" t="s">
-        <v>2978</v>
-      </c>
-      <c r="B322" s="7" t="s">
-        <v>2977</v>
+        <v>2983</v>
       </c>
       <c r="O322" s="7" t="s">
-        <v>2979</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="323" spans="1:15">
       <c r="A323" s="7" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="O323" s="7" t="s">
-        <v>2982</v>
-      </c>
-    </row>
-    <row r="324" spans="1:15">
-      <c r="A324" s="7" t="s">
-        <v>2986</v>
-      </c>
-      <c r="O324" s="7" t="s">
-        <v>2981</v>
+        <v>2979</v>
+      </c>
+    </row>
+    <row r="325" spans="1:15">
+      <c r="A325" s="7" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B325" s="7" t="s">
+        <v>2153</v>
+      </c>
+      <c r="O325" s="7" t="s">
+        <v>2154</v>
       </c>
     </row>
     <row r="326" spans="1:15">
       <c r="A326" s="7" t="s">
         <v>2155</v>
       </c>
-      <c r="B326" s="7" t="s">
-        <v>2155</v>
-      </c>
       <c r="O326" s="7" t="s">
         <v>2156</v>
       </c>
@@ -27175,68 +27179,71 @@
         <v>2157</v>
       </c>
       <c r="O327" s="7" t="s">
+        <v>2718</v>
+      </c>
+    </row>
+    <row r="329" spans="1:15">
+      <c r="A329" s="7" t="s">
         <v>2158</v>
       </c>
-    </row>
-    <row r="328" spans="1:15">
-      <c r="A328" s="7" t="s">
+      <c r="B329" s="7" t="s">
+        <v>2158</v>
+      </c>
+      <c r="O329" s="7" t="s">
         <v>2159</v>
-      </c>
-      <c r="O328" s="7" t="s">
-        <v>2720</v>
       </c>
     </row>
     <row r="330" spans="1:15">
       <c r="A330" s="7" t="s">
         <v>2160</v>
       </c>
-      <c r="B330" s="7" t="s">
-        <v>2160</v>
-      </c>
       <c r="O330" s="7" t="s">
-        <v>2161</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="331" spans="1:15">
       <c r="A331" s="7" t="s">
+        <v>2161</v>
+      </c>
+      <c r="O331" s="7" t="s">
+        <v>2766</v>
+      </c>
+    </row>
+    <row r="333" spans="1:15">
+      <c r="A333" s="7" t="s">
         <v>2162</v>
       </c>
-      <c r="O331" s="7" t="s">
-        <v>2768</v>
-      </c>
-    </row>
-    <row r="332" spans="1:15">
-      <c r="A332" s="7" t="s">
+      <c r="B333" s="7" t="s">
+        <v>2162</v>
+      </c>
+      <c r="O333" s="7" t="s">
         <v>2163</v>
-      </c>
-      <c r="O332" s="7" t="s">
-        <v>2768</v>
       </c>
     </row>
     <row r="334" spans="1:15">
       <c r="A334" s="7" t="s">
         <v>2164</v>
       </c>
-      <c r="B334" s="7" t="s">
-        <v>2164</v>
-      </c>
       <c r="O334" s="7" t="s">
-        <v>2165</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="335" spans="1:15">
       <c r="A335" s="7" t="s">
+        <v>2165</v>
+      </c>
+      <c r="O335" s="7" t="s">
         <v>2166</v>
       </c>
-      <c r="O335" s="7" t="s">
-        <v>2721</v>
-      </c>
-    </row>
-    <row r="336" spans="1:15">
-      <c r="A336" s="7" t="s">
+    </row>
+    <row r="337" spans="1:15">
+      <c r="A337" s="7" t="s">
         <v>2167</v>
       </c>
-      <c r="O336" s="7" t="s">
+      <c r="B337" s="7" t="s">
+        <v>2167</v>
+      </c>
+      <c r="O337" s="7" t="s">
         <v>2168</v>
       </c>
     </row>
@@ -27244,36 +27251,33 @@
       <c r="A338" s="7" t="s">
         <v>2169</v>
       </c>
-      <c r="B338" s="7" t="s">
-        <v>2169</v>
-      </c>
       <c r="O338" s="7" t="s">
-        <v>2170</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="339" spans="1:15">
       <c r="A339" s="7" t="s">
+        <v>2170</v>
+      </c>
+      <c r="O339" s="7" t="s">
+        <v>2721</v>
+      </c>
+    </row>
+    <row r="341" spans="1:15">
+      <c r="A341" s="7" t="s">
         <v>2171</v>
       </c>
-      <c r="O339" s="7" t="s">
-        <v>2722</v>
-      </c>
-    </row>
-    <row r="340" spans="1:15">
-      <c r="A340" s="7" t="s">
+      <c r="B341" s="7" t="s">
+        <v>2171</v>
+      </c>
+      <c r="O341" s="7" t="s">
         <v>2172</v>
-      </c>
-      <c r="O340" s="7" t="s">
-        <v>2723</v>
       </c>
     </row>
     <row r="342" spans="1:15">
       <c r="A342" s="7" t="s">
         <v>2173</v>
       </c>
-      <c r="B342" s="7" t="s">
-        <v>2173</v>
-      </c>
       <c r="O342" s="7" t="s">
         <v>2174</v>
       </c>
@@ -27286,11 +27290,14 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="344" spans="1:15">
-      <c r="A344" s="7" t="s">
+    <row r="345" spans="1:15">
+      <c r="A345" s="7" t="s">
         <v>2177</v>
       </c>
-      <c r="O344" s="7" t="s">
+      <c r="B345" s="7" t="s">
+        <v>2177</v>
+      </c>
+      <c r="O345" s="7" t="s">
         <v>2178</v>
       </c>
     </row>
@@ -27298,26 +27305,26 @@
       <c r="A346" s="7" t="s">
         <v>2179</v>
       </c>
-      <c r="B346" s="7" t="s">
-        <v>2179</v>
-      </c>
       <c r="O346" s="7" t="s">
-        <v>2180</v>
+        <v>2722</v>
       </c>
     </row>
     <row r="347" spans="1:15">
       <c r="A347" s="7" t="s">
+        <v>2180</v>
+      </c>
+      <c r="O347" s="7" t="s">
         <v>2181</v>
       </c>
-      <c r="O347" s="7" t="s">
-        <v>2724</v>
-      </c>
-    </row>
-    <row r="348" spans="1:15">
-      <c r="A348" s="7" t="s">
+    </row>
+    <row r="349" spans="1:15">
+      <c r="A349" s="7" t="s">
         <v>2182</v>
       </c>
-      <c r="O348" s="7" t="s">
+      <c r="B349" s="7" t="s">
+        <v>2182</v>
+      </c>
+      <c r="O349" s="7" t="s">
         <v>2183</v>
       </c>
     </row>
@@ -27325,9 +27332,6 @@
       <c r="A350" s="7" t="s">
         <v>2184</v>
       </c>
-      <c r="B350" s="7" t="s">
-        <v>2184</v>
-      </c>
       <c r="O350" s="7" t="s">
         <v>2185</v>
       </c>
@@ -27337,24 +27341,24 @@
         <v>2186</v>
       </c>
       <c r="O351" s="7" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="353" spans="1:15">
+      <c r="A353" s="7" t="s">
         <v>2187</v>
       </c>
-    </row>
-    <row r="352" spans="1:15">
-      <c r="A352" s="7" t="s">
+      <c r="B353" s="7" t="s">
+        <v>2187</v>
+      </c>
+      <c r="O353" s="7" t="s">
         <v>2188</v>
-      </c>
-      <c r="O352" s="7" t="s">
-        <v>2725</v>
       </c>
     </row>
     <row r="354" spans="1:15">
       <c r="A354" s="7" t="s">
         <v>2189</v>
       </c>
-      <c r="B354" s="7" t="s">
-        <v>2189</v>
-      </c>
       <c r="O354" s="7" t="s">
         <v>2190</v>
       </c>
@@ -27364,41 +27368,44 @@
         <v>2191</v>
       </c>
       <c r="O355" s="7" t="s">
+        <v>2724</v>
+      </c>
+    </row>
+    <row r="357" spans="1:15">
+      <c r="A357" s="7" t="s">
         <v>2192</v>
       </c>
-    </row>
-    <row r="356" spans="1:15">
-      <c r="A356" s="7" t="s">
+      <c r="B357" s="7" t="s">
+        <v>2192</v>
+      </c>
+      <c r="O357" s="7" t="s">
         <v>2193</v>
-      </c>
-      <c r="O356" s="7" t="s">
-        <v>2726</v>
       </c>
     </row>
     <row r="358" spans="1:15">
       <c r="A358" s="7" t="s">
         <v>2194</v>
       </c>
-      <c r="B358" s="7" t="s">
-        <v>2194</v>
-      </c>
       <c r="O358" s="7" t="s">
-        <v>2195</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="359" spans="1:15">
       <c r="A359" s="7" t="s">
+        <v>2195</v>
+      </c>
+      <c r="O359" s="7" t="s">
         <v>2196</v>
       </c>
-      <c r="O359" s="7" t="s">
-        <v>2727</v>
-      </c>
-    </row>
-    <row r="360" spans="1:15">
-      <c r="A360" s="7" t="s">
+    </row>
+    <row r="361" spans="1:15">
+      <c r="A361" s="7" t="s">
         <v>2197</v>
       </c>
-      <c r="O360" s="7" t="s">
+      <c r="B361" s="7" t="s">
+        <v>2197</v>
+      </c>
+      <c r="O361" s="7" t="s">
         <v>2198</v>
       </c>
     </row>
@@ -27406,9 +27413,6 @@
       <c r="A362" s="7" t="s">
         <v>2199</v>
       </c>
-      <c r="B362" s="7" t="s">
-        <v>2199</v>
-      </c>
       <c r="O362" s="7" t="s">
         <v>2200</v>
       </c>
@@ -27418,24 +27422,24 @@
         <v>2201</v>
       </c>
       <c r="O363" s="7" t="s">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="365" spans="1:15">
+      <c r="A365" s="7" t="s">
         <v>2202</v>
       </c>
-    </row>
-    <row r="364" spans="1:15">
-      <c r="A364" s="7" t="s">
+      <c r="B365" s="7" t="s">
+        <v>2202</v>
+      </c>
+      <c r="O365" s="7" t="s">
         <v>2203</v>
-      </c>
-      <c r="O364" s="7" t="s">
-        <v>2202</v>
       </c>
     </row>
     <row r="366" spans="1:15">
       <c r="A366" s="7" t="s">
         <v>2204</v>
       </c>
-      <c r="B366" s="7" t="s">
-        <v>2204</v>
-      </c>
       <c r="O366" s="7" t="s">
         <v>2205</v>
       </c>
@@ -27445,41 +27449,44 @@
         <v>2206</v>
       </c>
       <c r="O367" s="7" t="s">
+        <v>2726</v>
+      </c>
+    </row>
+    <row r="369" spans="1:15">
+      <c r="A369" s="7" t="s">
         <v>2207</v>
       </c>
-    </row>
-    <row r="368" spans="1:15">
-      <c r="A368" s="7" t="s">
+      <c r="B369" s="7" t="s">
+        <v>2207</v>
+      </c>
+      <c r="O369" s="7" t="s">
         <v>2208</v>
-      </c>
-      <c r="O368" s="7" t="s">
-        <v>2728</v>
       </c>
     </row>
     <row r="370" spans="1:15">
       <c r="A370" s="7" t="s">
         <v>2209</v>
       </c>
-      <c r="B370" s="7" t="s">
-        <v>2209</v>
-      </c>
       <c r="O370" s="7" t="s">
-        <v>2210</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="371" spans="1:15">
       <c r="A371" s="7" t="s">
+        <v>2210</v>
+      </c>
+      <c r="O371" s="7" t="s">
         <v>2211</v>
       </c>
-      <c r="O371" s="7" t="s">
-        <v>2729</v>
-      </c>
-    </row>
-    <row r="372" spans="1:15">
-      <c r="A372" s="7" t="s">
+    </row>
+    <row r="373" spans="1:15">
+      <c r="A373" s="7" t="s">
         <v>2212</v>
       </c>
-      <c r="O372" s="7" t="s">
+      <c r="B373" s="7" t="s">
+        <v>2213</v>
+      </c>
+      <c r="O373" s="7" t="s">
         <v>2213</v>
       </c>
     </row>
@@ -27487,9 +27494,6 @@
       <c r="A374" s="7" t="s">
         <v>2214</v>
       </c>
-      <c r="B374" s="7" t="s">
-        <v>2215</v>
-      </c>
       <c r="O374" s="7" t="s">
         <v>2215</v>
       </c>
@@ -27499,51 +27503,51 @@
         <v>2216</v>
       </c>
       <c r="O375" s="7" t="s">
+        <v>2728</v>
+      </c>
+    </row>
+    <row r="377" spans="1:15">
+      <c r="A377" s="7" t="s">
         <v>2217</v>
       </c>
-    </row>
-    <row r="376" spans="1:15">
-      <c r="A376" s="7" t="s">
+      <c r="B377" s="7" t="s">
+        <v>2217</v>
+      </c>
+      <c r="O377" s="7" t="s">
         <v>2218</v>
-      </c>
-      <c r="O376" s="7" t="s">
-        <v>2730</v>
       </c>
     </row>
     <row r="378" spans="1:15">
       <c r="A378" s="7" t="s">
         <v>2219</v>
       </c>
-      <c r="B378" s="7" t="s">
-        <v>2219</v>
-      </c>
       <c r="O378" s="7" t="s">
-        <v>2220</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="379" spans="1:15">
       <c r="A379" s="7" t="s">
+        <v>2220</v>
+      </c>
+      <c r="O379" s="7" t="s">
+        <v>2730</v>
+      </c>
+    </row>
+    <row r="381" spans="1:15">
+      <c r="A381" s="7" t="s">
         <v>2221</v>
       </c>
-      <c r="O379" s="7" t="s">
-        <v>2731</v>
-      </c>
-    </row>
-    <row r="380" spans="1:15">
-      <c r="A380" s="7" t="s">
+      <c r="B381" s="7" t="s">
+        <v>2221</v>
+      </c>
+      <c r="O381" s="7" t="s">
         <v>2222</v>
-      </c>
-      <c r="O380" s="7" t="s">
-        <v>2732</v>
       </c>
     </row>
     <row r="382" spans="1:15">
       <c r="A382" s="7" t="s">
         <v>2223</v>
       </c>
-      <c r="B382" s="7" t="s">
-        <v>2223</v>
-      </c>
       <c r="O382" s="7" t="s">
         <v>2224</v>
       </c>
@@ -27553,41 +27557,44 @@
         <v>2225</v>
       </c>
       <c r="O383" s="7" t="s">
+        <v>2731</v>
+      </c>
+    </row>
+    <row r="385" spans="1:15">
+      <c r="A385" s="7" t="s">
         <v>2226</v>
       </c>
-    </row>
-    <row r="384" spans="1:15">
-      <c r="A384" s="7" t="s">
+      <c r="B385" s="7" t="s">
+        <v>2226</v>
+      </c>
+      <c r="O385" s="7" t="s">
         <v>2227</v>
-      </c>
-      <c r="O384" s="7" t="s">
-        <v>2733</v>
       </c>
     </row>
     <row r="386" spans="1:15">
       <c r="A386" s="7" t="s">
         <v>2228</v>
       </c>
-      <c r="B386" s="7" t="s">
-        <v>2228</v>
-      </c>
       <c r="O386" s="7" t="s">
-        <v>2229</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="387" spans="1:15">
       <c r="A387" s="7" t="s">
+        <v>2229</v>
+      </c>
+      <c r="O387" s="7" t="s">
         <v>2230</v>
       </c>
-      <c r="O387" s="7" t="s">
-        <v>2734</v>
-      </c>
-    </row>
-    <row r="388" spans="1:15">
-      <c r="A388" s="7" t="s">
+    </row>
+    <row r="389" spans="1:15">
+      <c r="A389" s="7" t="s">
         <v>2231</v>
       </c>
-      <c r="O388" s="7" t="s">
+      <c r="B389" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="O389" s="7" t="s">
         <v>2232</v>
       </c>
     </row>
@@ -27595,35 +27602,32 @@
       <c r="A390" s="7" t="s">
         <v>2233</v>
       </c>
-      <c r="B390" s="7" t="s">
-        <v>2233</v>
-      </c>
       <c r="O390" s="7" t="s">
-        <v>2234</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="391" spans="1:15">
       <c r="A391" s="7" t="s">
+        <v>2234</v>
+      </c>
+      <c r="O391" s="7" t="s">
+        <v>2734</v>
+      </c>
+    </row>
+    <row r="393" spans="1:15">
+      <c r="A393" s="7" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B393" s="7" t="s">
+        <v>1820</v>
+      </c>
+      <c r="O393" s="7" t="s">
         <v>2235</v>
-      </c>
-      <c r="O391" s="7" t="s">
-        <v>2735</v>
-      </c>
-    </row>
-    <row r="392" spans="1:15">
-      <c r="A392" s="7" t="s">
-        <v>2236</v>
-      </c>
-      <c r="O392" s="7" t="s">
-        <v>2736</v>
       </c>
     </row>
     <row r="394" spans="1:15">
       <c r="A394" s="7" t="s">
-        <v>1822</v>
-      </c>
-      <c r="B394" s="7" t="s">
-        <v>1822</v>
+        <v>2236</v>
       </c>
       <c r="O394" s="7" t="s">
         <v>2237</v>
@@ -27634,24 +27638,24 @@
         <v>2238</v>
       </c>
       <c r="O395" s="7" t="s">
+        <v>2735</v>
+      </c>
+    </row>
+    <row r="397" spans="1:15">
+      <c r="A397" s="7" t="s">
         <v>2239</v>
       </c>
-    </row>
-    <row r="396" spans="1:15">
-      <c r="A396" s="7" t="s">
+      <c r="B397" s="7" t="s">
+        <v>2239</v>
+      </c>
+      <c r="O397" s="7" t="s">
         <v>2240</v>
-      </c>
-      <c r="O396" s="7" t="s">
-        <v>2737</v>
       </c>
     </row>
     <row r="398" spans="1:15">
       <c r="A398" s="7" t="s">
         <v>2241</v>
       </c>
-      <c r="B398" s="7" t="s">
-        <v>2241</v>
-      </c>
       <c r="O398" s="7" t="s">
         <v>2242</v>
       </c>
@@ -27661,53 +27665,53 @@
         <v>2243</v>
       </c>
       <c r="O399" s="7" t="s">
+        <v>2736</v>
+      </c>
+    </row>
+    <row r="401" spans="1:15">
+      <c r="A401" s="7" t="s">
         <v>2244</v>
       </c>
-    </row>
-    <row r="400" spans="1:15">
-      <c r="A400" s="7" t="s">
+      <c r="B401" s="7" t="s">
+        <v>2244</v>
+      </c>
+      <c r="O401" s="7" t="s">
         <v>2245</v>
-      </c>
-      <c r="O400" s="7" t="s">
-        <v>2738</v>
       </c>
     </row>
     <row r="402" spans="1:15">
       <c r="A402" s="7" t="s">
         <v>2246</v>
       </c>
-      <c r="B402" s="7" t="s">
-        <v>2246</v>
-      </c>
       <c r="O402" s="7" t="s">
-        <v>2247</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="403" spans="1:15">
       <c r="A403" s="7" t="s">
+        <v>2247</v>
+      </c>
+      <c r="O403" s="7" t="s">
+        <v>2738</v>
+      </c>
+    </row>
+    <row r="405" spans="1:15">
+      <c r="A405" s="7" t="s">
         <v>2248</v>
       </c>
-      <c r="O403" s="7" t="s">
-        <v>2739</v>
-      </c>
-    </row>
-    <row r="404" spans="1:15">
-      <c r="A404" s="7" t="s">
-        <v>2249</v>
-      </c>
-      <c r="O404" s="7" t="s">
-        <v>2740</v>
+      <c r="B405" s="7" t="s">
+        <v>2248</v>
+      </c>
+      <c r="O405" s="7" t="s">
+        <v>3179</v>
       </c>
     </row>
     <row r="406" spans="1:15">
       <c r="A406" s="7" t="s">
+        <v>2249</v>
+      </c>
+      <c r="O406" s="7" t="s">
         <v>2250</v>
-      </c>
-      <c r="B406" s="7" t="s">
-        <v>2250</v>
-      </c>
-      <c r="O406" s="7" t="s">
-        <v>3181</v>
       </c>
     </row>
     <row r="407" spans="1:15">
@@ -27718,11 +27722,14 @@
         <v>2252</v>
       </c>
     </row>
-    <row r="408" spans="1:15">
-      <c r="A408" s="7" t="s">
+    <row r="409" spans="1:15">
+      <c r="A409" s="7" t="s">
         <v>2253</v>
       </c>
-      <c r="O408" s="7" t="s">
+      <c r="B409" s="7" t="s">
+        <v>2739</v>
+      </c>
+      <c r="O409" s="7" t="s">
         <v>2254</v>
       </c>
     </row>
@@ -27730,53 +27737,53 @@
       <c r="A410" s="7" t="s">
         <v>2255</v>
       </c>
-      <c r="B410" s="7" t="s">
-        <v>2741</v>
-      </c>
       <c r="O410" s="7" t="s">
-        <v>2256</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="411" spans="1:15">
       <c r="A411" s="7" t="s">
+        <v>2256</v>
+      </c>
+      <c r="O411" s="7" t="s">
+        <v>2740</v>
+      </c>
+    </row>
+    <row r="413" spans="1:15">
+      <c r="A413" s="7" t="s">
         <v>2257</v>
       </c>
-      <c r="O411" s="7" t="s">
-        <v>2742</v>
-      </c>
-    </row>
-    <row r="412" spans="1:15">
-      <c r="A412" s="7" t="s">
+      <c r="B413" s="7" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O413" s="7" t="s">
         <v>2258</v>
-      </c>
-      <c r="O412" s="7" t="s">
-        <v>2742</v>
       </c>
     </row>
     <row r="414" spans="1:15">
       <c r="A414" s="7" t="s">
         <v>2259</v>
       </c>
-      <c r="B414" s="7" t="s">
-        <v>2259</v>
-      </c>
       <c r="O414" s="7" t="s">
-        <v>2260</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="415" spans="1:15">
       <c r="A415" s="7" t="s">
+        <v>2260</v>
+      </c>
+      <c r="O415" s="7" t="s">
         <v>2261</v>
       </c>
-      <c r="O415" s="7" t="s">
-        <v>2743</v>
-      </c>
-    </row>
-    <row r="416" spans="1:15">
-      <c r="A416" s="7" t="s">
+    </row>
+    <row r="417" spans="1:15">
+      <c r="A417" s="7" t="s">
         <v>2262</v>
       </c>
-      <c r="O416" s="7" t="s">
+      <c r="B417" s="7" t="s">
+        <v>2262</v>
+      </c>
+      <c r="O417" s="7" t="s">
         <v>2263</v>
       </c>
     </row>
@@ -27784,9 +27791,6 @@
       <c r="A418" s="7" t="s">
         <v>2264</v>
       </c>
-      <c r="B418" s="7" t="s">
-        <v>2264</v>
-      </c>
       <c r="O418" s="7" t="s">
         <v>2265</v>
       </c>
@@ -27799,147 +27803,139 @@
         <v>2267</v>
       </c>
     </row>
-    <row r="420" spans="1:15">
-      <c r="A420" s="7" t="s">
-        <v>2268</v>
-      </c>
-      <c r="O420" s="7" t="s">
-        <v>2269</v>
+    <row r="421" spans="1:15">
+      <c r="A421" s="7" t="s">
+        <v>2866</v>
+      </c>
+      <c r="B421" s="7" t="s">
+        <v>2866</v>
+      </c>
+      <c r="O421" s="7" t="s">
+        <v>2869</v>
       </c>
     </row>
     <row r="422" spans="1:15">
       <c r="A422" s="7" t="s">
-        <v>2868</v>
-      </c>
-      <c r="B422" s="7" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="O422" s="7" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
     </row>
     <row r="423" spans="1:15">
       <c r="A423" s="7" t="s">
-        <v>2869</v>
+        <v>2868</v>
       </c>
       <c r="O423" s="7" t="s">
-        <v>2872</v>
-      </c>
-    </row>
-    <row r="424" spans="1:15">
-      <c r="A424" s="7" t="s">
         <v>2870</v>
       </c>
-      <c r="O424" s="7" t="s">
-        <v>2872</v>
+    </row>
+    <row r="425" spans="1:15">
+      <c r="A425" s="7" t="s">
+        <v>2876</v>
+      </c>
+      <c r="B425" s="7" t="s">
+        <v>2876</v>
+      </c>
+      <c r="O425" s="7" t="s">
+        <v>2879</v>
       </c>
     </row>
     <row r="426" spans="1:15">
       <c r="A426" s="7" t="s">
-        <v>2878</v>
-      </c>
-      <c r="B426" s="7" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
       <c r="O426" s="7" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="427" spans="1:15">
       <c r="A427" s="7" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
       <c r="O427" s="7" t="s">
-        <v>2882</v>
-      </c>
-    </row>
-    <row r="428" spans="1:15">
-      <c r="A428" s="7" t="s">
         <v>2880</v>
       </c>
-      <c r="O428" s="7" t="s">
-        <v>2882</v>
+    </row>
+    <row r="429" spans="1:15">
+      <c r="A429" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="B429" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="O429" s="7" t="s">
+        <v>2269</v>
       </c>
     </row>
     <row r="430" spans="1:15">
       <c r="A430" s="7" t="s">
         <v>2270</v>
       </c>
-      <c r="B430" s="7" t="s">
-        <v>2270</v>
-      </c>
       <c r="O430" s="7" t="s">
-        <v>2271</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="431" spans="1:15">
       <c r="A431" s="7" t="s">
+        <v>2271</v>
+      </c>
+      <c r="O431" s="7" t="s">
+        <v>2742</v>
+      </c>
+    </row>
+    <row r="433" spans="1:15">
+      <c r="A433" s="7" t="s">
         <v>2272</v>
       </c>
-      <c r="O431" s="7" t="s">
-        <v>2744</v>
-      </c>
-    </row>
-    <row r="432" spans="1:15">
-      <c r="A432" s="7" t="s">
+      <c r="B433" s="7" t="s">
+        <v>2272</v>
+      </c>
+      <c r="O433" s="7" t="s">
         <v>2273</v>
-      </c>
-      <c r="O432" s="7" t="s">
-        <v>2744</v>
       </c>
     </row>
     <row r="434" spans="1:15">
       <c r="A434" s="7" t="s">
         <v>2274</v>
       </c>
-      <c r="B434" s="7" t="s">
-        <v>2274</v>
-      </c>
       <c r="O434" s="7" t="s">
-        <v>2275</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="435" spans="1:15">
       <c r="A435" s="7" t="s">
+        <v>2275</v>
+      </c>
+      <c r="O435" s="7" t="s">
+        <v>2743</v>
+      </c>
+    </row>
+    <row r="437" spans="1:15">
+      <c r="A437" s="7" t="s">
         <v>2276</v>
       </c>
-      <c r="O435" s="7" t="s">
-        <v>2745</v>
-      </c>
-    </row>
-    <row r="436" spans="1:15">
-      <c r="A436" s="7" t="s">
-        <v>2277</v>
-      </c>
-      <c r="O436" s="7" t="s">
-        <v>2745</v>
+      <c r="B437" s="7" t="s">
+        <v>2276</v>
+      </c>
+      <c r="O437" s="7" t="s">
+        <v>2273</v>
       </c>
     </row>
     <row r="438" spans="1:15">
       <c r="A438" s="7" t="s">
-        <v>2278</v>
-      </c>
-      <c r="B438" s="7" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="O438" s="7" t="s">
-        <v>2275</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="439" spans="1:15">
       <c r="A439" s="7" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="O439" s="7" t="s">
-        <v>2746</v>
-      </c>
-    </row>
-    <row r="440" spans="1:15">
-      <c r="A440" s="7" t="s">
-        <v>2280</v>
-      </c>
-      <c r="O440" s="7" t="s">
-        <v>2746</v>
+        <v>2744</v>
       </c>
     </row>
   </sheetData>
@@ -27951,7 +27947,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:Q111"/>
+  <dimension ref="A1:Q112"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="60" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.625" style="8" customWidth="1"/>
@@ -27965,908 +27961,916 @@
   <sheetData>
     <row r="1" spans="1:17" ht="20.100000000000001" customHeight="1">
       <c r="B1" s="9" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>1852</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>1853</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>1854</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>1855</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>1856</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>1857</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>1858</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>1859</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>1860</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>1861</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="N1" s="9" t="s">
         <v>1862</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>1863</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>1864</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="Q1" s="8" t="s">
         <v>1865</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>1866</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>1867</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="60" customHeight="1">
       <c r="A2" s="8" t="s">
-        <v>2316</v>
+        <v>2314</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>2776</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="60" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>3215</v>
+        <v>3211</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="60" customHeight="1">
       <c r="A4" s="8" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>2778</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="60" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>2319</v>
+        <v>2317</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>2779</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="60" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>2320</v>
+        <v>2318</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>2970</v>
+        <v>2968</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="60" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="60" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>2766</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="60" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>2322</v>
+        <v>2320</v>
       </c>
       <c r="O9" s="9" t="s">
-        <v>2312</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="60" customHeight="1">
       <c r="A10" s="8" t="s">
-        <v>2323</v>
+        <v>2321</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>2313</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="60" customHeight="1">
       <c r="A11" s="8" t="s">
-        <v>2324</v>
+        <v>2322</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>2780</v>
+        <v>2778</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="60" customHeight="1">
       <c r="A12" s="8" t="s">
-        <v>2325</v>
+        <v>2323</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>2781</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="60" customHeight="1">
       <c r="A13" s="8" t="s">
-        <v>2326</v>
+        <v>2324</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>2765</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="60" customHeight="1">
       <c r="A14" s="8" t="s">
-        <v>2327</v>
+        <v>2325</v>
       </c>
       <c r="O14" s="9" t="s">
-        <v>2764</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="60" customHeight="1">
       <c r="A15" s="8" t="s">
-        <v>2328</v>
+        <v>2326</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>2782</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="60" customHeight="1">
       <c r="A16" s="8" t="s">
-        <v>2329</v>
+        <v>2327</v>
       </c>
       <c r="O16" s="9" t="s">
-        <v>2783</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="60" customHeight="1">
       <c r="A17" s="8" t="s">
-        <v>2330</v>
+        <v>2328</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>2784</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="60" customHeight="1">
       <c r="A18" s="8" t="s">
-        <v>2331</v>
+        <v>2329</v>
       </c>
       <c r="O18" s="9" t="s">
-        <v>2785</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="60" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>2326</v>
+        <v>2324</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>2786</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="60" customHeight="1">
       <c r="A20" s="8" t="s">
-        <v>2332</v>
+        <v>2330</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>2787</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="60" customHeight="1">
       <c r="A21" s="8" t="s">
-        <v>2333</v>
+        <v>2331</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>2314</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="60" customHeight="1">
       <c r="A22" s="8" t="s">
-        <v>2334</v>
+        <v>2332</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>2915</v>
+        <v>2913</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="60" customHeight="1">
       <c r="A23" s="8" t="s">
-        <v>2335</v>
+        <v>2333</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>2788</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="60" customHeight="1">
       <c r="A24" s="8" t="s">
-        <v>2336</v>
+        <v>2334</v>
       </c>
       <c r="O24" s="9" t="s">
-        <v>2789</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="60" customHeight="1">
       <c r="A25" s="8" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>2790</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="60" customHeight="1">
       <c r="A26" s="8" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="O26" s="9" t="s">
-        <v>2791</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="60" customHeight="1">
       <c r="A27" s="8" t="s">
-        <v>3079</v>
+        <v>3077</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>3080</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="60" customHeight="1">
       <c r="A29" s="8" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>2792</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="60" customHeight="1">
       <c r="A30" s="8" t="s">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="O30" s="9" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="60" customHeight="1">
       <c r="A31" s="8" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>2793</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="60" customHeight="1">
       <c r="A32" s="8" t="s">
-        <v>2337</v>
+        <v>2335</v>
       </c>
       <c r="O32" s="9" t="s">
-        <v>2794</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="60" customHeight="1">
       <c r="A33" s="8" t="s">
-        <v>2338</v>
+        <v>2336</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>2315</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="60" customHeight="1">
       <c r="A34" s="8" t="s">
-        <v>2339</v>
+        <v>2337</v>
       </c>
       <c r="O34" s="9" t="s">
-        <v>2795</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="60" customHeight="1">
       <c r="A35" s="8" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>2796</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="60" customHeight="1">
       <c r="A36" s="8" t="s">
-        <v>2341</v>
+        <v>2339</v>
       </c>
       <c r="O36" s="9" t="s">
-        <v>2797</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="60" customHeight="1">
       <c r="A37" s="8" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>2798</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="60" customHeight="1">
       <c r="A38" s="8" t="s">
-        <v>2343</v>
+        <v>2341</v>
       </c>
       <c r="O38" s="9" t="s">
-        <v>2799</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="60" customHeight="1">
       <c r="A39" s="8" t="s">
-        <v>2344</v>
+        <v>2342</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>2800</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="60" customHeight="1">
       <c r="A40" s="8" t="s">
-        <v>2345</v>
+        <v>2343</v>
       </c>
       <c r="O40" s="9" t="s">
-        <v>2801</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="60" customHeight="1">
       <c r="A41" s="8" t="s">
-        <v>2346</v>
+        <v>2344</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>2802</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="60" customHeight="1">
       <c r="A42" s="8" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="O42" s="9" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="60" customHeight="1">
       <c r="A43" s="8" t="s">
-        <v>2348</v>
+        <v>2346</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>2803</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="60" customHeight="1">
       <c r="A44" s="8" t="s">
-        <v>2349</v>
+        <v>2347</v>
       </c>
       <c r="O44" s="9" t="s">
-        <v>2804</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="60" customHeight="1">
       <c r="A45" s="8" t="s">
-        <v>2350</v>
+        <v>2348</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>2805</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="60" customHeight="1">
       <c r="A46" s="8" t="s">
-        <v>3000</v>
+        <v>2998</v>
       </c>
       <c r="O46" s="9" t="s">
-        <v>3023</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="60" customHeight="1">
       <c r="A47" s="8" t="s">
-        <v>2351</v>
+        <v>2349</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>2806</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="60" customHeight="1">
       <c r="A48" s="8" t="s">
-        <v>2352</v>
+        <v>2350</v>
       </c>
       <c r="O48" s="9" t="s">
-        <v>2807</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="60" customHeight="1">
       <c r="A49" s="8" t="s">
-        <v>2905</v>
+        <v>2903</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>2913</v>
+        <v>2911</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="132.75" customHeight="1">
       <c r="A50" s="8" t="s">
-        <v>3212</v>
+        <v>3208</v>
       </c>
       <c r="O50" s="9" t="s">
-        <v>3220</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" ht="60" customHeight="1">
-      <c r="A52" s="8" t="s">
-        <v>2353</v>
-      </c>
-      <c r="O52" s="9" t="s">
-        <v>2808</v>
+        <v>3232</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="60" customHeight="1">
+      <c r="A51" s="8" t="s">
+        <v>3230</v>
+      </c>
+      <c r="O51" s="9" t="s">
+        <v>3231</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="60" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>2354</v>
+        <v>2351</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>2809</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="60" customHeight="1">
       <c r="A54" s="8" t="s">
-        <v>2355</v>
+        <v>2352</v>
       </c>
       <c r="O54" s="9" t="s">
-        <v>2763</v>
+        <v>2807</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="60" customHeight="1">
       <c r="A55" s="8" t="s">
-        <v>2356</v>
+        <v>2353</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>2810</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="60" customHeight="1">
       <c r="A56" s="8" t="s">
-        <v>2357</v>
+        <v>2354</v>
       </c>
       <c r="O56" s="9" t="s">
-        <v>2811</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="60" customHeight="1">
       <c r="A57" s="8" t="s">
-        <v>2358</v>
+        <v>2355</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>2762</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="60" customHeight="1">
       <c r="A58" s="8" t="s">
-        <v>2359</v>
+        <v>2356</v>
       </c>
       <c r="O58" s="9" t="s">
-        <v>2812</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="60" customHeight="1">
       <c r="A59" s="8" t="s">
-        <v>2360</v>
+        <v>2357</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>2813</v>
+        <v>2810</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="60" customHeight="1">
       <c r="A60" s="8" t="s">
-        <v>2361</v>
+        <v>2358</v>
       </c>
       <c r="O60" s="9" t="s">
-        <v>2814</v>
+        <v>2811</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="60" customHeight="1">
       <c r="A61" s="8" t="s">
-        <v>2362</v>
+        <v>2359</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>2815</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="60" customHeight="1">
       <c r="A62" s="8" t="s">
-        <v>2363</v>
+        <v>2360</v>
       </c>
       <c r="O62" s="9" t="s">
-        <v>2816</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="60" customHeight="1">
       <c r="A63" s="8" t="s">
-        <v>2364</v>
+        <v>2361</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>2817</v>
+        <v>2814</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="60" customHeight="1">
       <c r="A64" s="8" t="s">
-        <v>2365</v>
+        <v>2362</v>
       </c>
       <c r="O64" s="9" t="s">
-        <v>2818</v>
+        <v>2815</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="60" customHeight="1">
       <c r="A65" s="8" t="s">
-        <v>2853</v>
+        <v>2363</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>2819</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="60" customHeight="1">
       <c r="A66" s="8" t="s">
-        <v>2366</v>
+        <v>2851</v>
       </c>
       <c r="O66" s="9" t="s">
-        <v>2820</v>
+        <v>2817</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="60" customHeight="1">
       <c r="A67" s="8" t="s">
-        <v>2367</v>
+        <v>2364</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>2858</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="60" customHeight="1">
       <c r="A68" s="8" t="s">
-        <v>2368</v>
+        <v>2365</v>
       </c>
       <c r="O68" s="9" t="s">
-        <v>2821</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="60" customHeight="1">
       <c r="A69" s="8" t="s">
-        <v>2369</v>
+        <v>2366</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>2822</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="60" customHeight="1">
       <c r="A70" s="8" t="s">
-        <v>2370</v>
+        <v>2367</v>
       </c>
       <c r="O70" s="9" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="60" customHeight="1">
       <c r="A71" s="8" t="s">
-        <v>2371</v>
+        <v>2368</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>2824</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="60" customHeight="1">
       <c r="A72" s="8" t="s">
-        <v>2372</v>
+        <v>2369</v>
       </c>
       <c r="O72" s="9" t="s">
-        <v>1713</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="60" customHeight="1">
       <c r="A73" s="8" t="s">
-        <v>2373</v>
+        <v>2370</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>2825</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="60" customHeight="1">
       <c r="A74" s="8" t="s">
-        <v>2374</v>
+        <v>2371</v>
       </c>
       <c r="O74" s="9" t="s">
-        <v>2826</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="60" customHeight="1">
       <c r="A75" s="8" t="s">
-        <v>2375</v>
+        <v>2372</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>2827</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="60" customHeight="1">
       <c r="A76" s="8" t="s">
-        <v>2376</v>
+        <v>2373</v>
       </c>
       <c r="O76" s="9" t="s">
-        <v>2828</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="60" customHeight="1">
       <c r="A77" s="8" t="s">
-        <v>1845</v>
+        <v>2374</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>2862</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="60" customHeight="1">
       <c r="A78" s="8" t="s">
-        <v>2558</v>
+        <v>1843</v>
       </c>
       <c r="O78" s="9" t="s">
-        <v>2557</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="60" customHeight="1">
       <c r="A79" s="8" t="s">
-        <v>3082</v>
+        <v>2556</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>3083</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" ht="60" customHeight="1">
-      <c r="A81" s="8" t="s">
-        <v>2377</v>
-      </c>
-      <c r="O81" s="9" t="s">
-        <v>2829</v>
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" ht="60" customHeight="1">
+      <c r="A80" s="8" t="s">
+        <v>3080</v>
+      </c>
+      <c r="O80" s="9" t="s">
+        <v>3081</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="60" customHeight="1">
       <c r="A82" s="8" t="s">
-        <v>2317</v>
+        <v>2375</v>
       </c>
       <c r="O82" s="9" t="s">
-        <v>2777</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="83" spans="1:15" ht="60" customHeight="1">
       <c r="A83" s="8" t="s">
-        <v>2378</v>
+        <v>2315</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>2774</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="60" customHeight="1">
       <c r="A84" s="8" t="s">
-        <v>2379</v>
+        <v>2376</v>
       </c>
       <c r="O84" s="9" t="s">
-        <v>2830</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="85" spans="1:15" ht="60" customHeight="1">
       <c r="A85" s="8" t="s">
-        <v>2380</v>
+        <v>2377</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>2831</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="86" spans="1:15" ht="60" customHeight="1">
       <c r="A86" s="8" t="s">
-        <v>2980</v>
+        <v>2378</v>
       </c>
       <c r="O86" s="9" t="s">
-        <v>3024</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="87" spans="1:15" ht="60" customHeight="1">
       <c r="A87" s="8" t="s">
-        <v>2381</v>
+        <v>2978</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>2832</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="60" customHeight="1">
       <c r="A88" s="8" t="s">
-        <v>2382</v>
+        <v>2379</v>
       </c>
       <c r="O88" s="9" t="s">
-        <v>2833</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="60" customHeight="1">
       <c r="A89" s="8" t="s">
-        <v>2383</v>
+        <v>2380</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>2834</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="90" spans="1:15" ht="60" customHeight="1">
       <c r="A90" s="8" t="s">
-        <v>2384</v>
+        <v>2381</v>
       </c>
       <c r="O90" s="9" t="s">
-        <v>2835</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="60" customHeight="1">
       <c r="A91" s="8" t="s">
-        <v>2385</v>
+        <v>2382</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>2836</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="92" spans="1:15" ht="60" customHeight="1">
       <c r="A92" s="8" t="s">
-        <v>2386</v>
+        <v>2383</v>
       </c>
       <c r="O92" s="9" t="s">
-        <v>2837</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="93" spans="1:15" ht="60" customHeight="1">
       <c r="A93" s="8" t="s">
-        <v>2387</v>
+        <v>2384</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>2838</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="94" spans="1:15" ht="60" customHeight="1">
       <c r="A94" s="8" t="s">
-        <v>2388</v>
+        <v>2385</v>
       </c>
       <c r="O94" s="9" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="95" spans="1:15" ht="60" customHeight="1">
       <c r="A95" s="8" t="s">
-        <v>2389</v>
+        <v>2386</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>2840</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="96" spans="1:15" ht="60" customHeight="1">
       <c r="A96" s="8" t="s">
-        <v>2390</v>
+        <v>2387</v>
       </c>
       <c r="O96" s="9" t="s">
-        <v>2775</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="97" spans="1:15" ht="60" customHeight="1">
       <c r="A97" s="8" t="s">
-        <v>2391</v>
+        <v>2388</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>2841</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="98" spans="1:15" ht="60" customHeight="1">
       <c r="A98" s="8" t="s">
-        <v>2392</v>
+        <v>2389</v>
       </c>
       <c r="O98" s="9" t="s">
-        <v>2842</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="99" spans="1:15" ht="60" customHeight="1">
       <c r="A99" s="8" t="s">
-        <v>2393</v>
+        <v>2390</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>2843</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="100" spans="1:15" ht="60" customHeight="1">
       <c r="A100" s="8" t="s">
-        <v>2394</v>
+        <v>2391</v>
       </c>
       <c r="O100" s="9" t="s">
-        <v>2844</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="101" spans="1:15" ht="60" customHeight="1">
       <c r="A101" s="8" t="s">
-        <v>2395</v>
+        <v>2392</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>2845</v>
+        <v>2842</v>
       </c>
     </row>
     <row r="102" spans="1:15" ht="60" customHeight="1">
       <c r="A102" s="8" t="s">
-        <v>2396</v>
+        <v>2393</v>
       </c>
       <c r="O102" s="9" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="103" spans="1:15" ht="60" customHeight="1">
       <c r="A103" s="8" t="s">
-        <v>2397</v>
+        <v>2394</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>2847</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="104" spans="1:15" ht="60" customHeight="1">
       <c r="A104" s="8" t="s">
-        <v>2398</v>
+        <v>2395</v>
       </c>
       <c r="O104" s="9" t="s">
-        <v>2848</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="105" spans="1:15" ht="60" customHeight="1">
       <c r="A105" s="8" t="s">
-        <v>2399</v>
+        <v>2396</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>2849</v>
+        <v>2846</v>
       </c>
     </row>
     <row r="106" spans="1:15" ht="60" customHeight="1">
       <c r="A106" s="8" t="s">
-        <v>2400</v>
+        <v>2397</v>
       </c>
       <c r="O106" s="9" t="s">
-        <v>2850</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="107" spans="1:15" ht="60" customHeight="1">
       <c r="A107" s="8" t="s">
-        <v>2401</v>
+        <v>2398</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>2851</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="108" spans="1:15" ht="60" customHeight="1">
       <c r="A108" s="8" t="s">
-        <v>2402</v>
+        <v>2399</v>
       </c>
       <c r="O108" s="9" t="s">
-        <v>2852</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="109" spans="1:15" ht="60" customHeight="1">
       <c r="A109" s="8" t="s">
-        <v>2403</v>
+        <v>2400</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>2854</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="110" spans="1:15" ht="60" customHeight="1">
       <c r="A110" s="8" t="s">
-        <v>2873</v>
+        <v>2401</v>
       </c>
       <c r="O110" s="9" t="s">
-        <v>2874</v>
+        <v>2852</v>
       </c>
     </row>
     <row r="111" spans="1:15" ht="60" customHeight="1">
       <c r="A111" s="8" t="s">
-        <v>2883</v>
+        <v>2871</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>2898</v>
+        <v>2872</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" ht="60" customHeight="1">
+      <c r="A112" s="8" t="s">
+        <v>2881</v>
+      </c>
+      <c r="O112" s="9" t="s">
+        <v>2896</v>
       </c>
     </row>
   </sheetData>

--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Among Us code\TheOtherUs\TheOtherUs-Edited-Lite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830F0ABE-4B9F-4CE7-8B98-00975C740F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E9EE5B-DBF8-494A-A3EE-683FC2D092D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="1200" windowWidth="25755" windowHeight="14910" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="720" yWindow="1200" windowWidth="25755" windowHeight="14910" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Options" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Role Description" sheetId="11" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Options!$O$1:$O$1456</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Options!$O$1:$O$1457</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3556" uniqueCount="3235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3558" uniqueCount="3237">
   <si>
     <t>English</t>
   </si>
@@ -11526,6 +11526,14 @@
   </si>
   <si>
     <t xml:space="preserve"> (隐身)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnknownTeam</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>未知阵营</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -12125,7 +12133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1753"/>
+  <dimension ref="A1:Q1754"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40.375" style="2" customWidth="1"/>
@@ -12688,6516 +12696,6522 @@
       </c>
     </row>
     <row r="51" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A51" s="3"/>
+      <c r="A51" s="3" t="s">
+        <v>3235</v>
+      </c>
       <c r="B51" s="3"/>
+      <c r="O51" s="3" t="s">
+        <v>3236</v>
+      </c>
     </row>
     <row r="52" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+    </row>
+    <row r="53" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A53" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B53" s="3" t="s">
         <v>2752</v>
       </c>
-      <c r="O52" s="3" t="s">
+      <c r="O53" s="3" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A53" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="O53" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="24.95" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>66</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="24.95" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>2544</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>2545</v>
+        <v>66</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>2551</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="24.95" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>2557</v>
+        <v>2544</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>2558</v>
-      </c>
-      <c r="C56" s="3"/>
+        <v>2545</v>
+      </c>
       <c r="O56" s="3" t="s">
-        <v>2559</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="24.95" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>3026</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>3026</v>
-      </c>
-      <c r="O57" s="2" t="s">
-        <v>1150</v>
+        <v>2557</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>2558</v>
+      </c>
+      <c r="C57" s="3"/>
+      <c r="O57" s="3" t="s">
+        <v>2559</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="24.95" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>3049</v>
+        <v>3026</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>3026</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>3046</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="24.95" customHeight="1">
       <c r="A59" s="2" t="s">
+        <v>3049</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>3046</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A60" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B60" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="O59" s="2" t="s">
+      <c r="O60" s="2" t="s">
         <v>1154</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A60" s="3"/>
-    </row>
     <row r="61" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A61" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="M61" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="O61" s="2" t="s">
-        <v>72</v>
-      </c>
+      <c r="A61" s="3"/>
     </row>
     <row r="62" spans="1:15" ht="24.95" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>1670</v>
+        <v>70</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="24.95" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="24.95" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>79</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="24.95" customHeight="1">
       <c r="A65" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A66" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B66" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="O65" s="3" t="s">
+      <c r="O66" s="3" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A66" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="24.95" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>1672</v>
+        <v>85</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="24.95" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="O68" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>1672</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="24.95" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="24.95" customHeight="1">
       <c r="A70" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="O70" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A71" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B71" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="O70" s="2" t="s">
+      <c r="O71" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O73" s="2"/>
-    </row>
     <row r="74" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A74" s="2" t="s">
-        <v>1841</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>1841</v>
-      </c>
-      <c r="O74" s="2" t="s">
-        <v>1842</v>
-      </c>
+      <c r="O74" s="2"/>
     </row>
     <row r="75" spans="1:15" ht="24.95" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>2857</v>
+        <v>1841</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>2859</v>
+        <v>1841</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>2858</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="24.95" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>109</v>
+        <v>2857</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>110</v>
+        <v>2859</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>111</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="24.95" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="24.95" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>3041</v>
+        <v>112</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>3044</v>
+        <v>114</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="24.95" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>3043</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="24.95" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>117</v>
+        <v>3042</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>118</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="81" spans="1:15" ht="24.95" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="24.95" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="83" spans="1:15" ht="24.95" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="24.95" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="85" spans="1:15" ht="24.95" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="86" spans="1:15" ht="24.95" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="87" spans="1:15" ht="24.95" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="24.95" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="24.95" customHeight="1">
       <c r="A89" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="90" spans="1:15" ht="24.95" customHeight="1">
       <c r="A90" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="O90" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A91" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B91" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="O90" s="2" t="s">
+      <c r="O91" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="91" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O91" s="2"/>
-    </row>
     <row r="92" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A92" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="O92" s="2" t="s">
-        <v>151</v>
-      </c>
+      <c r="O92" s="2"/>
     </row>
     <row r="93" spans="1:15" ht="24.95" customHeight="1">
       <c r="A93" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="94" spans="1:15" ht="24.95" customHeight="1">
       <c r="A94" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="95" spans="1:15" ht="24.95" customHeight="1">
       <c r="A95" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="96" spans="1:15" ht="24.95" customHeight="1">
       <c r="A96" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="97" spans="1:15" ht="24.95" customHeight="1">
       <c r="A97" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="98" spans="1:15" ht="24.95" customHeight="1">
       <c r="A98" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="99" spans="1:15" ht="24.95" customHeight="1">
       <c r="A99" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>2519</v>
+        <v>168</v>
       </c>
       <c r="O99" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="100" spans="1:15" ht="24.95" customHeight="1">
       <c r="A100" s="2" t="s">
-        <v>2515</v>
+        <v>170</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>2756</v>
+        <v>171</v>
       </c>
     </row>
     <row r="101" spans="1:15" ht="24.95" customHeight="1">
       <c r="A101" s="2" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="102" spans="1:15" ht="24.95" customHeight="1">
       <c r="A102" s="2" t="s">
-        <v>172</v>
+        <v>2516</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>173</v>
+        <v>2517</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>174</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="103" spans="1:15" ht="24.95" customHeight="1">
       <c r="A103" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="104" spans="1:15" ht="24.95" customHeight="1">
       <c r="A104" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="105" spans="1:15" ht="24.95" customHeight="1">
       <c r="A105" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="O105" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A106" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="B106" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="O105" s="2" t="s">
+      <c r="O106" s="2" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="106" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O106" s="2"/>
-    </row>
     <row r="107" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A107" s="2" t="s">
-        <v>3123</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>3124</v>
-      </c>
-      <c r="O107" s="2" t="s">
-        <v>3129</v>
-      </c>
+      <c r="O107" s="2"/>
     </row>
     <row r="108" spans="1:15" ht="24.95" customHeight="1">
       <c r="A108" s="2" t="s">
-        <v>3139</v>
+        <v>3123</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>3122</v>
+        <v>3124</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
     </row>
     <row r="109" spans="1:15" ht="24.95" customHeight="1">
       <c r="A109" s="2" t="s">
-        <v>3138</v>
+        <v>3139</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>3125</v>
+        <v>3122</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="110" spans="1:15" ht="24.95" customHeight="1">
       <c r="A110" s="2" t="s">
-        <v>3137</v>
+        <v>3138</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="111" spans="1:15" ht="24.95" customHeight="1">
       <c r="A111" s="2" t="s">
-        <v>3136</v>
+        <v>3137</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>3134</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="112" spans="1:15" ht="24.95" customHeight="1">
       <c r="A112" s="2" t="s">
-        <v>3135</v>
+        <v>3136</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
       <c r="O112" s="2" t="s">
-        <v>3133</v>
+        <v>3134</v>
       </c>
     </row>
     <row r="113" spans="1:15" ht="24.95" customHeight="1">
       <c r="A113" s="2" t="s">
+        <v>3135</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>3128</v>
+      </c>
+      <c r="O113" s="2" t="s">
+        <v>3133</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A114" s="2" t="s">
         <v>3156</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="B114" s="2" t="s">
         <v>3157</v>
       </c>
-      <c r="O113" s="2" t="s">
+      <c r="O114" s="2" t="s">
         <v>3158</v>
       </c>
     </row>
-    <row r="114" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O114" s="2"/>
-    </row>
     <row r="115" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A115" s="2" t="s">
-        <v>3031</v>
-      </c>
-      <c r="O115" s="2" t="s">
-        <v>3036</v>
-      </c>
+      <c r="O115" s="2"/>
     </row>
     <row r="116" spans="1:15" ht="24.95" customHeight="1">
       <c r="A116" s="2" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="O116" s="2" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
     </row>
     <row r="117" spans="1:15" ht="24.95" customHeight="1">
       <c r="A117" s="2" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="O117" s="2" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="118" spans="1:15" ht="24.95" customHeight="1">
       <c r="A118" s="2" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="O118" s="2" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="119" spans="1:15" ht="24.95" customHeight="1">
       <c r="A119" s="2" t="s">
+        <v>3034</v>
+      </c>
+      <c r="O119" s="2" t="s">
+        <v>3039</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A120" s="2" t="s">
         <v>3035</v>
       </c>
-      <c r="O119" s="2" t="s">
+      <c r="O120" s="2" t="s">
         <v>3040</v>
       </c>
     </row>
-    <row r="120" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O120" s="2"/>
-    </row>
     <row r="121" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A121" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="O121" s="2" t="s">
-        <v>186</v>
-      </c>
+      <c r="O121" s="2"/>
     </row>
     <row r="122" spans="1:15" ht="24.95" customHeight="1">
       <c r="A122" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O122" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="123" spans="1:15" ht="24.95" customHeight="1">
       <c r="A123" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="O123" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="124" spans="1:15" ht="24.95" customHeight="1">
       <c r="A124" s="2" t="s">
-        <v>3016</v>
+        <v>190</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>3017</v>
+        <v>191</v>
       </c>
       <c r="O124" s="2" t="s">
-        <v>3018</v>
+        <v>192</v>
       </c>
     </row>
     <row r="125" spans="1:15" ht="24.95" customHeight="1">
       <c r="A125" s="2" t="s">
-        <v>193</v>
+        <v>3016</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>194</v>
+        <v>3017</v>
       </c>
       <c r="O125" s="2" t="s">
-        <v>195</v>
+        <v>3018</v>
       </c>
     </row>
     <row r="126" spans="1:15" ht="24.95" customHeight="1">
       <c r="A126" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O126" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="127" spans="1:15" ht="24.95" customHeight="1">
       <c r="A127" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="O127" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="128" spans="1:15" ht="24.95" customHeight="1">
       <c r="A128" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="O128" s="2" t="s">
-        <v>2421</v>
+        <v>201</v>
       </c>
     </row>
     <row r="129" spans="1:15" ht="24.95" customHeight="1">
       <c r="A129" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="O129" s="2" t="s">
-        <v>206</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="130" spans="1:15" ht="24.95" customHeight="1">
       <c r="A130" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="O130" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="131" spans="1:15" ht="24.95" customHeight="1">
       <c r="A131" s="2" t="s">
-        <v>2456</v>
+        <v>207</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O131" s="2" t="s">
-        <v>2461</v>
+        <v>209</v>
       </c>
     </row>
     <row r="132" spans="1:15" ht="24.95" customHeight="1">
       <c r="A132" s="2" t="s">
-        <v>211</v>
+        <v>2456</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="O132" s="2" t="s">
-        <v>213</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="133" spans="1:15" ht="24.95" customHeight="1">
       <c r="A133" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O133" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="134" spans="1:15" ht="24.95" customHeight="1">
       <c r="A134" s="2" t="s">
-        <v>2566</v>
+        <v>214</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>215</v>
       </c>
       <c r="O134" s="2" t="s">
-        <v>2567</v>
+        <v>216</v>
       </c>
     </row>
     <row r="135" spans="1:15" ht="24.95" customHeight="1">
       <c r="A135" s="2" t="s">
-        <v>1783</v>
-      </c>
-      <c r="O135" s="3" t="s">
-        <v>2552</v>
+        <v>2566</v>
+      </c>
+      <c r="O135" s="2" t="s">
+        <v>2567</v>
       </c>
     </row>
     <row r="136" spans="1:15" ht="24.95" customHeight="1">
       <c r="A136" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="O136" s="2" t="s">
-        <v>219</v>
+        <v>1783</v>
+      </c>
+      <c r="O136" s="3" t="s">
+        <v>2552</v>
       </c>
     </row>
     <row r="137" spans="1:15" ht="24.95" customHeight="1">
       <c r="A137" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="O137" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="138" spans="1:15" ht="24.95" customHeight="1">
       <c r="A138" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="O138" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="139" spans="1:15" ht="24.95" customHeight="1">
       <c r="A139" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O139" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="140" spans="1:15" ht="24.95" customHeight="1">
       <c r="A140" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O140" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="141" spans="1:15" ht="24.95" customHeight="1">
       <c r="A141" s="2" t="s">
-        <v>2506</v>
+        <v>229</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="O141" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="142" spans="1:15" ht="24.95" customHeight="1">
       <c r="A142" s="2" t="s">
+        <v>2506</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="O142" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A143" s="2" t="s">
         <v>2540</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="B143" s="2" t="s">
         <v>2541</v>
       </c>
-      <c r="O142" s="2" t="s">
+      <c r="O143" s="2" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="143" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O143" s="2"/>
-    </row>
     <row r="144" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A144" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="O144" s="2" t="s">
-        <v>237</v>
-      </c>
+      <c r="O144" s="2"/>
     </row>
     <row r="145" spans="1:15" ht="24.95" customHeight="1">
       <c r="A145" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="O145" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="146" spans="1:15" ht="24.95" customHeight="1">
       <c r="A146" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="O146" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="147" spans="1:15" ht="24.95" customHeight="1">
       <c r="A147" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="O147" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
+      </c>
+      <c r="O147" s="2" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="148" spans="1:15" ht="24.95" customHeight="1">
       <c r="A148" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1747</v>
+        <v>245</v>
       </c>
       <c r="O148" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="149" spans="1:15" ht="24.95" customHeight="1">
       <c r="A149" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1749</v>
-      </c>
-      <c r="O149" s="2" t="s">
-        <v>250</v>
+        <v>1747</v>
+      </c>
+      <c r="O149" s="3" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="150" spans="1:15" ht="24.95" customHeight="1">
       <c r="A150" s="2" t="s">
-        <v>1748</v>
+        <v>249</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="O150" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="151" spans="1:15" ht="24.95" customHeight="1">
       <c r="A151" s="2" t="s">
-        <v>251</v>
+        <v>1748</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="O151" s="2" t="s">
-        <v>1750</v>
+        <v>252</v>
       </c>
     </row>
     <row r="152" spans="1:15" ht="24.95" customHeight="1">
       <c r="A152" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1755</v>
+        <v>1752</v>
       </c>
       <c r="O152" s="2" t="s">
-        <v>254</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="153" spans="1:15" ht="24.95" customHeight="1">
       <c r="A153" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="O153" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="154" spans="1:15" ht="24.95" customHeight="1">
       <c r="A154" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="O154" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="155" spans="1:15" ht="24.95" customHeight="1">
       <c r="A155" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>1754</v>
+        <v>1757</v>
       </c>
       <c r="O155" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="156" spans="1:15" ht="24.95" customHeight="1">
       <c r="A156" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>1754</v>
+      </c>
+      <c r="O156" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A157" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B156" s="2" t="s">
+      <c r="B157" s="2" t="s">
         <v>1753</v>
       </c>
-      <c r="O156" s="2" t="s">
+      <c r="O157" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="157" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O157" s="2"/>
-    </row>
     <row r="158" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A158" s="2" t="s">
-        <v>2914</v>
-      </c>
-      <c r="O158" s="2" t="s">
-        <v>2916</v>
-      </c>
+      <c r="O158" s="2"/>
     </row>
     <row r="159" spans="1:15" ht="24.95" customHeight="1">
       <c r="A159" s="2" t="s">
+        <v>2914</v>
+      </c>
+      <c r="O159" s="2" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A160" s="2" t="s">
         <v>2915</v>
       </c>
-      <c r="O159" s="2" t="s">
+      <c r="O160" s="2" t="s">
         <v>2917</v>
       </c>
     </row>
-    <row r="160" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O160" s="2"/>
-    </row>
     <row r="161" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A161" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="O161" s="2" t="s">
-        <v>264</v>
-      </c>
+      <c r="O161" s="2"/>
     </row>
     <row r="162" spans="1:15" ht="24.95" customHeight="1">
       <c r="A162" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="O162" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="163" spans="1:15" ht="24.95" customHeight="1">
       <c r="A163" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="O163" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="164" spans="1:15" ht="24.95" customHeight="1">
       <c r="A164" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O164" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="165" spans="1:15" ht="24.95" customHeight="1">
       <c r="A165" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>1718</v>
+        <v>271</v>
       </c>
       <c r="O165" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="166" spans="1:15" ht="24.95" customHeight="1">
       <c r="A166" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>276</v>
+        <v>1718</v>
       </c>
       <c r="O166" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="167" spans="1:15" ht="24.95" customHeight="1">
       <c r="A167" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="O167" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="168" spans="1:15" ht="24.95" customHeight="1">
       <c r="A168" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="O168" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="169" spans="1:15" ht="24.95" customHeight="1">
       <c r="A169" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="O169" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="170" spans="1:15" ht="24.95" customHeight="1">
       <c r="A170" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>1716</v>
+        <v>285</v>
       </c>
       <c r="O170" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="171" spans="1:15" ht="24.95" customHeight="1">
       <c r="A171" s="2" t="s">
-        <v>1717</v>
+        <v>286</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="O171" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="172" spans="1:15" ht="24.95" customHeight="1">
       <c r="A172" s="2" t="s">
-        <v>289</v>
+        <v>1717</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="O172" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="173" spans="1:15" ht="24.95" customHeight="1">
       <c r="A173" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>292</v>
+        <v>1719</v>
       </c>
       <c r="O173" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="174" spans="1:15" ht="24.95" customHeight="1">
       <c r="A174" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="O174" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A175" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="B174" s="2" t="s">
+      <c r="B175" s="2" t="s">
         <v>1720</v>
       </c>
-      <c r="O174" s="2" t="s">
+      <c r="O175" s="2" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="175" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O175" s="2"/>
-    </row>
     <row r="176" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A176" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="O176" s="2" t="s">
-        <v>297</v>
-      </c>
+      <c r="O176" s="2"/>
     </row>
     <row r="177" spans="1:15" ht="24.95" customHeight="1">
       <c r="A177" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="O177" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A178" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="B177" s="2" t="s">
+      <c r="B178" s="2" t="s">
         <v>2467</v>
       </c>
-      <c r="O177" s="2" t="s">
+      <c r="O178" s="2" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="178" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O178" s="2"/>
-    </row>
     <row r="179" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A179" s="2" t="s">
-        <v>2464</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="O179" s="2" t="s">
-        <v>2463</v>
-      </c>
+      <c r="O179" s="2"/>
     </row>
     <row r="180" spans="1:15" ht="24.95" customHeight="1">
       <c r="A180" s="2" t="s">
-        <v>2564</v>
+        <v>2464</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>2563</v>
+        <v>300</v>
       </c>
       <c r="O180" s="2" t="s">
-        <v>2565</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="181" spans="1:15" ht="24.95" customHeight="1">
       <c r="A181" s="2" t="s">
-        <v>301</v>
+        <v>2564</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>302</v>
+        <v>2563</v>
       </c>
       <c r="O181" s="2" t="s">
-        <v>303</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="182" spans="1:15" ht="24.95" customHeight="1">
       <c r="A182" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="O182" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="183" spans="1:15" ht="24.95" customHeight="1">
       <c r="A183" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O183" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="184" spans="1:15" ht="24.95" customHeight="1">
       <c r="A184" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="O184" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
+      </c>
+      <c r="O184" s="2" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="185" spans="1:15" ht="24.95" customHeight="1">
       <c r="A185" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="O185" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
+      </c>
+      <c r="O185" s="3" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="186" spans="1:15" ht="24.95" customHeight="1">
       <c r="A186" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="O186" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="187" spans="1:15" ht="24.95" customHeight="1">
       <c r="A187" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="O187" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="188" spans="1:15" ht="24.95" customHeight="1">
       <c r="A188" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="O188" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="189" spans="1:15" ht="24.95" customHeight="1">
       <c r="A189" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="O189" s="2" t="s">
-        <v>1758</v>
+        <v>324</v>
       </c>
     </row>
     <row r="190" spans="1:15" ht="24.95" customHeight="1">
       <c r="A190" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="O190" s="2" t="s">
-        <v>329</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="191" spans="1:15" ht="24.95" customHeight="1">
       <c r="A191" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="O191" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A192" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B191" s="2" t="s">
+      <c r="B192" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="O191" s="2" t="s">
+      <c r="O192" s="2" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="192" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O192" s="2"/>
-    </row>
     <row r="193" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A193" s="2" t="s">
-        <v>3023</v>
-      </c>
-      <c r="O193" s="2" t="s">
-        <v>3045</v>
-      </c>
+      <c r="O193" s="2"/>
     </row>
     <row r="194" spans="1:15" ht="24.95" customHeight="1">
       <c r="A194" s="2" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="O194" s="2" t="s">
-        <v>3047</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="195" spans="1:15" ht="24.95" customHeight="1">
       <c r="A195" s="2" t="s">
+        <v>3024</v>
+      </c>
+      <c r="O195" s="2" t="s">
+        <v>3047</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A196" s="2" t="s">
         <v>3025</v>
       </c>
-      <c r="O195" s="2" t="s">
+      <c r="O196" s="2" t="s">
         <v>3048</v>
       </c>
     </row>
-    <row r="196" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O196" s="2"/>
-    </row>
     <row r="197" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A197" s="2" t="s">
-        <v>1798</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>1799</v>
-      </c>
-      <c r="O197" s="2" t="s">
-        <v>1800</v>
-      </c>
+      <c r="O197" s="2"/>
     </row>
     <row r="198" spans="1:15" ht="24.95" customHeight="1">
       <c r="A198" s="2" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>1799</v>
+      </c>
+      <c r="O198" s="2" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A199" s="2" t="s">
         <v>2538</v>
       </c>
-      <c r="B198" s="2" t="s">
+      <c r="B199" s="2" t="s">
         <v>2537</v>
       </c>
-      <c r="O198" s="2" t="s">
+      <c r="O199" s="2" t="s">
         <v>2539</v>
       </c>
     </row>
-    <row r="199" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O199" s="2"/>
-    </row>
     <row r="200" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A200" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>1721</v>
-      </c>
-      <c r="O200" s="2" t="s">
-        <v>334</v>
-      </c>
+      <c r="O200" s="2"/>
     </row>
     <row r="201" spans="1:15" ht="24.95" customHeight="1">
       <c r="A201" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="O201" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="202" spans="1:15" ht="24.95" customHeight="1">
       <c r="A202" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="O202" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="203" spans="1:15" ht="24.95" customHeight="1">
       <c r="A203" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="O203" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="204" spans="1:15" ht="24.95" customHeight="1">
       <c r="A204" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="O204" s="2" t="s">
-        <v>1819</v>
+        <v>340</v>
       </c>
     </row>
     <row r="205" spans="1:15" ht="24.95" customHeight="1">
       <c r="A205" s="2" t="s">
-        <v>1634</v>
+        <v>341</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="O205" s="2" t="s">
-        <v>1635</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="206" spans="1:15" ht="24.95" customHeight="1">
       <c r="A206" s="2" t="s">
-        <v>2302</v>
+        <v>1634</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>2304</v>
+        <v>1727</v>
       </c>
       <c r="O206" s="2" t="s">
-        <v>2303</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="207" spans="1:15" ht="24.95" customHeight="1">
       <c r="A207" s="2" t="s">
-        <v>342</v>
+        <v>2302</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>1726</v>
+        <v>2304</v>
       </c>
       <c r="O207" s="2" t="s">
-        <v>343</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="208" spans="1:15" ht="24.95" customHeight="1">
       <c r="A208" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>1732</v>
+        <v>1726</v>
       </c>
       <c r="O208" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="209" spans="1:15" ht="24.95" customHeight="1">
       <c r="A209" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="O209" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="210" spans="1:15" ht="24.95" customHeight="1">
       <c r="A210" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="O210" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="211" spans="1:15" ht="24.95" customHeight="1">
       <c r="A211" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>530</v>
+        <v>1729</v>
       </c>
       <c r="O211" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="212" spans="1:15" ht="24.95" customHeight="1">
       <c r="A212" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>1730</v>
+        <v>530</v>
       </c>
       <c r="O212" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="213" spans="1:15" ht="24.95" customHeight="1">
       <c r="A213" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="O213" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A214" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B213" s="2" t="s">
+      <c r="B214" s="2" t="s">
         <v>1731</v>
       </c>
-      <c r="O213" s="2" t="s">
+      <c r="O214" s="2" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="214" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O214" s="2"/>
-    </row>
     <row r="215" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A215" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="O215" s="2" t="s">
-        <v>358</v>
-      </c>
+      <c r="O215" s="2"/>
     </row>
     <row r="216" spans="1:15" ht="24.95" customHeight="1">
       <c r="A216" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="O216" s="2" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="217" spans="1:15" ht="24.95" customHeight="1">
       <c r="A217" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="O217" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="218" spans="1:15" ht="24.95" customHeight="1">
       <c r="A218" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="O218" s="2" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="219" spans="1:15" ht="24.95" customHeight="1">
       <c r="A219" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="O219" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="220" spans="1:15" ht="24.95" customHeight="1">
       <c r="A220" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="O220" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="221" spans="1:15" ht="24.95" customHeight="1">
       <c r="A221" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="O221" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="222" spans="1:15" ht="24.95" customHeight="1">
       <c r="A222" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="O222" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="223" spans="1:15" ht="24.95" customHeight="1">
       <c r="A223" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="O223" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="224" spans="1:15" ht="24.95" customHeight="1">
       <c r="A224" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="O224" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="225" spans="1:15" ht="24.95" customHeight="1">
       <c r="A225" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="O225" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="226" spans="1:15" ht="24.95" customHeight="1">
       <c r="A226" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O226" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="227" spans="1:15" ht="24.95" customHeight="1">
       <c r="A227" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="O227" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="228" spans="1:15" ht="24.95" customHeight="1">
       <c r="A228" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="O228" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A229" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="B228" s="2" t="s">
+      <c r="B229" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="O228" s="2" t="s">
+      <c r="O229" s="2" t="s">
         <v>397</v>
-      </c>
-    </row>
-    <row r="230" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A230" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="O230" s="2" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="231" spans="1:15" ht="24.95" customHeight="1">
       <c r="A231" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O231" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="232" spans="1:15" ht="24.95" customHeight="1">
       <c r="A232" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="O232" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="233" spans="1:15" ht="24.95" customHeight="1">
       <c r="A233" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="O233" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="234" spans="1:15" ht="24.95" customHeight="1">
       <c r="A234" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="O234" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="235" spans="1:15" ht="24.95" customHeight="1">
       <c r="A235" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="O235" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="236" spans="1:15" ht="24.95" customHeight="1">
       <c r="A236" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="O236" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="237" spans="1:15" ht="24.95" customHeight="1">
       <c r="A237" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="O237" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="238" spans="1:15" ht="24.95" customHeight="1">
       <c r="A238" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="O238" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="239" spans="1:15" ht="24.95" customHeight="1">
       <c r="A239" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="O239" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="240" spans="1:15" ht="24.95" customHeight="1">
       <c r="A240" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="O240" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A241" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="B240" s="2" t="s">
+      <c r="B241" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="O240" s="2" t="s">
+      <c r="O241" s="2" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="241" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O241" s="2"/>
-    </row>
     <row r="242" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A242" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="O242" s="2" t="s">
-        <v>433</v>
-      </c>
+      <c r="O242" s="2"/>
     </row>
     <row r="243" spans="1:15" ht="24.95" customHeight="1">
       <c r="A243" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="O243" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="244" spans="1:15" ht="24.95" customHeight="1">
       <c r="A244" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="O244" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="245" spans="1:15" ht="24.95" customHeight="1">
       <c r="A245" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="O245" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="246" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A246" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="B245" s="2" t="s">
+      <c r="B246" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="O245" s="2" t="s">
+      <c r="O246" s="2" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="246" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O246" s="2"/>
-    </row>
     <row r="247" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A247" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="O247" s="2" t="s">
-        <v>382</v>
-      </c>
+      <c r="O247" s="2"/>
     </row>
     <row r="248" spans="1:15" ht="24.95" customHeight="1">
       <c r="A248" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>445</v>
+        <v>381</v>
       </c>
       <c r="O248" s="2" t="s">
-        <v>446</v>
+        <v>382</v>
       </c>
     </row>
     <row r="249" spans="1:15" ht="24.95" customHeight="1">
       <c r="A249" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="O249" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="250" spans="1:15" ht="24.95" customHeight="1">
       <c r="A250" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>366</v>
+        <v>448</v>
       </c>
       <c r="O250" s="2" t="s">
-        <v>367</v>
+        <v>449</v>
       </c>
     </row>
     <row r="251" spans="1:15" ht="24.95" customHeight="1">
       <c r="A251" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
       <c r="O251" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="252" spans="1:15" ht="24.95" customHeight="1">
       <c r="A252" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>393</v>
+        <v>452</v>
       </c>
       <c r="O252" s="2" t="s">
-        <v>394</v>
+        <v>370</v>
       </c>
     </row>
     <row r="253" spans="1:15" ht="24.95" customHeight="1">
       <c r="A253" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="O253" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="254" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A254" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="B253" s="2" t="s">
+      <c r="B254" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="O253" s="2" t="s">
+      <c r="O254" s="2" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="254" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O254" s="2"/>
-    </row>
     <row r="255" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A255" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="O255" s="2" t="s">
-        <v>458</v>
-      </c>
+      <c r="O255" s="2"/>
     </row>
     <row r="256" spans="1:15" ht="24.95" customHeight="1">
       <c r="A256" s="2" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="O256" s="2" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
     </row>
     <row r="257" spans="1:15" ht="24.95" customHeight="1">
       <c r="A257" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="O257" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="258" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A258" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="B257" s="2" t="s">
+      <c r="B258" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="O257" s="2" t="s">
+      <c r="O258" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="258" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O258" s="2"/>
-    </row>
     <row r="259" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A259" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="O259" s="2" t="s">
-        <v>361</v>
-      </c>
+      <c r="O259" s="2"/>
     </row>
     <row r="260" spans="1:15" ht="24.95" customHeight="1">
       <c r="A260" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>461</v>
+        <v>363</v>
       </c>
       <c r="O260" s="2" t="s">
-        <v>400</v>
+        <v>361</v>
       </c>
     </row>
     <row r="261" spans="1:15" ht="24.95" customHeight="1">
       <c r="A261" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="O261" s="2" t="s">
-        <v>464</v>
+        <v>400</v>
       </c>
     </row>
     <row r="262" spans="1:15" ht="24.95" customHeight="1">
       <c r="A262" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="O262" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="263" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A263" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B262" s="2" t="s">
+      <c r="B263" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="O262" s="2" t="s">
+      <c r="O263" s="2" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="263" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O263" s="2"/>
-    </row>
     <row r="264" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A264" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="O264" s="2" t="s">
-        <v>470</v>
-      </c>
+      <c r="O264" s="2"/>
     </row>
     <row r="265" spans="1:15" ht="24.95" customHeight="1">
       <c r="A265" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="O265" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="266" spans="1:15" ht="24.95" customHeight="1">
       <c r="A266" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="O266" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="267" spans="1:15" ht="24.95" customHeight="1">
       <c r="A267" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>414</v>
+        <v>475</v>
       </c>
       <c r="O267" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="268" spans="1:15" ht="24.95" customHeight="1">
       <c r="A268" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>414</v>
       </c>
       <c r="O268" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="269" spans="1:15" ht="24.95" customHeight="1">
       <c r="A269" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="O269" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="270" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A270" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="B269" s="2" t="s">
+      <c r="B270" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="O269" s="2" t="s">
+      <c r="O270" s="2" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="270" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O270" s="2"/>
-    </row>
     <row r="271" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A271" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="B271" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="O271" s="2" t="s">
-        <v>486</v>
-      </c>
+      <c r="O271" s="2"/>
     </row>
     <row r="272" spans="1:15" ht="24.95" customHeight="1">
       <c r="A272" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="O272" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="273" spans="1:15" ht="24.95" customHeight="1">
       <c r="A273" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="O273" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="274" spans="1:15" ht="24.95" customHeight="1">
       <c r="A274" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="O274" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="275" spans="1:15" ht="24.95" customHeight="1">
       <c r="A275" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="O275" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="276" spans="1:15" ht="24.95" customHeight="1">
       <c r="A276" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="O276" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="277" spans="1:15" ht="24.95" customHeight="1">
       <c r="A277" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="O277" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="278" spans="1:15" ht="24.95" customHeight="1">
       <c r="A278" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="O278" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="279" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A279" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="B278" s="2" t="s">
+      <c r="B279" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="O278" s="2" t="s">
+      <c r="O279" s="2" t="s">
         <v>507</v>
-      </c>
-    </row>
-    <row r="280" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A280" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="B280" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="O280" s="2" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="281" spans="1:15" ht="24.95" customHeight="1">
       <c r="A281" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="O281" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="282" spans="1:15" ht="24.95" customHeight="1">
       <c r="A282" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="O282" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="283" spans="1:15" ht="24.95" customHeight="1">
       <c r="A283" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="O283" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="284" spans="1:15" ht="24.95" customHeight="1">
       <c r="A284" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="O284" s="4" t="s">
-        <v>522</v>
+        <v>518</v>
+      </c>
+      <c r="O284" s="2" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="285" spans="1:15" ht="24.95" customHeight="1">
       <c r="A285" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="O285" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
+      </c>
+      <c r="O285" s="4" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="286" spans="1:15" ht="24.95" customHeight="1">
       <c r="A286" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="O286" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="287" spans="1:15" ht="24.95" customHeight="1">
       <c r="A287" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="O287" s="4" t="s">
-        <v>531</v>
+        <v>527</v>
+      </c>
+      <c r="O287" s="2" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="288" spans="1:15" ht="24.95" customHeight="1">
       <c r="A288" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="O288" s="4" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="289" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A289" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="B288" s="2" t="s">
+      <c r="B289" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="O288" s="4" t="s">
+      <c r="O289" s="4" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="289" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O289" s="4"/>
-    </row>
     <row r="290" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A290" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="B290" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="O290" s="4" t="s">
-        <v>537</v>
-      </c>
+      <c r="O290" s="4"/>
     </row>
     <row r="291" spans="1:15" ht="24.95" customHeight="1">
       <c r="A291" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="O291" s="4" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="292" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A292" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="B291" s="2" t="s">
+      <c r="B292" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="O291" s="4" t="s">
+      <c r="O292" s="4" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="292" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O292" s="2"/>
-    </row>
     <row r="293" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A293" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="B293" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="O293" s="2" t="s">
-        <v>543</v>
-      </c>
+      <c r="O293" s="2"/>
     </row>
     <row r="294" spans="1:15" ht="24.95" customHeight="1">
       <c r="A294" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="O294" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="295" spans="1:15" ht="24.95" customHeight="1">
       <c r="A295" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="O295" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="296" spans="1:15" ht="24.95" customHeight="1">
       <c r="A296" s="2" t="s">
-        <v>2483</v>
+        <v>547</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>2489</v>
+        <v>548</v>
       </c>
       <c r="O296" s="2" t="s">
-        <v>2484</v>
+        <v>549</v>
       </c>
     </row>
     <row r="297" spans="1:15" ht="24.95" customHeight="1">
       <c r="A297" s="2" t="s">
-        <v>2486</v>
+        <v>2483</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="O297" s="2" t="s">
-        <v>2487</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="298" spans="1:15" ht="24.95" customHeight="1">
       <c r="A298" s="2" t="s">
+        <v>2486</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>2490</v>
+      </c>
+      <c r="O298" s="2" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="299" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A299" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="B298" s="2" t="s">
+      <c r="B299" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="O298" s="2" t="s">
+      <c r="O299" s="2" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="299" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O299" s="2"/>
-    </row>
     <row r="300" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A300" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="O300" s="2" t="s">
-        <v>555</v>
-      </c>
+      <c r="O300" s="2"/>
     </row>
     <row r="301" spans="1:15" ht="24.95" customHeight="1">
       <c r="A301" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="O301" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="302" spans="1:15" ht="24.95" customHeight="1">
       <c r="A302" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="O302" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="303" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A303" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="B302" s="2" t="s">
+      <c r="B303" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="O302" s="2" t="s">
+      <c r="O303" s="2" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="303" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O303" s="2"/>
-    </row>
     <row r="304" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A304" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="B304" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="O304" s="2" t="s">
-        <v>564</v>
-      </c>
+      <c r="O304" s="2"/>
     </row>
     <row r="305" spans="1:15" ht="24.95" customHeight="1">
       <c r="A305" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="O305" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="306" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A306" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="B305" s="2" t="s">
+      <c r="B306" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="O305" s="2" t="s">
+      <c r="O306" s="2" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="306" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O306" s="2"/>
-    </row>
     <row r="307" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A307" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="B307" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="O307" s="2" t="s">
-        <v>570</v>
-      </c>
+      <c r="O307" s="2"/>
     </row>
     <row r="308" spans="1:15" ht="24.95" customHeight="1">
       <c r="A308" s="2" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="O308" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="309" spans="1:15" ht="24.95" customHeight="1">
       <c r="A309" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="O309" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="310" spans="1:15" ht="24.95" customHeight="1">
       <c r="A310" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="O310" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="311" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A311" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="B310" s="2" t="s">
+      <c r="B311" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="O310" s="2" t="s">
+      <c r="O311" s="2" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="311" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O311" s="2"/>
-    </row>
     <row r="312" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A312" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="B312" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="O312" s="2" t="s">
-        <v>582</v>
-      </c>
+      <c r="O312" s="2"/>
     </row>
     <row r="313" spans="1:15" ht="24.95" customHeight="1">
       <c r="A313" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="O313" s="2" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="314" spans="1:15" ht="24.95" customHeight="1">
       <c r="A314" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="O314" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="315" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A315" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="B314" s="2" t="s">
+      <c r="B315" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="O314" s="2" t="s">
+      <c r="O315" s="2" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="315" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O315" s="2"/>
-    </row>
     <row r="316" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A316" s="2" t="s">
+      <c r="O316" s="2"/>
+    </row>
+    <row r="317" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A317" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B316" s="2" t="s">
+      <c r="B317" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="O316" s="2" t="s">
+      <c r="O317" s="2" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="317" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O317" s="2"/>
-    </row>
     <row r="318" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A318" s="2" t="s">
-        <v>1810</v>
-      </c>
-      <c r="B318" s="2" t="s">
-        <v>1817</v>
-      </c>
-      <c r="O318" s="2" t="s">
-        <v>1816</v>
-      </c>
+      <c r="O318" s="2"/>
     </row>
     <row r="319" spans="1:15" ht="24.95" customHeight="1">
       <c r="A319" s="2" t="s">
-        <v>1814</v>
+        <v>1810</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="O319" s="2" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="320" spans="1:15" ht="24.95" customHeight="1">
       <c r="A320" s="2" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="O320" s="2" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="321" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A321" s="2" t="s">
         <v>1811</v>
       </c>
-      <c r="B320" s="2" t="s">
+      <c r="B321" s="2" t="s">
         <v>1812</v>
       </c>
-      <c r="O320" s="2" t="s">
+      <c r="O321" s="2" t="s">
         <v>1813</v>
       </c>
     </row>
-    <row r="321" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O321" s="2"/>
-    </row>
     <row r="322" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A322" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="B322" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="O322" s="2" t="s">
-        <v>594</v>
-      </c>
+      <c r="O322" s="2"/>
     </row>
     <row r="323" spans="1:15" ht="24.95" customHeight="1">
       <c r="A323" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="O323" s="2" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="324" spans="1:15" ht="24.95" customHeight="1">
       <c r="A324" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="O324" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="325" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A325" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="B324" s="2" t="s">
+      <c r="B325" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="O324" s="4" t="s">
+      <c r="O325" s="4" t="s">
         <v>600</v>
-      </c>
-    </row>
-    <row r="326" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A326" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="B326" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="O326" s="4" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="327" spans="1:15" ht="24.95" customHeight="1">
       <c r="A327" s="2" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="O327" s="3" t="s">
-        <v>607</v>
+        <v>603</v>
+      </c>
+      <c r="O327" s="4" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="328" spans="1:15" ht="24.95" customHeight="1">
       <c r="A328" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B328" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="O328" s="3" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="329" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A329" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B328" s="2" t="s">
+      <c r="B329" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="O328" s="4" t="s">
+      <c r="O329" s="4" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="329" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O329" s="2"/>
-    </row>
     <row r="330" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A330" s="2" t="s">
+      <c r="O330" s="2"/>
+    </row>
+    <row r="331" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A331" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="B330" s="2" t="s">
+      <c r="B331" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="O330" s="3" t="s">
+      <c r="O331" s="3" t="s">
         <v>613</v>
-      </c>
-    </row>
-    <row r="332" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A332" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B332" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="O332" s="3" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="333" spans="1:15" ht="24.95" customHeight="1">
       <c r="A333" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B333" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="O333" s="3" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="334" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A334" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="B333" s="2" t="s">
+      <c r="B334" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="O333" s="3" t="s">
+      <c r="O334" s="3" t="s">
         <v>619</v>
-      </c>
-    </row>
-    <row r="335" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A335" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="B335" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="O335" s="3" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="336" spans="1:15" ht="24.95" customHeight="1">
       <c r="A336" s="2" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="O336" s="3" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="337" spans="1:15" ht="24.95" customHeight="1">
       <c r="A337" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="O337" s="3" t="s">
-        <v>2771</v>
+        <v>625</v>
       </c>
     </row>
     <row r="338" spans="1:15" ht="24.95" customHeight="1">
       <c r="A338" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="O338" s="3" t="s">
-        <v>630</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="339" spans="1:15" ht="24.95" customHeight="1">
       <c r="A339" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="O339" s="3" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="340" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A340" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B339" s="2" t="s">
+      <c r="B340" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="O339" s="3" t="s">
+      <c r="O340" s="3" t="s">
         <v>633</v>
-      </c>
-    </row>
-    <row r="341" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A341" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="B341" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="O341" s="3" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="342" spans="1:15" ht="24.95" customHeight="1">
       <c r="A342" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="O342" s="3" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="343" spans="1:15" ht="24.95" customHeight="1">
       <c r="A343" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="O343" s="4" t="s">
-        <v>642</v>
+        <v>638</v>
+      </c>
+      <c r="O343" s="3" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="344" spans="1:15" ht="24.95" customHeight="1">
       <c r="A344" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="O344" s="2" t="s">
-        <v>645</v>
+        <v>641</v>
+      </c>
+      <c r="O344" s="4" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="345" spans="1:15" ht="24.95" customHeight="1">
       <c r="A345" s="2" t="s">
-        <v>2482</v>
+        <v>643</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>2489</v>
+        <v>644</v>
       </c>
       <c r="O345" s="2" t="s">
-        <v>2485</v>
+        <v>645</v>
       </c>
     </row>
     <row r="346" spans="1:15" ht="24.95" customHeight="1">
       <c r="A346" s="2" t="s">
+        <v>2482</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>2489</v>
+      </c>
+      <c r="O346" s="2" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="347" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A347" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B346" s="2" t="s">
+      <c r="B347" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="O346" s="2" t="s">
+      <c r="O347" s="2" t="s">
         <v>2912</v>
       </c>
     </row>
-    <row r="347" spans="1:15" ht="24.95" customHeight="1">
-      <c r="B347" s="3"/>
-      <c r="M347" s="3"/>
-    </row>
     <row r="348" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A348" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="B348" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="O348" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B348" s="3"/>
+      <c r="M348" s="3"/>
     </row>
     <row r="349" spans="1:15" ht="24.95" customHeight="1">
       <c r="A349" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="B349" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="M349" s="3"/>
-      <c r="O349" s="3" t="s">
-        <v>653</v>
+        <v>648</v>
+      </c>
+      <c r="B349" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="O349" s="2" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="350" spans="1:15" ht="24.95" customHeight="1">
       <c r="A350" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="B350" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="O350" s="2" t="s">
-        <v>656</v>
+        <v>651</v>
+      </c>
+      <c r="B350" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="M350" s="3"/>
+      <c r="O350" s="3" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="351" spans="1:15" ht="24.95" customHeight="1">
       <c r="A351" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="O351" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="352" spans="1:15" ht="24.95" customHeight="1">
       <c r="A352" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="O352" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="353" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A353" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="B352" s="2" t="s">
+      <c r="B353" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="O352" s="2" t="s">
+      <c r="O353" s="2" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="353" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O353" s="2"/>
-    </row>
     <row r="354" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A354" s="2" t="s">
+      <c r="O354" s="2"/>
+    </row>
+    <row r="355" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A355" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="B354" s="2" t="s">
+      <c r="B355" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="O354" s="2" t="s">
+      <c r="O355" s="2" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="355" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O355" s="2"/>
-    </row>
     <row r="356" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A356" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="B356" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="O356" s="2" t="s">
-        <v>668</v>
-      </c>
+      <c r="O356" s="2"/>
     </row>
     <row r="357" spans="1:15" ht="24.95" customHeight="1">
       <c r="A357" s="2" t="s">
-        <v>2586</v>
+        <v>666</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="O357" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="358" spans="1:15" ht="24.95" customHeight="1">
       <c r="A358" s="2" t="s">
-        <v>2585</v>
+        <v>2586</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="O358" s="3" t="s">
-        <v>672</v>
+        <v>669</v>
+      </c>
+      <c r="O358" s="2" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="359" spans="1:15" ht="24.95" customHeight="1">
       <c r="A359" s="2" t="s">
-        <v>673</v>
+        <v>2585</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="O359" s="2" t="s">
-        <v>675</v>
+        <v>671</v>
+      </c>
+      <c r="O359" s="3" t="s">
+        <v>672</v>
       </c>
     </row>
     <row r="360" spans="1:15" ht="24.95" customHeight="1">
       <c r="A360" s="2" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="O360" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="361" spans="1:15" ht="24.95" customHeight="1">
       <c r="A361" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="O361" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="362" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A362" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="B361" s="2" t="s">
+      <c r="B362" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="O361" s="2" t="s">
+      <c r="O362" s="2" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="362" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O362" s="2"/>
-    </row>
     <row r="363" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A363" s="2" t="s">
+      <c r="O363" s="2"/>
+    </row>
+    <row r="364" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A364" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="B363" s="2" t="s">
+      <c r="B364" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="O363" s="2" t="s">
+      <c r="O364" s="2" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="364" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O364" s="2"/>
-    </row>
     <row r="365" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A365" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="B365" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="O365" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="O365" s="2"/>
     </row>
     <row r="366" spans="1:15" ht="24.95" customHeight="1">
       <c r="A366" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="O366" s="2" t="s">
-        <v>688</v>
+        <v>650</v>
       </c>
     </row>
     <row r="367" spans="1:15" ht="24.95" customHeight="1">
       <c r="A367" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="O367" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="368" spans="1:15" ht="24.95" customHeight="1">
       <c r="A368" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="O368" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="369" spans="1:15" ht="24.95" customHeight="1">
       <c r="A369" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="O369" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
     <row r="370" spans="1:15" ht="24.95" customHeight="1">
       <c r="A370" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="O370" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="371" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A371" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="B370" s="2" t="s">
+      <c r="B371" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="O370" s="2" t="s">
+      <c r="O371" s="2" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="371" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O371" s="2"/>
-    </row>
     <row r="372" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A372" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="B372" s="2" t="s">
-        <v>1733</v>
-      </c>
-      <c r="O372" s="2" t="s">
-        <v>702</v>
-      </c>
+      <c r="O372" s="2"/>
     </row>
     <row r="373" spans="1:15" ht="24.95" customHeight="1">
       <c r="A373" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="O373" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="374" spans="1:15" ht="24.95" customHeight="1">
       <c r="A374" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="O374" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="375" spans="1:15" ht="24.95" customHeight="1">
       <c r="A375" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="O375" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="376" spans="1:15" ht="24.95" customHeight="1">
       <c r="A376" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="O376" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="377" spans="1:15" ht="24.95" customHeight="1">
       <c r="A377" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="O377" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="378" spans="1:15" ht="24.95" customHeight="1">
       <c r="A378" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="O378" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="379" spans="1:15" ht="24.95" customHeight="1">
       <c r="A379" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="B379" s="2" t="s">
+        <v>1739</v>
+      </c>
+      <c r="O379" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="380" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A380" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="B379" s="2" t="s">
+      <c r="B380" s="2" t="s">
         <v>1740</v>
       </c>
-      <c r="O379" s="2" t="s">
+      <c r="O380" s="2" t="s">
         <v>716</v>
-      </c>
-    </row>
-    <row r="381" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A381" s="2" t="s">
-        <v>2293</v>
-      </c>
-      <c r="B381" s="2" t="s">
-        <v>2300</v>
-      </c>
-      <c r="O381" s="3" t="s">
-        <v>2298</v>
       </c>
     </row>
     <row r="382" spans="1:15" ht="24.95" customHeight="1">
       <c r="A382" s="2" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>2301</v>
-      </c>
-      <c r="O382" s="2" t="s">
-        <v>2297</v>
+        <v>2300</v>
+      </c>
+      <c r="O382" s="3" t="s">
+        <v>2298</v>
       </c>
     </row>
     <row r="383" spans="1:15" ht="24.95" customHeight="1">
       <c r="A383" s="2" t="s">
+        <v>2294</v>
+      </c>
+      <c r="B383" s="2" t="s">
+        <v>2301</v>
+      </c>
+      <c r="O383" s="2" t="s">
+        <v>2297</v>
+      </c>
+    </row>
+    <row r="384" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A384" s="2" t="s">
         <v>2295</v>
       </c>
-      <c r="B383" s="2" t="s">
+      <c r="B384" s="2" t="s">
         <v>2299</v>
       </c>
-      <c r="O383" s="2" t="s">
+      <c r="O384" s="2" t="s">
         <v>2296</v>
       </c>
     </row>
-    <row r="384" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O384" s="2"/>
-    </row>
     <row r="385" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A385" s="2" t="s">
-        <v>2607</v>
-      </c>
-      <c r="B385" s="2" t="s">
-        <v>2600</v>
-      </c>
-      <c r="O385" s="2" t="s">
-        <v>2602</v>
-      </c>
+      <c r="O385" s="2"/>
     </row>
     <row r="386" spans="1:15" ht="24.95" customHeight="1">
       <c r="A386" s="2" t="s">
-        <v>2606</v>
+        <v>2607</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>2599</v>
+        <v>2600</v>
       </c>
       <c r="O386" s="2" t="s">
-        <v>2601</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="387" spans="1:15" ht="24.95" customHeight="1">
       <c r="A387" s="2" t="s">
-        <v>2597</v>
+        <v>2606</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>2598</v>
+        <v>2599</v>
       </c>
       <c r="O387" s="2" t="s">
-        <v>2603</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="388" spans="1:15" ht="24.95" customHeight="1">
       <c r="A388" s="2" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>2594</v>
+        <v>2598</v>
       </c>
       <c r="O388" s="2" t="s">
-        <v>2595</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="389" spans="1:15" ht="24.95" customHeight="1">
       <c r="A389" s="2" t="s">
-        <v>2604</v>
+        <v>2596</v>
+      </c>
+      <c r="B389" s="2" t="s">
+        <v>2594</v>
       </c>
       <c r="O389" s="2" t="s">
-        <v>2608</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="390" spans="1:15" ht="24.95" customHeight="1">
       <c r="A390" s="2" t="s">
+        <v>2604</v>
+      </c>
+      <c r="O390" s="2" t="s">
+        <v>2608</v>
+      </c>
+    </row>
+    <row r="391" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A391" s="2" t="s">
         <v>2605</v>
       </c>
-      <c r="O390" s="2" t="s">
+      <c r="O391" s="2" t="s">
         <v>2609</v>
       </c>
     </row>
-    <row r="391" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O391" s="2"/>
-    </row>
     <row r="392" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A392" s="2" t="s">
-        <v>2286</v>
-      </c>
-      <c r="B392" s="2" t="s">
-        <v>2285</v>
-      </c>
-      <c r="O392" s="2" t="s">
-        <v>768</v>
-      </c>
+      <c r="O392" s="2"/>
     </row>
     <row r="393" spans="1:15" ht="24.95" customHeight="1">
       <c r="A393" s="2" t="s">
-        <v>3029</v>
+        <v>2286</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>1641</v>
+        <v>2285</v>
       </c>
       <c r="O393" s="2" t="s">
-        <v>1759</v>
+        <v>768</v>
       </c>
     </row>
     <row r="394" spans="1:15" ht="24.95" customHeight="1">
       <c r="A394" s="2" t="s">
-        <v>3028</v>
+        <v>3029</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>1664</v>
+        <v>1641</v>
       </c>
       <c r="O394" s="2" t="s">
-        <v>777</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="395" spans="1:15" ht="24.95" customHeight="1">
       <c r="A395" s="2" t="s">
+        <v>3028</v>
+      </c>
+      <c r="B395" s="2" t="s">
+        <v>1664</v>
+      </c>
+      <c r="O395" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="396" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A396" s="2" t="s">
         <v>3218</v>
       </c>
-      <c r="B395" s="2" t="s">
+      <c r="B396" s="2" t="s">
         <v>1639</v>
       </c>
-      <c r="O395" s="2" t="s">
+      <c r="O396" s="2" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="396" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O396" s="2"/>
-    </row>
     <row r="397" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A397" s="2" t="s">
-        <v>3083</v>
-      </c>
-      <c r="B397" s="2" t="s">
-        <v>2882</v>
-      </c>
-      <c r="O397" s="2" t="s">
-        <v>2883</v>
-      </c>
+      <c r="O397" s="2"/>
     </row>
     <row r="398" spans="1:15" ht="24.95" customHeight="1">
       <c r="A398" s="2" t="s">
-        <v>3000</v>
+        <v>3083</v>
+      </c>
+      <c r="B398" s="2" t="s">
+        <v>2882</v>
       </c>
       <c r="O398" s="2" t="s">
-        <v>3001</v>
+        <v>2883</v>
       </c>
     </row>
     <row r="399" spans="1:15" ht="24.95" customHeight="1">
       <c r="A399" s="2" t="s">
-        <v>3013</v>
+        <v>3000</v>
       </c>
       <c r="O399" s="2" t="s">
-        <v>3015</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="400" spans="1:15" ht="24.95" customHeight="1">
       <c r="A400" s="2" t="s">
+        <v>3013</v>
+      </c>
+      <c r="O400" s="2" t="s">
+        <v>3015</v>
+      </c>
+    </row>
+    <row r="401" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A401" s="2" t="s">
         <v>3012</v>
       </c>
-      <c r="O400" s="3" t="s">
+      <c r="O401" s="3" t="s">
         <v>3014</v>
       </c>
     </row>
-    <row r="401" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O401" s="2"/>
-    </row>
     <row r="402" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A402" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="B402" s="2" t="s">
-        <v>718</v>
-      </c>
-      <c r="O402" s="2" t="s">
-        <v>719</v>
-      </c>
+      <c r="O402" s="2"/>
     </row>
     <row r="403" spans="1:15" ht="24.95" customHeight="1">
       <c r="A403" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B403" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="O403" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="404" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A404" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="B403" s="2" t="s">
+      <c r="B404" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="O403" s="2" t="s">
+      <c r="O404" s="2" t="s">
         <v>1759</v>
       </c>
     </row>
-    <row r="404" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O404" s="2"/>
-    </row>
     <row r="405" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A405" s="2" t="s">
-        <v>1677</v>
-      </c>
-      <c r="O405" s="2" t="s">
-        <v>1684</v>
-      </c>
+      <c r="O405" s="2"/>
     </row>
     <row r="406" spans="1:15" ht="24.95" customHeight="1">
       <c r="A406" s="2" t="s">
-        <v>1678</v>
-      </c>
-      <c r="B406" s="2" t="s">
-        <v>1657</v>
+        <v>1677</v>
       </c>
       <c r="O406" s="2" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="407" spans="1:15" ht="24.95" customHeight="1">
       <c r="A407" s="2" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>1653</v>
+        <v>1657</v>
       </c>
       <c r="O407" s="2" t="s">
-        <v>1689</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="408" spans="1:15" ht="24.95" customHeight="1">
       <c r="A408" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="O408" s="2" t="s">
-        <v>1659</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="409" spans="1:15" ht="24.95" customHeight="1">
       <c r="A409" s="2" t="s">
-        <v>1690</v>
+        <v>1680</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>1663</v>
+        <v>1654</v>
       </c>
       <c r="O409" s="2" t="s">
-        <v>1691</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="410" spans="1:15" ht="24.95" customHeight="1">
       <c r="A410" s="2" t="s">
-        <v>1681</v>
+        <v>1690</v>
+      </c>
+      <c r="B410" s="2" t="s">
+        <v>1663</v>
       </c>
       <c r="O410" s="2" t="s">
-        <v>1686</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="411" spans="1:15" ht="24.95" customHeight="1">
       <c r="A411" s="2" t="s">
-        <v>1682</v>
-      </c>
-      <c r="B411" s="2" t="s">
-        <v>1658</v>
+        <v>1681</v>
       </c>
       <c r="O411" s="2" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="412" spans="1:15" ht="24.95" customHeight="1">
       <c r="A412" s="2" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B412" s="2" t="s">
+        <v>1658</v>
+      </c>
+      <c r="O412" s="2" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="413" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A413" s="2" t="s">
         <v>1683</v>
       </c>
-      <c r="B412" s="2" t="s">
+      <c r="B413" s="2" t="s">
         <v>1656</v>
       </c>
-      <c r="O412" s="2" t="s">
+      <c r="O413" s="2" t="s">
         <v>1687</v>
       </c>
     </row>
-    <row r="413" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O413" s="2"/>
-    </row>
     <row r="414" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A414" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="B414" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="O414" s="2" t="s">
-        <v>724</v>
-      </c>
+      <c r="O414" s="2"/>
     </row>
     <row r="415" spans="1:15" ht="24.95" customHeight="1">
       <c r="A415" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="B415" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="O415" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="416" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A416" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="B415" s="2" t="s">
+      <c r="B416" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="O415" s="2" t="s">
+      <c r="O416" s="2" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="416" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O416" s="2"/>
-    </row>
     <row r="417" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A417" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="B417" s="2" t="s">
-        <v>2408</v>
-      </c>
-      <c r="O417" s="2" t="s">
-        <v>729</v>
-      </c>
+      <c r="O417" s="2"/>
     </row>
     <row r="418" spans="1:15" ht="24.95" customHeight="1">
       <c r="A418" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="O418" s="2" t="s">
-        <v>2861</v>
+        <v>729</v>
       </c>
     </row>
     <row r="419" spans="1:15" ht="24.95" customHeight="1">
       <c r="A419" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B419" s="2" t="s">
+        <v>2409</v>
+      </c>
+      <c r="O419" s="2" t="s">
+        <v>2861</v>
+      </c>
+    </row>
+    <row r="420" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A420" s="2" t="s">
         <v>2863</v>
       </c>
-      <c r="O419" s="2" t="s">
+      <c r="O420" s="2" t="s">
         <v>2862</v>
       </c>
     </row>
-    <row r="420" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O420" s="2"/>
-    </row>
     <row r="421" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A421" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="B421" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="O421" s="2" t="s">
-        <v>733</v>
-      </c>
+      <c r="O421" s="2"/>
     </row>
     <row r="422" spans="1:15" ht="24.95" customHeight="1">
       <c r="A422" s="2" t="s">
-        <v>1605</v>
+        <v>731</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="O422" s="2" t="s">
-        <v>492</v>
+        <v>733</v>
       </c>
     </row>
     <row r="423" spans="1:15" ht="24.95" customHeight="1">
       <c r="A423" s="2" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="O423" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="424" spans="1:15" ht="24.95" customHeight="1">
       <c r="A424" s="2" t="s">
-        <v>736</v>
+        <v>1606</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O424" s="2" t="s">
-        <v>738</v>
+        <v>495</v>
       </c>
     </row>
     <row r="425" spans="1:15" ht="24.95" customHeight="1">
       <c r="A425" s="2" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="O425" s="2" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="426" spans="1:15" ht="24.95" customHeight="1">
       <c r="A426" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>1640</v>
+        <v>740</v>
       </c>
       <c r="O426" s="2" t="s">
-        <v>1760</v>
+        <v>741</v>
       </c>
     </row>
     <row r="427" spans="1:15" ht="24.95" customHeight="1">
       <c r="A427" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>744</v>
+        <v>1640</v>
       </c>
       <c r="O427" s="2" t="s">
-        <v>745</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="428" spans="1:15" ht="24.95" customHeight="1">
       <c r="A428" s="2" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="O428" s="2" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
     </row>
     <row r="429" spans="1:15" ht="24.95" customHeight="1">
       <c r="A429" s="2" t="s">
-        <v>2404</v>
+        <v>746</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>2405</v>
+        <v>747</v>
       </c>
       <c r="O429" s="2" t="s">
-        <v>2406</v>
+        <v>748</v>
       </c>
     </row>
     <row r="430" spans="1:15" ht="24.95" customHeight="1">
       <c r="A430" s="2" t="s">
-        <v>1713</v>
+        <v>2404</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>749</v>
+        <v>2405</v>
       </c>
       <c r="O430" s="2" t="s">
-        <v>750</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="431" spans="1:15" ht="24.95" customHeight="1">
       <c r="A431" s="2" t="s">
-        <v>751</v>
+        <v>1713</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="O431" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="432" spans="1:15" ht="24.95" customHeight="1">
       <c r="A432" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="O432" s="2" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
     </row>
     <row r="433" spans="1:15" ht="24.95" customHeight="1">
       <c r="A433" s="2" t="s">
-        <v>2402</v>
+        <v>754</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="O433" s="2" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="434" spans="1:15" ht="24.95" customHeight="1">
       <c r="A434" s="2" t="s">
+        <v>2402</v>
+      </c>
+      <c r="B434" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="O434" s="2" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="435" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A435" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="B434" s="2" t="s">
+      <c r="B435" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="O434" s="2" t="s">
+      <c r="O435" s="2" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="435" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O435" s="2"/>
-    </row>
     <row r="436" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A436" s="2" t="s">
-        <v>1610</v>
-      </c>
-      <c r="O436" s="2" t="s">
-        <v>2309</v>
-      </c>
+      <c r="O436" s="2"/>
     </row>
     <row r="437" spans="1:15" ht="24.95" customHeight="1">
       <c r="A437" s="2" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="O437" s="2" t="s">
-        <v>1631</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="438" spans="1:15" ht="24.95" customHeight="1">
       <c r="A438" s="2" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="O438" s="2" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="439" spans="1:15" ht="24.95" customHeight="1">
       <c r="A439" s="2" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="O439" s="2" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="440" spans="1:15" ht="24.95" customHeight="1">
       <c r="A440" s="2" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="O440" s="2" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="441" spans="1:15" ht="24.95" customHeight="1">
       <c r="A441" s="2" t="s">
-        <v>1618</v>
+        <v>1614</v>
       </c>
       <c r="O441" s="2" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="442" spans="1:15" ht="24.95" customHeight="1">
       <c r="A442" s="2" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="O442" s="2" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="443" spans="1:15" ht="24.95" customHeight="1">
       <c r="A443" s="2" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="O443" s="2" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="444" spans="1:15" ht="24.95" customHeight="1">
       <c r="A444" s="2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="O444" s="2" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="445" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A445" s="2" t="s">
         <v>1617</v>
       </c>
-      <c r="O444" s="2" t="s">
+      <c r="O445" s="2" t="s">
         <v>1624</v>
       </c>
     </row>
-    <row r="445" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O445" s="2"/>
-    </row>
     <row r="446" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A446" s="2" t="s">
-        <v>1619</v>
-      </c>
-      <c r="B446" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="O446" s="2" t="s">
-        <v>1623</v>
-      </c>
+      <c r="O446" s="2"/>
     </row>
     <row r="447" spans="1:15" ht="24.95" customHeight="1">
       <c r="A447" s="2" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="O447" s="2" t="s">
-        <v>495</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="448" spans="1:15" ht="24.95" customHeight="1">
       <c r="A448" s="2" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B448" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="O448" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="449" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A449" s="2" t="s">
         <v>2282</v>
       </c>
-      <c r="B448" s="2" t="s">
+      <c r="B449" s="2" t="s">
         <v>2283</v>
       </c>
-      <c r="O448" s="2" t="s">
+      <c r="O449" s="2" t="s">
         <v>2284</v>
       </c>
     </row>
-    <row r="449" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O449" s="2"/>
-    </row>
     <row r="450" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A450" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="B450" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="O450" s="2" t="s">
-        <v>789</v>
-      </c>
+      <c r="O450" s="2"/>
     </row>
     <row r="451" spans="1:15" ht="24.95" customHeight="1">
       <c r="A451" s="2" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="O451" s="2" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
     </row>
     <row r="452" spans="1:15" ht="24.95" customHeight="1">
       <c r="A452" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="B452" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="O452" s="2" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="453" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A453" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="B452" s="2" t="s">
+      <c r="B453" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="O452" s="2" t="s">
+      <c r="O453" s="2" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="453" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O453" s="2"/>
-    </row>
     <row r="454" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A454" s="2" t="s">
+      <c r="O454" s="2"/>
+    </row>
+    <row r="455" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A455" s="2" t="s">
         <v>1621</v>
       </c>
-      <c r="O454" s="2" t="s">
+      <c r="O455" s="2" t="s">
         <v>1622</v>
       </c>
     </row>
-    <row r="455" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O455" s="2"/>
-    </row>
     <row r="456" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A456" s="2" t="s">
-        <v>2985</v>
-      </c>
-      <c r="O456" s="2" t="s">
-        <v>2987</v>
-      </c>
+      <c r="O456" s="2"/>
     </row>
     <row r="457" spans="1:15" ht="24.95" customHeight="1">
       <c r="A457" s="2" t="s">
+        <v>2985</v>
+      </c>
+      <c r="O457" s="2" t="s">
+        <v>2987</v>
+      </c>
+    </row>
+    <row r="458" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A458" s="2" t="s">
         <v>2986</v>
       </c>
-      <c r="O457" s="2" t="s">
+      <c r="O458" s="2" t="s">
         <v>2988</v>
       </c>
     </row>
-    <row r="458" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O458" s="2"/>
-    </row>
     <row r="459" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A459" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="B459" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="O459" s="2" t="s">
-        <v>764</v>
-      </c>
+      <c r="O459" s="2"/>
     </row>
     <row r="460" spans="1:15" ht="24.95" customHeight="1">
       <c r="A460" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="O460" s="2" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="461" spans="1:15" ht="24.95" customHeight="1">
       <c r="A461" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B461" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="O461" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="462" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A462" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="B461" s="2" t="s">
+      <c r="B462" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="O461" s="2" t="s">
+      <c r="O462" s="2" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="462" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O462" s="2"/>
-    </row>
     <row r="463" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A463" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="B463" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="O463" s="2" t="s">
-        <v>773</v>
-      </c>
+      <c r="O463" s="2"/>
     </row>
     <row r="464" spans="1:15" ht="24.95" customHeight="1">
       <c r="A464" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="O464" s="2" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="465" spans="1:15" ht="24.95" customHeight="1">
       <c r="A465" s="2" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="O465" s="2" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
     </row>
     <row r="466" spans="1:15" ht="24.95" customHeight="1">
       <c r="A466" s="2" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="O466" s="2" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
     </row>
     <row r="467" spans="1:15" ht="24.95" customHeight="1">
       <c r="A467" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="B467" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="O467" s="2" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="468" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A468" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="O467" s="2" t="s">
+      <c r="O468" s="2" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="468" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O468" s="2"/>
-    </row>
     <row r="469" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A469" s="2" t="s">
-        <v>1609</v>
-      </c>
-      <c r="O469" s="2" t="s">
-        <v>3050</v>
-      </c>
+      <c r="O469" s="2"/>
     </row>
     <row r="470" spans="1:15" ht="24.95" customHeight="1">
       <c r="A470" s="2" t="s">
+        <v>1609</v>
+      </c>
+      <c r="O470" s="2" t="s">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="471" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A471" s="2" t="s">
         <v>1665</v>
       </c>
-      <c r="B470" s="2" t="s">
+      <c r="B471" s="2" t="s">
         <v>1796</v>
       </c>
-      <c r="O470" s="2" t="s">
+      <c r="O471" s="2" t="s">
         <v>3051</v>
       </c>
     </row>
-    <row r="471" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O471" s="2"/>
-    </row>
     <row r="472" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A472" s="2" t="s">
-        <v>1645</v>
-      </c>
-      <c r="O472" s="2" t="s">
-        <v>1646</v>
-      </c>
+      <c r="O472" s="2"/>
     </row>
     <row r="473" spans="1:15" ht="24.95" customHeight="1">
       <c r="A473" s="2" t="s">
-        <v>1649</v>
-      </c>
-      <c r="B473" s="2" t="s">
-        <v>1658</v>
+        <v>1645</v>
       </c>
       <c r="O473" s="2" t="s">
-        <v>1688</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="474" spans="1:15" ht="24.95" customHeight="1">
       <c r="A474" s="2" t="s">
-        <v>781</v>
+        <v>1649</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="O474" s="2" t="s">
-        <v>1660</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="475" spans="1:15" ht="24.95" customHeight="1">
       <c r="A475" s="2" t="s">
-        <v>1647</v>
+        <v>781</v>
+      </c>
+      <c r="B475" s="2" t="s">
+        <v>1656</v>
       </c>
       <c r="O475" s="2" t="s">
-        <v>1648</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="476" spans="1:15" ht="24.95" customHeight="1">
       <c r="A476" s="2" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B476" s="2" t="s">
-        <v>1653</v>
+        <v>1647</v>
       </c>
       <c r="O476" s="2" t="s">
-        <v>1689</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="477" spans="1:15" ht="24.95" customHeight="1">
       <c r="A477" s="2" t="s">
-        <v>1655</v>
+        <v>1650</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="O477" s="2" t="s">
-        <v>1659</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="478" spans="1:15" ht="24.95" customHeight="1">
       <c r="A478" s="2" t="s">
-        <v>1652</v>
+        <v>1655</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>1663</v>
+        <v>1654</v>
       </c>
       <c r="O478" s="2" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="479" spans="1:15" ht="24.95" customHeight="1">
       <c r="A479" s="2" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B479" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="O479" s="2" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="480" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A480" s="2" t="s">
         <v>1651</v>
       </c>
-      <c r="B479" s="2" t="s">
+      <c r="B480" s="2" t="s">
         <v>1657</v>
       </c>
-      <c r="O479" s="2" t="s">
+      <c r="O480" s="2" t="s">
         <v>1661</v>
       </c>
     </row>
-    <row r="480" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O480" s="2"/>
-    </row>
     <row r="481" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A481" s="2" t="s">
-        <v>2905</v>
-      </c>
-      <c r="O481" s="2" t="s">
-        <v>2910</v>
-      </c>
+      <c r="O481" s="2"/>
     </row>
     <row r="482" spans="1:15" ht="24.95" customHeight="1">
       <c r="A482" s="2" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="O482" s="2" t="s">
-        <v>2908</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="483" spans="1:15" ht="24.95" customHeight="1">
       <c r="A483" s="2" t="s">
-        <v>2907</v>
-      </c>
-      <c r="O483" s="3" t="s">
-        <v>2909</v>
+        <v>2906</v>
+      </c>
+      <c r="O483" s="2" t="s">
+        <v>2908</v>
       </c>
     </row>
     <row r="484" spans="1:15" ht="24.95" customHeight="1">
       <c r="A484" s="2" t="s">
+        <v>2907</v>
+      </c>
+      <c r="O484" s="3" t="s">
+        <v>2909</v>
+      </c>
+    </row>
+    <row r="485" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A485" s="2" t="s">
         <v>2973</v>
       </c>
-      <c r="O484" s="3" t="s">
+      <c r="O485" s="3" t="s">
         <v>2999</v>
-      </c>
-    </row>
-    <row r="486" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A486" s="2" t="s">
-        <v>3203</v>
-      </c>
-      <c r="O486" s="3" t="s">
-        <v>3206</v>
       </c>
     </row>
     <row r="487" spans="1:15" ht="24.95" customHeight="1">
       <c r="A487" s="2" t="s">
+        <v>3203</v>
+      </c>
+      <c r="O487" s="3" t="s">
+        <v>3206</v>
+      </c>
+    </row>
+    <row r="488" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A488" s="2" t="s">
         <v>3204</v>
       </c>
-      <c r="O487" s="3" t="s">
+      <c r="O488" s="3" t="s">
         <v>3205</v>
       </c>
     </row>
-    <row r="488" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O488" s="2"/>
-    </row>
     <row r="489" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A489" s="2" t="s">
-        <v>2480</v>
-      </c>
-      <c r="O489" s="3" t="s">
-        <v>2481</v>
-      </c>
+      <c r="O489" s="2"/>
     </row>
     <row r="490" spans="1:15" ht="24.95" customHeight="1">
       <c r="A490" s="2" t="s">
-        <v>2470</v>
-      </c>
-      <c r="O490" s="2" t="s">
-        <v>2468</v>
+        <v>2480</v>
+      </c>
+      <c r="O490" s="3" t="s">
+        <v>2481</v>
       </c>
     </row>
     <row r="491" spans="1:15" ht="24.95" customHeight="1">
       <c r="A491" s="2" t="s">
+        <v>2470</v>
+      </c>
+      <c r="O491" s="2" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="492" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A492" s="2" t="s">
         <v>2471</v>
       </c>
-      <c r="O491" s="2" t="s">
+      <c r="O492" s="2" t="s">
         <v>2469</v>
       </c>
     </row>
-    <row r="492" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O492" s="2"/>
-    </row>
     <row r="493" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A493" s="2" t="s">
-        <v>1607</v>
-      </c>
-      <c r="B493" s="2" t="s">
-        <v>1797</v>
-      </c>
-      <c r="O493" s="2" t="s">
-        <v>1632</v>
-      </c>
+      <c r="O493" s="2"/>
     </row>
     <row r="494" spans="1:15" ht="24.95" customHeight="1">
       <c r="A494" s="2" t="s">
-        <v>1608</v>
+        <v>1607</v>
+      </c>
+      <c r="B494" s="2" t="s">
+        <v>1797</v>
       </c>
       <c r="O494" s="2" t="s">
-        <v>2413</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="495" spans="1:15" ht="24.95" customHeight="1">
       <c r="A495" s="2" t="s">
-        <v>1633</v>
-      </c>
-      <c r="B495" s="2" t="s">
-        <v>2414</v>
+        <v>1608</v>
       </c>
       <c r="O495" s="2" t="s">
-        <v>1795</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="496" spans="1:15" ht="24.95" customHeight="1">
       <c r="A496" s="2" t="s">
-        <v>937</v>
+        <v>1633</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="O496" s="2" t="s">
-        <v>2417</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="497" spans="1:15" ht="24.95" customHeight="1">
       <c r="A497" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>2418</v>
+        <v>2415</v>
       </c>
       <c r="O497" s="2" t="s">
-        <v>939</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="498" spans="1:15" ht="24.95" customHeight="1">
       <c r="A498" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="B498" s="2" t="s">
+        <v>2418</v>
+      </c>
+      <c r="O498" s="2" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="499" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A499" s="2" t="s">
         <v>940</v>
       </c>
-      <c r="B498" s="2" t="s">
+      <c r="B499" s="2" t="s">
         <v>2416</v>
       </c>
-      <c r="O498" s="2" t="s">
+      <c r="O499" s="2" t="s">
         <v>2412</v>
       </c>
     </row>
-    <row r="499" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O499" s="2"/>
-    </row>
     <row r="500" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A500" s="2" t="s">
-        <v>966</v>
-      </c>
-      <c r="O500" s="2" t="s">
-        <v>967</v>
-      </c>
+      <c r="O500" s="2"/>
     </row>
     <row r="501" spans="1:15" ht="24.95" customHeight="1">
       <c r="A501" s="2" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="O501" s="2" t="s">
-        <v>2855</v>
+        <v>967</v>
       </c>
     </row>
     <row r="502" spans="1:15" ht="24.95" customHeight="1">
       <c r="A502" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="O502" s="2" t="s">
-        <v>970</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="503" spans="1:15" ht="24.95" customHeight="1">
       <c r="A503" s="2" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="O503" s="2" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="504" spans="1:15" ht="24.95" customHeight="1">
       <c r="A504" s="2" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="O504" s="2" t="s">
-        <v>2512</v>
+        <v>972</v>
       </c>
     </row>
     <row r="505" spans="1:15" ht="24.95" customHeight="1">
       <c r="A505" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="O505" s="2" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="506" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A506" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="O505" s="2" t="s">
+      <c r="O506" s="2" t="s">
         <v>975</v>
       </c>
     </row>
-    <row r="506" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O506" s="2"/>
-    </row>
     <row r="507" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A507" s="2" t="s">
-        <v>3227</v>
-      </c>
-      <c r="B507" s="2" t="s">
-        <v>3229</v>
-      </c>
-      <c r="O507" s="2" t="s">
-        <v>3228</v>
-      </c>
+      <c r="O507" s="2"/>
     </row>
     <row r="508" spans="1:15" ht="24.95" customHeight="1">
       <c r="A508" s="2" t="s">
-        <v>795</v>
+        <v>3227</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>796</v>
+        <v>3229</v>
       </c>
       <c r="O508" s="2" t="s">
-        <v>1638</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="509" spans="1:15" ht="24.95" customHeight="1">
       <c r="A509" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="O509" s="2" t="s">
-        <v>799</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="510" spans="1:15" ht="24.95" customHeight="1">
       <c r="A510" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="B510" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="O510" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="511" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A511" s="2" t="s">
         <v>1637</v>
       </c>
-      <c r="B510" s="2" t="s">
+      <c r="B511" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="O510" s="3" t="s">
+      <c r="O511" s="3" t="s">
         <v>1636</v>
-      </c>
-    </row>
-    <row r="512" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A512" s="2" t="s">
-        <v>3221</v>
-      </c>
-      <c r="O512" s="3" t="s">
-        <v>3224</v>
       </c>
     </row>
     <row r="513" spans="1:15" ht="24.95" customHeight="1">
       <c r="A513" s="2" t="s">
-        <v>3225</v>
+        <v>3221</v>
       </c>
       <c r="O513" s="3" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
     </row>
     <row r="514" spans="1:15" ht="24.95" customHeight="1">
       <c r="A514" s="2" t="s">
-        <v>3219</v>
+        <v>3225</v>
       </c>
       <c r="O514" s="3" t="s">
-        <v>3222</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="515" spans="1:15" ht="24.95" customHeight="1">
       <c r="A515" s="2" t="s">
+        <v>3219</v>
+      </c>
+      <c r="O515" s="3" t="s">
+        <v>3222</v>
+      </c>
+    </row>
+    <row r="516" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A516" s="2" t="s">
         <v>3220</v>
       </c>
-      <c r="O515" s="3" t="s">
+      <c r="O516" s="3" t="s">
         <v>3223</v>
       </c>
     </row>
-    <row r="518" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A518" s="2" t="s">
+    <row r="519" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A519" s="2" t="s">
         <v>2884</v>
       </c>
-      <c r="B518" s="2" t="s">
+      <c r="B519" s="2" t="s">
         <v>2885</v>
       </c>
-      <c r="O518" s="3" t="s">
+      <c r="O519" s="3" t="s">
         <v>2886</v>
       </c>
     </row>
-    <row r="519" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O519" s="2"/>
-    </row>
     <row r="520" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A520" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="B520" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="O520" s="2" t="s">
-        <v>803</v>
-      </c>
+      <c r="O520" s="2"/>
     </row>
     <row r="521" spans="1:15" ht="24.95" customHeight="1">
       <c r="A521" s="2" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="O521" s="2" t="s">
-        <v>519</v>
+        <v>803</v>
       </c>
     </row>
     <row r="522" spans="1:15" ht="24.95" customHeight="1">
       <c r="A522" s="2" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="O522" s="2" t="s">
-        <v>808</v>
+        <v>519</v>
       </c>
     </row>
     <row r="523" spans="1:15" ht="24.95" customHeight="1">
       <c r="A523" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="B523" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="O523" s="2" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="524" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A524" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="B523" s="2" t="s">
+      <c r="B524" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="O523" s="2" t="s">
+      <c r="O524" s="2" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="524" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O524" s="2"/>
-    </row>
     <row r="525" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A525" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="B525" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="O525" s="2" t="s">
-        <v>812</v>
-      </c>
+      <c r="O525" s="2"/>
     </row>
     <row r="526" spans="1:15" ht="24.95" customHeight="1">
       <c r="A526" s="2" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="O526" s="2" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
     </row>
     <row r="527" spans="1:15" ht="24.95" customHeight="1">
       <c r="A527" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="O527" s="2" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
     </row>
     <row r="528" spans="1:15" ht="24.95" customHeight="1">
       <c r="A528" s="2" t="s">
-        <v>2419</v>
+        <v>819</v>
+      </c>
+      <c r="B528" s="2" t="s">
+        <v>820</v>
       </c>
       <c r="O528" s="2" t="s">
-        <v>2420</v>
+        <v>821</v>
       </c>
     </row>
     <row r="529" spans="1:15" ht="24.95" customHeight="1">
       <c r="A529" s="2" t="s">
-        <v>822</v>
+        <v>2419</v>
       </c>
       <c r="O529" s="2" t="s">
-        <v>823</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="530" spans="1:15" ht="24.95" customHeight="1">
       <c r="A530" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="O530" s="2" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="531" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A531" s="2" t="s">
         <v>2292</v>
       </c>
-      <c r="O530" s="2" t="s">
+      <c r="O531" s="2" t="s">
         <v>2466</v>
       </c>
     </row>
-    <row r="531" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O531" s="2"/>
-    </row>
     <row r="532" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A532" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="B532" s="2" t="s">
-        <v>1669</v>
-      </c>
-      <c r="O532" s="2" t="s">
-        <v>825</v>
-      </c>
+      <c r="O532" s="2"/>
     </row>
     <row r="533" spans="1:15" ht="24.95" customHeight="1">
       <c r="A533" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="B533" s="2" t="s">
+        <v>1669</v>
+      </c>
+      <c r="O533" s="2" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="534" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A534" s="2" t="s">
         <v>813</v>
       </c>
-      <c r="B533" s="2" t="s">
+      <c r="B534" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="O533" s="2" t="s">
+      <c r="O534" s="2" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="534" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O534" s="2"/>
-    </row>
     <row r="535" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A535" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="B535" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="O535" s="2" t="s">
-        <v>828</v>
-      </c>
+      <c r="O535" s="2"/>
     </row>
     <row r="536" spans="1:15" ht="24.95" customHeight="1">
       <c r="A536" s="2" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="O536" s="2" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
     </row>
     <row r="537" spans="1:15" ht="24.95" customHeight="1">
       <c r="A537" s="2" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="O537" s="2" t="s">
-        <v>2465</v>
+        <v>831</v>
       </c>
     </row>
     <row r="538" spans="1:15" ht="24.95" customHeight="1">
       <c r="A538" s="2" t="s">
-        <v>1666</v>
+        <v>832</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>1668</v>
+        <v>833</v>
       </c>
       <c r="O538" s="2" t="s">
-        <v>1667</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="539" spans="1:15" ht="24.95" customHeight="1">
       <c r="A539" s="2" t="s">
-        <v>834</v>
+        <v>1666</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>835</v>
+        <v>1668</v>
       </c>
       <c r="O539" s="2" t="s">
-        <v>836</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="540" spans="1:15" ht="24.95" customHeight="1">
       <c r="A540" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B540" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="O540" s="2" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="541" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A541" s="2" t="s">
         <v>837</v>
       </c>
-      <c r="B540" s="2" t="s">
+      <c r="B541" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="O540" s="2" t="s">
+      <c r="O541" s="2" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="541" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O541" s="2"/>
-    </row>
     <row r="542" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A542" s="2" t="s">
+      <c r="O542" s="2"/>
+    </row>
+    <row r="543" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A543" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="B542" s="2" t="s">
+      <c r="B543" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="O542" s="2" t="s">
+      <c r="O543" s="2" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="543" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O543" s="2"/>
-    </row>
     <row r="544" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A544" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="B544" s="2" t="s">
-        <v>844</v>
-      </c>
-      <c r="O544" s="2" t="s">
-        <v>845</v>
-      </c>
+      <c r="O544" s="2"/>
     </row>
     <row r="545" spans="1:15" ht="24.95" customHeight="1">
       <c r="A545" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="O545" s="2" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
     </row>
     <row r="546" spans="1:15" ht="24.95" customHeight="1">
       <c r="A546" s="2" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="O546" s="2" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
     </row>
     <row r="547" spans="1:15" ht="24.95" customHeight="1">
       <c r="A547" s="2" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="O547" s="2" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
     </row>
     <row r="548" spans="1:15" ht="24.95" customHeight="1">
       <c r="A548" s="2" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="O548" s="2" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
     </row>
     <row r="549" spans="1:15" ht="24.95" customHeight="1">
       <c r="A549" s="2" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>651</v>
+        <v>856</v>
       </c>
       <c r="O549" s="2" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="550" spans="1:15" ht="24.95" customHeight="1">
       <c r="A550" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="B550" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="O550" s="2" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="551" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A551" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="B550" s="2" t="s">
+      <c r="B551" s="2" t="s">
         <v>1794</v>
       </c>
-      <c r="O550" s="2" t="s">
+      <c r="O551" s="2" t="s">
         <v>1793</v>
       </c>
     </row>
-    <row r="551" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O551" s="2"/>
-    </row>
     <row r="552" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A552" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="B552" s="2" t="s">
-        <v>862</v>
-      </c>
-      <c r="O552" s="2" t="s">
-        <v>863</v>
-      </c>
+      <c r="O552" s="2"/>
     </row>
     <row r="553" spans="1:15" ht="24.95" customHeight="1">
       <c r="A553" s="2" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="O553" s="2" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
     </row>
     <row r="554" spans="1:15" ht="24.95" customHeight="1">
       <c r="A554" s="2" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="O554" s="2" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
     </row>
     <row r="555" spans="1:15" ht="24.95" customHeight="1">
       <c r="A555" s="2" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="O555" s="2" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
     </row>
     <row r="556" spans="1:15" ht="24.95" customHeight="1">
       <c r="A556" s="2" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="O556" s="2" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
     </row>
     <row r="557" spans="1:15" ht="24.95" customHeight="1">
       <c r="A557" s="2" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="O557" s="2" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
     </row>
     <row r="558" spans="1:15" ht="24.95" customHeight="1">
       <c r="A558" s="2" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="O558" s="2" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
     </row>
     <row r="559" spans="1:15" ht="24.95" customHeight="1">
       <c r="A559" s="2" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="O559" s="2" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
     </row>
     <row r="560" spans="1:15" ht="24.95" customHeight="1">
       <c r="A560" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="B560" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="O560" s="2" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="561" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A561" s="2" t="s">
         <v>885</v>
       </c>
-      <c r="B560" s="2" t="s">
+      <c r="B561" s="2" t="s">
         <v>886</v>
       </c>
-      <c r="O560" s="2" t="s">
+      <c r="O561" s="2" t="s">
         <v>887</v>
       </c>
     </row>
-    <row r="561" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O561" s="2"/>
-    </row>
     <row r="562" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A562" s="2" t="s">
-        <v>1779</v>
-      </c>
-      <c r="B562" s="2" t="s">
-        <v>888</v>
-      </c>
-      <c r="O562" s="2" t="s">
-        <v>889</v>
-      </c>
+      <c r="O562" s="2"/>
     </row>
     <row r="563" spans="1:15" ht="24.95" customHeight="1">
       <c r="A563" s="2" t="s">
-        <v>1780</v>
+        <v>1779</v>
+      </c>
+      <c r="B563" s="2" t="s">
+        <v>888</v>
       </c>
       <c r="O563" s="2" t="s">
-        <v>1781</v>
+        <v>889</v>
       </c>
     </row>
     <row r="564" spans="1:15" ht="24.95" customHeight="1">
       <c r="A564" s="2" t="s">
-        <v>890</v>
-      </c>
-      <c r="B564" s="2" t="s">
-        <v>891</v>
+        <v>1780</v>
       </c>
       <c r="O564" s="2" t="s">
-        <v>892</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="565" spans="1:15" ht="24.95" customHeight="1">
       <c r="A565" s="2" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="O565" s="2" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
     </row>
     <row r="566" spans="1:15" ht="24.95" customHeight="1">
       <c r="A566" s="2" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="O566" s="2" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
     </row>
     <row r="567" spans="1:15" ht="24.95" customHeight="1">
       <c r="A567" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B567" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="O567" s="2" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="568" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A568" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="B567" s="2" t="s">
+      <c r="B568" s="2" t="s">
         <v>1774</v>
       </c>
-      <c r="O567" s="2" t="s">
+      <c r="O568" s="2" t="s">
         <v>900</v>
       </c>
     </row>
-    <row r="568" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O568" s="2"/>
-    </row>
     <row r="569" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A569" s="2" t="s">
-        <v>901</v>
-      </c>
-      <c r="B569" s="2" t="s">
-        <v>902</v>
-      </c>
-      <c r="O569" s="2" t="s">
-        <v>903</v>
-      </c>
+      <c r="O569" s="2"/>
     </row>
     <row r="570" spans="1:15" ht="24.95" customHeight="1">
       <c r="A570" s="2" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="O570" s="2" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
     </row>
     <row r="571" spans="1:15" ht="24.95" customHeight="1">
       <c r="A571" s="2" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="O571" s="2" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
     </row>
     <row r="572" spans="1:15" ht="24.95" customHeight="1">
       <c r="A572" s="2" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="O572" s="2" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
     </row>
     <row r="573" spans="1:15" ht="24.95" customHeight="1">
       <c r="A573" s="2" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="O573" s="2" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
     <row r="574" spans="1:15" ht="24.95" customHeight="1">
       <c r="A574" s="2" t="s">
-        <v>2287</v>
+        <v>913</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>932</v>
+        <v>914</v>
       </c>
       <c r="O574" s="2" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
     </row>
     <row r="575" spans="1:15" ht="24.95" customHeight="1">
       <c r="A575" s="2" t="s">
-        <v>916</v>
+        <v>2287</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>917</v>
+        <v>932</v>
       </c>
       <c r="O575" s="2" t="s">
-        <v>2288</v>
+        <v>918</v>
       </c>
     </row>
     <row r="576" spans="1:15" ht="24.95" customHeight="1">
       <c r="A576" s="2" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="O576" s="2" t="s">
-        <v>921</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="577" spans="1:15" ht="24.95" customHeight="1">
       <c r="A577" s="2" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="O577" s="2" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
     </row>
     <row r="578" spans="1:15" ht="24.95" customHeight="1">
       <c r="A578" s="2" t="s">
-        <v>1782</v>
+        <v>922</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="O578" s="2" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="579" spans="1:15" ht="24.95" customHeight="1">
       <c r="A579" s="2" t="s">
-        <v>927</v>
-      </c>
-      <c r="B579" s="3" t="s">
-        <v>2289</v>
+        <v>1782</v>
+      </c>
+      <c r="B579" s="2" t="s">
+        <v>925</v>
       </c>
       <c r="O579" s="2" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="580" spans="1:15" ht="24.95" customHeight="1">
       <c r="A580" s="2" t="s">
-        <v>929</v>
-      </c>
-      <c r="B580" s="2" t="s">
-        <v>930</v>
+        <v>927</v>
+      </c>
+      <c r="B580" s="3" t="s">
+        <v>2289</v>
       </c>
       <c r="O580" s="2" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
     </row>
     <row r="581" spans="1:15" ht="24.95" customHeight="1">
       <c r="A581" s="2" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>897</v>
+        <v>930</v>
       </c>
       <c r="O581" s="2" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="582" spans="1:15" ht="24.95" customHeight="1">
       <c r="A582" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="B582" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="O582" s="2" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="583" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A583" s="2" t="s">
         <v>935</v>
       </c>
-      <c r="B582" s="2" t="s">
+      <c r="B583" s="2" t="s">
         <v>2290</v>
       </c>
-      <c r="O582" s="2" t="s">
+      <c r="O583" s="2" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="583" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O583" s="2"/>
-    </row>
     <row r="584" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A584" s="2" t="s">
-        <v>941</v>
-      </c>
-      <c r="B584" s="2" t="s">
-        <v>942</v>
-      </c>
-      <c r="O584" s="2" t="s">
-        <v>943</v>
-      </c>
+      <c r="O584" s="2"/>
     </row>
     <row r="585" spans="1:15" ht="24.95" customHeight="1">
       <c r="A585" s="2" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="O585" s="2" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
     </row>
     <row r="586" spans="1:15" ht="24.95" customHeight="1">
       <c r="A586" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="B586" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="O586" s="2" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="587" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A587" s="2" t="s">
         <v>947</v>
       </c>
-      <c r="B586" s="2" t="s">
+      <c r="B587" s="2" t="s">
         <v>948</v>
       </c>
-      <c r="O586" s="2" t="s">
+      <c r="O587" s="2" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="587" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O587" s="2"/>
-    </row>
     <row r="588" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A588" s="2" t="s">
-        <v>1675</v>
-      </c>
-      <c r="B588" s="2" t="s">
-        <v>950</v>
-      </c>
-      <c r="O588" s="2" t="s">
-        <v>951</v>
-      </c>
+      <c r="O588" s="2"/>
     </row>
     <row r="589" spans="1:15" ht="24.95" customHeight="1">
       <c r="A589" s="2" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B589" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="O589" s="2" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="590" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A590" s="2" t="s">
         <v>1676</v>
       </c>
-      <c r="B589" s="2" t="s">
+      <c r="B590" s="2" t="s">
         <v>952</v>
       </c>
-      <c r="O589" s="2" t="s">
+      <c r="O590" s="2" t="s">
         <v>953</v>
       </c>
     </row>
-    <row r="590" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O590" s="2"/>
-    </row>
     <row r="591" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A591" s="2" t="s">
-        <v>954</v>
-      </c>
-      <c r="B591" s="2" t="s">
-        <v>955</v>
-      </c>
-      <c r="O591" s="2" t="s">
-        <v>956</v>
-      </c>
+      <c r="O591" s="2"/>
     </row>
     <row r="592" spans="1:15" ht="24.95" customHeight="1">
       <c r="A592" s="2" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="O592" s="2" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
     </row>
     <row r="593" spans="1:15" ht="24.95" customHeight="1">
       <c r="A593" s="2" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="O593" s="2" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
     </row>
     <row r="594" spans="1:15" ht="24.95" customHeight="1">
       <c r="A594" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="B594" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="O594" s="2" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="595" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A595" s="2" t="s">
         <v>963</v>
       </c>
-      <c r="B594" s="2" t="s">
+      <c r="B595" s="2" t="s">
         <v>964</v>
       </c>
-      <c r="O594" s="2" t="s">
+      <c r="O595" s="2" t="s">
         <v>965</v>
       </c>
     </row>
-    <row r="595" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O595" s="2"/>
-    </row>
     <row r="596" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A596" s="2" t="s">
-        <v>976</v>
-      </c>
-      <c r="B596" s="2" t="s">
-        <v>977</v>
-      </c>
-      <c r="O596" s="2" t="s">
-        <v>978</v>
-      </c>
+      <c r="O596" s="2"/>
     </row>
     <row r="597" spans="1:15" ht="24.95" customHeight="1">
       <c r="A597" s="2" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="B597" s="2" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="O597" s="2" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
     </row>
     <row r="598" spans="1:15" ht="24.95" customHeight="1">
       <c r="A598" s="2" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="O598" s="2" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
     </row>
     <row r="599" spans="1:15" ht="24.95" customHeight="1">
       <c r="A599" s="2" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="O599" s="2" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
     </row>
     <row r="600" spans="1:15" ht="24.95" customHeight="1">
       <c r="A600" s="2" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="O600" s="2" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
     </row>
     <row r="601" spans="1:15" ht="24.95" customHeight="1">
       <c r="A601" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="B601" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="O601" s="2" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="602" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A602" s="2" t="s">
         <v>991</v>
       </c>
-      <c r="B601" s="2" t="s">
+      <c r="B602" s="2" t="s">
         <v>992</v>
       </c>
-      <c r="O601" s="2" t="s">
+      <c r="O602" s="2" t="s">
         <v>993</v>
       </c>
     </row>
-    <row r="602" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O602" s="2"/>
-    </row>
     <row r="603" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A603" s="2" t="s">
-        <v>994</v>
-      </c>
-      <c r="B603" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="O603" s="2" t="s">
-        <v>996</v>
-      </c>
+      <c r="O603" s="2"/>
     </row>
     <row r="604" spans="1:15" ht="24.95" customHeight="1">
       <c r="A604" s="2" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="O604" s="2" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
     </row>
     <row r="605" spans="1:15" ht="24.95" customHeight="1">
       <c r="A605" s="2" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="O605" s="2" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
     </row>
     <row r="606" spans="1:15" ht="24.95" customHeight="1">
       <c r="A606" s="2" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="O606" s="2" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="607" spans="1:15" ht="24.95" customHeight="1">
       <c r="A607" s="2" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>964</v>
+        <v>1004</v>
       </c>
       <c r="O607" s="2" t="s">
-        <v>965</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="608" spans="1:15" ht="24.95" customHeight="1">
       <c r="A608" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B608" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="O608" s="2" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="609" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A609" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="B608" s="2" t="s">
+      <c r="B609" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="O608" s="2" t="s">
+      <c r="O609" s="2" t="s">
         <v>1009</v>
       </c>
     </row>
-    <row r="609" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O609" s="2"/>
-    </row>
     <row r="610" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A610" s="2" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B610" s="2" t="s">
-        <v>1011</v>
-      </c>
-      <c r="O610" s="2" t="s">
-        <v>633</v>
-      </c>
+      <c r="O610" s="2"/>
     </row>
     <row r="611" spans="1:15" ht="24.95" customHeight="1">
       <c r="A611" s="2" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="O611" s="2" t="s">
-        <v>1014</v>
+        <v>633</v>
       </c>
     </row>
     <row r="612" spans="1:15" ht="24.95" customHeight="1">
       <c r="A612" s="2" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="O612" s="2" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="613" spans="1:15" ht="24.95" customHeight="1">
       <c r="A613" s="2" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="O613" s="2" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="614" spans="1:15" ht="24.95" customHeight="1">
       <c r="A614" s="2" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="O614" s="2" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="615" spans="1:15" ht="24.95" customHeight="1">
       <c r="A615" s="2" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="O615" s="2" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="616" spans="1:15" ht="24.95" customHeight="1">
       <c r="A616" s="2" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="O616" s="2" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="617" spans="1:15" ht="24.95" customHeight="1">
       <c r="A617" s="2" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="O617" s="2" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="618" spans="1:15" ht="24.95" customHeight="1">
       <c r="A618" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B618" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="O618" s="2" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="619" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A619" s="2" t="s">
         <v>1033</v>
       </c>
-      <c r="B618" s="2" t="s">
+      <c r="B619" s="2" t="s">
         <v>1034</v>
       </c>
-      <c r="O618" s="2" t="s">
+      <c r="O619" s="2" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="619" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O619" s="2"/>
-    </row>
     <row r="620" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A620" s="2" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B620" s="2" t="s">
-        <v>1037</v>
-      </c>
-      <c r="O620" s="2" t="s">
-        <v>1038</v>
-      </c>
+      <c r="O620" s="2"/>
     </row>
     <row r="621" spans="1:15" ht="24.95" customHeight="1">
       <c r="A621" s="2" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="O621" s="2" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="622" spans="1:15" ht="24.95" customHeight="1">
       <c r="A622" s="2" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="O622" s="2" t="s">
-        <v>2291</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="623" spans="1:15" ht="24.95" customHeight="1">
       <c r="A623" s="2" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="O623" s="2" t="s">
-        <v>1046</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="624" spans="1:15" ht="24.95" customHeight="1">
       <c r="A624" s="2" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="O624" s="2" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="625" spans="1:15" ht="24.95" customHeight="1">
       <c r="A625" s="2" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>66</v>
+        <v>1048</v>
       </c>
       <c r="O625" s="2" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="626" spans="1:15" ht="24.95" customHeight="1">
       <c r="A626" s="2" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="B626" s="2" t="s">
-        <v>1053</v>
+        <v>66</v>
       </c>
       <c r="O626" s="2" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="627" spans="1:15" ht="24.95" customHeight="1">
       <c r="A627" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B627" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="O627" s="2" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="628" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A628" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="B627" s="2" t="s">
+      <c r="B628" s="2" t="s">
         <v>1056</v>
       </c>
-      <c r="O627" s="2" t="s">
+      <c r="O628" s="2" t="s">
         <v>1057</v>
       </c>
     </row>
-    <row r="628" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O628" s="2"/>
-    </row>
     <row r="629" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A629" s="2" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B629" s="2" t="s">
-        <v>1764</v>
-      </c>
-      <c r="O629" s="2" t="s">
-        <v>1059</v>
-      </c>
+      <c r="O629" s="2"/>
     </row>
     <row r="630" spans="1:15" ht="24.95" customHeight="1">
       <c r="A630" s="2" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="O630" s="2" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="631" spans="1:15" ht="24.95" customHeight="1">
       <c r="A631" s="2" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>1772</v>
+        <v>1765</v>
       </c>
       <c r="O631" s="2" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="632" spans="1:15" ht="24.95" customHeight="1">
       <c r="A632" s="2" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="B632" s="2" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="O632" s="2" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="633" spans="1:15" ht="24.95" customHeight="1">
       <c r="A633" s="2" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>1768</v>
+        <v>1771</v>
       </c>
       <c r="O633" s="2" t="s">
-        <v>1710</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="634" spans="1:15" ht="24.95" customHeight="1">
       <c r="A634" s="2" t="s">
-        <v>1769</v>
+        <v>1066</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="O634" s="2" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="635" spans="1:15" ht="24.95" customHeight="1">
       <c r="A635" s="2" t="s">
-        <v>1067</v>
+        <v>1769</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>1766</v>
+        <v>1770</v>
       </c>
       <c r="O635" s="2" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="636" spans="1:15" ht="24.95" customHeight="1">
       <c r="A636" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B636" s="2" t="s">
+        <v>1766</v>
+      </c>
+      <c r="O636" s="2" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="637" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A637" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="B636" s="2" t="s">
+      <c r="B637" s="2" t="s">
         <v>1767</v>
       </c>
-      <c r="O636" s="2" t="s">
+      <c r="O637" s="2" t="s">
         <v>1707</v>
       </c>
     </row>
-    <row r="637" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O637" s="2"/>
-    </row>
     <row r="638" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A638" s="2" t="s">
-        <v>1832</v>
-      </c>
-      <c r="B638" s="2" t="s">
-        <v>1822</v>
-      </c>
-      <c r="O638" s="2" t="s">
-        <v>1839</v>
-      </c>
+      <c r="O638" s="2"/>
     </row>
     <row r="639" spans="1:15" ht="24.95" customHeight="1">
       <c r="A639" s="2" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>1835</v>
+        <v>1822</v>
       </c>
       <c r="O639" s="2" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="640" spans="1:15" ht="24.95" customHeight="1">
       <c r="A640" s="2" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="O640" s="2" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="641" spans="1:15" ht="24.95" customHeight="1">
       <c r="A641" s="2" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B641" s="2" t="s">
+        <v>1836</v>
+      </c>
+      <c r="O641" s="2" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="642" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A642" s="2" t="s">
         <v>1840</v>
       </c>
-      <c r="B641" s="2" t="s">
+      <c r="B642" s="2" t="s">
         <v>1841</v>
       </c>
-      <c r="O641" s="2" t="s">
+      <c r="O642" s="2" t="s">
         <v>1842</v>
       </c>
     </row>
-    <row r="642" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O642" s="2"/>
-    </row>
     <row r="643" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A643" s="2" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B643" s="2" t="s">
-        <v>1070</v>
-      </c>
-      <c r="O643" s="2" t="s">
-        <v>3030</v>
-      </c>
+      <c r="O643" s="2"/>
     </row>
     <row r="644" spans="1:15" ht="24.95" customHeight="1">
       <c r="A644" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B644" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="O644" s="2" t="s">
+        <v>3030</v>
+      </c>
+    </row>
+    <row r="645" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A645" s="2" t="s">
         <v>1071</v>
       </c>
-      <c r="B644" s="2" t="s">
+      <c r="B645" s="2" t="s">
         <v>1072</v>
       </c>
-      <c r="O644" s="2" t="s">
+      <c r="O645" s="2" t="s">
         <v>1073</v>
       </c>
     </row>
-    <row r="645" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O645" s="2"/>
-    </row>
     <row r="646" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A646" s="2" t="s">
-        <v>1074</v>
-      </c>
-      <c r="B646" s="2" t="s">
-        <v>1075</v>
-      </c>
-      <c r="O646" s="2" t="s">
-        <v>1076</v>
-      </c>
+      <c r="O646" s="2"/>
     </row>
     <row r="647" spans="1:15" ht="24.95" customHeight="1">
       <c r="A647" s="2" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="O647" s="2" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="648" spans="1:15" ht="24.95" customHeight="1">
       <c r="A648" s="2" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="O648" s="2" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="649" spans="1:15" ht="24.95" customHeight="1">
       <c r="A649" s="2" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="O649" s="2" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="650" spans="1:15" ht="24.95" customHeight="1">
       <c r="A650" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B650" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="O650" s="2" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="651" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A651" s="2" t="s">
         <v>1086</v>
       </c>
-      <c r="B650" s="2" t="s">
+      <c r="B651" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="O650" s="2" t="s">
+      <c r="O651" s="2" t="s">
         <v>1088</v>
       </c>
     </row>
-    <row r="651" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O651" s="2"/>
-    </row>
     <row r="652" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A652" s="2" t="s">
-        <v>1089</v>
-      </c>
-      <c r="B652" s="2" t="s">
-        <v>1090</v>
-      </c>
-      <c r="O652" s="2" t="s">
-        <v>1091</v>
-      </c>
+      <c r="O652" s="2"/>
     </row>
     <row r="653" spans="1:15" ht="24.95" customHeight="1">
       <c r="A653" s="2" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="O653" s="2" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="654" spans="1:15" ht="24.95" customHeight="1">
       <c r="A654" s="2" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="O654" s="2" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="655" spans="1:15" ht="24.95" customHeight="1">
       <c r="A655" s="2" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="O655" s="2" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="656" spans="1:15" ht="24.95" customHeight="1">
       <c r="A656" s="2" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="O656" s="2" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="657" spans="1:15" ht="24.95" customHeight="1">
       <c r="A657" s="2" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="O657" s="2" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="658" spans="1:15" ht="24.95" customHeight="1">
       <c r="A658" s="2" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="B658" s="2" t="s">
-        <v>964</v>
+        <v>1105</v>
       </c>
       <c r="O658" s="2" t="s">
-        <v>965</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="659" spans="1:15" ht="24.95" customHeight="1">
       <c r="A659" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B659" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="O659" s="2" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="660" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A660" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="B659" s="2" t="s">
+      <c r="B660" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="O659" s="2" t="s">
+      <c r="O660" s="2" t="s">
         <v>1110</v>
       </c>
     </row>
-    <row r="660" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O660" s="2"/>
-    </row>
     <row r="661" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A661" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="B661" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="O661" s="2" t="s">
-        <v>1113</v>
-      </c>
+      <c r="O661" s="2"/>
     </row>
     <row r="662" spans="1:15" ht="24.95" customHeight="1">
       <c r="A662" s="2" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="O662" s="2" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="663" spans="1:15" ht="24.95" customHeight="1">
       <c r="A663" s="2" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="O663" s="2" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="664" spans="1:15" ht="24.95" customHeight="1">
       <c r="A664" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B664" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="O664" s="2" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="665" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A665" s="2" t="s">
         <v>1120</v>
       </c>
-      <c r="B664" s="2" t="s">
+      <c r="B665" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="O664" s="2" t="s">
+      <c r="O665" s="2" t="s">
         <v>1122</v>
       </c>
     </row>
-    <row r="665" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O665" s="2"/>
-    </row>
     <row r="666" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A666" s="2" t="s">
-        <v>1123</v>
-      </c>
-      <c r="B666" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="O666" s="2" t="s">
-        <v>1125</v>
-      </c>
+      <c r="O666" s="2"/>
     </row>
     <row r="667" spans="1:15" ht="24.95" customHeight="1">
       <c r="A667" s="2" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>599</v>
+        <v>1124</v>
       </c>
       <c r="O667" s="2" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="668" spans="1:15" ht="24.95" customHeight="1">
       <c r="A668" s="2" t="s">
-        <v>2462</v>
+        <v>1126</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="O668" s="2" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="669" spans="1:15" ht="24.95" customHeight="1">
       <c r="A669" s="2" t="s">
+        <v>2462</v>
+      </c>
+      <c r="B669" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="O669" s="2" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="670" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A670" s="2" t="s">
         <v>1129</v>
       </c>
-      <c r="B669" s="2" t="s">
+      <c r="B670" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="O669" s="2" t="s">
+      <c r="O670" s="2" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="670" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O670" s="2"/>
-    </row>
     <row r="671" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A671" s="2" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B671" s="2" t="s">
-        <v>920</v>
-      </c>
-      <c r="O671" s="2" t="s">
-        <v>3086</v>
-      </c>
+      <c r="O671" s="2"/>
     </row>
     <row r="672" spans="1:15" ht="24.95" customHeight="1">
       <c r="A672" s="2" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>1132</v>
+        <v>920</v>
       </c>
       <c r="O672" s="2" t="s">
-        <v>984</v>
+        <v>3086</v>
       </c>
     </row>
     <row r="673" spans="1:15" ht="24.95" customHeight="1">
       <c r="A673" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B673" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="O673" s="2" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="674" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A674" s="2" t="s">
         <v>1133</v>
       </c>
-      <c r="O673" s="2" t="s">
+      <c r="O674" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="674" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O674" s="2"/>
-    </row>
     <row r="675" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A675" s="2" t="s">
-        <v>2525</v>
-      </c>
-      <c r="O675" s="2" t="s">
-        <v>2527</v>
-      </c>
+      <c r="O675" s="2"/>
     </row>
     <row r="676" spans="1:15" ht="24.95" customHeight="1">
       <c r="A676" s="2" t="s">
+        <v>2525</v>
+      </c>
+      <c r="O676" s="2" t="s">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="677" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A677" s="2" t="s">
         <v>2526</v>
       </c>
-      <c r="O676" s="2" t="s">
+      <c r="O677" s="2" t="s">
         <v>2528</v>
       </c>
     </row>
-    <row r="677" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O677" s="2"/>
-    </row>
     <row r="678" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A678" s="2" t="s">
-        <v>1135</v>
-      </c>
-      <c r="B678" s="2" t="s">
-        <v>1136</v>
-      </c>
-      <c r="O678" s="2" t="s">
-        <v>1137</v>
-      </c>
+      <c r="O678" s="2"/>
     </row>
     <row r="679" spans="1:15" ht="24.95" customHeight="1">
       <c r="A679" s="2" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="O679" s="2" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="680" spans="1:15" ht="24.95" customHeight="1">
       <c r="A680" s="2" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>964</v>
+        <v>1139</v>
       </c>
       <c r="O680" s="2" t="s">
-        <v>965</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="681" spans="1:15" ht="24.95" customHeight="1">
       <c r="A681" s="2" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>1143</v>
+        <v>964</v>
       </c>
       <c r="O681" s="2" t="s">
-        <v>1144</v>
+        <v>965</v>
       </c>
     </row>
     <row r="682" spans="1:15" ht="24.95" customHeight="1">
       <c r="A682" s="2" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="O682" s="2" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="683" spans="1:15" ht="24.95" customHeight="1">
       <c r="A683" s="2" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1821</v>
+        <v>1146</v>
       </c>
       <c r="O683" s="2" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="684" spans="1:15" ht="24.95" customHeight="1">
       <c r="A684" s="2" t="s">
-        <v>3027</v>
+        <v>1148</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1151</v>
+        <v>1821</v>
       </c>
       <c r="O684" s="2" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="685" spans="1:15" ht="24.95" customHeight="1">
       <c r="A685" s="2" t="s">
+        <v>3027</v>
+      </c>
+      <c r="B685" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="O685" s="2" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="686" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A686" s="2" t="s">
         <v>1155</v>
       </c>
-      <c r="B685" s="2" t="s">
+      <c r="B686" s="2" t="s">
         <v>1156</v>
       </c>
-      <c r="O685" s="2" t="s">
+      <c r="O686" s="2" t="s">
         <v>1157</v>
       </c>
     </row>
-    <row r="686" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O686" s="2"/>
-    </row>
     <row r="687" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A687" s="2" t="s">
-        <v>3052</v>
-      </c>
-      <c r="O687" s="2" t="s">
-        <v>3057</v>
-      </c>
+      <c r="O687" s="2"/>
     </row>
     <row r="688" spans="1:15" ht="24.95" customHeight="1">
       <c r="A688" s="2" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="O688" s="2" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="689" spans="1:15" ht="24.95" customHeight="1">
       <c r="A689" s="2" t="s">
-        <v>3067</v>
+        <v>3053</v>
       </c>
       <c r="O689" s="2" t="s">
-        <v>3068</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="690" spans="1:15" ht="24.95" customHeight="1">
       <c r="A690" s="2" t="s">
-        <v>3054</v>
+        <v>3067</v>
       </c>
       <c r="O690" s="2" t="s">
-        <v>3059</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="691" spans="1:15" ht="24.95" customHeight="1">
       <c r="A691" s="2" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="O691" s="2" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="692" spans="1:15" ht="24.95" customHeight="1">
       <c r="A692" s="2" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="O692" s="2" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="693" spans="1:15" ht="24.95" customHeight="1">
       <c r="A693" s="2" t="s">
+        <v>3056</v>
+      </c>
+      <c r="O693" s="2" t="s">
+        <v>3061</v>
+      </c>
+    </row>
+    <row r="694" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A694" s="2" t="s">
         <v>3065</v>
       </c>
-      <c r="O693" s="2" t="s">
+      <c r="O694" s="2" t="s">
         <v>3087</v>
       </c>
     </row>
-    <row r="694" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O694" s="2"/>
-    </row>
     <row r="695" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A695" s="2" t="s">
+      <c r="O695" s="2"/>
+    </row>
+    <row r="696" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A696" s="2" t="s">
         <v>1158</v>
       </c>
-      <c r="B695" s="2" t="s">
+      <c r="B696" s="2" t="s">
         <v>1761</v>
       </c>
-      <c r="O695" s="2" t="s">
+      <c r="O696" s="2" t="s">
         <v>1159</v>
       </c>
     </row>
-    <row r="696" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O696" s="2"/>
-    </row>
     <row r="697" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A697" s="2" t="s">
+      <c r="O697" s="2"/>
+    </row>
+    <row r="698" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A698" s="2" t="s">
         <v>1160</v>
       </c>
-      <c r="B697" s="2" t="s">
+      <c r="B698" s="2" t="s">
         <v>1161</v>
       </c>
-      <c r="O697" s="2" t="s">
+      <c r="O698" s="2" t="s">
         <v>1162</v>
       </c>
     </row>
-    <row r="698" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O698" s="2"/>
-    </row>
     <row r="699" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A699" s="2" t="s">
-        <v>3174</v>
-      </c>
-      <c r="O699" s="2" t="s">
-        <v>3175</v>
-      </c>
+      <c r="O699" s="2"/>
     </row>
     <row r="700" spans="1:15" ht="24.95" customHeight="1">
       <c r="A700" s="2" t="s">
-        <v>2989</v>
+        <v>3174</v>
       </c>
       <c r="O700" s="2" t="s">
-        <v>2991</v>
+        <v>3175</v>
       </c>
     </row>
     <row r="701" spans="1:15" ht="24.95" customHeight="1">
       <c r="A701" s="2" t="s">
+        <v>2989</v>
+      </c>
+      <c r="O701" s="2" t="s">
+        <v>2991</v>
+      </c>
+    </row>
+    <row r="702" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A702" s="2" t="s">
         <v>2990</v>
       </c>
-      <c r="O701" s="2" t="s">
+      <c r="O702" s="2" t="s">
         <v>2992</v>
       </c>
     </row>
-    <row r="702" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O702" s="2"/>
-    </row>
     <row r="703" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A703" s="2" t="s">
-        <v>1163</v>
-      </c>
-      <c r="B703" s="2" t="s">
-        <v>1164</v>
-      </c>
-      <c r="O703" s="2" t="s">
-        <v>1165</v>
-      </c>
+      <c r="O703" s="2"/>
     </row>
     <row r="704" spans="1:15" ht="24.95" customHeight="1">
       <c r="A704" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B704" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="O704" s="2" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="705" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A705" s="2" t="s">
         <v>1166</v>
       </c>
-      <c r="B704" s="2" t="s">
+      <c r="B705" s="2" t="s">
         <v>1167</v>
       </c>
-      <c r="O704" s="2" t="s">
+      <c r="O705" s="2" t="s">
         <v>1168</v>
       </c>
     </row>
-    <row r="705" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O705" s="2"/>
-    </row>
     <row r="706" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A706" s="2" t="s">
+      <c r="O706" s="2"/>
+    </row>
+    <row r="707" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A707" s="2" t="s">
         <v>1169</v>
       </c>
-      <c r="B706" s="2" t="s">
+      <c r="B707" s="2" t="s">
         <v>1170</v>
       </c>
-      <c r="O706" s="2" t="s">
+      <c r="O707" s="2" t="s">
         <v>1171</v>
       </c>
     </row>
-    <row r="707" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O707" s="2"/>
-    </row>
     <row r="708" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A708" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="O708" s="2" t="s">
-        <v>1173</v>
-      </c>
+      <c r="O708" s="2"/>
     </row>
     <row r="709" spans="1:15" ht="24.95" customHeight="1">
       <c r="A709" s="2" t="s">
-        <v>1174</v>
-      </c>
-      <c r="B709" s="2" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="O709" s="2" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="710" spans="1:15" ht="24.95" customHeight="1">
       <c r="A710" s="2" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="O710" s="2" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="711" spans="1:15" ht="24.95" customHeight="1">
       <c r="A711" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B711" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="O711" s="2" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="712" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A712" s="2" t="s">
         <v>1180</v>
       </c>
-      <c r="B711" s="2" t="s">
+      <c r="B712" s="2" t="s">
         <v>1181</v>
       </c>
-      <c r="O711" s="2" t="s">
+      <c r="O712" s="2" t="s">
         <v>1182</v>
       </c>
     </row>
-    <row r="712" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O712" s="2"/>
-    </row>
     <row r="713" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A713" s="2" t="s">
-        <v>1183</v>
-      </c>
-      <c r="B713" s="2" t="s">
-        <v>1184</v>
-      </c>
-      <c r="O713" s="2" t="s">
-        <v>1185</v>
-      </c>
+      <c r="O713" s="2"/>
     </row>
     <row r="714" spans="1:15" ht="24.95" customHeight="1">
       <c r="A714" s="2" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="O714" s="2" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="715" spans="1:15" ht="24.95" customHeight="1">
       <c r="A715" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B715" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="O715" s="2" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="716" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A716" s="2" t="s">
         <v>1189</v>
       </c>
-      <c r="B715" s="2" t="s">
+      <c r="B716" s="2" t="s">
         <v>1190</v>
       </c>
-      <c r="O715" s="2" t="s">
+      <c r="O716" s="2" t="s">
         <v>1191</v>
       </c>
     </row>
-    <row r="716" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O716" s="2"/>
-    </row>
     <row r="717" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A717" s="2" t="s">
-        <v>1192</v>
-      </c>
-      <c r="B717" s="2" t="s">
-        <v>1193</v>
-      </c>
-      <c r="O717" s="2" t="s">
-        <v>1194</v>
-      </c>
+      <c r="O717" s="2"/>
     </row>
     <row r="718" spans="1:15" ht="24.95" customHeight="1">
       <c r="A718" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B718" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="O718" s="2" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="719" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A719" s="2" t="s">
         <v>1195</v>
       </c>
-      <c r="B718" s="2" t="s">
+      <c r="B719" s="2" t="s">
         <v>1196</v>
       </c>
-      <c r="O718" s="2" t="s">
+      <c r="O719" s="2" t="s">
         <v>1197</v>
       </c>
     </row>
-    <row r="719" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O719" s="2"/>
-    </row>
     <row r="720" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A720" s="2" t="s">
-        <v>1198</v>
-      </c>
-      <c r="B720" s="2" t="s">
-        <v>1199</v>
-      </c>
-      <c r="O720" s="2" t="s">
-        <v>1200</v>
-      </c>
+      <c r="O720" s="2"/>
     </row>
     <row r="721" spans="1:15" ht="24.95" customHeight="1">
       <c r="A721" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B721" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="O721" s="2" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="722" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A722" s="2" t="s">
         <v>1201</v>
       </c>
-      <c r="B721" s="2" t="s">
+      <c r="B722" s="2" t="s">
         <v>1202</v>
       </c>
-      <c r="O721" s="2" t="s">
+      <c r="O722" s="2" t="s">
         <v>1203</v>
       </c>
     </row>
-    <row r="722" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O722" s="2"/>
-    </row>
-    <row r="723" spans="1:15" ht="33">
-      <c r="A723" s="2" t="s">
+    <row r="723" spans="1:15" ht="24.95" customHeight="1">
+      <c r="O723" s="2"/>
+    </row>
+    <row r="724" spans="1:15" ht="33">
+      <c r="A724" s="2" t="s">
         <v>2966</v>
       </c>
-      <c r="O723" s="3" t="s">
+      <c r="O724" s="3" t="s">
         <v>2967</v>
       </c>
     </row>
-    <row r="724" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O724" s="2"/>
-    </row>
     <row r="725" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A725" s="2" t="s">
+      <c r="O725" s="2"/>
+    </row>
+    <row r="726" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A726" s="2" t="s">
         <v>1204</v>
       </c>
-      <c r="O725" s="2" t="s">
+      <c r="O726" s="2" t="s">
         <v>1773</v>
       </c>
     </row>
-    <row r="726" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O726" s="2"/>
-    </row>
     <row r="727" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A727" s="2" t="s">
-        <v>1205</v>
-      </c>
-      <c r="B727" s="2" t="s">
-        <v>1206</v>
-      </c>
-      <c r="O727" s="2" t="s">
-        <v>1207</v>
-      </c>
+      <c r="O727" s="2"/>
     </row>
     <row r="728" spans="1:15" ht="24.95" customHeight="1">
       <c r="A728" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B728" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="O728" s="2" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="729" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A729" s="2" t="s">
         <v>1208</v>
       </c>
-      <c r="B728" s="2" t="s">
+      <c r="B729" s="2" t="s">
         <v>1209</v>
       </c>
-      <c r="O728" s="2" t="s">
+      <c r="O729" s="2" t="s">
         <v>1210</v>
       </c>
     </row>
-    <row r="729" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O729" s="2"/>
-    </row>
     <row r="730" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A730" s="2" t="s">
+      <c r="O730" s="2"/>
+    </row>
+    <row r="731" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A731" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="B730" s="2" t="s">
+      <c r="B731" s="2" t="s">
         <v>1212</v>
       </c>
-      <c r="O730" s="2" t="s">
+      <c r="O731" s="2" t="s">
         <v>1213</v>
       </c>
     </row>
-    <row r="731" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O731" s="2"/>
-    </row>
     <row r="732" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A732" s="2" t="s">
-        <v>1214</v>
-      </c>
-      <c r="B732" s="2" t="s">
-        <v>1215</v>
-      </c>
-      <c r="O732" s="2" t="s">
-        <v>1216</v>
-      </c>
+      <c r="O732" s="2"/>
     </row>
     <row r="733" spans="1:15" ht="24.95" customHeight="1">
       <c r="A733" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B733" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="O733" s="2" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="734" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A734" s="2" t="s">
         <v>1217</v>
       </c>
-      <c r="B733" s="2" t="s">
+      <c r="B734" s="2" t="s">
         <v>1218</v>
       </c>
-      <c r="O733" s="2" t="s">
+      <c r="O734" s="2" t="s">
         <v>1219</v>
       </c>
     </row>
-    <row r="734" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O734" s="2"/>
-    </row>
     <row r="735" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A735" s="2" t="s">
+      <c r="O735" s="2"/>
+    </row>
+    <row r="736" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A736" s="2" t="s">
         <v>1220</v>
       </c>
-      <c r="B735" s="2" t="s">
+      <c r="B736" s="2" t="s">
         <v>1763</v>
       </c>
-      <c r="O735" s="2" t="s">
+      <c r="O736" s="2" t="s">
         <v>1221</v>
       </c>
     </row>
-    <row r="736" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O736" s="2"/>
-    </row>
     <row r="737" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A737" s="2" t="s">
+      <c r="O737" s="2"/>
+    </row>
+    <row r="738" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A738" s="2" t="s">
         <v>3178</v>
       </c>
-      <c r="O737" s="2" t="s">
+      <c r="O738" s="2" t="s">
         <v>3180</v>
       </c>
     </row>
-    <row r="738" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O738" s="2"/>
-    </row>
     <row r="739" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A739" s="2" t="s">
+      <c r="O739" s="2"/>
+    </row>
+    <row r="740" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A740" s="2" t="s">
         <v>1222</v>
       </c>
-      <c r="O739" s="2" t="s">
+      <c r="O740" s="2" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="740" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O740" s="2"/>
-    </row>
     <row r="741" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A741" s="2" t="s">
-        <v>3176</v>
-      </c>
-      <c r="O741" s="2" t="s">
-        <v>3177</v>
-      </c>
+      <c r="O741" s="2"/>
     </row>
     <row r="742" spans="1:15" ht="24.95" customHeight="1">
       <c r="A742" s="2" t="s">
+        <v>3176</v>
+      </c>
+      <c r="O742" s="2" t="s">
+        <v>3177</v>
+      </c>
+    </row>
+    <row r="743" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A743" s="2" t="s">
         <v>1223</v>
       </c>
-      <c r="B742" s="2" t="s">
+      <c r="B743" s="2" t="s">
         <v>1762</v>
       </c>
-      <c r="O742" s="2" t="s">
+      <c r="O743" s="2" t="s">
         <v>1224</v>
       </c>
     </row>
-    <row r="743" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O743" s="2"/>
-    </row>
     <row r="744" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A744" s="2" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B744" s="2" t="s">
-        <v>1226</v>
-      </c>
-      <c r="O744" s="2" t="s">
-        <v>1227</v>
-      </c>
+      <c r="O744" s="2"/>
     </row>
     <row r="745" spans="1:15" ht="24.95" customHeight="1">
       <c r="A745" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B745" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="O745" s="2" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="746" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A746" s="2" t="s">
         <v>1228</v>
       </c>
-      <c r="B745" s="2" t="s">
+      <c r="B746" s="2" t="s">
         <v>1229</v>
       </c>
-      <c r="O745" s="2" t="s">
+      <c r="O746" s="2" t="s">
         <v>1230</v>
       </c>
     </row>
-    <row r="746" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O746" s="2"/>
-    </row>
     <row r="747" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A747" s="2" t="s">
-        <v>1231</v>
-      </c>
-      <c r="B747" s="2" t="s">
-        <v>1232</v>
-      </c>
-      <c r="O747" s="2" t="s">
-        <v>1233</v>
-      </c>
+      <c r="O747" s="2"/>
     </row>
     <row r="748" spans="1:15" ht="24.95" customHeight="1">
       <c r="A748" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B748" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="O748" s="2" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="749" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A749" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="B748" s="2" t="s">
+      <c r="B749" s="2" t="s">
         <v>1235</v>
       </c>
-      <c r="O748" s="2" t="s">
+      <c r="O749" s="2" t="s">
         <v>1236</v>
       </c>
     </row>
-    <row r="749" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O749" s="2"/>
-    </row>
     <row r="750" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A750" s="2" t="s">
-        <v>1237</v>
-      </c>
-      <c r="B750" s="2" t="s">
-        <v>1238</v>
-      </c>
-      <c r="O750" s="2" t="s">
-        <v>1239</v>
-      </c>
+      <c r="O750" s="2"/>
     </row>
     <row r="751" spans="1:15" ht="24.95" customHeight="1">
       <c r="A751" s="2" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="B751" s="2" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="O751" s="2" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="752" spans="1:15" ht="24.95" customHeight="1">
       <c r="A752" s="2" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="B752" s="2" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="O752" s="2" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="753" spans="1:15" ht="24.95" customHeight="1">
       <c r="A753" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B753" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="O753" s="2" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="754" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A754" s="2" t="s">
         <v>1246</v>
       </c>
-      <c r="B753" s="2" t="s">
+      <c r="B754" s="2" t="s">
         <v>1247</v>
       </c>
-      <c r="O753" s="2" t="s">
+      <c r="O754" s="2" t="s">
         <v>1248</v>
       </c>
     </row>
-    <row r="754" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O754" s="2"/>
-    </row>
     <row r="755" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A755" s="2" t="s">
-        <v>1600</v>
-      </c>
-      <c r="O755" s="2" t="s">
-        <v>1602</v>
-      </c>
+      <c r="O755" s="2"/>
     </row>
     <row r="756" spans="1:15" ht="24.95" customHeight="1">
       <c r="A756" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="O756" s="2" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="757" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A757" s="2" t="s">
         <v>1601</v>
       </c>
-      <c r="O756" s="3" t="s">
+      <c r="O757" s="3" t="s">
         <v>1603</v>
       </c>
-    </row>
-    <row r="757" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O757" s="2"/>
     </row>
     <row r="758" spans="1:15" ht="24.95" customHeight="1">
       <c r="O758" s="2"/>
@@ -19487,8 +19501,8 @@
     <row r="853" spans="15:15" ht="24.95" customHeight="1">
       <c r="O853" s="2"/>
     </row>
-    <row r="855" spans="15:15" ht="24.95" customHeight="1">
-      <c r="O855" s="2"/>
+    <row r="854" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O854" s="2"/>
     </row>
     <row r="856" spans="15:15" ht="24.95" customHeight="1">
       <c r="O856" s="2"/>
@@ -20621,113 +20635,113 @@
     <row r="1232" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1232" s="2"/>
     </row>
-    <row r="1233" spans="1:15" ht="24.95" customHeight="1">
+    <row r="1233" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1233" s="2"/>
     </row>
-    <row r="1234" spans="1:15" ht="24.95" customHeight="1">
+    <row r="1234" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1234" s="2"/>
     </row>
-    <row r="1235" spans="1:15" ht="24.95" customHeight="1">
+    <row r="1235" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1235" s="2"/>
     </row>
-    <row r="1236" spans="1:15" ht="24.95" customHeight="1">
+    <row r="1236" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1236" s="2"/>
     </row>
-    <row r="1237" spans="1:15" ht="24.95" customHeight="1">
+    <row r="1237" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1237" s="2"/>
     </row>
-    <row r="1238" spans="1:15" ht="24.95" customHeight="1">
+    <row r="1238" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1238" s="2"/>
     </row>
-    <row r="1239" spans="1:15" ht="24.95" customHeight="1">
+    <row r="1239" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1239" s="2"/>
     </row>
-    <row r="1240" spans="1:15" ht="24.95" customHeight="1">
+    <row r="1240" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1240" s="2"/>
     </row>
-    <row r="1241" spans="1:15" ht="24.95" customHeight="1">
+    <row r="1241" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1241" s="2"/>
     </row>
-    <row r="1242" spans="1:15" ht="24.95" customHeight="1">
+    <row r="1242" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1242" s="2"/>
     </row>
-    <row r="1243" spans="1:15" ht="24.95" customHeight="1">
+    <row r="1243" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1243" s="2"/>
     </row>
-    <row r="1244" spans="1:15" ht="24.95" customHeight="1">
+    <row r="1244" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1244" s="2"/>
     </row>
-    <row r="1245" spans="1:15" ht="24.95" customHeight="1">
+    <row r="1245" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1245" s="2"/>
     </row>
-    <row r="1246" spans="1:15" ht="24.95" customHeight="1">
+    <row r="1246" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1246" s="2"/>
     </row>
-    <row r="1247" spans="1:15" ht="24.95" customHeight="1">
+    <row r="1247" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1247" s="2"/>
     </row>
-    <row r="1248" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A1248" s="5"/>
-      <c r="B1248" s="5"/>
-      <c r="D1248" s="5"/>
-      <c r="E1248" s="5"/>
-      <c r="F1248" s="5"/>
-      <c r="G1248" s="5"/>
-      <c r="H1248" s="5"/>
-      <c r="I1248" s="5"/>
-      <c r="J1248" s="5"/>
-      <c r="K1248" s="5"/>
-      <c r="L1248" s="5"/>
-      <c r="M1248" s="5"/>
-      <c r="N1248" s="5"/>
-      <c r="O1248" s="6"/>
-    </row>
-    <row r="1249" spans="15:15" ht="24.95" customHeight="1">
-      <c r="O1249" s="2"/>
-    </row>
-    <row r="1250" spans="15:15" ht="24.95" customHeight="1">
+    <row r="1248" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1248" s="2"/>
+    </row>
+    <row r="1249" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A1249" s="5"/>
+      <c r="B1249" s="5"/>
+      <c r="D1249" s="5"/>
+      <c r="E1249" s="5"/>
+      <c r="F1249" s="5"/>
+      <c r="G1249" s="5"/>
+      <c r="H1249" s="5"/>
+      <c r="I1249" s="5"/>
+      <c r="J1249" s="5"/>
+      <c r="K1249" s="5"/>
+      <c r="L1249" s="5"/>
+      <c r="M1249" s="5"/>
+      <c r="N1249" s="5"/>
+      <c r="O1249" s="6"/>
+    </row>
+    <row r="1250" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1250" s="2"/>
     </row>
-    <row r="1251" spans="15:15" ht="24.95" customHeight="1">
+    <row r="1251" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1251" s="2"/>
     </row>
-    <row r="1252" spans="15:15" ht="24.95" customHeight="1">
+    <row r="1252" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1252" s="2"/>
     </row>
-    <row r="1253" spans="15:15" ht="24.95" customHeight="1">
+    <row r="1253" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1253" s="2"/>
     </row>
-    <row r="1254" spans="15:15" ht="24.95" customHeight="1">
+    <row r="1254" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1254" s="2"/>
     </row>
-    <row r="1255" spans="15:15" ht="24.95" customHeight="1">
+    <row r="1255" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1255" s="2"/>
     </row>
-    <row r="1256" spans="15:15" ht="24.95" customHeight="1">
+    <row r="1256" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1256" s="2"/>
     </row>
-    <row r="1257" spans="15:15" ht="24.95" customHeight="1">
+    <row r="1257" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1257" s="2"/>
     </row>
-    <row r="1258" spans="15:15" ht="24.95" customHeight="1">
+    <row r="1258" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1258" s="2"/>
     </row>
-    <row r="1259" spans="15:15" ht="24.95" customHeight="1">
+    <row r="1259" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1259" s="2"/>
     </row>
-    <row r="1260" spans="15:15" ht="24.95" customHeight="1">
+    <row r="1260" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1260" s="2"/>
     </row>
-    <row r="1261" spans="15:15" ht="24.95" customHeight="1">
+    <row r="1261" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1261" s="2"/>
     </row>
-    <row r="1262" spans="15:15" ht="24.95" customHeight="1">
+    <row r="1262" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1262" s="2"/>
     </row>
-    <row r="1263" spans="15:15" ht="24.95" customHeight="1">
+    <row r="1263" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1263" s="2"/>
     </row>
-    <row r="1264" spans="15:15" ht="24.95" customHeight="1">
+    <row r="1264" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1264" s="2"/>
     </row>
     <row r="1265" spans="15:15" ht="24.95" customHeight="1">
@@ -22197,8 +22211,11 @@
     <row r="1753" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1753" s="2"/>
     </row>
+    <row r="1754" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1754" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="O1:O1456" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="O1:O1457" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Among Us code\TheOtherUs\TheOtherUs-Edited-Lite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E9EE5B-DBF8-494A-A3EE-683FC2D092D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E41F910-ED90-4603-8980-6A2B129424ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="1200" windowWidth="25755" windowHeight="14910" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="720" yWindow="1200" windowWidth="25755" windowHeight="14910" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Options" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Role Description" sheetId="11" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Options!$O$1:$O$1457</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Options!$O$1:$O$1460</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3558" uniqueCount="3237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3575" uniqueCount="3253">
   <si>
     <t>English</t>
   </si>
@@ -11534,6 +11534,66 @@
   </si>
   <si>
     <t>未知阵营</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gunsmith</t>
+  </si>
+  <si>
+    <t>GunsmithIntroDesc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GunsmithShortDesc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>快枪手</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>隐忍, 爆发！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>存下子弹, 等待时机击杀玩家</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GunsmithFullDesc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以在击杀冷却完毕后手动存下子弹，可以随时取出子弹。
+随时可以取出子弹，取出子弹后会将击杀按钮重置冷却。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>gunsmithSetKillCooldown</t>
+  </si>
+  <si>
+    <t>gunsmithMaxChangeCount</t>
+  </si>
+  <si>
+    <t>取出子弹时重置的冷却</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>弹匣中能存下的子弹上限</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>gunsmithAddBullets</t>
+  </si>
+  <si>
+    <t>gunsmithGetBullets</t>
+  </si>
+  <si>
+    <t>取出</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>存储</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -12133,7 +12193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1754"/>
+  <dimension ref="A1:Q1757"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40.375" style="2" customWidth="1"/>
@@ -15997,109 +16057,103 @@
     </row>
     <row r="393" spans="1:15" ht="24.95" customHeight="1">
       <c r="A393" s="2" t="s">
-        <v>2286</v>
-      </c>
-      <c r="B393" s="2" t="s">
-        <v>2285</v>
+        <v>3245</v>
       </c>
       <c r="O393" s="2" t="s">
-        <v>768</v>
+        <v>3247</v>
       </c>
     </row>
     <row r="394" spans="1:15" ht="24.95" customHeight="1">
       <c r="A394" s="2" t="s">
-        <v>3029</v>
-      </c>
-      <c r="B394" s="2" t="s">
-        <v>1641</v>
+        <v>3246</v>
       </c>
       <c r="O394" s="2" t="s">
-        <v>1759</v>
+        <v>3248</v>
       </c>
     </row>
     <row r="395" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A395" s="2" t="s">
-        <v>3028</v>
-      </c>
-      <c r="B395" s="2" t="s">
-        <v>1664</v>
-      </c>
-      <c r="O395" s="2" t="s">
-        <v>777</v>
-      </c>
+      <c r="O395" s="2"/>
     </row>
     <row r="396" spans="1:15" ht="24.95" customHeight="1">
       <c r="A396" s="2" t="s">
-        <v>3218</v>
+        <v>2286</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>1639</v>
+        <v>2285</v>
       </c>
       <c r="O396" s="2" t="s">
-        <v>794</v>
+        <v>768</v>
       </c>
     </row>
     <row r="397" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O397" s="2"/>
+      <c r="A397" s="2" t="s">
+        <v>3029</v>
+      </c>
+      <c r="B397" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="O397" s="2" t="s">
+        <v>1759</v>
+      </c>
     </row>
     <row r="398" spans="1:15" ht="24.95" customHeight="1">
       <c r="A398" s="2" t="s">
-        <v>3083</v>
+        <v>3028</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>2882</v>
+        <v>1664</v>
       </c>
       <c r="O398" s="2" t="s">
-        <v>2883</v>
+        <v>777</v>
       </c>
     </row>
     <row r="399" spans="1:15" ht="24.95" customHeight="1">
       <c r="A399" s="2" t="s">
-        <v>3000</v>
+        <v>3218</v>
+      </c>
+      <c r="B399" s="2" t="s">
+        <v>1639</v>
       </c>
       <c r="O399" s="2" t="s">
-        <v>3001</v>
+        <v>794</v>
       </c>
     </row>
     <row r="400" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A400" s="2" t="s">
-        <v>3013</v>
-      </c>
-      <c r="O400" s="2" t="s">
-        <v>3015</v>
-      </c>
+      <c r="O400" s="2"/>
     </row>
     <row r="401" spans="1:15" ht="24.95" customHeight="1">
       <c r="A401" s="2" t="s">
-        <v>3012</v>
-      </c>
-      <c r="O401" s="3" t="s">
-        <v>3014</v>
+        <v>3083</v>
+      </c>
+      <c r="B401" s="2" t="s">
+        <v>2882</v>
+      </c>
+      <c r="O401" s="2" t="s">
+        <v>2883</v>
       </c>
     </row>
     <row r="402" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O402" s="2"/>
+      <c r="A402" s="2" t="s">
+        <v>3000</v>
+      </c>
+      <c r="O402" s="2" t="s">
+        <v>3001</v>
+      </c>
     </row>
     <row r="403" spans="1:15" ht="24.95" customHeight="1">
       <c r="A403" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="B403" s="2" t="s">
-        <v>718</v>
+        <v>3013</v>
       </c>
       <c r="O403" s="2" t="s">
-        <v>719</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="404" spans="1:15" ht="24.95" customHeight="1">
       <c r="A404" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="B404" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="O404" s="2" t="s">
-        <v>1759</v>
+        <v>3012</v>
+      </c>
+      <c r="O404" s="3" t="s">
+        <v>3014</v>
       </c>
     </row>
     <row r="405" spans="1:15" ht="24.95" customHeight="1">
@@ -16107,109 +16161,109 @@
     </row>
     <row r="406" spans="1:15" ht="24.95" customHeight="1">
       <c r="A406" s="2" t="s">
-        <v>1677</v>
+        <v>717</v>
+      </c>
+      <c r="B406" s="2" t="s">
+        <v>718</v>
       </c>
       <c r="O406" s="2" t="s">
-        <v>1684</v>
+        <v>719</v>
       </c>
     </row>
     <row r="407" spans="1:15" ht="24.95" customHeight="1">
       <c r="A407" s="2" t="s">
-        <v>1678</v>
+        <v>720</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>1657</v>
+        <v>721</v>
       </c>
       <c r="O407" s="2" t="s">
-        <v>1685</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="408" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A408" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="B408" s="2" t="s">
-        <v>1653</v>
-      </c>
-      <c r="O408" s="2" t="s">
-        <v>1689</v>
-      </c>
+      <c r="O408" s="2"/>
     </row>
     <row r="409" spans="1:15" ht="24.95" customHeight="1">
       <c r="A409" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="B409" s="2" t="s">
-        <v>1654</v>
+        <v>1677</v>
       </c>
       <c r="O409" s="2" t="s">
-        <v>1659</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="410" spans="1:15" ht="24.95" customHeight="1">
       <c r="A410" s="2" t="s">
-        <v>1690</v>
+        <v>1678</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>1663</v>
+        <v>1657</v>
       </c>
       <c r="O410" s="2" t="s">
-        <v>1691</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="411" spans="1:15" ht="24.95" customHeight="1">
       <c r="A411" s="2" t="s">
-        <v>1681</v>
+        <v>1679</v>
+      </c>
+      <c r="B411" s="2" t="s">
+        <v>1653</v>
       </c>
       <c r="O411" s="2" t="s">
-        <v>1686</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="412" spans="1:15" ht="24.95" customHeight="1">
       <c r="A412" s="2" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="O412" s="2" t="s">
-        <v>1688</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="413" spans="1:15" ht="24.95" customHeight="1">
       <c r="A413" s="2" t="s">
-        <v>1683</v>
+        <v>1690</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>1656</v>
+        <v>1663</v>
       </c>
       <c r="O413" s="2" t="s">
-        <v>1687</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="414" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O414" s="2"/>
+      <c r="A414" s="2" t="s">
+        <v>1681</v>
+      </c>
+      <c r="O414" s="2" t="s">
+        <v>1686</v>
+      </c>
     </row>
     <row r="415" spans="1:15" ht="24.95" customHeight="1">
       <c r="A415" s="2" t="s">
-        <v>722</v>
+        <v>1682</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>723</v>
+        <v>1658</v>
       </c>
       <c r="O415" s="2" t="s">
-        <v>724</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="416" spans="1:15" ht="24.95" customHeight="1">
       <c r="A416" s="2" t="s">
-        <v>725</v>
+        <v>1683</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>726</v>
+        <v>1656</v>
       </c>
       <c r="O416" s="2" t="s">
-        <v>727</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="417" spans="1:15" ht="24.95" customHeight="1">
@@ -16217,366 +16271,372 @@
     </row>
     <row r="418" spans="1:15" ht="24.95" customHeight="1">
       <c r="A418" s="2" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>2408</v>
+        <v>723</v>
       </c>
       <c r="O418" s="2" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
     </row>
     <row r="419" spans="1:15" ht="24.95" customHeight="1">
       <c r="A419" s="2" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>2409</v>
+        <v>726</v>
       </c>
       <c r="O419" s="2" t="s">
-        <v>2861</v>
+        <v>727</v>
       </c>
     </row>
     <row r="420" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A420" s="2" t="s">
-        <v>2863</v>
-      </c>
-      <c r="O420" s="2" t="s">
-        <v>2862</v>
-      </c>
+      <c r="O420" s="2"/>
     </row>
     <row r="421" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O421" s="2"/>
+      <c r="A421" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="B421" s="2" t="s">
+        <v>2408</v>
+      </c>
+      <c r="O421" s="2" t="s">
+        <v>729</v>
+      </c>
     </row>
     <row r="422" spans="1:15" ht="24.95" customHeight="1">
       <c r="A422" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>732</v>
+        <v>2409</v>
       </c>
       <c r="O422" s="2" t="s">
-        <v>733</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="423" spans="1:15" ht="24.95" customHeight="1">
       <c r="A423" s="2" t="s">
-        <v>1605</v>
-      </c>
-      <c r="B423" s="2" t="s">
-        <v>734</v>
+        <v>2863</v>
       </c>
       <c r="O423" s="2" t="s">
-        <v>492</v>
+        <v>2862</v>
       </c>
     </row>
     <row r="424" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A424" s="2" t="s">
-        <v>1606</v>
-      </c>
-      <c r="B424" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="O424" s="2" t="s">
-        <v>495</v>
-      </c>
+      <c r="O424" s="2"/>
     </row>
     <row r="425" spans="1:15" ht="24.95" customHeight="1">
       <c r="A425" s="2" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="O425" s="2" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
     </row>
     <row r="426" spans="1:15" ht="24.95" customHeight="1">
       <c r="A426" s="2" t="s">
-        <v>739</v>
+        <v>1605</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="O426" s="2" t="s">
-        <v>741</v>
+        <v>492</v>
       </c>
     </row>
     <row r="427" spans="1:15" ht="24.95" customHeight="1">
       <c r="A427" s="2" t="s">
-        <v>742</v>
+        <v>1606</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>1640</v>
+        <v>735</v>
       </c>
       <c r="O427" s="2" t="s">
-        <v>1760</v>
+        <v>495</v>
       </c>
     </row>
     <row r="428" spans="1:15" ht="24.95" customHeight="1">
       <c r="A428" s="2" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="O428" s="2" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
     </row>
     <row r="429" spans="1:15" ht="24.95" customHeight="1">
       <c r="A429" s="2" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="O429" s="2" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
     </row>
     <row r="430" spans="1:15" ht="24.95" customHeight="1">
       <c r="A430" s="2" t="s">
-        <v>2404</v>
+        <v>742</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>2405</v>
+        <v>1640</v>
       </c>
       <c r="O430" s="2" t="s">
-        <v>2406</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="431" spans="1:15" ht="24.95" customHeight="1">
       <c r="A431" s="2" t="s">
-        <v>1713</v>
+        <v>743</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="O431" s="2" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
     </row>
     <row r="432" spans="1:15" ht="24.95" customHeight="1">
       <c r="A432" s="2" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="O432" s="2" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
     </row>
     <row r="433" spans="1:15" ht="24.95" customHeight="1">
       <c r="A433" s="2" t="s">
-        <v>754</v>
+        <v>2404</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>755</v>
+        <v>2405</v>
       </c>
       <c r="O433" s="2" t="s">
-        <v>756</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="434" spans="1:15" ht="24.95" customHeight="1">
       <c r="A434" s="2" t="s">
-        <v>2402</v>
+        <v>1713</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="O434" s="2" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
     </row>
     <row r="435" spans="1:15" ht="24.95" customHeight="1">
       <c r="A435" s="2" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="O435" s="2" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
     </row>
     <row r="436" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O436" s="2"/>
+      <c r="A436" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="B436" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="O436" s="2" t="s">
+        <v>756</v>
+      </c>
     </row>
     <row r="437" spans="1:15" ht="24.95" customHeight="1">
       <c r="A437" s="2" t="s">
-        <v>1610</v>
+        <v>2402</v>
+      </c>
+      <c r="B437" s="2" t="s">
+        <v>757</v>
       </c>
       <c r="O437" s="2" t="s">
-        <v>2309</v>
+        <v>758</v>
       </c>
     </row>
     <row r="438" spans="1:15" ht="24.95" customHeight="1">
       <c r="A438" s="2" t="s">
-        <v>1611</v>
+        <v>759</v>
+      </c>
+      <c r="B438" s="2" t="s">
+        <v>760</v>
       </c>
       <c r="O438" s="2" t="s">
-        <v>1631</v>
+        <v>761</v>
       </c>
     </row>
     <row r="439" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A439" s="2" t="s">
-        <v>1612</v>
-      </c>
-      <c r="O439" s="2" t="s">
-        <v>1630</v>
-      </c>
+      <c r="O439" s="2"/>
     </row>
     <row r="440" spans="1:15" ht="24.95" customHeight="1">
       <c r="A440" s="2" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="O440" s="2" t="s">
-        <v>1629</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="441" spans="1:15" ht="24.95" customHeight="1">
       <c r="A441" s="2" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="O441" s="2" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="442" spans="1:15" ht="24.95" customHeight="1">
       <c r="A442" s="2" t="s">
-        <v>1618</v>
+        <v>1612</v>
       </c>
       <c r="O442" s="2" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="443" spans="1:15" ht="24.95" customHeight="1">
       <c r="A443" s="2" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="O443" s="2" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="444" spans="1:15" ht="24.95" customHeight="1">
       <c r="A444" s="2" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="O444" s="2" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="445" spans="1:15" ht="24.95" customHeight="1">
       <c r="A445" s="2" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="O445" s="2" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="446" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O446" s="2"/>
+      <c r="A446" s="2" t="s">
+        <v>1615</v>
+      </c>
+      <c r="O446" s="2" t="s">
+        <v>1626</v>
+      </c>
     </row>
     <row r="447" spans="1:15" ht="24.95" customHeight="1">
       <c r="A447" s="2" t="s">
-        <v>1619</v>
-      </c>
-      <c r="B447" s="2" t="s">
-        <v>734</v>
+        <v>1616</v>
       </c>
       <c r="O447" s="2" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="448" spans="1:15" ht="24.95" customHeight="1">
       <c r="A448" s="2" t="s">
-        <v>1620</v>
-      </c>
-      <c r="B448" s="2" t="s">
-        <v>735</v>
+        <v>1617</v>
       </c>
       <c r="O448" s="2" t="s">
-        <v>495</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="449" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A449" s="2" t="s">
-        <v>2282</v>
-      </c>
-      <c r="B449" s="2" t="s">
-        <v>2283</v>
-      </c>
-      <c r="O449" s="2" t="s">
-        <v>2284</v>
-      </c>
+      <c r="O449" s="2"/>
     </row>
     <row r="450" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O450" s="2"/>
+      <c r="A450" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B450" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="O450" s="2" t="s">
+        <v>1623</v>
+      </c>
     </row>
     <row r="451" spans="1:15" ht="24.95" customHeight="1">
       <c r="A451" s="2" t="s">
-        <v>787</v>
+        <v>1620</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>788</v>
+        <v>735</v>
       </c>
       <c r="O451" s="2" t="s">
-        <v>789</v>
+        <v>495</v>
       </c>
     </row>
     <row r="452" spans="1:15" ht="24.95" customHeight="1">
       <c r="A452" s="2" t="s">
-        <v>790</v>
+        <v>2282</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>791</v>
+        <v>2283</v>
       </c>
       <c r="O452" s="2" t="s">
-        <v>792</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="453" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A453" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="B453" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="O453" s="2" t="s">
-        <v>794</v>
-      </c>
+      <c r="O453" s="2"/>
     </row>
     <row r="454" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O454" s="2"/>
+      <c r="A454" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="B454" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="O454" s="2" t="s">
+        <v>789</v>
+      </c>
     </row>
     <row r="455" spans="1:15" ht="24.95" customHeight="1">
       <c r="A455" s="2" t="s">
-        <v>1621</v>
+        <v>790</v>
+      </c>
+      <c r="B455" s="2" t="s">
+        <v>791</v>
       </c>
       <c r="O455" s="2" t="s">
-        <v>1622</v>
+        <v>792</v>
       </c>
     </row>
     <row r="456" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O456" s="2"/>
+      <c r="A456" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B456" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="O456" s="2" t="s">
+        <v>794</v>
+      </c>
     </row>
     <row r="457" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A457" s="2" t="s">
-        <v>2985</v>
-      </c>
-      <c r="O457" s="2" t="s">
-        <v>2987</v>
-      </c>
+      <c r="O457" s="2"/>
     </row>
     <row r="458" spans="1:15" ht="24.95" customHeight="1">
       <c r="A458" s="2" t="s">
-        <v>2986</v>
+        <v>1621</v>
       </c>
       <c r="O458" s="2" t="s">
-        <v>2988</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="459" spans="1:15" ht="24.95" customHeight="1">
@@ -16584,112 +16644,109 @@
     </row>
     <row r="460" spans="1:15" ht="24.95" customHeight="1">
       <c r="A460" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="B460" s="2" t="s">
-        <v>763</v>
+        <v>2985</v>
       </c>
       <c r="O460" s="2" t="s">
-        <v>764</v>
+        <v>2987</v>
       </c>
     </row>
     <row r="461" spans="1:15" ht="24.95" customHeight="1">
       <c r="A461" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="B461" s="2" t="s">
-        <v>766</v>
+        <v>2986</v>
       </c>
       <c r="O461" s="2" t="s">
-        <v>767</v>
+        <v>2988</v>
       </c>
     </row>
     <row r="462" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A462" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="B462" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="O462" s="2" t="s">
-        <v>724</v>
-      </c>
+      <c r="O462" s="2"/>
     </row>
     <row r="463" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O463" s="2"/>
+      <c r="A463" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B463" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="O463" s="2" t="s">
+        <v>764</v>
+      </c>
     </row>
     <row r="464" spans="1:15" ht="24.95" customHeight="1">
       <c r="A464" s="2" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="O464" s="2" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
     </row>
     <row r="465" spans="1:15" ht="24.95" customHeight="1">
       <c r="A465" s="2" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="O465" s="2" t="s">
-        <v>776</v>
+        <v>724</v>
       </c>
     </row>
     <row r="466" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A466" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="B466" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="O466" s="2" t="s">
-        <v>780</v>
-      </c>
+      <c r="O466" s="2"/>
     </row>
     <row r="467" spans="1:15" ht="24.95" customHeight="1">
       <c r="A467" s="2" t="s">
-        <v>782</v>
+        <v>771</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>783</v>
+        <v>772</v>
       </c>
       <c r="O467" s="2" t="s">
-        <v>784</v>
+        <v>773</v>
       </c>
     </row>
     <row r="468" spans="1:15" ht="24.95" customHeight="1">
       <c r="A468" s="2" t="s">
-        <v>785</v>
+        <v>774</v>
+      </c>
+      <c r="B468" s="2" t="s">
+        <v>775</v>
       </c>
       <c r="O468" s="2" t="s">
-        <v>786</v>
+        <v>776</v>
       </c>
     </row>
     <row r="469" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O469" s="2"/>
+      <c r="A469" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="B469" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="O469" s="2" t="s">
+        <v>780</v>
+      </c>
     </row>
     <row r="470" spans="1:15" ht="24.95" customHeight="1">
       <c r="A470" s="2" t="s">
-        <v>1609</v>
+        <v>782</v>
+      </c>
+      <c r="B470" s="2" t="s">
+        <v>783</v>
       </c>
       <c r="O470" s="2" t="s">
-        <v>3050</v>
+        <v>784</v>
       </c>
     </row>
     <row r="471" spans="1:15" ht="24.95" customHeight="1">
       <c r="A471" s="2" t="s">
-        <v>1665</v>
-      </c>
-      <c r="B471" s="2" t="s">
-        <v>1796</v>
+        <v>785</v>
       </c>
       <c r="O471" s="2" t="s">
-        <v>3051</v>
+        <v>786</v>
       </c>
     </row>
     <row r="472" spans="1:15" ht="24.95" customHeight="1">
@@ -16697,501 +16754,498 @@
     </row>
     <row r="473" spans="1:15" ht="24.95" customHeight="1">
       <c r="A473" s="2" t="s">
-        <v>1645</v>
+        <v>1609</v>
       </c>
       <c r="O473" s="2" t="s">
-        <v>1646</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="474" spans="1:15" ht="24.95" customHeight="1">
       <c r="A474" s="2" t="s">
-        <v>1649</v>
+        <v>1665</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>1658</v>
+        <v>1796</v>
       </c>
       <c r="O474" s="2" t="s">
-        <v>1688</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="475" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A475" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="B475" s="2" t="s">
-        <v>1656</v>
-      </c>
-      <c r="O475" s="2" t="s">
-        <v>1660</v>
-      </c>
+      <c r="O475" s="2"/>
     </row>
     <row r="476" spans="1:15" ht="24.95" customHeight="1">
       <c r="A476" s="2" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="O476" s="2" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="477" spans="1:15" ht="24.95" customHeight="1">
       <c r="A477" s="2" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>1653</v>
+        <v>1658</v>
       </c>
       <c r="O477" s="2" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="478" spans="1:15" ht="24.95" customHeight="1">
       <c r="A478" s="2" t="s">
-        <v>1655</v>
+        <v>781</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="O478" s="2" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="479" spans="1:15" ht="24.95" customHeight="1">
       <c r="A479" s="2" t="s">
-        <v>1652</v>
-      </c>
-      <c r="B479" s="2" t="s">
-        <v>1663</v>
+        <v>1647</v>
       </c>
       <c r="O479" s="2" t="s">
-        <v>1662</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="480" spans="1:15" ht="24.95" customHeight="1">
       <c r="A480" s="2" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>1657</v>
+        <v>1653</v>
       </c>
       <c r="O480" s="2" t="s">
-        <v>1661</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="481" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O481" s="2"/>
+      <c r="A481" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B481" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="O481" s="2" t="s">
+        <v>1659</v>
+      </c>
     </row>
     <row r="482" spans="1:15" ht="24.95" customHeight="1">
       <c r="A482" s="2" t="s">
-        <v>2905</v>
+        <v>1652</v>
+      </c>
+      <c r="B482" s="2" t="s">
+        <v>1663</v>
       </c>
       <c r="O482" s="2" t="s">
-        <v>2910</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="483" spans="1:15" ht="24.95" customHeight="1">
       <c r="A483" s="2" t="s">
-        <v>2906</v>
+        <v>1651</v>
+      </c>
+      <c r="B483" s="2" t="s">
+        <v>1657</v>
       </c>
       <c r="O483" s="2" t="s">
-        <v>2908</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="484" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A484" s="2" t="s">
-        <v>2907</v>
-      </c>
-      <c r="O484" s="3" t="s">
-        <v>2909</v>
-      </c>
+      <c r="O484" s="2"/>
     </row>
     <row r="485" spans="1:15" ht="24.95" customHeight="1">
       <c r="A485" s="2" t="s">
-        <v>2973</v>
-      </c>
-      <c r="O485" s="3" t="s">
-        <v>2999</v>
+        <v>2905</v>
+      </c>
+      <c r="O485" s="2" t="s">
+        <v>2910</v>
+      </c>
+    </row>
+    <row r="486" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A486" s="2" t="s">
+        <v>2906</v>
+      </c>
+      <c r="O486" s="2" t="s">
+        <v>2908</v>
       </c>
     </row>
     <row r="487" spans="1:15" ht="24.95" customHeight="1">
       <c r="A487" s="2" t="s">
-        <v>3203</v>
+        <v>2907</v>
       </c>
       <c r="O487" s="3" t="s">
-        <v>3206</v>
+        <v>2909</v>
       </c>
     </row>
     <row r="488" spans="1:15" ht="24.95" customHeight="1">
       <c r="A488" s="2" t="s">
-        <v>3204</v>
+        <v>2973</v>
       </c>
       <c r="O488" s="3" t="s">
-        <v>3205</v>
-      </c>
-    </row>
-    <row r="489" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O489" s="2"/>
+        <v>2999</v>
+      </c>
     </row>
     <row r="490" spans="1:15" ht="24.95" customHeight="1">
       <c r="A490" s="2" t="s">
-        <v>2480</v>
+        <v>3203</v>
       </c>
       <c r="O490" s="3" t="s">
-        <v>2481</v>
+        <v>3206</v>
       </c>
     </row>
     <row r="491" spans="1:15" ht="24.95" customHeight="1">
       <c r="A491" s="2" t="s">
-        <v>2470</v>
-      </c>
-      <c r="O491" s="2" t="s">
-        <v>2468</v>
+        <v>3204</v>
+      </c>
+      <c r="O491" s="3" t="s">
+        <v>3205</v>
       </c>
     </row>
     <row r="492" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A492" s="2" t="s">
-        <v>2471</v>
-      </c>
-      <c r="O492" s="2" t="s">
-        <v>2469</v>
-      </c>
+      <c r="O492" s="2"/>
     </row>
     <row r="493" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O493" s="2"/>
+      <c r="A493" s="2" t="s">
+        <v>2480</v>
+      </c>
+      <c r="O493" s="3" t="s">
+        <v>2481</v>
+      </c>
     </row>
     <row r="494" spans="1:15" ht="24.95" customHeight="1">
       <c r="A494" s="2" t="s">
-        <v>1607</v>
-      </c>
-      <c r="B494" s="2" t="s">
-        <v>1797</v>
+        <v>2470</v>
       </c>
       <c r="O494" s="2" t="s">
-        <v>1632</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="495" spans="1:15" ht="24.95" customHeight="1">
       <c r="A495" s="2" t="s">
-        <v>1608</v>
+        <v>2471</v>
       </c>
       <c r="O495" s="2" t="s">
-        <v>2413</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="496" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A496" s="2" t="s">
-        <v>1633</v>
-      </c>
-      <c r="B496" s="2" t="s">
-        <v>2414</v>
-      </c>
-      <c r="O496" s="2" t="s">
-        <v>1795</v>
-      </c>
+      <c r="O496" s="2"/>
     </row>
     <row r="497" spans="1:15" ht="24.95" customHeight="1">
       <c r="A497" s="2" t="s">
-        <v>937</v>
+        <v>1607</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>2415</v>
+        <v>1797</v>
       </c>
       <c r="O497" s="2" t="s">
-        <v>2417</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="498" spans="1:15" ht="24.95" customHeight="1">
       <c r="A498" s="2" t="s">
-        <v>938</v>
-      </c>
-      <c r="B498" s="2" t="s">
-        <v>2418</v>
+        <v>1608</v>
       </c>
       <c r="O498" s="2" t="s">
-        <v>939</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="499" spans="1:15" ht="24.95" customHeight="1">
       <c r="A499" s="2" t="s">
-        <v>940</v>
+        <v>1633</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
       <c r="O499" s="2" t="s">
-        <v>2412</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="500" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O500" s="2"/>
+      <c r="A500" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="B500" s="2" t="s">
+        <v>2415</v>
+      </c>
+      <c r="O500" s="2" t="s">
+        <v>2417</v>
+      </c>
     </row>
     <row r="501" spans="1:15" ht="24.95" customHeight="1">
       <c r="A501" s="2" t="s">
-        <v>966</v>
+        <v>938</v>
+      </c>
+      <c r="B501" s="2" t="s">
+        <v>2418</v>
       </c>
       <c r="O501" s="2" t="s">
-        <v>967</v>
+        <v>939</v>
       </c>
     </row>
     <row r="502" spans="1:15" ht="24.95" customHeight="1">
       <c r="A502" s="2" t="s">
-        <v>968</v>
+        <v>940</v>
+      </c>
+      <c r="B502" s="2" t="s">
+        <v>2416</v>
       </c>
       <c r="O502" s="2" t="s">
-        <v>2855</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="503" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A503" s="2" t="s">
-        <v>969</v>
-      </c>
-      <c r="O503" s="2" t="s">
-        <v>970</v>
-      </c>
+      <c r="O503" s="2"/>
     </row>
     <row r="504" spans="1:15" ht="24.95" customHeight="1">
       <c r="A504" s="2" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="O504" s="2" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
     </row>
     <row r="505" spans="1:15" ht="24.95" customHeight="1">
       <c r="A505" s="2" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="O505" s="2" t="s">
-        <v>2512</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="506" spans="1:15" ht="24.95" customHeight="1">
       <c r="A506" s="2" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="O506" s="2" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
     </row>
     <row r="507" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O507" s="2"/>
+      <c r="A507" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="O507" s="2" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="508" spans="1:15" ht="24.95" customHeight="1">
       <c r="A508" s="2" t="s">
-        <v>3227</v>
-      </c>
-      <c r="B508" s="2" t="s">
-        <v>3229</v>
+        <v>973</v>
       </c>
       <c r="O508" s="2" t="s">
-        <v>3228</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="509" spans="1:15" ht="24.95" customHeight="1">
       <c r="A509" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="B509" s="2" t="s">
-        <v>796</v>
+        <v>974</v>
       </c>
       <c r="O509" s="2" t="s">
-        <v>1638</v>
+        <v>975</v>
       </c>
     </row>
     <row r="510" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A510" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="B510" s="2" t="s">
-        <v>798</v>
-      </c>
-      <c r="O510" s="2" t="s">
-        <v>799</v>
-      </c>
+      <c r="O510" s="2"/>
     </row>
     <row r="511" spans="1:15" ht="24.95" customHeight="1">
       <c r="A511" s="2" t="s">
-        <v>1637</v>
+        <v>3227</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="O511" s="3" t="s">
-        <v>1636</v>
+        <v>3229</v>
+      </c>
+      <c r="O511" s="2" t="s">
+        <v>3228</v>
+      </c>
+    </row>
+    <row r="512" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A512" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="B512" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="O512" s="2" t="s">
+        <v>1638</v>
       </c>
     </row>
     <row r="513" spans="1:15" ht="24.95" customHeight="1">
       <c r="A513" s="2" t="s">
-        <v>3221</v>
-      </c>
-      <c r="O513" s="3" t="s">
-        <v>3224</v>
+        <v>797</v>
+      </c>
+      <c r="B513" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="O513" s="2" t="s">
+        <v>799</v>
       </c>
     </row>
     <row r="514" spans="1:15" ht="24.95" customHeight="1">
       <c r="A514" s="2" t="s">
-        <v>3225</v>
+        <v>1637</v>
+      </c>
+      <c r="B514" s="2" t="s">
+        <v>800</v>
       </c>
       <c r="O514" s="3" t="s">
-        <v>3226</v>
-      </c>
-    </row>
-    <row r="515" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A515" s="2" t="s">
-        <v>3219</v>
-      </c>
-      <c r="O515" s="3" t="s">
-        <v>3222</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="516" spans="1:15" ht="24.95" customHeight="1">
       <c r="A516" s="2" t="s">
-        <v>3220</v>
+        <v>3221</v>
       </c>
       <c r="O516" s="3" t="s">
-        <v>3223</v>
+        <v>3224</v>
+      </c>
+    </row>
+    <row r="517" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A517" s="2" t="s">
+        <v>3225</v>
+      </c>
+      <c r="O517" s="3" t="s">
+        <v>3226</v>
+      </c>
+    </row>
+    <row r="518" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A518" s="2" t="s">
+        <v>3219</v>
+      </c>
+      <c r="O518" s="3" t="s">
+        <v>3222</v>
       </c>
     </row>
     <row r="519" spans="1:15" ht="24.95" customHeight="1">
       <c r="A519" s="2" t="s">
-        <v>2884</v>
-      </c>
-      <c r="B519" s="2" t="s">
-        <v>2885</v>
+        <v>3220</v>
       </c>
       <c r="O519" s="3" t="s">
-        <v>2886</v>
-      </c>
-    </row>
-    <row r="520" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O520" s="2"/>
-    </row>
-    <row r="521" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A521" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="B521" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="O521" s="2" t="s">
-        <v>803</v>
+        <v>3223</v>
       </c>
     </row>
     <row r="522" spans="1:15" ht="24.95" customHeight="1">
       <c r="A522" s="2" t="s">
-        <v>804</v>
+        <v>2884</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="O522" s="2" t="s">
-        <v>519</v>
+        <v>2885</v>
+      </c>
+      <c r="O522" s="3" t="s">
+        <v>2886</v>
       </c>
     </row>
     <row r="523" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A523" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="B523" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="O523" s="2" t="s">
-        <v>808</v>
-      </c>
+      <c r="O523" s="2"/>
     </row>
     <row r="524" spans="1:15" ht="24.95" customHeight="1">
       <c r="A524" s="2" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>530</v>
+        <v>802</v>
       </c>
       <c r="O524" s="2" t="s">
-        <v>531</v>
+        <v>803</v>
       </c>
     </row>
     <row r="525" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O525" s="2"/>
+      <c r="A525" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="B525" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="O525" s="2" t="s">
+        <v>519</v>
+      </c>
     </row>
     <row r="526" spans="1:15" ht="24.95" customHeight="1">
       <c r="A526" s="2" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="O526" s="2" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
     </row>
     <row r="527" spans="1:15" ht="24.95" customHeight="1">
       <c r="A527" s="2" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>817</v>
+        <v>530</v>
       </c>
       <c r="O527" s="2" t="s">
-        <v>818</v>
+        <v>531</v>
       </c>
     </row>
     <row r="528" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A528" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="B528" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="O528" s="2" t="s">
-        <v>821</v>
-      </c>
+      <c r="O528" s="2"/>
     </row>
     <row r="529" spans="1:15" ht="24.95" customHeight="1">
       <c r="A529" s="2" t="s">
-        <v>2419</v>
+        <v>810</v>
+      </c>
+      <c r="B529" s="2" t="s">
+        <v>811</v>
       </c>
       <c r="O529" s="2" t="s">
-        <v>2420</v>
+        <v>812</v>
       </c>
     </row>
     <row r="530" spans="1:15" ht="24.95" customHeight="1">
       <c r="A530" s="2" t="s">
-        <v>822</v>
+        <v>816</v>
+      </c>
+      <c r="B530" s="2" t="s">
+        <v>817</v>
       </c>
       <c r="O530" s="2" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
     </row>
     <row r="531" spans="1:15" ht="24.95" customHeight="1">
       <c r="A531" s="2" t="s">
-        <v>2292</v>
+        <v>819</v>
+      </c>
+      <c r="B531" s="2" t="s">
+        <v>820</v>
       </c>
       <c r="O531" s="2" t="s">
-        <v>2466</v>
+        <v>821</v>
       </c>
     </row>
     <row r="532" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O532" s="2"/>
+      <c r="A532" s="2" t="s">
+        <v>2419</v>
+      </c>
+      <c r="O532" s="2" t="s">
+        <v>2420</v>
+      </c>
     </row>
     <row r="533" spans="1:15" ht="24.95" customHeight="1">
       <c r="A533" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="B533" s="2" t="s">
-        <v>1669</v>
+        <v>822</v>
       </c>
       <c r="O533" s="2" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="534" spans="1:15" ht="24.95" customHeight="1">
       <c r="A534" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="B534" s="2" t="s">
-        <v>814</v>
+        <v>2292</v>
       </c>
       <c r="O534" s="2" t="s">
-        <v>815</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="535" spans="1:15" ht="24.95" customHeight="1">
@@ -17199,548 +17253,548 @@
     </row>
     <row r="536" spans="1:15" ht="24.95" customHeight="1">
       <c r="A536" s="2" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>827</v>
+        <v>1669</v>
       </c>
       <c r="O536" s="2" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
     </row>
     <row r="537" spans="1:15" ht="24.95" customHeight="1">
       <c r="A537" s="2" t="s">
-        <v>829</v>
+        <v>813</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>830</v>
+        <v>814</v>
       </c>
       <c r="O537" s="2" t="s">
-        <v>831</v>
+        <v>815</v>
       </c>
     </row>
     <row r="538" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A538" s="2" t="s">
-        <v>832</v>
-      </c>
-      <c r="B538" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="O538" s="2" t="s">
-        <v>2465</v>
-      </c>
+      <c r="O538" s="2"/>
     </row>
     <row r="539" spans="1:15" ht="24.95" customHeight="1">
       <c r="A539" s="2" t="s">
-        <v>1666</v>
+        <v>826</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>1668</v>
+        <v>827</v>
       </c>
       <c r="O539" s="2" t="s">
-        <v>1667</v>
+        <v>828</v>
       </c>
     </row>
     <row r="540" spans="1:15" ht="24.95" customHeight="1">
       <c r="A540" s="2" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="O540" s="2" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
     </row>
     <row r="541" spans="1:15" ht="24.95" customHeight="1">
       <c r="A541" s="2" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="O541" s="2" t="s">
-        <v>839</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="542" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O542" s="2"/>
+      <c r="A542" s="2" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B542" s="2" t="s">
+        <v>1668</v>
+      </c>
+      <c r="O542" s="2" t="s">
+        <v>1667</v>
+      </c>
     </row>
     <row r="543" spans="1:15" ht="24.95" customHeight="1">
       <c r="A543" s="2" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="O543" s="2" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
     </row>
     <row r="544" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O544" s="2"/>
+      <c r="A544" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B544" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="O544" s="2" t="s">
+        <v>839</v>
+      </c>
     </row>
     <row r="545" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A545" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="B545" s="2" t="s">
-        <v>844</v>
-      </c>
-      <c r="O545" s="2" t="s">
-        <v>845</v>
-      </c>
+      <c r="O545" s="2"/>
     </row>
     <row r="546" spans="1:15" ht="24.95" customHeight="1">
       <c r="A546" s="2" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="O546" s="2" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
     </row>
     <row r="547" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A547" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="B547" s="2" t="s">
-        <v>850</v>
-      </c>
-      <c r="O547" s="2" t="s">
-        <v>851</v>
-      </c>
+      <c r="O547" s="2"/>
     </row>
     <row r="548" spans="1:15" ht="24.95" customHeight="1">
       <c r="A548" s="2" t="s">
-        <v>852</v>
+        <v>843</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="O548" s="2" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
     </row>
     <row r="549" spans="1:15" ht="24.95" customHeight="1">
       <c r="A549" s="2" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>856</v>
+        <v>847</v>
       </c>
       <c r="O549" s="2" t="s">
-        <v>857</v>
+        <v>848</v>
       </c>
     </row>
     <row r="550" spans="1:15" ht="24.95" customHeight="1">
       <c r="A550" s="2" t="s">
-        <v>858</v>
+        <v>849</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>651</v>
+        <v>850</v>
       </c>
       <c r="O550" s="2" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
     </row>
     <row r="551" spans="1:15" ht="24.95" customHeight="1">
       <c r="A551" s="2" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>1794</v>
+        <v>853</v>
       </c>
       <c r="O551" s="2" t="s">
-        <v>1793</v>
+        <v>854</v>
       </c>
     </row>
     <row r="552" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O552" s="2"/>
+      <c r="A552" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B552" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="O552" s="2" t="s">
+        <v>857</v>
+      </c>
     </row>
     <row r="553" spans="1:15" ht="24.95" customHeight="1">
       <c r="A553" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>862</v>
+        <v>651</v>
       </c>
       <c r="O553" s="2" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
     </row>
     <row r="554" spans="1:15" ht="24.95" customHeight="1">
       <c r="A554" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>865</v>
+        <v>1794</v>
       </c>
       <c r="O554" s="2" t="s">
-        <v>866</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="555" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A555" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="B555" s="2" t="s">
-        <v>868</v>
-      </c>
-      <c r="O555" s="2" t="s">
-        <v>869</v>
-      </c>
+      <c r="O555" s="2"/>
     </row>
     <row r="556" spans="1:15" ht="24.95" customHeight="1">
       <c r="A556" s="2" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="O556" s="2" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
     </row>
     <row r="557" spans="1:15" ht="24.95" customHeight="1">
       <c r="A557" s="2" t="s">
-        <v>873</v>
+        <v>864</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
       <c r="O557" s="2" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
     </row>
     <row r="558" spans="1:15" ht="24.95" customHeight="1">
       <c r="A558" s="2" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="O558" s="2" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
     </row>
     <row r="559" spans="1:15" ht="24.95" customHeight="1">
       <c r="A559" s="2" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
       <c r="O559" s="2" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
     </row>
     <row r="560" spans="1:15" ht="24.95" customHeight="1">
       <c r="A560" s="2" t="s">
-        <v>882</v>
+        <v>873</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>883</v>
+        <v>874</v>
       </c>
       <c r="O560" s="2" t="s">
-        <v>884</v>
+        <v>875</v>
       </c>
     </row>
     <row r="561" spans="1:15" ht="24.95" customHeight="1">
       <c r="A561" s="2" t="s">
-        <v>885</v>
+        <v>876</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="O561" s="2" t="s">
-        <v>887</v>
+        <v>878</v>
       </c>
     </row>
     <row r="562" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O562" s="2"/>
+      <c r="A562" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B562" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="O562" s="2" t="s">
+        <v>881</v>
+      </c>
     </row>
     <row r="563" spans="1:15" ht="24.95" customHeight="1">
       <c r="A563" s="2" t="s">
-        <v>1779</v>
+        <v>882</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="O563" s="2" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
     </row>
     <row r="564" spans="1:15" ht="24.95" customHeight="1">
       <c r="A564" s="2" t="s">
-        <v>1780</v>
+        <v>885</v>
+      </c>
+      <c r="B564" s="2" t="s">
+        <v>886</v>
       </c>
       <c r="O564" s="2" t="s">
-        <v>1781</v>
+        <v>887</v>
       </c>
     </row>
     <row r="565" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A565" s="2" t="s">
-        <v>890</v>
-      </c>
-      <c r="B565" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="O565" s="2" t="s">
-        <v>892</v>
-      </c>
+      <c r="O565" s="2"/>
     </row>
     <row r="566" spans="1:15" ht="24.95" customHeight="1">
       <c r="A566" s="2" t="s">
-        <v>893</v>
+        <v>1779</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="O566" s="2" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
     </row>
     <row r="567" spans="1:15" ht="24.95" customHeight="1">
       <c r="A567" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="B567" s="2" t="s">
-        <v>897</v>
+        <v>1780</v>
       </c>
       <c r="O567" s="2" t="s">
-        <v>898</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="568" spans="1:15" ht="24.95" customHeight="1">
       <c r="A568" s="2" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>1774</v>
+        <v>891</v>
       </c>
       <c r="O568" s="2" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
     </row>
     <row r="569" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O569" s="2"/>
+      <c r="A569" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B569" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="O569" s="2" t="s">
+        <v>895</v>
+      </c>
     </row>
     <row r="570" spans="1:15" ht="24.95" customHeight="1">
       <c r="A570" s="2" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="O570" s="2" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
     </row>
     <row r="571" spans="1:15" ht="24.95" customHeight="1">
       <c r="A571" s="2" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>905</v>
+        <v>1774</v>
       </c>
       <c r="O571" s="2" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
     </row>
     <row r="572" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A572" s="2" t="s">
-        <v>907</v>
-      </c>
-      <c r="B572" s="2" t="s">
-        <v>908</v>
-      </c>
-      <c r="O572" s="2" t="s">
-        <v>909</v>
-      </c>
+      <c r="O572" s="2"/>
     </row>
     <row r="573" spans="1:15" ht="24.95" customHeight="1">
       <c r="A573" s="2" t="s">
-        <v>910</v>
+        <v>901</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
       <c r="O573" s="2" t="s">
-        <v>912</v>
+        <v>903</v>
       </c>
     </row>
     <row r="574" spans="1:15" ht="24.95" customHeight="1">
       <c r="A574" s="2" t="s">
-        <v>913</v>
+        <v>904</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>914</v>
+        <v>905</v>
       </c>
       <c r="O574" s="2" t="s">
-        <v>915</v>
+        <v>906</v>
       </c>
     </row>
     <row r="575" spans="1:15" ht="24.95" customHeight="1">
       <c r="A575" s="2" t="s">
-        <v>2287</v>
+        <v>907</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>932</v>
+        <v>908</v>
       </c>
       <c r="O575" s="2" t="s">
-        <v>918</v>
+        <v>909</v>
       </c>
     </row>
     <row r="576" spans="1:15" ht="24.95" customHeight="1">
       <c r="A576" s="2" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="O576" s="2" t="s">
-        <v>2288</v>
+        <v>912</v>
       </c>
     </row>
     <row r="577" spans="1:15" ht="24.95" customHeight="1">
       <c r="A577" s="2" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="O577" s="2" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
     </row>
     <row r="578" spans="1:15" ht="24.95" customHeight="1">
       <c r="A578" s="2" t="s">
-        <v>922</v>
+        <v>2287</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="O578" s="2" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="579" spans="1:15" ht="24.95" customHeight="1">
       <c r="A579" s="2" t="s">
-        <v>1782</v>
+        <v>916</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="O579" s="2" t="s">
-        <v>926</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="580" spans="1:15" ht="24.95" customHeight="1">
       <c r="A580" s="2" t="s">
-        <v>927</v>
-      </c>
-      <c r="B580" s="3" t="s">
-        <v>2289</v>
+        <v>919</v>
+      </c>
+      <c r="B580" s="2" t="s">
+        <v>920</v>
       </c>
       <c r="O580" s="2" t="s">
-        <v>928</v>
+        <v>921</v>
       </c>
     </row>
     <row r="581" spans="1:15" ht="24.95" customHeight="1">
       <c r="A581" s="2" t="s">
-        <v>929</v>
+        <v>922</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>930</v>
+        <v>923</v>
       </c>
       <c r="O581" s="2" t="s">
-        <v>931</v>
+        <v>924</v>
       </c>
     </row>
     <row r="582" spans="1:15" ht="24.95" customHeight="1">
       <c r="A582" s="2" t="s">
-        <v>933</v>
+        <v>1782</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>897</v>
+        <v>925</v>
       </c>
       <c r="O582" s="2" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
     </row>
     <row r="583" spans="1:15" ht="24.95" customHeight="1">
       <c r="A583" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="B583" s="2" t="s">
-        <v>2290</v>
+        <v>927</v>
+      </c>
+      <c r="B583" s="3" t="s">
+        <v>2289</v>
       </c>
       <c r="O583" s="2" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
     </row>
     <row r="584" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O584" s="2"/>
+      <c r="A584" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="B584" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="O584" s="2" t="s">
+        <v>931</v>
+      </c>
     </row>
     <row r="585" spans="1:15" ht="24.95" customHeight="1">
       <c r="A585" s="2" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>942</v>
+        <v>897</v>
       </c>
       <c r="O585" s="2" t="s">
-        <v>943</v>
+        <v>934</v>
       </c>
     </row>
     <row r="586" spans="1:15" ht="24.95" customHeight="1">
       <c r="A586" s="2" t="s">
-        <v>944</v>
+        <v>935</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>945</v>
+        <v>2290</v>
       </c>
       <c r="O586" s="2" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
     </row>
     <row r="587" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A587" s="2" t="s">
-        <v>947</v>
-      </c>
-      <c r="B587" s="2" t="s">
-        <v>948</v>
-      </c>
-      <c r="O587" s="2" t="s">
-        <v>949</v>
-      </c>
+      <c r="O587" s="2"/>
     </row>
     <row r="588" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O588" s="2"/>
+      <c r="A588" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B588" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="O588" s="2" t="s">
+        <v>943</v>
+      </c>
     </row>
     <row r="589" spans="1:15" ht="24.95" customHeight="1">
       <c r="A589" s="2" t="s">
-        <v>1675</v>
+        <v>944</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="O589" s="2" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
     </row>
     <row r="590" spans="1:15" ht="24.95" customHeight="1">
       <c r="A590" s="2" t="s">
-        <v>1676</v>
+        <v>947</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="O590" s="2" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
     </row>
     <row r="591" spans="1:15" ht="24.95" customHeight="1">
@@ -17748,540 +17802,540 @@
     </row>
     <row r="592" spans="1:15" ht="24.95" customHeight="1">
       <c r="A592" s="2" t="s">
-        <v>954</v>
+        <v>1675</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="O592" s="2" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
     </row>
     <row r="593" spans="1:15" ht="24.95" customHeight="1">
       <c r="A593" s="2" t="s">
-        <v>957</v>
+        <v>1676</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="O593" s="2" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
     </row>
     <row r="594" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A594" s="2" t="s">
-        <v>960</v>
-      </c>
-      <c r="B594" s="2" t="s">
-        <v>961</v>
-      </c>
-      <c r="O594" s="2" t="s">
-        <v>962</v>
-      </c>
+      <c r="O594" s="2"/>
     </row>
     <row r="595" spans="1:15" ht="24.95" customHeight="1">
       <c r="A595" s="2" t="s">
-        <v>963</v>
+        <v>954</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>964</v>
+        <v>955</v>
       </c>
       <c r="O595" s="2" t="s">
-        <v>965</v>
+        <v>956</v>
       </c>
     </row>
     <row r="596" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O596" s="2"/>
+      <c r="A596" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="B596" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="O596" s="2" t="s">
+        <v>959</v>
+      </c>
     </row>
     <row r="597" spans="1:15" ht="24.95" customHeight="1">
       <c r="A597" s="2" t="s">
-        <v>976</v>
+        <v>960</v>
       </c>
       <c r="B597" s="2" t="s">
-        <v>977</v>
+        <v>961</v>
       </c>
       <c r="O597" s="2" t="s">
-        <v>978</v>
+        <v>962</v>
       </c>
     </row>
     <row r="598" spans="1:15" ht="24.95" customHeight="1">
       <c r="A598" s="2" t="s">
-        <v>979</v>
+        <v>963</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>980</v>
+        <v>964</v>
       </c>
       <c r="O598" s="2" t="s">
-        <v>981</v>
+        <v>965</v>
       </c>
     </row>
     <row r="599" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A599" s="2" t="s">
-        <v>982</v>
-      </c>
-      <c r="B599" s="2" t="s">
-        <v>983</v>
-      </c>
-      <c r="O599" s="2" t="s">
-        <v>984</v>
-      </c>
+      <c r="O599" s="2"/>
     </row>
     <row r="600" spans="1:15" ht="24.95" customHeight="1">
       <c r="A600" s="2" t="s">
-        <v>985</v>
+        <v>976</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>986</v>
+        <v>977</v>
       </c>
       <c r="O600" s="2" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
     </row>
     <row r="601" spans="1:15" ht="24.95" customHeight="1">
       <c r="A601" s="2" t="s">
-        <v>988</v>
+        <v>979</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>989</v>
+        <v>980</v>
       </c>
       <c r="O601" s="2" t="s">
-        <v>990</v>
+        <v>981</v>
       </c>
     </row>
     <row r="602" spans="1:15" ht="24.95" customHeight="1">
       <c r="A602" s="2" t="s">
-        <v>991</v>
+        <v>982</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>992</v>
+        <v>983</v>
       </c>
       <c r="O602" s="2" t="s">
-        <v>993</v>
+        <v>984</v>
       </c>
     </row>
     <row r="603" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O603" s="2"/>
+      <c r="A603" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="B603" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="O603" s="2" t="s">
+        <v>987</v>
+      </c>
     </row>
     <row r="604" spans="1:15" ht="24.95" customHeight="1">
       <c r="A604" s="2" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="O604" s="2" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
     </row>
     <row r="605" spans="1:15" ht="24.95" customHeight="1">
       <c r="A605" s="2" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="O605" s="2" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
     </row>
     <row r="606" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A606" s="2" t="s">
-        <v>1000</v>
-      </c>
-      <c r="B606" s="2" t="s">
-        <v>1001</v>
-      </c>
-      <c r="O606" s="2" t="s">
-        <v>1002</v>
-      </c>
+      <c r="O606" s="2"/>
     </row>
     <row r="607" spans="1:15" ht="24.95" customHeight="1">
       <c r="A607" s="2" t="s">
-        <v>1003</v>
+        <v>994</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>1004</v>
+        <v>995</v>
       </c>
       <c r="O607" s="2" t="s">
-        <v>1005</v>
+        <v>996</v>
       </c>
     </row>
     <row r="608" spans="1:15" ht="24.95" customHeight="1">
       <c r="A608" s="2" t="s">
-        <v>1006</v>
+        <v>997</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>964</v>
+        <v>998</v>
       </c>
       <c r="O608" s="2" t="s">
-        <v>965</v>
+        <v>999</v>
       </c>
     </row>
     <row r="609" spans="1:15" ht="24.95" customHeight="1">
       <c r="A609" s="2" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="O609" s="2" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="610" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O610" s="2"/>
+      <c r="A610" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B610" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="O610" s="2" t="s">
+        <v>1005</v>
+      </c>
     </row>
     <row r="611" spans="1:15" ht="24.95" customHeight="1">
       <c r="A611" s="2" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>1011</v>
+        <v>964</v>
       </c>
       <c r="O611" s="2" t="s">
-        <v>633</v>
+        <v>965</v>
       </c>
     </row>
     <row r="612" spans="1:15" ht="24.95" customHeight="1">
       <c r="A612" s="2" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="O612" s="2" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="613" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A613" s="2" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B613" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="O613" s="2" t="s">
-        <v>1017</v>
-      </c>
+      <c r="O613" s="2"/>
     </row>
     <row r="614" spans="1:15" ht="24.95" customHeight="1">
       <c r="A614" s="2" t="s">
-        <v>1018</v>
+        <v>1010</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>1019</v>
+        <v>1011</v>
       </c>
       <c r="O614" s="2" t="s">
-        <v>1020</v>
+        <v>633</v>
       </c>
     </row>
     <row r="615" spans="1:15" ht="24.95" customHeight="1">
       <c r="A615" s="2" t="s">
-        <v>1021</v>
+        <v>1012</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>1022</v>
+        <v>1013</v>
       </c>
       <c r="O615" s="2" t="s">
-        <v>1023</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="616" spans="1:15" ht="24.95" customHeight="1">
       <c r="A616" s="2" t="s">
-        <v>1024</v>
+        <v>1015</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>1025</v>
+        <v>1016</v>
       </c>
       <c r="O616" s="2" t="s">
-        <v>1026</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="617" spans="1:15" ht="24.95" customHeight="1">
       <c r="A617" s="2" t="s">
-        <v>1027</v>
+        <v>1018</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>1028</v>
+        <v>1019</v>
       </c>
       <c r="O617" s="2" t="s">
-        <v>1029</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="618" spans="1:15" ht="24.95" customHeight="1">
       <c r="A618" s="2" t="s">
-        <v>1030</v>
+        <v>1021</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>1031</v>
+        <v>1022</v>
       </c>
       <c r="O618" s="2" t="s">
-        <v>1032</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="619" spans="1:15" ht="24.95" customHeight="1">
       <c r="A619" s="2" t="s">
-        <v>1033</v>
+        <v>1024</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>1034</v>
+        <v>1025</v>
       </c>
       <c r="O619" s="2" t="s">
-        <v>1035</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="620" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O620" s="2"/>
+      <c r="A620" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B620" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="O620" s="2" t="s">
+        <v>1029</v>
+      </c>
     </row>
     <row r="621" spans="1:15" ht="24.95" customHeight="1">
       <c r="A621" s="2" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="O621" s="2" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="622" spans="1:15" ht="24.95" customHeight="1">
       <c r="A622" s="2" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="O622" s="2" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="623" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A623" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="B623" s="2" t="s">
-        <v>1043</v>
-      </c>
-      <c r="O623" s="2" t="s">
-        <v>2291</v>
-      </c>
+      <c r="O623" s="2"/>
     </row>
     <row r="624" spans="1:15" ht="24.95" customHeight="1">
       <c r="A624" s="2" t="s">
-        <v>1044</v>
+        <v>1036</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>1045</v>
+        <v>1037</v>
       </c>
       <c r="O624" s="2" t="s">
-        <v>1046</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="625" spans="1:15" ht="24.95" customHeight="1">
       <c r="A625" s="2" t="s">
-        <v>1047</v>
+        <v>1039</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>1048</v>
+        <v>1040</v>
       </c>
       <c r="O625" s="2" t="s">
-        <v>1049</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="626" spans="1:15" ht="24.95" customHeight="1">
       <c r="A626" s="2" t="s">
-        <v>1050</v>
+        <v>1042</v>
       </c>
       <c r="B626" s="2" t="s">
-        <v>66</v>
+        <v>1043</v>
       </c>
       <c r="O626" s="2" t="s">
-        <v>1051</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="627" spans="1:15" ht="24.95" customHeight="1">
       <c r="A627" s="2" t="s">
-        <v>1052</v>
+        <v>1044</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>1053</v>
+        <v>1045</v>
       </c>
       <c r="O627" s="2" t="s">
-        <v>1054</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="628" spans="1:15" ht="24.95" customHeight="1">
       <c r="A628" s="2" t="s">
-        <v>1055</v>
+        <v>1047</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>1056</v>
+        <v>1048</v>
       </c>
       <c r="O628" s="2" t="s">
-        <v>1057</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="629" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O629" s="2"/>
+      <c r="A629" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B629" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="O629" s="2" t="s">
+        <v>1051</v>
+      </c>
     </row>
     <row r="630" spans="1:15" ht="24.95" customHeight="1">
       <c r="A630" s="2" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>1764</v>
+        <v>1053</v>
       </c>
       <c r="O630" s="2" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="631" spans="1:15" ht="24.95" customHeight="1">
       <c r="A631" s="2" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>1765</v>
+        <v>1056</v>
       </c>
       <c r="O631" s="2" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="632" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A632" s="2" t="s">
-        <v>1062</v>
-      </c>
-      <c r="B632" s="2" t="s">
-        <v>1772</v>
-      </c>
-      <c r="O632" s="2" t="s">
-        <v>1063</v>
-      </c>
+      <c r="O632" s="2"/>
     </row>
     <row r="633" spans="1:15" ht="24.95" customHeight="1">
       <c r="A633" s="2" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>1771</v>
+        <v>1764</v>
       </c>
       <c r="O633" s="2" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="634" spans="1:15" ht="24.95" customHeight="1">
       <c r="A634" s="2" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>1768</v>
+        <v>1765</v>
       </c>
       <c r="O634" s="2" t="s">
-        <v>1710</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="635" spans="1:15" ht="24.95" customHeight="1">
       <c r="A635" s="2" t="s">
-        <v>1769</v>
+        <v>1062</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>1770</v>
+        <v>1772</v>
       </c>
       <c r="O635" s="2" t="s">
-        <v>1709</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="636" spans="1:15" ht="24.95" customHeight="1">
       <c r="A636" s="2" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>1766</v>
+        <v>1771</v>
       </c>
       <c r="O636" s="2" t="s">
-        <v>1708</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="637" spans="1:15" ht="24.95" customHeight="1">
       <c r="A637" s="2" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="O637" s="2" t="s">
-        <v>1707</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="638" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O638" s="2"/>
+      <c r="A638" s="2" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B638" s="2" t="s">
+        <v>1770</v>
+      </c>
+      <c r="O638" s="2" t="s">
+        <v>1709</v>
+      </c>
     </row>
     <row r="639" spans="1:15" ht="24.95" customHeight="1">
       <c r="A639" s="2" t="s">
-        <v>1832</v>
+        <v>1067</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>1822</v>
+        <v>1766</v>
       </c>
       <c r="O639" s="2" t="s">
-        <v>1839</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="640" spans="1:15" ht="24.95" customHeight="1">
       <c r="A640" s="2" t="s">
-        <v>1833</v>
+        <v>1068</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>1835</v>
+        <v>1767</v>
       </c>
       <c r="O640" s="2" t="s">
-        <v>1837</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="641" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A641" s="2" t="s">
-        <v>1834</v>
-      </c>
-      <c r="B641" s="2" t="s">
-        <v>1836</v>
-      </c>
-      <c r="O641" s="2" t="s">
-        <v>1838</v>
-      </c>
+      <c r="O641" s="2"/>
     </row>
     <row r="642" spans="1:15" ht="24.95" customHeight="1">
       <c r="A642" s="2" t="s">
-        <v>1840</v>
+        <v>1832</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>1841</v>
+        <v>1822</v>
       </c>
       <c r="O642" s="2" t="s">
-        <v>1842</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="643" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O643" s="2"/>
+      <c r="A643" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B643" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="O643" s="2" t="s">
+        <v>1837</v>
+      </c>
     </row>
     <row r="644" spans="1:15" ht="24.95" customHeight="1">
       <c r="A644" s="2" t="s">
-        <v>1069</v>
+        <v>1834</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>1070</v>
+        <v>1836</v>
       </c>
       <c r="O644" s="2" t="s">
-        <v>3030</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="645" spans="1:15" ht="24.95" customHeight="1">
       <c r="A645" s="2" t="s">
-        <v>1071</v>
+        <v>1840</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>1072</v>
+        <v>1841</v>
       </c>
       <c r="O645" s="2" t="s">
-        <v>1073</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="646" spans="1:15" ht="24.95" customHeight="1">
@@ -18289,294 +18343,300 @@
     </row>
     <row r="647" spans="1:15" ht="24.95" customHeight="1">
       <c r="A647" s="2" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="O647" s="2" t="s">
-        <v>1076</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="648" spans="1:15" ht="24.95" customHeight="1">
       <c r="A648" s="2" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="O648" s="2" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="649" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A649" s="2" t="s">
-        <v>1080</v>
-      </c>
-      <c r="B649" s="2" t="s">
-        <v>1081</v>
-      </c>
-      <c r="O649" s="2" t="s">
-        <v>1082</v>
-      </c>
+      <c r="O649" s="2"/>
     </row>
     <row r="650" spans="1:15" ht="24.95" customHeight="1">
       <c r="A650" s="2" t="s">
-        <v>1083</v>
+        <v>1074</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>1084</v>
+        <v>1075</v>
       </c>
       <c r="O650" s="2" t="s">
-        <v>1085</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="651" spans="1:15" ht="24.95" customHeight="1">
       <c r="A651" s="2" t="s">
-        <v>1086</v>
+        <v>1077</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>1087</v>
+        <v>1078</v>
       </c>
       <c r="O651" s="2" t="s">
-        <v>1088</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="652" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O652" s="2"/>
+      <c r="A652" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B652" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="O652" s="2" t="s">
+        <v>1082</v>
+      </c>
     </row>
     <row r="653" spans="1:15" ht="24.95" customHeight="1">
       <c r="A653" s="2" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="O653" s="2" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="654" spans="1:15" ht="24.95" customHeight="1">
       <c r="A654" s="2" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="O654" s="2" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="655" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A655" s="2" t="s">
-        <v>1095</v>
-      </c>
-      <c r="B655" s="2" t="s">
-        <v>1096</v>
-      </c>
-      <c r="O655" s="2" t="s">
-        <v>1097</v>
-      </c>
+      <c r="O655" s="2"/>
     </row>
     <row r="656" spans="1:15" ht="24.95" customHeight="1">
       <c r="A656" s="2" t="s">
-        <v>1098</v>
+        <v>1089</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>1099</v>
+        <v>1090</v>
       </c>
       <c r="O656" s="2" t="s">
-        <v>1100</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="657" spans="1:15" ht="24.95" customHeight="1">
       <c r="A657" s="2" t="s">
-        <v>1101</v>
+        <v>1092</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>1102</v>
+        <v>1093</v>
       </c>
       <c r="O657" s="2" t="s">
-        <v>1103</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="658" spans="1:15" ht="24.95" customHeight="1">
       <c r="A658" s="2" t="s">
-        <v>1104</v>
+        <v>1095</v>
       </c>
       <c r="B658" s="2" t="s">
-        <v>1105</v>
+        <v>1096</v>
       </c>
       <c r="O658" s="2" t="s">
-        <v>1106</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="659" spans="1:15" ht="24.95" customHeight="1">
       <c r="A659" s="2" t="s">
-        <v>1107</v>
+        <v>1098</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>964</v>
+        <v>1099</v>
       </c>
       <c r="O659" s="2" t="s">
-        <v>965</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="660" spans="1:15" ht="24.95" customHeight="1">
       <c r="A660" s="2" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>1109</v>
+        <v>1102</v>
       </c>
       <c r="O660" s="2" t="s">
-        <v>1110</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="661" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O661" s="2"/>
+      <c r="A661" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B661" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="O661" s="2" t="s">
+        <v>1106</v>
+      </c>
     </row>
     <row r="662" spans="1:15" ht="24.95" customHeight="1">
       <c r="A662" s="2" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>1112</v>
+        <v>964</v>
       </c>
       <c r="O662" s="2" t="s">
-        <v>1113</v>
+        <v>965</v>
       </c>
     </row>
     <row r="663" spans="1:15" ht="24.95" customHeight="1">
       <c r="A663" s="2" t="s">
-        <v>1114</v>
+        <v>1108</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>1115</v>
+        <v>1109</v>
       </c>
       <c r="O663" s="2" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="664" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A664" s="2" t="s">
-        <v>1117</v>
-      </c>
-      <c r="B664" s="2" t="s">
-        <v>1118</v>
-      </c>
-      <c r="O664" s="2" t="s">
-        <v>1119</v>
-      </c>
+      <c r="O664" s="2"/>
     </row>
     <row r="665" spans="1:15" ht="24.95" customHeight="1">
       <c r="A665" s="2" t="s">
-        <v>1120</v>
+        <v>1111</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>1121</v>
+        <v>1112</v>
       </c>
       <c r="O665" s="2" t="s">
-        <v>1122</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="666" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O666" s="2"/>
+      <c r="A666" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B666" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="O666" s="2" t="s">
+        <v>1116</v>
+      </c>
     </row>
     <row r="667" spans="1:15" ht="24.95" customHeight="1">
       <c r="A667" s="2" t="s">
-        <v>1123</v>
+        <v>1117</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="O667" s="2" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="668" spans="1:15" ht="24.95" customHeight="1">
       <c r="A668" s="2" t="s">
-        <v>1126</v>
+        <v>1120</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>599</v>
+        <v>1121</v>
       </c>
       <c r="O668" s="2" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="669" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A669" s="2" t="s">
-        <v>2462</v>
-      </c>
-      <c r="B669" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="O669" s="2" t="s">
-        <v>1128</v>
-      </c>
+      <c r="O669" s="2"/>
     </row>
     <row r="670" spans="1:15" ht="24.95" customHeight="1">
       <c r="A670" s="2" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>593</v>
+        <v>1124</v>
       </c>
       <c r="O670" s="2" t="s">
-        <v>594</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="671" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O671" s="2"/>
+      <c r="A671" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B671" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="O671" s="2" t="s">
+        <v>1127</v>
+      </c>
     </row>
     <row r="672" spans="1:15" ht="24.95" customHeight="1">
       <c r="A672" s="2" t="s">
-        <v>1130</v>
+        <v>2462</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>920</v>
+        <v>601</v>
       </c>
       <c r="O672" s="2" t="s">
-        <v>3086</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="673" spans="1:15" ht="24.95" customHeight="1">
       <c r="A673" s="2" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>1132</v>
+        <v>593</v>
       </c>
       <c r="O673" s="2" t="s">
-        <v>984</v>
+        <v>594</v>
       </c>
     </row>
     <row r="674" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A674" s="2" t="s">
-        <v>1133</v>
-      </c>
-      <c r="O674" s="2" t="s">
-        <v>1134</v>
-      </c>
+      <c r="O674" s="2"/>
     </row>
     <row r="675" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O675" s="2"/>
+      <c r="A675" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B675" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="O675" s="2" t="s">
+        <v>3086</v>
+      </c>
     </row>
     <row r="676" spans="1:15" ht="24.95" customHeight="1">
       <c r="A676" s="2" t="s">
-        <v>2525</v>
+        <v>1131</v>
+      </c>
+      <c r="B676" s="2" t="s">
+        <v>1132</v>
       </c>
       <c r="O676" s="2" t="s">
-        <v>2527</v>
+        <v>984</v>
       </c>
     </row>
     <row r="677" spans="1:15" ht="24.95" customHeight="1">
       <c r="A677" s="2" t="s">
-        <v>2526</v>
+        <v>1133</v>
       </c>
       <c r="O677" s="2" t="s">
-        <v>2528</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="678" spans="1:15" ht="24.95" customHeight="1">
@@ -18584,229 +18644,223 @@
     </row>
     <row r="679" spans="1:15" ht="24.95" customHeight="1">
       <c r="A679" s="2" t="s">
-        <v>1135</v>
-      </c>
-      <c r="B679" s="2" t="s">
-        <v>1136</v>
+        <v>2525</v>
       </c>
       <c r="O679" s="2" t="s">
-        <v>1137</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="680" spans="1:15" ht="24.95" customHeight="1">
       <c r="A680" s="2" t="s">
-        <v>1138</v>
-      </c>
-      <c r="B680" s="2" t="s">
-        <v>1139</v>
+        <v>2526</v>
       </c>
       <c r="O680" s="2" t="s">
-        <v>1140</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="681" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A681" s="2" t="s">
-        <v>1141</v>
-      </c>
-      <c r="B681" s="2" t="s">
-        <v>964</v>
-      </c>
-      <c r="O681" s="2" t="s">
-        <v>965</v>
-      </c>
+      <c r="O681" s="2"/>
     </row>
     <row r="682" spans="1:15" ht="24.95" customHeight="1">
       <c r="A682" s="2" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>1143</v>
+        <v>1136</v>
       </c>
       <c r="O682" s="2" t="s">
-        <v>1144</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="683" spans="1:15" ht="24.95" customHeight="1">
       <c r="A683" s="2" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
       <c r="O683" s="2" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="684" spans="1:15" ht="24.95" customHeight="1">
       <c r="A684" s="2" t="s">
-        <v>1148</v>
+        <v>1141</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1821</v>
+        <v>964</v>
       </c>
       <c r="O684" s="2" t="s">
-        <v>1149</v>
+        <v>965</v>
       </c>
     </row>
     <row r="685" spans="1:15" ht="24.95" customHeight="1">
       <c r="A685" s="2" t="s">
-        <v>3027</v>
+        <v>1142</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>1151</v>
+        <v>1143</v>
       </c>
       <c r="O685" s="2" t="s">
-        <v>1152</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="686" spans="1:15" ht="24.95" customHeight="1">
       <c r="A686" s="2" t="s">
-        <v>1155</v>
+        <v>1145</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>1156</v>
+        <v>1146</v>
       </c>
       <c r="O686" s="2" t="s">
-        <v>1157</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="687" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O687" s="2"/>
+      <c r="A687" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B687" s="2" t="s">
+        <v>1821</v>
+      </c>
+      <c r="O687" s="2" t="s">
+        <v>1149</v>
+      </c>
     </row>
     <row r="688" spans="1:15" ht="24.95" customHeight="1">
       <c r="A688" s="2" t="s">
-        <v>3052</v>
+        <v>3027</v>
+      </c>
+      <c r="B688" s="2" t="s">
+        <v>1151</v>
       </c>
       <c r="O688" s="2" t="s">
-        <v>3057</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="689" spans="1:15" ht="24.95" customHeight="1">
       <c r="A689" s="2" t="s">
-        <v>3053</v>
+        <v>1155</v>
+      </c>
+      <c r="B689" s="2" t="s">
+        <v>1156</v>
       </c>
       <c r="O689" s="2" t="s">
-        <v>3058</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="690" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A690" s="2" t="s">
-        <v>3067</v>
-      </c>
-      <c r="O690" s="2" t="s">
-        <v>3068</v>
-      </c>
+      <c r="O690" s="2"/>
     </row>
     <row r="691" spans="1:15" ht="24.95" customHeight="1">
       <c r="A691" s="2" t="s">
-        <v>3054</v>
+        <v>3052</v>
       </c>
       <c r="O691" s="2" t="s">
-        <v>3059</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="692" spans="1:15" ht="24.95" customHeight="1">
       <c r="A692" s="2" t="s">
-        <v>3055</v>
+        <v>3053</v>
       </c>
       <c r="O692" s="2" t="s">
-        <v>3060</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="693" spans="1:15" ht="24.95" customHeight="1">
       <c r="A693" s="2" t="s">
-        <v>3056</v>
+        <v>3067</v>
       </c>
       <c r="O693" s="2" t="s">
-        <v>3061</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="694" spans="1:15" ht="24.95" customHeight="1">
       <c r="A694" s="2" t="s">
-        <v>3065</v>
+        <v>3054</v>
       </c>
       <c r="O694" s="2" t="s">
-        <v>3087</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="695" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O695" s="2"/>
+      <c r="A695" s="2" t="s">
+        <v>3055</v>
+      </c>
+      <c r="O695" s="2" t="s">
+        <v>3060</v>
+      </c>
     </row>
     <row r="696" spans="1:15" ht="24.95" customHeight="1">
       <c r="A696" s="2" t="s">
+        <v>3056</v>
+      </c>
+      <c r="O696" s="2" t="s">
+        <v>3061</v>
+      </c>
+    </row>
+    <row r="697" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A697" s="2" t="s">
+        <v>3065</v>
+      </c>
+      <c r="O697" s="2" t="s">
+        <v>3087</v>
+      </c>
+    </row>
+    <row r="698" spans="1:15" ht="24.95" customHeight="1">
+      <c r="O698" s="2"/>
+    </row>
+    <row r="699" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A699" s="2" t="s">
         <v>1158</v>
       </c>
-      <c r="B696" s="2" t="s">
+      <c r="B699" s="2" t="s">
         <v>1761</v>
       </c>
-      <c r="O696" s="2" t="s">
+      <c r="O699" s="2" t="s">
         <v>1159</v>
       </c>
     </row>
-    <row r="697" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O697" s="2"/>
-    </row>
-    <row r="698" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A698" s="2" t="s">
-        <v>1160</v>
-      </c>
-      <c r="B698" s="2" t="s">
-        <v>1161</v>
-      </c>
-      <c r="O698" s="2" t="s">
-        <v>1162</v>
-      </c>
-    </row>
-    <row r="699" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O699" s="2"/>
-    </row>
     <row r="700" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A700" s="2" t="s">
-        <v>3174</v>
-      </c>
-      <c r="O700" s="2" t="s">
-        <v>3175</v>
-      </c>
+      <c r="O700" s="2"/>
     </row>
     <row r="701" spans="1:15" ht="24.95" customHeight="1">
       <c r="A701" s="2" t="s">
-        <v>2989</v>
+        <v>1160</v>
+      </c>
+      <c r="B701" s="2" t="s">
+        <v>1161</v>
       </c>
       <c r="O701" s="2" t="s">
-        <v>2991</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="702" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A702" s="2" t="s">
-        <v>2990</v>
-      </c>
-      <c r="O702" s="2" t="s">
-        <v>2992</v>
-      </c>
+      <c r="O702" s="2"/>
     </row>
     <row r="703" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O703" s="2"/>
+      <c r="A703" s="2" t="s">
+        <v>3174</v>
+      </c>
+      <c r="O703" s="2" t="s">
+        <v>3175</v>
+      </c>
     </row>
     <row r="704" spans="1:15" ht="24.95" customHeight="1">
       <c r="A704" s="2" t="s">
-        <v>1163</v>
-      </c>
-      <c r="B704" s="2" t="s">
-        <v>1164</v>
+        <v>2989</v>
       </c>
       <c r="O704" s="2" t="s">
-        <v>1165</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="705" spans="1:15" ht="24.95" customHeight="1">
       <c r="A705" s="2" t="s">
-        <v>1166</v>
-      </c>
-      <c r="B705" s="2" t="s">
-        <v>1167</v>
+        <v>2990</v>
       </c>
       <c r="O705" s="2" t="s">
-        <v>1168</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="706" spans="1:15" ht="24.95" customHeight="1">
@@ -18814,118 +18868,118 @@
     </row>
     <row r="707" spans="1:15" ht="24.95" customHeight="1">
       <c r="A707" s="2" t="s">
-        <v>1169</v>
+        <v>1163</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>1170</v>
+        <v>1164</v>
       </c>
       <c r="O707" s="2" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="708" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O708" s="2"/>
+      <c r="A708" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B708" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="O708" s="2" t="s">
+        <v>1168</v>
+      </c>
     </row>
     <row r="709" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A709" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="O709" s="2" t="s">
-        <v>1173</v>
-      </c>
+      <c r="O709" s="2"/>
     </row>
     <row r="710" spans="1:15" ht="24.95" customHeight="1">
       <c r="A710" s="2" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
       <c r="O710" s="2" t="s">
-        <v>1176</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="711" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A711" s="2" t="s">
-        <v>1177</v>
-      </c>
-      <c r="B711" s="2" t="s">
-        <v>1178</v>
-      </c>
-      <c r="O711" s="2" t="s">
-        <v>1179</v>
-      </c>
+      <c r="O711" s="2"/>
     </row>
     <row r="712" spans="1:15" ht="24.95" customHeight="1">
       <c r="A712" s="2" t="s">
-        <v>1180</v>
-      </c>
-      <c r="B712" s="2" t="s">
-        <v>1181</v>
+        <v>1172</v>
       </c>
       <c r="O712" s="2" t="s">
-        <v>1182</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="713" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O713" s="2"/>
+      <c r="A713" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B713" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="O713" s="2" t="s">
+        <v>1176</v>
+      </c>
     </row>
     <row r="714" spans="1:15" ht="24.95" customHeight="1">
       <c r="A714" s="2" t="s">
-        <v>1183</v>
+        <v>1177</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
       <c r="O714" s="2" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="715" spans="1:15" ht="24.95" customHeight="1">
       <c r="A715" s="2" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="O715" s="2" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="716" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A716" s="2" t="s">
-        <v>1189</v>
-      </c>
-      <c r="B716" s="2" t="s">
-        <v>1190</v>
-      </c>
-      <c r="O716" s="2" t="s">
-        <v>1191</v>
-      </c>
+      <c r="O716" s="2"/>
     </row>
     <row r="717" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O717" s="2"/>
+      <c r="A717" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B717" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="O717" s="2" t="s">
+        <v>1185</v>
+      </c>
     </row>
     <row r="718" spans="1:15" ht="24.95" customHeight="1">
       <c r="A718" s="2" t="s">
-        <v>1192</v>
+        <v>1186</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="O718" s="2" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="719" spans="1:15" ht="24.95" customHeight="1">
       <c r="A719" s="2" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
       <c r="O719" s="2" t="s">
-        <v>1197</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="720" spans="1:15" ht="24.95" customHeight="1">
@@ -18933,71 +18987,71 @@
     </row>
     <row r="721" spans="1:15" ht="24.95" customHeight="1">
       <c r="A721" s="2" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="O721" s="2" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="722" spans="1:15" ht="24.95" customHeight="1">
       <c r="A722" s="2" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="O722" s="2" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="723" spans="1:15" ht="24.95" customHeight="1">
       <c r="O723" s="2"/>
     </row>
-    <row r="724" spans="1:15" ht="33">
+    <row r="724" spans="1:15" ht="24.95" customHeight="1">
       <c r="A724" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B724" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="O724" s="2" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="725" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A725" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B725" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="O725" s="2" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="726" spans="1:15" ht="24.95" customHeight="1">
+      <c r="O726" s="2"/>
+    </row>
+    <row r="727" spans="1:15" ht="33">
+      <c r="A727" s="2" t="s">
         <v>2966</v>
       </c>
-      <c r="O724" s="3" t="s">
+      <c r="O727" s="3" t="s">
         <v>2967</v>
       </c>
     </row>
-    <row r="725" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O725" s="2"/>
-    </row>
-    <row r="726" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A726" s="2" t="s">
-        <v>1204</v>
-      </c>
-      <c r="O726" s="2" t="s">
-        <v>1773</v>
-      </c>
-    </row>
-    <row r="727" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O727" s="2"/>
-    </row>
     <row r="728" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A728" s="2" t="s">
-        <v>1205</v>
-      </c>
-      <c r="B728" s="2" t="s">
-        <v>1206</v>
-      </c>
-      <c r="O728" s="2" t="s">
-        <v>1207</v>
-      </c>
+      <c r="O728" s="2"/>
     </row>
     <row r="729" spans="1:15" ht="24.95" customHeight="1">
       <c r="A729" s="2" t="s">
-        <v>1208</v>
-      </c>
-      <c r="B729" s="2" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="O729" s="2" t="s">
-        <v>1210</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="730" spans="1:15" ht="24.95" customHeight="1">
@@ -19005,38 +19059,38 @@
     </row>
     <row r="731" spans="1:15" ht="24.95" customHeight="1">
       <c r="A731" s="2" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="O731" s="2" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="732" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O732" s="2"/>
+      <c r="A732" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B732" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="O732" s="2" t="s">
+        <v>1210</v>
+      </c>
     </row>
     <row r="733" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A733" s="2" t="s">
-        <v>1214</v>
-      </c>
-      <c r="B733" s="2" t="s">
-        <v>1215</v>
-      </c>
-      <c r="O733" s="2" t="s">
-        <v>1216</v>
-      </c>
+      <c r="O733" s="2"/>
     </row>
     <row r="734" spans="1:15" ht="24.95" customHeight="1">
       <c r="A734" s="2" t="s">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="O734" s="2" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="735" spans="1:15" ht="24.95" customHeight="1">
@@ -19044,57 +19098,60 @@
     </row>
     <row r="736" spans="1:15" ht="24.95" customHeight="1">
       <c r="A736" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B736" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="O736" s="2" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="737" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A737" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B737" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="O737" s="2" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="738" spans="1:15" ht="24.95" customHeight="1">
+      <c r="O738" s="2"/>
+    </row>
+    <row r="739" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A739" s="2" t="s">
         <v>1220</v>
       </c>
-      <c r="B736" s="2" t="s">
+      <c r="B739" s="2" t="s">
         <v>1763</v>
       </c>
-      <c r="O736" s="2" t="s">
+      <c r="O739" s="2" t="s">
         <v>1221</v>
       </c>
     </row>
-    <row r="737" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O737" s="2"/>
-    </row>
-    <row r="738" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A738" s="2" t="s">
+    <row r="740" spans="1:15" ht="24.95" customHeight="1">
+      <c r="O740" s="2"/>
+    </row>
+    <row r="741" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A741" s="2" t="s">
         <v>3178</v>
       </c>
-      <c r="O738" s="2" t="s">
+      <c r="O741" s="2" t="s">
         <v>3180</v>
       </c>
     </row>
-    <row r="739" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O739" s="2"/>
-    </row>
-    <row r="740" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A740" s="2" t="s">
-        <v>1222</v>
-      </c>
-      <c r="O740" s="2" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="741" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O741" s="2"/>
-    </row>
     <row r="742" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A742" s="2" t="s">
-        <v>3176</v>
-      </c>
-      <c r="O742" s="2" t="s">
-        <v>3177</v>
-      </c>
+      <c r="O742" s="2"/>
     </row>
     <row r="743" spans="1:15" ht="24.95" customHeight="1">
       <c r="A743" s="2" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B743" s="2" t="s">
-        <v>1762</v>
+        <v>1222</v>
       </c>
       <c r="O743" s="2" t="s">
-        <v>1224</v>
+        <v>823</v>
       </c>
     </row>
     <row r="744" spans="1:15" ht="24.95" customHeight="1">
@@ -19102,24 +19159,21 @@
     </row>
     <row r="745" spans="1:15" ht="24.95" customHeight="1">
       <c r="A745" s="2" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B745" s="2" t="s">
-        <v>1226</v>
+        <v>3176</v>
       </c>
       <c r="O745" s="2" t="s">
-        <v>1227</v>
+        <v>3177</v>
       </c>
     </row>
     <row r="746" spans="1:15" ht="24.95" customHeight="1">
       <c r="A746" s="2" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>1229</v>
+        <v>1762</v>
       </c>
       <c r="O746" s="2" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="747" spans="1:15" ht="24.95" customHeight="1">
@@ -19127,24 +19181,24 @@
     </row>
     <row r="748" spans="1:15" ht="24.95" customHeight="1">
       <c r="A748" s="2" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="B748" s="2" t="s">
-        <v>1232</v>
+        <v>1226</v>
       </c>
       <c r="O748" s="2" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="749" spans="1:15" ht="24.95" customHeight="1">
       <c r="A749" s="2" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="B749" s="2" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="O749" s="2" t="s">
-        <v>1236</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="750" spans="1:15" ht="24.95" customHeight="1">
@@ -19152,75 +19206,91 @@
     </row>
     <row r="751" spans="1:15" ht="24.95" customHeight="1">
       <c r="A751" s="2" t="s">
-        <v>1237</v>
+        <v>1231</v>
       </c>
       <c r="B751" s="2" t="s">
-        <v>1238</v>
+        <v>1232</v>
       </c>
       <c r="O751" s="2" t="s">
-        <v>1239</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="752" spans="1:15" ht="24.95" customHeight="1">
       <c r="A752" s="2" t="s">
-        <v>1240</v>
+        <v>1234</v>
       </c>
       <c r="B752" s="2" t="s">
-        <v>1241</v>
+        <v>1235</v>
       </c>
       <c r="O752" s="2" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="753" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A753" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="B753" s="2" t="s">
-        <v>1244</v>
-      </c>
-      <c r="O753" s="2" t="s">
-        <v>1245</v>
-      </c>
+      <c r="O753" s="2"/>
     </row>
     <row r="754" spans="1:15" ht="24.95" customHeight="1">
       <c r="A754" s="2" t="s">
-        <v>1246</v>
+        <v>1237</v>
       </c>
       <c r="B754" s="2" t="s">
-        <v>1247</v>
+        <v>1238</v>
       </c>
       <c r="O754" s="2" t="s">
-        <v>1248</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="755" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O755" s="2"/>
+      <c r="A755" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B755" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="O755" s="2" t="s">
+        <v>1242</v>
+      </c>
     </row>
     <row r="756" spans="1:15" ht="24.95" customHeight="1">
       <c r="A756" s="2" t="s">
-        <v>1600</v>
+        <v>1243</v>
+      </c>
+      <c r="B756" s="2" t="s">
+        <v>1244</v>
       </c>
       <c r="O756" s="2" t="s">
-        <v>1602</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="757" spans="1:15" ht="24.95" customHeight="1">
       <c r="A757" s="2" t="s">
-        <v>1601</v>
-      </c>
-      <c r="O757" s="3" t="s">
-        <v>1603</v>
+        <v>1246</v>
+      </c>
+      <c r="B757" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="O757" s="2" t="s">
+        <v>1248</v>
       </c>
     </row>
     <row r="758" spans="1:15" ht="24.95" customHeight="1">
       <c r="O758" s="2"/>
     </row>
     <row r="759" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O759" s="2"/>
+      <c r="A759" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="O759" s="2" t="s">
+        <v>1602</v>
+      </c>
     </row>
     <row r="760" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O760" s="2"/>
+      <c r="A760" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="O760" s="3" t="s">
+        <v>1603</v>
+      </c>
     </row>
     <row r="761" spans="1:15" ht="24.95" customHeight="1">
       <c r="O761" s="2"/>
@@ -19504,15 +19574,15 @@
     <row r="854" spans="15:15" ht="24.95" customHeight="1">
       <c r="O854" s="2"/>
     </row>
+    <row r="855" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O855" s="2"/>
+    </row>
     <row r="856" spans="15:15" ht="24.95" customHeight="1">
       <c r="O856" s="2"/>
     </row>
     <row r="857" spans="15:15" ht="24.95" customHeight="1">
       <c r="O857" s="2"/>
     </row>
-    <row r="858" spans="15:15" ht="24.95" customHeight="1">
-      <c r="O858" s="2"/>
-    </row>
     <row r="859" spans="15:15" ht="24.95" customHeight="1">
       <c r="O859" s="2"/>
     </row>
@@ -20684,20 +20754,7 @@
       <c r="O1248" s="2"/>
     </row>
     <row r="1249" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A1249" s="5"/>
-      <c r="B1249" s="5"/>
-      <c r="D1249" s="5"/>
-      <c r="E1249" s="5"/>
-      <c r="F1249" s="5"/>
-      <c r="G1249" s="5"/>
-      <c r="H1249" s="5"/>
-      <c r="I1249" s="5"/>
-      <c r="J1249" s="5"/>
-      <c r="K1249" s="5"/>
-      <c r="L1249" s="5"/>
-      <c r="M1249" s="5"/>
-      <c r="N1249" s="5"/>
-      <c r="O1249" s="6"/>
+      <c r="O1249" s="2"/>
     </row>
     <row r="1250" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1250" s="2"/>
@@ -20706,7 +20763,20 @@
       <c r="O1251" s="2"/>
     </row>
     <row r="1252" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O1252" s="2"/>
+      <c r="A1252" s="5"/>
+      <c r="B1252" s="5"/>
+      <c r="D1252" s="5"/>
+      <c r="E1252" s="5"/>
+      <c r="F1252" s="5"/>
+      <c r="G1252" s="5"/>
+      <c r="H1252" s="5"/>
+      <c r="I1252" s="5"/>
+      <c r="J1252" s="5"/>
+      <c r="K1252" s="5"/>
+      <c r="L1252" s="5"/>
+      <c r="M1252" s="5"/>
+      <c r="N1252" s="5"/>
+      <c r="O1252" s="6"/>
     </row>
     <row r="1253" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1253" s="2"/>
@@ -22214,8 +22284,17 @@
     <row r="1754" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1754" s="2"/>
     </row>
+    <row r="1755" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1755" s="2"/>
+    </row>
+    <row r="1756" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1756" s="2"/>
+    </row>
+    <row r="1757" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1757" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="O1:O1457" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="O1:O1460" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -22224,7 +22303,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q107"/>
+  <dimension ref="A1:Q108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
@@ -22677,612 +22756,612 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A47" s="1" t="s">
-        <v>1604</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>1300</v>
-      </c>
-      <c r="O47" s="1" t="s">
-        <v>1301</v>
-      </c>
-    </row>
     <row r="48" spans="1:15" ht="24.95" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>1302</v>
+        <v>1604</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="24.95" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="24.95" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>2509</v>
+        <v>1306</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="24.95" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>2457</v>
+        <v>1308</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>2458</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="24.95" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>2507</v>
+        <v>2457</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>2511</v>
+        <v>2508</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>2510</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="24.95" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>1310</v>
+        <v>2507</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1311</v>
+        <v>2511</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>1312</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="24.95" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>2898</v>
+        <v>1310</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>2900</v>
+        <v>1311</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>2897</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="24.95" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>2901</v>
+        <v>2898</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>2902</v>
+        <v>2900</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>2982</v>
+        <v>2897</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="24.95" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>2899</v>
+        <v>2901</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>2900</v>
+        <v>2902</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>2904</v>
+        <v>2982</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="24.95" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>2755</v>
+        <v>2899</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>2758</v>
+        <v>2900</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>2759</v>
+        <v>2904</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="24.95" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>3212</v>
+        <v>2755</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>2758</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>3214</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="24.95" customHeight="1">
       <c r="A59" s="1" t="s">
+        <v>3212</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>3214</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A60" s="1" t="s">
         <v>3213</v>
       </c>
-      <c r="O59" s="1" t="s">
+      <c r="O60" s="1" t="s">
         <v>3215</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A61" s="1" t="s">
-        <v>3189</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>3188</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="24.95" customHeight="1">
       <c r="A62" s="1" t="s">
+        <v>3189</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>3188</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A63" s="1" t="s">
         <v>3192</v>
       </c>
-      <c r="O62" s="1" t="s">
+      <c r="O63" s="1" t="s">
         <v>3207</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A64" s="1" t="s">
-        <v>2529</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>2530</v>
-      </c>
-      <c r="O64" s="1" t="s">
-        <v>2531</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="24.95" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>2533</v>
+        <v>2529</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>2532</v>
+        <v>2530</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>3209</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="24.95" customHeight="1">
       <c r="A66" s="1" t="s">
+        <v>2533</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>2532</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>3209</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A67" s="1" t="s">
         <v>2534</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>2535</v>
       </c>
-      <c r="O66" s="1" t="s">
+      <c r="O67" s="1" t="s">
         <v>2536</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A68" s="1" t="s">
-        <v>2919</v>
-      </c>
-      <c r="O68" s="1" t="s">
-        <v>2949</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="24.95" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>2948</v>
+        <v>2949</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="24.95" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>3199</v>
+        <v>2920</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>3201</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="24.95" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="24.95" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>2921</v>
+        <v>3200</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>2947</v>
+        <v>3202</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="24.95" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>2946</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="24.95" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>2945</v>
+        <v>2946</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="24.95" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="24.95" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="24.95" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>3002</v>
+        <v>2925</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>3003</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="24.95" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>2926</v>
+        <v>3002</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>2942</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="24.95" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="24.95" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="81" spans="1:15" ht="24.95" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>2956</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="24.95" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>2955</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="83" spans="1:15" ht="24.95" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>2939</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="24.95" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>2954</v>
+        <v>2939</v>
       </c>
     </row>
     <row r="85" spans="1:15" ht="24.95" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="86" spans="1:15" ht="24.95" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>2938</v>
+        <v>2953</v>
       </c>
     </row>
     <row r="87" spans="1:15" ht="24.95" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>2952</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="24.95" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>2950</v>
+        <v>2952</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="24.95" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="90" spans="1:15" ht="24.95" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>2957</v>
+        <v>2937</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>2958</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="24.95" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>2959</v>
+        <v>2957</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>2960</v>
+        <v>2958</v>
       </c>
     </row>
     <row r="92" spans="1:15" ht="24.95" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>2961</v>
+        <v>2959</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>2962</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="93" spans="1:15" ht="24.95" customHeight="1">
       <c r="A93" s="1" t="s">
+        <v>2961</v>
+      </c>
+      <c r="O93" s="1" t="s">
+        <v>2962</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A94" s="1" t="s">
         <v>3191</v>
       </c>
-      <c r="O93" s="1" t="s">
+      <c r="O94" s="1" t="s">
         <v>3190</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A95" s="1" t="s">
-        <v>3148</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>3147</v>
-      </c>
-      <c r="O95" s="1" t="s">
-        <v>3149</v>
       </c>
     </row>
     <row r="96" spans="1:15" ht="24.95" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>3168</v>
+        <v>3148</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>3093</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>3107</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>3108</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>3109</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>3110</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>3111</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>3112</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>3113</v>
-      </c>
-      <c r="J96" s="1" t="s">
-        <v>3114</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>3115</v>
-      </c>
-      <c r="L96" s="1" t="s">
-        <v>3116</v>
-      </c>
-      <c r="M96" s="1" t="s">
-        <v>3117</v>
-      </c>
-      <c r="N96" s="1" t="s">
-        <v>3118</v>
+        <v>3147</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>3146</v>
+        <v>3149</v>
       </c>
     </row>
     <row r="97" spans="1:15" ht="24.95" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>3119</v>
+        <v>3168</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>3145</v>
+        <v>3093</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>3095</v>
+        <v>3107</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>3096</v>
+        <v>3108</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>3097</v>
+        <v>3109</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>3098</v>
+        <v>3110</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>3099</v>
+        <v>3111</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>3100</v>
+        <v>3112</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>3101</v>
+        <v>3113</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>3102</v>
+        <v>3114</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>3103</v>
+        <v>3115</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>3104</v>
+        <v>3116</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>3105</v>
+        <v>3117</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>3106</v>
+        <v>3118</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>3144</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="98" spans="1:15" ht="24.95" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>3170</v>
+        <v>3145</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>3095</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>3096</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>3097</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>3098</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>3099</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>3100</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>3101</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>3102</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>3103</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>3104</v>
+      </c>
+      <c r="M98" s="1" t="s">
+        <v>3105</v>
+      </c>
+      <c r="N98" s="1" t="s">
+        <v>3106</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>3172</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="99" spans="1:15" ht="24.95" customHeight="1">
       <c r="A99" s="1" t="s">
-        <v>3169</v>
+        <v>3120</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="100" spans="1:15" ht="24.95" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>3121</v>
+        <v>3169</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>3094</v>
+        <v>3171</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>3143</v>
+        <v>3173</v>
       </c>
     </row>
     <row r="101" spans="1:15" ht="24.95" customHeight="1">
       <c r="A101" s="1" t="s">
-        <v>3140</v>
+        <v>3121</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>3141</v>
+        <v>3094</v>
       </c>
       <c r="O101" s="1" t="s">
-        <v>3142</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="102" spans="1:15" ht="24.95" customHeight="1">
       <c r="A102" s="1" t="s">
-        <v>3151</v>
+        <v>3140</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>3150</v>
+        <v>3141</v>
       </c>
       <c r="O102" s="1" t="s">
-        <v>3154</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="103" spans="1:15" ht="24.95" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>3153</v>
+        <v>3150</v>
       </c>
       <c r="O103" s="1" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
     </row>
     <row r="104" spans="1:15" ht="24.95" customHeight="1">
       <c r="A104" s="1" t="s">
-        <v>3159</v>
+        <v>3152</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>3160</v>
+        <v>3153</v>
       </c>
       <c r="O104" s="1" t="s">
-        <v>2546</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="105" spans="1:15" ht="24.95" customHeight="1">
       <c r="A105" s="1" t="s">
-        <v>3165</v>
+        <v>3159</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>1842</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="106" spans="1:15" ht="24.95" customHeight="1">
       <c r="A106" s="1" t="s">
-        <v>3164</v>
+        <v>3165</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>3166</v>
+        <v>3161</v>
       </c>
       <c r="O106" s="1" t="s">
-        <v>3167</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="107" spans="1:15" ht="24.95" customHeight="1">
       <c r="A107" s="1" t="s">
+        <v>3164</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>3166</v>
+      </c>
+      <c r="O107" s="1" t="s">
+        <v>3167</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A108" s="1" t="s">
         <v>3140</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B108" s="1" t="s">
         <v>3162</v>
       </c>
-      <c r="O107" s="1" t="s">
+      <c r="O108" s="1" t="s">
         <v>3163</v>
       </c>
     </row>
@@ -23816,7 +23895,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:S94"/>
+  <dimension ref="A1:S96"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21.5" style="2" customWidth="1"/>
@@ -24921,6 +25000,22 @@
         <v>3085</v>
       </c>
     </row>
+    <row r="95" spans="1:19" ht="20.100000000000001" customHeight="1">
+      <c r="A95" s="2" t="s">
+        <v>3249</v>
+      </c>
+      <c r="O95" s="2" t="s">
+        <v>3252</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" ht="20.100000000000001" customHeight="1">
+      <c r="A96" s="2" t="s">
+        <v>3250</v>
+      </c>
+      <c r="O96" s="2" t="s">
+        <v>3251</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24929,7 +25024,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:Q439"/>
+  <dimension ref="A1:Q443"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="27.875" style="7" customWidth="1"/>
@@ -25716,2224 +25811,2224 @@
     </row>
     <row r="109" spans="1:15">
       <c r="A109" s="7" t="s">
-        <v>1692</v>
+        <v>3237</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>1692</v>
+        <v>3237</v>
       </c>
       <c r="O109" s="7" t="s">
-        <v>1697</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="110" spans="1:15">
       <c r="A110" s="7" t="s">
-        <v>1694</v>
+        <v>3238</v>
       </c>
       <c r="O110" s="7" t="s">
-        <v>2651</v>
+        <v>3241</v>
       </c>
     </row>
     <row r="111" spans="1:15">
       <c r="A111" s="7" t="s">
-        <v>1696</v>
+        <v>3239</v>
       </c>
       <c r="O111" s="7" t="s">
-        <v>1698</v>
+        <v>3242</v>
       </c>
     </row>
     <row r="113" spans="1:15">
       <c r="A113" s="7" t="s">
-        <v>1960</v>
+        <v>1692</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>1960</v>
+        <v>1692</v>
       </c>
       <c r="O113" s="7" t="s">
-        <v>1961</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="114" spans="1:15">
       <c r="A114" s="7" t="s">
-        <v>1962</v>
+        <v>1694</v>
       </c>
       <c r="O114" s="7" t="s">
-        <v>1963</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="115" spans="1:15">
       <c r="A115" s="7" t="s">
-        <v>1964</v>
+        <v>1696</v>
       </c>
       <c r="O115" s="7" t="s">
-        <v>1965</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="117" spans="1:15">
       <c r="A117" s="7" t="s">
-        <v>1966</v>
+        <v>1960</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>1966</v>
+        <v>1960</v>
       </c>
       <c r="O117" s="7" t="s">
-        <v>1967</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="118" spans="1:15">
       <c r="A118" s="7" t="s">
-        <v>1968</v>
+        <v>1962</v>
       </c>
       <c r="O118" s="7" t="s">
-        <v>2652</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="119" spans="1:15">
       <c r="A119" s="7" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="O119" s="7" t="s">
-        <v>1970</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="121" spans="1:15">
       <c r="A121" s="7" t="s">
-        <v>1971</v>
+        <v>1966</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>1971</v>
+        <v>1966</v>
       </c>
       <c r="O121" s="7" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="122" spans="1:15">
       <c r="A122" s="7" t="s">
-        <v>1973</v>
+        <v>1968</v>
       </c>
       <c r="O122" s="7" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="123" spans="1:15">
       <c r="A123" s="7" t="s">
-        <v>1974</v>
+        <v>1969</v>
       </c>
       <c r="O123" s="7" t="s">
-        <v>2654</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="125" spans="1:15">
       <c r="A125" s="7" t="s">
-        <v>1975</v>
+        <v>1971</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>1975</v>
+        <v>1971</v>
       </c>
       <c r="O125" s="7" t="s">
-        <v>1976</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="126" spans="1:15">
       <c r="A126" s="7" t="s">
-        <v>1977</v>
+        <v>1973</v>
       </c>
       <c r="O126" s="7" t="s">
-        <v>2655</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="127" spans="1:15">
       <c r="A127" s="7" t="s">
-        <v>1978</v>
+        <v>1974</v>
       </c>
       <c r="O127" s="7" t="s">
-        <v>2656</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="129" spans="1:15">
       <c r="A129" s="7" t="s">
-        <v>1979</v>
+        <v>1975</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>1979</v>
+        <v>1975</v>
       </c>
       <c r="O129" s="7" t="s">
-        <v>1980</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="130" spans="1:15">
       <c r="A130" s="7" t="s">
-        <v>1981</v>
+        <v>1977</v>
       </c>
       <c r="O130" s="7" t="s">
-        <v>2657</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="131" spans="1:15">
       <c r="A131" s="7" t="s">
-        <v>1982</v>
+        <v>1978</v>
       </c>
       <c r="O131" s="7" t="s">
-        <v>2658</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="133" spans="1:15">
       <c r="A133" s="7" t="s">
-        <v>1983</v>
+        <v>1979</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>1983</v>
+        <v>1979</v>
       </c>
       <c r="O133" s="7" t="s">
-        <v>2659</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="134" spans="1:15">
       <c r="A134" s="7" t="s">
-        <v>1984</v>
+        <v>1981</v>
       </c>
       <c r="O134" s="7" t="s">
-        <v>1985</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="135" spans="1:15">
       <c r="A135" s="7" t="s">
-        <v>1986</v>
+        <v>1982</v>
       </c>
       <c r="O135" s="7" t="s">
-        <v>1985</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="137" spans="1:15">
       <c r="A137" s="7" t="s">
-        <v>2889</v>
+        <v>1983</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>2888</v>
+        <v>1983</v>
       </c>
       <c r="O137" s="7" t="s">
-        <v>2887</v>
+        <v>2659</v>
       </c>
     </row>
     <row r="138" spans="1:15">
       <c r="A138" s="7" t="s">
-        <v>2890</v>
+        <v>1984</v>
       </c>
       <c r="O138" s="7" t="s">
-        <v>2894</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="139" spans="1:15">
       <c r="A139" s="7" t="s">
-        <v>2891</v>
+        <v>1986</v>
       </c>
       <c r="O139" s="7" t="s">
-        <v>2895</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="141" spans="1:15">
       <c r="A141" s="7" t="s">
-        <v>3195</v>
+        <v>2889</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>3194</v>
+        <v>2888</v>
       </c>
       <c r="O141" s="7" t="s">
-        <v>3196</v>
+        <v>2887</v>
       </c>
     </row>
     <row r="142" spans="1:15">
       <c r="A142" s="7" t="s">
-        <v>3197</v>
+        <v>2890</v>
       </c>
       <c r="O142" s="7" t="s">
-        <v>3207</v>
+        <v>2894</v>
       </c>
     </row>
     <row r="143" spans="1:15">
       <c r="A143" s="7" t="s">
-        <v>3198</v>
+        <v>2891</v>
       </c>
       <c r="O143" s="7" t="s">
-        <v>3210</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="145" spans="1:15">
       <c r="A145" s="7" t="s">
-        <v>2473</v>
+        <v>3195</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>2472</v>
+        <v>3194</v>
       </c>
       <c r="O145" s="7" t="s">
-        <v>2476</v>
+        <v>3196</v>
       </c>
     </row>
     <row r="146" spans="1:15">
       <c r="A146" s="7" t="s">
-        <v>2474</v>
+        <v>3197</v>
       </c>
       <c r="O146" s="7" t="s">
-        <v>2477</v>
+        <v>3207</v>
       </c>
     </row>
     <row r="147" spans="1:15">
       <c r="A147" s="7" t="s">
-        <v>2475</v>
+        <v>3198</v>
       </c>
       <c r="O147" s="7" t="s">
-        <v>2660</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="149" spans="1:15">
       <c r="A149" s="7" t="s">
-        <v>1987</v>
+        <v>2473</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>1987</v>
+        <v>2472</v>
       </c>
       <c r="O149" s="7" t="s">
-        <v>1988</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="150" spans="1:15">
       <c r="A150" s="7" t="s">
-        <v>1989</v>
+        <v>2474</v>
       </c>
       <c r="O150" s="7" t="s">
-        <v>2661</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="151" spans="1:15">
       <c r="A151" s="7" t="s">
-        <v>1990</v>
+        <v>2475</v>
       </c>
       <c r="O151" s="7" t="s">
-        <v>1991</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="153" spans="1:15">
       <c r="A153" s="7" t="s">
-        <v>1992</v>
+        <v>1987</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>1992</v>
+        <v>1987</v>
       </c>
       <c r="O153" s="7" t="s">
-        <v>1993</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="154" spans="1:15">
       <c r="A154" s="7" t="s">
-        <v>1994</v>
+        <v>1989</v>
       </c>
       <c r="O154" s="7" t="s">
-        <v>1995</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="155" spans="1:15">
       <c r="A155" s="7" t="s">
-        <v>1996</v>
+        <v>1990</v>
       </c>
       <c r="O155" s="7" t="s">
-        <v>1995</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="157" spans="1:15">
       <c r="A157" s="7" t="s">
-        <v>1997</v>
+        <v>1992</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>1702</v>
+        <v>1992</v>
       </c>
       <c r="O157" s="7" t="s">
-        <v>1998</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="158" spans="1:15">
       <c r="A158" s="7" t="s">
-        <v>1999</v>
+        <v>1994</v>
       </c>
       <c r="O158" s="7" t="s">
-        <v>2000</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="159" spans="1:15">
       <c r="A159" s="7" t="s">
-        <v>2001</v>
+        <v>1996</v>
       </c>
       <c r="O159" s="7" t="s">
-        <v>2002</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="161" spans="1:15">
       <c r="A161" s="7" t="s">
-        <v>2003</v>
+        <v>1997</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="O161" s="7" t="s">
-        <v>2004</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="162" spans="1:15">
       <c r="A162" s="7" t="s">
-        <v>2005</v>
+        <v>1999</v>
       </c>
       <c r="O162" s="7" t="s">
-        <v>2006</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="163" spans="1:15">
       <c r="A163" s="7" t="s">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="O163" s="7" t="s">
-        <v>2006</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="165" spans="1:15">
       <c r="A165" s="7" t="s">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>2008</v>
+        <v>1703</v>
       </c>
       <c r="O165" s="7" t="s">
-        <v>2662</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="166" spans="1:15">
       <c r="A166" s="7" t="s">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="O166" s="7" t="s">
-        <v>2663</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="167" spans="1:15">
       <c r="A167" s="7" t="s">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="O167" s="7" t="s">
-        <v>2663</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="169" spans="1:15">
       <c r="A169" s="7" t="s">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="O169" s="7" t="s">
-        <v>2664</v>
+        <v>2662</v>
       </c>
     </row>
     <row r="170" spans="1:15">
       <c r="A170" s="7" t="s">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="O170" s="7" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="171" spans="1:15">
       <c r="A171" s="7" t="s">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="O171" s="7" t="s">
-        <v>2666</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="173" spans="1:15">
       <c r="A173" s="7" t="s">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="O173" s="7" t="s">
-        <v>2015</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="174" spans="1:15">
       <c r="A174" s="7" t="s">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="O174" s="7" t="s">
-        <v>2017</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="175" spans="1:15">
       <c r="A175" s="7" t="s">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="O175" s="7" t="s">
-        <v>2667</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="177" spans="1:15">
       <c r="A177" s="7" t="s">
-        <v>3185</v>
+        <v>2014</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>3181</v>
+        <v>2014</v>
       </c>
       <c r="O177" s="7" t="s">
-        <v>3182</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="178" spans="1:15">
       <c r="A178" s="7" t="s">
-        <v>3184</v>
+        <v>2016</v>
       </c>
       <c r="O178" s="7" t="s">
-        <v>3187</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="179" spans="1:15">
       <c r="A179" s="7" t="s">
-        <v>3183</v>
+        <v>2018</v>
       </c>
       <c r="O179" s="7" t="s">
-        <v>3186</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="181" spans="1:15">
       <c r="A181" s="7" t="s">
-        <v>2019</v>
+        <v>3185</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>2019</v>
+        <v>3181</v>
       </c>
       <c r="O181" s="7" t="s">
-        <v>2668</v>
+        <v>3182</v>
       </c>
     </row>
     <row r="182" spans="1:15">
       <c r="A182" s="7" t="s">
-        <v>2020</v>
+        <v>3184</v>
       </c>
       <c r="O182" s="7" t="s">
-        <v>2669</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="183" spans="1:15">
       <c r="A183" s="7" t="s">
-        <v>2021</v>
+        <v>3183</v>
       </c>
       <c r="O183" s="7" t="s">
-        <v>2022</v>
+        <v>3186</v>
       </c>
     </row>
     <row r="185" spans="1:15">
       <c r="A185" s="7" t="s">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="O185" s="7" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="186" spans="1:15">
       <c r="A186" s="7" t="s">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="O186" s="7" t="s">
-        <v>2671</v>
+        <v>2669</v>
       </c>
     </row>
     <row r="187" spans="1:15">
       <c r="A187" s="7" t="s">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="O187" s="7" t="s">
-        <v>2026</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="189" spans="1:15">
       <c r="A189" s="7" t="s">
-        <v>2993</v>
+        <v>2023</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>2993</v>
+        <v>2023</v>
       </c>
       <c r="O189" s="7" t="s">
-        <v>3019</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="190" spans="1:15">
       <c r="A190" s="7" t="s">
-        <v>2995</v>
+        <v>2024</v>
       </c>
       <c r="O190" s="7" t="s">
-        <v>3020</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="191" spans="1:15">
       <c r="A191" s="7" t="s">
-        <v>2994</v>
+        <v>2025</v>
       </c>
       <c r="O191" s="7" t="s">
-        <v>2996</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="193" spans="1:15">
       <c r="A193" s="7" t="s">
-        <v>2027</v>
+        <v>2993</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>2027</v>
+        <v>2993</v>
       </c>
       <c r="O193" s="7" t="s">
-        <v>2672</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="194" spans="1:15">
       <c r="A194" s="7" t="s">
-        <v>2028</v>
+        <v>2995</v>
       </c>
       <c r="O194" s="7" t="s">
-        <v>2673</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="195" spans="1:15">
       <c r="A195" s="7" t="s">
-        <v>2029</v>
+        <v>2994</v>
       </c>
       <c r="O195" s="7" t="s">
-        <v>2674</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="197" spans="1:15">
       <c r="A197" s="7" t="s">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="O197" s="7" t="s">
-        <v>2031</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="198" spans="1:15">
       <c r="A198" s="7" t="s">
-        <v>2032</v>
+        <v>2028</v>
       </c>
       <c r="O198" s="7" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="199" spans="1:15">
       <c r="A199" s="7" t="s">
-        <v>2033</v>
+        <v>2029</v>
       </c>
       <c r="O199" s="7" t="s">
-        <v>2676</v>
+        <v>2674</v>
       </c>
     </row>
     <row r="201" spans="1:15">
       <c r="A201" s="7" t="s">
-        <v>2034</v>
+        <v>2030</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>2034</v>
+        <v>2030</v>
       </c>
       <c r="O201" s="7" t="s">
-        <v>2035</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="202" spans="1:15">
       <c r="A202" s="7" t="s">
-        <v>2036</v>
+        <v>2032</v>
       </c>
       <c r="O202" s="7" t="s">
-        <v>2037</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="203" spans="1:15">
       <c r="A203" s="7" t="s">
-        <v>2038</v>
+        <v>2033</v>
       </c>
       <c r="O203" s="7" t="s">
-        <v>2677</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="205" spans="1:15">
       <c r="A205" s="7" t="s">
-        <v>2039</v>
+        <v>2034</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>2039</v>
+        <v>2034</v>
       </c>
       <c r="O205" s="7" t="s">
-        <v>2040</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="206" spans="1:15">
       <c r="A206" s="7" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
       <c r="O206" s="7" t="s">
-        <v>2678</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="207" spans="1:15">
       <c r="A207" s="7" t="s">
-        <v>2042</v>
+        <v>2038</v>
       </c>
       <c r="O207" s="7" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="209" spans="1:15">
       <c r="A209" s="7" t="s">
-        <v>2043</v>
+        <v>2039</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>2043</v>
+        <v>2039</v>
       </c>
       <c r="O209" s="7" t="s">
-        <v>2044</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="210" spans="1:15">
       <c r="A210" s="7" t="s">
-        <v>2045</v>
+        <v>2041</v>
       </c>
       <c r="O210" s="7" t="s">
-        <v>2680</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="211" spans="1:15">
       <c r="A211" s="7" t="s">
-        <v>2046</v>
+        <v>2042</v>
       </c>
       <c r="O211" s="7" t="s">
-        <v>2047</v>
+        <v>2679</v>
       </c>
     </row>
     <row r="213" spans="1:15">
       <c r="A213" s="7" t="s">
-        <v>2048</v>
+        <v>2043</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>2048</v>
+        <v>2043</v>
       </c>
       <c r="O213" s="7" t="s">
-        <v>2049</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="214" spans="1:15">
       <c r="A214" s="7" t="s">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="O214" s="7" t="s">
-        <v>2051</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="215" spans="1:15">
       <c r="A215" s="7" t="s">
-        <v>2052</v>
+        <v>2046</v>
       </c>
       <c r="O215" s="7" t="s">
-        <v>2053</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="217" spans="1:15">
       <c r="A217" s="7" t="s">
-        <v>2054</v>
+        <v>2048</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>2054</v>
+        <v>2048</v>
       </c>
       <c r="O217" s="7" t="s">
-        <v>2055</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="218" spans="1:15">
       <c r="A218" s="7" t="s">
-        <v>2056</v>
+        <v>2050</v>
       </c>
       <c r="O218" s="7" t="s">
-        <v>2681</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="219" spans="1:15">
       <c r="A219" s="7" t="s">
-        <v>2057</v>
+        <v>2052</v>
       </c>
       <c r="O219" s="7" t="s">
-        <v>2682</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="221" spans="1:15">
       <c r="A221" s="7" t="s">
-        <v>2058</v>
+        <v>2054</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>2058</v>
+        <v>2054</v>
       </c>
       <c r="O221" s="7" t="s">
-        <v>2683</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="222" spans="1:15">
       <c r="A222" s="7" t="s">
-        <v>2059</v>
+        <v>2056</v>
       </c>
       <c r="O222" s="7" t="s">
-        <v>2684</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="223" spans="1:15">
       <c r="A223" s="7" t="s">
-        <v>2060</v>
+        <v>2057</v>
       </c>
       <c r="O223" s="7" t="s">
-        <v>2061</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="225" spans="1:15">
       <c r="A225" s="7" t="s">
-        <v>2062</v>
+        <v>2058</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>2062</v>
+        <v>2058</v>
       </c>
       <c r="O225" s="7" t="s">
-        <v>2063</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="226" spans="1:15">
       <c r="A226" s="7" t="s">
-        <v>2064</v>
+        <v>2059</v>
       </c>
       <c r="O226" s="7" t="s">
-        <v>2685</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="227" spans="1:15">
       <c r="A227" s="7" t="s">
-        <v>2065</v>
+        <v>2060</v>
       </c>
       <c r="O227" s="7" t="s">
-        <v>2686</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="229" spans="1:15">
       <c r="A229" s="7" t="s">
-        <v>2066</v>
+        <v>2062</v>
       </c>
       <c r="B229" s="7" t="s">
-        <v>2066</v>
+        <v>2062</v>
       </c>
       <c r="O229" s="7" t="s">
-        <v>2067</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="230" spans="1:15">
       <c r="A230" s="7" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
       <c r="O230" s="7" t="s">
-        <v>2687</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="231" spans="1:15">
       <c r="A231" s="7" t="s">
-        <v>2069</v>
+        <v>2065</v>
       </c>
       <c r="O231" s="7" t="s">
-        <v>2070</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="233" spans="1:15">
       <c r="A233" s="7" t="s">
-        <v>2071</v>
+        <v>2066</v>
       </c>
       <c r="B233" s="7" t="s">
-        <v>2071</v>
+        <v>2066</v>
       </c>
       <c r="O233" s="7" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="234" spans="1:15">
       <c r="A234" s="7" t="s">
-        <v>2073</v>
+        <v>2068</v>
       </c>
       <c r="O234" s="7" t="s">
-        <v>2688</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="235" spans="1:15">
       <c r="A235" s="7" t="s">
-        <v>2074</v>
+        <v>2069</v>
       </c>
       <c r="O235" s="7" t="s">
-        <v>2688</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="237" spans="1:15">
       <c r="A237" s="7" t="s">
-        <v>2075</v>
+        <v>2071</v>
       </c>
       <c r="B237" s="7" t="s">
-        <v>2075</v>
+        <v>2071</v>
       </c>
       <c r="O237" s="7" t="s">
-        <v>2076</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="238" spans="1:15">
       <c r="A238" s="7" t="s">
-        <v>2077</v>
+        <v>2073</v>
       </c>
       <c r="O238" s="7" t="s">
-        <v>2689</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="239" spans="1:15">
       <c r="A239" s="7" t="s">
-        <v>2078</v>
+        <v>2074</v>
       </c>
       <c r="O239" s="7" t="s">
-        <v>2631</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="241" spans="1:15">
       <c r="A241" s="7" t="s">
-        <v>2079</v>
+        <v>2075</v>
       </c>
       <c r="B241" s="7" t="s">
-        <v>2080</v>
+        <v>2075</v>
       </c>
       <c r="O241" s="7" t="s">
-        <v>2690</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="242" spans="1:15">
       <c r="A242" s="7" t="s">
-        <v>2081</v>
+        <v>2077</v>
       </c>
       <c r="O242" s="7" t="s">
-        <v>2691</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="243" spans="1:15">
       <c r="A243" s="7" t="s">
-        <v>2082</v>
+        <v>2078</v>
       </c>
       <c r="O243" s="7" t="s">
-        <v>2692</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="245" spans="1:15">
       <c r="A245" s="7" t="s">
-        <v>2083</v>
+        <v>2079</v>
       </c>
       <c r="B245" s="7" t="s">
-        <v>2084</v>
+        <v>2080</v>
       </c>
       <c r="O245" s="7" t="s">
-        <v>2693</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="246" spans="1:15">
       <c r="A246" s="7" t="s">
-        <v>2085</v>
+        <v>2081</v>
       </c>
       <c r="O246" s="7" t="s">
-        <v>2086</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="247" spans="1:15">
       <c r="A247" s="7" t="s">
-        <v>2087</v>
+        <v>2082</v>
       </c>
       <c r="O247" s="7" t="s">
-        <v>2694</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="249" spans="1:15">
       <c r="A249" s="7" t="s">
-        <v>1674</v>
+        <v>2083</v>
       </c>
       <c r="B249" s="7" t="s">
-        <v>1674</v>
+        <v>2084</v>
       </c>
       <c r="O249" s="7" t="s">
-        <v>2088</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="250" spans="1:15">
       <c r="A250" s="7" t="s">
-        <v>2695</v>
+        <v>2085</v>
       </c>
       <c r="O250" s="7" t="s">
-        <v>2696</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="251" spans="1:15">
       <c r="A251" s="7" t="s">
-        <v>2697</v>
+        <v>2087</v>
       </c>
       <c r="O251" s="7" t="s">
-        <v>2698</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="253" spans="1:15">
       <c r="A253" s="7" t="s">
-        <v>2089</v>
+        <v>1674</v>
       </c>
       <c r="B253" s="7" t="s">
-        <v>2089</v>
+        <v>1674</v>
       </c>
       <c r="O253" s="7" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="254" spans="1:15">
       <c r="A254" s="7" t="s">
-        <v>2091</v>
+        <v>2695</v>
       </c>
       <c r="O254" s="7" t="s">
-        <v>2092</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="255" spans="1:15">
       <c r="A255" s="7" t="s">
-        <v>2093</v>
+        <v>2697</v>
       </c>
       <c r="O255" s="7" t="s">
-        <v>2699</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="257" spans="1:15">
       <c r="A257" s="7" t="s">
-        <v>2094</v>
+        <v>2089</v>
       </c>
       <c r="B257" s="7" t="s">
-        <v>2094</v>
+        <v>2089</v>
       </c>
       <c r="O257" s="7" t="s">
-        <v>2095</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="258" spans="1:15">
       <c r="A258" s="7" t="s">
-        <v>2096</v>
+        <v>2091</v>
       </c>
       <c r="O258" s="7" t="s">
-        <v>2700</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="259" spans="1:15">
       <c r="A259" s="7" t="s">
-        <v>2097</v>
+        <v>2093</v>
       </c>
       <c r="O259" s="7" t="s">
-        <v>2701</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="261" spans="1:15">
       <c r="A261" s="7" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
       <c r="B261" s="7" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
       <c r="O261" s="7" t="s">
-        <v>2099</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="262" spans="1:15">
       <c r="A262" s="7" t="s">
-        <v>2100</v>
+        <v>2096</v>
       </c>
       <c r="O262" s="7" t="s">
-        <v>2702</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="263" spans="1:15">
       <c r="A263" s="7" t="s">
-        <v>2101</v>
+        <v>2097</v>
       </c>
       <c r="O263" s="7" t="s">
-        <v>2102</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="265" spans="1:15">
       <c r="A265" s="7" t="s">
-        <v>2103</v>
+        <v>2098</v>
       </c>
       <c r="B265" s="7" t="s">
-        <v>2103</v>
+        <v>2098</v>
       </c>
       <c r="O265" s="7" t="s">
-        <v>2104</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="266" spans="1:15">
       <c r="A266" s="7" t="s">
-        <v>2105</v>
+        <v>2100</v>
       </c>
       <c r="O266" s="7" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="267" spans="1:15">
       <c r="A267" s="7" t="s">
-        <v>2106</v>
+        <v>2101</v>
       </c>
       <c r="O267" s="7" t="s">
-        <v>2704</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="269" spans="1:15">
       <c r="A269" s="7" t="s">
-        <v>2107</v>
+        <v>2103</v>
       </c>
       <c r="B269" s="7" t="s">
-        <v>2107</v>
+        <v>2103</v>
       </c>
       <c r="O269" s="7" t="s">
-        <v>2108</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="270" spans="1:15">
       <c r="A270" s="7" t="s">
-        <v>2109</v>
+        <v>2105</v>
       </c>
       <c r="O270" s="7" t="s">
-        <v>2705</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="271" spans="1:15">
       <c r="A271" s="7" t="s">
-        <v>2110</v>
+        <v>2106</v>
       </c>
       <c r="O271" s="7" t="s">
-        <v>2111</v>
+        <v>2704</v>
       </c>
     </row>
     <row r="273" spans="1:15">
       <c r="A273" s="7" t="s">
-        <v>2112</v>
+        <v>2107</v>
       </c>
       <c r="B273" s="7" t="s">
-        <v>2112</v>
+        <v>2107</v>
       </c>
       <c r="O273" s="7" t="s">
-        <v>2113</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="274" spans="1:15">
       <c r="A274" s="7" t="s">
-        <v>2114</v>
+        <v>2109</v>
       </c>
       <c r="O274" s="7" t="s">
-        <v>2706</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="275" spans="1:15">
       <c r="A275" s="7" t="s">
-        <v>2115</v>
+        <v>2110</v>
       </c>
       <c r="O275" s="7" t="s">
-        <v>2707</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="277" spans="1:15">
       <c r="A277" s="7" t="s">
-        <v>2116</v>
+        <v>2112</v>
       </c>
       <c r="B277" s="7" t="s">
-        <v>2116</v>
+        <v>2112</v>
       </c>
       <c r="O277" s="7" t="s">
-        <v>2117</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="278" spans="1:15">
       <c r="A278" s="7" t="s">
-        <v>2118</v>
+        <v>2114</v>
       </c>
       <c r="O278" s="7" t="s">
-        <v>2708</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="279" spans="1:15">
       <c r="A279" s="7" t="s">
-        <v>2119</v>
+        <v>2115</v>
       </c>
       <c r="O279" s="7" t="s">
-        <v>2120</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="281" spans="1:15">
       <c r="A281" s="7" t="s">
-        <v>2121</v>
+        <v>2116</v>
       </c>
       <c r="B281" s="7" t="s">
-        <v>2121</v>
+        <v>2116</v>
       </c>
       <c r="O281" s="7" t="s">
-        <v>2122</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="282" spans="1:15">
       <c r="A282" s="7" t="s">
-        <v>2123</v>
+        <v>2118</v>
       </c>
       <c r="O282" s="7" t="s">
-        <v>2124</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="283" spans="1:15">
       <c r="A283" s="7" t="s">
-        <v>2125</v>
+        <v>2119</v>
       </c>
       <c r="O283" s="7" t="s">
-        <v>2709</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="285" spans="1:15">
       <c r="A285" s="7" t="s">
-        <v>2126</v>
+        <v>2121</v>
       </c>
       <c r="B285" s="7" t="s">
-        <v>2126</v>
+        <v>2121</v>
       </c>
       <c r="O285" s="7" t="s">
-        <v>2127</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="286" spans="1:15">
       <c r="A286" s="7" t="s">
-        <v>2128</v>
+        <v>2123</v>
       </c>
       <c r="O286" s="7" t="s">
-        <v>2129</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="287" spans="1:15">
       <c r="A287" s="7" t="s">
-        <v>2130</v>
+        <v>2125</v>
       </c>
       <c r="O287" s="7" t="s">
-        <v>2710</v>
+        <v>2709</v>
       </c>
     </row>
     <row r="289" spans="1:15">
       <c r="A289" s="7" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="B289" s="7" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="O289" s="7" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="290" spans="1:15">
       <c r="A290" s="7" t="s">
-        <v>2133</v>
+        <v>2128</v>
       </c>
       <c r="O290" s="7" t="s">
-        <v>2711</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="291" spans="1:15">
       <c r="A291" s="7" t="s">
-        <v>2134</v>
+        <v>2130</v>
       </c>
       <c r="O291" s="7" t="s">
-        <v>2712</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="293" spans="1:15">
       <c r="A293" s="7" t="s">
-        <v>2135</v>
+        <v>2131</v>
       </c>
       <c r="B293" s="7" t="s">
-        <v>2135</v>
+        <v>2131</v>
       </c>
       <c r="O293" s="7" t="s">
-        <v>2136</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="294" spans="1:15">
       <c r="A294" s="7" t="s">
-        <v>1826</v>
+        <v>2133</v>
       </c>
       <c r="O294" s="7" t="s">
-        <v>2137</v>
+        <v>2711</v>
       </c>
     </row>
     <row r="295" spans="1:15">
       <c r="A295" s="7" t="s">
-        <v>1828</v>
+        <v>2134</v>
       </c>
       <c r="O295" s="7" t="s">
-        <v>2713</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="297" spans="1:15">
       <c r="A297" s="7" t="s">
-        <v>1823</v>
+        <v>2135</v>
       </c>
       <c r="B297" s="7" t="s">
-        <v>1824</v>
+        <v>2135</v>
       </c>
       <c r="O297" s="7" t="s">
-        <v>1825</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="298" spans="1:15">
       <c r="A298" s="7" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="O298" s="7" t="s">
-        <v>1831</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="299" spans="1:15">
       <c r="A299" s="7" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="O299" s="7" t="s">
-        <v>1830</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="301" spans="1:15">
       <c r="A301" s="7" t="s">
-        <v>2520</v>
+        <v>1823</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>2520</v>
+        <v>1824</v>
       </c>
       <c r="O301" s="7" t="s">
-        <v>2523</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="302" spans="1:15">
       <c r="A302" s="7" t="s">
-        <v>2521</v>
+        <v>1827</v>
       </c>
       <c r="O302" s="7" t="s">
-        <v>2612</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="303" spans="1:15">
       <c r="A303" s="7" t="s">
-        <v>2522</v>
+        <v>1829</v>
       </c>
       <c r="O303" s="7" t="s">
-        <v>2524</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="305" spans="1:15">
       <c r="A305" s="7" t="s">
-        <v>3079</v>
+        <v>2520</v>
       </c>
       <c r="B305" s="7" t="s">
-        <v>3079</v>
+        <v>2520</v>
       </c>
       <c r="O305" s="7" t="s">
-        <v>3064</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="306" spans="1:15">
       <c r="A306" s="7" t="s">
-        <v>3062</v>
+        <v>2521</v>
       </c>
       <c r="O306" s="7" t="s">
-        <v>3076</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="307" spans="1:15">
       <c r="A307" s="7" t="s">
-        <v>3063</v>
+        <v>2522</v>
       </c>
       <c r="O307" s="7" t="s">
-        <v>3075</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="309" spans="1:15">
       <c r="A309" s="7" t="s">
-        <v>2138</v>
+        <v>3079</v>
       </c>
       <c r="B309" s="7" t="s">
-        <v>2138</v>
+        <v>3079</v>
       </c>
       <c r="O309" s="7" t="s">
-        <v>2139</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="310" spans="1:15">
       <c r="A310" s="7" t="s">
-        <v>2140</v>
+        <v>3062</v>
       </c>
       <c r="O310" s="7" t="s">
-        <v>2714</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="311" spans="1:15">
       <c r="A311" s="7" t="s">
-        <v>2141</v>
+        <v>3063</v>
       </c>
       <c r="O311" s="7" t="s">
-        <v>2142</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="313" spans="1:15">
       <c r="A313" s="7" t="s">
-        <v>2143</v>
+        <v>2138</v>
       </c>
       <c r="B313" s="7" t="s">
-        <v>2715</v>
+        <v>2138</v>
       </c>
       <c r="O313" s="7" t="s">
-        <v>2144</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="314" spans="1:15">
       <c r="A314" s="7" t="s">
-        <v>2145</v>
+        <v>2140</v>
       </c>
       <c r="O314" s="7" t="s">
-        <v>2716</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="315" spans="1:15">
       <c r="A315" s="7" t="s">
-        <v>2146</v>
+        <v>2141</v>
       </c>
       <c r="O315" s="7" t="s">
-        <v>2717</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="317" spans="1:15">
       <c r="A317" s="7" t="s">
-        <v>2147</v>
+        <v>2143</v>
       </c>
       <c r="B317" s="7" t="s">
-        <v>2147</v>
+        <v>2715</v>
       </c>
       <c r="O317" s="7" t="s">
-        <v>2148</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="318" spans="1:15">
       <c r="A318" s="7" t="s">
-        <v>2149</v>
+        <v>2145</v>
       </c>
       <c r="O318" s="7" t="s">
-        <v>2150</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="319" spans="1:15">
       <c r="A319" s="7" t="s">
-        <v>2151</v>
+        <v>2146</v>
       </c>
       <c r="O319" s="7" t="s">
-        <v>2152</v>
+        <v>2717</v>
       </c>
     </row>
     <row r="321" spans="1:15">
       <c r="A321" s="7" t="s">
-        <v>2976</v>
+        <v>2147</v>
       </c>
       <c r="B321" s="7" t="s">
-        <v>2975</v>
+        <v>2147</v>
       </c>
       <c r="O321" s="7" t="s">
-        <v>2977</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="322" spans="1:15">
       <c r="A322" s="7" t="s">
-        <v>2983</v>
+        <v>2149</v>
       </c>
       <c r="O322" s="7" t="s">
-        <v>2980</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="323" spans="1:15">
       <c r="A323" s="7" t="s">
-        <v>2984</v>
+        <v>2151</v>
       </c>
       <c r="O323" s="7" t="s">
-        <v>2979</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="325" spans="1:15">
       <c r="A325" s="7" t="s">
-        <v>2153</v>
+        <v>2976</v>
       </c>
       <c r="B325" s="7" t="s">
-        <v>2153</v>
+        <v>2975</v>
       </c>
       <c r="O325" s="7" t="s">
-        <v>2154</v>
+        <v>2977</v>
       </c>
     </row>
     <row r="326" spans="1:15">
       <c r="A326" s="7" t="s">
-        <v>2155</v>
+        <v>2983</v>
       </c>
       <c r="O326" s="7" t="s">
-        <v>2156</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="327" spans="1:15">
       <c r="A327" s="7" t="s">
-        <v>2157</v>
+        <v>2984</v>
       </c>
       <c r="O327" s="7" t="s">
-        <v>2718</v>
+        <v>2979</v>
       </c>
     </row>
     <row r="329" spans="1:15">
       <c r="A329" s="7" t="s">
-        <v>2158</v>
+        <v>2153</v>
       </c>
       <c r="B329" s="7" t="s">
-        <v>2158</v>
+        <v>2153</v>
       </c>
       <c r="O329" s="7" t="s">
-        <v>2159</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="330" spans="1:15">
       <c r="A330" s="7" t="s">
-        <v>2160</v>
+        <v>2155</v>
       </c>
       <c r="O330" s="7" t="s">
-        <v>2766</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="331" spans="1:15">
       <c r="A331" s="7" t="s">
-        <v>2161</v>
+        <v>2157</v>
       </c>
       <c r="O331" s="7" t="s">
-        <v>2766</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="333" spans="1:15">
       <c r="A333" s="7" t="s">
-        <v>2162</v>
+        <v>2158</v>
       </c>
       <c r="B333" s="7" t="s">
-        <v>2162</v>
+        <v>2158</v>
       </c>
       <c r="O333" s="7" t="s">
-        <v>2163</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="334" spans="1:15">
       <c r="A334" s="7" t="s">
-        <v>2164</v>
+        <v>2160</v>
       </c>
       <c r="O334" s="7" t="s">
-        <v>2719</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="335" spans="1:15">
       <c r="A335" s="7" t="s">
-        <v>2165</v>
+        <v>2161</v>
       </c>
       <c r="O335" s="7" t="s">
-        <v>2166</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="337" spans="1:15">
       <c r="A337" s="7" t="s">
-        <v>2167</v>
+        <v>2162</v>
       </c>
       <c r="B337" s="7" t="s">
-        <v>2167</v>
+        <v>2162</v>
       </c>
       <c r="O337" s="7" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="338" spans="1:15">
       <c r="A338" s="7" t="s">
-        <v>2169</v>
+        <v>2164</v>
       </c>
       <c r="O338" s="7" t="s">
-        <v>2720</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="339" spans="1:15">
       <c r="A339" s="7" t="s">
-        <v>2170</v>
+        <v>2165</v>
       </c>
       <c r="O339" s="7" t="s">
-        <v>2721</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="341" spans="1:15">
       <c r="A341" s="7" t="s">
-        <v>2171</v>
+        <v>2167</v>
       </c>
       <c r="B341" s="7" t="s">
-        <v>2171</v>
+        <v>2167</v>
       </c>
       <c r="O341" s="7" t="s">
-        <v>2172</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="342" spans="1:15">
       <c r="A342" s="7" t="s">
-        <v>2173</v>
+        <v>2169</v>
       </c>
       <c r="O342" s="7" t="s">
-        <v>2174</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="343" spans="1:15">
       <c r="A343" s="7" t="s">
-        <v>2175</v>
+        <v>2170</v>
       </c>
       <c r="O343" s="7" t="s">
-        <v>2176</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="345" spans="1:15">
       <c r="A345" s="7" t="s">
-        <v>2177</v>
+        <v>2171</v>
       </c>
       <c r="B345" s="7" t="s">
-        <v>2177</v>
+        <v>2171</v>
       </c>
       <c r="O345" s="7" t="s">
-        <v>2178</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="346" spans="1:15">
       <c r="A346" s="7" t="s">
-        <v>2179</v>
+        <v>2173</v>
       </c>
       <c r="O346" s="7" t="s">
-        <v>2722</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="347" spans="1:15">
       <c r="A347" s="7" t="s">
-        <v>2180</v>
+        <v>2175</v>
       </c>
       <c r="O347" s="7" t="s">
-        <v>2181</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="349" spans="1:15">
       <c r="A349" s="7" t="s">
-        <v>2182</v>
+        <v>2177</v>
       </c>
       <c r="B349" s="7" t="s">
-        <v>2182</v>
+        <v>2177</v>
       </c>
       <c r="O349" s="7" t="s">
-        <v>2183</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="350" spans="1:15">
       <c r="A350" s="7" t="s">
-        <v>2184</v>
+        <v>2179</v>
       </c>
       <c r="O350" s="7" t="s">
-        <v>2185</v>
+        <v>2722</v>
       </c>
     </row>
     <row r="351" spans="1:15">
       <c r="A351" s="7" t="s">
-        <v>2186</v>
+        <v>2180</v>
       </c>
       <c r="O351" s="7" t="s">
-        <v>2723</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="353" spans="1:15">
       <c r="A353" s="7" t="s">
-        <v>2187</v>
+        <v>2182</v>
       </c>
       <c r="B353" s="7" t="s">
-        <v>2187</v>
+        <v>2182</v>
       </c>
       <c r="O353" s="7" t="s">
-        <v>2188</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="354" spans="1:15">
       <c r="A354" s="7" t="s">
-        <v>2189</v>
+        <v>2184</v>
       </c>
       <c r="O354" s="7" t="s">
-        <v>2190</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="355" spans="1:15">
       <c r="A355" s="7" t="s">
-        <v>2191</v>
+        <v>2186</v>
       </c>
       <c r="O355" s="7" t="s">
-        <v>2724</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="357" spans="1:15">
       <c r="A357" s="7" t="s">
-        <v>2192</v>
+        <v>2187</v>
       </c>
       <c r="B357" s="7" t="s">
-        <v>2192</v>
+        <v>2187</v>
       </c>
       <c r="O357" s="7" t="s">
-        <v>2193</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="358" spans="1:15">
       <c r="A358" s="7" t="s">
-        <v>2194</v>
+        <v>2189</v>
       </c>
       <c r="O358" s="7" t="s">
-        <v>2725</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="359" spans="1:15">
       <c r="A359" s="7" t="s">
-        <v>2195</v>
+        <v>2191</v>
       </c>
       <c r="O359" s="7" t="s">
-        <v>2196</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="361" spans="1:15">
       <c r="A361" s="7" t="s">
-        <v>2197</v>
+        <v>2192</v>
       </c>
       <c r="B361" s="7" t="s">
-        <v>2197</v>
+        <v>2192</v>
       </c>
       <c r="O361" s="7" t="s">
-        <v>2198</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="362" spans="1:15">
       <c r="A362" s="7" t="s">
-        <v>2199</v>
+        <v>2194</v>
       </c>
       <c r="O362" s="7" t="s">
-        <v>2200</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="363" spans="1:15">
       <c r="A363" s="7" t="s">
-        <v>2201</v>
+        <v>2195</v>
       </c>
       <c r="O363" s="7" t="s">
-        <v>2200</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="365" spans="1:15">
       <c r="A365" s="7" t="s">
-        <v>2202</v>
+        <v>2197</v>
       </c>
       <c r="B365" s="7" t="s">
-        <v>2202</v>
+        <v>2197</v>
       </c>
       <c r="O365" s="7" t="s">
-        <v>2203</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="366" spans="1:15">
       <c r="A366" s="7" t="s">
-        <v>2204</v>
+        <v>2199</v>
       </c>
       <c r="O366" s="7" t="s">
-        <v>2205</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="367" spans="1:15">
       <c r="A367" s="7" t="s">
-        <v>2206</v>
+        <v>2201</v>
       </c>
       <c r="O367" s="7" t="s">
-        <v>2726</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="369" spans="1:15">
       <c r="A369" s="7" t="s">
-        <v>2207</v>
+        <v>2202</v>
       </c>
       <c r="B369" s="7" t="s">
-        <v>2207</v>
+        <v>2202</v>
       </c>
       <c r="O369" s="7" t="s">
-        <v>2208</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="370" spans="1:15">
       <c r="A370" s="7" t="s">
-        <v>2209</v>
+        <v>2204</v>
       </c>
       <c r="O370" s="7" t="s">
-        <v>2727</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="371" spans="1:15">
       <c r="A371" s="7" t="s">
-        <v>2210</v>
+        <v>2206</v>
       </c>
       <c r="O371" s="7" t="s">
-        <v>2211</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="373" spans="1:15">
       <c r="A373" s="7" t="s">
-        <v>2212</v>
+        <v>2207</v>
       </c>
       <c r="B373" s="7" t="s">
-        <v>2213</v>
+        <v>2207</v>
       </c>
       <c r="O373" s="7" t="s">
-        <v>2213</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="374" spans="1:15">
       <c r="A374" s="7" t="s">
-        <v>2214</v>
+        <v>2209</v>
       </c>
       <c r="O374" s="7" t="s">
-        <v>2215</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="375" spans="1:15">
       <c r="A375" s="7" t="s">
-        <v>2216</v>
+        <v>2210</v>
       </c>
       <c r="O375" s="7" t="s">
-        <v>2728</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="377" spans="1:15">
       <c r="A377" s="7" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="B377" s="7" t="s">
-        <v>2217</v>
+        <v>2213</v>
       </c>
       <c r="O377" s="7" t="s">
-        <v>2218</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="378" spans="1:15">
       <c r="A378" s="7" t="s">
-        <v>2219</v>
+        <v>2214</v>
       </c>
       <c r="O378" s="7" t="s">
-        <v>2729</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="379" spans="1:15">
       <c r="A379" s="7" t="s">
-        <v>2220</v>
+        <v>2216</v>
       </c>
       <c r="O379" s="7" t="s">
-        <v>2730</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="381" spans="1:15">
       <c r="A381" s="7" t="s">
-        <v>2221</v>
+        <v>2217</v>
       </c>
       <c r="B381" s="7" t="s">
-        <v>2221</v>
+        <v>2217</v>
       </c>
       <c r="O381" s="7" t="s">
-        <v>2222</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="382" spans="1:15">
       <c r="A382" s="7" t="s">
-        <v>2223</v>
+        <v>2219</v>
       </c>
       <c r="O382" s="7" t="s">
-        <v>2224</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="383" spans="1:15">
       <c r="A383" s="7" t="s">
-        <v>2225</v>
+        <v>2220</v>
       </c>
       <c r="O383" s="7" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="385" spans="1:15">
       <c r="A385" s="7" t="s">
-        <v>2226</v>
+        <v>2221</v>
       </c>
       <c r="B385" s="7" t="s">
-        <v>2226</v>
+        <v>2221</v>
       </c>
       <c r="O385" s="7" t="s">
-        <v>2227</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="386" spans="1:15">
       <c r="A386" s="7" t="s">
-        <v>2228</v>
+        <v>2223</v>
       </c>
       <c r="O386" s="7" t="s">
-        <v>2732</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="387" spans="1:15">
       <c r="A387" s="7" t="s">
-        <v>2229</v>
+        <v>2225</v>
       </c>
       <c r="O387" s="7" t="s">
-        <v>2230</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="389" spans="1:15">
       <c r="A389" s="7" t="s">
-        <v>2231</v>
+        <v>2226</v>
       </c>
       <c r="B389" s="7" t="s">
-        <v>2231</v>
+        <v>2226</v>
       </c>
       <c r="O389" s="7" t="s">
-        <v>2232</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="390" spans="1:15">
       <c r="A390" s="7" t="s">
-        <v>2233</v>
+        <v>2228</v>
       </c>
       <c r="O390" s="7" t="s">
-        <v>2733</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="391" spans="1:15">
       <c r="A391" s="7" t="s">
-        <v>2234</v>
+        <v>2229</v>
       </c>
       <c r="O391" s="7" t="s">
-        <v>2734</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="393" spans="1:15">
       <c r="A393" s="7" t="s">
-        <v>1820</v>
+        <v>2231</v>
       </c>
       <c r="B393" s="7" t="s">
-        <v>1820</v>
+        <v>2231</v>
       </c>
       <c r="O393" s="7" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="394" spans="1:15">
       <c r="A394" s="7" t="s">
-        <v>2236</v>
+        <v>2233</v>
       </c>
       <c r="O394" s="7" t="s">
-        <v>2237</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="395" spans="1:15">
       <c r="A395" s="7" t="s">
-        <v>2238</v>
+        <v>2234</v>
       </c>
       <c r="O395" s="7" t="s">
-        <v>2735</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="397" spans="1:15">
       <c r="A397" s="7" t="s">
-        <v>2239</v>
+        <v>1820</v>
       </c>
       <c r="B397" s="7" t="s">
-        <v>2239</v>
+        <v>1820</v>
       </c>
       <c r="O397" s="7" t="s">
-        <v>2240</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="398" spans="1:15">
       <c r="A398" s="7" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="O398" s="7" t="s">
-        <v>2242</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="399" spans="1:15">
       <c r="A399" s="7" t="s">
-        <v>2243</v>
+        <v>2238</v>
       </c>
       <c r="O399" s="7" t="s">
-        <v>2736</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="401" spans="1:15">
       <c r="A401" s="7" t="s">
-        <v>2244</v>
+        <v>2239</v>
       </c>
       <c r="B401" s="7" t="s">
-        <v>2244</v>
+        <v>2239</v>
       </c>
       <c r="O401" s="7" t="s">
-        <v>2245</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="402" spans="1:15">
       <c r="A402" s="7" t="s">
-        <v>2246</v>
+        <v>2241</v>
       </c>
       <c r="O402" s="7" t="s">
-        <v>2737</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="403" spans="1:15">
       <c r="A403" s="7" t="s">
-        <v>2247</v>
+        <v>2243</v>
       </c>
       <c r="O403" s="7" t="s">
-        <v>2738</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="405" spans="1:15">
       <c r="A405" s="7" t="s">
-        <v>2248</v>
+        <v>2244</v>
       </c>
       <c r="B405" s="7" t="s">
-        <v>2248</v>
+        <v>2244</v>
       </c>
       <c r="O405" s="7" t="s">
-        <v>3179</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="406" spans="1:15">
       <c r="A406" s="7" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
       <c r="O406" s="7" t="s">
-        <v>2250</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="407" spans="1:15">
       <c r="A407" s="7" t="s">
-        <v>2251</v>
+        <v>2247</v>
       </c>
       <c r="O407" s="7" t="s">
-        <v>2252</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="409" spans="1:15">
       <c r="A409" s="7" t="s">
-        <v>2253</v>
+        <v>2248</v>
       </c>
       <c r="B409" s="7" t="s">
-        <v>2739</v>
+        <v>2248</v>
       </c>
       <c r="O409" s="7" t="s">
-        <v>2254</v>
+        <v>3179</v>
       </c>
     </row>
     <row r="410" spans="1:15">
       <c r="A410" s="7" t="s">
-        <v>2255</v>
+        <v>2249</v>
       </c>
       <c r="O410" s="7" t="s">
-        <v>2740</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="411" spans="1:15">
       <c r="A411" s="7" t="s">
-        <v>2256</v>
+        <v>2251</v>
       </c>
       <c r="O411" s="7" t="s">
-        <v>2740</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="413" spans="1:15">
       <c r="A413" s="7" t="s">
-        <v>2257</v>
+        <v>2253</v>
       </c>
       <c r="B413" s="7" t="s">
-        <v>2257</v>
+        <v>2739</v>
       </c>
       <c r="O413" s="7" t="s">
-        <v>2258</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="414" spans="1:15">
       <c r="A414" s="7" t="s">
-        <v>2259</v>
+        <v>2255</v>
       </c>
       <c r="O414" s="7" t="s">
-        <v>2741</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="415" spans="1:15">
       <c r="A415" s="7" t="s">
-        <v>2260</v>
+        <v>2256</v>
       </c>
       <c r="O415" s="7" t="s">
-        <v>2261</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="417" spans="1:15">
       <c r="A417" s="7" t="s">
-        <v>2262</v>
+        <v>2257</v>
       </c>
       <c r="B417" s="7" t="s">
-        <v>2262</v>
+        <v>2257</v>
       </c>
       <c r="O417" s="7" t="s">
-        <v>2263</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="418" spans="1:15">
       <c r="A418" s="7" t="s">
-        <v>2264</v>
+        <v>2259</v>
       </c>
       <c r="O418" s="7" t="s">
-        <v>2265</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="419" spans="1:15">
       <c r="A419" s="7" t="s">
-        <v>2266</v>
+        <v>2260</v>
       </c>
       <c r="O419" s="7" t="s">
-        <v>2267</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="421" spans="1:15">
       <c r="A421" s="7" t="s">
-        <v>2866</v>
+        <v>2262</v>
       </c>
       <c r="B421" s="7" t="s">
-        <v>2866</v>
+        <v>2262</v>
       </c>
       <c r="O421" s="7" t="s">
-        <v>2869</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="422" spans="1:15">
       <c r="A422" s="7" t="s">
-        <v>2867</v>
+        <v>2264</v>
       </c>
       <c r="O422" s="7" t="s">
-        <v>2870</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="423" spans="1:15">
       <c r="A423" s="7" t="s">
-        <v>2868</v>
+        <v>2266</v>
       </c>
       <c r="O423" s="7" t="s">
-        <v>2870</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="425" spans="1:15">
       <c r="A425" s="7" t="s">
-        <v>2876</v>
+        <v>2866</v>
       </c>
       <c r="B425" s="7" t="s">
-        <v>2876</v>
+        <v>2866</v>
       </c>
       <c r="O425" s="7" t="s">
-        <v>2879</v>
+        <v>2869</v>
       </c>
     </row>
     <row r="426" spans="1:15">
       <c r="A426" s="7" t="s">
-        <v>2877</v>
+        <v>2867</v>
       </c>
       <c r="O426" s="7" t="s">
-        <v>2880</v>
+        <v>2870</v>
       </c>
     </row>
     <row r="427" spans="1:15">
       <c r="A427" s="7" t="s">
-        <v>2878</v>
+        <v>2868</v>
       </c>
       <c r="O427" s="7" t="s">
-        <v>2880</v>
+        <v>2870</v>
       </c>
     </row>
     <row r="429" spans="1:15">
       <c r="A429" s="7" t="s">
-        <v>2268</v>
+        <v>2876</v>
       </c>
       <c r="B429" s="7" t="s">
-        <v>2268</v>
+        <v>2876</v>
       </c>
       <c r="O429" s="7" t="s">
-        <v>2269</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="430" spans="1:15">
       <c r="A430" s="7" t="s">
-        <v>2270</v>
+        <v>2877</v>
       </c>
       <c r="O430" s="7" t="s">
-        <v>2742</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="431" spans="1:15">
       <c r="A431" s="7" t="s">
-        <v>2271</v>
+        <v>2878</v>
       </c>
       <c r="O431" s="7" t="s">
-        <v>2742</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="433" spans="1:15">
       <c r="A433" s="7" t="s">
-        <v>2272</v>
+        <v>2268</v>
       </c>
       <c r="B433" s="7" t="s">
-        <v>2272</v>
+        <v>2268</v>
       </c>
       <c r="O433" s="7" t="s">
-        <v>2273</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="434" spans="1:15">
       <c r="A434" s="7" t="s">
-        <v>2274</v>
+        <v>2270</v>
       </c>
       <c r="O434" s="7" t="s">
-        <v>2743</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="435" spans="1:15">
       <c r="A435" s="7" t="s">
-        <v>2275</v>
+        <v>2271</v>
       </c>
       <c r="O435" s="7" t="s">
-        <v>2743</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="437" spans="1:15">
       <c r="A437" s="7" t="s">
-        <v>2276</v>
+        <v>2272</v>
       </c>
       <c r="B437" s="7" t="s">
-        <v>2276</v>
+        <v>2272</v>
       </c>
       <c r="O437" s="7" t="s">
         <v>2273</v>
@@ -27941,17 +28036,44 @@
     </row>
     <row r="438" spans="1:15">
       <c r="A438" s="7" t="s">
-        <v>2277</v>
+        <v>2274</v>
       </c>
       <c r="O438" s="7" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="439" spans="1:15">
       <c r="A439" s="7" t="s">
+        <v>2275</v>
+      </c>
+      <c r="O439" s="7" t="s">
+        <v>2743</v>
+      </c>
+    </row>
+    <row r="441" spans="1:15">
+      <c r="A441" s="7" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B441" s="7" t="s">
+        <v>2276</v>
+      </c>
+      <c r="O441" s="7" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="442" spans="1:15">
+      <c r="A442" s="7" t="s">
+        <v>2277</v>
+      </c>
+      <c r="O442" s="7" t="s">
+        <v>2744</v>
+      </c>
+    </row>
+    <row r="443" spans="1:15">
+      <c r="A443" s="7" t="s">
         <v>2278</v>
       </c>
-      <c r="O439" s="7" t="s">
+      <c r="O443" s="7" t="s">
         <v>2744</v>
       </c>
     </row>
@@ -27964,7 +28086,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:Q112"/>
+  <dimension ref="A1:Q113"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="60" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.625" style="8" customWidth="1"/>
@@ -28234,659 +28356,667 @@
         <v>3078</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="60" customHeight="1">
-      <c r="A29" s="8" t="s">
-        <v>1705</v>
-      </c>
-      <c r="O29" s="9" t="s">
-        <v>2790</v>
+    <row r="28" spans="1:15" ht="60" customHeight="1">
+      <c r="A28" s="8" t="s">
+        <v>3243</v>
+      </c>
+      <c r="O28" s="9" t="s">
+        <v>3244</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="60" customHeight="1">
       <c r="A30" s="8" t="s">
-        <v>2514</v>
+        <v>1705</v>
       </c>
       <c r="O30" s="9" t="s">
-        <v>2513</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="60" customHeight="1">
       <c r="A31" s="8" t="s">
-        <v>1704</v>
+        <v>2514</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>2791</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="60" customHeight="1">
       <c r="A32" s="8" t="s">
-        <v>2335</v>
+        <v>1704</v>
       </c>
       <c r="O32" s="9" t="s">
-        <v>2792</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="60" customHeight="1">
       <c r="A33" s="8" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>2313</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="60" customHeight="1">
       <c r="A34" s="8" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="O34" s="9" t="s">
-        <v>2793</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="60" customHeight="1">
       <c r="A35" s="8" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>2794</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="60" customHeight="1">
       <c r="A36" s="8" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="O36" s="9" t="s">
-        <v>2795</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="60" customHeight="1">
       <c r="A37" s="8" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>2796</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="60" customHeight="1">
       <c r="A38" s="8" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="O38" s="9" t="s">
-        <v>2797</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="60" customHeight="1">
       <c r="A39" s="8" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>2798</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="60" customHeight="1">
       <c r="A40" s="8" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="O40" s="9" t="s">
-        <v>2799</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="60" customHeight="1">
       <c r="A41" s="8" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="60" customHeight="1">
       <c r="A42" s="8" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="O42" s="9" t="s">
-        <v>2974</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="60" customHeight="1">
       <c r="A43" s="8" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>2801</v>
+        <v>2974</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="60" customHeight="1">
       <c r="A44" s="8" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="O44" s="9" t="s">
-        <v>2802</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="60" customHeight="1">
       <c r="A45" s="8" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>2803</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="60" customHeight="1">
       <c r="A46" s="8" t="s">
-        <v>2998</v>
+        <v>2348</v>
       </c>
       <c r="O46" s="9" t="s">
-        <v>3021</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="60" customHeight="1">
       <c r="A47" s="8" t="s">
-        <v>2349</v>
+        <v>2998</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>2804</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="60" customHeight="1">
       <c r="A48" s="8" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="O48" s="9" t="s">
-        <v>2805</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="60" customHeight="1">
       <c r="A49" s="8" t="s">
+        <v>2350</v>
+      </c>
+      <c r="O49" s="9" t="s">
+        <v>2805</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="60" customHeight="1">
+      <c r="A50" s="8" t="s">
         <v>2903</v>
       </c>
-      <c r="O49" s="9" t="s">
+      <c r="O50" s="9" t="s">
         <v>2911</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="132.75" customHeight="1">
-      <c r="A50" s="8" t="s">
+    <row r="51" spans="1:15" ht="132.75" customHeight="1">
+      <c r="A51" s="8" t="s">
         <v>3208</v>
       </c>
-      <c r="O50" s="9" t="s">
+      <c r="O51" s="9" t="s">
         <v>3232</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="60" customHeight="1">
-      <c r="A51" s="8" t="s">
+    <row r="52" spans="1:15" ht="60" customHeight="1">
+      <c r="A52" s="8" t="s">
         <v>3230</v>
       </c>
-      <c r="O51" s="9" t="s">
+      <c r="O52" s="9" t="s">
         <v>3231</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" ht="60" customHeight="1">
-      <c r="A53" s="8" t="s">
-        <v>2351</v>
-      </c>
-      <c r="O53" s="9" t="s">
-        <v>2806</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="60" customHeight="1">
       <c r="A54" s="8" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="O54" s="9" t="s">
-        <v>2807</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="60" customHeight="1">
       <c r="A55" s="8" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>2761</v>
+        <v>2807</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="60" customHeight="1">
       <c r="A56" s="8" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="O56" s="9" t="s">
-        <v>2808</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="60" customHeight="1">
       <c r="A57" s="8" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="60" customHeight="1">
       <c r="A58" s="8" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="O58" s="9" t="s">
-        <v>2760</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="60" customHeight="1">
       <c r="A59" s="8" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>2810</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="60" customHeight="1">
       <c r="A60" s="8" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="O60" s="9" t="s">
-        <v>2811</v>
+        <v>2810</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="60" customHeight="1">
       <c r="A61" s="8" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="60" customHeight="1">
       <c r="A62" s="8" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="O62" s="9" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="60" customHeight="1">
       <c r="A63" s="8" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>2814</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="60" customHeight="1">
       <c r="A64" s="8" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="O64" s="9" t="s">
-        <v>2815</v>
+        <v>2814</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="60" customHeight="1">
       <c r="A65" s="8" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>2816</v>
+        <v>2815</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="60" customHeight="1">
       <c r="A66" s="8" t="s">
-        <v>2851</v>
+        <v>2363</v>
       </c>
       <c r="O66" s="9" t="s">
-        <v>2817</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="60" customHeight="1">
       <c r="A67" s="8" t="s">
-        <v>2364</v>
+        <v>2851</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>2818</v>
+        <v>2817</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="60" customHeight="1">
       <c r="A68" s="8" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="O68" s="9" t="s">
-        <v>2856</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="60" customHeight="1">
       <c r="A69" s="8" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>2819</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="60" customHeight="1">
       <c r="A70" s="8" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="O70" s="9" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="60" customHeight="1">
       <c r="A71" s="8" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="60" customHeight="1">
       <c r="A72" s="8" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="O72" s="9" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="60" customHeight="1">
       <c r="A73" s="8" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>1711</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="60" customHeight="1">
       <c r="A74" s="8" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="O74" s="9" t="s">
-        <v>2823</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="60" customHeight="1">
       <c r="A75" s="8" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="60" customHeight="1">
       <c r="A76" s="8" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="O76" s="9" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="60" customHeight="1">
       <c r="A77" s="8" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>2826</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="60" customHeight="1">
       <c r="A78" s="8" t="s">
-        <v>1843</v>
+        <v>2374</v>
       </c>
       <c r="O78" s="9" t="s">
-        <v>2860</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="60" customHeight="1">
       <c r="A79" s="8" t="s">
-        <v>2556</v>
+        <v>1843</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>2555</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="60" customHeight="1">
       <c r="A80" s="8" t="s">
+        <v>2556</v>
+      </c>
+      <c r="O80" s="9" t="s">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" ht="60" customHeight="1">
+      <c r="A81" s="8" t="s">
         <v>3080</v>
       </c>
-      <c r="O80" s="9" t="s">
+      <c r="O81" s="9" t="s">
         <v>3081</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" ht="60" customHeight="1">
-      <c r="A82" s="8" t="s">
-        <v>2375</v>
-      </c>
-      <c r="O82" s="9" t="s">
-        <v>2827</v>
       </c>
     </row>
     <row r="83" spans="1:15" ht="60" customHeight="1">
       <c r="A83" s="8" t="s">
-        <v>2315</v>
+        <v>2375</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>2775</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="60" customHeight="1">
       <c r="A84" s="8" t="s">
-        <v>2376</v>
+        <v>2315</v>
       </c>
       <c r="O84" s="9" t="s">
-        <v>2772</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="85" spans="1:15" ht="60" customHeight="1">
       <c r="A85" s="8" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>2828</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="86" spans="1:15" ht="60" customHeight="1">
       <c r="A86" s="8" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="O86" s="9" t="s">
-        <v>2829</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="87" spans="1:15" ht="60" customHeight="1">
       <c r="A87" s="8" t="s">
-        <v>2978</v>
+        <v>2378</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>3022</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="60" customHeight="1">
       <c r="A88" s="8" t="s">
-        <v>2379</v>
+        <v>2978</v>
       </c>
       <c r="O88" s="9" t="s">
-        <v>2830</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="60" customHeight="1">
       <c r="A89" s="8" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="90" spans="1:15" ht="60" customHeight="1">
       <c r="A90" s="8" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="O90" s="9" t="s">
-        <v>2832</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="60" customHeight="1">
       <c r="A91" s="8" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="92" spans="1:15" ht="60" customHeight="1">
       <c r="A92" s="8" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="O92" s="9" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="93" spans="1:15" ht="60" customHeight="1">
       <c r="A93" s="8" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="94" spans="1:15" ht="60" customHeight="1">
       <c r="A94" s="8" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="O94" s="9" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="95" spans="1:15" ht="60" customHeight="1">
       <c r="A95" s="8" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="96" spans="1:15" ht="60" customHeight="1">
       <c r="A96" s="8" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="O96" s="9" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="97" spans="1:15" ht="60" customHeight="1">
       <c r="A97" s="8" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>2773</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="98" spans="1:15" ht="60" customHeight="1">
       <c r="A98" s="8" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="O98" s="9" t="s">
-        <v>2839</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="99" spans="1:15" ht="60" customHeight="1">
       <c r="A99" s="8" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="100" spans="1:15" ht="60" customHeight="1">
       <c r="A100" s="8" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="O100" s="9" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="101" spans="1:15" ht="60" customHeight="1">
       <c r="A101" s="8" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="102" spans="1:15" ht="60" customHeight="1">
       <c r="A102" s="8" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="O102" s="9" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
     </row>
     <row r="103" spans="1:15" ht="60" customHeight="1">
       <c r="A103" s="8" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="104" spans="1:15" ht="60" customHeight="1">
       <c r="A104" s="8" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="O104" s="9" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="105" spans="1:15" ht="60" customHeight="1">
       <c r="A105" s="8" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="106" spans="1:15" ht="60" customHeight="1">
       <c r="A106" s="8" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="O106" s="9" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
     </row>
     <row r="107" spans="1:15" ht="60" customHeight="1">
       <c r="A107" s="8" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="108" spans="1:15" ht="60" customHeight="1">
       <c r="A108" s="8" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="O108" s="9" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="109" spans="1:15" ht="60" customHeight="1">
       <c r="A109" s="8" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="110" spans="1:15" ht="60" customHeight="1">
       <c r="A110" s="8" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="O110" s="9" t="s">
-        <v>2852</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="111" spans="1:15" ht="60" customHeight="1">
       <c r="A111" s="8" t="s">
-        <v>2871</v>
+        <v>2401</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>2872</v>
+        <v>2852</v>
       </c>
     </row>
     <row r="112" spans="1:15" ht="60" customHeight="1">
       <c r="A112" s="8" t="s">
+        <v>2871</v>
+      </c>
+      <c r="O112" s="9" t="s">
+        <v>2872</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" ht="60" customHeight="1">
+      <c r="A113" s="8" t="s">
         <v>2881</v>
       </c>
-      <c r="O112" s="9" t="s">
+      <c r="O113" s="9" t="s">
         <v>2896</v>
       </c>
     </row>

--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Among Us code\TheOtherUs\TheOtherUs-Edited-Lite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E41F910-ED90-4603-8980-6A2B129424ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0C40EE-BEB3-44F0-9360-01DF02AE23C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="1200" windowWidth="25755" windowHeight="14910" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="720" yWindow="1200" windowWidth="25755" windowHeight="14910" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Options" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Role Description" sheetId="11" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Options!$O$1:$O$1460</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Options!$O$1:$O$1463</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3575" uniqueCount="3253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3586" uniqueCount="3263">
   <si>
     <t>English</t>
   </si>
@@ -11564,36 +11564,75 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>gunsmithSetKillCooldown</t>
+  </si>
+  <si>
+    <t>gunsmithMaxChangeCount</t>
+  </si>
+  <si>
+    <t>取出子弹时重置的冷却</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>弹匣中能存下的子弹上限</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>gunsmithAddBullets</t>
+  </si>
+  <si>
+    <t>gunsmithGetBullets</t>
+  </si>
+  <si>
+    <t>取出</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>存储</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Berserker</t>
+  </si>
+  <si>
+    <t>BerserkerFullDesc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BerserkerIntroDesc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BerserkerShortDesc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>狂战士</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>狂暴持续时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>狂暴蓄力时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>berserkerKillDuration</t>
+  </si>
+  <si>
+    <t>berserkerRampageCooldown</t>
+  </si>
+  <si>
+    <t>狂战士在击杀时会狂暴，击杀玩家后可在极短时间内0CD无限出刀。
+初始的持续时间为0.1s，在击杀冷却完毕后等待充能来获得更长的持续时间。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>可以在击杀冷却完毕后手动存下子弹，可以随时取出子弹。
-随时可以取出子弹，取出子弹后会将击杀按钮重置冷却。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>gunsmithSetKillCooldown</t>
-  </si>
-  <si>
-    <t>gunsmithMaxChangeCount</t>
-  </si>
-  <si>
-    <t>取出子弹时重置的冷却</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>弹匣中能存下的子弹上限</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>gunsmithAddBullets</t>
-  </si>
-  <si>
-    <t>gunsmithGetBullets</t>
-  </si>
-  <si>
-    <t>取出</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>存储</t>
+随时可以取出子弹，取出子弹后会将击杀按钮重置冷却。
+存入的子弹有上限！</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -12193,7 +12232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1757"/>
+  <dimension ref="A1:Q1760"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40.375" style="2" customWidth="1"/>
@@ -16057,128 +16096,119 @@
     </row>
     <row r="393" spans="1:15" ht="24.95" customHeight="1">
       <c r="A393" s="2" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="O393" s="2" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="394" spans="1:15" ht="24.95" customHeight="1">
       <c r="A394" s="2" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="O394" s="2" t="s">
-        <v>3248</v>
-      </c>
-    </row>
-    <row r="395" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O395" s="2"/>
+        <v>3247</v>
+      </c>
     </row>
     <row r="396" spans="1:15" ht="24.95" customHeight="1">
       <c r="A396" s="2" t="s">
-        <v>2286</v>
-      </c>
-      <c r="B396" s="2" t="s">
-        <v>2285</v>
+        <v>3260</v>
       </c>
       <c r="O396" s="2" t="s">
-        <v>768</v>
+        <v>3258</v>
       </c>
     </row>
     <row r="397" spans="1:15" ht="24.95" customHeight="1">
       <c r="A397" s="2" t="s">
-        <v>3029</v>
-      </c>
-      <c r="B397" s="2" t="s">
-        <v>1641</v>
+        <v>3259</v>
       </c>
       <c r="O397" s="2" t="s">
-        <v>1759</v>
+        <v>3257</v>
       </c>
     </row>
     <row r="398" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A398" s="2" t="s">
-        <v>3028</v>
-      </c>
-      <c r="B398" s="2" t="s">
-        <v>1664</v>
-      </c>
-      <c r="O398" s="2" t="s">
-        <v>777</v>
-      </c>
+      <c r="O398" s="2"/>
     </row>
     <row r="399" spans="1:15" ht="24.95" customHeight="1">
       <c r="A399" s="2" t="s">
-        <v>3218</v>
+        <v>2286</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>1639</v>
+        <v>2285</v>
       </c>
       <c r="O399" s="2" t="s">
-        <v>794</v>
+        <v>768</v>
       </c>
     </row>
     <row r="400" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O400" s="2"/>
+      <c r="A400" s="2" t="s">
+        <v>3029</v>
+      </c>
+      <c r="B400" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="O400" s="2" t="s">
+        <v>1759</v>
+      </c>
     </row>
     <row r="401" spans="1:15" ht="24.95" customHeight="1">
       <c r="A401" s="2" t="s">
-        <v>3083</v>
+        <v>3028</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>2882</v>
+        <v>1664</v>
       </c>
       <c r="O401" s="2" t="s">
-        <v>2883</v>
+        <v>777</v>
       </c>
     </row>
     <row r="402" spans="1:15" ht="24.95" customHeight="1">
       <c r="A402" s="2" t="s">
-        <v>3000</v>
+        <v>3218</v>
+      </c>
+      <c r="B402" s="2" t="s">
+        <v>1639</v>
       </c>
       <c r="O402" s="2" t="s">
-        <v>3001</v>
+        <v>794</v>
       </c>
     </row>
     <row r="403" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A403" s="2" t="s">
-        <v>3013</v>
-      </c>
-      <c r="O403" s="2" t="s">
-        <v>3015</v>
-      </c>
+      <c r="O403" s="2"/>
     </row>
     <row r="404" spans="1:15" ht="24.95" customHeight="1">
       <c r="A404" s="2" t="s">
-        <v>3012</v>
-      </c>
-      <c r="O404" s="3" t="s">
-        <v>3014</v>
+        <v>3083</v>
+      </c>
+      <c r="B404" s="2" t="s">
+        <v>2882</v>
+      </c>
+      <c r="O404" s="2" t="s">
+        <v>2883</v>
       </c>
     </row>
     <row r="405" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O405" s="2"/>
+      <c r="A405" s="2" t="s">
+        <v>3000</v>
+      </c>
+      <c r="O405" s="2" t="s">
+        <v>3001</v>
+      </c>
     </row>
     <row r="406" spans="1:15" ht="24.95" customHeight="1">
       <c r="A406" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="B406" s="2" t="s">
-        <v>718</v>
+        <v>3013</v>
       </c>
       <c r="O406" s="2" t="s">
-        <v>719</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="407" spans="1:15" ht="24.95" customHeight="1">
       <c r="A407" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="B407" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="O407" s="2" t="s">
-        <v>1759</v>
+        <v>3012</v>
+      </c>
+      <c r="O407" s="3" t="s">
+        <v>3014</v>
       </c>
     </row>
     <row r="408" spans="1:15" ht="24.95" customHeight="1">
@@ -16186,109 +16216,109 @@
     </row>
     <row r="409" spans="1:15" ht="24.95" customHeight="1">
       <c r="A409" s="2" t="s">
-        <v>1677</v>
+        <v>717</v>
+      </c>
+      <c r="B409" s="2" t="s">
+        <v>718</v>
       </c>
       <c r="O409" s="2" t="s">
-        <v>1684</v>
+        <v>719</v>
       </c>
     </row>
     <row r="410" spans="1:15" ht="24.95" customHeight="1">
       <c r="A410" s="2" t="s">
-        <v>1678</v>
+        <v>720</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>1657</v>
+        <v>721</v>
       </c>
       <c r="O410" s="2" t="s">
-        <v>1685</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="411" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A411" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="B411" s="2" t="s">
-        <v>1653</v>
-      </c>
-      <c r="O411" s="2" t="s">
-        <v>1689</v>
-      </c>
+      <c r="O411" s="2"/>
     </row>
     <row r="412" spans="1:15" ht="24.95" customHeight="1">
       <c r="A412" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="B412" s="2" t="s">
-        <v>1654</v>
+        <v>1677</v>
       </c>
       <c r="O412" s="2" t="s">
-        <v>1659</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="413" spans="1:15" ht="24.95" customHeight="1">
       <c r="A413" s="2" t="s">
-        <v>1690</v>
+        <v>1678</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>1663</v>
+        <v>1657</v>
       </c>
       <c r="O413" s="2" t="s">
-        <v>1691</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="414" spans="1:15" ht="24.95" customHeight="1">
       <c r="A414" s="2" t="s">
-        <v>1681</v>
+        <v>1679</v>
+      </c>
+      <c r="B414" s="2" t="s">
+        <v>1653</v>
       </c>
       <c r="O414" s="2" t="s">
-        <v>1686</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="415" spans="1:15" ht="24.95" customHeight="1">
       <c r="A415" s="2" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="O415" s="2" t="s">
-        <v>1688</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="416" spans="1:15" ht="24.95" customHeight="1">
       <c r="A416" s="2" t="s">
-        <v>1683</v>
+        <v>1690</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>1656</v>
+        <v>1663</v>
       </c>
       <c r="O416" s="2" t="s">
-        <v>1687</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="417" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O417" s="2"/>
+      <c r="A417" s="2" t="s">
+        <v>1681</v>
+      </c>
+      <c r="O417" s="2" t="s">
+        <v>1686</v>
+      </c>
     </row>
     <row r="418" spans="1:15" ht="24.95" customHeight="1">
       <c r="A418" s="2" t="s">
-        <v>722</v>
+        <v>1682</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>723</v>
+        <v>1658</v>
       </c>
       <c r="O418" s="2" t="s">
-        <v>724</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="419" spans="1:15" ht="24.95" customHeight="1">
       <c r="A419" s="2" t="s">
-        <v>725</v>
+        <v>1683</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>726</v>
+        <v>1656</v>
       </c>
       <c r="O419" s="2" t="s">
-        <v>727</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="420" spans="1:15" ht="24.95" customHeight="1">
@@ -16296,366 +16326,372 @@
     </row>
     <row r="421" spans="1:15" ht="24.95" customHeight="1">
       <c r="A421" s="2" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>2408</v>
+        <v>723</v>
       </c>
       <c r="O421" s="2" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
     </row>
     <row r="422" spans="1:15" ht="24.95" customHeight="1">
       <c r="A422" s="2" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>2409</v>
+        <v>726</v>
       </c>
       <c r="O422" s="2" t="s">
-        <v>2861</v>
+        <v>727</v>
       </c>
     </row>
     <row r="423" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A423" s="2" t="s">
-        <v>2863</v>
-      </c>
-      <c r="O423" s="2" t="s">
-        <v>2862</v>
-      </c>
+      <c r="O423" s="2"/>
     </row>
     <row r="424" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O424" s="2"/>
+      <c r="A424" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="B424" s="2" t="s">
+        <v>2408</v>
+      </c>
+      <c r="O424" s="2" t="s">
+        <v>729</v>
+      </c>
     </row>
     <row r="425" spans="1:15" ht="24.95" customHeight="1">
       <c r="A425" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>732</v>
+        <v>2409</v>
       </c>
       <c r="O425" s="2" t="s">
-        <v>733</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="426" spans="1:15" ht="24.95" customHeight="1">
       <c r="A426" s="2" t="s">
-        <v>1605</v>
-      </c>
-      <c r="B426" s="2" t="s">
-        <v>734</v>
+        <v>2863</v>
       </c>
       <c r="O426" s="2" t="s">
-        <v>492</v>
+        <v>2862</v>
       </c>
     </row>
     <row r="427" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A427" s="2" t="s">
-        <v>1606</v>
-      </c>
-      <c r="B427" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="O427" s="2" t="s">
-        <v>495</v>
-      </c>
+      <c r="O427" s="2"/>
     </row>
     <row r="428" spans="1:15" ht="24.95" customHeight="1">
       <c r="A428" s="2" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="O428" s="2" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
     </row>
     <row r="429" spans="1:15" ht="24.95" customHeight="1">
       <c r="A429" s="2" t="s">
-        <v>739</v>
+        <v>1605</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="O429" s="2" t="s">
-        <v>741</v>
+        <v>492</v>
       </c>
     </row>
     <row r="430" spans="1:15" ht="24.95" customHeight="1">
       <c r="A430" s="2" t="s">
-        <v>742</v>
+        <v>1606</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>1640</v>
+        <v>735</v>
       </c>
       <c r="O430" s="2" t="s">
-        <v>1760</v>
+        <v>495</v>
       </c>
     </row>
     <row r="431" spans="1:15" ht="24.95" customHeight="1">
       <c r="A431" s="2" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="O431" s="2" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
     </row>
     <row r="432" spans="1:15" ht="24.95" customHeight="1">
       <c r="A432" s="2" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="O432" s="2" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
     </row>
     <row r="433" spans="1:15" ht="24.95" customHeight="1">
       <c r="A433" s="2" t="s">
-        <v>2404</v>
+        <v>742</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>2405</v>
+        <v>1640</v>
       </c>
       <c r="O433" s="2" t="s">
-        <v>2406</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="434" spans="1:15" ht="24.95" customHeight="1">
       <c r="A434" s="2" t="s">
-        <v>1713</v>
+        <v>743</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="O434" s="2" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
     </row>
     <row r="435" spans="1:15" ht="24.95" customHeight="1">
       <c r="A435" s="2" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="O435" s="2" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
     </row>
     <row r="436" spans="1:15" ht="24.95" customHeight="1">
       <c r="A436" s="2" t="s">
-        <v>754</v>
+        <v>2404</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>755</v>
+        <v>2405</v>
       </c>
       <c r="O436" s="2" t="s">
-        <v>756</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="437" spans="1:15" ht="24.95" customHeight="1">
       <c r="A437" s="2" t="s">
-        <v>2402</v>
+        <v>1713</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="O437" s="2" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
     </row>
     <row r="438" spans="1:15" ht="24.95" customHeight="1">
       <c r="A438" s="2" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="O438" s="2" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
     </row>
     <row r="439" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O439" s="2"/>
+      <c r="A439" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="B439" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="O439" s="2" t="s">
+        <v>756</v>
+      </c>
     </row>
     <row r="440" spans="1:15" ht="24.95" customHeight="1">
       <c r="A440" s="2" t="s">
-        <v>1610</v>
+        <v>2402</v>
+      </c>
+      <c r="B440" s="2" t="s">
+        <v>757</v>
       </c>
       <c r="O440" s="2" t="s">
-        <v>2309</v>
+        <v>758</v>
       </c>
     </row>
     <row r="441" spans="1:15" ht="24.95" customHeight="1">
       <c r="A441" s="2" t="s">
-        <v>1611</v>
+        <v>759</v>
+      </c>
+      <c r="B441" s="2" t="s">
+        <v>760</v>
       </c>
       <c r="O441" s="2" t="s">
-        <v>1631</v>
+        <v>761</v>
       </c>
     </row>
     <row r="442" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A442" s="2" t="s">
-        <v>1612</v>
-      </c>
-      <c r="O442" s="2" t="s">
-        <v>1630</v>
-      </c>
+      <c r="O442" s="2"/>
     </row>
     <row r="443" spans="1:15" ht="24.95" customHeight="1">
       <c r="A443" s="2" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="O443" s="2" t="s">
-        <v>1629</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="444" spans="1:15" ht="24.95" customHeight="1">
       <c r="A444" s="2" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="O444" s="2" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="445" spans="1:15" ht="24.95" customHeight="1">
       <c r="A445" s="2" t="s">
-        <v>1618</v>
+        <v>1612</v>
       </c>
       <c r="O445" s="2" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="446" spans="1:15" ht="24.95" customHeight="1">
       <c r="A446" s="2" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="O446" s="2" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="447" spans="1:15" ht="24.95" customHeight="1">
       <c r="A447" s="2" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="O447" s="2" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="448" spans="1:15" ht="24.95" customHeight="1">
       <c r="A448" s="2" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="O448" s="2" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="449" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O449" s="2"/>
+      <c r="A449" s="2" t="s">
+        <v>1615</v>
+      </c>
+      <c r="O449" s="2" t="s">
+        <v>1626</v>
+      </c>
     </row>
     <row r="450" spans="1:15" ht="24.95" customHeight="1">
       <c r="A450" s="2" t="s">
-        <v>1619</v>
-      </c>
-      <c r="B450" s="2" t="s">
-        <v>734</v>
+        <v>1616</v>
       </c>
       <c r="O450" s="2" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="451" spans="1:15" ht="24.95" customHeight="1">
       <c r="A451" s="2" t="s">
-        <v>1620</v>
-      </c>
-      <c r="B451" s="2" t="s">
-        <v>735</v>
+        <v>1617</v>
       </c>
       <c r="O451" s="2" t="s">
-        <v>495</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="452" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A452" s="2" t="s">
-        <v>2282</v>
-      </c>
-      <c r="B452" s="2" t="s">
-        <v>2283</v>
-      </c>
-      <c r="O452" s="2" t="s">
-        <v>2284</v>
-      </c>
+      <c r="O452" s="2"/>
     </row>
     <row r="453" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O453" s="2"/>
+      <c r="A453" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B453" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="O453" s="2" t="s">
+        <v>1623</v>
+      </c>
     </row>
     <row r="454" spans="1:15" ht="24.95" customHeight="1">
       <c r="A454" s="2" t="s">
-        <v>787</v>
+        <v>1620</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>788</v>
+        <v>735</v>
       </c>
       <c r="O454" s="2" t="s">
-        <v>789</v>
+        <v>495</v>
       </c>
     </row>
     <row r="455" spans="1:15" ht="24.95" customHeight="1">
       <c r="A455" s="2" t="s">
-        <v>790</v>
+        <v>2282</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>791</v>
+        <v>2283</v>
       </c>
       <c r="O455" s="2" t="s">
-        <v>792</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="456" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A456" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="B456" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="O456" s="2" t="s">
-        <v>794</v>
-      </c>
+      <c r="O456" s="2"/>
     </row>
     <row r="457" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O457" s="2"/>
+      <c r="A457" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="B457" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="O457" s="2" t="s">
+        <v>789</v>
+      </c>
     </row>
     <row r="458" spans="1:15" ht="24.95" customHeight="1">
       <c r="A458" s="2" t="s">
-        <v>1621</v>
+        <v>790</v>
+      </c>
+      <c r="B458" s="2" t="s">
+        <v>791</v>
       </c>
       <c r="O458" s="2" t="s">
-        <v>1622</v>
+        <v>792</v>
       </c>
     </row>
     <row r="459" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O459" s="2"/>
+      <c r="A459" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B459" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="O459" s="2" t="s">
+        <v>794</v>
+      </c>
     </row>
     <row r="460" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A460" s="2" t="s">
-        <v>2985</v>
-      </c>
-      <c r="O460" s="2" t="s">
-        <v>2987</v>
-      </c>
+      <c r="O460" s="2"/>
     </row>
     <row r="461" spans="1:15" ht="24.95" customHeight="1">
       <c r="A461" s="2" t="s">
-        <v>2986</v>
+        <v>1621</v>
       </c>
       <c r="O461" s="2" t="s">
-        <v>2988</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="462" spans="1:15" ht="24.95" customHeight="1">
@@ -16663,112 +16699,109 @@
     </row>
     <row r="463" spans="1:15" ht="24.95" customHeight="1">
       <c r="A463" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="B463" s="2" t="s">
-        <v>763</v>
+        <v>2985</v>
       </c>
       <c r="O463" s="2" t="s">
-        <v>764</v>
+        <v>2987</v>
       </c>
     </row>
     <row r="464" spans="1:15" ht="24.95" customHeight="1">
       <c r="A464" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="B464" s="2" t="s">
-        <v>766</v>
+        <v>2986</v>
       </c>
       <c r="O464" s="2" t="s">
-        <v>767</v>
+        <v>2988</v>
       </c>
     </row>
     <row r="465" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A465" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="B465" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="O465" s="2" t="s">
-        <v>724</v>
-      </c>
+      <c r="O465" s="2"/>
     </row>
     <row r="466" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O466" s="2"/>
+      <c r="A466" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B466" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="O466" s="2" t="s">
+        <v>764</v>
+      </c>
     </row>
     <row r="467" spans="1:15" ht="24.95" customHeight="1">
       <c r="A467" s="2" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="O467" s="2" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
     </row>
     <row r="468" spans="1:15" ht="24.95" customHeight="1">
       <c r="A468" s="2" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="O468" s="2" t="s">
-        <v>776</v>
+        <v>724</v>
       </c>
     </row>
     <row r="469" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A469" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="B469" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="O469" s="2" t="s">
-        <v>780</v>
-      </c>
+      <c r="O469" s="2"/>
     </row>
     <row r="470" spans="1:15" ht="24.95" customHeight="1">
       <c r="A470" s="2" t="s">
-        <v>782</v>
+        <v>771</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>783</v>
+        <v>772</v>
       </c>
       <c r="O470" s="2" t="s">
-        <v>784</v>
+        <v>773</v>
       </c>
     </row>
     <row r="471" spans="1:15" ht="24.95" customHeight="1">
       <c r="A471" s="2" t="s">
-        <v>785</v>
+        <v>774</v>
+      </c>
+      <c r="B471" s="2" t="s">
+        <v>775</v>
       </c>
       <c r="O471" s="2" t="s">
-        <v>786</v>
+        <v>776</v>
       </c>
     </row>
     <row r="472" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O472" s="2"/>
+      <c r="A472" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="B472" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="O472" s="2" t="s">
+        <v>780</v>
+      </c>
     </row>
     <row r="473" spans="1:15" ht="24.95" customHeight="1">
       <c r="A473" s="2" t="s">
-        <v>1609</v>
+        <v>782</v>
+      </c>
+      <c r="B473" s="2" t="s">
+        <v>783</v>
       </c>
       <c r="O473" s="2" t="s">
-        <v>3050</v>
+        <v>784</v>
       </c>
     </row>
     <row r="474" spans="1:15" ht="24.95" customHeight="1">
       <c r="A474" s="2" t="s">
-        <v>1665</v>
-      </c>
-      <c r="B474" s="2" t="s">
-        <v>1796</v>
+        <v>785</v>
       </c>
       <c r="O474" s="2" t="s">
-        <v>3051</v>
+        <v>786</v>
       </c>
     </row>
     <row r="475" spans="1:15" ht="24.95" customHeight="1">
@@ -16776,501 +16809,498 @@
     </row>
     <row r="476" spans="1:15" ht="24.95" customHeight="1">
       <c r="A476" s="2" t="s">
-        <v>1645</v>
+        <v>1609</v>
       </c>
       <c r="O476" s="2" t="s">
-        <v>1646</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="477" spans="1:15" ht="24.95" customHeight="1">
       <c r="A477" s="2" t="s">
-        <v>1649</v>
+        <v>1665</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>1658</v>
+        <v>1796</v>
       </c>
       <c r="O477" s="2" t="s">
-        <v>1688</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="478" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A478" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="B478" s="2" t="s">
-        <v>1656</v>
-      </c>
-      <c r="O478" s="2" t="s">
-        <v>1660</v>
-      </c>
+      <c r="O478" s="2"/>
     </row>
     <row r="479" spans="1:15" ht="24.95" customHeight="1">
       <c r="A479" s="2" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="O479" s="2" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="480" spans="1:15" ht="24.95" customHeight="1">
       <c r="A480" s="2" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>1653</v>
+        <v>1658</v>
       </c>
       <c r="O480" s="2" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="481" spans="1:15" ht="24.95" customHeight="1">
       <c r="A481" s="2" t="s">
-        <v>1655</v>
+        <v>781</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="O481" s="2" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="482" spans="1:15" ht="24.95" customHeight="1">
       <c r="A482" s="2" t="s">
-        <v>1652</v>
-      </c>
-      <c r="B482" s="2" t="s">
-        <v>1663</v>
+        <v>1647</v>
       </c>
       <c r="O482" s="2" t="s">
-        <v>1662</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="483" spans="1:15" ht="24.95" customHeight="1">
       <c r="A483" s="2" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>1657</v>
+        <v>1653</v>
       </c>
       <c r="O483" s="2" t="s">
-        <v>1661</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="484" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O484" s="2"/>
+      <c r="A484" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B484" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="O484" s="2" t="s">
+        <v>1659</v>
+      </c>
     </row>
     <row r="485" spans="1:15" ht="24.95" customHeight="1">
       <c r="A485" s="2" t="s">
-        <v>2905</v>
+        <v>1652</v>
+      </c>
+      <c r="B485" s="2" t="s">
+        <v>1663</v>
       </c>
       <c r="O485" s="2" t="s">
-        <v>2910</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="486" spans="1:15" ht="24.95" customHeight="1">
       <c r="A486" s="2" t="s">
-        <v>2906</v>
+        <v>1651</v>
+      </c>
+      <c r="B486" s="2" t="s">
+        <v>1657</v>
       </c>
       <c r="O486" s="2" t="s">
-        <v>2908</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="487" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A487" s="2" t="s">
-        <v>2907</v>
-      </c>
-      <c r="O487" s="3" t="s">
-        <v>2909</v>
-      </c>
+      <c r="O487" s="2"/>
     </row>
     <row r="488" spans="1:15" ht="24.95" customHeight="1">
       <c r="A488" s="2" t="s">
-        <v>2973</v>
-      </c>
-      <c r="O488" s="3" t="s">
-        <v>2999</v>
+        <v>2905</v>
+      </c>
+      <c r="O488" s="2" t="s">
+        <v>2910</v>
+      </c>
+    </row>
+    <row r="489" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A489" s="2" t="s">
+        <v>2906</v>
+      </c>
+      <c r="O489" s="2" t="s">
+        <v>2908</v>
       </c>
     </row>
     <row r="490" spans="1:15" ht="24.95" customHeight="1">
       <c r="A490" s="2" t="s">
-        <v>3203</v>
+        <v>2907</v>
       </c>
       <c r="O490" s="3" t="s">
-        <v>3206</v>
+        <v>2909</v>
       </c>
     </row>
     <row r="491" spans="1:15" ht="24.95" customHeight="1">
       <c r="A491" s="2" t="s">
-        <v>3204</v>
+        <v>2973</v>
       </c>
       <c r="O491" s="3" t="s">
-        <v>3205</v>
-      </c>
-    </row>
-    <row r="492" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O492" s="2"/>
+        <v>2999</v>
+      </c>
     </row>
     <row r="493" spans="1:15" ht="24.95" customHeight="1">
       <c r="A493" s="2" t="s">
-        <v>2480</v>
+        <v>3203</v>
       </c>
       <c r="O493" s="3" t="s">
-        <v>2481</v>
+        <v>3206</v>
       </c>
     </row>
     <row r="494" spans="1:15" ht="24.95" customHeight="1">
       <c r="A494" s="2" t="s">
-        <v>2470</v>
-      </c>
-      <c r="O494" s="2" t="s">
-        <v>2468</v>
+        <v>3204</v>
+      </c>
+      <c r="O494" s="3" t="s">
+        <v>3205</v>
       </c>
     </row>
     <row r="495" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A495" s="2" t="s">
-        <v>2471</v>
-      </c>
-      <c r="O495" s="2" t="s">
-        <v>2469</v>
-      </c>
+      <c r="O495" s="2"/>
     </row>
     <row r="496" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O496" s="2"/>
+      <c r="A496" s="2" t="s">
+        <v>2480</v>
+      </c>
+      <c r="O496" s="3" t="s">
+        <v>2481</v>
+      </c>
     </row>
     <row r="497" spans="1:15" ht="24.95" customHeight="1">
       <c r="A497" s="2" t="s">
-        <v>1607</v>
-      </c>
-      <c r="B497" s="2" t="s">
-        <v>1797</v>
+        <v>2470</v>
       </c>
       <c r="O497" s="2" t="s">
-        <v>1632</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="498" spans="1:15" ht="24.95" customHeight="1">
       <c r="A498" s="2" t="s">
-        <v>1608</v>
+        <v>2471</v>
       </c>
       <c r="O498" s="2" t="s">
-        <v>2413</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="499" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A499" s="2" t="s">
-        <v>1633</v>
-      </c>
-      <c r="B499" s="2" t="s">
-        <v>2414</v>
-      </c>
-      <c r="O499" s="2" t="s">
-        <v>1795</v>
-      </c>
+      <c r="O499" s="2"/>
     </row>
     <row r="500" spans="1:15" ht="24.95" customHeight="1">
       <c r="A500" s="2" t="s">
-        <v>937</v>
+        <v>1607</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>2415</v>
+        <v>1797</v>
       </c>
       <c r="O500" s="2" t="s">
-        <v>2417</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="501" spans="1:15" ht="24.95" customHeight="1">
       <c r="A501" s="2" t="s">
-        <v>938</v>
-      </c>
-      <c r="B501" s="2" t="s">
-        <v>2418</v>
+        <v>1608</v>
       </c>
       <c r="O501" s="2" t="s">
-        <v>939</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="502" spans="1:15" ht="24.95" customHeight="1">
       <c r="A502" s="2" t="s">
-        <v>940</v>
+        <v>1633</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
       <c r="O502" s="2" t="s">
-        <v>2412</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="503" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O503" s="2"/>
+      <c r="A503" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="B503" s="2" t="s">
+        <v>2415</v>
+      </c>
+      <c r="O503" s="2" t="s">
+        <v>2417</v>
+      </c>
     </row>
     <row r="504" spans="1:15" ht="24.95" customHeight="1">
       <c r="A504" s="2" t="s">
-        <v>966</v>
+        <v>938</v>
+      </c>
+      <c r="B504" s="2" t="s">
+        <v>2418</v>
       </c>
       <c r="O504" s="2" t="s">
-        <v>967</v>
+        <v>939</v>
       </c>
     </row>
     <row r="505" spans="1:15" ht="24.95" customHeight="1">
       <c r="A505" s="2" t="s">
-        <v>968</v>
+        <v>940</v>
+      </c>
+      <c r="B505" s="2" t="s">
+        <v>2416</v>
       </c>
       <c r="O505" s="2" t="s">
-        <v>2855</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="506" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A506" s="2" t="s">
-        <v>969</v>
-      </c>
-      <c r="O506" s="2" t="s">
-        <v>970</v>
-      </c>
+      <c r="O506" s="2"/>
     </row>
     <row r="507" spans="1:15" ht="24.95" customHeight="1">
       <c r="A507" s="2" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="O507" s="2" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
     </row>
     <row r="508" spans="1:15" ht="24.95" customHeight="1">
       <c r="A508" s="2" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="O508" s="2" t="s">
-        <v>2512</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="509" spans="1:15" ht="24.95" customHeight="1">
       <c r="A509" s="2" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="O509" s="2" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
     </row>
     <row r="510" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O510" s="2"/>
+      <c r="A510" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="O510" s="2" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="511" spans="1:15" ht="24.95" customHeight="1">
       <c r="A511" s="2" t="s">
-        <v>3227</v>
-      </c>
-      <c r="B511" s="2" t="s">
-        <v>3229</v>
+        <v>973</v>
       </c>
       <c r="O511" s="2" t="s">
-        <v>3228</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="512" spans="1:15" ht="24.95" customHeight="1">
       <c r="A512" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="B512" s="2" t="s">
-        <v>796</v>
+        <v>974</v>
       </c>
       <c r="O512" s="2" t="s">
-        <v>1638</v>
+        <v>975</v>
       </c>
     </row>
     <row r="513" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A513" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="B513" s="2" t="s">
-        <v>798</v>
-      </c>
-      <c r="O513" s="2" t="s">
-        <v>799</v>
-      </c>
+      <c r="O513" s="2"/>
     </row>
     <row r="514" spans="1:15" ht="24.95" customHeight="1">
       <c r="A514" s="2" t="s">
-        <v>1637</v>
+        <v>3227</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="O514" s="3" t="s">
-        <v>1636</v>
+        <v>3229</v>
+      </c>
+      <c r="O514" s="2" t="s">
+        <v>3228</v>
+      </c>
+    </row>
+    <row r="515" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A515" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="B515" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="O515" s="2" t="s">
+        <v>1638</v>
       </c>
     </row>
     <row r="516" spans="1:15" ht="24.95" customHeight="1">
       <c r="A516" s="2" t="s">
-        <v>3221</v>
-      </c>
-      <c r="O516" s="3" t="s">
-        <v>3224</v>
+        <v>797</v>
+      </c>
+      <c r="B516" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="O516" s="2" t="s">
+        <v>799</v>
       </c>
     </row>
     <row r="517" spans="1:15" ht="24.95" customHeight="1">
       <c r="A517" s="2" t="s">
-        <v>3225</v>
+        <v>1637</v>
+      </c>
+      <c r="B517" s="2" t="s">
+        <v>800</v>
       </c>
       <c r="O517" s="3" t="s">
-        <v>3226</v>
-      </c>
-    </row>
-    <row r="518" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A518" s="2" t="s">
-        <v>3219</v>
-      </c>
-      <c r="O518" s="3" t="s">
-        <v>3222</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="519" spans="1:15" ht="24.95" customHeight="1">
       <c r="A519" s="2" t="s">
-        <v>3220</v>
+        <v>3221</v>
       </c>
       <c r="O519" s="3" t="s">
-        <v>3223</v>
+        <v>3224</v>
+      </c>
+    </row>
+    <row r="520" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A520" s="2" t="s">
+        <v>3225</v>
+      </c>
+      <c r="O520" s="3" t="s">
+        <v>3226</v>
+      </c>
+    </row>
+    <row r="521" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A521" s="2" t="s">
+        <v>3219</v>
+      </c>
+      <c r="O521" s="3" t="s">
+        <v>3222</v>
       </c>
     </row>
     <row r="522" spans="1:15" ht="24.95" customHeight="1">
       <c r="A522" s="2" t="s">
-        <v>2884</v>
-      </c>
-      <c r="B522" s="2" t="s">
-        <v>2885</v>
+        <v>3220</v>
       </c>
       <c r="O522" s="3" t="s">
-        <v>2886</v>
-      </c>
-    </row>
-    <row r="523" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O523" s="2"/>
-    </row>
-    <row r="524" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A524" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="B524" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="O524" s="2" t="s">
-        <v>803</v>
+        <v>3223</v>
       </c>
     </row>
     <row r="525" spans="1:15" ht="24.95" customHeight="1">
       <c r="A525" s="2" t="s">
-        <v>804</v>
+        <v>2884</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="O525" s="2" t="s">
-        <v>519</v>
+        <v>2885</v>
+      </c>
+      <c r="O525" s="3" t="s">
+        <v>2886</v>
       </c>
     </row>
     <row r="526" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A526" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="B526" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="O526" s="2" t="s">
-        <v>808</v>
-      </c>
+      <c r="O526" s="2"/>
     </row>
     <row r="527" spans="1:15" ht="24.95" customHeight="1">
       <c r="A527" s="2" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>530</v>
+        <v>802</v>
       </c>
       <c r="O527" s="2" t="s">
-        <v>531</v>
+        <v>803</v>
       </c>
     </row>
     <row r="528" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O528" s="2"/>
+      <c r="A528" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="B528" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="O528" s="2" t="s">
+        <v>519</v>
+      </c>
     </row>
     <row r="529" spans="1:15" ht="24.95" customHeight="1">
       <c r="A529" s="2" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="O529" s="2" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
     </row>
     <row r="530" spans="1:15" ht="24.95" customHeight="1">
       <c r="A530" s="2" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>817</v>
+        <v>530</v>
       </c>
       <c r="O530" s="2" t="s">
-        <v>818</v>
+        <v>531</v>
       </c>
     </row>
     <row r="531" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A531" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="B531" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="O531" s="2" t="s">
-        <v>821</v>
-      </c>
+      <c r="O531" s="2"/>
     </row>
     <row r="532" spans="1:15" ht="24.95" customHeight="1">
       <c r="A532" s="2" t="s">
-        <v>2419</v>
+        <v>810</v>
+      </c>
+      <c r="B532" s="2" t="s">
+        <v>811</v>
       </c>
       <c r="O532" s="2" t="s">
-        <v>2420</v>
+        <v>812</v>
       </c>
     </row>
     <row r="533" spans="1:15" ht="24.95" customHeight="1">
       <c r="A533" s="2" t="s">
-        <v>822</v>
+        <v>816</v>
+      </c>
+      <c r="B533" s="2" t="s">
+        <v>817</v>
       </c>
       <c r="O533" s="2" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
     </row>
     <row r="534" spans="1:15" ht="24.95" customHeight="1">
       <c r="A534" s="2" t="s">
-        <v>2292</v>
+        <v>819</v>
+      </c>
+      <c r="B534" s="2" t="s">
+        <v>820</v>
       </c>
       <c r="O534" s="2" t="s">
-        <v>2466</v>
+        <v>821</v>
       </c>
     </row>
     <row r="535" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O535" s="2"/>
+      <c r="A535" s="2" t="s">
+        <v>2419</v>
+      </c>
+      <c r="O535" s="2" t="s">
+        <v>2420</v>
+      </c>
     </row>
     <row r="536" spans="1:15" ht="24.95" customHeight="1">
       <c r="A536" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="B536" s="2" t="s">
-        <v>1669</v>
+        <v>822</v>
       </c>
       <c r="O536" s="2" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="537" spans="1:15" ht="24.95" customHeight="1">
       <c r="A537" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="B537" s="2" t="s">
-        <v>814</v>
+        <v>2292</v>
       </c>
       <c r="O537" s="2" t="s">
-        <v>815</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="538" spans="1:15" ht="24.95" customHeight="1">
@@ -17278,548 +17308,548 @@
     </row>
     <row r="539" spans="1:15" ht="24.95" customHeight="1">
       <c r="A539" s="2" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>827</v>
+        <v>1669</v>
       </c>
       <c r="O539" s="2" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
     </row>
     <row r="540" spans="1:15" ht="24.95" customHeight="1">
       <c r="A540" s="2" t="s">
-        <v>829</v>
+        <v>813</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>830</v>
+        <v>814</v>
       </c>
       <c r="O540" s="2" t="s">
-        <v>831</v>
+        <v>815</v>
       </c>
     </row>
     <row r="541" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A541" s="2" t="s">
-        <v>832</v>
-      </c>
-      <c r="B541" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="O541" s="2" t="s">
-        <v>2465</v>
-      </c>
+      <c r="O541" s="2"/>
     </row>
     <row r="542" spans="1:15" ht="24.95" customHeight="1">
       <c r="A542" s="2" t="s">
-        <v>1666</v>
+        <v>826</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>1668</v>
+        <v>827</v>
       </c>
       <c r="O542" s="2" t="s">
-        <v>1667</v>
+        <v>828</v>
       </c>
     </row>
     <row r="543" spans="1:15" ht="24.95" customHeight="1">
       <c r="A543" s="2" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="O543" s="2" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
     </row>
     <row r="544" spans="1:15" ht="24.95" customHeight="1">
       <c r="A544" s="2" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="O544" s="2" t="s">
-        <v>839</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="545" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O545" s="2"/>
+      <c r="A545" s="2" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B545" s="2" t="s">
+        <v>1668</v>
+      </c>
+      <c r="O545" s="2" t="s">
+        <v>1667</v>
+      </c>
     </row>
     <row r="546" spans="1:15" ht="24.95" customHeight="1">
       <c r="A546" s="2" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="O546" s="2" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
     </row>
     <row r="547" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O547" s="2"/>
+      <c r="A547" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B547" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="O547" s="2" t="s">
+        <v>839</v>
+      </c>
     </row>
     <row r="548" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A548" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="B548" s="2" t="s">
-        <v>844</v>
-      </c>
-      <c r="O548" s="2" t="s">
-        <v>845</v>
-      </c>
+      <c r="O548" s="2"/>
     </row>
     <row r="549" spans="1:15" ht="24.95" customHeight="1">
       <c r="A549" s="2" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="O549" s="2" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
     </row>
     <row r="550" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A550" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="B550" s="2" t="s">
-        <v>850</v>
-      </c>
-      <c r="O550" s="2" t="s">
-        <v>851</v>
-      </c>
+      <c r="O550" s="2"/>
     </row>
     <row r="551" spans="1:15" ht="24.95" customHeight="1">
       <c r="A551" s="2" t="s">
-        <v>852</v>
+        <v>843</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="O551" s="2" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
     </row>
     <row r="552" spans="1:15" ht="24.95" customHeight="1">
       <c r="A552" s="2" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>856</v>
+        <v>847</v>
       </c>
       <c r="O552" s="2" t="s">
-        <v>857</v>
+        <v>848</v>
       </c>
     </row>
     <row r="553" spans="1:15" ht="24.95" customHeight="1">
       <c r="A553" s="2" t="s">
-        <v>858</v>
+        <v>849</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>651</v>
+        <v>850</v>
       </c>
       <c r="O553" s="2" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
     </row>
     <row r="554" spans="1:15" ht="24.95" customHeight="1">
       <c r="A554" s="2" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>1794</v>
+        <v>853</v>
       </c>
       <c r="O554" s="2" t="s">
-        <v>1793</v>
+        <v>854</v>
       </c>
     </row>
     <row r="555" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O555" s="2"/>
+      <c r="A555" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B555" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="O555" s="2" t="s">
+        <v>857</v>
+      </c>
     </row>
     <row r="556" spans="1:15" ht="24.95" customHeight="1">
       <c r="A556" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>862</v>
+        <v>651</v>
       </c>
       <c r="O556" s="2" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
     </row>
     <row r="557" spans="1:15" ht="24.95" customHeight="1">
       <c r="A557" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>865</v>
+        <v>1794</v>
       </c>
       <c r="O557" s="2" t="s">
-        <v>866</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="558" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A558" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="B558" s="2" t="s">
-        <v>868</v>
-      </c>
-      <c r="O558" s="2" t="s">
-        <v>869</v>
-      </c>
+      <c r="O558" s="2"/>
     </row>
     <row r="559" spans="1:15" ht="24.95" customHeight="1">
       <c r="A559" s="2" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="O559" s="2" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
     </row>
     <row r="560" spans="1:15" ht="24.95" customHeight="1">
       <c r="A560" s="2" t="s">
-        <v>873</v>
+        <v>864</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
       <c r="O560" s="2" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
     </row>
     <row r="561" spans="1:15" ht="24.95" customHeight="1">
       <c r="A561" s="2" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="O561" s="2" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
     </row>
     <row r="562" spans="1:15" ht="24.95" customHeight="1">
       <c r="A562" s="2" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
       <c r="O562" s="2" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
     </row>
     <row r="563" spans="1:15" ht="24.95" customHeight="1">
       <c r="A563" s="2" t="s">
-        <v>882</v>
+        <v>873</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>883</v>
+        <v>874</v>
       </c>
       <c r="O563" s="2" t="s">
-        <v>884</v>
+        <v>875</v>
       </c>
     </row>
     <row r="564" spans="1:15" ht="24.95" customHeight="1">
       <c r="A564" s="2" t="s">
-        <v>885</v>
+        <v>876</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="O564" s="2" t="s">
-        <v>887</v>
+        <v>878</v>
       </c>
     </row>
     <row r="565" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O565" s="2"/>
+      <c r="A565" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B565" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="O565" s="2" t="s">
+        <v>881</v>
+      </c>
     </row>
     <row r="566" spans="1:15" ht="24.95" customHeight="1">
       <c r="A566" s="2" t="s">
-        <v>1779</v>
+        <v>882</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="O566" s="2" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
     </row>
     <row r="567" spans="1:15" ht="24.95" customHeight="1">
       <c r="A567" s="2" t="s">
-        <v>1780</v>
+        <v>885</v>
+      </c>
+      <c r="B567" s="2" t="s">
+        <v>886</v>
       </c>
       <c r="O567" s="2" t="s">
-        <v>1781</v>
+        <v>887</v>
       </c>
     </row>
     <row r="568" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A568" s="2" t="s">
-        <v>890</v>
-      </c>
-      <c r="B568" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="O568" s="2" t="s">
-        <v>892</v>
-      </c>
+      <c r="O568" s="2"/>
     </row>
     <row r="569" spans="1:15" ht="24.95" customHeight="1">
       <c r="A569" s="2" t="s">
-        <v>893</v>
+        <v>1779</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="O569" s="2" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
     </row>
     <row r="570" spans="1:15" ht="24.95" customHeight="1">
       <c r="A570" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="B570" s="2" t="s">
-        <v>897</v>
+        <v>1780</v>
       </c>
       <c r="O570" s="2" t="s">
-        <v>898</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="571" spans="1:15" ht="24.95" customHeight="1">
       <c r="A571" s="2" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>1774</v>
+        <v>891</v>
       </c>
       <c r="O571" s="2" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
     </row>
     <row r="572" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O572" s="2"/>
+      <c r="A572" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B572" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="O572" s="2" t="s">
+        <v>895</v>
+      </c>
     </row>
     <row r="573" spans="1:15" ht="24.95" customHeight="1">
       <c r="A573" s="2" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="O573" s="2" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
     </row>
     <row r="574" spans="1:15" ht="24.95" customHeight="1">
       <c r="A574" s="2" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>905</v>
+        <v>1774</v>
       </c>
       <c r="O574" s="2" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
     </row>
     <row r="575" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A575" s="2" t="s">
-        <v>907</v>
-      </c>
-      <c r="B575" s="2" t="s">
-        <v>908</v>
-      </c>
-      <c r="O575" s="2" t="s">
-        <v>909</v>
-      </c>
+      <c r="O575" s="2"/>
     </row>
     <row r="576" spans="1:15" ht="24.95" customHeight="1">
       <c r="A576" s="2" t="s">
-        <v>910</v>
+        <v>901</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
       <c r="O576" s="2" t="s">
-        <v>912</v>
+        <v>903</v>
       </c>
     </row>
     <row r="577" spans="1:15" ht="24.95" customHeight="1">
       <c r="A577" s="2" t="s">
-        <v>913</v>
+        <v>904</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>914</v>
+        <v>905</v>
       </c>
       <c r="O577" s="2" t="s">
-        <v>915</v>
+        <v>906</v>
       </c>
     </row>
     <row r="578" spans="1:15" ht="24.95" customHeight="1">
       <c r="A578" s="2" t="s">
-        <v>2287</v>
+        <v>907</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>932</v>
+        <v>908</v>
       </c>
       <c r="O578" s="2" t="s">
-        <v>918</v>
+        <v>909</v>
       </c>
     </row>
     <row r="579" spans="1:15" ht="24.95" customHeight="1">
       <c r="A579" s="2" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="O579" s="2" t="s">
-        <v>2288</v>
+        <v>912</v>
       </c>
     </row>
     <row r="580" spans="1:15" ht="24.95" customHeight="1">
       <c r="A580" s="2" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="O580" s="2" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
     </row>
     <row r="581" spans="1:15" ht="24.95" customHeight="1">
       <c r="A581" s="2" t="s">
-        <v>922</v>
+        <v>2287</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="O581" s="2" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="582" spans="1:15" ht="24.95" customHeight="1">
       <c r="A582" s="2" t="s">
-        <v>1782</v>
+        <v>916</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="O582" s="2" t="s">
-        <v>926</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="583" spans="1:15" ht="24.95" customHeight="1">
       <c r="A583" s="2" t="s">
-        <v>927</v>
-      </c>
-      <c r="B583" s="3" t="s">
-        <v>2289</v>
+        <v>919</v>
+      </c>
+      <c r="B583" s="2" t="s">
+        <v>920</v>
       </c>
       <c r="O583" s="2" t="s">
-        <v>928</v>
+        <v>921</v>
       </c>
     </row>
     <row r="584" spans="1:15" ht="24.95" customHeight="1">
       <c r="A584" s="2" t="s">
-        <v>929</v>
+        <v>922</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>930</v>
+        <v>923</v>
       </c>
       <c r="O584" s="2" t="s">
-        <v>931</v>
+        <v>924</v>
       </c>
     </row>
     <row r="585" spans="1:15" ht="24.95" customHeight="1">
       <c r="A585" s="2" t="s">
-        <v>933</v>
+        <v>1782</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>897</v>
+        <v>925</v>
       </c>
       <c r="O585" s="2" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
     </row>
     <row r="586" spans="1:15" ht="24.95" customHeight="1">
       <c r="A586" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="B586" s="2" t="s">
-        <v>2290</v>
+        <v>927</v>
+      </c>
+      <c r="B586" s="3" t="s">
+        <v>2289</v>
       </c>
       <c r="O586" s="2" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
     </row>
     <row r="587" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O587" s="2"/>
+      <c r="A587" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="B587" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="O587" s="2" t="s">
+        <v>931</v>
+      </c>
     </row>
     <row r="588" spans="1:15" ht="24.95" customHeight="1">
       <c r="A588" s="2" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>942</v>
+        <v>897</v>
       </c>
       <c r="O588" s="2" t="s">
-        <v>943</v>
+        <v>934</v>
       </c>
     </row>
     <row r="589" spans="1:15" ht="24.95" customHeight="1">
       <c r="A589" s="2" t="s">
-        <v>944</v>
+        <v>935</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>945</v>
+        <v>2290</v>
       </c>
       <c r="O589" s="2" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
     </row>
     <row r="590" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A590" s="2" t="s">
-        <v>947</v>
-      </c>
-      <c r="B590" s="2" t="s">
-        <v>948</v>
-      </c>
-      <c r="O590" s="2" t="s">
-        <v>949</v>
-      </c>
+      <c r="O590" s="2"/>
     </row>
     <row r="591" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O591" s="2"/>
+      <c r="A591" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B591" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="O591" s="2" t="s">
+        <v>943</v>
+      </c>
     </row>
     <row r="592" spans="1:15" ht="24.95" customHeight="1">
       <c r="A592" s="2" t="s">
-        <v>1675</v>
+        <v>944</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="O592" s="2" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
     </row>
     <row r="593" spans="1:15" ht="24.95" customHeight="1">
       <c r="A593" s="2" t="s">
-        <v>1676</v>
+        <v>947</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="O593" s="2" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
     </row>
     <row r="594" spans="1:15" ht="24.95" customHeight="1">
@@ -17827,540 +17857,540 @@
     </row>
     <row r="595" spans="1:15" ht="24.95" customHeight="1">
       <c r="A595" s="2" t="s">
-        <v>954</v>
+        <v>1675</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="O595" s="2" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
     </row>
     <row r="596" spans="1:15" ht="24.95" customHeight="1">
       <c r="A596" s="2" t="s">
-        <v>957</v>
+        <v>1676</v>
       </c>
       <c r="B596" s="2" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="O596" s="2" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
     </row>
     <row r="597" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A597" s="2" t="s">
-        <v>960</v>
-      </c>
-      <c r="B597" s="2" t="s">
-        <v>961</v>
-      </c>
-      <c r="O597" s="2" t="s">
-        <v>962</v>
-      </c>
+      <c r="O597" s="2"/>
     </row>
     <row r="598" spans="1:15" ht="24.95" customHeight="1">
       <c r="A598" s="2" t="s">
-        <v>963</v>
+        <v>954</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>964</v>
+        <v>955</v>
       </c>
       <c r="O598" s="2" t="s">
-        <v>965</v>
+        <v>956</v>
       </c>
     </row>
     <row r="599" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O599" s="2"/>
+      <c r="A599" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="B599" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="O599" s="2" t="s">
+        <v>959</v>
+      </c>
     </row>
     <row r="600" spans="1:15" ht="24.95" customHeight="1">
       <c r="A600" s="2" t="s">
-        <v>976</v>
+        <v>960</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>977</v>
+        <v>961</v>
       </c>
       <c r="O600" s="2" t="s">
-        <v>978</v>
+        <v>962</v>
       </c>
     </row>
     <row r="601" spans="1:15" ht="24.95" customHeight="1">
       <c r="A601" s="2" t="s">
-        <v>979</v>
+        <v>963</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>980</v>
+        <v>964</v>
       </c>
       <c r="O601" s="2" t="s">
-        <v>981</v>
+        <v>965</v>
       </c>
     </row>
     <row r="602" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A602" s="2" t="s">
-        <v>982</v>
-      </c>
-      <c r="B602" s="2" t="s">
-        <v>983</v>
-      </c>
-      <c r="O602" s="2" t="s">
-        <v>984</v>
-      </c>
+      <c r="O602" s="2"/>
     </row>
     <row r="603" spans="1:15" ht="24.95" customHeight="1">
       <c r="A603" s="2" t="s">
-        <v>985</v>
+        <v>976</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>986</v>
+        <v>977</v>
       </c>
       <c r="O603" s="2" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
     </row>
     <row r="604" spans="1:15" ht="24.95" customHeight="1">
       <c r="A604" s="2" t="s">
-        <v>988</v>
+        <v>979</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>989</v>
+        <v>980</v>
       </c>
       <c r="O604" s="2" t="s">
-        <v>990</v>
+        <v>981</v>
       </c>
     </row>
     <row r="605" spans="1:15" ht="24.95" customHeight="1">
       <c r="A605" s="2" t="s">
-        <v>991</v>
+        <v>982</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>992</v>
+        <v>983</v>
       </c>
       <c r="O605" s="2" t="s">
-        <v>993</v>
+        <v>984</v>
       </c>
     </row>
     <row r="606" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O606" s="2"/>
+      <c r="A606" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="B606" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="O606" s="2" t="s">
+        <v>987</v>
+      </c>
     </row>
     <row r="607" spans="1:15" ht="24.95" customHeight="1">
       <c r="A607" s="2" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="O607" s="2" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
     </row>
     <row r="608" spans="1:15" ht="24.95" customHeight="1">
       <c r="A608" s="2" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="O608" s="2" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
     </row>
     <row r="609" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A609" s="2" t="s">
-        <v>1000</v>
-      </c>
-      <c r="B609" s="2" t="s">
-        <v>1001</v>
-      </c>
-      <c r="O609" s="2" t="s">
-        <v>1002</v>
-      </c>
+      <c r="O609" s="2"/>
     </row>
     <row r="610" spans="1:15" ht="24.95" customHeight="1">
       <c r="A610" s="2" t="s">
-        <v>1003</v>
+        <v>994</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>1004</v>
+        <v>995</v>
       </c>
       <c r="O610" s="2" t="s">
-        <v>1005</v>
+        <v>996</v>
       </c>
     </row>
     <row r="611" spans="1:15" ht="24.95" customHeight="1">
       <c r="A611" s="2" t="s">
-        <v>1006</v>
+        <v>997</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>964</v>
+        <v>998</v>
       </c>
       <c r="O611" s="2" t="s">
-        <v>965</v>
+        <v>999</v>
       </c>
     </row>
     <row r="612" spans="1:15" ht="24.95" customHeight="1">
       <c r="A612" s="2" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="O612" s="2" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="613" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O613" s="2"/>
+      <c r="A613" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B613" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="O613" s="2" t="s">
+        <v>1005</v>
+      </c>
     </row>
     <row r="614" spans="1:15" ht="24.95" customHeight="1">
       <c r="A614" s="2" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>1011</v>
+        <v>964</v>
       </c>
       <c r="O614" s="2" t="s">
-        <v>633</v>
+        <v>965</v>
       </c>
     </row>
     <row r="615" spans="1:15" ht="24.95" customHeight="1">
       <c r="A615" s="2" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="O615" s="2" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="616" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A616" s="2" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B616" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="O616" s="2" t="s">
-        <v>1017</v>
-      </c>
+      <c r="O616" s="2"/>
     </row>
     <row r="617" spans="1:15" ht="24.95" customHeight="1">
       <c r="A617" s="2" t="s">
-        <v>1018</v>
+        <v>1010</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>1019</v>
+        <v>1011</v>
       </c>
       <c r="O617" s="2" t="s">
-        <v>1020</v>
+        <v>633</v>
       </c>
     </row>
     <row r="618" spans="1:15" ht="24.95" customHeight="1">
       <c r="A618" s="2" t="s">
-        <v>1021</v>
+        <v>1012</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>1022</v>
+        <v>1013</v>
       </c>
       <c r="O618" s="2" t="s">
-        <v>1023</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="619" spans="1:15" ht="24.95" customHeight="1">
       <c r="A619" s="2" t="s">
-        <v>1024</v>
+        <v>1015</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>1025</v>
+        <v>1016</v>
       </c>
       <c r="O619" s="2" t="s">
-        <v>1026</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="620" spans="1:15" ht="24.95" customHeight="1">
       <c r="A620" s="2" t="s">
-        <v>1027</v>
+        <v>1018</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>1028</v>
+        <v>1019</v>
       </c>
       <c r="O620" s="2" t="s">
-        <v>1029</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="621" spans="1:15" ht="24.95" customHeight="1">
       <c r="A621" s="2" t="s">
-        <v>1030</v>
+        <v>1021</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>1031</v>
+        <v>1022</v>
       </c>
       <c r="O621" s="2" t="s">
-        <v>1032</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="622" spans="1:15" ht="24.95" customHeight="1">
       <c r="A622" s="2" t="s">
-        <v>1033</v>
+        <v>1024</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>1034</v>
+        <v>1025</v>
       </c>
       <c r="O622" s="2" t="s">
-        <v>1035</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="623" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O623" s="2"/>
+      <c r="A623" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B623" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="O623" s="2" t="s">
+        <v>1029</v>
+      </c>
     </row>
     <row r="624" spans="1:15" ht="24.95" customHeight="1">
       <c r="A624" s="2" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="O624" s="2" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="625" spans="1:15" ht="24.95" customHeight="1">
       <c r="A625" s="2" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="O625" s="2" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="626" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A626" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="B626" s="2" t="s">
-        <v>1043</v>
-      </c>
-      <c r="O626" s="2" t="s">
-        <v>2291</v>
-      </c>
+      <c r="O626" s="2"/>
     </row>
     <row r="627" spans="1:15" ht="24.95" customHeight="1">
       <c r="A627" s="2" t="s">
-        <v>1044</v>
+        <v>1036</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>1045</v>
+        <v>1037</v>
       </c>
       <c r="O627" s="2" t="s">
-        <v>1046</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="628" spans="1:15" ht="24.95" customHeight="1">
       <c r="A628" s="2" t="s">
-        <v>1047</v>
+        <v>1039</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>1048</v>
+        <v>1040</v>
       </c>
       <c r="O628" s="2" t="s">
-        <v>1049</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="629" spans="1:15" ht="24.95" customHeight="1">
       <c r="A629" s="2" t="s">
-        <v>1050</v>
+        <v>1042</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>66</v>
+        <v>1043</v>
       </c>
       <c r="O629" s="2" t="s">
-        <v>1051</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="630" spans="1:15" ht="24.95" customHeight="1">
       <c r="A630" s="2" t="s">
-        <v>1052</v>
+        <v>1044</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>1053</v>
+        <v>1045</v>
       </c>
       <c r="O630" s="2" t="s">
-        <v>1054</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="631" spans="1:15" ht="24.95" customHeight="1">
       <c r="A631" s="2" t="s">
-        <v>1055</v>
+        <v>1047</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>1056</v>
+        <v>1048</v>
       </c>
       <c r="O631" s="2" t="s">
-        <v>1057</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="632" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O632" s="2"/>
+      <c r="A632" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B632" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="O632" s="2" t="s">
+        <v>1051</v>
+      </c>
     </row>
     <row r="633" spans="1:15" ht="24.95" customHeight="1">
       <c r="A633" s="2" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>1764</v>
+        <v>1053</v>
       </c>
       <c r="O633" s="2" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="634" spans="1:15" ht="24.95" customHeight="1">
       <c r="A634" s="2" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>1765</v>
+        <v>1056</v>
       </c>
       <c r="O634" s="2" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="635" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A635" s="2" t="s">
-        <v>1062</v>
-      </c>
-      <c r="B635" s="2" t="s">
-        <v>1772</v>
-      </c>
-      <c r="O635" s="2" t="s">
-        <v>1063</v>
-      </c>
+      <c r="O635" s="2"/>
     </row>
     <row r="636" spans="1:15" ht="24.95" customHeight="1">
       <c r="A636" s="2" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>1771</v>
+        <v>1764</v>
       </c>
       <c r="O636" s="2" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="637" spans="1:15" ht="24.95" customHeight="1">
       <c r="A637" s="2" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>1768</v>
+        <v>1765</v>
       </c>
       <c r="O637" s="2" t="s">
-        <v>1710</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="638" spans="1:15" ht="24.95" customHeight="1">
       <c r="A638" s="2" t="s">
-        <v>1769</v>
+        <v>1062</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>1770</v>
+        <v>1772</v>
       </c>
       <c r="O638" s="2" t="s">
-        <v>1709</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="639" spans="1:15" ht="24.95" customHeight="1">
       <c r="A639" s="2" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>1766</v>
+        <v>1771</v>
       </c>
       <c r="O639" s="2" t="s">
-        <v>1708</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="640" spans="1:15" ht="24.95" customHeight="1">
       <c r="A640" s="2" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="O640" s="2" t="s">
-        <v>1707</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="641" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O641" s="2"/>
+      <c r="A641" s="2" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B641" s="2" t="s">
+        <v>1770</v>
+      </c>
+      <c r="O641" s="2" t="s">
+        <v>1709</v>
+      </c>
     </row>
     <row r="642" spans="1:15" ht="24.95" customHeight="1">
       <c r="A642" s="2" t="s">
-        <v>1832</v>
+        <v>1067</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>1822</v>
+        <v>1766</v>
       </c>
       <c r="O642" s="2" t="s">
-        <v>1839</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="643" spans="1:15" ht="24.95" customHeight="1">
       <c r="A643" s="2" t="s">
-        <v>1833</v>
+        <v>1068</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>1835</v>
+        <v>1767</v>
       </c>
       <c r="O643" s="2" t="s">
-        <v>1837</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="644" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A644" s="2" t="s">
-        <v>1834</v>
-      </c>
-      <c r="B644" s="2" t="s">
-        <v>1836</v>
-      </c>
-      <c r="O644" s="2" t="s">
-        <v>1838</v>
-      </c>
+      <c r="O644" s="2"/>
     </row>
     <row r="645" spans="1:15" ht="24.95" customHeight="1">
       <c r="A645" s="2" t="s">
-        <v>1840</v>
+        <v>1832</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>1841</v>
+        <v>1822</v>
       </c>
       <c r="O645" s="2" t="s">
-        <v>1842</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="646" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O646" s="2"/>
+      <c r="A646" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B646" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="O646" s="2" t="s">
+        <v>1837</v>
+      </c>
     </row>
     <row r="647" spans="1:15" ht="24.95" customHeight="1">
       <c r="A647" s="2" t="s">
-        <v>1069</v>
+        <v>1834</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>1070</v>
+        <v>1836</v>
       </c>
       <c r="O647" s="2" t="s">
-        <v>3030</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="648" spans="1:15" ht="24.95" customHeight="1">
       <c r="A648" s="2" t="s">
-        <v>1071</v>
+        <v>1840</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>1072</v>
+        <v>1841</v>
       </c>
       <c r="O648" s="2" t="s">
-        <v>1073</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="649" spans="1:15" ht="24.95" customHeight="1">
@@ -18368,294 +18398,300 @@
     </row>
     <row r="650" spans="1:15" ht="24.95" customHeight="1">
       <c r="A650" s="2" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="O650" s="2" t="s">
-        <v>1076</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="651" spans="1:15" ht="24.95" customHeight="1">
       <c r="A651" s="2" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="O651" s="2" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="652" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A652" s="2" t="s">
-        <v>1080</v>
-      </c>
-      <c r="B652" s="2" t="s">
-        <v>1081</v>
-      </c>
-      <c r="O652" s="2" t="s">
-        <v>1082</v>
-      </c>
+      <c r="O652" s="2"/>
     </row>
     <row r="653" spans="1:15" ht="24.95" customHeight="1">
       <c r="A653" s="2" t="s">
-        <v>1083</v>
+        <v>1074</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>1084</v>
+        <v>1075</v>
       </c>
       <c r="O653" s="2" t="s">
-        <v>1085</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="654" spans="1:15" ht="24.95" customHeight="1">
       <c r="A654" s="2" t="s">
-        <v>1086</v>
+        <v>1077</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1087</v>
+        <v>1078</v>
       </c>
       <c r="O654" s="2" t="s">
-        <v>1088</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="655" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O655" s="2"/>
+      <c r="A655" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B655" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="O655" s="2" t="s">
+        <v>1082</v>
+      </c>
     </row>
     <row r="656" spans="1:15" ht="24.95" customHeight="1">
       <c r="A656" s="2" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="O656" s="2" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="657" spans="1:15" ht="24.95" customHeight="1">
       <c r="A657" s="2" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="O657" s="2" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="658" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A658" s="2" t="s">
-        <v>1095</v>
-      </c>
-      <c r="B658" s="2" t="s">
-        <v>1096</v>
-      </c>
-      <c r="O658" s="2" t="s">
-        <v>1097</v>
-      </c>
+      <c r="O658" s="2"/>
     </row>
     <row r="659" spans="1:15" ht="24.95" customHeight="1">
       <c r="A659" s="2" t="s">
-        <v>1098</v>
+        <v>1089</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>1099</v>
+        <v>1090</v>
       </c>
       <c r="O659" s="2" t="s">
-        <v>1100</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="660" spans="1:15" ht="24.95" customHeight="1">
       <c r="A660" s="2" t="s">
-        <v>1101</v>
+        <v>1092</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>1102</v>
+        <v>1093</v>
       </c>
       <c r="O660" s="2" t="s">
-        <v>1103</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="661" spans="1:15" ht="24.95" customHeight="1">
       <c r="A661" s="2" t="s">
-        <v>1104</v>
+        <v>1095</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>1105</v>
+        <v>1096</v>
       </c>
       <c r="O661" s="2" t="s">
-        <v>1106</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="662" spans="1:15" ht="24.95" customHeight="1">
       <c r="A662" s="2" t="s">
-        <v>1107</v>
+        <v>1098</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>964</v>
+        <v>1099</v>
       </c>
       <c r="O662" s="2" t="s">
-        <v>965</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="663" spans="1:15" ht="24.95" customHeight="1">
       <c r="A663" s="2" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>1109</v>
+        <v>1102</v>
       </c>
       <c r="O663" s="2" t="s">
-        <v>1110</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="664" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O664" s="2"/>
+      <c r="A664" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B664" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="O664" s="2" t="s">
+        <v>1106</v>
+      </c>
     </row>
     <row r="665" spans="1:15" ht="24.95" customHeight="1">
       <c r="A665" s="2" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>1112</v>
+        <v>964</v>
       </c>
       <c r="O665" s="2" t="s">
-        <v>1113</v>
+        <v>965</v>
       </c>
     </row>
     <row r="666" spans="1:15" ht="24.95" customHeight="1">
       <c r="A666" s="2" t="s">
-        <v>1114</v>
+        <v>1108</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1115</v>
+        <v>1109</v>
       </c>
       <c r="O666" s="2" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="667" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A667" s="2" t="s">
-        <v>1117</v>
-      </c>
-      <c r="B667" s="2" t="s">
-        <v>1118</v>
-      </c>
-      <c r="O667" s="2" t="s">
-        <v>1119</v>
-      </c>
+      <c r="O667" s="2"/>
     </row>
     <row r="668" spans="1:15" ht="24.95" customHeight="1">
       <c r="A668" s="2" t="s">
-        <v>1120</v>
+        <v>1111</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>1121</v>
+        <v>1112</v>
       </c>
       <c r="O668" s="2" t="s">
-        <v>1122</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="669" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O669" s="2"/>
+      <c r="A669" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B669" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="O669" s="2" t="s">
+        <v>1116</v>
+      </c>
     </row>
     <row r="670" spans="1:15" ht="24.95" customHeight="1">
       <c r="A670" s="2" t="s">
-        <v>1123</v>
+        <v>1117</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="O670" s="2" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="671" spans="1:15" ht="24.95" customHeight="1">
       <c r="A671" s="2" t="s">
-        <v>1126</v>
+        <v>1120</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>599</v>
+        <v>1121</v>
       </c>
       <c r="O671" s="2" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="672" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A672" s="2" t="s">
-        <v>2462</v>
-      </c>
-      <c r="B672" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="O672" s="2" t="s">
-        <v>1128</v>
-      </c>
+      <c r="O672" s="2"/>
     </row>
     <row r="673" spans="1:15" ht="24.95" customHeight="1">
       <c r="A673" s="2" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>593</v>
+        <v>1124</v>
       </c>
       <c r="O673" s="2" t="s">
-        <v>594</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="674" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O674" s="2"/>
+      <c r="A674" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B674" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="O674" s="2" t="s">
+        <v>1127</v>
+      </c>
     </row>
     <row r="675" spans="1:15" ht="24.95" customHeight="1">
       <c r="A675" s="2" t="s">
-        <v>1130</v>
+        <v>2462</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>920</v>
+        <v>601</v>
       </c>
       <c r="O675" s="2" t="s">
-        <v>3086</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="676" spans="1:15" ht="24.95" customHeight="1">
       <c r="A676" s="2" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>1132</v>
+        <v>593</v>
       </c>
       <c r="O676" s="2" t="s">
-        <v>984</v>
+        <v>594</v>
       </c>
     </row>
     <row r="677" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A677" s="2" t="s">
-        <v>1133</v>
-      </c>
-      <c r="O677" s="2" t="s">
-        <v>1134</v>
-      </c>
+      <c r="O677" s="2"/>
     </row>
     <row r="678" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O678" s="2"/>
+      <c r="A678" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B678" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="O678" s="2" t="s">
+        <v>3086</v>
+      </c>
     </row>
     <row r="679" spans="1:15" ht="24.95" customHeight="1">
       <c r="A679" s="2" t="s">
-        <v>2525</v>
+        <v>1131</v>
+      </c>
+      <c r="B679" s="2" t="s">
+        <v>1132</v>
       </c>
       <c r="O679" s="2" t="s">
-        <v>2527</v>
+        <v>984</v>
       </c>
     </row>
     <row r="680" spans="1:15" ht="24.95" customHeight="1">
       <c r="A680" s="2" t="s">
-        <v>2526</v>
+        <v>1133</v>
       </c>
       <c r="O680" s="2" t="s">
-        <v>2528</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="681" spans="1:15" ht="24.95" customHeight="1">
@@ -18663,229 +18699,223 @@
     </row>
     <row r="682" spans="1:15" ht="24.95" customHeight="1">
       <c r="A682" s="2" t="s">
-        <v>1135</v>
-      </c>
-      <c r="B682" s="2" t="s">
-        <v>1136</v>
+        <v>2525</v>
       </c>
       <c r="O682" s="2" t="s">
-        <v>1137</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="683" spans="1:15" ht="24.95" customHeight="1">
       <c r="A683" s="2" t="s">
-        <v>1138</v>
-      </c>
-      <c r="B683" s="2" t="s">
-        <v>1139</v>
+        <v>2526</v>
       </c>
       <c r="O683" s="2" t="s">
-        <v>1140</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="684" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A684" s="2" t="s">
-        <v>1141</v>
-      </c>
-      <c r="B684" s="2" t="s">
-        <v>964</v>
-      </c>
-      <c r="O684" s="2" t="s">
-        <v>965</v>
-      </c>
+      <c r="O684" s="2"/>
     </row>
     <row r="685" spans="1:15" ht="24.95" customHeight="1">
       <c r="A685" s="2" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>1143</v>
+        <v>1136</v>
       </c>
       <c r="O685" s="2" t="s">
-        <v>1144</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="686" spans="1:15" ht="24.95" customHeight="1">
       <c r="A686" s="2" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
       <c r="O686" s="2" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="687" spans="1:15" ht="24.95" customHeight="1">
       <c r="A687" s="2" t="s">
-        <v>1148</v>
+        <v>1141</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>1821</v>
+        <v>964</v>
       </c>
       <c r="O687" s="2" t="s">
-        <v>1149</v>
+        <v>965</v>
       </c>
     </row>
     <row r="688" spans="1:15" ht="24.95" customHeight="1">
       <c r="A688" s="2" t="s">
-        <v>3027</v>
+        <v>1142</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>1151</v>
+        <v>1143</v>
       </c>
       <c r="O688" s="2" t="s">
-        <v>1152</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="689" spans="1:15" ht="24.95" customHeight="1">
       <c r="A689" s="2" t="s">
-        <v>1155</v>
+        <v>1145</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>1156</v>
+        <v>1146</v>
       </c>
       <c r="O689" s="2" t="s">
-        <v>1157</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="690" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O690" s="2"/>
+      <c r="A690" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B690" s="2" t="s">
+        <v>1821</v>
+      </c>
+      <c r="O690" s="2" t="s">
+        <v>1149</v>
+      </c>
     </row>
     <row r="691" spans="1:15" ht="24.95" customHeight="1">
       <c r="A691" s="2" t="s">
-        <v>3052</v>
+        <v>3027</v>
+      </c>
+      <c r="B691" s="2" t="s">
+        <v>1151</v>
       </c>
       <c r="O691" s="2" t="s">
-        <v>3057</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="692" spans="1:15" ht="24.95" customHeight="1">
       <c r="A692" s="2" t="s">
-        <v>3053</v>
+        <v>1155</v>
+      </c>
+      <c r="B692" s="2" t="s">
+        <v>1156</v>
       </c>
       <c r="O692" s="2" t="s">
-        <v>3058</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="693" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A693" s="2" t="s">
-        <v>3067</v>
-      </c>
-      <c r="O693" s="2" t="s">
-        <v>3068</v>
-      </c>
+      <c r="O693" s="2"/>
     </row>
     <row r="694" spans="1:15" ht="24.95" customHeight="1">
       <c r="A694" s="2" t="s">
-        <v>3054</v>
+        <v>3052</v>
       </c>
       <c r="O694" s="2" t="s">
-        <v>3059</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="695" spans="1:15" ht="24.95" customHeight="1">
       <c r="A695" s="2" t="s">
-        <v>3055</v>
+        <v>3053</v>
       </c>
       <c r="O695" s="2" t="s">
-        <v>3060</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="696" spans="1:15" ht="24.95" customHeight="1">
       <c r="A696" s="2" t="s">
-        <v>3056</v>
+        <v>3067</v>
       </c>
       <c r="O696" s="2" t="s">
-        <v>3061</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="697" spans="1:15" ht="24.95" customHeight="1">
       <c r="A697" s="2" t="s">
-        <v>3065</v>
+        <v>3054</v>
       </c>
       <c r="O697" s="2" t="s">
-        <v>3087</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="698" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O698" s="2"/>
+      <c r="A698" s="2" t="s">
+        <v>3055</v>
+      </c>
+      <c r="O698" s="2" t="s">
+        <v>3060</v>
+      </c>
     </row>
     <row r="699" spans="1:15" ht="24.95" customHeight="1">
       <c r="A699" s="2" t="s">
+        <v>3056</v>
+      </c>
+      <c r="O699" s="2" t="s">
+        <v>3061</v>
+      </c>
+    </row>
+    <row r="700" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A700" s="2" t="s">
+        <v>3065</v>
+      </c>
+      <c r="O700" s="2" t="s">
+        <v>3087</v>
+      </c>
+    </row>
+    <row r="701" spans="1:15" ht="24.95" customHeight="1">
+      <c r="O701" s="2"/>
+    </row>
+    <row r="702" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A702" s="2" t="s">
         <v>1158</v>
       </c>
-      <c r="B699" s="2" t="s">
+      <c r="B702" s="2" t="s">
         <v>1761</v>
       </c>
-      <c r="O699" s="2" t="s">
+      <c r="O702" s="2" t="s">
         <v>1159</v>
       </c>
     </row>
-    <row r="700" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O700" s="2"/>
-    </row>
-    <row r="701" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A701" s="2" t="s">
-        <v>1160</v>
-      </c>
-      <c r="B701" s="2" t="s">
-        <v>1161</v>
-      </c>
-      <c r="O701" s="2" t="s">
-        <v>1162</v>
-      </c>
-    </row>
-    <row r="702" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O702" s="2"/>
-    </row>
     <row r="703" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A703" s="2" t="s">
-        <v>3174</v>
-      </c>
-      <c r="O703" s="2" t="s">
-        <v>3175</v>
-      </c>
+      <c r="O703" s="2"/>
     </row>
     <row r="704" spans="1:15" ht="24.95" customHeight="1">
       <c r="A704" s="2" t="s">
-        <v>2989</v>
+        <v>1160</v>
+      </c>
+      <c r="B704" s="2" t="s">
+        <v>1161</v>
       </c>
       <c r="O704" s="2" t="s">
-        <v>2991</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="705" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A705" s="2" t="s">
-        <v>2990</v>
-      </c>
-      <c r="O705" s="2" t="s">
-        <v>2992</v>
-      </c>
+      <c r="O705" s="2"/>
     </row>
     <row r="706" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O706" s="2"/>
+      <c r="A706" s="2" t="s">
+        <v>3174</v>
+      </c>
+      <c r="O706" s="2" t="s">
+        <v>3175</v>
+      </c>
     </row>
     <row r="707" spans="1:15" ht="24.95" customHeight="1">
       <c r="A707" s="2" t="s">
-        <v>1163</v>
-      </c>
-      <c r="B707" s="2" t="s">
-        <v>1164</v>
+        <v>2989</v>
       </c>
       <c r="O707" s="2" t="s">
-        <v>1165</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="708" spans="1:15" ht="24.95" customHeight="1">
       <c r="A708" s="2" t="s">
-        <v>1166</v>
-      </c>
-      <c r="B708" s="2" t="s">
-        <v>1167</v>
+        <v>2990</v>
       </c>
       <c r="O708" s="2" t="s">
-        <v>1168</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="709" spans="1:15" ht="24.95" customHeight="1">
@@ -18893,118 +18923,118 @@
     </row>
     <row r="710" spans="1:15" ht="24.95" customHeight="1">
       <c r="A710" s="2" t="s">
-        <v>1169</v>
+        <v>1163</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>1170</v>
+        <v>1164</v>
       </c>
       <c r="O710" s="2" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="711" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O711" s="2"/>
+      <c r="A711" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B711" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="O711" s="2" t="s">
+        <v>1168</v>
+      </c>
     </row>
     <row r="712" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A712" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="O712" s="2" t="s">
-        <v>1173</v>
-      </c>
+      <c r="O712" s="2"/>
     </row>
     <row r="713" spans="1:15" ht="24.95" customHeight="1">
       <c r="A713" s="2" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
       <c r="O713" s="2" t="s">
-        <v>1176</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="714" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A714" s="2" t="s">
-        <v>1177</v>
-      </c>
-      <c r="B714" s="2" t="s">
-        <v>1178</v>
-      </c>
-      <c r="O714" s="2" t="s">
-        <v>1179</v>
-      </c>
+      <c r="O714" s="2"/>
     </row>
     <row r="715" spans="1:15" ht="24.95" customHeight="1">
       <c r="A715" s="2" t="s">
-        <v>1180</v>
-      </c>
-      <c r="B715" s="2" t="s">
-        <v>1181</v>
+        <v>1172</v>
       </c>
       <c r="O715" s="2" t="s">
-        <v>1182</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="716" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O716" s="2"/>
+      <c r="A716" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B716" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="O716" s="2" t="s">
+        <v>1176</v>
+      </c>
     </row>
     <row r="717" spans="1:15" ht="24.95" customHeight="1">
       <c r="A717" s="2" t="s">
-        <v>1183</v>
+        <v>1177</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
       <c r="O717" s="2" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="718" spans="1:15" ht="24.95" customHeight="1">
       <c r="A718" s="2" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="O718" s="2" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="719" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A719" s="2" t="s">
-        <v>1189</v>
-      </c>
-      <c r="B719" s="2" t="s">
-        <v>1190</v>
-      </c>
-      <c r="O719" s="2" t="s">
-        <v>1191</v>
-      </c>
+      <c r="O719" s="2"/>
     </row>
     <row r="720" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O720" s="2"/>
+      <c r="A720" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B720" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="O720" s="2" t="s">
+        <v>1185</v>
+      </c>
     </row>
     <row r="721" spans="1:15" ht="24.95" customHeight="1">
       <c r="A721" s="2" t="s">
-        <v>1192</v>
+        <v>1186</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="O721" s="2" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="722" spans="1:15" ht="24.95" customHeight="1">
       <c r="A722" s="2" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
       <c r="O722" s="2" t="s">
-        <v>1197</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="723" spans="1:15" ht="24.95" customHeight="1">
@@ -19012,71 +19042,71 @@
     </row>
     <row r="724" spans="1:15" ht="24.95" customHeight="1">
       <c r="A724" s="2" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="O724" s="2" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="725" spans="1:15" ht="24.95" customHeight="1">
       <c r="A725" s="2" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="O725" s="2" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="726" spans="1:15" ht="24.95" customHeight="1">
       <c r="O726" s="2"/>
     </row>
-    <row r="727" spans="1:15" ht="33">
+    <row r="727" spans="1:15" ht="24.95" customHeight="1">
       <c r="A727" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B727" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="O727" s="2" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="728" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A728" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B728" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="O728" s="2" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="729" spans="1:15" ht="24.95" customHeight="1">
+      <c r="O729" s="2"/>
+    </row>
+    <row r="730" spans="1:15" ht="33">
+      <c r="A730" s="2" t="s">
         <v>2966</v>
       </c>
-      <c r="O727" s="3" t="s">
+      <c r="O730" s="3" t="s">
         <v>2967</v>
       </c>
     </row>
-    <row r="728" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O728" s="2"/>
-    </row>
-    <row r="729" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A729" s="2" t="s">
-        <v>1204</v>
-      </c>
-      <c r="O729" s="2" t="s">
-        <v>1773</v>
-      </c>
-    </row>
-    <row r="730" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O730" s="2"/>
-    </row>
     <row r="731" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A731" s="2" t="s">
-        <v>1205</v>
-      </c>
-      <c r="B731" s="2" t="s">
-        <v>1206</v>
-      </c>
-      <c r="O731" s="2" t="s">
-        <v>1207</v>
-      </c>
+      <c r="O731" s="2"/>
     </row>
     <row r="732" spans="1:15" ht="24.95" customHeight="1">
       <c r="A732" s="2" t="s">
-        <v>1208</v>
-      </c>
-      <c r="B732" s="2" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="O732" s="2" t="s">
-        <v>1210</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="733" spans="1:15" ht="24.95" customHeight="1">
@@ -19084,38 +19114,38 @@
     </row>
     <row r="734" spans="1:15" ht="24.95" customHeight="1">
       <c r="A734" s="2" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="O734" s="2" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="735" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O735" s="2"/>
+      <c r="A735" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B735" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="O735" s="2" t="s">
+        <v>1210</v>
+      </c>
     </row>
     <row r="736" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A736" s="2" t="s">
-        <v>1214</v>
-      </c>
-      <c r="B736" s="2" t="s">
-        <v>1215</v>
-      </c>
-      <c r="O736" s="2" t="s">
-        <v>1216</v>
-      </c>
+      <c r="O736" s="2"/>
     </row>
     <row r="737" spans="1:15" ht="24.95" customHeight="1">
       <c r="A737" s="2" t="s">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="O737" s="2" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="738" spans="1:15" ht="24.95" customHeight="1">
@@ -19123,57 +19153,60 @@
     </row>
     <row r="739" spans="1:15" ht="24.95" customHeight="1">
       <c r="A739" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B739" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="O739" s="2" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="740" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A740" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B740" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="O740" s="2" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="741" spans="1:15" ht="24.95" customHeight="1">
+      <c r="O741" s="2"/>
+    </row>
+    <row r="742" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A742" s="2" t="s">
         <v>1220</v>
       </c>
-      <c r="B739" s="2" t="s">
+      <c r="B742" s="2" t="s">
         <v>1763</v>
       </c>
-      <c r="O739" s="2" t="s">
+      <c r="O742" s="2" t="s">
         <v>1221</v>
       </c>
     </row>
-    <row r="740" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O740" s="2"/>
-    </row>
-    <row r="741" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A741" s="2" t="s">
+    <row r="743" spans="1:15" ht="24.95" customHeight="1">
+      <c r="O743" s="2"/>
+    </row>
+    <row r="744" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A744" s="2" t="s">
         <v>3178</v>
       </c>
-      <c r="O741" s="2" t="s">
+      <c r="O744" s="2" t="s">
         <v>3180</v>
       </c>
     </row>
-    <row r="742" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O742" s="2"/>
-    </row>
-    <row r="743" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A743" s="2" t="s">
-        <v>1222</v>
-      </c>
-      <c r="O743" s="2" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="744" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O744" s="2"/>
-    </row>
     <row r="745" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A745" s="2" t="s">
-        <v>3176</v>
-      </c>
-      <c r="O745" s="2" t="s">
-        <v>3177</v>
-      </c>
+      <c r="O745" s="2"/>
     </row>
     <row r="746" spans="1:15" ht="24.95" customHeight="1">
       <c r="A746" s="2" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B746" s="2" t="s">
-        <v>1762</v>
+        <v>1222</v>
       </c>
       <c r="O746" s="2" t="s">
-        <v>1224</v>
+        <v>823</v>
       </c>
     </row>
     <row r="747" spans="1:15" ht="24.95" customHeight="1">
@@ -19181,24 +19214,21 @@
     </row>
     <row r="748" spans="1:15" ht="24.95" customHeight="1">
       <c r="A748" s="2" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B748" s="2" t="s">
-        <v>1226</v>
+        <v>3176</v>
       </c>
       <c r="O748" s="2" t="s">
-        <v>1227</v>
+        <v>3177</v>
       </c>
     </row>
     <row r="749" spans="1:15" ht="24.95" customHeight="1">
       <c r="A749" s="2" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="B749" s="2" t="s">
-        <v>1229</v>
+        <v>1762</v>
       </c>
       <c r="O749" s="2" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="750" spans="1:15" ht="24.95" customHeight="1">
@@ -19206,24 +19236,24 @@
     </row>
     <row r="751" spans="1:15" ht="24.95" customHeight="1">
       <c r="A751" s="2" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="B751" s="2" t="s">
-        <v>1232</v>
+        <v>1226</v>
       </c>
       <c r="O751" s="2" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="752" spans="1:15" ht="24.95" customHeight="1">
       <c r="A752" s="2" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="B752" s="2" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="O752" s="2" t="s">
-        <v>1236</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="753" spans="1:15" ht="24.95" customHeight="1">
@@ -19231,75 +19261,91 @@
     </row>
     <row r="754" spans="1:15" ht="24.95" customHeight="1">
       <c r="A754" s="2" t="s">
-        <v>1237</v>
+        <v>1231</v>
       </c>
       <c r="B754" s="2" t="s">
-        <v>1238</v>
+        <v>1232</v>
       </c>
       <c r="O754" s="2" t="s">
-        <v>1239</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="755" spans="1:15" ht="24.95" customHeight="1">
       <c r="A755" s="2" t="s">
-        <v>1240</v>
+        <v>1234</v>
       </c>
       <c r="B755" s="2" t="s">
-        <v>1241</v>
+        <v>1235</v>
       </c>
       <c r="O755" s="2" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="756" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A756" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="B756" s="2" t="s">
-        <v>1244</v>
-      </c>
-      <c r="O756" s="2" t="s">
-        <v>1245</v>
-      </c>
+      <c r="O756" s="2"/>
     </row>
     <row r="757" spans="1:15" ht="24.95" customHeight="1">
       <c r="A757" s="2" t="s">
-        <v>1246</v>
+        <v>1237</v>
       </c>
       <c r="B757" s="2" t="s">
-        <v>1247</v>
+        <v>1238</v>
       </c>
       <c r="O757" s="2" t="s">
-        <v>1248</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="758" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O758" s="2"/>
+      <c r="A758" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B758" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="O758" s="2" t="s">
+        <v>1242</v>
+      </c>
     </row>
     <row r="759" spans="1:15" ht="24.95" customHeight="1">
       <c r="A759" s="2" t="s">
-        <v>1600</v>
+        <v>1243</v>
+      </c>
+      <c r="B759" s="2" t="s">
+        <v>1244</v>
       </c>
       <c r="O759" s="2" t="s">
-        <v>1602</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="760" spans="1:15" ht="24.95" customHeight="1">
       <c r="A760" s="2" t="s">
-        <v>1601</v>
-      </c>
-      <c r="O760" s="3" t="s">
-        <v>1603</v>
+        <v>1246</v>
+      </c>
+      <c r="B760" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="O760" s="2" t="s">
+        <v>1248</v>
       </c>
     </row>
     <row r="761" spans="1:15" ht="24.95" customHeight="1">
       <c r="O761" s="2"/>
     </row>
     <row r="762" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O762" s="2"/>
+      <c r="A762" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="O762" s="2" t="s">
+        <v>1602</v>
+      </c>
     </row>
     <row r="763" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O763" s="2"/>
+      <c r="A763" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="O763" s="3" t="s">
+        <v>1603</v>
+      </c>
     </row>
     <row r="764" spans="1:15" ht="24.95" customHeight="1">
       <c r="O764" s="2"/>
@@ -19583,15 +19629,15 @@
     <row r="857" spans="15:15" ht="24.95" customHeight="1">
       <c r="O857" s="2"/>
     </row>
+    <row r="858" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O858" s="2"/>
+    </row>
     <row r="859" spans="15:15" ht="24.95" customHeight="1">
       <c r="O859" s="2"/>
     </row>
     <row r="860" spans="15:15" ht="24.95" customHeight="1">
       <c r="O860" s="2"/>
     </row>
-    <row r="861" spans="15:15" ht="24.95" customHeight="1">
-      <c r="O861" s="2"/>
-    </row>
     <row r="862" spans="15:15" ht="24.95" customHeight="1">
       <c r="O862" s="2"/>
     </row>
@@ -20763,20 +20809,7 @@
       <c r="O1251" s="2"/>
     </row>
     <row r="1252" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A1252" s="5"/>
-      <c r="B1252" s="5"/>
-      <c r="D1252" s="5"/>
-      <c r="E1252" s="5"/>
-      <c r="F1252" s="5"/>
-      <c r="G1252" s="5"/>
-      <c r="H1252" s="5"/>
-      <c r="I1252" s="5"/>
-      <c r="J1252" s="5"/>
-      <c r="K1252" s="5"/>
-      <c r="L1252" s="5"/>
-      <c r="M1252" s="5"/>
-      <c r="N1252" s="5"/>
-      <c r="O1252" s="6"/>
+      <c r="O1252" s="2"/>
     </row>
     <row r="1253" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1253" s="2"/>
@@ -20785,7 +20818,20 @@
       <c r="O1254" s="2"/>
     </row>
     <row r="1255" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O1255" s="2"/>
+      <c r="A1255" s="5"/>
+      <c r="B1255" s="5"/>
+      <c r="D1255" s="5"/>
+      <c r="E1255" s="5"/>
+      <c r="F1255" s="5"/>
+      <c r="G1255" s="5"/>
+      <c r="H1255" s="5"/>
+      <c r="I1255" s="5"/>
+      <c r="J1255" s="5"/>
+      <c r="K1255" s="5"/>
+      <c r="L1255" s="5"/>
+      <c r="M1255" s="5"/>
+      <c r="N1255" s="5"/>
+      <c r="O1255" s="6"/>
     </row>
     <row r="1256" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1256" s="2"/>
@@ -22293,8 +22339,17 @@
     <row r="1757" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1757" s="2"/>
     </row>
+    <row r="1758" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1758" s="2"/>
+    </row>
+    <row r="1759" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1759" s="2"/>
+    </row>
+    <row r="1760" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1760" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="O1:O1460" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="O1:O1463" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -25002,18 +25057,18 @@
     </row>
     <row r="95" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A95" s="2" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
     </row>
     <row r="96" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A96" s="2" t="s">
+        <v>3249</v>
+      </c>
+      <c r="O96" s="2" t="s">
         <v>3250</v>
-      </c>
-      <c r="O96" s="2" t="s">
-        <v>3251</v>
       </c>
     </row>
   </sheetData>
@@ -25024,7 +25079,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:Q443"/>
+  <dimension ref="A1:Q447"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="27.875" style="7" customWidth="1"/>
@@ -25838,2224 +25893,2218 @@
     </row>
     <row r="113" spans="1:15">
       <c r="A113" s="7" t="s">
-        <v>1692</v>
+        <v>3252</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>1692</v>
+        <v>3252</v>
       </c>
       <c r="O113" s="7" t="s">
-        <v>1697</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="114" spans="1:15">
       <c r="A114" s="7" t="s">
-        <v>1694</v>
-      </c>
-      <c r="O114" s="7" t="s">
-        <v>2651</v>
+        <v>3254</v>
       </c>
     </row>
     <row r="115" spans="1:15">
       <c r="A115" s="7" t="s">
-        <v>1696</v>
-      </c>
-      <c r="O115" s="7" t="s">
-        <v>1698</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="117" spans="1:15">
       <c r="A117" s="7" t="s">
-        <v>1960</v>
+        <v>1692</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>1960</v>
+        <v>1692</v>
       </c>
       <c r="O117" s="7" t="s">
-        <v>1961</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="118" spans="1:15">
       <c r="A118" s="7" t="s">
-        <v>1962</v>
+        <v>1694</v>
       </c>
       <c r="O118" s="7" t="s">
-        <v>1963</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="119" spans="1:15">
       <c r="A119" s="7" t="s">
-        <v>1964</v>
+        <v>1696</v>
       </c>
       <c r="O119" s="7" t="s">
-        <v>1965</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="121" spans="1:15">
       <c r="A121" s="7" t="s">
-        <v>1966</v>
+        <v>1960</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>1966</v>
+        <v>1960</v>
       </c>
       <c r="O121" s="7" t="s">
-        <v>1967</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="122" spans="1:15">
       <c r="A122" s="7" t="s">
-        <v>1968</v>
+        <v>1962</v>
       </c>
       <c r="O122" s="7" t="s">
-        <v>2652</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="123" spans="1:15">
       <c r="A123" s="7" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="O123" s="7" t="s">
-        <v>1970</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="125" spans="1:15">
       <c r="A125" s="7" t="s">
-        <v>1971</v>
+        <v>1966</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>1971</v>
+        <v>1966</v>
       </c>
       <c r="O125" s="7" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="126" spans="1:15">
       <c r="A126" s="7" t="s">
-        <v>1973</v>
+        <v>1968</v>
       </c>
       <c r="O126" s="7" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="127" spans="1:15">
       <c r="A127" s="7" t="s">
-        <v>1974</v>
+        <v>1969</v>
       </c>
       <c r="O127" s="7" t="s">
-        <v>2654</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="129" spans="1:15">
       <c r="A129" s="7" t="s">
-        <v>1975</v>
+        <v>1971</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>1975</v>
+        <v>1971</v>
       </c>
       <c r="O129" s="7" t="s">
-        <v>1976</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="130" spans="1:15">
       <c r="A130" s="7" t="s">
-        <v>1977</v>
+        <v>1973</v>
       </c>
       <c r="O130" s="7" t="s">
-        <v>2655</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="131" spans="1:15">
       <c r="A131" s="7" t="s">
-        <v>1978</v>
+        <v>1974</v>
       </c>
       <c r="O131" s="7" t="s">
-        <v>2656</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="133" spans="1:15">
       <c r="A133" s="7" t="s">
-        <v>1979</v>
+        <v>1975</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>1979</v>
+        <v>1975</v>
       </c>
       <c r="O133" s="7" t="s">
-        <v>1980</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="134" spans="1:15">
       <c r="A134" s="7" t="s">
-        <v>1981</v>
+        <v>1977</v>
       </c>
       <c r="O134" s="7" t="s">
-        <v>2657</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="135" spans="1:15">
       <c r="A135" s="7" t="s">
-        <v>1982</v>
+        <v>1978</v>
       </c>
       <c r="O135" s="7" t="s">
-        <v>2658</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="137" spans="1:15">
       <c r="A137" s="7" t="s">
-        <v>1983</v>
+        <v>1979</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>1983</v>
+        <v>1979</v>
       </c>
       <c r="O137" s="7" t="s">
-        <v>2659</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="138" spans="1:15">
       <c r="A138" s="7" t="s">
-        <v>1984</v>
+        <v>1981</v>
       </c>
       <c r="O138" s="7" t="s">
-        <v>1985</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="139" spans="1:15">
       <c r="A139" s="7" t="s">
-        <v>1986</v>
+        <v>1982</v>
       </c>
       <c r="O139" s="7" t="s">
-        <v>1985</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="141" spans="1:15">
       <c r="A141" s="7" t="s">
-        <v>2889</v>
+        <v>1983</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>2888</v>
+        <v>1983</v>
       </c>
       <c r="O141" s="7" t="s">
-        <v>2887</v>
+        <v>2659</v>
       </c>
     </row>
     <row r="142" spans="1:15">
       <c r="A142" s="7" t="s">
-        <v>2890</v>
+        <v>1984</v>
       </c>
       <c r="O142" s="7" t="s">
-        <v>2894</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="143" spans="1:15">
       <c r="A143" s="7" t="s">
-        <v>2891</v>
+        <v>1986</v>
       </c>
       <c r="O143" s="7" t="s">
-        <v>2895</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="145" spans="1:15">
       <c r="A145" s="7" t="s">
-        <v>3195</v>
+        <v>2889</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>3194</v>
+        <v>2888</v>
       </c>
       <c r="O145" s="7" t="s">
-        <v>3196</v>
+        <v>2887</v>
       </c>
     </row>
     <row r="146" spans="1:15">
       <c r="A146" s="7" t="s">
-        <v>3197</v>
+        <v>2890</v>
       </c>
       <c r="O146" s="7" t="s">
-        <v>3207</v>
+        <v>2894</v>
       </c>
     </row>
     <row r="147" spans="1:15">
       <c r="A147" s="7" t="s">
-        <v>3198</v>
+        <v>2891</v>
       </c>
       <c r="O147" s="7" t="s">
-        <v>3210</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="149" spans="1:15">
       <c r="A149" s="7" t="s">
-        <v>2473</v>
+        <v>3195</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>2472</v>
+        <v>3194</v>
       </c>
       <c r="O149" s="7" t="s">
-        <v>2476</v>
+        <v>3196</v>
       </c>
     </row>
     <row r="150" spans="1:15">
       <c r="A150" s="7" t="s">
-        <v>2474</v>
+        <v>3197</v>
       </c>
       <c r="O150" s="7" t="s">
-        <v>2477</v>
+        <v>3207</v>
       </c>
     </row>
     <row r="151" spans="1:15">
       <c r="A151" s="7" t="s">
-        <v>2475</v>
+        <v>3198</v>
       </c>
       <c r="O151" s="7" t="s">
-        <v>2660</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="153" spans="1:15">
       <c r="A153" s="7" t="s">
-        <v>1987</v>
+        <v>2473</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>1987</v>
+        <v>2472</v>
       </c>
       <c r="O153" s="7" t="s">
-        <v>1988</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="154" spans="1:15">
       <c r="A154" s="7" t="s">
-        <v>1989</v>
+        <v>2474</v>
       </c>
       <c r="O154" s="7" t="s">
-        <v>2661</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="155" spans="1:15">
       <c r="A155" s="7" t="s">
-        <v>1990</v>
+        <v>2475</v>
       </c>
       <c r="O155" s="7" t="s">
-        <v>1991</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="157" spans="1:15">
       <c r="A157" s="7" t="s">
-        <v>1992</v>
+        <v>1987</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>1992</v>
+        <v>1987</v>
       </c>
       <c r="O157" s="7" t="s">
-        <v>1993</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="158" spans="1:15">
       <c r="A158" s="7" t="s">
-        <v>1994</v>
+        <v>1989</v>
       </c>
       <c r="O158" s="7" t="s">
-        <v>1995</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="159" spans="1:15">
       <c r="A159" s="7" t="s">
-        <v>1996</v>
+        <v>1990</v>
       </c>
       <c r="O159" s="7" t="s">
-        <v>1995</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="161" spans="1:15">
       <c r="A161" s="7" t="s">
-        <v>1997</v>
+        <v>1992</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>1702</v>
+        <v>1992</v>
       </c>
       <c r="O161" s="7" t="s">
-        <v>1998</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="162" spans="1:15">
       <c r="A162" s="7" t="s">
-        <v>1999</v>
+        <v>1994</v>
       </c>
       <c r="O162" s="7" t="s">
-        <v>2000</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="163" spans="1:15">
       <c r="A163" s="7" t="s">
-        <v>2001</v>
+        <v>1996</v>
       </c>
       <c r="O163" s="7" t="s">
-        <v>2002</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="165" spans="1:15">
       <c r="A165" s="7" t="s">
-        <v>2003</v>
+        <v>1997</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="O165" s="7" t="s">
-        <v>2004</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="166" spans="1:15">
       <c r="A166" s="7" t="s">
-        <v>2005</v>
+        <v>1999</v>
       </c>
       <c r="O166" s="7" t="s">
-        <v>2006</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="167" spans="1:15">
       <c r="A167" s="7" t="s">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="O167" s="7" t="s">
-        <v>2006</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="169" spans="1:15">
       <c r="A169" s="7" t="s">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>2008</v>
+        <v>1703</v>
       </c>
       <c r="O169" s="7" t="s">
-        <v>2662</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="170" spans="1:15">
       <c r="A170" s="7" t="s">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="O170" s="7" t="s">
-        <v>2663</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="171" spans="1:15">
       <c r="A171" s="7" t="s">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="O171" s="7" t="s">
-        <v>2663</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="173" spans="1:15">
       <c r="A173" s="7" t="s">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="O173" s="7" t="s">
-        <v>2664</v>
+        <v>2662</v>
       </c>
     </row>
     <row r="174" spans="1:15">
       <c r="A174" s="7" t="s">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="O174" s="7" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="175" spans="1:15">
       <c r="A175" s="7" t="s">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="O175" s="7" t="s">
-        <v>2666</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="177" spans="1:15">
       <c r="A177" s="7" t="s">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="O177" s="7" t="s">
-        <v>2015</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="178" spans="1:15">
       <c r="A178" s="7" t="s">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="O178" s="7" t="s">
-        <v>2017</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="179" spans="1:15">
       <c r="A179" s="7" t="s">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="O179" s="7" t="s">
-        <v>2667</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="181" spans="1:15">
       <c r="A181" s="7" t="s">
-        <v>3185</v>
+        <v>2014</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>3181</v>
+        <v>2014</v>
       </c>
       <c r="O181" s="7" t="s">
-        <v>3182</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="182" spans="1:15">
       <c r="A182" s="7" t="s">
-        <v>3184</v>
+        <v>2016</v>
       </c>
       <c r="O182" s="7" t="s">
-        <v>3187</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="183" spans="1:15">
       <c r="A183" s="7" t="s">
-        <v>3183</v>
+        <v>2018</v>
       </c>
       <c r="O183" s="7" t="s">
-        <v>3186</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="185" spans="1:15">
       <c r="A185" s="7" t="s">
-        <v>2019</v>
+        <v>3185</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>2019</v>
+        <v>3181</v>
       </c>
       <c r="O185" s="7" t="s">
-        <v>2668</v>
+        <v>3182</v>
       </c>
     </row>
     <row r="186" spans="1:15">
       <c r="A186" s="7" t="s">
-        <v>2020</v>
+        <v>3184</v>
       </c>
       <c r="O186" s="7" t="s">
-        <v>2669</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="187" spans="1:15">
       <c r="A187" s="7" t="s">
-        <v>2021</v>
+        <v>3183</v>
       </c>
       <c r="O187" s="7" t="s">
-        <v>2022</v>
+        <v>3186</v>
       </c>
     </row>
     <row r="189" spans="1:15">
       <c r="A189" s="7" t="s">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="O189" s="7" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="190" spans="1:15">
       <c r="A190" s="7" t="s">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="O190" s="7" t="s">
-        <v>2671</v>
+        <v>2669</v>
       </c>
     </row>
     <row r="191" spans="1:15">
       <c r="A191" s="7" t="s">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="O191" s="7" t="s">
-        <v>2026</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="193" spans="1:15">
       <c r="A193" s="7" t="s">
-        <v>2993</v>
+        <v>2023</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>2993</v>
+        <v>2023</v>
       </c>
       <c r="O193" s="7" t="s">
-        <v>3019</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="194" spans="1:15">
       <c r="A194" s="7" t="s">
-        <v>2995</v>
+        <v>2024</v>
       </c>
       <c r="O194" s="7" t="s">
-        <v>3020</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="195" spans="1:15">
       <c r="A195" s="7" t="s">
-        <v>2994</v>
+        <v>2025</v>
       </c>
       <c r="O195" s="7" t="s">
-        <v>2996</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="197" spans="1:15">
       <c r="A197" s="7" t="s">
-        <v>2027</v>
+        <v>2993</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>2027</v>
+        <v>2993</v>
       </c>
       <c r="O197" s="7" t="s">
-        <v>2672</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="198" spans="1:15">
       <c r="A198" s="7" t="s">
-        <v>2028</v>
+        <v>2995</v>
       </c>
       <c r="O198" s="7" t="s">
-        <v>2673</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="199" spans="1:15">
       <c r="A199" s="7" t="s">
-        <v>2029</v>
+        <v>2994</v>
       </c>
       <c r="O199" s="7" t="s">
-        <v>2674</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="201" spans="1:15">
       <c r="A201" s="7" t="s">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="O201" s="7" t="s">
-        <v>2031</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="202" spans="1:15">
       <c r="A202" s="7" t="s">
-        <v>2032</v>
+        <v>2028</v>
       </c>
       <c r="O202" s="7" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="203" spans="1:15">
       <c r="A203" s="7" t="s">
-        <v>2033</v>
+        <v>2029</v>
       </c>
       <c r="O203" s="7" t="s">
-        <v>2676</v>
+        <v>2674</v>
       </c>
     </row>
     <row r="205" spans="1:15">
       <c r="A205" s="7" t="s">
-        <v>2034</v>
+        <v>2030</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>2034</v>
+        <v>2030</v>
       </c>
       <c r="O205" s="7" t="s">
-        <v>2035</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="206" spans="1:15">
       <c r="A206" s="7" t="s">
-        <v>2036</v>
+        <v>2032</v>
       </c>
       <c r="O206" s="7" t="s">
-        <v>2037</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="207" spans="1:15">
       <c r="A207" s="7" t="s">
-        <v>2038</v>
+        <v>2033</v>
       </c>
       <c r="O207" s="7" t="s">
-        <v>2677</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="209" spans="1:15">
       <c r="A209" s="7" t="s">
-        <v>2039</v>
+        <v>2034</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>2039</v>
+        <v>2034</v>
       </c>
       <c r="O209" s="7" t="s">
-        <v>2040</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="210" spans="1:15">
       <c r="A210" s="7" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
       <c r="O210" s="7" t="s">
-        <v>2678</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="211" spans="1:15">
       <c r="A211" s="7" t="s">
-        <v>2042</v>
+        <v>2038</v>
       </c>
       <c r="O211" s="7" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="213" spans="1:15">
       <c r="A213" s="7" t="s">
-        <v>2043</v>
+        <v>2039</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>2043</v>
+        <v>2039</v>
       </c>
       <c r="O213" s="7" t="s">
-        <v>2044</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="214" spans="1:15">
       <c r="A214" s="7" t="s">
-        <v>2045</v>
+        <v>2041</v>
       </c>
       <c r="O214" s="7" t="s">
-        <v>2680</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="215" spans="1:15">
       <c r="A215" s="7" t="s">
-        <v>2046</v>
+        <v>2042</v>
       </c>
       <c r="O215" s="7" t="s">
-        <v>2047</v>
+        <v>2679</v>
       </c>
     </row>
     <row r="217" spans="1:15">
       <c r="A217" s="7" t="s">
-        <v>2048</v>
+        <v>2043</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>2048</v>
+        <v>2043</v>
       </c>
       <c r="O217" s="7" t="s">
-        <v>2049</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="218" spans="1:15">
       <c r="A218" s="7" t="s">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="O218" s="7" t="s">
-        <v>2051</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="219" spans="1:15">
       <c r="A219" s="7" t="s">
-        <v>2052</v>
+        <v>2046</v>
       </c>
       <c r="O219" s="7" t="s">
-        <v>2053</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="221" spans="1:15">
       <c r="A221" s="7" t="s">
-        <v>2054</v>
+        <v>2048</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>2054</v>
+        <v>2048</v>
       </c>
       <c r="O221" s="7" t="s">
-        <v>2055</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="222" spans="1:15">
       <c r="A222" s="7" t="s">
-        <v>2056</v>
+        <v>2050</v>
       </c>
       <c r="O222" s="7" t="s">
-        <v>2681</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="223" spans="1:15">
       <c r="A223" s="7" t="s">
-        <v>2057</v>
+        <v>2052</v>
       </c>
       <c r="O223" s="7" t="s">
-        <v>2682</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="225" spans="1:15">
       <c r="A225" s="7" t="s">
-        <v>2058</v>
+        <v>2054</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>2058</v>
+        <v>2054</v>
       </c>
       <c r="O225" s="7" t="s">
-        <v>2683</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="226" spans="1:15">
       <c r="A226" s="7" t="s">
-        <v>2059</v>
+        <v>2056</v>
       </c>
       <c r="O226" s="7" t="s">
-        <v>2684</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="227" spans="1:15">
       <c r="A227" s="7" t="s">
-        <v>2060</v>
+        <v>2057</v>
       </c>
       <c r="O227" s="7" t="s">
-        <v>2061</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="229" spans="1:15">
       <c r="A229" s="7" t="s">
-        <v>2062</v>
+        <v>2058</v>
       </c>
       <c r="B229" s="7" t="s">
-        <v>2062</v>
+        <v>2058</v>
       </c>
       <c r="O229" s="7" t="s">
-        <v>2063</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="230" spans="1:15">
       <c r="A230" s="7" t="s">
-        <v>2064</v>
+        <v>2059</v>
       </c>
       <c r="O230" s="7" t="s">
-        <v>2685</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="231" spans="1:15">
       <c r="A231" s="7" t="s">
-        <v>2065</v>
+        <v>2060</v>
       </c>
       <c r="O231" s="7" t="s">
-        <v>2686</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="233" spans="1:15">
       <c r="A233" s="7" t="s">
-        <v>2066</v>
+        <v>2062</v>
       </c>
       <c r="B233" s="7" t="s">
-        <v>2066</v>
+        <v>2062</v>
       </c>
       <c r="O233" s="7" t="s">
-        <v>2067</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="234" spans="1:15">
       <c r="A234" s="7" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
       <c r="O234" s="7" t="s">
-        <v>2687</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="235" spans="1:15">
       <c r="A235" s="7" t="s">
-        <v>2069</v>
+        <v>2065</v>
       </c>
       <c r="O235" s="7" t="s">
-        <v>2070</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="237" spans="1:15">
       <c r="A237" s="7" t="s">
-        <v>2071</v>
+        <v>2066</v>
       </c>
       <c r="B237" s="7" t="s">
-        <v>2071</v>
+        <v>2066</v>
       </c>
       <c r="O237" s="7" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="238" spans="1:15">
       <c r="A238" s="7" t="s">
-        <v>2073</v>
+        <v>2068</v>
       </c>
       <c r="O238" s="7" t="s">
-        <v>2688</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="239" spans="1:15">
       <c r="A239" s="7" t="s">
-        <v>2074</v>
+        <v>2069</v>
       </c>
       <c r="O239" s="7" t="s">
-        <v>2688</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="241" spans="1:15">
       <c r="A241" s="7" t="s">
-        <v>2075</v>
+        <v>2071</v>
       </c>
       <c r="B241" s="7" t="s">
-        <v>2075</v>
+        <v>2071</v>
       </c>
       <c r="O241" s="7" t="s">
-        <v>2076</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="242" spans="1:15">
       <c r="A242" s="7" t="s">
-        <v>2077</v>
+        <v>2073</v>
       </c>
       <c r="O242" s="7" t="s">
-        <v>2689</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="243" spans="1:15">
       <c r="A243" s="7" t="s">
-        <v>2078</v>
+        <v>2074</v>
       </c>
       <c r="O243" s="7" t="s">
-        <v>2631</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="245" spans="1:15">
       <c r="A245" s="7" t="s">
-        <v>2079</v>
+        <v>2075</v>
       </c>
       <c r="B245" s="7" t="s">
-        <v>2080</v>
+        <v>2075</v>
       </c>
       <c r="O245" s="7" t="s">
-        <v>2690</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="246" spans="1:15">
       <c r="A246" s="7" t="s">
-        <v>2081</v>
+        <v>2077</v>
       </c>
       <c r="O246" s="7" t="s">
-        <v>2691</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="247" spans="1:15">
       <c r="A247" s="7" t="s">
-        <v>2082</v>
+        <v>2078</v>
       </c>
       <c r="O247" s="7" t="s">
-        <v>2692</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="249" spans="1:15">
       <c r="A249" s="7" t="s">
-        <v>2083</v>
+        <v>2079</v>
       </c>
       <c r="B249" s="7" t="s">
-        <v>2084</v>
+        <v>2080</v>
       </c>
       <c r="O249" s="7" t="s">
-        <v>2693</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="250" spans="1:15">
       <c r="A250" s="7" t="s">
-        <v>2085</v>
+        <v>2081</v>
       </c>
       <c r="O250" s="7" t="s">
-        <v>2086</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="251" spans="1:15">
       <c r="A251" s="7" t="s">
-        <v>2087</v>
+        <v>2082</v>
       </c>
       <c r="O251" s="7" t="s">
-        <v>2694</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="253" spans="1:15">
       <c r="A253" s="7" t="s">
-        <v>1674</v>
+        <v>2083</v>
       </c>
       <c r="B253" s="7" t="s">
-        <v>1674</v>
+        <v>2084</v>
       </c>
       <c r="O253" s="7" t="s">
-        <v>2088</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="254" spans="1:15">
       <c r="A254" s="7" t="s">
-        <v>2695</v>
+        <v>2085</v>
       </c>
       <c r="O254" s="7" t="s">
-        <v>2696</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="255" spans="1:15">
       <c r="A255" s="7" t="s">
-        <v>2697</v>
+        <v>2087</v>
       </c>
       <c r="O255" s="7" t="s">
-        <v>2698</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="257" spans="1:15">
       <c r="A257" s="7" t="s">
-        <v>2089</v>
+        <v>1674</v>
       </c>
       <c r="B257" s="7" t="s">
-        <v>2089</v>
+        <v>1674</v>
       </c>
       <c r="O257" s="7" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="258" spans="1:15">
       <c r="A258" s="7" t="s">
-        <v>2091</v>
+        <v>2695</v>
       </c>
       <c r="O258" s="7" t="s">
-        <v>2092</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="259" spans="1:15">
       <c r="A259" s="7" t="s">
-        <v>2093</v>
+        <v>2697</v>
       </c>
       <c r="O259" s="7" t="s">
-        <v>2699</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="261" spans="1:15">
       <c r="A261" s="7" t="s">
-        <v>2094</v>
+        <v>2089</v>
       </c>
       <c r="B261" s="7" t="s">
-        <v>2094</v>
+        <v>2089</v>
       </c>
       <c r="O261" s="7" t="s">
-        <v>2095</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="262" spans="1:15">
       <c r="A262" s="7" t="s">
-        <v>2096</v>
+        <v>2091</v>
       </c>
       <c r="O262" s="7" t="s">
-        <v>2700</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="263" spans="1:15">
       <c r="A263" s="7" t="s">
-        <v>2097</v>
+        <v>2093</v>
       </c>
       <c r="O263" s="7" t="s">
-        <v>2701</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="265" spans="1:15">
       <c r="A265" s="7" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
       <c r="B265" s="7" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
       <c r="O265" s="7" t="s">
-        <v>2099</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="266" spans="1:15">
       <c r="A266" s="7" t="s">
-        <v>2100</v>
+        <v>2096</v>
       </c>
       <c r="O266" s="7" t="s">
-        <v>2702</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="267" spans="1:15">
       <c r="A267" s="7" t="s">
-        <v>2101</v>
+        <v>2097</v>
       </c>
       <c r="O267" s="7" t="s">
-        <v>2102</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="269" spans="1:15">
       <c r="A269" s="7" t="s">
-        <v>2103</v>
+        <v>2098</v>
       </c>
       <c r="B269" s="7" t="s">
-        <v>2103</v>
+        <v>2098</v>
       </c>
       <c r="O269" s="7" t="s">
-        <v>2104</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="270" spans="1:15">
       <c r="A270" s="7" t="s">
-        <v>2105</v>
+        <v>2100</v>
       </c>
       <c r="O270" s="7" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="271" spans="1:15">
       <c r="A271" s="7" t="s">
-        <v>2106</v>
+        <v>2101</v>
       </c>
       <c r="O271" s="7" t="s">
-        <v>2704</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="273" spans="1:15">
       <c r="A273" s="7" t="s">
-        <v>2107</v>
+        <v>2103</v>
       </c>
       <c r="B273" s="7" t="s">
-        <v>2107</v>
+        <v>2103</v>
       </c>
       <c r="O273" s="7" t="s">
-        <v>2108</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="274" spans="1:15">
       <c r="A274" s="7" t="s">
-        <v>2109</v>
+        <v>2105</v>
       </c>
       <c r="O274" s="7" t="s">
-        <v>2705</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="275" spans="1:15">
       <c r="A275" s="7" t="s">
-        <v>2110</v>
+        <v>2106</v>
       </c>
       <c r="O275" s="7" t="s">
-        <v>2111</v>
+        <v>2704</v>
       </c>
     </row>
     <row r="277" spans="1:15">
       <c r="A277" s="7" t="s">
-        <v>2112</v>
+        <v>2107</v>
       </c>
       <c r="B277" s="7" t="s">
-        <v>2112</v>
+        <v>2107</v>
       </c>
       <c r="O277" s="7" t="s">
-        <v>2113</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="278" spans="1:15">
       <c r="A278" s="7" t="s">
-        <v>2114</v>
+        <v>2109</v>
       </c>
       <c r="O278" s="7" t="s">
-        <v>2706</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="279" spans="1:15">
       <c r="A279" s="7" t="s">
-        <v>2115</v>
+        <v>2110</v>
       </c>
       <c r="O279" s="7" t="s">
-        <v>2707</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="281" spans="1:15">
       <c r="A281" s="7" t="s">
-        <v>2116</v>
+        <v>2112</v>
       </c>
       <c r="B281" s="7" t="s">
-        <v>2116</v>
+        <v>2112</v>
       </c>
       <c r="O281" s="7" t="s">
-        <v>2117</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="282" spans="1:15">
       <c r="A282" s="7" t="s">
-        <v>2118</v>
+        <v>2114</v>
       </c>
       <c r="O282" s="7" t="s">
-        <v>2708</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="283" spans="1:15">
       <c r="A283" s="7" t="s">
-        <v>2119</v>
+        <v>2115</v>
       </c>
       <c r="O283" s="7" t="s">
-        <v>2120</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="285" spans="1:15">
       <c r="A285" s="7" t="s">
-        <v>2121</v>
+        <v>2116</v>
       </c>
       <c r="B285" s="7" t="s">
-        <v>2121</v>
+        <v>2116</v>
       </c>
       <c r="O285" s="7" t="s">
-        <v>2122</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="286" spans="1:15">
       <c r="A286" s="7" t="s">
-        <v>2123</v>
+        <v>2118</v>
       </c>
       <c r="O286" s="7" t="s">
-        <v>2124</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="287" spans="1:15">
       <c r="A287" s="7" t="s">
-        <v>2125</v>
+        <v>2119</v>
       </c>
       <c r="O287" s="7" t="s">
-        <v>2709</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="289" spans="1:15">
       <c r="A289" s="7" t="s">
-        <v>2126</v>
+        <v>2121</v>
       </c>
       <c r="B289" s="7" t="s">
-        <v>2126</v>
+        <v>2121</v>
       </c>
       <c r="O289" s="7" t="s">
-        <v>2127</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="290" spans="1:15">
       <c r="A290" s="7" t="s">
-        <v>2128</v>
+        <v>2123</v>
       </c>
       <c r="O290" s="7" t="s">
-        <v>2129</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="291" spans="1:15">
       <c r="A291" s="7" t="s">
-        <v>2130</v>
+        <v>2125</v>
       </c>
       <c r="O291" s="7" t="s">
-        <v>2710</v>
+        <v>2709</v>
       </c>
     </row>
     <row r="293" spans="1:15">
       <c r="A293" s="7" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="B293" s="7" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="O293" s="7" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="294" spans="1:15">
       <c r="A294" s="7" t="s">
-        <v>2133</v>
+        <v>2128</v>
       </c>
       <c r="O294" s="7" t="s">
-        <v>2711</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="295" spans="1:15">
       <c r="A295" s="7" t="s">
-        <v>2134</v>
+        <v>2130</v>
       </c>
       <c r="O295" s="7" t="s">
-        <v>2712</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="297" spans="1:15">
       <c r="A297" s="7" t="s">
-        <v>2135</v>
+        <v>2131</v>
       </c>
       <c r="B297" s="7" t="s">
-        <v>2135</v>
+        <v>2131</v>
       </c>
       <c r="O297" s="7" t="s">
-        <v>2136</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="298" spans="1:15">
       <c r="A298" s="7" t="s">
-        <v>1826</v>
+        <v>2133</v>
       </c>
       <c r="O298" s="7" t="s">
-        <v>2137</v>
+        <v>2711</v>
       </c>
     </row>
     <row r="299" spans="1:15">
       <c r="A299" s="7" t="s">
-        <v>1828</v>
+        <v>2134</v>
       </c>
       <c r="O299" s="7" t="s">
-        <v>2713</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="301" spans="1:15">
       <c r="A301" s="7" t="s">
-        <v>1823</v>
+        <v>2135</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>1824</v>
+        <v>2135</v>
       </c>
       <c r="O301" s="7" t="s">
-        <v>1825</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="302" spans="1:15">
       <c r="A302" s="7" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="O302" s="7" t="s">
-        <v>1831</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="303" spans="1:15">
       <c r="A303" s="7" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="O303" s="7" t="s">
-        <v>1830</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="305" spans="1:15">
       <c r="A305" s="7" t="s">
-        <v>2520</v>
+        <v>1823</v>
       </c>
       <c r="B305" s="7" t="s">
-        <v>2520</v>
+        <v>1824</v>
       </c>
       <c r="O305" s="7" t="s">
-        <v>2523</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="306" spans="1:15">
       <c r="A306" s="7" t="s">
-        <v>2521</v>
+        <v>1827</v>
       </c>
       <c r="O306" s="7" t="s">
-        <v>2612</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="307" spans="1:15">
       <c r="A307" s="7" t="s">
-        <v>2522</v>
+        <v>1829</v>
       </c>
       <c r="O307" s="7" t="s">
-        <v>2524</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="309" spans="1:15">
       <c r="A309" s="7" t="s">
-        <v>3079</v>
+        <v>2520</v>
       </c>
       <c r="B309" s="7" t="s">
-        <v>3079</v>
+        <v>2520</v>
       </c>
       <c r="O309" s="7" t="s">
-        <v>3064</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="310" spans="1:15">
       <c r="A310" s="7" t="s">
-        <v>3062</v>
+        <v>2521</v>
       </c>
       <c r="O310" s="7" t="s">
-        <v>3076</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="311" spans="1:15">
       <c r="A311" s="7" t="s">
-        <v>3063</v>
+        <v>2522</v>
       </c>
       <c r="O311" s="7" t="s">
-        <v>3075</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="313" spans="1:15">
       <c r="A313" s="7" t="s">
-        <v>2138</v>
+        <v>3079</v>
       </c>
       <c r="B313" s="7" t="s">
-        <v>2138</v>
+        <v>3079</v>
       </c>
       <c r="O313" s="7" t="s">
-        <v>2139</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="314" spans="1:15">
       <c r="A314" s="7" t="s">
-        <v>2140</v>
+        <v>3062</v>
       </c>
       <c r="O314" s="7" t="s">
-        <v>2714</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="315" spans="1:15">
       <c r="A315" s="7" t="s">
-        <v>2141</v>
+        <v>3063</v>
       </c>
       <c r="O315" s="7" t="s">
-        <v>2142</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="317" spans="1:15">
       <c r="A317" s="7" t="s">
-        <v>2143</v>
+        <v>2138</v>
       </c>
       <c r="B317" s="7" t="s">
-        <v>2715</v>
+        <v>2138</v>
       </c>
       <c r="O317" s="7" t="s">
-        <v>2144</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="318" spans="1:15">
       <c r="A318" s="7" t="s">
-        <v>2145</v>
+        <v>2140</v>
       </c>
       <c r="O318" s="7" t="s">
-        <v>2716</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="319" spans="1:15">
       <c r="A319" s="7" t="s">
-        <v>2146</v>
+        <v>2141</v>
       </c>
       <c r="O319" s="7" t="s">
-        <v>2717</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="321" spans="1:15">
       <c r="A321" s="7" t="s">
-        <v>2147</v>
+        <v>2143</v>
       </c>
       <c r="B321" s="7" t="s">
-        <v>2147</v>
+        <v>2715</v>
       </c>
       <c r="O321" s="7" t="s">
-        <v>2148</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="322" spans="1:15">
       <c r="A322" s="7" t="s">
-        <v>2149</v>
+        <v>2145</v>
       </c>
       <c r="O322" s="7" t="s">
-        <v>2150</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="323" spans="1:15">
       <c r="A323" s="7" t="s">
-        <v>2151</v>
+        <v>2146</v>
       </c>
       <c r="O323" s="7" t="s">
-        <v>2152</v>
+        <v>2717</v>
       </c>
     </row>
     <row r="325" spans="1:15">
       <c r="A325" s="7" t="s">
-        <v>2976</v>
+        <v>2147</v>
       </c>
       <c r="B325" s="7" t="s">
-        <v>2975</v>
+        <v>2147</v>
       </c>
       <c r="O325" s="7" t="s">
-        <v>2977</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="326" spans="1:15">
       <c r="A326" s="7" t="s">
-        <v>2983</v>
+        <v>2149</v>
       </c>
       <c r="O326" s="7" t="s">
-        <v>2980</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="327" spans="1:15">
       <c r="A327" s="7" t="s">
-        <v>2984</v>
+        <v>2151</v>
       </c>
       <c r="O327" s="7" t="s">
-        <v>2979</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="329" spans="1:15">
       <c r="A329" s="7" t="s">
-        <v>2153</v>
+        <v>2976</v>
       </c>
       <c r="B329" s="7" t="s">
-        <v>2153</v>
+        <v>2975</v>
       </c>
       <c r="O329" s="7" t="s">
-        <v>2154</v>
+        <v>2977</v>
       </c>
     </row>
     <row r="330" spans="1:15">
       <c r="A330" s="7" t="s">
-        <v>2155</v>
+        <v>2983</v>
       </c>
       <c r="O330" s="7" t="s">
-        <v>2156</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="331" spans="1:15">
       <c r="A331" s="7" t="s">
-        <v>2157</v>
+        <v>2984</v>
       </c>
       <c r="O331" s="7" t="s">
-        <v>2718</v>
+        <v>2979</v>
       </c>
     </row>
     <row r="333" spans="1:15">
       <c r="A333" s="7" t="s">
-        <v>2158</v>
+        <v>2153</v>
       </c>
       <c r="B333" s="7" t="s">
-        <v>2158</v>
+        <v>2153</v>
       </c>
       <c r="O333" s="7" t="s">
-        <v>2159</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="334" spans="1:15">
       <c r="A334" s="7" t="s">
-        <v>2160</v>
+        <v>2155</v>
       </c>
       <c r="O334" s="7" t="s">
-        <v>2766</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="335" spans="1:15">
       <c r="A335" s="7" t="s">
-        <v>2161</v>
+        <v>2157</v>
       </c>
       <c r="O335" s="7" t="s">
-        <v>2766</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="337" spans="1:15">
       <c r="A337" s="7" t="s">
-        <v>2162</v>
+        <v>2158</v>
       </c>
       <c r="B337" s="7" t="s">
-        <v>2162</v>
+        <v>2158</v>
       </c>
       <c r="O337" s="7" t="s">
-        <v>2163</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="338" spans="1:15">
       <c r="A338" s="7" t="s">
-        <v>2164</v>
+        <v>2160</v>
       </c>
       <c r="O338" s="7" t="s">
-        <v>2719</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="339" spans="1:15">
       <c r="A339" s="7" t="s">
-        <v>2165</v>
+        <v>2161</v>
       </c>
       <c r="O339" s="7" t="s">
-        <v>2166</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="341" spans="1:15">
       <c r="A341" s="7" t="s">
-        <v>2167</v>
+        <v>2162</v>
       </c>
       <c r="B341" s="7" t="s">
-        <v>2167</v>
+        <v>2162</v>
       </c>
       <c r="O341" s="7" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="342" spans="1:15">
       <c r="A342" s="7" t="s">
-        <v>2169</v>
+        <v>2164</v>
       </c>
       <c r="O342" s="7" t="s">
-        <v>2720</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="343" spans="1:15">
       <c r="A343" s="7" t="s">
-        <v>2170</v>
+        <v>2165</v>
       </c>
       <c r="O343" s="7" t="s">
-        <v>2721</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="345" spans="1:15">
       <c r="A345" s="7" t="s">
-        <v>2171</v>
+        <v>2167</v>
       </c>
       <c r="B345" s="7" t="s">
-        <v>2171</v>
+        <v>2167</v>
       </c>
       <c r="O345" s="7" t="s">
-        <v>2172</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="346" spans="1:15">
       <c r="A346" s="7" t="s">
-        <v>2173</v>
+        <v>2169</v>
       </c>
       <c r="O346" s="7" t="s">
-        <v>2174</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="347" spans="1:15">
       <c r="A347" s="7" t="s">
-        <v>2175</v>
+        <v>2170</v>
       </c>
       <c r="O347" s="7" t="s">
-        <v>2176</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="349" spans="1:15">
       <c r="A349" s="7" t="s">
-        <v>2177</v>
+        <v>2171</v>
       </c>
       <c r="B349" s="7" t="s">
-        <v>2177</v>
+        <v>2171</v>
       </c>
       <c r="O349" s="7" t="s">
-        <v>2178</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="350" spans="1:15">
       <c r="A350" s="7" t="s">
-        <v>2179</v>
+        <v>2173</v>
       </c>
       <c r="O350" s="7" t="s">
-        <v>2722</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="351" spans="1:15">
       <c r="A351" s="7" t="s">
-        <v>2180</v>
+        <v>2175</v>
       </c>
       <c r="O351" s="7" t="s">
-        <v>2181</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="353" spans="1:15">
       <c r="A353" s="7" t="s">
-        <v>2182</v>
+        <v>2177</v>
       </c>
       <c r="B353" s="7" t="s">
-        <v>2182</v>
+        <v>2177</v>
       </c>
       <c r="O353" s="7" t="s">
-        <v>2183</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="354" spans="1:15">
       <c r="A354" s="7" t="s">
-        <v>2184</v>
+        <v>2179</v>
       </c>
       <c r="O354" s="7" t="s">
-        <v>2185</v>
+        <v>2722</v>
       </c>
     </row>
     <row r="355" spans="1:15">
       <c r="A355" s="7" t="s">
-        <v>2186</v>
+        <v>2180</v>
       </c>
       <c r="O355" s="7" t="s">
-        <v>2723</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="357" spans="1:15">
       <c r="A357" s="7" t="s">
-        <v>2187</v>
+        <v>2182</v>
       </c>
       <c r="B357" s="7" t="s">
-        <v>2187</v>
+        <v>2182</v>
       </c>
       <c r="O357" s="7" t="s">
-        <v>2188</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="358" spans="1:15">
       <c r="A358" s="7" t="s">
-        <v>2189</v>
+        <v>2184</v>
       </c>
       <c r="O358" s="7" t="s">
-        <v>2190</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="359" spans="1:15">
       <c r="A359" s="7" t="s">
-        <v>2191</v>
+        <v>2186</v>
       </c>
       <c r="O359" s="7" t="s">
-        <v>2724</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="361" spans="1:15">
       <c r="A361" s="7" t="s">
-        <v>2192</v>
+        <v>2187</v>
       </c>
       <c r="B361" s="7" t="s">
-        <v>2192</v>
+        <v>2187</v>
       </c>
       <c r="O361" s="7" t="s">
-        <v>2193</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="362" spans="1:15">
       <c r="A362" s="7" t="s">
-        <v>2194</v>
+        <v>2189</v>
       </c>
       <c r="O362" s="7" t="s">
-        <v>2725</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="363" spans="1:15">
       <c r="A363" s="7" t="s">
-        <v>2195</v>
+        <v>2191</v>
       </c>
       <c r="O363" s="7" t="s">
-        <v>2196</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="365" spans="1:15">
       <c r="A365" s="7" t="s">
-        <v>2197</v>
+        <v>2192</v>
       </c>
       <c r="B365" s="7" t="s">
-        <v>2197</v>
+        <v>2192</v>
       </c>
       <c r="O365" s="7" t="s">
-        <v>2198</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="366" spans="1:15">
       <c r="A366" s="7" t="s">
-        <v>2199</v>
+        <v>2194</v>
       </c>
       <c r="O366" s="7" t="s">
-        <v>2200</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="367" spans="1:15">
       <c r="A367" s="7" t="s">
-        <v>2201</v>
+        <v>2195</v>
       </c>
       <c r="O367" s="7" t="s">
-        <v>2200</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="369" spans="1:15">
       <c r="A369" s="7" t="s">
-        <v>2202</v>
+        <v>2197</v>
       </c>
       <c r="B369" s="7" t="s">
-        <v>2202</v>
+        <v>2197</v>
       </c>
       <c r="O369" s="7" t="s">
-        <v>2203</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="370" spans="1:15">
       <c r="A370" s="7" t="s">
-        <v>2204</v>
+        <v>2199</v>
       </c>
       <c r="O370" s="7" t="s">
-        <v>2205</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="371" spans="1:15">
       <c r="A371" s="7" t="s">
-        <v>2206</v>
+        <v>2201</v>
       </c>
       <c r="O371" s="7" t="s">
-        <v>2726</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="373" spans="1:15">
       <c r="A373" s="7" t="s">
-        <v>2207</v>
+        <v>2202</v>
       </c>
       <c r="B373" s="7" t="s">
-        <v>2207</v>
+        <v>2202</v>
       </c>
       <c r="O373" s="7" t="s">
-        <v>2208</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="374" spans="1:15">
       <c r="A374" s="7" t="s">
-        <v>2209</v>
+        <v>2204</v>
       </c>
       <c r="O374" s="7" t="s">
-        <v>2727</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="375" spans="1:15">
       <c r="A375" s="7" t="s">
-        <v>2210</v>
+        <v>2206</v>
       </c>
       <c r="O375" s="7" t="s">
-        <v>2211</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="377" spans="1:15">
       <c r="A377" s="7" t="s">
-        <v>2212</v>
+        <v>2207</v>
       </c>
       <c r="B377" s="7" t="s">
-        <v>2213</v>
+        <v>2207</v>
       </c>
       <c r="O377" s="7" t="s">
-        <v>2213</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="378" spans="1:15">
       <c r="A378" s="7" t="s">
-        <v>2214</v>
+        <v>2209</v>
       </c>
       <c r="O378" s="7" t="s">
-        <v>2215</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="379" spans="1:15">
       <c r="A379" s="7" t="s">
-        <v>2216</v>
+        <v>2210</v>
       </c>
       <c r="O379" s="7" t="s">
-        <v>2728</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="381" spans="1:15">
       <c r="A381" s="7" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="B381" s="7" t="s">
-        <v>2217</v>
+        <v>2213</v>
       </c>
       <c r="O381" s="7" t="s">
-        <v>2218</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="382" spans="1:15">
       <c r="A382" s="7" t="s">
-        <v>2219</v>
+        <v>2214</v>
       </c>
       <c r="O382" s="7" t="s">
-        <v>2729</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="383" spans="1:15">
       <c r="A383" s="7" t="s">
-        <v>2220</v>
+        <v>2216</v>
       </c>
       <c r="O383" s="7" t="s">
-        <v>2730</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="385" spans="1:15">
       <c r="A385" s="7" t="s">
-        <v>2221</v>
+        <v>2217</v>
       </c>
       <c r="B385" s="7" t="s">
-        <v>2221</v>
+        <v>2217</v>
       </c>
       <c r="O385" s="7" t="s">
-        <v>2222</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="386" spans="1:15">
       <c r="A386" s="7" t="s">
-        <v>2223</v>
+        <v>2219</v>
       </c>
       <c r="O386" s="7" t="s">
-        <v>2224</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="387" spans="1:15">
       <c r="A387" s="7" t="s">
-        <v>2225</v>
+        <v>2220</v>
       </c>
       <c r="O387" s="7" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="389" spans="1:15">
       <c r="A389" s="7" t="s">
-        <v>2226</v>
+        <v>2221</v>
       </c>
       <c r="B389" s="7" t="s">
-        <v>2226</v>
+        <v>2221</v>
       </c>
       <c r="O389" s="7" t="s">
-        <v>2227</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="390" spans="1:15">
       <c r="A390" s="7" t="s">
-        <v>2228</v>
+        <v>2223</v>
       </c>
       <c r="O390" s="7" t="s">
-        <v>2732</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="391" spans="1:15">
       <c r="A391" s="7" t="s">
-        <v>2229</v>
+        <v>2225</v>
       </c>
       <c r="O391" s="7" t="s">
-        <v>2230</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="393" spans="1:15">
       <c r="A393" s="7" t="s">
-        <v>2231</v>
+        <v>2226</v>
       </c>
       <c r="B393" s="7" t="s">
-        <v>2231</v>
+        <v>2226</v>
       </c>
       <c r="O393" s="7" t="s">
-        <v>2232</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="394" spans="1:15">
       <c r="A394" s="7" t="s">
-        <v>2233</v>
+        <v>2228</v>
       </c>
       <c r="O394" s="7" t="s">
-        <v>2733</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="395" spans="1:15">
       <c r="A395" s="7" t="s">
-        <v>2234</v>
+        <v>2229</v>
       </c>
       <c r="O395" s="7" t="s">
-        <v>2734</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="397" spans="1:15">
       <c r="A397" s="7" t="s">
-        <v>1820</v>
+        <v>2231</v>
       </c>
       <c r="B397" s="7" t="s">
-        <v>1820</v>
+        <v>2231</v>
       </c>
       <c r="O397" s="7" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="398" spans="1:15">
       <c r="A398" s="7" t="s">
-        <v>2236</v>
+        <v>2233</v>
       </c>
       <c r="O398" s="7" t="s">
-        <v>2237</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="399" spans="1:15">
       <c r="A399" s="7" t="s">
-        <v>2238</v>
+        <v>2234</v>
       </c>
       <c r="O399" s="7" t="s">
-        <v>2735</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="401" spans="1:15">
       <c r="A401" s="7" t="s">
-        <v>2239</v>
+        <v>1820</v>
       </c>
       <c r="B401" s="7" t="s">
-        <v>2239</v>
+        <v>1820</v>
       </c>
       <c r="O401" s="7" t="s">
-        <v>2240</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="402" spans="1:15">
       <c r="A402" s="7" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="O402" s="7" t="s">
-        <v>2242</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="403" spans="1:15">
       <c r="A403" s="7" t="s">
-        <v>2243</v>
+        <v>2238</v>
       </c>
       <c r="O403" s="7" t="s">
-        <v>2736</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="405" spans="1:15">
       <c r="A405" s="7" t="s">
-        <v>2244</v>
+        <v>2239</v>
       </c>
       <c r="B405" s="7" t="s">
-        <v>2244</v>
+        <v>2239</v>
       </c>
       <c r="O405" s="7" t="s">
-        <v>2245</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="406" spans="1:15">
       <c r="A406" s="7" t="s">
-        <v>2246</v>
+        <v>2241</v>
       </c>
       <c r="O406" s="7" t="s">
-        <v>2737</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="407" spans="1:15">
       <c r="A407" s="7" t="s">
-        <v>2247</v>
+        <v>2243</v>
       </c>
       <c r="O407" s="7" t="s">
-        <v>2738</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="409" spans="1:15">
       <c r="A409" s="7" t="s">
-        <v>2248</v>
+        <v>2244</v>
       </c>
       <c r="B409" s="7" t="s">
-        <v>2248</v>
+        <v>2244</v>
       </c>
       <c r="O409" s="7" t="s">
-        <v>3179</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="410" spans="1:15">
       <c r="A410" s="7" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
       <c r="O410" s="7" t="s">
-        <v>2250</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="411" spans="1:15">
       <c r="A411" s="7" t="s">
-        <v>2251</v>
+        <v>2247</v>
       </c>
       <c r="O411" s="7" t="s">
-        <v>2252</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="413" spans="1:15">
       <c r="A413" s="7" t="s">
-        <v>2253</v>
+        <v>2248</v>
       </c>
       <c r="B413" s="7" t="s">
-        <v>2739</v>
+        <v>2248</v>
       </c>
       <c r="O413" s="7" t="s">
-        <v>2254</v>
+        <v>3179</v>
       </c>
     </row>
     <row r="414" spans="1:15">
       <c r="A414" s="7" t="s">
-        <v>2255</v>
+        <v>2249</v>
       </c>
       <c r="O414" s="7" t="s">
-        <v>2740</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="415" spans="1:15">
       <c r="A415" s="7" t="s">
-        <v>2256</v>
+        <v>2251</v>
       </c>
       <c r="O415" s="7" t="s">
-        <v>2740</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="417" spans="1:15">
       <c r="A417" s="7" t="s">
-        <v>2257</v>
+        <v>2253</v>
       </c>
       <c r="B417" s="7" t="s">
-        <v>2257</v>
+        <v>2739</v>
       </c>
       <c r="O417" s="7" t="s">
-        <v>2258</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="418" spans="1:15">
       <c r="A418" s="7" t="s">
-        <v>2259</v>
+        <v>2255</v>
       </c>
       <c r="O418" s="7" t="s">
-        <v>2741</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="419" spans="1:15">
       <c r="A419" s="7" t="s">
-        <v>2260</v>
+        <v>2256</v>
       </c>
       <c r="O419" s="7" t="s">
-        <v>2261</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="421" spans="1:15">
       <c r="A421" s="7" t="s">
-        <v>2262</v>
+        <v>2257</v>
       </c>
       <c r="B421" s="7" t="s">
-        <v>2262</v>
+        <v>2257</v>
       </c>
       <c r="O421" s="7" t="s">
-        <v>2263</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="422" spans="1:15">
       <c r="A422" s="7" t="s">
-        <v>2264</v>
+        <v>2259</v>
       </c>
       <c r="O422" s="7" t="s">
-        <v>2265</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="423" spans="1:15">
       <c r="A423" s="7" t="s">
-        <v>2266</v>
+        <v>2260</v>
       </c>
       <c r="O423" s="7" t="s">
-        <v>2267</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="425" spans="1:15">
       <c r="A425" s="7" t="s">
-        <v>2866</v>
+        <v>2262</v>
       </c>
       <c r="B425" s="7" t="s">
-        <v>2866</v>
+        <v>2262</v>
       </c>
       <c r="O425" s="7" t="s">
-        <v>2869</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="426" spans="1:15">
       <c r="A426" s="7" t="s">
-        <v>2867</v>
+        <v>2264</v>
       </c>
       <c r="O426" s="7" t="s">
-        <v>2870</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="427" spans="1:15">
       <c r="A427" s="7" t="s">
-        <v>2868</v>
+        <v>2266</v>
       </c>
       <c r="O427" s="7" t="s">
-        <v>2870</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="429" spans="1:15">
       <c r="A429" s="7" t="s">
-        <v>2876</v>
+        <v>2866</v>
       </c>
       <c r="B429" s="7" t="s">
-        <v>2876</v>
+        <v>2866</v>
       </c>
       <c r="O429" s="7" t="s">
-        <v>2879</v>
+        <v>2869</v>
       </c>
     </row>
     <row r="430" spans="1:15">
       <c r="A430" s="7" t="s">
-        <v>2877</v>
+        <v>2867</v>
       </c>
       <c r="O430" s="7" t="s">
-        <v>2880</v>
+        <v>2870</v>
       </c>
     </row>
     <row r="431" spans="1:15">
       <c r="A431" s="7" t="s">
-        <v>2878</v>
+        <v>2868</v>
       </c>
       <c r="O431" s="7" t="s">
-        <v>2880</v>
+        <v>2870</v>
       </c>
     </row>
     <row r="433" spans="1:15">
       <c r="A433" s="7" t="s">
-        <v>2268</v>
+        <v>2876</v>
       </c>
       <c r="B433" s="7" t="s">
-        <v>2268</v>
+        <v>2876</v>
       </c>
       <c r="O433" s="7" t="s">
-        <v>2269</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="434" spans="1:15">
       <c r="A434" s="7" t="s">
-        <v>2270</v>
+        <v>2877</v>
       </c>
       <c r="O434" s="7" t="s">
-        <v>2742</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="435" spans="1:15">
       <c r="A435" s="7" t="s">
-        <v>2271</v>
+        <v>2878</v>
       </c>
       <c r="O435" s="7" t="s">
-        <v>2742</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="437" spans="1:15">
       <c r="A437" s="7" t="s">
-        <v>2272</v>
+        <v>2268</v>
       </c>
       <c r="B437" s="7" t="s">
-        <v>2272</v>
+        <v>2268</v>
       </c>
       <c r="O437" s="7" t="s">
-        <v>2273</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="438" spans="1:15">
       <c r="A438" s="7" t="s">
-        <v>2274</v>
+        <v>2270</v>
       </c>
       <c r="O438" s="7" t="s">
-        <v>2743</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="439" spans="1:15">
       <c r="A439" s="7" t="s">
-        <v>2275</v>
+        <v>2271</v>
       </c>
       <c r="O439" s="7" t="s">
-        <v>2743</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="441" spans="1:15">
       <c r="A441" s="7" t="s">
-        <v>2276</v>
+        <v>2272</v>
       </c>
       <c r="B441" s="7" t="s">
-        <v>2276</v>
+        <v>2272</v>
       </c>
       <c r="O441" s="7" t="s">
         <v>2273</v>
@@ -28063,17 +28112,44 @@
     </row>
     <row r="442" spans="1:15">
       <c r="A442" s="7" t="s">
-        <v>2277</v>
+        <v>2274</v>
       </c>
       <c r="O442" s="7" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="443" spans="1:15">
       <c r="A443" s="7" t="s">
+        <v>2275</v>
+      </c>
+      <c r="O443" s="7" t="s">
+        <v>2743</v>
+      </c>
+    </row>
+    <row r="445" spans="1:15">
+      <c r="A445" s="7" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B445" s="7" t="s">
+        <v>2276</v>
+      </c>
+      <c r="O445" s="7" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="446" spans="1:15">
+      <c r="A446" s="7" t="s">
+        <v>2277</v>
+      </c>
+      <c r="O446" s="7" t="s">
+        <v>2744</v>
+      </c>
+    </row>
+    <row r="447" spans="1:15">
+      <c r="A447" s="7" t="s">
         <v>2278</v>
       </c>
-      <c r="O443" s="7" t="s">
+      <c r="O447" s="7" t="s">
         <v>2744</v>
       </c>
     </row>
@@ -28086,7 +28162,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:Q113"/>
+  <dimension ref="A1:Q114"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="60" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.625" style="8" customWidth="1"/>
@@ -28361,662 +28437,670 @@
         <v>3243</v>
       </c>
       <c r="O28" s="9" t="s">
-        <v>3244</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="60" customHeight="1">
-      <c r="A30" s="8" t="s">
-        <v>1705</v>
-      </c>
-      <c r="O30" s="9" t="s">
-        <v>2790</v>
+        <v>3262</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="60" customHeight="1">
+      <c r="A29" s="8" t="s">
+        <v>3253</v>
+      </c>
+      <c r="O29" s="9" t="s">
+        <v>3261</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="60" customHeight="1">
       <c r="A31" s="8" t="s">
-        <v>2514</v>
+        <v>1705</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>2513</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="60" customHeight="1">
       <c r="A32" s="8" t="s">
-        <v>1704</v>
+        <v>2514</v>
       </c>
       <c r="O32" s="9" t="s">
-        <v>2791</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="60" customHeight="1">
       <c r="A33" s="8" t="s">
-        <v>2335</v>
+        <v>1704</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>2792</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="60" customHeight="1">
       <c r="A34" s="8" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="O34" s="9" t="s">
-        <v>2313</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="60" customHeight="1">
       <c r="A35" s="8" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>2793</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="60" customHeight="1">
       <c r="A36" s="8" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="O36" s="9" t="s">
-        <v>2794</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="60" customHeight="1">
       <c r="A37" s="8" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>2795</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="60" customHeight="1">
       <c r="A38" s="8" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="O38" s="9" t="s">
-        <v>2796</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="60" customHeight="1">
       <c r="A39" s="8" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>2797</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="60" customHeight="1">
       <c r="A40" s="8" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="O40" s="9" t="s">
-        <v>2798</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="60" customHeight="1">
       <c r="A41" s="8" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>2799</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="60" customHeight="1">
       <c r="A42" s="8" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="O42" s="9" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="60" customHeight="1">
       <c r="A43" s="8" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>2974</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="60" customHeight="1">
       <c r="A44" s="8" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="O44" s="9" t="s">
-        <v>2801</v>
+        <v>2974</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="60" customHeight="1">
       <c r="A45" s="8" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>2802</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="60" customHeight="1">
       <c r="A46" s="8" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="O46" s="9" t="s">
-        <v>2803</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="60" customHeight="1">
       <c r="A47" s="8" t="s">
-        <v>2998</v>
+        <v>2348</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>3021</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="60" customHeight="1">
       <c r="A48" s="8" t="s">
-        <v>2349</v>
+        <v>2998</v>
       </c>
       <c r="O48" s="9" t="s">
-        <v>2804</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="60" customHeight="1">
       <c r="A49" s="8" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>2805</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="60" customHeight="1">
       <c r="A50" s="8" t="s">
+        <v>2350</v>
+      </c>
+      <c r="O50" s="9" t="s">
+        <v>2805</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="60" customHeight="1">
+      <c r="A51" s="8" t="s">
         <v>2903</v>
       </c>
-      <c r="O50" s="9" t="s">
+      <c r="O51" s="9" t="s">
         <v>2911</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="132.75" customHeight="1">
-      <c r="A51" s="8" t="s">
+    <row r="52" spans="1:15" ht="132.75" customHeight="1">
+      <c r="A52" s="8" t="s">
         <v>3208</v>
       </c>
-      <c r="O51" s="9" t="s">
+      <c r="O52" s="9" t="s">
         <v>3232</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="60" customHeight="1">
-      <c r="A52" s="8" t="s">
+    <row r="53" spans="1:15" ht="60" customHeight="1">
+      <c r="A53" s="8" t="s">
         <v>3230</v>
       </c>
-      <c r="O52" s="9" t="s">
+      <c r="O53" s="9" t="s">
         <v>3231</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" ht="60" customHeight="1">
-      <c r="A54" s="8" t="s">
-        <v>2351</v>
-      </c>
-      <c r="O54" s="9" t="s">
-        <v>2806</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="60" customHeight="1">
       <c r="A55" s="8" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>2807</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="60" customHeight="1">
       <c r="A56" s="8" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="O56" s="9" t="s">
-        <v>2761</v>
+        <v>2807</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="60" customHeight="1">
       <c r="A57" s="8" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>2808</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="60" customHeight="1">
       <c r="A58" s="8" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="O58" s="9" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="60" customHeight="1">
       <c r="A59" s="8" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>2760</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="60" customHeight="1">
       <c r="A60" s="8" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="O60" s="9" t="s">
-        <v>2810</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="60" customHeight="1">
       <c r="A61" s="8" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>2811</v>
+        <v>2810</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="60" customHeight="1">
       <c r="A62" s="8" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="O62" s="9" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="60" customHeight="1">
       <c r="A63" s="8" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="60" customHeight="1">
       <c r="A64" s="8" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="O64" s="9" t="s">
-        <v>2814</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="60" customHeight="1">
       <c r="A65" s="8" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>2815</v>
+        <v>2814</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="60" customHeight="1">
       <c r="A66" s="8" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="O66" s="9" t="s">
-        <v>2816</v>
+        <v>2815</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="60" customHeight="1">
       <c r="A67" s="8" t="s">
-        <v>2851</v>
+        <v>2363</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>2817</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="60" customHeight="1">
       <c r="A68" s="8" t="s">
-        <v>2364</v>
+        <v>2851</v>
       </c>
       <c r="O68" s="9" t="s">
-        <v>2818</v>
+        <v>2817</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="60" customHeight="1">
       <c r="A69" s="8" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>2856</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="60" customHeight="1">
       <c r="A70" s="8" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="O70" s="9" t="s">
-        <v>2819</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="60" customHeight="1">
       <c r="A71" s="8" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="60" customHeight="1">
       <c r="A72" s="8" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="O72" s="9" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="60" customHeight="1">
       <c r="A73" s="8" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="60" customHeight="1">
       <c r="A74" s="8" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="O74" s="9" t="s">
-        <v>1711</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="60" customHeight="1">
       <c r="A75" s="8" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>2823</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="60" customHeight="1">
       <c r="A76" s="8" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="O76" s="9" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="60" customHeight="1">
       <c r="A77" s="8" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="60" customHeight="1">
       <c r="A78" s="8" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="O78" s="9" t="s">
-        <v>2826</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="60" customHeight="1">
       <c r="A79" s="8" t="s">
-        <v>1843</v>
+        <v>2374</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>2860</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="60" customHeight="1">
       <c r="A80" s="8" t="s">
-        <v>2556</v>
+        <v>1843</v>
       </c>
       <c r="O80" s="9" t="s">
-        <v>2555</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="81" spans="1:15" ht="60" customHeight="1">
       <c r="A81" s="8" t="s">
+        <v>2556</v>
+      </c>
+      <c r="O81" s="9" t="s">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" ht="60" customHeight="1">
+      <c r="A82" s="8" t="s">
         <v>3080</v>
       </c>
-      <c r="O81" s="9" t="s">
+      <c r="O82" s="9" t="s">
         <v>3081</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" ht="60" customHeight="1">
-      <c r="A83" s="8" t="s">
-        <v>2375</v>
-      </c>
-      <c r="O83" s="9" t="s">
-        <v>2827</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="60" customHeight="1">
       <c r="A84" s="8" t="s">
-        <v>2315</v>
+        <v>2375</v>
       </c>
       <c r="O84" s="9" t="s">
-        <v>2775</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="85" spans="1:15" ht="60" customHeight="1">
       <c r="A85" s="8" t="s">
-        <v>2376</v>
+        <v>2315</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>2772</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="86" spans="1:15" ht="60" customHeight="1">
       <c r="A86" s="8" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="O86" s="9" t="s">
-        <v>2828</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="87" spans="1:15" ht="60" customHeight="1">
       <c r="A87" s="8" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>2829</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="60" customHeight="1">
       <c r="A88" s="8" t="s">
-        <v>2978</v>
+        <v>2378</v>
       </c>
       <c r="O88" s="9" t="s">
-        <v>3022</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="60" customHeight="1">
       <c r="A89" s="8" t="s">
-        <v>2379</v>
+        <v>2978</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>2830</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="90" spans="1:15" ht="60" customHeight="1">
       <c r="A90" s="8" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="O90" s="9" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="60" customHeight="1">
       <c r="A91" s="8" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>2832</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="92" spans="1:15" ht="60" customHeight="1">
       <c r="A92" s="8" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="O92" s="9" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="93" spans="1:15" ht="60" customHeight="1">
       <c r="A93" s="8" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="94" spans="1:15" ht="60" customHeight="1">
       <c r="A94" s="8" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="O94" s="9" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="95" spans="1:15" ht="60" customHeight="1">
       <c r="A95" s="8" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="96" spans="1:15" ht="60" customHeight="1">
       <c r="A96" s="8" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="O96" s="9" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="97" spans="1:15" ht="60" customHeight="1">
       <c r="A97" s="8" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="98" spans="1:15" ht="60" customHeight="1">
       <c r="A98" s="8" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="O98" s="9" t="s">
-        <v>2773</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="99" spans="1:15" ht="60" customHeight="1">
       <c r="A99" s="8" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>2839</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="100" spans="1:15" ht="60" customHeight="1">
       <c r="A100" s="8" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="O100" s="9" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="101" spans="1:15" ht="60" customHeight="1">
       <c r="A101" s="8" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="102" spans="1:15" ht="60" customHeight="1">
       <c r="A102" s="8" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="O102" s="9" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="103" spans="1:15" ht="60" customHeight="1">
       <c r="A103" s="8" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
     </row>
     <row r="104" spans="1:15" ht="60" customHeight="1">
       <c r="A104" s="8" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="O104" s="9" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="105" spans="1:15" ht="60" customHeight="1">
       <c r="A105" s="8" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="106" spans="1:15" ht="60" customHeight="1">
       <c r="A106" s="8" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="O106" s="9" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="107" spans="1:15" ht="60" customHeight="1">
       <c r="A107" s="8" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
     </row>
     <row r="108" spans="1:15" ht="60" customHeight="1">
       <c r="A108" s="8" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="O108" s="9" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="109" spans="1:15" ht="60" customHeight="1">
       <c r="A109" s="8" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="110" spans="1:15" ht="60" customHeight="1">
       <c r="A110" s="8" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="O110" s="9" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="111" spans="1:15" ht="60" customHeight="1">
       <c r="A111" s="8" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>2852</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="112" spans="1:15" ht="60" customHeight="1">
       <c r="A112" s="8" t="s">
-        <v>2871</v>
+        <v>2401</v>
       </c>
       <c r="O112" s="9" t="s">
-        <v>2872</v>
+        <v>2852</v>
       </c>
     </row>
     <row r="113" spans="1:15" ht="60" customHeight="1">
       <c r="A113" s="8" t="s">
+        <v>2871</v>
+      </c>
+      <c r="O113" s="9" t="s">
+        <v>2872</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" ht="60" customHeight="1">
+      <c r="A114" s="8" t="s">
         <v>2881</v>
       </c>
-      <c r="O113" s="9" t="s">
+      <c r="O114" s="9" t="s">
         <v>2896</v>
       </c>
     </row>

--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Among Us code\TheOtherUs\TheOtherUs-Edited-Lite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0C40EE-BEB3-44F0-9360-01DF02AE23C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF36E63-E174-4D89-AA60-10CB8592989A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="720" yWindow="1200" windowWidth="25755" windowHeight="14910" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3586" uniqueCount="3263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3588" uniqueCount="3266">
   <si>
     <t>English</t>
   </si>
@@ -11552,10 +11552,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>隐忍, 爆发！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>存下子弹, 等待时机击杀玩家</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -11625,14 +11621,30 @@
     <t>berserkerRampageCooldown</t>
   </si>
   <si>
-    <t>狂战士在击杀时会狂暴，击杀玩家后可在极短时间内0CD无限出刀。
-初始的持续时间为0.1s，在击杀冷却完毕后等待充能来获得更长的持续时间。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以在击杀冷却完毕后手动存下子弹，可以随时取出子弹。
+    <t>只懂的杀戮的好战机器</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓄力！斩杀！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我起了，一枪秒了</t>
+  </si>
+  <si>
+    <t xml:space="preserve">可以在击杀冷却完毕后手动存下子弹，存入的子弹有上限。
 随时可以取出子弹，取出子弹后会将击杀按钮重置冷却。
-存入的子弹有上限！</t>
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gunsmith</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>狂战士在击杀时会狂暴，击杀玩家后可在极短时间内无限制多次击杀。
+初始的持续时间为0.1s，在击杀冷却完毕后会开始蓄力，
+蓄力时间越长，击杀持续时间越长。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -16096,34 +16108,34 @@
     </row>
     <row r="393" spans="1:15" ht="24.95" customHeight="1">
       <c r="A393" s="2" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="O393" s="2" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
     </row>
     <row r="394" spans="1:15" ht="24.95" customHeight="1">
       <c r="A394" s="2" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="O394" s="2" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="396" spans="1:15" ht="24.95" customHeight="1">
       <c r="A396" s="2" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="O396" s="2" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
     </row>
     <row r="397" spans="1:15" ht="24.95" customHeight="1">
       <c r="A397" s="2" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="O397" s="2" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="398" spans="1:15" ht="24.95" customHeight="1">
@@ -25057,18 +25069,18 @@
     </row>
     <row r="95" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A95" s="2" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="96" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A96" s="2" t="s">
+        <v>3248</v>
+      </c>
+      <c r="O96" s="2" t="s">
         <v>3249</v>
-      </c>
-      <c r="O96" s="2" t="s">
-        <v>3250</v>
       </c>
     </row>
   </sheetData>
@@ -25869,7 +25881,7 @@
         <v>3237</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>3237</v>
+        <v>3264</v>
       </c>
       <c r="O109" s="7" t="s">
         <v>3240</v>
@@ -25880,7 +25892,7 @@
         <v>3238</v>
       </c>
       <c r="O110" s="7" t="s">
-        <v>3241</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="111" spans="1:15">
@@ -25888,28 +25900,34 @@
         <v>3239</v>
       </c>
       <c r="O111" s="7" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
     </row>
     <row r="113" spans="1:15">
       <c r="A113" s="7" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="O113" s="7" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="114" spans="1:15">
       <c r="A114" s="7" t="s">
-        <v>3254</v>
+        <v>3253</v>
+      </c>
+      <c r="O114" s="7" t="s">
+        <v>3260</v>
       </c>
     </row>
     <row r="115" spans="1:15">
       <c r="A115" s="7" t="s">
-        <v>3255</v>
+        <v>3254</v>
+      </c>
+      <c r="O115" s="7" t="s">
+        <v>3261</v>
       </c>
     </row>
     <row r="117" spans="1:15">
@@ -28434,18 +28452,18 @@
     </row>
     <row r="28" spans="1:15" ht="60" customHeight="1">
       <c r="A28" s="8" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="O28" s="9" t="s">
-        <v>3262</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="60" customHeight="1">
       <c r="A29" s="8" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>3261</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="60" customHeight="1">

--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Among Us code\TheOtherUs\TheOtherUs-Edited-Lite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF36E63-E174-4D89-AA60-10CB8592989A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFC2675-D9B8-4CBB-9E03-9DB5B8DD6FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="1200" windowWidth="25755" windowHeight="14910" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="720" yWindow="1170" windowWidth="25755" windowHeight="14940" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Options" sheetId="3" r:id="rId1"/>
@@ -11412,14 +11412,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>在会议中可以揭示身份，获得一次在会议中击杀玩家的机会。且无法被猜测
-狼之主揭示身份后无法再使用赌怪能力，
-同时，如果狼之主使用赌怪能力则本轮会议无法揭示身份。
-（猎杀和赌怪一次会议只能用一个能力）
-职业创意来自：尕丶天堂</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>BandLeaderBad</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -11645,6 +11637,13 @@
     <t>狂战士在击杀时会狂暴，击杀玩家后可在极短时间内无限制多次击杀。
 初始的持续时间为0.1s，在击杀冷却完毕后会开始蓄力，
 蓄力时间越长，击杀持续时间越长。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>在会议中可以揭示身份，获得一次在会议中击杀玩家的机会。且无法被猜测
+同时，如果狼之主使用赌怪能力则本轮会议无法揭示身份。
+（猎杀和赌怪一次会议只能用一个能力）
+职业创意来自：尕丶天堂</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -12808,11 +12807,11 @@
     </row>
     <row r="51" spans="1:15" ht="24.95" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="B51" s="3"/>
       <c r="O51" s="3" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="24.95" customHeight="1">
@@ -16108,34 +16107,34 @@
     </row>
     <row r="393" spans="1:15" ht="24.95" customHeight="1">
       <c r="A393" s="2" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="O393" s="2" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
     </row>
     <row r="394" spans="1:15" ht="24.95" customHeight="1">
       <c r="A394" s="2" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="O394" s="2" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
     </row>
     <row r="396" spans="1:15" ht="24.95" customHeight="1">
       <c r="A396" s="2" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="O396" s="2" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="397" spans="1:15" ht="24.95" customHeight="1">
       <c r="A397" s="2" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
       <c r="O397" s="2" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="398" spans="1:15" ht="24.95" customHeight="1">
@@ -16176,7 +16175,7 @@
     </row>
     <row r="402" spans="1:15" ht="24.95" customHeight="1">
       <c r="A402" s="2" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="B402" s="2" t="s">
         <v>1639</v>
@@ -17123,13 +17122,13 @@
     </row>
     <row r="514" spans="1:15" ht="24.95" customHeight="1">
       <c r="A514" s="2" t="s">
+        <v>3226</v>
+      </c>
+      <c r="B514" s="2" t="s">
+        <v>3228</v>
+      </c>
+      <c r="O514" s="2" t="s">
         <v>3227</v>
-      </c>
-      <c r="B514" s="2" t="s">
-        <v>3229</v>
-      </c>
-      <c r="O514" s="2" t="s">
-        <v>3228</v>
       </c>
     </row>
     <row r="515" spans="1:15" ht="24.95" customHeight="1">
@@ -17167,34 +17166,34 @@
     </row>
     <row r="519" spans="1:15" ht="24.95" customHeight="1">
       <c r="A519" s="2" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
       <c r="O519" s="3" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
     </row>
     <row r="520" spans="1:15" ht="24.95" customHeight="1">
       <c r="A520" s="2" t="s">
+        <v>3224</v>
+      </c>
+      <c r="O520" s="3" t="s">
         <v>3225</v>
-      </c>
-      <c r="O520" s="3" t="s">
-        <v>3226</v>
       </c>
     </row>
     <row r="521" spans="1:15" ht="24.95" customHeight="1">
       <c r="A521" s="2" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="O521" s="3" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
     </row>
     <row r="522" spans="1:15" ht="24.95" customHeight="1">
       <c r="A522" s="2" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="O522" s="3" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="525" spans="1:15" ht="24.95" customHeight="1">
@@ -22550,7 +22549,7 @@
         <v>2488</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="45" customHeight="1">
@@ -22566,7 +22565,7 @@
         <v>2491</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="45" customHeight="1">
@@ -22946,18 +22945,18 @@
     </row>
     <row r="59" spans="1:15" ht="24.95" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="24.95" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="24.95" customHeight="1">
@@ -25069,18 +25068,18 @@
     </row>
     <row r="95" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A95" s="2" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="96" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A96" s="2" t="s">
+        <v>3247</v>
+      </c>
+      <c r="O96" s="2" t="s">
         <v>3248</v>
-      </c>
-      <c r="O96" s="2" t="s">
-        <v>3249</v>
       </c>
     </row>
   </sheetData>
@@ -25164,13 +25163,13 @@
     </row>
     <row r="3" spans="1:17" ht="24.95" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>1642</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="24.95" customHeight="1"/>
@@ -25878,56 +25877,56 @@
     </row>
     <row r="109" spans="1:15">
       <c r="A109" s="7" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
       <c r="O109" s="7" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
     </row>
     <row r="110" spans="1:15">
       <c r="A110" s="7" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="O110" s="7" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="111" spans="1:15">
       <c r="A111" s="7" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="O111" s="7" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="113" spans="1:15">
       <c r="A113" s="7" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="O113" s="7" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
     </row>
     <row r="114" spans="1:15">
       <c r="A114" s="7" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="O114" s="7" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="115" spans="1:15">
       <c r="A115" s="7" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="O115" s="7" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="117" spans="1:15">
@@ -28255,7 +28254,7 @@
         <v>2981</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>3211</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="60" customHeight="1">
@@ -28452,18 +28451,18 @@
     </row>
     <row r="28" spans="1:15" ht="60" customHeight="1">
       <c r="A28" s="8" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="O28" s="9" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="60" customHeight="1">
       <c r="A29" s="8" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="60" customHeight="1">
@@ -28639,15 +28638,15 @@
         <v>3208</v>
       </c>
       <c r="O52" s="9" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="60" customHeight="1">
       <c r="A53" s="8" t="s">
+        <v>3229</v>
+      </c>
+      <c r="O53" s="9" t="s">
         <v>3230</v>
-      </c>
-      <c r="O53" s="9" t="s">
-        <v>3231</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="60" customHeight="1">

--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Among Us code\TheOtherUs\TheOtherUs-Edited-Lite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFC2675-D9B8-4CBB-9E03-9DB5B8DD6FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB4AF53-678E-42CA-89A6-18F87B52084F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="1170" windowWidth="25755" windowHeight="14940" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1275" yWindow="1260" windowWidth="25755" windowHeight="14940" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Options" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Role Description" sheetId="11" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Options!$O$1:$O$1463</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Options!$O$1:$O$1469</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3588" uniqueCount="3266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3609" uniqueCount="3283">
   <si>
     <t>English</t>
   </si>
@@ -11640,10 +11640,76 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>Poltergeist</t>
+  </si>
+  <si>
+    <t>PoltergeistIntroDesc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PoltergeistShortDesc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>捣蛋鬼</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>尸体会在哪里呢</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>捣蛋鬼 (幽灵职业)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Poltergeist (Ghost)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PoltergeistOptions</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>poltergeistCooldown</t>
+  </si>
+  <si>
+    <t>poltergeistRadius</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能冷却</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能使用范围</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>poltergeistButton</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Poltergeist</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PoltergeistFullDesc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>捣蛋鬼可以移动附近的某一具尸体到自己脚下。
+默认范围 x 0.75 (1倍为正常报告范围)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>在会议中可以揭示身份，获得一次在会议中击杀玩家的机会。且无法被猜测
 同时，如果狼之主使用赌怪能力则本轮会议无法揭示身份。
-（猎杀和赌怪一次会议只能用一个能力）
-职业创意来自：尕丶天堂</t>
+（猎杀和赌怪一次会议只能用一个能力）</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -12243,7 +12309,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1760"/>
+  <dimension ref="A1:Q1766"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40.375" style="2" customWidth="1"/>
@@ -17207,1284 +17273,1253 @@
         <v>2886</v>
       </c>
     </row>
-    <row r="526" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O526" s="2"/>
-    </row>
     <row r="527" spans="1:15" ht="24.95" customHeight="1">
       <c r="A527" s="2" t="s">
-        <v>801</v>
+        <v>3272</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="O527" s="2" t="s">
-        <v>803</v>
+        <v>3271</v>
+      </c>
+      <c r="O527" s="3" t="s">
+        <v>3270</v>
       </c>
     </row>
     <row r="528" spans="1:15" ht="24.95" customHeight="1">
       <c r="A528" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="B528" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="O528" s="2" t="s">
-        <v>519</v>
+        <v>3273</v>
+      </c>
+      <c r="O528" s="3" t="s">
+        <v>3275</v>
       </c>
     </row>
     <row r="529" spans="1:15" ht="24.95" customHeight="1">
       <c r="A529" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="B529" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="O529" s="2" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="530" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A530" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="B530" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="O530" s="2" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="531" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O531" s="2"/>
+        <v>3274</v>
+      </c>
+      <c r="O529" s="3" t="s">
+        <v>3276</v>
+      </c>
     </row>
     <row r="532" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A532" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="B532" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="O532" s="2" t="s">
-        <v>812</v>
-      </c>
+      <c r="O532" s="2"/>
     </row>
     <row r="533" spans="1:15" ht="24.95" customHeight="1">
       <c r="A533" s="2" t="s">
-        <v>816</v>
+        <v>801</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>817</v>
+        <v>802</v>
       </c>
       <c r="O533" s="2" t="s">
-        <v>818</v>
+        <v>803</v>
       </c>
     </row>
     <row r="534" spans="1:15" ht="24.95" customHeight="1">
       <c r="A534" s="2" t="s">
-        <v>819</v>
+        <v>804</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="O534" s="2" t="s">
-        <v>821</v>
+        <v>519</v>
       </c>
     </row>
     <row r="535" spans="1:15" ht="24.95" customHeight="1">
       <c r="A535" s="2" t="s">
-        <v>2419</v>
+        <v>806</v>
+      </c>
+      <c r="B535" s="2" t="s">
+        <v>807</v>
       </c>
       <c r="O535" s="2" t="s">
-        <v>2420</v>
+        <v>808</v>
       </c>
     </row>
     <row r="536" spans="1:15" ht="24.95" customHeight="1">
       <c r="A536" s="2" t="s">
-        <v>822</v>
+        <v>809</v>
+      </c>
+      <c r="B536" s="2" t="s">
+        <v>530</v>
       </c>
       <c r="O536" s="2" t="s">
-        <v>823</v>
+        <v>531</v>
       </c>
     </row>
     <row r="537" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A537" s="2" t="s">
-        <v>2292</v>
-      </c>
-      <c r="O537" s="2" t="s">
-        <v>2466</v>
-      </c>
+      <c r="O537" s="2"/>
     </row>
     <row r="538" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O538" s="2"/>
+      <c r="A538" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="B538" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="O538" s="2" t="s">
+        <v>812</v>
+      </c>
     </row>
     <row r="539" spans="1:15" ht="24.95" customHeight="1">
       <c r="A539" s="2" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>1669</v>
+        <v>817</v>
       </c>
       <c r="O539" s="2" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
     </row>
     <row r="540" spans="1:15" ht="24.95" customHeight="1">
       <c r="A540" s="2" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="O540" s="2" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
     </row>
     <row r="541" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O541" s="2"/>
+      <c r="A541" s="2" t="s">
+        <v>2419</v>
+      </c>
+      <c r="O541" s="2" t="s">
+        <v>2420</v>
+      </c>
     </row>
     <row r="542" spans="1:15" ht="24.95" customHeight="1">
       <c r="A542" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="B542" s="2" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="O542" s="2" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
     </row>
     <row r="543" spans="1:15" ht="24.95" customHeight="1">
       <c r="A543" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="B543" s="2" t="s">
-        <v>830</v>
+        <v>2292</v>
       </c>
       <c r="O543" s="2" t="s">
-        <v>831</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="544" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A544" s="2" t="s">
-        <v>832</v>
-      </c>
-      <c r="B544" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="O544" s="2" t="s">
-        <v>2465</v>
-      </c>
+      <c r="O544" s="2"/>
     </row>
     <row r="545" spans="1:15" ht="24.95" customHeight="1">
       <c r="A545" s="2" t="s">
-        <v>1666</v>
+        <v>824</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="O545" s="2" t="s">
-        <v>1667</v>
+        <v>825</v>
       </c>
     </row>
     <row r="546" spans="1:15" ht="24.95" customHeight="1">
       <c r="A546" s="2" t="s">
-        <v>834</v>
+        <v>813</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>835</v>
+        <v>814</v>
       </c>
       <c r="O546" s="2" t="s">
-        <v>836</v>
+        <v>815</v>
       </c>
     </row>
     <row r="547" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A547" s="2" t="s">
-        <v>837</v>
-      </c>
-      <c r="B547" s="2" t="s">
-        <v>838</v>
-      </c>
-      <c r="O547" s="2" t="s">
-        <v>839</v>
-      </c>
+      <c r="O547" s="2"/>
     </row>
     <row r="548" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O548" s="2"/>
+      <c r="A548" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B548" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="O548" s="2" t="s">
+        <v>828</v>
+      </c>
     </row>
     <row r="549" spans="1:15" ht="24.95" customHeight="1">
       <c r="A549" s="2" t="s">
-        <v>840</v>
+        <v>829</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>841</v>
+        <v>830</v>
       </c>
       <c r="O549" s="2" t="s">
-        <v>842</v>
+        <v>831</v>
       </c>
     </row>
     <row r="550" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O550" s="2"/>
+      <c r="A550" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="B550" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="O550" s="2" t="s">
+        <v>2465</v>
+      </c>
     </row>
     <row r="551" spans="1:15" ht="24.95" customHeight="1">
       <c r="A551" s="2" t="s">
-        <v>843</v>
+        <v>1666</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>844</v>
+        <v>1668</v>
       </c>
       <c r="O551" s="2" t="s">
-        <v>845</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="552" spans="1:15" ht="24.95" customHeight="1">
       <c r="A552" s="2" t="s">
-        <v>846</v>
+        <v>834</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>847</v>
+        <v>835</v>
       </c>
       <c r="O552" s="2" t="s">
-        <v>848</v>
+        <v>836</v>
       </c>
     </row>
     <row r="553" spans="1:15" ht="24.95" customHeight="1">
       <c r="A553" s="2" t="s">
-        <v>849</v>
+        <v>837</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>850</v>
+        <v>838</v>
       </c>
       <c r="O553" s="2" t="s">
-        <v>851</v>
+        <v>839</v>
       </c>
     </row>
     <row r="554" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A554" s="2" t="s">
-        <v>852</v>
-      </c>
-      <c r="B554" s="2" t="s">
-        <v>853</v>
-      </c>
-      <c r="O554" s="2" t="s">
-        <v>854</v>
-      </c>
+      <c r="O554" s="2"/>
     </row>
     <row r="555" spans="1:15" ht="24.95" customHeight="1">
       <c r="A555" s="2" t="s">
-        <v>855</v>
+        <v>840</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>856</v>
+        <v>841</v>
       </c>
       <c r="O555" s="2" t="s">
-        <v>857</v>
+        <v>842</v>
       </c>
     </row>
     <row r="556" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A556" s="2" t="s">
-        <v>858</v>
-      </c>
-      <c r="B556" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="O556" s="2" t="s">
-        <v>859</v>
-      </c>
+      <c r="O556" s="2"/>
     </row>
     <row r="557" spans="1:15" ht="24.95" customHeight="1">
       <c r="A557" s="2" t="s">
-        <v>860</v>
+        <v>843</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>1794</v>
+        <v>844</v>
       </c>
       <c r="O557" s="2" t="s">
-        <v>1793</v>
+        <v>845</v>
       </c>
     </row>
     <row r="558" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O558" s="2"/>
+      <c r="A558" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="B558" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="O558" s="2" t="s">
+        <v>848</v>
+      </c>
     </row>
     <row r="559" spans="1:15" ht="24.95" customHeight="1">
       <c r="A559" s="2" t="s">
-        <v>861</v>
+        <v>849</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>862</v>
+        <v>850</v>
       </c>
       <c r="O559" s="2" t="s">
-        <v>863</v>
+        <v>851</v>
       </c>
     </row>
     <row r="560" spans="1:15" ht="24.95" customHeight="1">
       <c r="A560" s="2" t="s">
-        <v>864</v>
+        <v>852</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>865</v>
+        <v>853</v>
       </c>
       <c r="O560" s="2" t="s">
-        <v>866</v>
+        <v>854</v>
       </c>
     </row>
     <row r="561" spans="1:15" ht="24.95" customHeight="1">
       <c r="A561" s="2" t="s">
-        <v>867</v>
+        <v>855</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>868</v>
+        <v>856</v>
       </c>
       <c r="O561" s="2" t="s">
-        <v>869</v>
+        <v>857</v>
       </c>
     </row>
     <row r="562" spans="1:15" ht="24.95" customHeight="1">
       <c r="A562" s="2" t="s">
-        <v>870</v>
+        <v>858</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>871</v>
+        <v>651</v>
       </c>
       <c r="O562" s="2" t="s">
-        <v>872</v>
+        <v>859</v>
       </c>
     </row>
     <row r="563" spans="1:15" ht="24.95" customHeight="1">
       <c r="A563" s="2" t="s">
-        <v>873</v>
+        <v>860</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>874</v>
+        <v>1794</v>
       </c>
       <c r="O563" s="2" t="s">
-        <v>875</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="564" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A564" s="2" t="s">
-        <v>876</v>
-      </c>
-      <c r="B564" s="2" t="s">
-        <v>877</v>
-      </c>
-      <c r="O564" s="2" t="s">
-        <v>878</v>
-      </c>
+      <c r="O564" s="2"/>
     </row>
     <row r="565" spans="1:15" ht="24.95" customHeight="1">
       <c r="A565" s="2" t="s">
-        <v>879</v>
+        <v>861</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>880</v>
+        <v>862</v>
       </c>
       <c r="O565" s="2" t="s">
-        <v>881</v>
+        <v>863</v>
       </c>
     </row>
     <row r="566" spans="1:15" ht="24.95" customHeight="1">
       <c r="A566" s="2" t="s">
-        <v>882</v>
+        <v>864</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>883</v>
+        <v>865</v>
       </c>
       <c r="O566" s="2" t="s">
-        <v>884</v>
+        <v>866</v>
       </c>
     </row>
     <row r="567" spans="1:15" ht="24.95" customHeight="1">
       <c r="A567" s="2" t="s">
-        <v>885</v>
+        <v>867</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>886</v>
+        <v>868</v>
       </c>
       <c r="O567" s="2" t="s">
-        <v>887</v>
+        <v>869</v>
       </c>
     </row>
     <row r="568" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O568" s="2"/>
+      <c r="A568" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="B568" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="O568" s="2" t="s">
+        <v>872</v>
+      </c>
     </row>
     <row r="569" spans="1:15" ht="24.95" customHeight="1">
       <c r="A569" s="2" t="s">
-        <v>1779</v>
+        <v>873</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>888</v>
+        <v>874</v>
       </c>
       <c r="O569" s="2" t="s">
-        <v>889</v>
+        <v>875</v>
       </c>
     </row>
     <row r="570" spans="1:15" ht="24.95" customHeight="1">
       <c r="A570" s="2" t="s">
-        <v>1780</v>
+        <v>876</v>
+      </c>
+      <c r="B570" s="2" t="s">
+        <v>877</v>
       </c>
       <c r="O570" s="2" t="s">
-        <v>1781</v>
+        <v>878</v>
       </c>
     </row>
     <row r="571" spans="1:15" ht="24.95" customHeight="1">
       <c r="A571" s="2" t="s">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>891</v>
+        <v>880</v>
       </c>
       <c r="O571" s="2" t="s">
-        <v>892</v>
+        <v>881</v>
       </c>
     </row>
     <row r="572" spans="1:15" ht="24.95" customHeight="1">
       <c r="A572" s="2" t="s">
-        <v>893</v>
+        <v>882</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>894</v>
+        <v>883</v>
       </c>
       <c r="O572" s="2" t="s">
-        <v>895</v>
+        <v>884</v>
       </c>
     </row>
     <row r="573" spans="1:15" ht="24.95" customHeight="1">
       <c r="A573" s="2" t="s">
-        <v>896</v>
+        <v>885</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>897</v>
+        <v>886</v>
       </c>
       <c r="O573" s="2" t="s">
-        <v>898</v>
+        <v>887</v>
       </c>
     </row>
     <row r="574" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A574" s="2" t="s">
-        <v>899</v>
-      </c>
-      <c r="B574" s="2" t="s">
-        <v>1774</v>
-      </c>
-      <c r="O574" s="2" t="s">
-        <v>900</v>
-      </c>
+      <c r="O574" s="2"/>
     </row>
     <row r="575" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O575" s="2"/>
+      <c r="A575" s="2" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B575" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="O575" s="2" t="s">
+        <v>889</v>
+      </c>
     </row>
     <row r="576" spans="1:15" ht="24.95" customHeight="1">
       <c r="A576" s="2" t="s">
-        <v>901</v>
-      </c>
-      <c r="B576" s="2" t="s">
-        <v>902</v>
+        <v>1780</v>
       </c>
       <c r="O576" s="2" t="s">
-        <v>903</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="577" spans="1:15" ht="24.95" customHeight="1">
       <c r="A577" s="2" t="s">
-        <v>904</v>
+        <v>890</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>905</v>
+        <v>891</v>
       </c>
       <c r="O577" s="2" t="s">
-        <v>906</v>
+        <v>892</v>
       </c>
     </row>
     <row r="578" spans="1:15" ht="24.95" customHeight="1">
       <c r="A578" s="2" t="s">
-        <v>907</v>
+        <v>893</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>908</v>
+        <v>894</v>
       </c>
       <c r="O578" s="2" t="s">
-        <v>909</v>
+        <v>895</v>
       </c>
     </row>
     <row r="579" spans="1:15" ht="24.95" customHeight="1">
       <c r="A579" s="2" t="s">
-        <v>910</v>
+        <v>896</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>911</v>
+        <v>897</v>
       </c>
       <c r="O579" s="2" t="s">
-        <v>912</v>
+        <v>898</v>
       </c>
     </row>
     <row r="580" spans="1:15" ht="24.95" customHeight="1">
       <c r="A580" s="2" t="s">
-        <v>913</v>
+        <v>899</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>914</v>
+        <v>1774</v>
       </c>
       <c r="O580" s="2" t="s">
-        <v>915</v>
+        <v>900</v>
       </c>
     </row>
     <row r="581" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A581" s="2" t="s">
-        <v>2287</v>
-      </c>
-      <c r="B581" s="2" t="s">
-        <v>932</v>
-      </c>
-      <c r="O581" s="2" t="s">
-        <v>918</v>
-      </c>
+      <c r="O581" s="2"/>
     </row>
     <row r="582" spans="1:15" ht="24.95" customHeight="1">
       <c r="A582" s="2" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>917</v>
+        <v>902</v>
       </c>
       <c r="O582" s="2" t="s">
-        <v>2288</v>
+        <v>903</v>
       </c>
     </row>
     <row r="583" spans="1:15" ht="24.95" customHeight="1">
       <c r="A583" s="2" t="s">
-        <v>919</v>
+        <v>904</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>920</v>
+        <v>905</v>
       </c>
       <c r="O583" s="2" t="s">
-        <v>921</v>
+        <v>906</v>
       </c>
     </row>
     <row r="584" spans="1:15" ht="24.95" customHeight="1">
       <c r="A584" s="2" t="s">
-        <v>922</v>
+        <v>907</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>923</v>
+        <v>908</v>
       </c>
       <c r="O584" s="2" t="s">
-        <v>924</v>
+        <v>909</v>
       </c>
     </row>
     <row r="585" spans="1:15" ht="24.95" customHeight="1">
       <c r="A585" s="2" t="s">
-        <v>1782</v>
+        <v>910</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>925</v>
+        <v>911</v>
       </c>
       <c r="O585" s="2" t="s">
-        <v>926</v>
+        <v>912</v>
       </c>
     </row>
     <row r="586" spans="1:15" ht="24.95" customHeight="1">
       <c r="A586" s="2" t="s">
-        <v>927</v>
-      </c>
-      <c r="B586" s="3" t="s">
-        <v>2289</v>
+        <v>913</v>
+      </c>
+      <c r="B586" s="2" t="s">
+        <v>914</v>
       </c>
       <c r="O586" s="2" t="s">
-        <v>928</v>
+        <v>915</v>
       </c>
     </row>
     <row r="587" spans="1:15" ht="24.95" customHeight="1">
       <c r="A587" s="2" t="s">
-        <v>929</v>
+        <v>2287</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="O587" s="2" t="s">
-        <v>931</v>
+        <v>918</v>
       </c>
     </row>
     <row r="588" spans="1:15" ht="24.95" customHeight="1">
       <c r="A588" s="2" t="s">
-        <v>933</v>
+        <v>916</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>897</v>
+        <v>917</v>
       </c>
       <c r="O588" s="2" t="s">
-        <v>934</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="589" spans="1:15" ht="24.95" customHeight="1">
       <c r="A589" s="2" t="s">
-        <v>935</v>
+        <v>919</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>2290</v>
+        <v>920</v>
       </c>
       <c r="O589" s="2" t="s">
-        <v>936</v>
+        <v>921</v>
       </c>
     </row>
     <row r="590" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O590" s="2"/>
+      <c r="A590" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="B590" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="O590" s="2" t="s">
+        <v>924</v>
+      </c>
     </row>
     <row r="591" spans="1:15" ht="24.95" customHeight="1">
       <c r="A591" s="2" t="s">
-        <v>941</v>
+        <v>1782</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>942</v>
+        <v>925</v>
       </c>
       <c r="O591" s="2" t="s">
-        <v>943</v>
+        <v>926</v>
       </c>
     </row>
     <row r="592" spans="1:15" ht="24.95" customHeight="1">
       <c r="A592" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="B592" s="2" t="s">
-        <v>945</v>
+        <v>927</v>
+      </c>
+      <c r="B592" s="3" t="s">
+        <v>2289</v>
       </c>
       <c r="O592" s="2" t="s">
-        <v>946</v>
+        <v>928</v>
       </c>
     </row>
     <row r="593" spans="1:15" ht="24.95" customHeight="1">
       <c r="A593" s="2" t="s">
-        <v>947</v>
+        <v>929</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>948</v>
+        <v>930</v>
       </c>
       <c r="O593" s="2" t="s">
-        <v>949</v>
+        <v>931</v>
       </c>
     </row>
     <row r="594" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O594" s="2"/>
+      <c r="A594" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="B594" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="O594" s="2" t="s">
+        <v>934</v>
+      </c>
     </row>
     <row r="595" spans="1:15" ht="24.95" customHeight="1">
       <c r="A595" s="2" t="s">
-        <v>1675</v>
+        <v>935</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>950</v>
+        <v>2290</v>
       </c>
       <c r="O595" s="2" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
     </row>
     <row r="596" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A596" s="2" t="s">
-        <v>1676</v>
-      </c>
-      <c r="B596" s="2" t="s">
-        <v>952</v>
-      </c>
-      <c r="O596" s="2" t="s">
-        <v>953</v>
-      </c>
+      <c r="O596" s="2"/>
     </row>
     <row r="597" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O597" s="2"/>
+      <c r="A597" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B597" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="O597" s="2" t="s">
+        <v>943</v>
+      </c>
     </row>
     <row r="598" spans="1:15" ht="24.95" customHeight="1">
       <c r="A598" s="2" t="s">
-        <v>954</v>
+        <v>944</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>955</v>
+        <v>945</v>
       </c>
       <c r="O598" s="2" t="s">
-        <v>956</v>
+        <v>946</v>
       </c>
     </row>
     <row r="599" spans="1:15" ht="24.95" customHeight="1">
       <c r="A599" s="2" t="s">
-        <v>957</v>
+        <v>947</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>958</v>
+        <v>948</v>
       </c>
       <c r="O599" s="2" t="s">
-        <v>959</v>
+        <v>949</v>
       </c>
     </row>
     <row r="600" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A600" s="2" t="s">
-        <v>960</v>
-      </c>
-      <c r="B600" s="2" t="s">
-        <v>961</v>
-      </c>
-      <c r="O600" s="2" t="s">
-        <v>962</v>
-      </c>
+      <c r="O600" s="2"/>
     </row>
     <row r="601" spans="1:15" ht="24.95" customHeight="1">
       <c r="A601" s="2" t="s">
-        <v>963</v>
+        <v>1675</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="O601" s="2" t="s">
-        <v>965</v>
+        <v>951</v>
       </c>
     </row>
     <row r="602" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O602" s="2"/>
+      <c r="A602" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B602" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="O602" s="2" t="s">
+        <v>953</v>
+      </c>
     </row>
     <row r="603" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A603" s="2" t="s">
-        <v>976</v>
-      </c>
-      <c r="B603" s="2" t="s">
-        <v>977</v>
-      </c>
-      <c r="O603" s="2" t="s">
-        <v>978</v>
-      </c>
+      <c r="O603" s="2"/>
     </row>
     <row r="604" spans="1:15" ht="24.95" customHeight="1">
       <c r="A604" s="2" t="s">
-        <v>979</v>
+        <v>954</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>980</v>
+        <v>955</v>
       </c>
       <c r="O604" s="2" t="s">
-        <v>981</v>
+        <v>956</v>
       </c>
     </row>
     <row r="605" spans="1:15" ht="24.95" customHeight="1">
       <c r="A605" s="2" t="s">
-        <v>982</v>
+        <v>957</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>983</v>
+        <v>958</v>
       </c>
       <c r="O605" s="2" t="s">
-        <v>984</v>
+        <v>959</v>
       </c>
     </row>
     <row r="606" spans="1:15" ht="24.95" customHeight="1">
       <c r="A606" s="2" t="s">
-        <v>985</v>
+        <v>960</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>986</v>
+        <v>961</v>
       </c>
       <c r="O606" s="2" t="s">
-        <v>987</v>
+        <v>962</v>
       </c>
     </row>
     <row r="607" spans="1:15" ht="24.95" customHeight="1">
       <c r="A607" s="2" t="s">
-        <v>988</v>
+        <v>963</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>989</v>
+        <v>964</v>
       </c>
       <c r="O607" s="2" t="s">
-        <v>990</v>
+        <v>965</v>
       </c>
     </row>
     <row r="608" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A608" s="2" t="s">
-        <v>991</v>
-      </c>
-      <c r="B608" s="2" t="s">
-        <v>992</v>
-      </c>
-      <c r="O608" s="2" t="s">
-        <v>993</v>
-      </c>
+      <c r="O608" s="2"/>
     </row>
     <row r="609" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O609" s="2"/>
+      <c r="A609" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="B609" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="O609" s="2" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="610" spans="1:15" ht="24.95" customHeight="1">
       <c r="A610" s="2" t="s">
-        <v>994</v>
+        <v>979</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>995</v>
+        <v>980</v>
       </c>
       <c r="O610" s="2" t="s">
-        <v>996</v>
+        <v>981</v>
       </c>
     </row>
     <row r="611" spans="1:15" ht="24.95" customHeight="1">
       <c r="A611" s="2" t="s">
-        <v>997</v>
+        <v>982</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>998</v>
+        <v>983</v>
       </c>
       <c r="O611" s="2" t="s">
-        <v>999</v>
+        <v>984</v>
       </c>
     </row>
     <row r="612" spans="1:15" ht="24.95" customHeight="1">
       <c r="A612" s="2" t="s">
-        <v>1000</v>
+        <v>985</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>1001</v>
+        <v>986</v>
       </c>
       <c r="O612" s="2" t="s">
-        <v>1002</v>
+        <v>987</v>
       </c>
     </row>
     <row r="613" spans="1:15" ht="24.95" customHeight="1">
       <c r="A613" s="2" t="s">
-        <v>1003</v>
+        <v>988</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>1004</v>
+        <v>989</v>
       </c>
       <c r="O613" s="2" t="s">
-        <v>1005</v>
+        <v>990</v>
       </c>
     </row>
     <row r="614" spans="1:15" ht="24.95" customHeight="1">
       <c r="A614" s="2" t="s">
-        <v>1006</v>
+        <v>991</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>964</v>
+        <v>992</v>
       </c>
       <c r="O614" s="2" t="s">
-        <v>965</v>
+        <v>993</v>
       </c>
     </row>
     <row r="615" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A615" s="2" t="s">
-        <v>1007</v>
-      </c>
-      <c r="B615" s="2" t="s">
-        <v>1008</v>
-      </c>
-      <c r="O615" s="2" t="s">
-        <v>1009</v>
-      </c>
+      <c r="O615" s="2"/>
     </row>
     <row r="616" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O616" s="2"/>
+      <c r="A616" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B616" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="O616" s="2" t="s">
+        <v>996</v>
+      </c>
     </row>
     <row r="617" spans="1:15" ht="24.95" customHeight="1">
       <c r="A617" s="2" t="s">
-        <v>1010</v>
+        <v>997</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>1011</v>
+        <v>998</v>
       </c>
       <c r="O617" s="2" t="s">
-        <v>633</v>
+        <v>999</v>
       </c>
     </row>
     <row r="618" spans="1:15" ht="24.95" customHeight="1">
       <c r="A618" s="2" t="s">
-        <v>1012</v>
+        <v>1000</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>1013</v>
+        <v>1001</v>
       </c>
       <c r="O618" s="2" t="s">
-        <v>1014</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="619" spans="1:15" ht="24.95" customHeight="1">
       <c r="A619" s="2" t="s">
-        <v>1015</v>
+        <v>1003</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>1016</v>
+        <v>1004</v>
       </c>
       <c r="O619" s="2" t="s">
-        <v>1017</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="620" spans="1:15" ht="24.95" customHeight="1">
       <c r="A620" s="2" t="s">
-        <v>1018</v>
+        <v>1006</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>1019</v>
+        <v>964</v>
       </c>
       <c r="O620" s="2" t="s">
-        <v>1020</v>
+        <v>965</v>
       </c>
     </row>
     <row r="621" spans="1:15" ht="24.95" customHeight="1">
       <c r="A621" s="2" t="s">
-        <v>1021</v>
+        <v>1007</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>1022</v>
+        <v>1008</v>
       </c>
       <c r="O621" s="2" t="s">
-        <v>1023</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="622" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A622" s="2" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B622" s="2" t="s">
-        <v>1025</v>
-      </c>
-      <c r="O622" s="2" t="s">
-        <v>1026</v>
-      </c>
+      <c r="O622" s="2"/>
     </row>
     <row r="623" spans="1:15" ht="24.95" customHeight="1">
       <c r="A623" s="2" t="s">
-        <v>1027</v>
+        <v>1010</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>1028</v>
+        <v>1011</v>
       </c>
       <c r="O623" s="2" t="s">
-        <v>1029</v>
+        <v>633</v>
       </c>
     </row>
     <row r="624" spans="1:15" ht="24.95" customHeight="1">
       <c r="A624" s="2" t="s">
-        <v>1030</v>
+        <v>1012</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>1031</v>
+        <v>1013</v>
       </c>
       <c r="O624" s="2" t="s">
-        <v>1032</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="625" spans="1:15" ht="24.95" customHeight="1">
       <c r="A625" s="2" t="s">
-        <v>1033</v>
+        <v>1015</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>1034</v>
+        <v>1016</v>
       </c>
       <c r="O625" s="2" t="s">
-        <v>1035</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="626" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O626" s="2"/>
+      <c r="A626" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B626" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="O626" s="2" t="s">
+        <v>1020</v>
+      </c>
     </row>
     <row r="627" spans="1:15" ht="24.95" customHeight="1">
       <c r="A627" s="2" t="s">
-        <v>1036</v>
+        <v>1021</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>1037</v>
+        <v>1022</v>
       </c>
       <c r="O627" s="2" t="s">
-        <v>1038</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="628" spans="1:15" ht="24.95" customHeight="1">
       <c r="A628" s="2" t="s">
-        <v>1039</v>
+        <v>1024</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>1040</v>
+        <v>1025</v>
       </c>
       <c r="O628" s="2" t="s">
-        <v>1041</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="629" spans="1:15" ht="24.95" customHeight="1">
       <c r="A629" s="2" t="s">
-        <v>1042</v>
+        <v>1027</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>1043</v>
+        <v>1028</v>
       </c>
       <c r="O629" s="2" t="s">
-        <v>2291</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="630" spans="1:15" ht="24.95" customHeight="1">
       <c r="A630" s="2" t="s">
-        <v>1044</v>
+        <v>1030</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>1045</v>
+        <v>1031</v>
       </c>
       <c r="O630" s="2" t="s">
-        <v>1046</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="631" spans="1:15" ht="24.95" customHeight="1">
       <c r="A631" s="2" t="s">
-        <v>1047</v>
+        <v>1033</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>1048</v>
+        <v>1034</v>
       </c>
       <c r="O631" s="2" t="s">
-        <v>1049</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="632" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A632" s="2" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B632" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="O632" s="2" t="s">
-        <v>1051</v>
-      </c>
+      <c r="O632" s="2"/>
     </row>
     <row r="633" spans="1:15" ht="24.95" customHeight="1">
       <c r="A633" s="2" t="s">
-        <v>1052</v>
+        <v>1036</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>1053</v>
+        <v>1037</v>
       </c>
       <c r="O633" s="2" t="s">
-        <v>1054</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="634" spans="1:15" ht="24.95" customHeight="1">
       <c r="A634" s="2" t="s">
-        <v>1055</v>
+        <v>1039</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>1056</v>
+        <v>1040</v>
       </c>
       <c r="O634" s="2" t="s">
-        <v>1057</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="635" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O635" s="2"/>
+      <c r="A635" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B635" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="O635" s="2" t="s">
+        <v>2291</v>
+      </c>
     </row>
     <row r="636" spans="1:15" ht="24.95" customHeight="1">
       <c r="A636" s="2" t="s">
-        <v>1058</v>
+        <v>1044</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>1764</v>
+        <v>1045</v>
       </c>
       <c r="O636" s="2" t="s">
-        <v>1059</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="637" spans="1:15" ht="24.95" customHeight="1">
       <c r="A637" s="2" t="s">
-        <v>1060</v>
+        <v>1047</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>1765</v>
+        <v>1048</v>
       </c>
       <c r="O637" s="2" t="s">
-        <v>1061</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="638" spans="1:15" ht="24.95" customHeight="1">
       <c r="A638" s="2" t="s">
-        <v>1062</v>
+        <v>1050</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>1772</v>
+        <v>66</v>
       </c>
       <c r="O638" s="2" t="s">
-        <v>1063</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="639" spans="1:15" ht="24.95" customHeight="1">
       <c r="A639" s="2" t="s">
-        <v>1064</v>
+        <v>1052</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>1771</v>
+        <v>1053</v>
       </c>
       <c r="O639" s="2" t="s">
-        <v>1065</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="640" spans="1:15" ht="24.95" customHeight="1">
       <c r="A640" s="2" t="s">
-        <v>1066</v>
+        <v>1055</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>1768</v>
+        <v>1056</v>
       </c>
       <c r="O640" s="2" t="s">
-        <v>1710</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="641" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A641" s="2" t="s">
-        <v>1769</v>
-      </c>
-      <c r="B641" s="2" t="s">
-        <v>1770</v>
-      </c>
-      <c r="O641" s="2" t="s">
-        <v>1709</v>
-      </c>
+      <c r="O641" s="2"/>
     </row>
     <row r="642" spans="1:15" ht="24.95" customHeight="1">
       <c r="A642" s="2" t="s">
-        <v>1067</v>
+        <v>1058</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="O642" s="2" t="s">
-        <v>1708</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="643" spans="1:15" ht="24.95" customHeight="1">
       <c r="A643" s="2" t="s">
-        <v>1068</v>
+        <v>1060</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="O643" s="2" t="s">
-        <v>1707</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="644" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O644" s="2"/>
+      <c r="A644" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B644" s="2" t="s">
+        <v>1772</v>
+      </c>
+      <c r="O644" s="2" t="s">
+        <v>1063</v>
+      </c>
     </row>
     <row r="645" spans="1:15" ht="24.95" customHeight="1">
       <c r="A645" s="2" t="s">
-        <v>1832</v>
+        <v>1064</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>1822</v>
+        <v>1771</v>
       </c>
       <c r="O645" s="2" t="s">
-        <v>1839</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="646" spans="1:15" ht="24.95" customHeight="1">
       <c r="A646" s="2" t="s">
-        <v>1833</v>
+        <v>1066</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>1835</v>
+        <v>1768</v>
       </c>
       <c r="O646" s="2" t="s">
-        <v>1837</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="647" spans="1:15" ht="24.95" customHeight="1">
       <c r="A647" s="2" t="s">
-        <v>1834</v>
+        <v>1769</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>1836</v>
+        <v>1770</v>
       </c>
       <c r="O647" s="2" t="s">
-        <v>1838</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="648" spans="1:15" ht="24.95" customHeight="1">
       <c r="A648" s="2" t="s">
-        <v>1840</v>
+        <v>1067</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>1841</v>
+        <v>1766</v>
       </c>
       <c r="O648" s="2" t="s">
-        <v>1842</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="649" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O649" s="2"/>
+      <c r="A649" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B649" s="2" t="s">
+        <v>1767</v>
+      </c>
+      <c r="O649" s="2" t="s">
+        <v>1707</v>
+      </c>
     </row>
     <row r="650" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A650" s="2" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B650" s="2" t="s">
-        <v>1070</v>
-      </c>
-      <c r="O650" s="2" t="s">
-        <v>3030</v>
-      </c>
+      <c r="O650" s="2"/>
     </row>
     <row r="651" spans="1:15" ht="24.95" customHeight="1">
       <c r="A651" s="2" t="s">
-        <v>1071</v>
+        <v>1832</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>1072</v>
+        <v>1822</v>
       </c>
       <c r="O651" s="2" t="s">
-        <v>1073</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="652" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O652" s="2"/>
+      <c r="A652" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B652" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="O652" s="2" t="s">
+        <v>1837</v>
+      </c>
     </row>
     <row r="653" spans="1:15" ht="24.95" customHeight="1">
       <c r="A653" s="2" t="s">
-        <v>1074</v>
+        <v>1834</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>1075</v>
+        <v>1836</v>
       </c>
       <c r="O653" s="2" t="s">
-        <v>1076</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="654" spans="1:15" ht="24.95" customHeight="1">
       <c r="A654" s="2" t="s">
-        <v>1077</v>
+        <v>1840</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1078</v>
+        <v>1841</v>
       </c>
       <c r="O654" s="2" t="s">
-        <v>1079</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="655" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A655" s="2" t="s">
-        <v>1080</v>
-      </c>
-      <c r="B655" s="2" t="s">
-        <v>1081</v>
-      </c>
-      <c r="O655" s="2" t="s">
-        <v>1082</v>
-      </c>
+      <c r="O655" s="2"/>
     </row>
     <row r="656" spans="1:15" ht="24.95" customHeight="1">
       <c r="A656" s="2" t="s">
-        <v>1083</v>
+        <v>1069</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>1084</v>
+        <v>1070</v>
       </c>
       <c r="O656" s="2" t="s">
-        <v>1085</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="657" spans="1:15" ht="24.95" customHeight="1">
       <c r="A657" s="2" t="s">
-        <v>1086</v>
+        <v>1071</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>1087</v>
+        <v>1072</v>
       </c>
       <c r="O657" s="2" t="s">
-        <v>1088</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="658" spans="1:15" ht="24.95" customHeight="1">
@@ -18492,441 +18527,458 @@
     </row>
     <row r="659" spans="1:15" ht="24.95" customHeight="1">
       <c r="A659" s="2" t="s">
-        <v>1089</v>
+        <v>1074</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>1090</v>
+        <v>1075</v>
       </c>
       <c r="O659" s="2" t="s">
-        <v>1091</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="660" spans="1:15" ht="24.95" customHeight="1">
       <c r="A660" s="2" t="s">
-        <v>1092</v>
+        <v>1077</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>1093</v>
+        <v>1078</v>
       </c>
       <c r="O660" s="2" t="s">
-        <v>1094</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="661" spans="1:15" ht="24.95" customHeight="1">
       <c r="A661" s="2" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="O661" s="2" t="s">
-        <v>1097</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="662" spans="1:15" ht="24.95" customHeight="1">
       <c r="A662" s="2" t="s">
-        <v>1098</v>
+        <v>1083</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>1099</v>
+        <v>1084</v>
       </c>
       <c r="O662" s="2" t="s">
-        <v>1100</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="663" spans="1:15" ht="24.95" customHeight="1">
       <c r="A663" s="2" t="s">
-        <v>1101</v>
+        <v>1086</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>1102</v>
+        <v>1087</v>
       </c>
       <c r="O663" s="2" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="664" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A664" s="2" t="s">
-        <v>1104</v>
-      </c>
-      <c r="B664" s="2" t="s">
-        <v>1105</v>
-      </c>
-      <c r="O664" s="2" t="s">
-        <v>1106</v>
-      </c>
+      <c r="O664" s="2"/>
     </row>
     <row r="665" spans="1:15" ht="24.95" customHeight="1">
       <c r="A665" s="2" t="s">
-        <v>1107</v>
+        <v>1089</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>964</v>
+        <v>1090</v>
       </c>
       <c r="O665" s="2" t="s">
-        <v>965</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="666" spans="1:15" ht="24.95" customHeight="1">
       <c r="A666" s="2" t="s">
-        <v>1108</v>
+        <v>1092</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1109</v>
+        <v>1093</v>
       </c>
       <c r="O666" s="2" t="s">
-        <v>1110</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="667" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O667" s="2"/>
+      <c r="A667" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B667" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="O667" s="2" t="s">
+        <v>1097</v>
+      </c>
     </row>
     <row r="668" spans="1:15" ht="24.95" customHeight="1">
       <c r="A668" s="2" t="s">
-        <v>1111</v>
+        <v>1098</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>1112</v>
+        <v>1099</v>
       </c>
       <c r="O668" s="2" t="s">
-        <v>1113</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="669" spans="1:15" ht="24.95" customHeight="1">
       <c r="A669" s="2" t="s">
-        <v>1114</v>
+        <v>1101</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>1115</v>
+        <v>1102</v>
       </c>
       <c r="O669" s="2" t="s">
-        <v>1116</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="670" spans="1:15" ht="24.95" customHeight="1">
       <c r="A670" s="2" t="s">
-        <v>1117</v>
+        <v>1104</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>1118</v>
+        <v>1105</v>
       </c>
       <c r="O670" s="2" t="s">
-        <v>1119</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="671" spans="1:15" ht="24.95" customHeight="1">
       <c r="A671" s="2" t="s">
-        <v>1120</v>
+        <v>1107</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>1121</v>
+        <v>964</v>
       </c>
       <c r="O671" s="2" t="s">
-        <v>1122</v>
+        <v>965</v>
       </c>
     </row>
     <row r="672" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O672" s="2"/>
+      <c r="A672" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B672" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="O672" s="2" t="s">
+        <v>1110</v>
+      </c>
     </row>
     <row r="673" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A673" s="2" t="s">
-        <v>1123</v>
-      </c>
-      <c r="B673" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="O673" s="2" t="s">
-        <v>1125</v>
-      </c>
+      <c r="O673" s="2"/>
     </row>
     <row r="674" spans="1:15" ht="24.95" customHeight="1">
       <c r="A674" s="2" t="s">
-        <v>1126</v>
+        <v>1111</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>599</v>
+        <v>1112</v>
       </c>
       <c r="O674" s="2" t="s">
-        <v>1127</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="675" spans="1:15" ht="24.95" customHeight="1">
       <c r="A675" s="2" t="s">
-        <v>2462</v>
+        <v>1114</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>601</v>
+        <v>1115</v>
       </c>
       <c r="O675" s="2" t="s">
-        <v>1128</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="676" spans="1:15" ht="24.95" customHeight="1">
       <c r="A676" s="2" t="s">
-        <v>1129</v>
+        <v>1117</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>593</v>
+        <v>1118</v>
       </c>
       <c r="O676" s="2" t="s">
-        <v>594</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="677" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O677" s="2"/>
+      <c r="A677" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B677" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="O677" s="2" t="s">
+        <v>1122</v>
+      </c>
     </row>
     <row r="678" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A678" s="2" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B678" s="2" t="s">
-        <v>920</v>
-      </c>
-      <c r="O678" s="2" t="s">
-        <v>3086</v>
-      </c>
+      <c r="O678" s="2"/>
     </row>
     <row r="679" spans="1:15" ht="24.95" customHeight="1">
       <c r="A679" s="2" t="s">
-        <v>1131</v>
+        <v>1123</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>1132</v>
+        <v>1124</v>
       </c>
       <c r="O679" s="2" t="s">
-        <v>984</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="680" spans="1:15" ht="24.95" customHeight="1">
       <c r="A680" s="2" t="s">
-        <v>1133</v>
+        <v>1126</v>
+      </c>
+      <c r="B680" s="2" t="s">
+        <v>599</v>
       </c>
       <c r="O680" s="2" t="s">
-        <v>1134</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="681" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O681" s="2"/>
+      <c r="A681" s="2" t="s">
+        <v>2462</v>
+      </c>
+      <c r="B681" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="O681" s="2" t="s">
+        <v>1128</v>
+      </c>
     </row>
     <row r="682" spans="1:15" ht="24.95" customHeight="1">
       <c r="A682" s="2" t="s">
-        <v>2525</v>
+        <v>1129</v>
+      </c>
+      <c r="B682" s="2" t="s">
+        <v>593</v>
       </c>
       <c r="O682" s="2" t="s">
-        <v>2527</v>
+        <v>594</v>
       </c>
     </row>
     <row r="683" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A683" s="2" t="s">
-        <v>2526</v>
-      </c>
-      <c r="O683" s="2" t="s">
-        <v>2528</v>
-      </c>
+      <c r="O683" s="2"/>
     </row>
     <row r="684" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O684" s="2"/>
+      <c r="A684" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B684" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="O684" s="2" t="s">
+        <v>3086</v>
+      </c>
     </row>
     <row r="685" spans="1:15" ht="24.95" customHeight="1">
       <c r="A685" s="2" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="O685" s="2" t="s">
-        <v>1137</v>
+        <v>984</v>
       </c>
     </row>
     <row r="686" spans="1:15" ht="24.95" customHeight="1">
       <c r="A686" s="2" t="s">
-        <v>1138</v>
-      </c>
-      <c r="B686" s="2" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="O686" s="2" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="687" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A687" s="2" t="s">
-        <v>1141</v>
-      </c>
-      <c r="B687" s="2" t="s">
-        <v>964</v>
-      </c>
-      <c r="O687" s="2" t="s">
-        <v>965</v>
-      </c>
+      <c r="O687" s="2"/>
     </row>
     <row r="688" spans="1:15" ht="24.95" customHeight="1">
       <c r="A688" s="2" t="s">
-        <v>1142</v>
-      </c>
-      <c r="B688" s="2" t="s">
-        <v>1143</v>
+        <v>2525</v>
       </c>
       <c r="O688" s="2" t="s">
-        <v>1144</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="689" spans="1:15" ht="24.95" customHeight="1">
       <c r="A689" s="2" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B689" s="2" t="s">
-        <v>1146</v>
+        <v>2526</v>
       </c>
       <c r="O689" s="2" t="s">
-        <v>1147</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="690" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A690" s="2" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B690" s="2" t="s">
-        <v>1821</v>
-      </c>
-      <c r="O690" s="2" t="s">
-        <v>1149</v>
-      </c>
+      <c r="O690" s="2"/>
     </row>
     <row r="691" spans="1:15" ht="24.95" customHeight="1">
       <c r="A691" s="2" t="s">
-        <v>3027</v>
+        <v>1135</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1151</v>
+        <v>1136</v>
       </c>
       <c r="O691" s="2" t="s">
-        <v>1152</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="692" spans="1:15" ht="24.95" customHeight="1">
       <c r="A692" s="2" t="s">
-        <v>1155</v>
+        <v>1138</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>1156</v>
+        <v>1139</v>
       </c>
       <c r="O692" s="2" t="s">
-        <v>1157</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="693" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O693" s="2"/>
+      <c r="A693" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B693" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="O693" s="2" t="s">
+        <v>965</v>
+      </c>
     </row>
     <row r="694" spans="1:15" ht="24.95" customHeight="1">
       <c r="A694" s="2" t="s">
-        <v>3052</v>
+        <v>1142</v>
+      </c>
+      <c r="B694" s="2" t="s">
+        <v>1143</v>
       </c>
       <c r="O694" s="2" t="s">
-        <v>3057</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="695" spans="1:15" ht="24.95" customHeight="1">
       <c r="A695" s="2" t="s">
-        <v>3053</v>
+        <v>1145</v>
+      </c>
+      <c r="B695" s="2" t="s">
+        <v>1146</v>
       </c>
       <c r="O695" s="2" t="s">
-        <v>3058</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="696" spans="1:15" ht="24.95" customHeight="1">
       <c r="A696" s="2" t="s">
-        <v>3067</v>
+        <v>1148</v>
+      </c>
+      <c r="B696" s="2" t="s">
+        <v>1821</v>
       </c>
       <c r="O696" s="2" t="s">
-        <v>3068</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="697" spans="1:15" ht="24.95" customHeight="1">
       <c r="A697" s="2" t="s">
-        <v>3054</v>
+        <v>3027</v>
+      </c>
+      <c r="B697" s="2" t="s">
+        <v>1151</v>
       </c>
       <c r="O697" s="2" t="s">
-        <v>3059</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="698" spans="1:15" ht="24.95" customHeight="1">
       <c r="A698" s="2" t="s">
-        <v>3055</v>
+        <v>1155</v>
+      </c>
+      <c r="B698" s="2" t="s">
+        <v>1156</v>
       </c>
       <c r="O698" s="2" t="s">
-        <v>3060</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="699" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A699" s="2" t="s">
-        <v>3056</v>
-      </c>
-      <c r="O699" s="2" t="s">
-        <v>3061</v>
-      </c>
+      <c r="O699" s="2"/>
     </row>
     <row r="700" spans="1:15" ht="24.95" customHeight="1">
       <c r="A700" s="2" t="s">
-        <v>3065</v>
+        <v>3052</v>
       </c>
       <c r="O700" s="2" t="s">
-        <v>3087</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="701" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O701" s="2"/>
+      <c r="A701" s="2" t="s">
+        <v>3053</v>
+      </c>
+      <c r="O701" s="2" t="s">
+        <v>3058</v>
+      </c>
     </row>
     <row r="702" spans="1:15" ht="24.95" customHeight="1">
       <c r="A702" s="2" t="s">
-        <v>1158</v>
-      </c>
-      <c r="B702" s="2" t="s">
-        <v>1761</v>
+        <v>3067</v>
       </c>
       <c r="O702" s="2" t="s">
-        <v>1159</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="703" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O703" s="2"/>
+      <c r="A703" s="2" t="s">
+        <v>3054</v>
+      </c>
+      <c r="O703" s="2" t="s">
+        <v>3059</v>
+      </c>
     </row>
     <row r="704" spans="1:15" ht="24.95" customHeight="1">
       <c r="A704" s="2" t="s">
-        <v>1160</v>
-      </c>
-      <c r="B704" s="2" t="s">
-        <v>1161</v>
+        <v>3055</v>
       </c>
       <c r="O704" s="2" t="s">
-        <v>1162</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="705" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O705" s="2"/>
+      <c r="A705" s="2" t="s">
+        <v>3056</v>
+      </c>
+      <c r="O705" s="2" t="s">
+        <v>3061</v>
+      </c>
     </row>
     <row r="706" spans="1:15" ht="24.95" customHeight="1">
       <c r="A706" s="2" t="s">
-        <v>3174</v>
+        <v>3065</v>
       </c>
       <c r="O706" s="2" t="s">
-        <v>3175</v>
+        <v>3087</v>
       </c>
     </row>
     <row r="707" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A707" s="2" t="s">
-        <v>2989</v>
-      </c>
-      <c r="O707" s="2" t="s">
-        <v>2991</v>
-      </c>
+      <c r="O707" s="2"/>
     </row>
     <row r="708" spans="1:15" ht="24.95" customHeight="1">
       <c r="A708" s="2" t="s">
-        <v>2990</v>
+        <v>1158</v>
+      </c>
+      <c r="B708" s="2" t="s">
+        <v>1761</v>
       </c>
       <c r="O708" s="2" t="s">
-        <v>2992</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="709" spans="1:15" ht="24.95" customHeight="1">
@@ -18934,290 +18986,295 @@
     </row>
     <row r="710" spans="1:15" ht="24.95" customHeight="1">
       <c r="A710" s="2" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="O710" s="2" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="711" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A711" s="2" t="s">
-        <v>1166</v>
-      </c>
-      <c r="B711" s="2" t="s">
-        <v>1167</v>
-      </c>
-      <c r="O711" s="2" t="s">
-        <v>1168</v>
-      </c>
+      <c r="O711" s="2"/>
     </row>
     <row r="712" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O712" s="2"/>
+      <c r="A712" s="2" t="s">
+        <v>3174</v>
+      </c>
+      <c r="O712" s="2" t="s">
+        <v>3175</v>
+      </c>
     </row>
     <row r="713" spans="1:15" ht="24.95" customHeight="1">
       <c r="A713" s="2" t="s">
-        <v>1169</v>
-      </c>
-      <c r="B713" s="2" t="s">
-        <v>1170</v>
+        <v>2989</v>
       </c>
       <c r="O713" s="2" t="s">
-        <v>1171</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="714" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O714" s="2"/>
+      <c r="A714" s="2" t="s">
+        <v>2990</v>
+      </c>
+      <c r="O714" s="2" t="s">
+        <v>2992</v>
+      </c>
     </row>
     <row r="715" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A715" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="O715" s="2" t="s">
-        <v>1173</v>
-      </c>
+      <c r="O715" s="2"/>
     </row>
     <row r="716" spans="1:15" ht="24.95" customHeight="1">
       <c r="A716" s="2" t="s">
-        <v>1174</v>
+        <v>1163</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>1175</v>
+        <v>1164</v>
       </c>
       <c r="O716" s="2" t="s">
-        <v>1176</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="717" spans="1:15" ht="24.95" customHeight="1">
       <c r="A717" s="2" t="s">
-        <v>1177</v>
+        <v>1166</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>1178</v>
+        <v>1167</v>
       </c>
       <c r="O717" s="2" t="s">
-        <v>1179</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="718" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A718" s="2" t="s">
-        <v>1180</v>
-      </c>
-      <c r="B718" s="2" t="s">
-        <v>1181</v>
-      </c>
-      <c r="O718" s="2" t="s">
-        <v>1182</v>
-      </c>
+      <c r="O718" s="2"/>
     </row>
     <row r="719" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O719" s="2"/>
+      <c r="A719" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B719" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="O719" s="2" t="s">
+        <v>1171</v>
+      </c>
     </row>
     <row r="720" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A720" s="2" t="s">
-        <v>1183</v>
-      </c>
-      <c r="B720" s="2" t="s">
-        <v>1184</v>
-      </c>
-      <c r="O720" s="2" t="s">
-        <v>1185</v>
-      </c>
+      <c r="O720" s="2"/>
     </row>
     <row r="721" spans="1:15" ht="24.95" customHeight="1">
       <c r="A721" s="2" t="s">
-        <v>1186</v>
-      </c>
-      <c r="B721" s="2" t="s">
-        <v>1187</v>
+        <v>1172</v>
       </c>
       <c r="O721" s="2" t="s">
-        <v>1188</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="722" spans="1:15" ht="24.95" customHeight="1">
       <c r="A722" s="2" t="s">
-        <v>1189</v>
+        <v>1174</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>1190</v>
+        <v>1175</v>
       </c>
       <c r="O722" s="2" t="s">
-        <v>1191</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="723" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O723" s="2"/>
+      <c r="A723" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B723" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="O723" s="2" t="s">
+        <v>1179</v>
+      </c>
     </row>
     <row r="724" spans="1:15" ht="24.95" customHeight="1">
       <c r="A724" s="2" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>1193</v>
+        <v>1181</v>
       </c>
       <c r="O724" s="2" t="s">
-        <v>1194</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="725" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A725" s="2" t="s">
-        <v>1195</v>
-      </c>
-      <c r="B725" s="2" t="s">
-        <v>1196</v>
-      </c>
-      <c r="O725" s="2" t="s">
-        <v>1197</v>
-      </c>
+      <c r="O725" s="2"/>
     </row>
     <row r="726" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O726" s="2"/>
+      <c r="A726" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B726" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="O726" s="2" t="s">
+        <v>1185</v>
+      </c>
     </row>
     <row r="727" spans="1:15" ht="24.95" customHeight="1">
       <c r="A727" s="2" t="s">
-        <v>1198</v>
+        <v>1186</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>1199</v>
+        <v>1187</v>
       </c>
       <c r="O727" s="2" t="s">
-        <v>1200</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="728" spans="1:15" ht="24.95" customHeight="1">
       <c r="A728" s="2" t="s">
-        <v>1201</v>
+        <v>1189</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>1202</v>
+        <v>1190</v>
       </c>
       <c r="O728" s="2" t="s">
-        <v>1203</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="729" spans="1:15" ht="24.95" customHeight="1">
       <c r="O729" s="2"/>
     </row>
-    <row r="730" spans="1:15" ht="33">
+    <row r="730" spans="1:15" ht="24.95" customHeight="1">
       <c r="A730" s="2" t="s">
-        <v>2966</v>
-      </c>
-      <c r="O730" s="3" t="s">
-        <v>2967</v>
+        <v>1192</v>
+      </c>
+      <c r="B730" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="O730" s="2" t="s">
+        <v>1194</v>
       </c>
     </row>
     <row r="731" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O731" s="2"/>
+      <c r="A731" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B731" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="O731" s="2" t="s">
+        <v>1197</v>
+      </c>
     </row>
     <row r="732" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A732" s="2" t="s">
-        <v>1204</v>
-      </c>
-      <c r="O732" s="2" t="s">
-        <v>1773</v>
-      </c>
+      <c r="O732" s="2"/>
     </row>
     <row r="733" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O733" s="2"/>
+      <c r="A733" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B733" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="O733" s="2" t="s">
+        <v>1200</v>
+      </c>
     </row>
     <row r="734" spans="1:15" ht="24.95" customHeight="1">
       <c r="A734" s="2" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="O734" s="2" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="735" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A735" s="2" t="s">
-        <v>1208</v>
-      </c>
-      <c r="B735" s="2" t="s">
-        <v>1209</v>
-      </c>
-      <c r="O735" s="2" t="s">
-        <v>1210</v>
-      </c>
-    </row>
-    <row r="736" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O736" s="2"/>
+      <c r="O735" s="2"/>
+    </row>
+    <row r="736" spans="1:15" ht="33">
+      <c r="A736" s="2" t="s">
+        <v>2966</v>
+      </c>
+      <c r="O736" s="3" t="s">
+        <v>2967</v>
+      </c>
     </row>
     <row r="737" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A737" s="2" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B737" s="2" t="s">
-        <v>1212</v>
-      </c>
-      <c r="O737" s="2" t="s">
-        <v>1213</v>
-      </c>
+      <c r="O737" s="2"/>
     </row>
     <row r="738" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O738" s="2"/>
+      <c r="A738" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="O738" s="2" t="s">
+        <v>1773</v>
+      </c>
     </row>
     <row r="739" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A739" s="2" t="s">
-        <v>1214</v>
-      </c>
-      <c r="B739" s="2" t="s">
-        <v>1215</v>
-      </c>
-      <c r="O739" s="2" t="s">
-        <v>1216</v>
-      </c>
+      <c r="O739" s="2"/>
     </row>
     <row r="740" spans="1:15" ht="24.95" customHeight="1">
       <c r="A740" s="2" t="s">
-        <v>1217</v>
+        <v>1205</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>1218</v>
+        <v>1206</v>
       </c>
       <c r="O740" s="2" t="s">
-        <v>1219</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="741" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O741" s="2"/>
+      <c r="A741" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B741" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="O741" s="2" t="s">
+        <v>1210</v>
+      </c>
     </row>
     <row r="742" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A742" s="2" t="s">
-        <v>1220</v>
-      </c>
-      <c r="B742" s="2" t="s">
-        <v>1763</v>
-      </c>
-      <c r="O742" s="2" t="s">
-        <v>1221</v>
-      </c>
+      <c r="O742" s="2"/>
     </row>
     <row r="743" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O743" s="2"/>
+      <c r="A743" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B743" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="O743" s="2" t="s">
+        <v>1213</v>
+      </c>
     </row>
     <row r="744" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A744" s="2" t="s">
-        <v>3178</v>
-      </c>
-      <c r="O744" s="2" t="s">
-        <v>3180</v>
-      </c>
+      <c r="O744" s="2"/>
     </row>
     <row r="745" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O745" s="2"/>
+      <c r="A745" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B745" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="O745" s="2" t="s">
+        <v>1216</v>
+      </c>
     </row>
     <row r="746" spans="1:15" ht="24.95" customHeight="1">
       <c r="A746" s="2" t="s">
-        <v>1222</v>
+        <v>1217</v>
+      </c>
+      <c r="B746" s="2" t="s">
+        <v>1218</v>
       </c>
       <c r="O746" s="2" t="s">
-        <v>823</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="747" spans="1:15" ht="24.95" customHeight="1">
@@ -19225,46 +19282,35 @@
     </row>
     <row r="748" spans="1:15" ht="24.95" customHeight="1">
       <c r="A748" s="2" t="s">
-        <v>3176</v>
+        <v>1220</v>
+      </c>
+      <c r="B748" s="2" t="s">
+        <v>1763</v>
       </c>
       <c r="O748" s="2" t="s">
-        <v>3177</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="749" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A749" s="2" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B749" s="2" t="s">
-        <v>1762</v>
-      </c>
-      <c r="O749" s="2" t="s">
-        <v>1224</v>
-      </c>
+      <c r="O749" s="2"/>
     </row>
     <row r="750" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O750" s="2"/>
+      <c r="A750" s="2" t="s">
+        <v>3178</v>
+      </c>
+      <c r="O750" s="2" t="s">
+        <v>3180</v>
+      </c>
     </row>
     <row r="751" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A751" s="2" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B751" s="2" t="s">
-        <v>1226</v>
-      </c>
-      <c r="O751" s="2" t="s">
-        <v>1227</v>
-      </c>
+      <c r="O751" s="2"/>
     </row>
     <row r="752" spans="1:15" ht="24.95" customHeight="1">
       <c r="A752" s="2" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B752" s="2" t="s">
-        <v>1229</v>
+        <v>1222</v>
       </c>
       <c r="O752" s="2" t="s">
-        <v>1230</v>
+        <v>823</v>
       </c>
     </row>
     <row r="753" spans="1:15" ht="24.95" customHeight="1">
@@ -19272,24 +19318,21 @@
     </row>
     <row r="754" spans="1:15" ht="24.95" customHeight="1">
       <c r="A754" s="2" t="s">
-        <v>1231</v>
-      </c>
-      <c r="B754" s="2" t="s">
-        <v>1232</v>
+        <v>3176</v>
       </c>
       <c r="O754" s="2" t="s">
-        <v>1233</v>
+        <v>3177</v>
       </c>
     </row>
     <row r="755" spans="1:15" ht="24.95" customHeight="1">
       <c r="A755" s="2" t="s">
-        <v>1234</v>
+        <v>1223</v>
       </c>
       <c r="B755" s="2" t="s">
-        <v>1235</v>
+        <v>1762</v>
       </c>
       <c r="O755" s="2" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="756" spans="1:15" ht="24.95" customHeight="1">
@@ -19297,128 +19340,160 @@
     </row>
     <row r="757" spans="1:15" ht="24.95" customHeight="1">
       <c r="A757" s="2" t="s">
-        <v>1237</v>
+        <v>1225</v>
       </c>
       <c r="B757" s="2" t="s">
-        <v>1238</v>
+        <v>1226</v>
       </c>
       <c r="O757" s="2" t="s">
-        <v>1239</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="758" spans="1:15" ht="24.95" customHeight="1">
       <c r="A758" s="2" t="s">
-        <v>1240</v>
+        <v>1228</v>
       </c>
       <c r="B758" s="2" t="s">
-        <v>1241</v>
+        <v>1229</v>
       </c>
       <c r="O758" s="2" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="759" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A759" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="B759" s="2" t="s">
-        <v>1244</v>
-      </c>
-      <c r="O759" s="2" t="s">
-        <v>1245</v>
-      </c>
+      <c r="O759" s="2"/>
     </row>
     <row r="760" spans="1:15" ht="24.95" customHeight="1">
       <c r="A760" s="2" t="s">
-        <v>1246</v>
+        <v>1231</v>
       </c>
       <c r="B760" s="2" t="s">
-        <v>1247</v>
+        <v>1232</v>
       </c>
       <c r="O760" s="2" t="s">
-        <v>1248</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="761" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O761" s="2"/>
+      <c r="A761" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B761" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="O761" s="2" t="s">
+        <v>1236</v>
+      </c>
     </row>
     <row r="762" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A762" s="2" t="s">
-        <v>1600</v>
-      </c>
-      <c r="O762" s="2" t="s">
-        <v>1602</v>
-      </c>
+      <c r="O762" s="2"/>
     </row>
     <row r="763" spans="1:15" ht="24.95" customHeight="1">
       <c r="A763" s="2" t="s">
-        <v>1601</v>
-      </c>
-      <c r="O763" s="3" t="s">
-        <v>1603</v>
+        <v>1237</v>
+      </c>
+      <c r="B763" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="O763" s="2" t="s">
+        <v>1239</v>
       </c>
     </row>
     <row r="764" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O764" s="2"/>
+      <c r="A764" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B764" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="O764" s="2" t="s">
+        <v>1242</v>
+      </c>
     </row>
     <row r="765" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O765" s="2"/>
+      <c r="A765" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B765" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="O765" s="2" t="s">
+        <v>1245</v>
+      </c>
     </row>
     <row r="766" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O766" s="2"/>
+      <c r="A766" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B766" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="O766" s="2" t="s">
+        <v>1248</v>
+      </c>
     </row>
     <row r="767" spans="1:15" ht="24.95" customHeight="1">
       <c r="O767" s="2"/>
     </row>
     <row r="768" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O768" s="2"/>
-    </row>
-    <row r="769" spans="15:15" ht="24.95" customHeight="1">
-      <c r="O769" s="2"/>
-    </row>
-    <row r="770" spans="15:15" ht="24.95" customHeight="1">
+      <c r="A768" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="O768" s="2" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="769" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A769" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="O769" s="3" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="770" spans="1:15" ht="24.95" customHeight="1">
       <c r="O770" s="2"/>
     </row>
-    <row r="771" spans="15:15" ht="24.95" customHeight="1">
+    <row r="771" spans="1:15" ht="24.95" customHeight="1">
       <c r="O771" s="2"/>
     </row>
-    <row r="772" spans="15:15" ht="24.95" customHeight="1">
+    <row r="772" spans="1:15" ht="24.95" customHeight="1">
       <c r="O772" s="2"/>
     </row>
-    <row r="773" spans="15:15" ht="24.95" customHeight="1">
+    <row r="773" spans="1:15" ht="24.95" customHeight="1">
       <c r="O773" s="2"/>
     </row>
-    <row r="774" spans="15:15" ht="24.95" customHeight="1">
+    <row r="774" spans="1:15" ht="24.95" customHeight="1">
       <c r="O774" s="2"/>
     </row>
-    <row r="775" spans="15:15" ht="24.95" customHeight="1">
+    <row r="775" spans="1:15" ht="24.95" customHeight="1">
       <c r="O775" s="2"/>
     </row>
-    <row r="776" spans="15:15" ht="24.95" customHeight="1">
+    <row r="776" spans="1:15" ht="24.95" customHeight="1">
       <c r="O776" s="2"/>
     </row>
-    <row r="777" spans="15:15" ht="24.95" customHeight="1">
+    <row r="777" spans="1:15" ht="24.95" customHeight="1">
       <c r="O777" s="2"/>
     </row>
-    <row r="778" spans="15:15" ht="24.95" customHeight="1">
+    <row r="778" spans="1:15" ht="24.95" customHeight="1">
       <c r="O778" s="2"/>
     </row>
-    <row r="779" spans="15:15" ht="24.95" customHeight="1">
+    <row r="779" spans="1:15" ht="24.95" customHeight="1">
       <c r="O779" s="2"/>
     </row>
-    <row r="780" spans="15:15" ht="24.95" customHeight="1">
+    <row r="780" spans="1:15" ht="24.95" customHeight="1">
       <c r="O780" s="2"/>
     </row>
-    <row r="781" spans="15:15" ht="24.95" customHeight="1">
+    <row r="781" spans="1:15" ht="24.95" customHeight="1">
       <c r="O781" s="2"/>
     </row>
-    <row r="782" spans="15:15" ht="24.95" customHeight="1">
+    <row r="782" spans="1:15" ht="24.95" customHeight="1">
       <c r="O782" s="2"/>
     </row>
-    <row r="783" spans="15:15" ht="24.95" customHeight="1">
+    <row r="783" spans="1:15" ht="24.95" customHeight="1">
       <c r="O783" s="2"/>
     </row>
-    <row r="784" spans="15:15" ht="24.95" customHeight="1">
+    <row r="784" spans="1:15" ht="24.95" customHeight="1">
       <c r="O784" s="2"/>
     </row>
     <row r="785" spans="15:15" ht="24.95" customHeight="1">
@@ -19649,6 +19724,9 @@
     <row r="860" spans="15:15" ht="24.95" customHeight="1">
       <c r="O860" s="2"/>
     </row>
+    <row r="861" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O861" s="2"/>
+    </row>
     <row r="862" spans="15:15" ht="24.95" customHeight="1">
       <c r="O862" s="2"/>
     </row>
@@ -19664,9 +19742,6 @@
     <row r="866" spans="15:15" ht="24.95" customHeight="1">
       <c r="O866" s="2"/>
     </row>
-    <row r="867" spans="15:15" ht="24.95" customHeight="1">
-      <c r="O867" s="2"/>
-    </row>
     <row r="868" spans="15:15" ht="24.95" customHeight="1">
       <c r="O868" s="2"/>
     </row>
@@ -20829,20 +20904,7 @@
       <c r="O1254" s="2"/>
     </row>
     <row r="1255" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A1255" s="5"/>
-      <c r="B1255" s="5"/>
-      <c r="D1255" s="5"/>
-      <c r="E1255" s="5"/>
-      <c r="F1255" s="5"/>
-      <c r="G1255" s="5"/>
-      <c r="H1255" s="5"/>
-      <c r="I1255" s="5"/>
-      <c r="J1255" s="5"/>
-      <c r="K1255" s="5"/>
-      <c r="L1255" s="5"/>
-      <c r="M1255" s="5"/>
-      <c r="N1255" s="5"/>
-      <c r="O1255" s="6"/>
+      <c r="O1255" s="2"/>
     </row>
     <row r="1256" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1256" s="2"/>
@@ -20860,7 +20922,20 @@
       <c r="O1260" s="2"/>
     </row>
     <row r="1261" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O1261" s="2"/>
+      <c r="A1261" s="5"/>
+      <c r="B1261" s="5"/>
+      <c r="D1261" s="5"/>
+      <c r="E1261" s="5"/>
+      <c r="F1261" s="5"/>
+      <c r="G1261" s="5"/>
+      <c r="H1261" s="5"/>
+      <c r="I1261" s="5"/>
+      <c r="J1261" s="5"/>
+      <c r="K1261" s="5"/>
+      <c r="L1261" s="5"/>
+      <c r="M1261" s="5"/>
+      <c r="N1261" s="5"/>
+      <c r="O1261" s="6"/>
     </row>
     <row r="1262" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1262" s="2"/>
@@ -22359,8 +22434,26 @@
     <row r="1760" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1760" s="2"/>
     </row>
+    <row r="1761" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1761" s="2"/>
+    </row>
+    <row r="1762" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1762" s="2"/>
+    </row>
+    <row r="1763" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1763" s="2"/>
+    </row>
+    <row r="1764" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1764" s="2"/>
+    </row>
+    <row r="1765" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1765" s="2"/>
+    </row>
+    <row r="1766" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1766" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="O1:O1463" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="O1:O1469" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -23961,7 +24054,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:S96"/>
+  <dimension ref="A1:S97"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21.5" style="2" customWidth="1"/>
@@ -25070,6 +25163,9 @@
       <c r="A95" s="2" t="s">
         <v>3246</v>
       </c>
+      <c r="B95" s="2" t="s">
+        <v>1438</v>
+      </c>
       <c r="O95" s="2" t="s">
         <v>3249</v>
       </c>
@@ -25078,8 +25174,22 @@
       <c r="A96" s="2" t="s">
         <v>3247</v>
       </c>
+      <c r="B96" s="2" t="s">
+        <v>1438</v>
+      </c>
       <c r="O96" s="2" t="s">
         <v>3248</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" ht="20.100000000000001" customHeight="1">
+      <c r="A97" s="2" t="s">
+        <v>3277</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="O97" s="2" t="s">
+        <v>3278</v>
       </c>
     </row>
   </sheetData>
@@ -25090,7 +25200,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:Q447"/>
+  <dimension ref="A1:Q451"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="27.875" style="7" customWidth="1"/>
@@ -28091,64 +28201,64 @@
     </row>
     <row r="437" spans="1:15">
       <c r="A437" s="7" t="s">
-        <v>2268</v>
+        <v>3279</v>
       </c>
       <c r="B437" s="7" t="s">
-        <v>2268</v>
+        <v>3265</v>
       </c>
       <c r="O437" s="7" t="s">
-        <v>2269</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="438" spans="1:15">
       <c r="A438" s="7" t="s">
-        <v>2270</v>
+        <v>3266</v>
       </c>
       <c r="O438" s="7" t="s">
-        <v>2742</v>
+        <v>3269</v>
       </c>
     </row>
     <row r="439" spans="1:15">
       <c r="A439" s="7" t="s">
-        <v>2271</v>
+        <v>3267</v>
       </c>
       <c r="O439" s="7" t="s">
-        <v>2742</v>
+        <v>3269</v>
       </c>
     </row>
     <row r="441" spans="1:15">
       <c r="A441" s="7" t="s">
-        <v>2272</v>
+        <v>2268</v>
       </c>
       <c r="B441" s="7" t="s">
-        <v>2272</v>
+        <v>2268</v>
       </c>
       <c r="O441" s="7" t="s">
-        <v>2273</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="442" spans="1:15">
       <c r="A442" s="7" t="s">
-        <v>2274</v>
+        <v>2270</v>
       </c>
       <c r="O442" s="7" t="s">
-        <v>2743</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="443" spans="1:15">
       <c r="A443" s="7" t="s">
-        <v>2275</v>
+        <v>2271</v>
       </c>
       <c r="O443" s="7" t="s">
-        <v>2743</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="445" spans="1:15">
       <c r="A445" s="7" t="s">
-        <v>2276</v>
+        <v>2272</v>
       </c>
       <c r="B445" s="7" t="s">
-        <v>2276</v>
+        <v>2272</v>
       </c>
       <c r="O445" s="7" t="s">
         <v>2273</v>
@@ -28156,17 +28266,44 @@
     </row>
     <row r="446" spans="1:15">
       <c r="A446" s="7" t="s">
-        <v>2277</v>
+        <v>2274</v>
       </c>
       <c r="O446" s="7" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="447" spans="1:15">
       <c r="A447" s="7" t="s">
+        <v>2275</v>
+      </c>
+      <c r="O447" s="7" t="s">
+        <v>2743</v>
+      </c>
+    </row>
+    <row r="449" spans="1:15">
+      <c r="A449" s="7" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B449" s="7" t="s">
+        <v>2276</v>
+      </c>
+      <c r="O449" s="7" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="450" spans="1:15">
+      <c r="A450" s="7" t="s">
+        <v>2277</v>
+      </c>
+      <c r="O450" s="7" t="s">
+        <v>2744</v>
+      </c>
+    </row>
+    <row r="451" spans="1:15">
+      <c r="A451" s="7" t="s">
         <v>2278</v>
       </c>
-      <c r="O447" s="7" t="s">
+      <c r="O451" s="7" t="s">
         <v>2744</v>
       </c>
     </row>
@@ -28179,7 +28316,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:Q114"/>
+  <dimension ref="A1:Q115"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="60" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.625" style="8" customWidth="1"/>
@@ -28254,7 +28391,7 @@
         <v>2981</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>3265</v>
+        <v>3282</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="60" customHeight="1">
@@ -29119,6 +29256,14 @@
       </c>
       <c r="O114" s="9" t="s">
         <v>2896</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" ht="60" customHeight="1">
+      <c r="A115" s="8" t="s">
+        <v>3280</v>
+      </c>
+      <c r="O115" s="9" t="s">
+        <v>3281</v>
       </c>
     </row>
   </sheetData>

--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Among Us code\TheOtherUs\TheOtherUs-Edited-Lite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB4AF53-678E-42CA-89A6-18F87B52084F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF8FC71-4866-40D9-A00B-7ABE58C97FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1275" yWindow="1260" windowWidth="25755" windowHeight="14940" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1275" yWindow="1260" windowWidth="25755" windowHeight="14940" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Options" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Role Description" sheetId="11" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Options!$O$1:$O$1469</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Options!$O$1:$O$1470</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3609" uniqueCount="3283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3611" uniqueCount="3285">
   <si>
     <t>English</t>
   </si>
@@ -11710,6 +11710,14 @@
     <t>在会议中可以揭示身份，获得一次在会议中击杀玩家的机会。且无法被猜测
 同时，如果狼之主使用赌怪能力则本轮会议无法揭示身份。
 （猎杀和赌怪一次会议只能用一个能力）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>jesterCanDragDeadBody</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>小丑可以拖动尸体</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -12309,7 +12317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1766"/>
+  <dimension ref="A1:Q1767"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40.375" style="2" customWidth="1"/>
@@ -16314,3145 +16322,3150 @@
       </c>
     </row>
     <row r="411" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O411" s="2"/>
+      <c r="A411" s="2" t="s">
+        <v>3283</v>
+      </c>
+      <c r="O411" s="2" t="s">
+        <v>3284</v>
+      </c>
     </row>
     <row r="412" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A412" s="2" t="s">
-        <v>1677</v>
-      </c>
-      <c r="O412" s="2" t="s">
-        <v>1684</v>
-      </c>
+      <c r="O412" s="2"/>
     </row>
     <row r="413" spans="1:15" ht="24.95" customHeight="1">
       <c r="A413" s="2" t="s">
-        <v>1678</v>
-      </c>
-      <c r="B413" s="2" t="s">
-        <v>1657</v>
+        <v>1677</v>
       </c>
       <c r="O413" s="2" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="414" spans="1:15" ht="24.95" customHeight="1">
       <c r="A414" s="2" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>1653</v>
+        <v>1657</v>
       </c>
       <c r="O414" s="2" t="s">
-        <v>1689</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="415" spans="1:15" ht="24.95" customHeight="1">
       <c r="A415" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="O415" s="2" t="s">
-        <v>1659</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="416" spans="1:15" ht="24.95" customHeight="1">
       <c r="A416" s="2" t="s">
-        <v>1690</v>
+        <v>1680</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>1663</v>
+        <v>1654</v>
       </c>
       <c r="O416" s="2" t="s">
-        <v>1691</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="417" spans="1:15" ht="24.95" customHeight="1">
       <c r="A417" s="2" t="s">
-        <v>1681</v>
+        <v>1690</v>
+      </c>
+      <c r="B417" s="2" t="s">
+        <v>1663</v>
       </c>
       <c r="O417" s="2" t="s">
-        <v>1686</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="418" spans="1:15" ht="24.95" customHeight="1">
       <c r="A418" s="2" t="s">
-        <v>1682</v>
-      </c>
-      <c r="B418" s="2" t="s">
-        <v>1658</v>
+        <v>1681</v>
       </c>
       <c r="O418" s="2" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="419" spans="1:15" ht="24.95" customHeight="1">
       <c r="A419" s="2" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B419" s="2" t="s">
+        <v>1658</v>
+      </c>
+      <c r="O419" s="2" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="420" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A420" s="2" t="s">
         <v>1683</v>
       </c>
-      <c r="B419" s="2" t="s">
+      <c r="B420" s="2" t="s">
         <v>1656</v>
       </c>
-      <c r="O419" s="2" t="s">
+      <c r="O420" s="2" t="s">
         <v>1687</v>
       </c>
     </row>
-    <row r="420" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O420" s="2"/>
-    </row>
     <row r="421" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A421" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="B421" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="O421" s="2" t="s">
-        <v>724</v>
-      </c>
+      <c r="O421" s="2"/>
     </row>
     <row r="422" spans="1:15" ht="24.95" customHeight="1">
       <c r="A422" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="B422" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="O422" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="423" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A423" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="B422" s="2" t="s">
+      <c r="B423" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="O422" s="2" t="s">
+      <c r="O423" s="2" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="423" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O423" s="2"/>
-    </row>
     <row r="424" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A424" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="B424" s="2" t="s">
-        <v>2408</v>
-      </c>
-      <c r="O424" s="2" t="s">
-        <v>729</v>
-      </c>
+      <c r="O424" s="2"/>
     </row>
     <row r="425" spans="1:15" ht="24.95" customHeight="1">
       <c r="A425" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="O425" s="2" t="s">
-        <v>2861</v>
+        <v>729</v>
       </c>
     </row>
     <row r="426" spans="1:15" ht="24.95" customHeight="1">
       <c r="A426" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B426" s="2" t="s">
+        <v>2409</v>
+      </c>
+      <c r="O426" s="2" t="s">
+        <v>2861</v>
+      </c>
+    </row>
+    <row r="427" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A427" s="2" t="s">
         <v>2863</v>
       </c>
-      <c r="O426" s="2" t="s">
+      <c r="O427" s="2" t="s">
         <v>2862</v>
       </c>
     </row>
-    <row r="427" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O427" s="2"/>
-    </row>
     <row r="428" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A428" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="B428" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="O428" s="2" t="s">
-        <v>733</v>
-      </c>
+      <c r="O428" s="2"/>
     </row>
     <row r="429" spans="1:15" ht="24.95" customHeight="1">
       <c r="A429" s="2" t="s">
-        <v>1605</v>
+        <v>731</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="O429" s="2" t="s">
-        <v>492</v>
+        <v>733</v>
       </c>
     </row>
     <row r="430" spans="1:15" ht="24.95" customHeight="1">
       <c r="A430" s="2" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="O430" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="431" spans="1:15" ht="24.95" customHeight="1">
       <c r="A431" s="2" t="s">
-        <v>736</v>
+        <v>1606</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O431" s="2" t="s">
-        <v>738</v>
+        <v>495</v>
       </c>
     </row>
     <row r="432" spans="1:15" ht="24.95" customHeight="1">
       <c r="A432" s="2" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="O432" s="2" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="433" spans="1:15" ht="24.95" customHeight="1">
       <c r="A433" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>1640</v>
+        <v>740</v>
       </c>
       <c r="O433" s="2" t="s">
-        <v>1760</v>
+        <v>741</v>
       </c>
     </row>
     <row r="434" spans="1:15" ht="24.95" customHeight="1">
       <c r="A434" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>744</v>
+        <v>1640</v>
       </c>
       <c r="O434" s="2" t="s">
-        <v>745</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="435" spans="1:15" ht="24.95" customHeight="1">
       <c r="A435" s="2" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="O435" s="2" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
     </row>
     <row r="436" spans="1:15" ht="24.95" customHeight="1">
       <c r="A436" s="2" t="s">
-        <v>2404</v>
+        <v>746</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>2405</v>
+        <v>747</v>
       </c>
       <c r="O436" s="2" t="s">
-        <v>2406</v>
+        <v>748</v>
       </c>
     </row>
     <row r="437" spans="1:15" ht="24.95" customHeight="1">
       <c r="A437" s="2" t="s">
-        <v>1713</v>
+        <v>2404</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>749</v>
+        <v>2405</v>
       </c>
       <c r="O437" s="2" t="s">
-        <v>750</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="438" spans="1:15" ht="24.95" customHeight="1">
       <c r="A438" s="2" t="s">
-        <v>751</v>
+        <v>1713</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="O438" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="439" spans="1:15" ht="24.95" customHeight="1">
       <c r="A439" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="O439" s="2" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
     </row>
     <row r="440" spans="1:15" ht="24.95" customHeight="1">
       <c r="A440" s="2" t="s">
-        <v>2402</v>
+        <v>754</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="O440" s="2" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="441" spans="1:15" ht="24.95" customHeight="1">
       <c r="A441" s="2" t="s">
+        <v>2402</v>
+      </c>
+      <c r="B441" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="O441" s="2" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="442" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A442" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="B441" s="2" t="s">
+      <c r="B442" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="O441" s="2" t="s">
+      <c r="O442" s="2" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="442" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O442" s="2"/>
-    </row>
     <row r="443" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A443" s="2" t="s">
-        <v>1610</v>
-      </c>
-      <c r="O443" s="2" t="s">
-        <v>2309</v>
-      </c>
+      <c r="O443" s="2"/>
     </row>
     <row r="444" spans="1:15" ht="24.95" customHeight="1">
       <c r="A444" s="2" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="O444" s="2" t="s">
-        <v>1631</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="445" spans="1:15" ht="24.95" customHeight="1">
       <c r="A445" s="2" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="O445" s="2" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="446" spans="1:15" ht="24.95" customHeight="1">
       <c r="A446" s="2" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="O446" s="2" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="447" spans="1:15" ht="24.95" customHeight="1">
       <c r="A447" s="2" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="O447" s="2" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="448" spans="1:15" ht="24.95" customHeight="1">
       <c r="A448" s="2" t="s">
-        <v>1618</v>
+        <v>1614</v>
       </c>
       <c r="O448" s="2" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="449" spans="1:15" ht="24.95" customHeight="1">
       <c r="A449" s="2" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="O449" s="2" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="450" spans="1:15" ht="24.95" customHeight="1">
       <c r="A450" s="2" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="O450" s="2" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="451" spans="1:15" ht="24.95" customHeight="1">
       <c r="A451" s="2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="O451" s="2" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="452" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A452" s="2" t="s">
         <v>1617</v>
       </c>
-      <c r="O451" s="2" t="s">
+      <c r="O452" s="2" t="s">
         <v>1624</v>
       </c>
     </row>
-    <row r="452" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O452" s="2"/>
-    </row>
     <row r="453" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A453" s="2" t="s">
-        <v>1619</v>
-      </c>
-      <c r="B453" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="O453" s="2" t="s">
-        <v>1623</v>
-      </c>
+      <c r="O453" s="2"/>
     </row>
     <row r="454" spans="1:15" ht="24.95" customHeight="1">
       <c r="A454" s="2" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="O454" s="2" t="s">
-        <v>495</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="455" spans="1:15" ht="24.95" customHeight="1">
       <c r="A455" s="2" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B455" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="O455" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="456" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A456" s="2" t="s">
         <v>2282</v>
       </c>
-      <c r="B455" s="2" t="s">
+      <c r="B456" s="2" t="s">
         <v>2283</v>
       </c>
-      <c r="O455" s="2" t="s">
+      <c r="O456" s="2" t="s">
         <v>2284</v>
       </c>
     </row>
-    <row r="456" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O456" s="2"/>
-    </row>
     <row r="457" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A457" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="B457" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="O457" s="2" t="s">
-        <v>789</v>
-      </c>
+      <c r="O457" s="2"/>
     </row>
     <row r="458" spans="1:15" ht="24.95" customHeight="1">
       <c r="A458" s="2" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="O458" s="2" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
     </row>
     <row r="459" spans="1:15" ht="24.95" customHeight="1">
       <c r="A459" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="B459" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="O459" s="2" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="460" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A460" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="B459" s="2" t="s">
+      <c r="B460" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="O459" s="2" t="s">
+      <c r="O460" s="2" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="460" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O460" s="2"/>
-    </row>
     <row r="461" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A461" s="2" t="s">
+      <c r="O461" s="2"/>
+    </row>
+    <row r="462" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A462" s="2" t="s">
         <v>1621</v>
       </c>
-      <c r="O461" s="2" t="s">
+      <c r="O462" s="2" t="s">
         <v>1622</v>
       </c>
     </row>
-    <row r="462" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O462" s="2"/>
-    </row>
     <row r="463" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A463" s="2" t="s">
-        <v>2985</v>
-      </c>
-      <c r="O463" s="2" t="s">
-        <v>2987</v>
-      </c>
+      <c r="O463" s="2"/>
     </row>
     <row r="464" spans="1:15" ht="24.95" customHeight="1">
       <c r="A464" s="2" t="s">
+        <v>2985</v>
+      </c>
+      <c r="O464" s="2" t="s">
+        <v>2987</v>
+      </c>
+    </row>
+    <row r="465" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A465" s="2" t="s">
         <v>2986</v>
       </c>
-      <c r="O464" s="2" t="s">
+      <c r="O465" s="2" t="s">
         <v>2988</v>
       </c>
     </row>
-    <row r="465" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O465" s="2"/>
-    </row>
     <row r="466" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A466" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="B466" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="O466" s="2" t="s">
-        <v>764</v>
-      </c>
+      <c r="O466" s="2"/>
     </row>
     <row r="467" spans="1:15" ht="24.95" customHeight="1">
       <c r="A467" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="O467" s="2" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="468" spans="1:15" ht="24.95" customHeight="1">
       <c r="A468" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B468" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="O468" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="469" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A469" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="B468" s="2" t="s">
+      <c r="B469" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="O468" s="2" t="s">
+      <c r="O469" s="2" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="469" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O469" s="2"/>
-    </row>
     <row r="470" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A470" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="B470" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="O470" s="2" t="s">
-        <v>773</v>
-      </c>
+      <c r="O470" s="2"/>
     </row>
     <row r="471" spans="1:15" ht="24.95" customHeight="1">
       <c r="A471" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="O471" s="2" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="472" spans="1:15" ht="24.95" customHeight="1">
       <c r="A472" s="2" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="O472" s="2" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
     </row>
     <row r="473" spans="1:15" ht="24.95" customHeight="1">
       <c r="A473" s="2" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="O473" s="2" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
     </row>
     <row r="474" spans="1:15" ht="24.95" customHeight="1">
       <c r="A474" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="B474" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="O474" s="2" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="475" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A475" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="O474" s="2" t="s">
+      <c r="O475" s="2" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="475" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O475" s="2"/>
-    </row>
     <row r="476" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A476" s="2" t="s">
-        <v>1609</v>
-      </c>
-      <c r="O476" s="2" t="s">
-        <v>3050</v>
-      </c>
+      <c r="O476" s="2"/>
     </row>
     <row r="477" spans="1:15" ht="24.95" customHeight="1">
       <c r="A477" s="2" t="s">
+        <v>1609</v>
+      </c>
+      <c r="O477" s="2" t="s">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="478" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A478" s="2" t="s">
         <v>1665</v>
       </c>
-      <c r="B477" s="2" t="s">
+      <c r="B478" s="2" t="s">
         <v>1796</v>
       </c>
-      <c r="O477" s="2" t="s">
+      <c r="O478" s="2" t="s">
         <v>3051</v>
       </c>
     </row>
-    <row r="478" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O478" s="2"/>
-    </row>
     <row r="479" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A479" s="2" t="s">
-        <v>1645</v>
-      </c>
-      <c r="O479" s="2" t="s">
-        <v>1646</v>
-      </c>
+      <c r="O479" s="2"/>
     </row>
     <row r="480" spans="1:15" ht="24.95" customHeight="1">
       <c r="A480" s="2" t="s">
-        <v>1649</v>
-      </c>
-      <c r="B480" s="2" t="s">
-        <v>1658</v>
+        <v>1645</v>
       </c>
       <c r="O480" s="2" t="s">
-        <v>1688</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="481" spans="1:15" ht="24.95" customHeight="1">
       <c r="A481" s="2" t="s">
-        <v>781</v>
+        <v>1649</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="O481" s="2" t="s">
-        <v>1660</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="482" spans="1:15" ht="24.95" customHeight="1">
       <c r="A482" s="2" t="s">
-        <v>1647</v>
+        <v>781</v>
+      </c>
+      <c r="B482" s="2" t="s">
+        <v>1656</v>
       </c>
       <c r="O482" s="2" t="s">
-        <v>1648</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="483" spans="1:15" ht="24.95" customHeight="1">
       <c r="A483" s="2" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B483" s="2" t="s">
-        <v>1653</v>
+        <v>1647</v>
       </c>
       <c r="O483" s="2" t="s">
-        <v>1689</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="484" spans="1:15" ht="24.95" customHeight="1">
       <c r="A484" s="2" t="s">
-        <v>1655</v>
+        <v>1650</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="O484" s="2" t="s">
-        <v>1659</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="485" spans="1:15" ht="24.95" customHeight="1">
       <c r="A485" s="2" t="s">
-        <v>1652</v>
+        <v>1655</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>1663</v>
+        <v>1654</v>
       </c>
       <c r="O485" s="2" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="486" spans="1:15" ht="24.95" customHeight="1">
       <c r="A486" s="2" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B486" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="O486" s="2" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="487" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A487" s="2" t="s">
         <v>1651</v>
       </c>
-      <c r="B486" s="2" t="s">
+      <c r="B487" s="2" t="s">
         <v>1657</v>
       </c>
-      <c r="O486" s="2" t="s">
+      <c r="O487" s="2" t="s">
         <v>1661</v>
       </c>
     </row>
-    <row r="487" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O487" s="2"/>
-    </row>
     <row r="488" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A488" s="2" t="s">
-        <v>2905</v>
-      </c>
-      <c r="O488" s="2" t="s">
-        <v>2910</v>
-      </c>
+      <c r="O488" s="2"/>
     </row>
     <row r="489" spans="1:15" ht="24.95" customHeight="1">
       <c r="A489" s="2" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="O489" s="2" t="s">
-        <v>2908</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="490" spans="1:15" ht="24.95" customHeight="1">
       <c r="A490" s="2" t="s">
-        <v>2907</v>
-      </c>
-      <c r="O490" s="3" t="s">
-        <v>2909</v>
+        <v>2906</v>
+      </c>
+      <c r="O490" s="2" t="s">
+        <v>2908</v>
       </c>
     </row>
     <row r="491" spans="1:15" ht="24.95" customHeight="1">
       <c r="A491" s="2" t="s">
+        <v>2907</v>
+      </c>
+      <c r="O491" s="3" t="s">
+        <v>2909</v>
+      </c>
+    </row>
+    <row r="492" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A492" s="2" t="s">
         <v>2973</v>
       </c>
-      <c r="O491" s="3" t="s">
+      <c r="O492" s="3" t="s">
         <v>2999</v>
-      </c>
-    </row>
-    <row r="493" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A493" s="2" t="s">
-        <v>3203</v>
-      </c>
-      <c r="O493" s="3" t="s">
-        <v>3206</v>
       </c>
     </row>
     <row r="494" spans="1:15" ht="24.95" customHeight="1">
       <c r="A494" s="2" t="s">
+        <v>3203</v>
+      </c>
+      <c r="O494" s="3" t="s">
+        <v>3206</v>
+      </c>
+    </row>
+    <row r="495" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A495" s="2" t="s">
         <v>3204</v>
       </c>
-      <c r="O494" s="3" t="s">
+      <c r="O495" s="3" t="s">
         <v>3205</v>
       </c>
     </row>
-    <row r="495" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O495" s="2"/>
-    </row>
     <row r="496" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A496" s="2" t="s">
-        <v>2480</v>
-      </c>
-      <c r="O496" s="3" t="s">
-        <v>2481</v>
-      </c>
+      <c r="O496" s="2"/>
     </row>
     <row r="497" spans="1:15" ht="24.95" customHeight="1">
       <c r="A497" s="2" t="s">
-        <v>2470</v>
-      </c>
-      <c r="O497" s="2" t="s">
-        <v>2468</v>
+        <v>2480</v>
+      </c>
+      <c r="O497" s="3" t="s">
+        <v>2481</v>
       </c>
     </row>
     <row r="498" spans="1:15" ht="24.95" customHeight="1">
       <c r="A498" s="2" t="s">
+        <v>2470</v>
+      </c>
+      <c r="O498" s="2" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="499" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A499" s="2" t="s">
         <v>2471</v>
       </c>
-      <c r="O498" s="2" t="s">
+      <c r="O499" s="2" t="s">
         <v>2469</v>
       </c>
     </row>
-    <row r="499" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O499" s="2"/>
-    </row>
     <row r="500" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A500" s="2" t="s">
-        <v>1607</v>
-      </c>
-      <c r="B500" s="2" t="s">
-        <v>1797</v>
-      </c>
-      <c r="O500" s="2" t="s">
-        <v>1632</v>
-      </c>
+      <c r="O500" s="2"/>
     </row>
     <row r="501" spans="1:15" ht="24.95" customHeight="1">
       <c r="A501" s="2" t="s">
-        <v>1608</v>
+        <v>1607</v>
+      </c>
+      <c r="B501" s="2" t="s">
+        <v>1797</v>
       </c>
       <c r="O501" s="2" t="s">
-        <v>2413</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="502" spans="1:15" ht="24.95" customHeight="1">
       <c r="A502" s="2" t="s">
-        <v>1633</v>
-      </c>
-      <c r="B502" s="2" t="s">
-        <v>2414</v>
+        <v>1608</v>
       </c>
       <c r="O502" s="2" t="s">
-        <v>1795</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="503" spans="1:15" ht="24.95" customHeight="1">
       <c r="A503" s="2" t="s">
-        <v>937</v>
+        <v>1633</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="O503" s="2" t="s">
-        <v>2417</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="504" spans="1:15" ht="24.95" customHeight="1">
       <c r="A504" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>2418</v>
+        <v>2415</v>
       </c>
       <c r="O504" s="2" t="s">
-        <v>939</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="505" spans="1:15" ht="24.95" customHeight="1">
       <c r="A505" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="B505" s="2" t="s">
+        <v>2418</v>
+      </c>
+      <c r="O505" s="2" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="506" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A506" s="2" t="s">
         <v>940</v>
       </c>
-      <c r="B505" s="2" t="s">
+      <c r="B506" s="2" t="s">
         <v>2416</v>
       </c>
-      <c r="O505" s="2" t="s">
+      <c r="O506" s="2" t="s">
         <v>2412</v>
       </c>
     </row>
-    <row r="506" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O506" s="2"/>
-    </row>
     <row r="507" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A507" s="2" t="s">
-        <v>966</v>
-      </c>
-      <c r="O507" s="2" t="s">
-        <v>967</v>
-      </c>
+      <c r="O507" s="2"/>
     </row>
     <row r="508" spans="1:15" ht="24.95" customHeight="1">
       <c r="A508" s="2" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="O508" s="2" t="s">
-        <v>2855</v>
+        <v>967</v>
       </c>
     </row>
     <row r="509" spans="1:15" ht="24.95" customHeight="1">
       <c r="A509" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="O509" s="2" t="s">
-        <v>970</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="510" spans="1:15" ht="24.95" customHeight="1">
       <c r="A510" s="2" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="O510" s="2" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="511" spans="1:15" ht="24.95" customHeight="1">
       <c r="A511" s="2" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="O511" s="2" t="s">
-        <v>2512</v>
+        <v>972</v>
       </c>
     </row>
     <row r="512" spans="1:15" ht="24.95" customHeight="1">
       <c r="A512" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="O512" s="2" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="513" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A513" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="O512" s="2" t="s">
+      <c r="O513" s="2" t="s">
         <v>975</v>
       </c>
     </row>
-    <row r="513" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O513" s="2"/>
-    </row>
     <row r="514" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A514" s="2" t="s">
-        <v>3226</v>
-      </c>
-      <c r="B514" s="2" t="s">
-        <v>3228</v>
-      </c>
-      <c r="O514" s="2" t="s">
-        <v>3227</v>
-      </c>
+      <c r="O514" s="2"/>
     </row>
     <row r="515" spans="1:15" ht="24.95" customHeight="1">
       <c r="A515" s="2" t="s">
-        <v>795</v>
+        <v>3226</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>796</v>
+        <v>3228</v>
       </c>
       <c r="O515" s="2" t="s">
-        <v>1638</v>
+        <v>3227</v>
       </c>
     </row>
     <row r="516" spans="1:15" ht="24.95" customHeight="1">
       <c r="A516" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="O516" s="2" t="s">
-        <v>799</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="517" spans="1:15" ht="24.95" customHeight="1">
       <c r="A517" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="B517" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="O517" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="518" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A518" s="2" t="s">
         <v>1637</v>
       </c>
-      <c r="B517" s="2" t="s">
+      <c r="B518" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="O517" s="3" t="s">
+      <c r="O518" s="3" t="s">
         <v>1636</v>
-      </c>
-    </row>
-    <row r="519" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A519" s="2" t="s">
-        <v>3220</v>
-      </c>
-      <c r="O519" s="3" t="s">
-        <v>3223</v>
       </c>
     </row>
     <row r="520" spans="1:15" ht="24.95" customHeight="1">
       <c r="A520" s="2" t="s">
-        <v>3224</v>
+        <v>3220</v>
       </c>
       <c r="O520" s="3" t="s">
-        <v>3225</v>
+        <v>3223</v>
       </c>
     </row>
     <row r="521" spans="1:15" ht="24.95" customHeight="1">
       <c r="A521" s="2" t="s">
-        <v>3218</v>
+        <v>3224</v>
       </c>
       <c r="O521" s="3" t="s">
-        <v>3221</v>
+        <v>3225</v>
       </c>
     </row>
     <row r="522" spans="1:15" ht="24.95" customHeight="1">
       <c r="A522" s="2" t="s">
+        <v>3218</v>
+      </c>
+      <c r="O522" s="3" t="s">
+        <v>3221</v>
+      </c>
+    </row>
+    <row r="523" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A523" s="2" t="s">
         <v>3219</v>
       </c>
-      <c r="O522" s="3" t="s">
+      <c r="O523" s="3" t="s">
         <v>3222</v>
       </c>
     </row>
-    <row r="525" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A525" s="2" t="s">
+    <row r="526" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A526" s="2" t="s">
         <v>2884</v>
       </c>
-      <c r="B525" s="2" t="s">
+      <c r="B526" s="2" t="s">
         <v>2885</v>
       </c>
-      <c r="O525" s="3" t="s">
+      <c r="O526" s="3" t="s">
         <v>2886</v>
-      </c>
-    </row>
-    <row r="527" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A527" s="2" t="s">
-        <v>3272</v>
-      </c>
-      <c r="B527" s="2" t="s">
-        <v>3271</v>
-      </c>
-      <c r="O527" s="3" t="s">
-        <v>3270</v>
       </c>
     </row>
     <row r="528" spans="1:15" ht="24.95" customHeight="1">
       <c r="A528" s="2" t="s">
-        <v>3273</v>
+        <v>3272</v>
+      </c>
+      <c r="B528" s="2" t="s">
+        <v>3271</v>
       </c>
       <c r="O528" s="3" t="s">
-        <v>3275</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="529" spans="1:15" ht="24.95" customHeight="1">
       <c r="A529" s="2" t="s">
+        <v>3273</v>
+      </c>
+      <c r="O529" s="3" t="s">
+        <v>3275</v>
+      </c>
+    </row>
+    <row r="530" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A530" s="2" t="s">
         <v>3274</v>
       </c>
-      <c r="O529" s="3" t="s">
+      <c r="O530" s="3" t="s">
         <v>3276</v>
       </c>
     </row>
-    <row r="532" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O532" s="2"/>
-    </row>
     <row r="533" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A533" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="B533" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="O533" s="2" t="s">
-        <v>803</v>
-      </c>
+      <c r="O533" s="2"/>
     </row>
     <row r="534" spans="1:15" ht="24.95" customHeight="1">
       <c r="A534" s="2" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="O534" s="2" t="s">
-        <v>519</v>
+        <v>803</v>
       </c>
     </row>
     <row r="535" spans="1:15" ht="24.95" customHeight="1">
       <c r="A535" s="2" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="O535" s="2" t="s">
-        <v>808</v>
+        <v>519</v>
       </c>
     </row>
     <row r="536" spans="1:15" ht="24.95" customHeight="1">
       <c r="A536" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="B536" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="O536" s="2" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="537" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A537" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="B536" s="2" t="s">
+      <c r="B537" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="O536" s="2" t="s">
+      <c r="O537" s="2" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="537" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O537" s="2"/>
-    </row>
     <row r="538" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A538" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="B538" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="O538" s="2" t="s">
-        <v>812</v>
-      </c>
+      <c r="O538" s="2"/>
     </row>
     <row r="539" spans="1:15" ht="24.95" customHeight="1">
       <c r="A539" s="2" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="O539" s="2" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
     </row>
     <row r="540" spans="1:15" ht="24.95" customHeight="1">
       <c r="A540" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="O540" s="2" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
     </row>
     <row r="541" spans="1:15" ht="24.95" customHeight="1">
       <c r="A541" s="2" t="s">
-        <v>2419</v>
+        <v>819</v>
+      </c>
+      <c r="B541" s="2" t="s">
+        <v>820</v>
       </c>
       <c r="O541" s="2" t="s">
-        <v>2420</v>
+        <v>821</v>
       </c>
     </row>
     <row r="542" spans="1:15" ht="24.95" customHeight="1">
       <c r="A542" s="2" t="s">
-        <v>822</v>
+        <v>2419</v>
       </c>
       <c r="O542" s="2" t="s">
-        <v>823</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="543" spans="1:15" ht="24.95" customHeight="1">
       <c r="A543" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="O543" s="2" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="544" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A544" s="2" t="s">
         <v>2292</v>
       </c>
-      <c r="O543" s="2" t="s">
+      <c r="O544" s="2" t="s">
         <v>2466</v>
       </c>
     </row>
-    <row r="544" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O544" s="2"/>
-    </row>
     <row r="545" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A545" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="B545" s="2" t="s">
-        <v>1669</v>
-      </c>
-      <c r="O545" s="2" t="s">
-        <v>825</v>
-      </c>
+      <c r="O545" s="2"/>
     </row>
     <row r="546" spans="1:15" ht="24.95" customHeight="1">
       <c r="A546" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="B546" s="2" t="s">
+        <v>1669</v>
+      </c>
+      <c r="O546" s="2" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="547" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A547" s="2" t="s">
         <v>813</v>
       </c>
-      <c r="B546" s="2" t="s">
+      <c r="B547" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="O546" s="2" t="s">
+      <c r="O547" s="2" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="547" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O547" s="2"/>
-    </row>
     <row r="548" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A548" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="B548" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="O548" s="2" t="s">
-        <v>828</v>
-      </c>
+      <c r="O548" s="2"/>
     </row>
     <row r="549" spans="1:15" ht="24.95" customHeight="1">
       <c r="A549" s="2" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="O549" s="2" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
     </row>
     <row r="550" spans="1:15" ht="24.95" customHeight="1">
       <c r="A550" s="2" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="O550" s="2" t="s">
-        <v>2465</v>
+        <v>831</v>
       </c>
     </row>
     <row r="551" spans="1:15" ht="24.95" customHeight="1">
       <c r="A551" s="2" t="s">
-        <v>1666</v>
+        <v>832</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>1668</v>
+        <v>833</v>
       </c>
       <c r="O551" s="2" t="s">
-        <v>1667</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="552" spans="1:15" ht="24.95" customHeight="1">
       <c r="A552" s="2" t="s">
-        <v>834</v>
+        <v>1666</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>835</v>
+        <v>1668</v>
       </c>
       <c r="O552" s="2" t="s">
-        <v>836</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="553" spans="1:15" ht="24.95" customHeight="1">
       <c r="A553" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B553" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="O553" s="2" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="554" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A554" s="2" t="s">
         <v>837</v>
       </c>
-      <c r="B553" s="2" t="s">
+      <c r="B554" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="O553" s="2" t="s">
+      <c r="O554" s="2" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="554" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O554" s="2"/>
-    </row>
     <row r="555" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A555" s="2" t="s">
+      <c r="O555" s="2"/>
+    </row>
+    <row r="556" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A556" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="B555" s="2" t="s">
+      <c r="B556" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="O555" s="2" t="s">
+      <c r="O556" s="2" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="556" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O556" s="2"/>
-    </row>
     <row r="557" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A557" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="B557" s="2" t="s">
-        <v>844</v>
-      </c>
-      <c r="O557" s="2" t="s">
-        <v>845</v>
-      </c>
+      <c r="O557" s="2"/>
     </row>
     <row r="558" spans="1:15" ht="24.95" customHeight="1">
       <c r="A558" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="O558" s="2" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
     </row>
     <row r="559" spans="1:15" ht="24.95" customHeight="1">
       <c r="A559" s="2" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="O559" s="2" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
     </row>
     <row r="560" spans="1:15" ht="24.95" customHeight="1">
       <c r="A560" s="2" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="O560" s="2" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
     </row>
     <row r="561" spans="1:15" ht="24.95" customHeight="1">
       <c r="A561" s="2" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="O561" s="2" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
     </row>
     <row r="562" spans="1:15" ht="24.95" customHeight="1">
       <c r="A562" s="2" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>651</v>
+        <v>856</v>
       </c>
       <c r="O562" s="2" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="563" spans="1:15" ht="24.95" customHeight="1">
       <c r="A563" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="B563" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="O563" s="2" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="564" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A564" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="B563" s="2" t="s">
+      <c r="B564" s="2" t="s">
         <v>1794</v>
       </c>
-      <c r="O563" s="2" t="s">
+      <c r="O564" s="2" t="s">
         <v>1793</v>
       </c>
     </row>
-    <row r="564" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O564" s="2"/>
-    </row>
     <row r="565" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A565" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="B565" s="2" t="s">
-        <v>862</v>
-      </c>
-      <c r="O565" s="2" t="s">
-        <v>863</v>
-      </c>
+      <c r="O565" s="2"/>
     </row>
     <row r="566" spans="1:15" ht="24.95" customHeight="1">
       <c r="A566" s="2" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="O566" s="2" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
     </row>
     <row r="567" spans="1:15" ht="24.95" customHeight="1">
       <c r="A567" s="2" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="O567" s="2" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
     </row>
     <row r="568" spans="1:15" ht="24.95" customHeight="1">
       <c r="A568" s="2" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="O568" s="2" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
     </row>
     <row r="569" spans="1:15" ht="24.95" customHeight="1">
       <c r="A569" s="2" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="O569" s="2" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
     </row>
     <row r="570" spans="1:15" ht="24.95" customHeight="1">
       <c r="A570" s="2" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="O570" s="2" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
     </row>
     <row r="571" spans="1:15" ht="24.95" customHeight="1">
       <c r="A571" s="2" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="O571" s="2" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
     </row>
     <row r="572" spans="1:15" ht="24.95" customHeight="1">
       <c r="A572" s="2" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="O572" s="2" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
     </row>
     <row r="573" spans="1:15" ht="24.95" customHeight="1">
       <c r="A573" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="B573" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="O573" s="2" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="574" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A574" s="2" t="s">
         <v>885</v>
       </c>
-      <c r="B573" s="2" t="s">
+      <c r="B574" s="2" t="s">
         <v>886</v>
       </c>
-      <c r="O573" s="2" t="s">
+      <c r="O574" s="2" t="s">
         <v>887</v>
       </c>
     </row>
-    <row r="574" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O574" s="2"/>
-    </row>
     <row r="575" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A575" s="2" t="s">
-        <v>1779</v>
-      </c>
-      <c r="B575" s="2" t="s">
-        <v>888</v>
-      </c>
-      <c r="O575" s="2" t="s">
-        <v>889</v>
-      </c>
+      <c r="O575" s="2"/>
     </row>
     <row r="576" spans="1:15" ht="24.95" customHeight="1">
       <c r="A576" s="2" t="s">
-        <v>1780</v>
+        <v>1779</v>
+      </c>
+      <c r="B576" s="2" t="s">
+        <v>888</v>
       </c>
       <c r="O576" s="2" t="s">
-        <v>1781</v>
+        <v>889</v>
       </c>
     </row>
     <row r="577" spans="1:15" ht="24.95" customHeight="1">
       <c r="A577" s="2" t="s">
-        <v>890</v>
-      </c>
-      <c r="B577" s="2" t="s">
-        <v>891</v>
+        <v>1780</v>
       </c>
       <c r="O577" s="2" t="s">
-        <v>892</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="578" spans="1:15" ht="24.95" customHeight="1">
       <c r="A578" s="2" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="O578" s="2" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
     </row>
     <row r="579" spans="1:15" ht="24.95" customHeight="1">
       <c r="A579" s="2" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="O579" s="2" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
     </row>
     <row r="580" spans="1:15" ht="24.95" customHeight="1">
       <c r="A580" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B580" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="O580" s="2" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="581" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A581" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="B580" s="2" t="s">
+      <c r="B581" s="2" t="s">
         <v>1774</v>
       </c>
-      <c r="O580" s="2" t="s">
+      <c r="O581" s="2" t="s">
         <v>900</v>
       </c>
     </row>
-    <row r="581" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O581" s="2"/>
-    </row>
     <row r="582" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A582" s="2" t="s">
-        <v>901</v>
-      </c>
-      <c r="B582" s="2" t="s">
-        <v>902</v>
-      </c>
-      <c r="O582" s="2" t="s">
-        <v>903</v>
-      </c>
+      <c r="O582" s="2"/>
     </row>
     <row r="583" spans="1:15" ht="24.95" customHeight="1">
       <c r="A583" s="2" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="O583" s="2" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
     </row>
     <row r="584" spans="1:15" ht="24.95" customHeight="1">
       <c r="A584" s="2" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="O584" s="2" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
     </row>
     <row r="585" spans="1:15" ht="24.95" customHeight="1">
       <c r="A585" s="2" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="O585" s="2" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
     </row>
     <row r="586" spans="1:15" ht="24.95" customHeight="1">
       <c r="A586" s="2" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="O586" s="2" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
     <row r="587" spans="1:15" ht="24.95" customHeight="1">
       <c r="A587" s="2" t="s">
-        <v>2287</v>
+        <v>913</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>932</v>
+        <v>914</v>
       </c>
       <c r="O587" s="2" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
     </row>
     <row r="588" spans="1:15" ht="24.95" customHeight="1">
       <c r="A588" s="2" t="s">
-        <v>916</v>
+        <v>2287</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>917</v>
+        <v>932</v>
       </c>
       <c r="O588" s="2" t="s">
-        <v>2288</v>
+        <v>918</v>
       </c>
     </row>
     <row r="589" spans="1:15" ht="24.95" customHeight="1">
       <c r="A589" s="2" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="O589" s="2" t="s">
-        <v>921</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="590" spans="1:15" ht="24.95" customHeight="1">
       <c r="A590" s="2" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="O590" s="2" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
     </row>
     <row r="591" spans="1:15" ht="24.95" customHeight="1">
       <c r="A591" s="2" t="s">
-        <v>1782</v>
+        <v>922</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="O591" s="2" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="592" spans="1:15" ht="24.95" customHeight="1">
       <c r="A592" s="2" t="s">
-        <v>927</v>
-      </c>
-      <c r="B592" s="3" t="s">
-        <v>2289</v>
+        <v>1782</v>
+      </c>
+      <c r="B592" s="2" t="s">
+        <v>925</v>
       </c>
       <c r="O592" s="2" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="593" spans="1:15" ht="24.95" customHeight="1">
       <c r="A593" s="2" t="s">
-        <v>929</v>
-      </c>
-      <c r="B593" s="2" t="s">
-        <v>930</v>
+        <v>927</v>
+      </c>
+      <c r="B593" s="3" t="s">
+        <v>2289</v>
       </c>
       <c r="O593" s="2" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
     </row>
     <row r="594" spans="1:15" ht="24.95" customHeight="1">
       <c r="A594" s="2" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>897</v>
+        <v>930</v>
       </c>
       <c r="O594" s="2" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="595" spans="1:15" ht="24.95" customHeight="1">
       <c r="A595" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="B595" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="O595" s="2" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="596" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A596" s="2" t="s">
         <v>935</v>
       </c>
-      <c r="B595" s="2" t="s">
+      <c r="B596" s="2" t="s">
         <v>2290</v>
       </c>
-      <c r="O595" s="2" t="s">
+      <c r="O596" s="2" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="596" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O596" s="2"/>
-    </row>
     <row r="597" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A597" s="2" t="s">
-        <v>941</v>
-      </c>
-      <c r="B597" s="2" t="s">
-        <v>942</v>
-      </c>
-      <c r="O597" s="2" t="s">
-        <v>943</v>
-      </c>
+      <c r="O597" s="2"/>
     </row>
     <row r="598" spans="1:15" ht="24.95" customHeight="1">
       <c r="A598" s="2" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="O598" s="2" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
     </row>
     <row r="599" spans="1:15" ht="24.95" customHeight="1">
       <c r="A599" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="B599" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="O599" s="2" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="600" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A600" s="2" t="s">
         <v>947</v>
       </c>
-      <c r="B599" s="2" t="s">
+      <c r="B600" s="2" t="s">
         <v>948</v>
       </c>
-      <c r="O599" s="2" t="s">
+      <c r="O600" s="2" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="600" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O600" s="2"/>
-    </row>
     <row r="601" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A601" s="2" t="s">
-        <v>1675</v>
-      </c>
-      <c r="B601" s="2" t="s">
-        <v>950</v>
-      </c>
-      <c r="O601" s="2" t="s">
-        <v>951</v>
-      </c>
+      <c r="O601" s="2"/>
     </row>
     <row r="602" spans="1:15" ht="24.95" customHeight="1">
       <c r="A602" s="2" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B602" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="O602" s="2" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="603" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A603" s="2" t="s">
         <v>1676</v>
       </c>
-      <c r="B602" s="2" t="s">
+      <c r="B603" s="2" t="s">
         <v>952</v>
       </c>
-      <c r="O602" s="2" t="s">
+      <c r="O603" s="2" t="s">
         <v>953</v>
       </c>
     </row>
-    <row r="603" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O603" s="2"/>
-    </row>
     <row r="604" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A604" s="2" t="s">
-        <v>954</v>
-      </c>
-      <c r="B604" s="2" t="s">
-        <v>955</v>
-      </c>
-      <c r="O604" s="2" t="s">
-        <v>956</v>
-      </c>
+      <c r="O604" s="2"/>
     </row>
     <row r="605" spans="1:15" ht="24.95" customHeight="1">
       <c r="A605" s="2" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="O605" s="2" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
     </row>
     <row r="606" spans="1:15" ht="24.95" customHeight="1">
       <c r="A606" s="2" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="O606" s="2" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
     </row>
     <row r="607" spans="1:15" ht="24.95" customHeight="1">
       <c r="A607" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="B607" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="O607" s="2" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="608" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A608" s="2" t="s">
         <v>963</v>
       </c>
-      <c r="B607" s="2" t="s">
+      <c r="B608" s="2" t="s">
         <v>964</v>
       </c>
-      <c r="O607" s="2" t="s">
+      <c r="O608" s="2" t="s">
         <v>965</v>
       </c>
     </row>
-    <row r="608" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O608" s="2"/>
-    </row>
     <row r="609" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A609" s="2" t="s">
-        <v>976</v>
-      </c>
-      <c r="B609" s="2" t="s">
-        <v>977</v>
-      </c>
-      <c r="O609" s="2" t="s">
-        <v>978</v>
-      </c>
+      <c r="O609" s="2"/>
     </row>
     <row r="610" spans="1:15" ht="24.95" customHeight="1">
       <c r="A610" s="2" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="O610" s="2" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
     </row>
     <row r="611" spans="1:15" ht="24.95" customHeight="1">
       <c r="A611" s="2" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="O611" s="2" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
     </row>
     <row r="612" spans="1:15" ht="24.95" customHeight="1">
       <c r="A612" s="2" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="O612" s="2" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
     </row>
     <row r="613" spans="1:15" ht="24.95" customHeight="1">
       <c r="A613" s="2" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="O613" s="2" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
     </row>
     <row r="614" spans="1:15" ht="24.95" customHeight="1">
       <c r="A614" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="B614" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="O614" s="2" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="615" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A615" s="2" t="s">
         <v>991</v>
       </c>
-      <c r="B614" s="2" t="s">
+      <c r="B615" s="2" t="s">
         <v>992</v>
       </c>
-      <c r="O614" s="2" t="s">
+      <c r="O615" s="2" t="s">
         <v>993</v>
       </c>
     </row>
-    <row r="615" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O615" s="2"/>
-    </row>
     <row r="616" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A616" s="2" t="s">
-        <v>994</v>
-      </c>
-      <c r="B616" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="O616" s="2" t="s">
-        <v>996</v>
-      </c>
+      <c r="O616" s="2"/>
     </row>
     <row r="617" spans="1:15" ht="24.95" customHeight="1">
       <c r="A617" s="2" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="O617" s="2" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
     </row>
     <row r="618" spans="1:15" ht="24.95" customHeight="1">
       <c r="A618" s="2" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="O618" s="2" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
     </row>
     <row r="619" spans="1:15" ht="24.95" customHeight="1">
       <c r="A619" s="2" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="O619" s="2" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="620" spans="1:15" ht="24.95" customHeight="1">
       <c r="A620" s="2" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>964</v>
+        <v>1004</v>
       </c>
       <c r="O620" s="2" t="s">
-        <v>965</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="621" spans="1:15" ht="24.95" customHeight="1">
       <c r="A621" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B621" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="O621" s="2" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="622" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A622" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="B621" s="2" t="s">
+      <c r="B622" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="O621" s="2" t="s">
+      <c r="O622" s="2" t="s">
         <v>1009</v>
       </c>
     </row>
-    <row r="622" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O622" s="2"/>
-    </row>
     <row r="623" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A623" s="2" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B623" s="2" t="s">
-        <v>1011</v>
-      </c>
-      <c r="O623" s="2" t="s">
-        <v>633</v>
-      </c>
+      <c r="O623" s="2"/>
     </row>
     <row r="624" spans="1:15" ht="24.95" customHeight="1">
       <c r="A624" s="2" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="O624" s="2" t="s">
-        <v>1014</v>
+        <v>633</v>
       </c>
     </row>
     <row r="625" spans="1:15" ht="24.95" customHeight="1">
       <c r="A625" s="2" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="O625" s="2" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="626" spans="1:15" ht="24.95" customHeight="1">
       <c r="A626" s="2" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="B626" s="2" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="O626" s="2" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="627" spans="1:15" ht="24.95" customHeight="1">
       <c r="A627" s="2" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="O627" s="2" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="628" spans="1:15" ht="24.95" customHeight="1">
       <c r="A628" s="2" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="O628" s="2" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="629" spans="1:15" ht="24.95" customHeight="1">
       <c r="A629" s="2" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="O629" s="2" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="630" spans="1:15" ht="24.95" customHeight="1">
       <c r="A630" s="2" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="O630" s="2" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="631" spans="1:15" ht="24.95" customHeight="1">
       <c r="A631" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B631" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="O631" s="2" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="632" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A632" s="2" t="s">
         <v>1033</v>
       </c>
-      <c r="B631" s="2" t="s">
+      <c r="B632" s="2" t="s">
         <v>1034</v>
       </c>
-      <c r="O631" s="2" t="s">
+      <c r="O632" s="2" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="632" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O632" s="2"/>
-    </row>
     <row r="633" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A633" s="2" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B633" s="2" t="s">
-        <v>1037</v>
-      </c>
-      <c r="O633" s="2" t="s">
-        <v>1038</v>
-      </c>
+      <c r="O633" s="2"/>
     </row>
     <row r="634" spans="1:15" ht="24.95" customHeight="1">
       <c r="A634" s="2" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="O634" s="2" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="635" spans="1:15" ht="24.95" customHeight="1">
       <c r="A635" s="2" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="O635" s="2" t="s">
-        <v>2291</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="636" spans="1:15" ht="24.95" customHeight="1">
       <c r="A636" s="2" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="O636" s="2" t="s">
-        <v>1046</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="637" spans="1:15" ht="24.95" customHeight="1">
       <c r="A637" s="2" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="O637" s="2" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="638" spans="1:15" ht="24.95" customHeight="1">
       <c r="A638" s="2" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>66</v>
+        <v>1048</v>
       </c>
       <c r="O638" s="2" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="639" spans="1:15" ht="24.95" customHeight="1">
       <c r="A639" s="2" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>1053</v>
+        <v>66</v>
       </c>
       <c r="O639" s="2" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="640" spans="1:15" ht="24.95" customHeight="1">
       <c r="A640" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B640" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="O640" s="2" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="641" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A641" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="B640" s="2" t="s">
+      <c r="B641" s="2" t="s">
         <v>1056</v>
       </c>
-      <c r="O640" s="2" t="s">
+      <c r="O641" s="2" t="s">
         <v>1057</v>
       </c>
     </row>
-    <row r="641" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O641" s="2"/>
-    </row>
     <row r="642" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A642" s="2" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B642" s="2" t="s">
-        <v>1764</v>
-      </c>
-      <c r="O642" s="2" t="s">
-        <v>1059</v>
-      </c>
+      <c r="O642" s="2"/>
     </row>
     <row r="643" spans="1:15" ht="24.95" customHeight="1">
       <c r="A643" s="2" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="O643" s="2" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="644" spans="1:15" ht="24.95" customHeight="1">
       <c r="A644" s="2" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>1772</v>
+        <v>1765</v>
       </c>
       <c r="O644" s="2" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="645" spans="1:15" ht="24.95" customHeight="1">
       <c r="A645" s="2" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="O645" s="2" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="646" spans="1:15" ht="24.95" customHeight="1">
       <c r="A646" s="2" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>1768</v>
+        <v>1771</v>
       </c>
       <c r="O646" s="2" t="s">
-        <v>1710</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="647" spans="1:15" ht="24.95" customHeight="1">
       <c r="A647" s="2" t="s">
-        <v>1769</v>
+        <v>1066</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="O647" s="2" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="648" spans="1:15" ht="24.95" customHeight="1">
       <c r="A648" s="2" t="s">
-        <v>1067</v>
+        <v>1769</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>1766</v>
+        <v>1770</v>
       </c>
       <c r="O648" s="2" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="649" spans="1:15" ht="24.95" customHeight="1">
       <c r="A649" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B649" s="2" t="s">
+        <v>1766</v>
+      </c>
+      <c r="O649" s="2" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="650" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A650" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="B649" s="2" t="s">
+      <c r="B650" s="2" t="s">
         <v>1767</v>
       </c>
-      <c r="O649" s="2" t="s">
+      <c r="O650" s="2" t="s">
         <v>1707</v>
       </c>
     </row>
-    <row r="650" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O650" s="2"/>
-    </row>
     <row r="651" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A651" s="2" t="s">
-        <v>1832</v>
-      </c>
-      <c r="B651" s="2" t="s">
-        <v>1822</v>
-      </c>
-      <c r="O651" s="2" t="s">
-        <v>1839</v>
-      </c>
+      <c r="O651" s="2"/>
     </row>
     <row r="652" spans="1:15" ht="24.95" customHeight="1">
       <c r="A652" s="2" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>1835</v>
+        <v>1822</v>
       </c>
       <c r="O652" s="2" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="653" spans="1:15" ht="24.95" customHeight="1">
       <c r="A653" s="2" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="O653" s="2" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="654" spans="1:15" ht="24.95" customHeight="1">
       <c r="A654" s="2" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B654" s="2" t="s">
+        <v>1836</v>
+      </c>
+      <c r="O654" s="2" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="655" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A655" s="2" t="s">
         <v>1840</v>
       </c>
-      <c r="B654" s="2" t="s">
+      <c r="B655" s="2" t="s">
         <v>1841</v>
       </c>
-      <c r="O654" s="2" t="s">
+      <c r="O655" s="2" t="s">
         <v>1842</v>
       </c>
     </row>
-    <row r="655" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O655" s="2"/>
-    </row>
     <row r="656" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A656" s="2" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B656" s="2" t="s">
-        <v>1070</v>
-      </c>
-      <c r="O656" s="2" t="s">
-        <v>3030</v>
-      </c>
+      <c r="O656" s="2"/>
     </row>
     <row r="657" spans="1:15" ht="24.95" customHeight="1">
       <c r="A657" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B657" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="O657" s="2" t="s">
+        <v>3030</v>
+      </c>
+    </row>
+    <row r="658" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A658" s="2" t="s">
         <v>1071</v>
       </c>
-      <c r="B657" s="2" t="s">
+      <c r="B658" s="2" t="s">
         <v>1072</v>
       </c>
-      <c r="O657" s="2" t="s">
+      <c r="O658" s="2" t="s">
         <v>1073</v>
       </c>
     </row>
-    <row r="658" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O658" s="2"/>
-    </row>
     <row r="659" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A659" s="2" t="s">
-        <v>1074</v>
-      </c>
-      <c r="B659" s="2" t="s">
-        <v>1075</v>
-      </c>
-      <c r="O659" s="2" t="s">
-        <v>1076</v>
-      </c>
+      <c r="O659" s="2"/>
     </row>
     <row r="660" spans="1:15" ht="24.95" customHeight="1">
       <c r="A660" s="2" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="O660" s="2" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="661" spans="1:15" ht="24.95" customHeight="1">
       <c r="A661" s="2" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="O661" s="2" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="662" spans="1:15" ht="24.95" customHeight="1">
       <c r="A662" s="2" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="O662" s="2" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="663" spans="1:15" ht="24.95" customHeight="1">
       <c r="A663" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B663" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="O663" s="2" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="664" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A664" s="2" t="s">
         <v>1086</v>
       </c>
-      <c r="B663" s="2" t="s">
+      <c r="B664" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="O663" s="2" t="s">
+      <c r="O664" s="2" t="s">
         <v>1088</v>
       </c>
     </row>
-    <row r="664" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O664" s="2"/>
-    </row>
     <row r="665" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A665" s="2" t="s">
-        <v>1089</v>
-      </c>
-      <c r="B665" s="2" t="s">
-        <v>1090</v>
-      </c>
-      <c r="O665" s="2" t="s">
-        <v>1091</v>
-      </c>
+      <c r="O665" s="2"/>
     </row>
     <row r="666" spans="1:15" ht="24.95" customHeight="1">
       <c r="A666" s="2" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="O666" s="2" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="667" spans="1:15" ht="24.95" customHeight="1">
       <c r="A667" s="2" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="O667" s="2" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="668" spans="1:15" ht="24.95" customHeight="1">
       <c r="A668" s="2" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="O668" s="2" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="669" spans="1:15" ht="24.95" customHeight="1">
       <c r="A669" s="2" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="O669" s="2" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="670" spans="1:15" ht="24.95" customHeight="1">
       <c r="A670" s="2" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="O670" s="2" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="671" spans="1:15" ht="24.95" customHeight="1">
       <c r="A671" s="2" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>964</v>
+        <v>1105</v>
       </c>
       <c r="O671" s="2" t="s">
-        <v>965</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="672" spans="1:15" ht="24.95" customHeight="1">
       <c r="A672" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B672" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="O672" s="2" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="673" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A673" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="B672" s="2" t="s">
+      <c r="B673" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="O672" s="2" t="s">
+      <c r="O673" s="2" t="s">
         <v>1110</v>
       </c>
     </row>
-    <row r="673" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O673" s="2"/>
-    </row>
     <row r="674" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A674" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="B674" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="O674" s="2" t="s">
-        <v>1113</v>
-      </c>
+      <c r="O674" s="2"/>
     </row>
     <row r="675" spans="1:15" ht="24.95" customHeight="1">
       <c r="A675" s="2" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="O675" s="2" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="676" spans="1:15" ht="24.95" customHeight="1">
       <c r="A676" s="2" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="O676" s="2" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="677" spans="1:15" ht="24.95" customHeight="1">
       <c r="A677" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B677" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="O677" s="2" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="678" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A678" s="2" t="s">
         <v>1120</v>
       </c>
-      <c r="B677" s="2" t="s">
+      <c r="B678" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="O677" s="2" t="s">
+      <c r="O678" s="2" t="s">
         <v>1122</v>
       </c>
     </row>
-    <row r="678" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O678" s="2"/>
-    </row>
     <row r="679" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A679" s="2" t="s">
-        <v>1123</v>
-      </c>
-      <c r="B679" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="O679" s="2" t="s">
-        <v>1125</v>
-      </c>
+      <c r="O679" s="2"/>
     </row>
     <row r="680" spans="1:15" ht="24.95" customHeight="1">
       <c r="A680" s="2" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>599</v>
+        <v>1124</v>
       </c>
       <c r="O680" s="2" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="681" spans="1:15" ht="24.95" customHeight="1">
       <c r="A681" s="2" t="s">
-        <v>2462</v>
+        <v>1126</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="O681" s="2" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="682" spans="1:15" ht="24.95" customHeight="1">
       <c r="A682" s="2" t="s">
+        <v>2462</v>
+      </c>
+      <c r="B682" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="O682" s="2" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="683" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A683" s="2" t="s">
         <v>1129</v>
       </c>
-      <c r="B682" s="2" t="s">
+      <c r="B683" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="O682" s="2" t="s">
+      <c r="O683" s="2" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="683" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O683" s="2"/>
-    </row>
     <row r="684" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A684" s="2" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B684" s="2" t="s">
-        <v>920</v>
-      </c>
-      <c r="O684" s="2" t="s">
-        <v>3086</v>
-      </c>
+      <c r="O684" s="2"/>
     </row>
     <row r="685" spans="1:15" ht="24.95" customHeight="1">
       <c r="A685" s="2" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>1132</v>
+        <v>920</v>
       </c>
       <c r="O685" s="2" t="s">
-        <v>984</v>
+        <v>3086</v>
       </c>
     </row>
     <row r="686" spans="1:15" ht="24.95" customHeight="1">
       <c r="A686" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B686" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="O686" s="2" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="687" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A687" s="2" t="s">
         <v>1133</v>
       </c>
-      <c r="O686" s="2" t="s">
+      <c r="O687" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="687" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O687" s="2"/>
-    </row>
     <row r="688" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A688" s="2" t="s">
-        <v>2525</v>
-      </c>
-      <c r="O688" s="2" t="s">
-        <v>2527</v>
-      </c>
+      <c r="O688" s="2"/>
     </row>
     <row r="689" spans="1:15" ht="24.95" customHeight="1">
       <c r="A689" s="2" t="s">
+        <v>2525</v>
+      </c>
+      <c r="O689" s="2" t="s">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="690" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A690" s="2" t="s">
         <v>2526</v>
       </c>
-      <c r="O689" s="2" t="s">
+      <c r="O690" s="2" t="s">
         <v>2528</v>
       </c>
     </row>
-    <row r="690" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O690" s="2"/>
-    </row>
     <row r="691" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A691" s="2" t="s">
-        <v>1135</v>
-      </c>
-      <c r="B691" s="2" t="s">
-        <v>1136</v>
-      </c>
-      <c r="O691" s="2" t="s">
-        <v>1137</v>
-      </c>
+      <c r="O691" s="2"/>
     </row>
     <row r="692" spans="1:15" ht="24.95" customHeight="1">
       <c r="A692" s="2" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="O692" s="2" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="693" spans="1:15" ht="24.95" customHeight="1">
       <c r="A693" s="2" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>964</v>
+        <v>1139</v>
       </c>
       <c r="O693" s="2" t="s">
-        <v>965</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="694" spans="1:15" ht="24.95" customHeight="1">
       <c r="A694" s="2" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>1143</v>
+        <v>964</v>
       </c>
       <c r="O694" s="2" t="s">
-        <v>1144</v>
+        <v>965</v>
       </c>
     </row>
     <row r="695" spans="1:15" ht="24.95" customHeight="1">
       <c r="A695" s="2" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="O695" s="2" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="696" spans="1:15" ht="24.95" customHeight="1">
       <c r="A696" s="2" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>1821</v>
+        <v>1146</v>
       </c>
       <c r="O696" s="2" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="697" spans="1:15" ht="24.95" customHeight="1">
       <c r="A697" s="2" t="s">
-        <v>3027</v>
+        <v>1148</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>1151</v>
+        <v>1821</v>
       </c>
       <c r="O697" s="2" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="698" spans="1:15" ht="24.95" customHeight="1">
       <c r="A698" s="2" t="s">
+        <v>3027</v>
+      </c>
+      <c r="B698" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="O698" s="2" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="699" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A699" s="2" t="s">
         <v>1155</v>
       </c>
-      <c r="B698" s="2" t="s">
+      <c r="B699" s="2" t="s">
         <v>1156</v>
       </c>
-      <c r="O698" s="2" t="s">
+      <c r="O699" s="2" t="s">
         <v>1157</v>
       </c>
     </row>
-    <row r="699" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O699" s="2"/>
-    </row>
     <row r="700" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A700" s="2" t="s">
-        <v>3052</v>
-      </c>
-      <c r="O700" s="2" t="s">
-        <v>3057</v>
-      </c>
+      <c r="O700" s="2"/>
     </row>
     <row r="701" spans="1:15" ht="24.95" customHeight="1">
       <c r="A701" s="2" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="O701" s="2" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="702" spans="1:15" ht="24.95" customHeight="1">
       <c r="A702" s="2" t="s">
-        <v>3067</v>
+        <v>3053</v>
       </c>
       <c r="O702" s="2" t="s">
-        <v>3068</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="703" spans="1:15" ht="24.95" customHeight="1">
       <c r="A703" s="2" t="s">
-        <v>3054</v>
+        <v>3067</v>
       </c>
       <c r="O703" s="2" t="s">
-        <v>3059</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="704" spans="1:15" ht="24.95" customHeight="1">
       <c r="A704" s="2" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="O704" s="2" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="705" spans="1:15" ht="24.95" customHeight="1">
       <c r="A705" s="2" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="O705" s="2" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="706" spans="1:15" ht="24.95" customHeight="1">
       <c r="A706" s="2" t="s">
+        <v>3056</v>
+      </c>
+      <c r="O706" s="2" t="s">
+        <v>3061</v>
+      </c>
+    </row>
+    <row r="707" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A707" s="2" t="s">
         <v>3065</v>
       </c>
-      <c r="O706" s="2" t="s">
+      <c r="O707" s="2" t="s">
         <v>3087</v>
       </c>
     </row>
-    <row r="707" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O707" s="2"/>
-    </row>
     <row r="708" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A708" s="2" t="s">
+      <c r="O708" s="2"/>
+    </row>
+    <row r="709" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A709" s="2" t="s">
         <v>1158</v>
       </c>
-      <c r="B708" s="2" t="s">
+      <c r="B709" s="2" t="s">
         <v>1761</v>
       </c>
-      <c r="O708" s="2" t="s">
+      <c r="O709" s="2" t="s">
         <v>1159</v>
       </c>
     </row>
-    <row r="709" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O709" s="2"/>
-    </row>
     <row r="710" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A710" s="2" t="s">
+      <c r="O710" s="2"/>
+    </row>
+    <row r="711" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A711" s="2" t="s">
         <v>1160</v>
       </c>
-      <c r="B710" s="2" t="s">
+      <c r="B711" s="2" t="s">
         <v>1161</v>
       </c>
-      <c r="O710" s="2" t="s">
+      <c r="O711" s="2" t="s">
         <v>1162</v>
       </c>
     </row>
-    <row r="711" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O711" s="2"/>
-    </row>
     <row r="712" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A712" s="2" t="s">
-        <v>3174</v>
-      </c>
-      <c r="O712" s="2" t="s">
-        <v>3175</v>
-      </c>
+      <c r="O712" s="2"/>
     </row>
     <row r="713" spans="1:15" ht="24.95" customHeight="1">
       <c r="A713" s="2" t="s">
-        <v>2989</v>
+        <v>3174</v>
       </c>
       <c r="O713" s="2" t="s">
-        <v>2991</v>
+        <v>3175</v>
       </c>
     </row>
     <row r="714" spans="1:15" ht="24.95" customHeight="1">
       <c r="A714" s="2" t="s">
+        <v>2989</v>
+      </c>
+      <c r="O714" s="2" t="s">
+        <v>2991</v>
+      </c>
+    </row>
+    <row r="715" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A715" s="2" t="s">
         <v>2990</v>
       </c>
-      <c r="O714" s="2" t="s">
+      <c r="O715" s="2" t="s">
         <v>2992</v>
       </c>
     </row>
-    <row r="715" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O715" s="2"/>
-    </row>
     <row r="716" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A716" s="2" t="s">
-        <v>1163</v>
-      </c>
-      <c r="B716" s="2" t="s">
-        <v>1164</v>
-      </c>
-      <c r="O716" s="2" t="s">
-        <v>1165</v>
-      </c>
+      <c r="O716" s="2"/>
     </row>
     <row r="717" spans="1:15" ht="24.95" customHeight="1">
       <c r="A717" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B717" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="O717" s="2" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="718" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A718" s="2" t="s">
         <v>1166</v>
       </c>
-      <c r="B717" s="2" t="s">
+      <c r="B718" s="2" t="s">
         <v>1167</v>
       </c>
-      <c r="O717" s="2" t="s">
+      <c r="O718" s="2" t="s">
         <v>1168</v>
       </c>
     </row>
-    <row r="718" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O718" s="2"/>
-    </row>
     <row r="719" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A719" s="2" t="s">
+      <c r="O719" s="2"/>
+    </row>
+    <row r="720" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A720" s="2" t="s">
         <v>1169</v>
       </c>
-      <c r="B719" s="2" t="s">
+      <c r="B720" s="2" t="s">
         <v>1170</v>
       </c>
-      <c r="O719" s="2" t="s">
+      <c r="O720" s="2" t="s">
         <v>1171</v>
       </c>
     </row>
-    <row r="720" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O720" s="2"/>
-    </row>
     <row r="721" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A721" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="O721" s="2" t="s">
-        <v>1173</v>
-      </c>
+      <c r="O721" s="2"/>
     </row>
     <row r="722" spans="1:15" ht="24.95" customHeight="1">
       <c r="A722" s="2" t="s">
-        <v>1174</v>
-      </c>
-      <c r="B722" s="2" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="O722" s="2" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="723" spans="1:15" ht="24.95" customHeight="1">
       <c r="A723" s="2" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="O723" s="2" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="724" spans="1:15" ht="24.95" customHeight="1">
       <c r="A724" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B724" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="O724" s="2" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="725" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A725" s="2" t="s">
         <v>1180</v>
       </c>
-      <c r="B724" s="2" t="s">
+      <c r="B725" s="2" t="s">
         <v>1181</v>
       </c>
-      <c r="O724" s="2" t="s">
+      <c r="O725" s="2" t="s">
         <v>1182</v>
       </c>
     </row>
-    <row r="725" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O725" s="2"/>
-    </row>
     <row r="726" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A726" s="2" t="s">
-        <v>1183</v>
-      </c>
-      <c r="B726" s="2" t="s">
-        <v>1184</v>
-      </c>
-      <c r="O726" s="2" t="s">
-        <v>1185</v>
-      </c>
+      <c r="O726" s="2"/>
     </row>
     <row r="727" spans="1:15" ht="24.95" customHeight="1">
       <c r="A727" s="2" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="O727" s="2" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="728" spans="1:15" ht="24.95" customHeight="1">
       <c r="A728" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B728" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="O728" s="2" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="729" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A729" s="2" t="s">
         <v>1189</v>
       </c>
-      <c r="B728" s="2" t="s">
+      <c r="B729" s="2" t="s">
         <v>1190</v>
       </c>
-      <c r="O728" s="2" t="s">
+      <c r="O729" s="2" t="s">
         <v>1191</v>
       </c>
     </row>
-    <row r="729" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O729" s="2"/>
-    </row>
     <row r="730" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A730" s="2" t="s">
-        <v>1192</v>
-      </c>
-      <c r="B730" s="2" t="s">
-        <v>1193</v>
-      </c>
-      <c r="O730" s="2" t="s">
-        <v>1194</v>
-      </c>
+      <c r="O730" s="2"/>
     </row>
     <row r="731" spans="1:15" ht="24.95" customHeight="1">
       <c r="A731" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B731" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="O731" s="2" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="732" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A732" s="2" t="s">
         <v>1195</v>
       </c>
-      <c r="B731" s="2" t="s">
+      <c r="B732" s="2" t="s">
         <v>1196</v>
       </c>
-      <c r="O731" s="2" t="s">
+      <c r="O732" s="2" t="s">
         <v>1197</v>
       </c>
     </row>
-    <row r="732" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O732" s="2"/>
-    </row>
     <row r="733" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A733" s="2" t="s">
-        <v>1198</v>
-      </c>
-      <c r="B733" s="2" t="s">
-        <v>1199</v>
-      </c>
-      <c r="O733" s="2" t="s">
-        <v>1200</v>
-      </c>
+      <c r="O733" s="2"/>
     </row>
     <row r="734" spans="1:15" ht="24.95" customHeight="1">
       <c r="A734" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B734" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="O734" s="2" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="735" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A735" s="2" t="s">
         <v>1201</v>
       </c>
-      <c r="B734" s="2" t="s">
+      <c r="B735" s="2" t="s">
         <v>1202</v>
       </c>
-      <c r="O734" s="2" t="s">
+      <c r="O735" s="2" t="s">
         <v>1203</v>
       </c>
     </row>
-    <row r="735" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O735" s="2"/>
-    </row>
-    <row r="736" spans="1:15" ht="33">
-      <c r="A736" s="2" t="s">
+    <row r="736" spans="1:15" ht="24.95" customHeight="1">
+      <c r="O736" s="2"/>
+    </row>
+    <row r="737" spans="1:15" ht="33">
+      <c r="A737" s="2" t="s">
         <v>2966</v>
       </c>
-      <c r="O736" s="3" t="s">
+      <c r="O737" s="3" t="s">
         <v>2967</v>
       </c>
     </row>
-    <row r="737" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O737" s="2"/>
-    </row>
     <row r="738" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A738" s="2" t="s">
+      <c r="O738" s="2"/>
+    </row>
+    <row r="739" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A739" s="2" t="s">
         <v>1204</v>
       </c>
-      <c r="O738" s="2" t="s">
+      <c r="O739" s="2" t="s">
         <v>1773</v>
       </c>
     </row>
-    <row r="739" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O739" s="2"/>
-    </row>
     <row r="740" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A740" s="2" t="s">
-        <v>1205</v>
-      </c>
-      <c r="B740" s="2" t="s">
-        <v>1206</v>
-      </c>
-      <c r="O740" s="2" t="s">
-        <v>1207</v>
-      </c>
+      <c r="O740" s="2"/>
     </row>
     <row r="741" spans="1:15" ht="24.95" customHeight="1">
       <c r="A741" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B741" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="O741" s="2" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="742" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A742" s="2" t="s">
         <v>1208</v>
       </c>
-      <c r="B741" s="2" t="s">
+      <c r="B742" s="2" t="s">
         <v>1209</v>
       </c>
-      <c r="O741" s="2" t="s">
+      <c r="O742" s="2" t="s">
         <v>1210</v>
       </c>
     </row>
-    <row r="742" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O742" s="2"/>
-    </row>
     <row r="743" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A743" s="2" t="s">
+      <c r="O743" s="2"/>
+    </row>
+    <row r="744" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A744" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="B743" s="2" t="s">
+      <c r="B744" s="2" t="s">
         <v>1212</v>
       </c>
-      <c r="O743" s="2" t="s">
+      <c r="O744" s="2" t="s">
         <v>1213</v>
       </c>
     </row>
-    <row r="744" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O744" s="2"/>
-    </row>
     <row r="745" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A745" s="2" t="s">
-        <v>1214</v>
-      </c>
-      <c r="B745" s="2" t="s">
-        <v>1215</v>
-      </c>
-      <c r="O745" s="2" t="s">
-        <v>1216</v>
-      </c>
+      <c r="O745" s="2"/>
     </row>
     <row r="746" spans="1:15" ht="24.95" customHeight="1">
       <c r="A746" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B746" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="O746" s="2" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="747" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A747" s="2" t="s">
         <v>1217</v>
       </c>
-      <c r="B746" s="2" t="s">
+      <c r="B747" s="2" t="s">
         <v>1218</v>
       </c>
-      <c r="O746" s="2" t="s">
+      <c r="O747" s="2" t="s">
         <v>1219</v>
       </c>
     </row>
-    <row r="747" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O747" s="2"/>
-    </row>
     <row r="748" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A748" s="2" t="s">
+      <c r="O748" s="2"/>
+    </row>
+    <row r="749" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A749" s="2" t="s">
         <v>1220</v>
       </c>
-      <c r="B748" s="2" t="s">
+      <c r="B749" s="2" t="s">
         <v>1763</v>
       </c>
-      <c r="O748" s="2" t="s">
+      <c r="O749" s="2" t="s">
         <v>1221</v>
       </c>
     </row>
-    <row r="749" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O749" s="2"/>
-    </row>
     <row r="750" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A750" s="2" t="s">
+      <c r="O750" s="2"/>
+    </row>
+    <row r="751" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A751" s="2" t="s">
         <v>3178</v>
       </c>
-      <c r="O750" s="2" t="s">
+      <c r="O751" s="2" t="s">
         <v>3180</v>
       </c>
     </row>
-    <row r="751" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O751" s="2"/>
-    </row>
     <row r="752" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A752" s="2" t="s">
+      <c r="O752" s="2"/>
+    </row>
+    <row r="753" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A753" s="2" t="s">
         <v>1222</v>
       </c>
-      <c r="O752" s="2" t="s">
+      <c r="O753" s="2" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="753" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O753" s="2"/>
-    </row>
     <row r="754" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A754" s="2" t="s">
-        <v>3176</v>
-      </c>
-      <c r="O754" s="2" t="s">
-        <v>3177</v>
-      </c>
+      <c r="O754" s="2"/>
     </row>
     <row r="755" spans="1:15" ht="24.95" customHeight="1">
       <c r="A755" s="2" t="s">
+        <v>3176</v>
+      </c>
+      <c r="O755" s="2" t="s">
+        <v>3177</v>
+      </c>
+    </row>
+    <row r="756" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A756" s="2" t="s">
         <v>1223</v>
       </c>
-      <c r="B755" s="2" t="s">
+      <c r="B756" s="2" t="s">
         <v>1762</v>
       </c>
-      <c r="O755" s="2" t="s">
+      <c r="O756" s="2" t="s">
         <v>1224</v>
       </c>
     </row>
-    <row r="756" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O756" s="2"/>
-    </row>
     <row r="757" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A757" s="2" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B757" s="2" t="s">
-        <v>1226</v>
-      </c>
-      <c r="O757" s="2" t="s">
-        <v>1227</v>
-      </c>
+      <c r="O757" s="2"/>
     </row>
     <row r="758" spans="1:15" ht="24.95" customHeight="1">
       <c r="A758" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B758" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="O758" s="2" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="759" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A759" s="2" t="s">
         <v>1228</v>
       </c>
-      <c r="B758" s="2" t="s">
+      <c r="B759" s="2" t="s">
         <v>1229</v>
       </c>
-      <c r="O758" s="2" t="s">
+      <c r="O759" s="2" t="s">
         <v>1230</v>
       </c>
     </row>
-    <row r="759" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O759" s="2"/>
-    </row>
     <row r="760" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A760" s="2" t="s">
-        <v>1231</v>
-      </c>
-      <c r="B760" s="2" t="s">
-        <v>1232</v>
-      </c>
-      <c r="O760" s="2" t="s">
-        <v>1233</v>
-      </c>
+      <c r="O760" s="2"/>
     </row>
     <row r="761" spans="1:15" ht="24.95" customHeight="1">
       <c r="A761" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B761" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="O761" s="2" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="762" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A762" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="B761" s="2" t="s">
+      <c r="B762" s="2" t="s">
         <v>1235</v>
       </c>
-      <c r="O761" s="2" t="s">
+      <c r="O762" s="2" t="s">
         <v>1236</v>
       </c>
     </row>
-    <row r="762" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O762" s="2"/>
-    </row>
     <row r="763" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A763" s="2" t="s">
-        <v>1237</v>
-      </c>
-      <c r="B763" s="2" t="s">
-        <v>1238</v>
-      </c>
-      <c r="O763" s="2" t="s">
-        <v>1239</v>
-      </c>
+      <c r="O763" s="2"/>
     </row>
     <row r="764" spans="1:15" ht="24.95" customHeight="1">
       <c r="A764" s="2" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="B764" s="2" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="O764" s="2" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="765" spans="1:15" ht="24.95" customHeight="1">
       <c r="A765" s="2" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="B765" s="2" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="O765" s="2" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="766" spans="1:15" ht="24.95" customHeight="1">
       <c r="A766" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B766" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="O766" s="2" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="767" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A767" s="2" t="s">
         <v>1246</v>
       </c>
-      <c r="B766" s="2" t="s">
+      <c r="B767" s="2" t="s">
         <v>1247</v>
       </c>
-      <c r="O766" s="2" t="s">
+      <c r="O767" s="2" t="s">
         <v>1248</v>
       </c>
     </row>
-    <row r="767" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O767" s="2"/>
-    </row>
     <row r="768" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A768" s="2" t="s">
-        <v>1600</v>
-      </c>
-      <c r="O768" s="2" t="s">
-        <v>1602</v>
-      </c>
+      <c r="O768" s="2"/>
     </row>
     <row r="769" spans="1:15" ht="24.95" customHeight="1">
       <c r="A769" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="O769" s="2" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="770" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A770" s="2" t="s">
         <v>1601</v>
       </c>
-      <c r="O769" s="3" t="s">
+      <c r="O770" s="3" t="s">
         <v>1603</v>
       </c>
-    </row>
-    <row r="770" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O770" s="2"/>
     </row>
     <row r="771" spans="1:15" ht="24.95" customHeight="1">
       <c r="O771" s="2"/>
@@ -19742,8 +19755,8 @@
     <row r="866" spans="15:15" ht="24.95" customHeight="1">
       <c r="O866" s="2"/>
     </row>
-    <row r="868" spans="15:15" ht="24.95" customHeight="1">
-      <c r="O868" s="2"/>
+    <row r="867" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O867" s="2"/>
     </row>
     <row r="869" spans="15:15" ht="24.95" customHeight="1">
       <c r="O869" s="2"/>
@@ -20922,23 +20935,23 @@
       <c r="O1260" s="2"/>
     </row>
     <row r="1261" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A1261" s="5"/>
-      <c r="B1261" s="5"/>
-      <c r="D1261" s="5"/>
-      <c r="E1261" s="5"/>
-      <c r="F1261" s="5"/>
-      <c r="G1261" s="5"/>
-      <c r="H1261" s="5"/>
-      <c r="I1261" s="5"/>
-      <c r="J1261" s="5"/>
-      <c r="K1261" s="5"/>
-      <c r="L1261" s="5"/>
-      <c r="M1261" s="5"/>
-      <c r="N1261" s="5"/>
-      <c r="O1261" s="6"/>
+      <c r="O1261" s="2"/>
     </row>
     <row r="1262" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O1262" s="2"/>
+      <c r="A1262" s="5"/>
+      <c r="B1262" s="5"/>
+      <c r="D1262" s="5"/>
+      <c r="E1262" s="5"/>
+      <c r="F1262" s="5"/>
+      <c r="G1262" s="5"/>
+      <c r="H1262" s="5"/>
+      <c r="I1262" s="5"/>
+      <c r="J1262" s="5"/>
+      <c r="K1262" s="5"/>
+      <c r="L1262" s="5"/>
+      <c r="M1262" s="5"/>
+      <c r="N1262" s="5"/>
+      <c r="O1262" s="6"/>
     </row>
     <row r="1263" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1263" s="2"/>
@@ -22452,8 +22465,11 @@
     <row r="1766" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1766" s="2"/>
     </row>
+    <row r="1767" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1767" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="O1:O1469" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="O1:O1470" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Among Us code\TheOtherUs\TheOtherUs-Edited-Lite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF8FC71-4866-40D9-A00B-7ABE58C97FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34EB389-B5AF-49FE-A90B-EF95D6DE9FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1275" yWindow="1260" windowWidth="25755" windowHeight="14940" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Role Description" sheetId="11" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Options!$O$1:$O$1470</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Options!$O$1:$O$1471</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3611" uniqueCount="3285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3615" uniqueCount="3289">
   <si>
     <t>English</t>
   </si>
@@ -9452,10 +9452,6 @@
 Thanks to The Other Roles, The Other Roles CE, The Other Roles GM IA, Town of Us, Stellar Roles, SuperNewRoles!
 Thanks to miniduikboot &amp; GD for hosting modded servers (and so much more)
 </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀非目标后叠加的惩罚冷却</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -11718,6 +11714,26 @@
   </si>
   <si>
     <t>小丑可以拖动尸体</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bountyHunterChangeTargetCooldown</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>更换目标冷却时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeTarget</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>更换目标</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>错误击杀额外增加的冷却</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -12317,7 +12333,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1767"/>
+  <dimension ref="A1:Q1768"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40.375" style="2" customWidth="1"/>
@@ -12530,7 +12546,7 @@
     </row>
     <row r="17" spans="1:15" ht="24.95" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>2434</v>
@@ -12541,7 +12557,7 @@
     </row>
     <row r="18" spans="1:15" ht="24.95" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>2440</v>
@@ -12665,7 +12681,7 @@
     </row>
     <row r="30" spans="1:15" ht="24.95" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>42</v>
@@ -12731,13 +12747,13 @@
     </row>
     <row r="36" spans="1:15" ht="24.95" customHeight="1">
       <c r="A36" s="2" t="s">
+        <v>2872</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>2873</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="O36" s="3" t="s">
         <v>2874</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>2875</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="24.95" customHeight="1">
@@ -12822,13 +12838,13 @@
     </row>
     <row r="45" spans="1:15" ht="24.95" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>2863</v>
+      </c>
+      <c r="O45" s="3" t="s">
         <v>2864</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>2865</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="24.95" customHeight="1">
@@ -12881,11 +12897,11 @@
     </row>
     <row r="51" spans="1:15" ht="24.95" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="B51" s="3"/>
       <c r="O51" s="3" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="24.95" customHeight="1">
@@ -12950,10 +12966,10 @@
     </row>
     <row r="58" spans="1:15" ht="24.95" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>1150</v>
@@ -12961,10 +12977,10 @@
     </row>
     <row r="59" spans="1:15" ht="24.95" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="24.95" customHeight="1">
@@ -13110,13 +13126,13 @@
     </row>
     <row r="76" spans="1:15" ht="24.95" customHeight="1">
       <c r="A76" s="2" t="s">
+        <v>2856</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>2858</v>
+      </c>
+      <c r="O76" s="2" t="s">
         <v>2857</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>2859</v>
-      </c>
-      <c r="O76" s="2" t="s">
-        <v>2858</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="24.95" customHeight="1">
@@ -13143,18 +13159,18 @@
     </row>
     <row r="79" spans="1:15" ht="24.95" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="24.95" customHeight="1">
       <c r="A80" s="2" t="s">
+        <v>3041</v>
+      </c>
+      <c r="O80" s="2" t="s">
         <v>3042</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>3043</v>
       </c>
     </row>
     <row r="81" spans="1:15" ht="24.95" customHeight="1">
@@ -13443,79 +13459,79 @@
     </row>
     <row r="108" spans="1:15" ht="24.95" customHeight="1">
       <c r="A108" s="2" t="s">
+        <v>3122</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>3123</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>3124</v>
-      </c>
       <c r="O108" s="2" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
     </row>
     <row r="109" spans="1:15" ht="24.95" customHeight="1">
       <c r="A109" s="2" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
     </row>
     <row r="110" spans="1:15" ht="24.95" customHeight="1">
       <c r="A110" s="2" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="111" spans="1:15" ht="24.95" customHeight="1">
       <c r="A111" s="2" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="112" spans="1:15" ht="24.95" customHeight="1">
       <c r="A112" s="2" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="O112" s="2" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
     </row>
     <row r="113" spans="1:15" ht="24.95" customHeight="1">
       <c r="A113" s="2" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
       <c r="O113" s="2" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="114" spans="1:15" ht="24.95" customHeight="1">
       <c r="A114" s="2" t="s">
+        <v>3155</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>3156</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="O114" s="2" t="s">
         <v>3157</v>
-      </c>
-      <c r="O114" s="2" t="s">
-        <v>3158</v>
       </c>
     </row>
     <row r="115" spans="1:15" ht="24.95" customHeight="1">
@@ -13523,42 +13539,42 @@
     </row>
     <row r="116" spans="1:15" ht="24.95" customHeight="1">
       <c r="A116" s="2" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="O116" s="2" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
     </row>
     <row r="117" spans="1:15" ht="24.95" customHeight="1">
       <c r="A117" s="2" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="O117" s="2" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
     </row>
     <row r="118" spans="1:15" ht="24.95" customHeight="1">
       <c r="A118" s="2" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="O118" s="2" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="119" spans="1:15" ht="24.95" customHeight="1">
       <c r="A119" s="2" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="O119" s="2" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="120" spans="1:15" ht="24.95" customHeight="1">
       <c r="A120" s="2" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="O120" s="2" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
     </row>
     <row r="121" spans="1:15" ht="24.95" customHeight="1">
@@ -13599,13 +13615,13 @@
     </row>
     <row r="125" spans="1:15" ht="24.95" customHeight="1">
       <c r="A125" s="2" t="s">
+        <v>3015</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>3016</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="O125" s="2" t="s">
         <v>3017</v>
-      </c>
-      <c r="O125" s="2" t="s">
-        <v>3018</v>
       </c>
     </row>
     <row r="126" spans="1:15" ht="24.95" customHeight="1">
@@ -13951,18 +13967,18 @@
     </row>
     <row r="159" spans="1:15" ht="24.95" customHeight="1">
       <c r="A159" s="2" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="O159" s="2" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="160" spans="1:15" ht="24.95" customHeight="1">
       <c r="A160" s="2" t="s">
-        <v>2915</v>
+        <v>2914</v>
       </c>
       <c r="O160" s="2" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="161" spans="1:15" ht="24.95" customHeight="1">
@@ -14298,26 +14314,26 @@
     </row>
     <row r="194" spans="1:15" ht="24.95" customHeight="1">
       <c r="A194" s="2" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="O194" s="2" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="195" spans="1:15" ht="24.95" customHeight="1">
       <c r="A195" s="2" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="O195" s="2" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="196" spans="1:15" ht="24.95" customHeight="1">
       <c r="A196" s="2" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="O196" s="2" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
     </row>
     <row r="197" spans="1:15" ht="24.95" customHeight="1">
@@ -15672,7 +15688,7 @@
         <v>627</v>
       </c>
       <c r="O338" s="3" t="s">
-        <v>2771</v>
+        <v>3288</v>
       </c>
     </row>
     <row r="339" spans="1:15" ht="24.95" customHeight="1">
@@ -15697,510 +15713,510 @@
         <v>633</v>
       </c>
     </row>
-    <row r="342" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A342" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="B342" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="O342" s="3" t="s">
-        <v>636</v>
+    <row r="341" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A341" s="2" t="s">
+        <v>3284</v>
+      </c>
+      <c r="O341" s="3" t="s">
+        <v>3285</v>
       </c>
     </row>
     <row r="343" spans="1:15" ht="24.95" customHeight="1">
       <c r="A343" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="O343" s="3" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="344" spans="1:15" ht="24.95" customHeight="1">
       <c r="A344" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="O344" s="4" t="s">
-        <v>642</v>
+        <v>638</v>
+      </c>
+      <c r="O344" s="3" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="345" spans="1:15" ht="24.95" customHeight="1">
       <c r="A345" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="O345" s="2" t="s">
-        <v>645</v>
+        <v>641</v>
+      </c>
+      <c r="O345" s="4" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="346" spans="1:15" ht="24.95" customHeight="1">
       <c r="A346" s="2" t="s">
-        <v>2482</v>
+        <v>643</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>2489</v>
+        <v>644</v>
       </c>
       <c r="O346" s="2" t="s">
-        <v>2485</v>
+        <v>645</v>
       </c>
     </row>
     <row r="347" spans="1:15" ht="24.95" customHeight="1">
       <c r="A347" s="2" t="s">
+        <v>2482</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>2489</v>
+      </c>
+      <c r="O347" s="2" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="348" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A348" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B347" s="2" t="s">
+      <c r="B348" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="O347" s="2" t="s">
-        <v>2912</v>
-      </c>
-    </row>
-    <row r="348" spans="1:15" ht="24.95" customHeight="1">
-      <c r="B348" s="3"/>
-      <c r="M348" s="3"/>
+      <c r="O348" s="2" t="s">
+        <v>2911</v>
+      </c>
     </row>
     <row r="349" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A349" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="B349" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="O349" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B349" s="3"/>
+      <c r="M349" s="3"/>
     </row>
     <row r="350" spans="1:15" ht="24.95" customHeight="1">
       <c r="A350" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="B350" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="M350" s="3"/>
-      <c r="O350" s="3" t="s">
-        <v>653</v>
+        <v>648</v>
+      </c>
+      <c r="B350" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="O350" s="2" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="351" spans="1:15" ht="24.95" customHeight="1">
       <c r="A351" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="B351" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="O351" s="2" t="s">
-        <v>656</v>
+        <v>651</v>
+      </c>
+      <c r="B351" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="M351" s="3"/>
+      <c r="O351" s="3" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="352" spans="1:15" ht="24.95" customHeight="1">
       <c r="A352" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="O352" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="353" spans="1:15" ht="24.95" customHeight="1">
       <c r="A353" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="O353" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="354" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A354" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="B353" s="2" t="s">
+      <c r="B354" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="O353" s="2" t="s">
+      <c r="O354" s="2" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="354" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O354" s="2"/>
-    </row>
     <row r="355" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A355" s="2" t="s">
+      <c r="O355" s="2"/>
+    </row>
+    <row r="356" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A356" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="B355" s="2" t="s">
+      <c r="B356" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="O355" s="2" t="s">
+      <c r="O356" s="2" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="356" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O356" s="2"/>
-    </row>
     <row r="357" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A357" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="B357" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="O357" s="2" t="s">
-        <v>668</v>
-      </c>
+      <c r="O357" s="2"/>
     </row>
     <row r="358" spans="1:15" ht="24.95" customHeight="1">
       <c r="A358" s="2" t="s">
-        <v>2586</v>
+        <v>666</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="O358" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="359" spans="1:15" ht="24.95" customHeight="1">
       <c r="A359" s="2" t="s">
-        <v>2585</v>
+        <v>2586</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="O359" s="3" t="s">
-        <v>672</v>
+        <v>669</v>
+      </c>
+      <c r="O359" s="2" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="360" spans="1:15" ht="24.95" customHeight="1">
       <c r="A360" s="2" t="s">
-        <v>673</v>
+        <v>2585</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="O360" s="2" t="s">
-        <v>675</v>
+        <v>671</v>
+      </c>
+      <c r="O360" s="3" t="s">
+        <v>672</v>
       </c>
     </row>
     <row r="361" spans="1:15" ht="24.95" customHeight="1">
       <c r="A361" s="2" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="O361" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="362" spans="1:15" ht="24.95" customHeight="1">
       <c r="A362" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="B362" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="O362" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="363" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A363" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="B362" s="2" t="s">
+      <c r="B363" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="O362" s="2" t="s">
+      <c r="O363" s="2" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="363" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O363" s="2"/>
-    </row>
     <row r="364" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A364" s="2" t="s">
+      <c r="O364" s="2"/>
+    </row>
+    <row r="365" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A365" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="B364" s="2" t="s">
+      <c r="B365" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="O364" s="2" t="s">
+      <c r="O365" s="2" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="365" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O365" s="2"/>
-    </row>
     <row r="366" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A366" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="B366" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="O366" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="O366" s="2"/>
     </row>
     <row r="367" spans="1:15" ht="24.95" customHeight="1">
       <c r="A367" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="O367" s="2" t="s">
-        <v>688</v>
+        <v>650</v>
       </c>
     </row>
     <row r="368" spans="1:15" ht="24.95" customHeight="1">
       <c r="A368" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="O368" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="369" spans="1:15" ht="24.95" customHeight="1">
       <c r="A369" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="O369" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="370" spans="1:15" ht="24.95" customHeight="1">
       <c r="A370" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="O370" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
     <row r="371" spans="1:15" ht="24.95" customHeight="1">
       <c r="A371" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="O371" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="372" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A372" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="B371" s="2" t="s">
+      <c r="B372" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="O371" s="2" t="s">
+      <c r="O372" s="2" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="372" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O372" s="2"/>
-    </row>
     <row r="373" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A373" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="B373" s="2" t="s">
-        <v>1733</v>
-      </c>
-      <c r="O373" s="2" t="s">
-        <v>702</v>
-      </c>
+      <c r="O373" s="2"/>
     </row>
     <row r="374" spans="1:15" ht="24.95" customHeight="1">
       <c r="A374" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="O374" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="375" spans="1:15" ht="24.95" customHeight="1">
       <c r="A375" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="O375" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="376" spans="1:15" ht="24.95" customHeight="1">
       <c r="A376" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="O376" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="377" spans="1:15" ht="24.95" customHeight="1">
       <c r="A377" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="O377" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="378" spans="1:15" ht="24.95" customHeight="1">
       <c r="A378" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="O378" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="379" spans="1:15" ht="24.95" customHeight="1">
       <c r="A379" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="O379" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="380" spans="1:15" ht="24.95" customHeight="1">
       <c r="A380" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="B380" s="2" t="s">
+        <v>1739</v>
+      </c>
+      <c r="O380" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="381" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A381" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="B380" s="2" t="s">
+      <c r="B381" s="2" t="s">
         <v>1740</v>
       </c>
-      <c r="O380" s="2" t="s">
+      <c r="O381" s="2" t="s">
         <v>716</v>
-      </c>
-    </row>
-    <row r="382" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A382" s="2" t="s">
-        <v>2293</v>
-      </c>
-      <c r="B382" s="2" t="s">
-        <v>2300</v>
-      </c>
-      <c r="O382" s="3" t="s">
-        <v>2298</v>
       </c>
     </row>
     <row r="383" spans="1:15" ht="24.95" customHeight="1">
       <c r="A383" s="2" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>2301</v>
-      </c>
-      <c r="O383" s="2" t="s">
-        <v>2297</v>
+        <v>2300</v>
+      </c>
+      <c r="O383" s="3" t="s">
+        <v>2298</v>
       </c>
     </row>
     <row r="384" spans="1:15" ht="24.95" customHeight="1">
       <c r="A384" s="2" t="s">
+        <v>2294</v>
+      </c>
+      <c r="B384" s="2" t="s">
+        <v>2301</v>
+      </c>
+      <c r="O384" s="2" t="s">
+        <v>2297</v>
+      </c>
+    </row>
+    <row r="385" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A385" s="2" t="s">
         <v>2295</v>
       </c>
-      <c r="B384" s="2" t="s">
+      <c r="B385" s="2" t="s">
         <v>2299</v>
       </c>
-      <c r="O384" s="2" t="s">
+      <c r="O385" s="2" t="s">
         <v>2296</v>
       </c>
     </row>
-    <row r="385" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O385" s="2"/>
-    </row>
     <row r="386" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A386" s="2" t="s">
-        <v>2607</v>
-      </c>
-      <c r="B386" s="2" t="s">
-        <v>2600</v>
-      </c>
-      <c r="O386" s="2" t="s">
-        <v>2602</v>
-      </c>
+      <c r="O386" s="2"/>
     </row>
     <row r="387" spans="1:15" ht="24.95" customHeight="1">
       <c r="A387" s="2" t="s">
-        <v>2606</v>
+        <v>2607</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>2599</v>
+        <v>2600</v>
       </c>
       <c r="O387" s="2" t="s">
-        <v>2601</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="388" spans="1:15" ht="24.95" customHeight="1">
       <c r="A388" s="2" t="s">
-        <v>2597</v>
+        <v>2606</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>2598</v>
+        <v>2599</v>
       </c>
       <c r="O388" s="2" t="s">
-        <v>2603</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="389" spans="1:15" ht="24.95" customHeight="1">
       <c r="A389" s="2" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>2594</v>
+        <v>2598</v>
       </c>
       <c r="O389" s="2" t="s">
-        <v>2595</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="390" spans="1:15" ht="24.95" customHeight="1">
       <c r="A390" s="2" t="s">
-        <v>2604</v>
+        <v>2596</v>
+      </c>
+      <c r="B390" s="2" t="s">
+        <v>2594</v>
       </c>
       <c r="O390" s="2" t="s">
-        <v>2608</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="391" spans="1:15" ht="24.95" customHeight="1">
       <c r="A391" s="2" t="s">
+        <v>2604</v>
+      </c>
+      <c r="O391" s="2" t="s">
+        <v>2608</v>
+      </c>
+    </row>
+    <row r="392" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A392" s="2" t="s">
         <v>2605</v>
       </c>
-      <c r="O391" s="2" t="s">
+      <c r="O392" s="2" t="s">
         <v>2609</v>
       </c>
     </row>
-    <row r="392" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O392" s="2"/>
-    </row>
     <row r="393" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A393" s="2" t="s">
-        <v>3242</v>
-      </c>
-      <c r="O393" s="2" t="s">
-        <v>3244</v>
-      </c>
+      <c r="O393" s="2"/>
     </row>
     <row r="394" spans="1:15" ht="24.95" customHeight="1">
       <c r="A394" s="2" t="s">
+        <v>3241</v>
+      </c>
+      <c r="O394" s="2" t="s">
         <v>3243</v>
       </c>
-      <c r="O394" s="2" t="s">
-        <v>3245</v>
-      </c>
-    </row>
-    <row r="396" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A396" s="2" t="s">
-        <v>3258</v>
-      </c>
-      <c r="O396" s="2" t="s">
-        <v>3256</v>
+    </row>
+    <row r="395" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A395" s="2" t="s">
+        <v>3242</v>
+      </c>
+      <c r="O395" s="2" t="s">
+        <v>3244</v>
       </c>
     </row>
     <row r="397" spans="1:15" ht="24.95" customHeight="1">
@@ -16212,28 +16228,25 @@
       </c>
     </row>
     <row r="398" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O398" s="2"/>
+      <c r="A398" s="2" t="s">
+        <v>3256</v>
+      </c>
+      <c r="O398" s="2" t="s">
+        <v>3254</v>
+      </c>
     </row>
     <row r="399" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A399" s="2" t="s">
-        <v>2286</v>
-      </c>
-      <c r="B399" s="2" t="s">
-        <v>2285</v>
-      </c>
-      <c r="O399" s="2" t="s">
-        <v>768</v>
-      </c>
+      <c r="O399" s="2"/>
     </row>
     <row r="400" spans="1:15" ht="24.95" customHeight="1">
       <c r="A400" s="2" t="s">
-        <v>3029</v>
+        <v>2286</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>1641</v>
+        <v>2285</v>
       </c>
       <c r="O400" s="2" t="s">
-        <v>1759</v>
+        <v>768</v>
       </c>
     </row>
     <row r="401" spans="1:15" ht="24.95" customHeight="1">
@@ -16241,3234 +16254,3242 @@
         <v>3028</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>1664</v>
+        <v>1641</v>
       </c>
       <c r="O401" s="2" t="s">
-        <v>777</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="402" spans="1:15" ht="24.95" customHeight="1">
       <c r="A402" s="2" t="s">
-        <v>3217</v>
+        <v>3027</v>
       </c>
       <c r="B402" s="2" t="s">
+        <v>1664</v>
+      </c>
+      <c r="O402" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="403" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A403" s="2" t="s">
+        <v>3216</v>
+      </c>
+      <c r="B403" s="2" t="s">
         <v>1639</v>
       </c>
-      <c r="O402" s="2" t="s">
+      <c r="O403" s="2" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="403" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O403" s="2"/>
-    </row>
     <row r="404" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A404" s="2" t="s">
-        <v>3083</v>
-      </c>
-      <c r="B404" s="2" t="s">
-        <v>2882</v>
-      </c>
-      <c r="O404" s="2" t="s">
-        <v>2883</v>
-      </c>
+      <c r="O404" s="2"/>
     </row>
     <row r="405" spans="1:15" ht="24.95" customHeight="1">
       <c r="A405" s="2" t="s">
-        <v>3000</v>
+        <v>3082</v>
+      </c>
+      <c r="B405" s="2" t="s">
+        <v>2881</v>
       </c>
       <c r="O405" s="2" t="s">
-        <v>3001</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="406" spans="1:15" ht="24.95" customHeight="1">
       <c r="A406" s="2" t="s">
-        <v>3013</v>
+        <v>2999</v>
       </c>
       <c r="O406" s="2" t="s">
-        <v>3015</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="407" spans="1:15" ht="24.95" customHeight="1">
       <c r="A407" s="2" t="s">
         <v>3012</v>
       </c>
-      <c r="O407" s="3" t="s">
+      <c r="O407" s="2" t="s">
         <v>3014</v>
       </c>
     </row>
     <row r="408" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O408" s="2"/>
+      <c r="A408" s="2" t="s">
+        <v>3011</v>
+      </c>
+      <c r="O408" s="3" t="s">
+        <v>3013</v>
+      </c>
     </row>
     <row r="409" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A409" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="B409" s="2" t="s">
-        <v>718</v>
-      </c>
-      <c r="O409" s="2" t="s">
-        <v>719</v>
-      </c>
+      <c r="O409" s="2"/>
     </row>
     <row r="410" spans="1:15" ht="24.95" customHeight="1">
       <c r="A410" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="O410" s="2" t="s">
-        <v>1759</v>
+        <v>719</v>
       </c>
     </row>
     <row r="411" spans="1:15" ht="24.95" customHeight="1">
       <c r="A411" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B411" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="O411" s="2" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="412" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A412" s="2" t="s">
+        <v>3282</v>
+      </c>
+      <c r="O412" s="2" t="s">
         <v>3283</v>
       </c>
-      <c r="O411" s="2" t="s">
-        <v>3284</v>
-      </c>
-    </row>
-    <row r="412" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O412" s="2"/>
     </row>
     <row r="413" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A413" s="2" t="s">
-        <v>1677</v>
-      </c>
-      <c r="O413" s="2" t="s">
-        <v>1684</v>
-      </c>
+      <c r="O413" s="2"/>
     </row>
     <row r="414" spans="1:15" ht="24.95" customHeight="1">
       <c r="A414" s="2" t="s">
-        <v>1678</v>
-      </c>
-      <c r="B414" s="2" t="s">
-        <v>1657</v>
+        <v>1677</v>
       </c>
       <c r="O414" s="2" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="415" spans="1:15" ht="24.95" customHeight="1">
       <c r="A415" s="2" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>1653</v>
+        <v>1657</v>
       </c>
       <c r="O415" s="2" t="s">
-        <v>1689</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="416" spans="1:15" ht="24.95" customHeight="1">
       <c r="A416" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="O416" s="2" t="s">
-        <v>1659</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="417" spans="1:15" ht="24.95" customHeight="1">
       <c r="A417" s="2" t="s">
-        <v>1690</v>
+        <v>1680</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>1663</v>
+        <v>1654</v>
       </c>
       <c r="O417" s="2" t="s">
-        <v>1691</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="418" spans="1:15" ht="24.95" customHeight="1">
       <c r="A418" s="2" t="s">
-        <v>1681</v>
+        <v>1690</v>
+      </c>
+      <c r="B418" s="2" t="s">
+        <v>1663</v>
       </c>
       <c r="O418" s="2" t="s">
-        <v>1686</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="419" spans="1:15" ht="24.95" customHeight="1">
       <c r="A419" s="2" t="s">
-        <v>1682</v>
-      </c>
-      <c r="B419" s="2" t="s">
-        <v>1658</v>
+        <v>1681</v>
       </c>
       <c r="O419" s="2" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="420" spans="1:15" ht="24.95" customHeight="1">
       <c r="A420" s="2" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B420" s="2" t="s">
+        <v>1658</v>
+      </c>
+      <c r="O420" s="2" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="421" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A421" s="2" t="s">
         <v>1683</v>
       </c>
-      <c r="B420" s="2" t="s">
+      <c r="B421" s="2" t="s">
         <v>1656</v>
       </c>
-      <c r="O420" s="2" t="s">
+      <c r="O421" s="2" t="s">
         <v>1687</v>
       </c>
     </row>
-    <row r="421" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O421" s="2"/>
-    </row>
     <row r="422" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A422" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="B422" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="O422" s="2" t="s">
-        <v>724</v>
-      </c>
+      <c r="O422" s="2"/>
     </row>
     <row r="423" spans="1:15" ht="24.95" customHeight="1">
       <c r="A423" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="B423" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="O423" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="424" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A424" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="B423" s="2" t="s">
+      <c r="B424" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="O423" s="2" t="s">
+      <c r="O424" s="2" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="424" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O424" s="2"/>
-    </row>
     <row r="425" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A425" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="B425" s="2" t="s">
-        <v>2408</v>
-      </c>
-      <c r="O425" s="2" t="s">
-        <v>729</v>
-      </c>
+      <c r="O425" s="2"/>
     </row>
     <row r="426" spans="1:15" ht="24.95" customHeight="1">
       <c r="A426" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="O426" s="2" t="s">
-        <v>2861</v>
+        <v>729</v>
       </c>
     </row>
     <row r="427" spans="1:15" ht="24.95" customHeight="1">
       <c r="A427" s="2" t="s">
-        <v>2863</v>
+        <v>730</v>
+      </c>
+      <c r="B427" s="2" t="s">
+        <v>2409</v>
       </c>
       <c r="O427" s="2" t="s">
+        <v>2860</v>
+      </c>
+    </row>
+    <row r="428" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A428" s="2" t="s">
         <v>2862</v>
       </c>
-    </row>
-    <row r="428" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O428" s="2"/>
+      <c r="O428" s="2" t="s">
+        <v>2861</v>
+      </c>
     </row>
     <row r="429" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A429" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="B429" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="O429" s="2" t="s">
-        <v>733</v>
-      </c>
+      <c r="O429" s="2"/>
     </row>
     <row r="430" spans="1:15" ht="24.95" customHeight="1">
       <c r="A430" s="2" t="s">
-        <v>1605</v>
+        <v>731</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="O430" s="2" t="s">
-        <v>492</v>
+        <v>733</v>
       </c>
     </row>
     <row r="431" spans="1:15" ht="24.95" customHeight="1">
       <c r="A431" s="2" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="O431" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="432" spans="1:15" ht="24.95" customHeight="1">
       <c r="A432" s="2" t="s">
-        <v>736</v>
+        <v>1606</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O432" s="2" t="s">
-        <v>738</v>
+        <v>495</v>
       </c>
     </row>
     <row r="433" spans="1:15" ht="24.95" customHeight="1">
       <c r="A433" s="2" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="O433" s="2" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="434" spans="1:15" ht="24.95" customHeight="1">
       <c r="A434" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>1640</v>
+        <v>740</v>
       </c>
       <c r="O434" s="2" t="s">
-        <v>1760</v>
+        <v>741</v>
       </c>
     </row>
     <row r="435" spans="1:15" ht="24.95" customHeight="1">
       <c r="A435" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>744</v>
+        <v>1640</v>
       </c>
       <c r="O435" s="2" t="s">
-        <v>745</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="436" spans="1:15" ht="24.95" customHeight="1">
       <c r="A436" s="2" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="O436" s="2" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
     </row>
     <row r="437" spans="1:15" ht="24.95" customHeight="1">
       <c r="A437" s="2" t="s">
-        <v>2404</v>
+        <v>746</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>2405</v>
+        <v>747</v>
       </c>
       <c r="O437" s="2" t="s">
-        <v>2406</v>
+        <v>748</v>
       </c>
     </row>
     <row r="438" spans="1:15" ht="24.95" customHeight="1">
       <c r="A438" s="2" t="s">
-        <v>1713</v>
+        <v>2404</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>749</v>
+        <v>2405</v>
       </c>
       <c r="O438" s="2" t="s">
-        <v>750</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="439" spans="1:15" ht="24.95" customHeight="1">
       <c r="A439" s="2" t="s">
-        <v>751</v>
+        <v>1713</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="O439" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="440" spans="1:15" ht="24.95" customHeight="1">
       <c r="A440" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="O440" s="2" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
     </row>
     <row r="441" spans="1:15" ht="24.95" customHeight="1">
       <c r="A441" s="2" t="s">
-        <v>2402</v>
+        <v>754</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="O441" s="2" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="442" spans="1:15" ht="24.95" customHeight="1">
       <c r="A442" s="2" t="s">
+        <v>2402</v>
+      </c>
+      <c r="B442" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="O442" s="2" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="443" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A443" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="B442" s="2" t="s">
+      <c r="B443" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="O442" s="2" t="s">
+      <c r="O443" s="2" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="443" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O443" s="2"/>
-    </row>
     <row r="444" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A444" s="2" t="s">
-        <v>1610</v>
-      </c>
-      <c r="O444" s="2" t="s">
-        <v>2309</v>
-      </c>
+      <c r="O444" s="2"/>
     </row>
     <row r="445" spans="1:15" ht="24.95" customHeight="1">
       <c r="A445" s="2" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="O445" s="2" t="s">
-        <v>1631</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="446" spans="1:15" ht="24.95" customHeight="1">
       <c r="A446" s="2" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="O446" s="2" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="447" spans="1:15" ht="24.95" customHeight="1">
       <c r="A447" s="2" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="O447" s="2" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="448" spans="1:15" ht="24.95" customHeight="1">
       <c r="A448" s="2" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="O448" s="2" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="449" spans="1:15" ht="24.95" customHeight="1">
       <c r="A449" s="2" t="s">
-        <v>1618</v>
+        <v>1614</v>
       </c>
       <c r="O449" s="2" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="450" spans="1:15" ht="24.95" customHeight="1">
       <c r="A450" s="2" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="O450" s="2" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="451" spans="1:15" ht="24.95" customHeight="1">
       <c r="A451" s="2" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="O451" s="2" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="452" spans="1:15" ht="24.95" customHeight="1">
       <c r="A452" s="2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="O452" s="2" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="453" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A453" s="2" t="s">
         <v>1617</v>
       </c>
-      <c r="O452" s="2" t="s">
+      <c r="O453" s="2" t="s">
         <v>1624</v>
       </c>
     </row>
-    <row r="453" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O453" s="2"/>
-    </row>
     <row r="454" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A454" s="2" t="s">
-        <v>1619</v>
-      </c>
-      <c r="B454" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="O454" s="2" t="s">
-        <v>1623</v>
-      </c>
+      <c r="O454" s="2"/>
     </row>
     <row r="455" spans="1:15" ht="24.95" customHeight="1">
       <c r="A455" s="2" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="O455" s="2" t="s">
-        <v>495</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="456" spans="1:15" ht="24.95" customHeight="1">
       <c r="A456" s="2" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B456" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="O456" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="457" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A457" s="2" t="s">
         <v>2282</v>
       </c>
-      <c r="B456" s="2" t="s">
+      <c r="B457" s="2" t="s">
         <v>2283</v>
       </c>
-      <c r="O456" s="2" t="s">
+      <c r="O457" s="2" t="s">
         <v>2284</v>
       </c>
     </row>
-    <row r="457" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O457" s="2"/>
-    </row>
     <row r="458" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A458" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="B458" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="O458" s="2" t="s">
-        <v>789</v>
-      </c>
+      <c r="O458" s="2"/>
     </row>
     <row r="459" spans="1:15" ht="24.95" customHeight="1">
       <c r="A459" s="2" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="O459" s="2" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
     </row>
     <row r="460" spans="1:15" ht="24.95" customHeight="1">
       <c r="A460" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="B460" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="O460" s="2" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="461" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A461" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="B460" s="2" t="s">
+      <c r="B461" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="O460" s="2" t="s">
+      <c r="O461" s="2" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="461" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O461" s="2"/>
-    </row>
     <row r="462" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A462" s="2" t="s">
+      <c r="O462" s="2"/>
+    </row>
+    <row r="463" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A463" s="2" t="s">
         <v>1621</v>
       </c>
-      <c r="O462" s="2" t="s">
+      <c r="O463" s="2" t="s">
         <v>1622</v>
       </c>
     </row>
-    <row r="463" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O463" s="2"/>
-    </row>
     <row r="464" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A464" s="2" t="s">
-        <v>2985</v>
-      </c>
-      <c r="O464" s="2" t="s">
-        <v>2987</v>
-      </c>
+      <c r="O464" s="2"/>
     </row>
     <row r="465" spans="1:15" ht="24.95" customHeight="1">
       <c r="A465" s="2" t="s">
+        <v>2984</v>
+      </c>
+      <c r="O465" s="2" t="s">
         <v>2986</v>
       </c>
-      <c r="O465" s="2" t="s">
-        <v>2988</v>
-      </c>
     </row>
     <row r="466" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O466" s="2"/>
+      <c r="A466" s="2" t="s">
+        <v>2985</v>
+      </c>
+      <c r="O466" s="2" t="s">
+        <v>2987</v>
+      </c>
     </row>
     <row r="467" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A467" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="B467" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="O467" s="2" t="s">
-        <v>764</v>
-      </c>
+      <c r="O467" s="2"/>
     </row>
     <row r="468" spans="1:15" ht="24.95" customHeight="1">
       <c r="A468" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="O468" s="2" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="469" spans="1:15" ht="24.95" customHeight="1">
       <c r="A469" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B469" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="O469" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="470" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A470" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="B469" s="2" t="s">
+      <c r="B470" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="O469" s="2" t="s">
+      <c r="O470" s="2" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="470" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O470" s="2"/>
-    </row>
     <row r="471" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A471" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="B471" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="O471" s="2" t="s">
-        <v>773</v>
-      </c>
+      <c r="O471" s="2"/>
     </row>
     <row r="472" spans="1:15" ht="24.95" customHeight="1">
       <c r="A472" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="O472" s="2" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="473" spans="1:15" ht="24.95" customHeight="1">
       <c r="A473" s="2" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="O473" s="2" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
     </row>
     <row r="474" spans="1:15" ht="24.95" customHeight="1">
       <c r="A474" s="2" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="O474" s="2" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
     </row>
     <row r="475" spans="1:15" ht="24.95" customHeight="1">
       <c r="A475" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="B475" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="O475" s="2" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="476" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A476" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="O475" s="2" t="s">
+      <c r="O476" s="2" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="476" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O476" s="2"/>
-    </row>
     <row r="477" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A477" s="2" t="s">
-        <v>1609</v>
-      </c>
-      <c r="O477" s="2" t="s">
-        <v>3050</v>
-      </c>
+      <c r="O477" s="2"/>
     </row>
     <row r="478" spans="1:15" ht="24.95" customHeight="1">
       <c r="A478" s="2" t="s">
+        <v>1609</v>
+      </c>
+      <c r="O478" s="2" t="s">
+        <v>3049</v>
+      </c>
+    </row>
+    <row r="479" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A479" s="2" t="s">
         <v>1665</v>
       </c>
-      <c r="B478" s="2" t="s">
+      <c r="B479" s="2" t="s">
         <v>1796</v>
       </c>
-      <c r="O478" s="2" t="s">
-        <v>3051</v>
-      </c>
-    </row>
-    <row r="479" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O479" s="2"/>
+      <c r="O479" s="2" t="s">
+        <v>3050</v>
+      </c>
     </row>
     <row r="480" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A480" s="2" t="s">
-        <v>1645</v>
-      </c>
-      <c r="O480" s="2" t="s">
-        <v>1646</v>
-      </c>
+      <c r="O480" s="2"/>
     </row>
     <row r="481" spans="1:15" ht="24.95" customHeight="1">
       <c r="A481" s="2" t="s">
-        <v>1649</v>
-      </c>
-      <c r="B481" s="2" t="s">
-        <v>1658</v>
+        <v>1645</v>
       </c>
       <c r="O481" s="2" t="s">
-        <v>1688</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="482" spans="1:15" ht="24.95" customHeight="1">
       <c r="A482" s="2" t="s">
-        <v>781</v>
+        <v>1649</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="O482" s="2" t="s">
-        <v>1660</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="483" spans="1:15" ht="24.95" customHeight="1">
       <c r="A483" s="2" t="s">
-        <v>1647</v>
+        <v>781</v>
+      </c>
+      <c r="B483" s="2" t="s">
+        <v>1656</v>
       </c>
       <c r="O483" s="2" t="s">
-        <v>1648</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="484" spans="1:15" ht="24.95" customHeight="1">
       <c r="A484" s="2" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B484" s="2" t="s">
-        <v>1653</v>
+        <v>1647</v>
       </c>
       <c r="O484" s="2" t="s">
-        <v>1689</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="485" spans="1:15" ht="24.95" customHeight="1">
       <c r="A485" s="2" t="s">
-        <v>1655</v>
+        <v>1650</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="O485" s="2" t="s">
-        <v>1659</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="486" spans="1:15" ht="24.95" customHeight="1">
       <c r="A486" s="2" t="s">
-        <v>1652</v>
+        <v>1655</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>1663</v>
+        <v>1654</v>
       </c>
       <c r="O486" s="2" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="487" spans="1:15" ht="24.95" customHeight="1">
       <c r="A487" s="2" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B487" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="O487" s="2" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="488" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A488" s="2" t="s">
         <v>1651</v>
       </c>
-      <c r="B487" s="2" t="s">
+      <c r="B488" s="2" t="s">
         <v>1657</v>
       </c>
-      <c r="O487" s="2" t="s">
+      <c r="O488" s="2" t="s">
         <v>1661</v>
       </c>
     </row>
-    <row r="488" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O488" s="2"/>
-    </row>
     <row r="489" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A489" s="2" t="s">
-        <v>2905</v>
-      </c>
-      <c r="O489" s="2" t="s">
-        <v>2910</v>
-      </c>
+      <c r="O489" s="2"/>
     </row>
     <row r="490" spans="1:15" ht="24.95" customHeight="1">
       <c r="A490" s="2" t="s">
-        <v>2906</v>
+        <v>2904</v>
       </c>
       <c r="O490" s="2" t="s">
-        <v>2908</v>
+        <v>2909</v>
       </c>
     </row>
     <row r="491" spans="1:15" ht="24.95" customHeight="1">
       <c r="A491" s="2" t="s">
+        <v>2905</v>
+      </c>
+      <c r="O491" s="2" t="s">
         <v>2907</v>
-      </c>
-      <c r="O491" s="3" t="s">
-        <v>2909</v>
       </c>
     </row>
     <row r="492" spans="1:15" ht="24.95" customHeight="1">
       <c r="A492" s="2" t="s">
-        <v>2973</v>
+        <v>2906</v>
       </c>
       <c r="O492" s="3" t="s">
-        <v>2999</v>
-      </c>
-    </row>
-    <row r="494" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A494" s="2" t="s">
-        <v>3203</v>
-      </c>
-      <c r="O494" s="3" t="s">
-        <v>3206</v>
+        <v>2908</v>
+      </c>
+    </row>
+    <row r="493" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A493" s="2" t="s">
+        <v>2972</v>
+      </c>
+      <c r="O493" s="3" t="s">
+        <v>2998</v>
       </c>
     </row>
     <row r="495" spans="1:15" ht="24.95" customHeight="1">
       <c r="A495" s="2" t="s">
-        <v>3204</v>
+        <v>3202</v>
       </c>
       <c r="O495" s="3" t="s">
         <v>3205</v>
       </c>
     </row>
     <row r="496" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O496" s="2"/>
+      <c r="A496" s="2" t="s">
+        <v>3203</v>
+      </c>
+      <c r="O496" s="3" t="s">
+        <v>3204</v>
+      </c>
     </row>
     <row r="497" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A497" s="2" t="s">
-        <v>2480</v>
-      </c>
-      <c r="O497" s="3" t="s">
-        <v>2481</v>
-      </c>
+      <c r="O497" s="2"/>
     </row>
     <row r="498" spans="1:15" ht="24.95" customHeight="1">
       <c r="A498" s="2" t="s">
-        <v>2470</v>
-      </c>
-      <c r="O498" s="2" t="s">
-        <v>2468</v>
+        <v>2480</v>
+      </c>
+      <c r="O498" s="3" t="s">
+        <v>2481</v>
       </c>
     </row>
     <row r="499" spans="1:15" ht="24.95" customHeight="1">
       <c r="A499" s="2" t="s">
+        <v>2470</v>
+      </c>
+      <c r="O499" s="2" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="500" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A500" s="2" t="s">
         <v>2471</v>
       </c>
-      <c r="O499" s="2" t="s">
+      <c r="O500" s="2" t="s">
         <v>2469</v>
       </c>
     </row>
-    <row r="500" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O500" s="2"/>
-    </row>
     <row r="501" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A501" s="2" t="s">
-        <v>1607</v>
-      </c>
-      <c r="B501" s="2" t="s">
-        <v>1797</v>
-      </c>
-      <c r="O501" s="2" t="s">
-        <v>1632</v>
-      </c>
+      <c r="O501" s="2"/>
     </row>
     <row r="502" spans="1:15" ht="24.95" customHeight="1">
       <c r="A502" s="2" t="s">
-        <v>1608</v>
+        <v>1607</v>
+      </c>
+      <c r="B502" s="2" t="s">
+        <v>1797</v>
       </c>
       <c r="O502" s="2" t="s">
-        <v>2413</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="503" spans="1:15" ht="24.95" customHeight="1">
       <c r="A503" s="2" t="s">
-        <v>1633</v>
-      </c>
-      <c r="B503" s="2" t="s">
-        <v>2414</v>
+        <v>1608</v>
       </c>
       <c r="O503" s="2" t="s">
-        <v>1795</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="504" spans="1:15" ht="24.95" customHeight="1">
       <c r="A504" s="2" t="s">
-        <v>937</v>
+        <v>1633</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="O504" s="2" t="s">
-        <v>2417</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="505" spans="1:15" ht="24.95" customHeight="1">
       <c r="A505" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>2418</v>
+        <v>2415</v>
       </c>
       <c r="O505" s="2" t="s">
-        <v>939</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="506" spans="1:15" ht="24.95" customHeight="1">
       <c r="A506" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="B506" s="2" t="s">
+        <v>2418</v>
+      </c>
+      <c r="O506" s="2" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="507" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A507" s="2" t="s">
         <v>940</v>
       </c>
-      <c r="B506" s="2" t="s">
+      <c r="B507" s="2" t="s">
         <v>2416</v>
       </c>
-      <c r="O506" s="2" t="s">
+      <c r="O507" s="2" t="s">
         <v>2412</v>
       </c>
     </row>
-    <row r="507" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O507" s="2"/>
-    </row>
     <row r="508" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A508" s="2" t="s">
-        <v>966</v>
-      </c>
-      <c r="O508" s="2" t="s">
-        <v>967</v>
-      </c>
+      <c r="O508" s="2"/>
     </row>
     <row r="509" spans="1:15" ht="24.95" customHeight="1">
       <c r="A509" s="2" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="O509" s="2" t="s">
-        <v>2855</v>
+        <v>967</v>
       </c>
     </row>
     <row r="510" spans="1:15" ht="24.95" customHeight="1">
       <c r="A510" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="O510" s="2" t="s">
-        <v>970</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="511" spans="1:15" ht="24.95" customHeight="1">
       <c r="A511" s="2" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="O511" s="2" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="512" spans="1:15" ht="24.95" customHeight="1">
       <c r="A512" s="2" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="O512" s="2" t="s">
-        <v>2512</v>
+        <v>972</v>
       </c>
     </row>
     <row r="513" spans="1:15" ht="24.95" customHeight="1">
       <c r="A513" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="O513" s="2" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="514" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A514" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="O513" s="2" t="s">
+      <c r="O514" s="2" t="s">
         <v>975</v>
       </c>
     </row>
-    <row r="514" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O514" s="2"/>
-    </row>
     <row r="515" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A515" s="2" t="s">
-        <v>3226</v>
-      </c>
-      <c r="B515" s="2" t="s">
-        <v>3228</v>
-      </c>
-      <c r="O515" s="2" t="s">
-        <v>3227</v>
-      </c>
+      <c r="O515" s="2"/>
     </row>
     <row r="516" spans="1:15" ht="24.95" customHeight="1">
       <c r="A516" s="2" t="s">
-        <v>795</v>
+        <v>3225</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>796</v>
+        <v>3227</v>
       </c>
       <c r="O516" s="2" t="s">
-        <v>1638</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="517" spans="1:15" ht="24.95" customHeight="1">
       <c r="A517" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="O517" s="2" t="s">
-        <v>799</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="518" spans="1:15" ht="24.95" customHeight="1">
       <c r="A518" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="B518" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="O518" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="519" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A519" s="2" t="s">
         <v>1637</v>
       </c>
-      <c r="B518" s="2" t="s">
+      <c r="B519" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="O518" s="3" t="s">
+      <c r="O519" s="3" t="s">
         <v>1636</v>
-      </c>
-    </row>
-    <row r="520" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A520" s="2" t="s">
-        <v>3220</v>
-      </c>
-      <c r="O520" s="3" t="s">
-        <v>3223</v>
       </c>
     </row>
     <row r="521" spans="1:15" ht="24.95" customHeight="1">
       <c r="A521" s="2" t="s">
-        <v>3224</v>
+        <v>3219</v>
       </c>
       <c r="O521" s="3" t="s">
-        <v>3225</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="522" spans="1:15" ht="24.95" customHeight="1">
       <c r="A522" s="2" t="s">
-        <v>3218</v>
+        <v>3223</v>
       </c>
       <c r="O522" s="3" t="s">
-        <v>3221</v>
+        <v>3224</v>
       </c>
     </row>
     <row r="523" spans="1:15" ht="24.95" customHeight="1">
       <c r="A523" s="2" t="s">
-        <v>3219</v>
+        <v>3217</v>
       </c>
       <c r="O523" s="3" t="s">
-        <v>3222</v>
-      </c>
-    </row>
-    <row r="526" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A526" s="2" t="s">
+        <v>3220</v>
+      </c>
+    </row>
+    <row r="524" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A524" s="2" t="s">
+        <v>3218</v>
+      </c>
+      <c r="O524" s="3" t="s">
+        <v>3221</v>
+      </c>
+    </row>
+    <row r="527" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A527" s="2" t="s">
+        <v>2883</v>
+      </c>
+      <c r="B527" s="2" t="s">
         <v>2884</v>
       </c>
-      <c r="B526" s="2" t="s">
+      <c r="O527" s="3" t="s">
         <v>2885</v>
-      </c>
-      <c r="O526" s="3" t="s">
-        <v>2886</v>
-      </c>
-    </row>
-    <row r="528" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A528" s="2" t="s">
-        <v>3272</v>
-      </c>
-      <c r="B528" s="2" t="s">
-        <v>3271</v>
-      </c>
-      <c r="O528" s="3" t="s">
-        <v>3270</v>
       </c>
     </row>
     <row r="529" spans="1:15" ht="24.95" customHeight="1">
       <c r="A529" s="2" t="s">
-        <v>3273</v>
+        <v>3271</v>
+      </c>
+      <c r="B529" s="2" t="s">
+        <v>3270</v>
       </c>
       <c r="O529" s="3" t="s">
-        <v>3275</v>
+        <v>3269</v>
       </c>
     </row>
     <row r="530" spans="1:15" ht="24.95" customHeight="1">
       <c r="A530" s="2" t="s">
+        <v>3272</v>
+      </c>
+      <c r="O530" s="3" t="s">
         <v>3274</v>
       </c>
-      <c r="O530" s="3" t="s">
-        <v>3276</v>
-      </c>
-    </row>
-    <row r="533" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O533" s="2"/>
+    </row>
+    <row r="531" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A531" s="2" t="s">
+        <v>3273</v>
+      </c>
+      <c r="O531" s="3" t="s">
+        <v>3275</v>
+      </c>
     </row>
     <row r="534" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A534" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="B534" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="O534" s="2" t="s">
-        <v>803</v>
-      </c>
+      <c r="O534" s="2"/>
     </row>
     <row r="535" spans="1:15" ht="24.95" customHeight="1">
       <c r="A535" s="2" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="O535" s="2" t="s">
-        <v>519</v>
+        <v>803</v>
       </c>
     </row>
     <row r="536" spans="1:15" ht="24.95" customHeight="1">
       <c r="A536" s="2" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="O536" s="2" t="s">
-        <v>808</v>
+        <v>519</v>
       </c>
     </row>
     <row r="537" spans="1:15" ht="24.95" customHeight="1">
       <c r="A537" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="B537" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="O537" s="2" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="538" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A538" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="B537" s="2" t="s">
+      <c r="B538" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="O537" s="2" t="s">
+      <c r="O538" s="2" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="538" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O538" s="2"/>
-    </row>
     <row r="539" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A539" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="B539" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="O539" s="2" t="s">
-        <v>812</v>
-      </c>
+      <c r="O539" s="2"/>
     </row>
     <row r="540" spans="1:15" ht="24.95" customHeight="1">
       <c r="A540" s="2" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="O540" s="2" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
     </row>
     <row r="541" spans="1:15" ht="24.95" customHeight="1">
       <c r="A541" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="O541" s="2" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
     </row>
     <row r="542" spans="1:15" ht="24.95" customHeight="1">
       <c r="A542" s="2" t="s">
-        <v>2419</v>
+        <v>819</v>
+      </c>
+      <c r="B542" s="2" t="s">
+        <v>820</v>
       </c>
       <c r="O542" s="2" t="s">
-        <v>2420</v>
+        <v>821</v>
       </c>
     </row>
     <row r="543" spans="1:15" ht="24.95" customHeight="1">
       <c r="A543" s="2" t="s">
-        <v>822</v>
+        <v>2419</v>
       </c>
       <c r="O543" s="2" t="s">
-        <v>823</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="544" spans="1:15" ht="24.95" customHeight="1">
       <c r="A544" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="O544" s="2" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="545" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A545" s="2" t="s">
         <v>2292</v>
       </c>
-      <c r="O544" s="2" t="s">
+      <c r="O545" s="2" t="s">
         <v>2466</v>
       </c>
     </row>
-    <row r="545" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O545" s="2"/>
-    </row>
     <row r="546" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A546" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="B546" s="2" t="s">
-        <v>1669</v>
-      </c>
-      <c r="O546" s="2" t="s">
-        <v>825</v>
-      </c>
+      <c r="O546" s="2"/>
     </row>
     <row r="547" spans="1:15" ht="24.95" customHeight="1">
       <c r="A547" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="B547" s="2" t="s">
+        <v>1669</v>
+      </c>
+      <c r="O547" s="2" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="548" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A548" s="2" t="s">
         <v>813</v>
       </c>
-      <c r="B547" s="2" t="s">
+      <c r="B548" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="O547" s="2" t="s">
+      <c r="O548" s="2" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="548" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O548" s="2"/>
-    </row>
     <row r="549" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A549" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="B549" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="O549" s="2" t="s">
-        <v>828</v>
-      </c>
+      <c r="O549" s="2"/>
     </row>
     <row r="550" spans="1:15" ht="24.95" customHeight="1">
       <c r="A550" s="2" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="O550" s="2" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
     </row>
     <row r="551" spans="1:15" ht="24.95" customHeight="1">
       <c r="A551" s="2" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="O551" s="2" t="s">
-        <v>2465</v>
+        <v>831</v>
       </c>
     </row>
     <row r="552" spans="1:15" ht="24.95" customHeight="1">
       <c r="A552" s="2" t="s">
-        <v>1666</v>
+        <v>832</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>1668</v>
+        <v>833</v>
       </c>
       <c r="O552" s="2" t="s">
-        <v>1667</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="553" spans="1:15" ht="24.95" customHeight="1">
       <c r="A553" s="2" t="s">
-        <v>834</v>
+        <v>1666</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>835</v>
+        <v>1668</v>
       </c>
       <c r="O553" s="2" t="s">
-        <v>836</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="554" spans="1:15" ht="24.95" customHeight="1">
       <c r="A554" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B554" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="O554" s="2" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="555" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A555" s="2" t="s">
         <v>837</v>
       </c>
-      <c r="B554" s="2" t="s">
+      <c r="B555" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="O554" s="2" t="s">
+      <c r="O555" s="2" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="555" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O555" s="2"/>
-    </row>
     <row r="556" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A556" s="2" t="s">
+      <c r="O556" s="2"/>
+    </row>
+    <row r="557" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A557" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="B556" s="2" t="s">
+      <c r="B557" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="O556" s="2" t="s">
+      <c r="O557" s="2" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="557" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O557" s="2"/>
-    </row>
     <row r="558" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A558" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="B558" s="2" t="s">
-        <v>844</v>
-      </c>
-      <c r="O558" s="2" t="s">
-        <v>845</v>
-      </c>
+      <c r="O558" s="2"/>
     </row>
     <row r="559" spans="1:15" ht="24.95" customHeight="1">
       <c r="A559" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="O559" s="2" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
     </row>
     <row r="560" spans="1:15" ht="24.95" customHeight="1">
       <c r="A560" s="2" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="O560" s="2" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
     </row>
     <row r="561" spans="1:15" ht="24.95" customHeight="1">
       <c r="A561" s="2" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="O561" s="2" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
     </row>
     <row r="562" spans="1:15" ht="24.95" customHeight="1">
       <c r="A562" s="2" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="O562" s="2" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
     </row>
     <row r="563" spans="1:15" ht="24.95" customHeight="1">
       <c r="A563" s="2" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>651</v>
+        <v>856</v>
       </c>
       <c r="O563" s="2" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="564" spans="1:15" ht="24.95" customHeight="1">
       <c r="A564" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="B564" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="O564" s="2" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="565" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A565" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="B564" s="2" t="s">
+      <c r="B565" s="2" t="s">
         <v>1794</v>
       </c>
-      <c r="O564" s="2" t="s">
+      <c r="O565" s="2" t="s">
         <v>1793</v>
       </c>
     </row>
-    <row r="565" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O565" s="2"/>
-    </row>
     <row r="566" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A566" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="B566" s="2" t="s">
-        <v>862</v>
-      </c>
-      <c r="O566" s="2" t="s">
-        <v>863</v>
-      </c>
+      <c r="O566" s="2"/>
     </row>
     <row r="567" spans="1:15" ht="24.95" customHeight="1">
       <c r="A567" s="2" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="O567" s="2" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
     </row>
     <row r="568" spans="1:15" ht="24.95" customHeight="1">
       <c r="A568" s="2" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="O568" s="2" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
     </row>
     <row r="569" spans="1:15" ht="24.95" customHeight="1">
       <c r="A569" s="2" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="O569" s="2" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
     </row>
     <row r="570" spans="1:15" ht="24.95" customHeight="1">
       <c r="A570" s="2" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="O570" s="2" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
     </row>
     <row r="571" spans="1:15" ht="24.95" customHeight="1">
       <c r="A571" s="2" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="O571" s="2" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
     </row>
     <row r="572" spans="1:15" ht="24.95" customHeight="1">
       <c r="A572" s="2" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="O572" s="2" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
     </row>
     <row r="573" spans="1:15" ht="24.95" customHeight="1">
       <c r="A573" s="2" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="O573" s="2" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
     </row>
     <row r="574" spans="1:15" ht="24.95" customHeight="1">
       <c r="A574" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="B574" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="O574" s="2" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="575" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A575" s="2" t="s">
         <v>885</v>
       </c>
-      <c r="B574" s="2" t="s">
+      <c r="B575" s="2" t="s">
         <v>886</v>
       </c>
-      <c r="O574" s="2" t="s">
+      <c r="O575" s="2" t="s">
         <v>887</v>
       </c>
     </row>
-    <row r="575" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O575" s="2"/>
-    </row>
     <row r="576" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A576" s="2" t="s">
-        <v>1779</v>
-      </c>
-      <c r="B576" s="2" t="s">
-        <v>888</v>
-      </c>
-      <c r="O576" s="2" t="s">
-        <v>889</v>
-      </c>
+      <c r="O576" s="2"/>
     </row>
     <row r="577" spans="1:15" ht="24.95" customHeight="1">
       <c r="A577" s="2" t="s">
-        <v>1780</v>
+        <v>1779</v>
+      </c>
+      <c r="B577" s="2" t="s">
+        <v>888</v>
       </c>
       <c r="O577" s="2" t="s">
-        <v>1781</v>
+        <v>889</v>
       </c>
     </row>
     <row r="578" spans="1:15" ht="24.95" customHeight="1">
       <c r="A578" s="2" t="s">
-        <v>890</v>
-      </c>
-      <c r="B578" s="2" t="s">
-        <v>891</v>
+        <v>1780</v>
       </c>
       <c r="O578" s="2" t="s">
-        <v>892</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="579" spans="1:15" ht="24.95" customHeight="1">
       <c r="A579" s="2" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="O579" s="2" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
     </row>
     <row r="580" spans="1:15" ht="24.95" customHeight="1">
       <c r="A580" s="2" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="O580" s="2" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
     </row>
     <row r="581" spans="1:15" ht="24.95" customHeight="1">
       <c r="A581" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B581" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="O581" s="2" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="582" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A582" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="B581" s="2" t="s">
+      <c r="B582" s="2" t="s">
         <v>1774</v>
       </c>
-      <c r="O581" s="2" t="s">
+      <c r="O582" s="2" t="s">
         <v>900</v>
       </c>
     </row>
-    <row r="582" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O582" s="2"/>
-    </row>
     <row r="583" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A583" s="2" t="s">
-        <v>901</v>
-      </c>
-      <c r="B583" s="2" t="s">
-        <v>902</v>
-      </c>
-      <c r="O583" s="2" t="s">
-        <v>903</v>
-      </c>
+      <c r="O583" s="2"/>
     </row>
     <row r="584" spans="1:15" ht="24.95" customHeight="1">
       <c r="A584" s="2" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="O584" s="2" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
     </row>
     <row r="585" spans="1:15" ht="24.95" customHeight="1">
       <c r="A585" s="2" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="O585" s="2" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
     </row>
     <row r="586" spans="1:15" ht="24.95" customHeight="1">
       <c r="A586" s="2" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="O586" s="2" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
     </row>
     <row r="587" spans="1:15" ht="24.95" customHeight="1">
       <c r="A587" s="2" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="O587" s="2" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
     <row r="588" spans="1:15" ht="24.95" customHeight="1">
       <c r="A588" s="2" t="s">
-        <v>2287</v>
+        <v>913</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>932</v>
+        <v>914</v>
       </c>
       <c r="O588" s="2" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
     </row>
     <row r="589" spans="1:15" ht="24.95" customHeight="1">
       <c r="A589" s="2" t="s">
-        <v>916</v>
+        <v>2287</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>917</v>
+        <v>932</v>
       </c>
       <c r="O589" s="2" t="s">
-        <v>2288</v>
+        <v>918</v>
       </c>
     </row>
     <row r="590" spans="1:15" ht="24.95" customHeight="1">
       <c r="A590" s="2" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="O590" s="2" t="s">
-        <v>921</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="591" spans="1:15" ht="24.95" customHeight="1">
       <c r="A591" s="2" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="O591" s="2" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
     </row>
     <row r="592" spans="1:15" ht="24.95" customHeight="1">
       <c r="A592" s="2" t="s">
-        <v>1782</v>
+        <v>922</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="O592" s="2" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="593" spans="1:15" ht="24.95" customHeight="1">
       <c r="A593" s="2" t="s">
-        <v>927</v>
-      </c>
-      <c r="B593" s="3" t="s">
-        <v>2289</v>
+        <v>1782</v>
+      </c>
+      <c r="B593" s="2" t="s">
+        <v>925</v>
       </c>
       <c r="O593" s="2" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="594" spans="1:15" ht="24.95" customHeight="1">
       <c r="A594" s="2" t="s">
-        <v>929</v>
-      </c>
-      <c r="B594" s="2" t="s">
-        <v>930</v>
+        <v>927</v>
+      </c>
+      <c r="B594" s="3" t="s">
+        <v>2289</v>
       </c>
       <c r="O594" s="2" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
     </row>
     <row r="595" spans="1:15" ht="24.95" customHeight="1">
       <c r="A595" s="2" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>897</v>
+        <v>930</v>
       </c>
       <c r="O595" s="2" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="596" spans="1:15" ht="24.95" customHeight="1">
       <c r="A596" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="B596" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="O596" s="2" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="597" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A597" s="2" t="s">
         <v>935</v>
       </c>
-      <c r="B596" s="2" t="s">
+      <c r="B597" s="2" t="s">
         <v>2290</v>
       </c>
-      <c r="O596" s="2" t="s">
+      <c r="O597" s="2" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="597" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O597" s="2"/>
-    </row>
     <row r="598" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A598" s="2" t="s">
-        <v>941</v>
-      </c>
-      <c r="B598" s="2" t="s">
-        <v>942</v>
-      </c>
-      <c r="O598" s="2" t="s">
-        <v>943</v>
-      </c>
+      <c r="O598" s="2"/>
     </row>
     <row r="599" spans="1:15" ht="24.95" customHeight="1">
       <c r="A599" s="2" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="O599" s="2" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
     </row>
     <row r="600" spans="1:15" ht="24.95" customHeight="1">
       <c r="A600" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="B600" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="O600" s="2" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="601" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A601" s="2" t="s">
         <v>947</v>
       </c>
-      <c r="B600" s="2" t="s">
+      <c r="B601" s="2" t="s">
         <v>948</v>
       </c>
-      <c r="O600" s="2" t="s">
+      <c r="O601" s="2" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="601" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O601" s="2"/>
-    </row>
     <row r="602" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A602" s="2" t="s">
-        <v>1675</v>
-      </c>
-      <c r="B602" s="2" t="s">
-        <v>950</v>
-      </c>
-      <c r="O602" s="2" t="s">
-        <v>951</v>
-      </c>
+      <c r="O602" s="2"/>
     </row>
     <row r="603" spans="1:15" ht="24.95" customHeight="1">
       <c r="A603" s="2" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B603" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="O603" s="2" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="604" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A604" s="2" t="s">
         <v>1676</v>
       </c>
-      <c r="B603" s="2" t="s">
+      <c r="B604" s="2" t="s">
         <v>952</v>
       </c>
-      <c r="O603" s="2" t="s">
+      <c r="O604" s="2" t="s">
         <v>953</v>
       </c>
     </row>
-    <row r="604" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O604" s="2"/>
-    </row>
     <row r="605" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A605" s="2" t="s">
-        <v>954</v>
-      </c>
-      <c r="B605" s="2" t="s">
-        <v>955</v>
-      </c>
-      <c r="O605" s="2" t="s">
-        <v>956</v>
-      </c>
+      <c r="O605" s="2"/>
     </row>
     <row r="606" spans="1:15" ht="24.95" customHeight="1">
       <c r="A606" s="2" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="O606" s="2" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
     </row>
     <row r="607" spans="1:15" ht="24.95" customHeight="1">
       <c r="A607" s="2" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="O607" s="2" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
     </row>
     <row r="608" spans="1:15" ht="24.95" customHeight="1">
       <c r="A608" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="B608" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="O608" s="2" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="609" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A609" s="2" t="s">
         <v>963</v>
       </c>
-      <c r="B608" s="2" t="s">
+      <c r="B609" s="2" t="s">
         <v>964</v>
       </c>
-      <c r="O608" s="2" t="s">
+      <c r="O609" s="2" t="s">
         <v>965</v>
       </c>
     </row>
-    <row r="609" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O609" s="2"/>
-    </row>
     <row r="610" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A610" s="2" t="s">
-        <v>976</v>
-      </c>
-      <c r="B610" s="2" t="s">
-        <v>977</v>
-      </c>
-      <c r="O610" s="2" t="s">
-        <v>978</v>
-      </c>
+      <c r="O610" s="2"/>
     </row>
     <row r="611" spans="1:15" ht="24.95" customHeight="1">
       <c r="A611" s="2" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="O611" s="2" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
     </row>
     <row r="612" spans="1:15" ht="24.95" customHeight="1">
       <c r="A612" s="2" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="O612" s="2" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
     </row>
     <row r="613" spans="1:15" ht="24.95" customHeight="1">
       <c r="A613" s="2" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="O613" s="2" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
     </row>
     <row r="614" spans="1:15" ht="24.95" customHeight="1">
       <c r="A614" s="2" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="O614" s="2" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
     </row>
     <row r="615" spans="1:15" ht="24.95" customHeight="1">
       <c r="A615" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="B615" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="O615" s="2" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="616" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A616" s="2" t="s">
         <v>991</v>
       </c>
-      <c r="B615" s="2" t="s">
+      <c r="B616" s="2" t="s">
         <v>992</v>
       </c>
-      <c r="O615" s="2" t="s">
+      <c r="O616" s="2" t="s">
         <v>993</v>
       </c>
     </row>
-    <row r="616" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O616" s="2"/>
-    </row>
     <row r="617" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A617" s="2" t="s">
-        <v>994</v>
-      </c>
-      <c r="B617" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="O617" s="2" t="s">
-        <v>996</v>
-      </c>
+      <c r="O617" s="2"/>
     </row>
     <row r="618" spans="1:15" ht="24.95" customHeight="1">
       <c r="A618" s="2" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="O618" s="2" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
     </row>
     <row r="619" spans="1:15" ht="24.95" customHeight="1">
       <c r="A619" s="2" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="O619" s="2" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
     </row>
     <row r="620" spans="1:15" ht="24.95" customHeight="1">
       <c r="A620" s="2" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="O620" s="2" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="621" spans="1:15" ht="24.95" customHeight="1">
       <c r="A621" s="2" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>964</v>
+        <v>1004</v>
       </c>
       <c r="O621" s="2" t="s">
-        <v>965</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="622" spans="1:15" ht="24.95" customHeight="1">
       <c r="A622" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B622" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="O622" s="2" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="623" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A623" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="B622" s="2" t="s">
+      <c r="B623" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="O622" s="2" t="s">
+      <c r="O623" s="2" t="s">
         <v>1009</v>
       </c>
     </row>
-    <row r="623" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O623" s="2"/>
-    </row>
     <row r="624" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A624" s="2" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B624" s="2" t="s">
-        <v>1011</v>
-      </c>
-      <c r="O624" s="2" t="s">
-        <v>633</v>
-      </c>
+      <c r="O624" s="2"/>
     </row>
     <row r="625" spans="1:15" ht="24.95" customHeight="1">
       <c r="A625" s="2" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="O625" s="2" t="s">
-        <v>1014</v>
+        <v>633</v>
       </c>
     </row>
     <row r="626" spans="1:15" ht="24.95" customHeight="1">
       <c r="A626" s="2" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="B626" s="2" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="O626" s="2" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="627" spans="1:15" ht="24.95" customHeight="1">
       <c r="A627" s="2" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="O627" s="2" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="628" spans="1:15" ht="24.95" customHeight="1">
       <c r="A628" s="2" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="O628" s="2" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="629" spans="1:15" ht="24.95" customHeight="1">
       <c r="A629" s="2" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="O629" s="2" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="630" spans="1:15" ht="24.95" customHeight="1">
       <c r="A630" s="2" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="O630" s="2" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="631" spans="1:15" ht="24.95" customHeight="1">
       <c r="A631" s="2" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="O631" s="2" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="632" spans="1:15" ht="24.95" customHeight="1">
       <c r="A632" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B632" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="O632" s="2" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="633" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A633" s="2" t="s">
         <v>1033</v>
       </c>
-      <c r="B632" s="2" t="s">
+      <c r="B633" s="2" t="s">
         <v>1034</v>
       </c>
-      <c r="O632" s="2" t="s">
+      <c r="O633" s="2" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="633" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O633" s="2"/>
-    </row>
     <row r="634" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A634" s="2" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B634" s="2" t="s">
-        <v>1037</v>
-      </c>
-      <c r="O634" s="2" t="s">
-        <v>1038</v>
-      </c>
+      <c r="O634" s="2"/>
     </row>
     <row r="635" spans="1:15" ht="24.95" customHeight="1">
       <c r="A635" s="2" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="O635" s="2" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="636" spans="1:15" ht="24.95" customHeight="1">
       <c r="A636" s="2" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="O636" s="2" t="s">
-        <v>2291</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="637" spans="1:15" ht="24.95" customHeight="1">
       <c r="A637" s="2" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="O637" s="2" t="s">
-        <v>1046</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="638" spans="1:15" ht="24.95" customHeight="1">
       <c r="A638" s="2" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="O638" s="2" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="639" spans="1:15" ht="24.95" customHeight="1">
       <c r="A639" s="2" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>66</v>
+        <v>1048</v>
       </c>
       <c r="O639" s="2" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="640" spans="1:15" ht="24.95" customHeight="1">
       <c r="A640" s="2" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>1053</v>
+        <v>66</v>
       </c>
       <c r="O640" s="2" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="641" spans="1:15" ht="24.95" customHeight="1">
       <c r="A641" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B641" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="O641" s="2" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="642" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A642" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="B641" s="2" t="s">
+      <c r="B642" s="2" t="s">
         <v>1056</v>
       </c>
-      <c r="O641" s="2" t="s">
+      <c r="O642" s="2" t="s">
         <v>1057</v>
       </c>
     </row>
-    <row r="642" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O642" s="2"/>
-    </row>
     <row r="643" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A643" s="2" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B643" s="2" t="s">
-        <v>1764</v>
-      </c>
-      <c r="O643" s="2" t="s">
-        <v>1059</v>
-      </c>
+      <c r="O643" s="2"/>
     </row>
     <row r="644" spans="1:15" ht="24.95" customHeight="1">
       <c r="A644" s="2" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="O644" s="2" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="645" spans="1:15" ht="24.95" customHeight="1">
       <c r="A645" s="2" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>1772</v>
+        <v>1765</v>
       </c>
       <c r="O645" s="2" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="646" spans="1:15" ht="24.95" customHeight="1">
       <c r="A646" s="2" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="O646" s="2" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="647" spans="1:15" ht="24.95" customHeight="1">
       <c r="A647" s="2" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>1768</v>
+        <v>1771</v>
       </c>
       <c r="O647" s="2" t="s">
-        <v>1710</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="648" spans="1:15" ht="24.95" customHeight="1">
       <c r="A648" s="2" t="s">
-        <v>1769</v>
+        <v>1066</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="O648" s="2" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="649" spans="1:15" ht="24.95" customHeight="1">
       <c r="A649" s="2" t="s">
-        <v>1067</v>
+        <v>1769</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>1766</v>
+        <v>1770</v>
       </c>
       <c r="O649" s="2" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="650" spans="1:15" ht="24.95" customHeight="1">
       <c r="A650" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B650" s="2" t="s">
+        <v>1766</v>
+      </c>
+      <c r="O650" s="2" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="651" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A651" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="B650" s="2" t="s">
+      <c r="B651" s="2" t="s">
         <v>1767</v>
       </c>
-      <c r="O650" s="2" t="s">
+      <c r="O651" s="2" t="s">
         <v>1707</v>
       </c>
     </row>
-    <row r="651" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O651" s="2"/>
-    </row>
     <row r="652" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A652" s="2" t="s">
-        <v>1832</v>
-      </c>
-      <c r="B652" s="2" t="s">
-        <v>1822</v>
-      </c>
-      <c r="O652" s="2" t="s">
-        <v>1839</v>
-      </c>
+      <c r="O652" s="2"/>
     </row>
     <row r="653" spans="1:15" ht="24.95" customHeight="1">
       <c r="A653" s="2" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>1835</v>
+        <v>1822</v>
       </c>
       <c r="O653" s="2" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="654" spans="1:15" ht="24.95" customHeight="1">
       <c r="A654" s="2" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="O654" s="2" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="655" spans="1:15" ht="24.95" customHeight="1">
       <c r="A655" s="2" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B655" s="2" t="s">
+        <v>1836</v>
+      </c>
+      <c r="O655" s="2" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="656" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A656" s="2" t="s">
         <v>1840</v>
       </c>
-      <c r="B655" s="2" t="s">
+      <c r="B656" s="2" t="s">
         <v>1841</v>
       </c>
-      <c r="O655" s="2" t="s">
+      <c r="O656" s="2" t="s">
         <v>1842</v>
       </c>
     </row>
-    <row r="656" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O656" s="2"/>
-    </row>
     <row r="657" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A657" s="2" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B657" s="2" t="s">
-        <v>1070</v>
-      </c>
-      <c r="O657" s="2" t="s">
-        <v>3030</v>
-      </c>
+      <c r="O657" s="2"/>
     </row>
     <row r="658" spans="1:15" ht="24.95" customHeight="1">
       <c r="A658" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B658" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="O658" s="2" t="s">
+        <v>3029</v>
+      </c>
+    </row>
+    <row r="659" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A659" s="2" t="s">
         <v>1071</v>
       </c>
-      <c r="B658" s="2" t="s">
+      <c r="B659" s="2" t="s">
         <v>1072</v>
       </c>
-      <c r="O658" s="2" t="s">
+      <c r="O659" s="2" t="s">
         <v>1073</v>
       </c>
     </row>
-    <row r="659" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O659" s="2"/>
-    </row>
     <row r="660" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A660" s="2" t="s">
-        <v>1074</v>
-      </c>
-      <c r="B660" s="2" t="s">
-        <v>1075</v>
-      </c>
-      <c r="O660" s="2" t="s">
-        <v>1076</v>
-      </c>
+      <c r="O660" s="2"/>
     </row>
     <row r="661" spans="1:15" ht="24.95" customHeight="1">
       <c r="A661" s="2" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="O661" s="2" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="662" spans="1:15" ht="24.95" customHeight="1">
       <c r="A662" s="2" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="O662" s="2" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="663" spans="1:15" ht="24.95" customHeight="1">
       <c r="A663" s="2" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="O663" s="2" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="664" spans="1:15" ht="24.95" customHeight="1">
       <c r="A664" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B664" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="O664" s="2" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="665" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A665" s="2" t="s">
         <v>1086</v>
       </c>
-      <c r="B664" s="2" t="s">
+      <c r="B665" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="O664" s="2" t="s">
+      <c r="O665" s="2" t="s">
         <v>1088</v>
       </c>
     </row>
-    <row r="665" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O665" s="2"/>
-    </row>
     <row r="666" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A666" s="2" t="s">
-        <v>1089</v>
-      </c>
-      <c r="B666" s="2" t="s">
-        <v>1090</v>
-      </c>
-      <c r="O666" s="2" t="s">
-        <v>1091</v>
-      </c>
+      <c r="O666" s="2"/>
     </row>
     <row r="667" spans="1:15" ht="24.95" customHeight="1">
       <c r="A667" s="2" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="O667" s="2" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="668" spans="1:15" ht="24.95" customHeight="1">
       <c r="A668" s="2" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="O668" s="2" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="669" spans="1:15" ht="24.95" customHeight="1">
       <c r="A669" s="2" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="O669" s="2" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="670" spans="1:15" ht="24.95" customHeight="1">
       <c r="A670" s="2" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="O670" s="2" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="671" spans="1:15" ht="24.95" customHeight="1">
       <c r="A671" s="2" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="O671" s="2" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="672" spans="1:15" ht="24.95" customHeight="1">
       <c r="A672" s="2" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>964</v>
+        <v>1105</v>
       </c>
       <c r="O672" s="2" t="s">
-        <v>965</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="673" spans="1:15" ht="24.95" customHeight="1">
       <c r="A673" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B673" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="O673" s="2" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="674" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A674" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="B673" s="2" t="s">
+      <c r="B674" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="O673" s="2" t="s">
+      <c r="O674" s="2" t="s">
         <v>1110</v>
       </c>
     </row>
-    <row r="674" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O674" s="2"/>
-    </row>
     <row r="675" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A675" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="B675" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="O675" s="2" t="s">
-        <v>1113</v>
-      </c>
+      <c r="O675" s="2"/>
     </row>
     <row r="676" spans="1:15" ht="24.95" customHeight="1">
       <c r="A676" s="2" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="O676" s="2" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="677" spans="1:15" ht="24.95" customHeight="1">
       <c r="A677" s="2" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="O677" s="2" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="678" spans="1:15" ht="24.95" customHeight="1">
       <c r="A678" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B678" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="O678" s="2" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="679" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A679" s="2" t="s">
         <v>1120</v>
       </c>
-      <c r="B678" s="2" t="s">
+      <c r="B679" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="O678" s="2" t="s">
+      <c r="O679" s="2" t="s">
         <v>1122</v>
       </c>
     </row>
-    <row r="679" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O679" s="2"/>
-    </row>
     <row r="680" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A680" s="2" t="s">
-        <v>1123</v>
-      </c>
-      <c r="B680" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="O680" s="2" t="s">
-        <v>1125</v>
-      </c>
+      <c r="O680" s="2"/>
     </row>
     <row r="681" spans="1:15" ht="24.95" customHeight="1">
       <c r="A681" s="2" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>599</v>
+        <v>1124</v>
       </c>
       <c r="O681" s="2" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="682" spans="1:15" ht="24.95" customHeight="1">
       <c r="A682" s="2" t="s">
-        <v>2462</v>
+        <v>1126</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="O682" s="2" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="683" spans="1:15" ht="24.95" customHeight="1">
       <c r="A683" s="2" t="s">
+        <v>2462</v>
+      </c>
+      <c r="B683" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="O683" s="2" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="684" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A684" s="2" t="s">
         <v>1129</v>
       </c>
-      <c r="B683" s="2" t="s">
+      <c r="B684" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="O683" s="2" t="s">
+      <c r="O684" s="2" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="684" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O684" s="2"/>
-    </row>
     <row r="685" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A685" s="2" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B685" s="2" t="s">
-        <v>920</v>
-      </c>
-      <c r="O685" s="2" t="s">
-        <v>3086</v>
-      </c>
+      <c r="O685" s="2"/>
     </row>
     <row r="686" spans="1:15" ht="24.95" customHeight="1">
       <c r="A686" s="2" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>1132</v>
+        <v>920</v>
       </c>
       <c r="O686" s="2" t="s">
-        <v>984</v>
+        <v>3085</v>
       </c>
     </row>
     <row r="687" spans="1:15" ht="24.95" customHeight="1">
       <c r="A687" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B687" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="O687" s="2" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="688" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A688" s="2" t="s">
         <v>1133</v>
       </c>
-      <c r="O687" s="2" t="s">
+      <c r="O688" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="688" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O688" s="2"/>
-    </row>
     <row r="689" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A689" s="2" t="s">
-        <v>2525</v>
-      </c>
-      <c r="O689" s="2" t="s">
-        <v>2527</v>
-      </c>
+      <c r="O689" s="2"/>
     </row>
     <row r="690" spans="1:15" ht="24.95" customHeight="1">
       <c r="A690" s="2" t="s">
+        <v>2525</v>
+      </c>
+      <c r="O690" s="2" t="s">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="691" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A691" s="2" t="s">
         <v>2526</v>
       </c>
-      <c r="O690" s="2" t="s">
+      <c r="O691" s="2" t="s">
         <v>2528</v>
       </c>
     </row>
-    <row r="691" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O691" s="2"/>
-    </row>
     <row r="692" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A692" s="2" t="s">
-        <v>1135</v>
-      </c>
-      <c r="B692" s="2" t="s">
-        <v>1136</v>
-      </c>
-      <c r="O692" s="2" t="s">
-        <v>1137</v>
-      </c>
+      <c r="O692" s="2"/>
     </row>
     <row r="693" spans="1:15" ht="24.95" customHeight="1">
       <c r="A693" s="2" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="O693" s="2" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="694" spans="1:15" ht="24.95" customHeight="1">
       <c r="A694" s="2" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>964</v>
+        <v>1139</v>
       </c>
       <c r="O694" s="2" t="s">
-        <v>965</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="695" spans="1:15" ht="24.95" customHeight="1">
       <c r="A695" s="2" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>1143</v>
+        <v>964</v>
       </c>
       <c r="O695" s="2" t="s">
-        <v>1144</v>
+        <v>965</v>
       </c>
     </row>
     <row r="696" spans="1:15" ht="24.95" customHeight="1">
       <c r="A696" s="2" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="O696" s="2" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="697" spans="1:15" ht="24.95" customHeight="1">
       <c r="A697" s="2" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>1821</v>
+        <v>1146</v>
       </c>
       <c r="O697" s="2" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="698" spans="1:15" ht="24.95" customHeight="1">
       <c r="A698" s="2" t="s">
-        <v>3027</v>
+        <v>1148</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>1151</v>
+        <v>1821</v>
       </c>
       <c r="O698" s="2" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="699" spans="1:15" ht="24.95" customHeight="1">
       <c r="A699" s="2" t="s">
+        <v>3026</v>
+      </c>
+      <c r="B699" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="O699" s="2" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="700" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A700" s="2" t="s">
         <v>1155</v>
       </c>
-      <c r="B699" s="2" t="s">
+      <c r="B700" s="2" t="s">
         <v>1156</v>
       </c>
-      <c r="O699" s="2" t="s">
+      <c r="O700" s="2" t="s">
         <v>1157</v>
       </c>
     </row>
-    <row r="700" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O700" s="2"/>
-    </row>
     <row r="701" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A701" s="2" t="s">
-        <v>3052</v>
-      </c>
-      <c r="O701" s="2" t="s">
-        <v>3057</v>
-      </c>
+      <c r="O701" s="2"/>
     </row>
     <row r="702" spans="1:15" ht="24.95" customHeight="1">
       <c r="A702" s="2" t="s">
-        <v>3053</v>
+        <v>3051</v>
       </c>
       <c r="O702" s="2" t="s">
-        <v>3058</v>
+        <v>3056</v>
       </c>
     </row>
     <row r="703" spans="1:15" ht="24.95" customHeight="1">
       <c r="A703" s="2" t="s">
-        <v>3067</v>
+        <v>3052</v>
       </c>
       <c r="O703" s="2" t="s">
-        <v>3068</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="704" spans="1:15" ht="24.95" customHeight="1">
       <c r="A704" s="2" t="s">
-        <v>3054</v>
+        <v>3066</v>
       </c>
       <c r="O704" s="2" t="s">
-        <v>3059</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="705" spans="1:15" ht="24.95" customHeight="1">
       <c r="A705" s="2" t="s">
-        <v>3055</v>
+        <v>3053</v>
       </c>
       <c r="O705" s="2" t="s">
-        <v>3060</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="706" spans="1:15" ht="24.95" customHeight="1">
       <c r="A706" s="2" t="s">
-        <v>3056</v>
+        <v>3054</v>
       </c>
       <c r="O706" s="2" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="707" spans="1:15" ht="24.95" customHeight="1">
       <c r="A707" s="2" t="s">
-        <v>3065</v>
+        <v>3055</v>
       </c>
       <c r="O707" s="2" t="s">
-        <v>3087</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="708" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O708" s="2"/>
+      <c r="A708" s="2" t="s">
+        <v>3064</v>
+      </c>
+      <c r="O708" s="2" t="s">
+        <v>3086</v>
+      </c>
     </row>
     <row r="709" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A709" s="2" t="s">
+      <c r="O709" s="2"/>
+    </row>
+    <row r="710" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A710" s="2" t="s">
         <v>1158</v>
       </c>
-      <c r="B709" s="2" t="s">
+      <c r="B710" s="2" t="s">
         <v>1761</v>
       </c>
-      <c r="O709" s="2" t="s">
+      <c r="O710" s="2" t="s">
         <v>1159</v>
       </c>
     </row>
-    <row r="710" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O710" s="2"/>
-    </row>
     <row r="711" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A711" s="2" t="s">
+      <c r="O711" s="2"/>
+    </row>
+    <row r="712" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A712" s="2" t="s">
         <v>1160</v>
       </c>
-      <c r="B711" s="2" t="s">
+      <c r="B712" s="2" t="s">
         <v>1161</v>
       </c>
-      <c r="O711" s="2" t="s">
+      <c r="O712" s="2" t="s">
         <v>1162</v>
       </c>
     </row>
-    <row r="712" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O712" s="2"/>
-    </row>
     <row r="713" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A713" s="2" t="s">
-        <v>3174</v>
-      </c>
-      <c r="O713" s="2" t="s">
-        <v>3175</v>
-      </c>
+      <c r="O713" s="2"/>
     </row>
     <row r="714" spans="1:15" ht="24.95" customHeight="1">
       <c r="A714" s="2" t="s">
-        <v>2989</v>
+        <v>3173</v>
       </c>
       <c r="O714" s="2" t="s">
-        <v>2991</v>
+        <v>3174</v>
       </c>
     </row>
     <row r="715" spans="1:15" ht="24.95" customHeight="1">
       <c r="A715" s="2" t="s">
+        <v>2988</v>
+      </c>
+      <c r="O715" s="2" t="s">
         <v>2990</v>
       </c>
-      <c r="O715" s="2" t="s">
-        <v>2992</v>
-      </c>
     </row>
     <row r="716" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O716" s="2"/>
+      <c r="A716" s="2" t="s">
+        <v>2989</v>
+      </c>
+      <c r="O716" s="2" t="s">
+        <v>2991</v>
+      </c>
     </row>
     <row r="717" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A717" s="2" t="s">
-        <v>1163</v>
-      </c>
-      <c r="B717" s="2" t="s">
-        <v>1164</v>
-      </c>
-      <c r="O717" s="2" t="s">
-        <v>1165</v>
-      </c>
+      <c r="O717" s="2"/>
     </row>
     <row r="718" spans="1:15" ht="24.95" customHeight="1">
       <c r="A718" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B718" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="O718" s="2" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="719" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A719" s="2" t="s">
         <v>1166</v>
       </c>
-      <c r="B718" s="2" t="s">
+      <c r="B719" s="2" t="s">
         <v>1167</v>
       </c>
-      <c r="O718" s="2" t="s">
+      <c r="O719" s="2" t="s">
         <v>1168</v>
       </c>
     </row>
-    <row r="719" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O719" s="2"/>
-    </row>
     <row r="720" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A720" s="2" t="s">
+      <c r="O720" s="2"/>
+    </row>
+    <row r="721" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A721" s="2" t="s">
         <v>1169</v>
       </c>
-      <c r="B720" s="2" t="s">
+      <c r="B721" s="2" t="s">
         <v>1170</v>
       </c>
-      <c r="O720" s="2" t="s">
+      <c r="O721" s="2" t="s">
         <v>1171</v>
       </c>
     </row>
-    <row r="721" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O721" s="2"/>
-    </row>
     <row r="722" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A722" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="O722" s="2" t="s">
-        <v>1173</v>
-      </c>
+      <c r="O722" s="2"/>
     </row>
     <row r="723" spans="1:15" ht="24.95" customHeight="1">
       <c r="A723" s="2" t="s">
-        <v>1174</v>
-      </c>
-      <c r="B723" s="2" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="O723" s="2" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="724" spans="1:15" ht="24.95" customHeight="1">
       <c r="A724" s="2" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="O724" s="2" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="725" spans="1:15" ht="24.95" customHeight="1">
       <c r="A725" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B725" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="O725" s="2" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="726" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A726" s="2" t="s">
         <v>1180</v>
       </c>
-      <c r="B725" s="2" t="s">
+      <c r="B726" s="2" t="s">
         <v>1181</v>
       </c>
-      <c r="O725" s="2" t="s">
+      <c r="O726" s="2" t="s">
         <v>1182</v>
       </c>
     </row>
-    <row r="726" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O726" s="2"/>
-    </row>
     <row r="727" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A727" s="2" t="s">
-        <v>1183</v>
-      </c>
-      <c r="B727" s="2" t="s">
-        <v>1184</v>
-      </c>
-      <c r="O727" s="2" t="s">
-        <v>1185</v>
-      </c>
+      <c r="O727" s="2"/>
     </row>
     <row r="728" spans="1:15" ht="24.95" customHeight="1">
       <c r="A728" s="2" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="O728" s="2" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="729" spans="1:15" ht="24.95" customHeight="1">
       <c r="A729" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B729" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="O729" s="2" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="730" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A730" s="2" t="s">
         <v>1189</v>
       </c>
-      <c r="B729" s="2" t="s">
+      <c r="B730" s="2" t="s">
         <v>1190</v>
       </c>
-      <c r="O729" s="2" t="s">
+      <c r="O730" s="2" t="s">
         <v>1191</v>
       </c>
     </row>
-    <row r="730" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O730" s="2"/>
-    </row>
     <row r="731" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A731" s="2" t="s">
-        <v>1192</v>
-      </c>
-      <c r="B731" s="2" t="s">
-        <v>1193</v>
-      </c>
-      <c r="O731" s="2" t="s">
-        <v>1194</v>
-      </c>
+      <c r="O731" s="2"/>
     </row>
     <row r="732" spans="1:15" ht="24.95" customHeight="1">
       <c r="A732" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B732" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="O732" s="2" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="733" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A733" s="2" t="s">
         <v>1195</v>
       </c>
-      <c r="B732" s="2" t="s">
+      <c r="B733" s="2" t="s">
         <v>1196</v>
       </c>
-      <c r="O732" s="2" t="s">
+      <c r="O733" s="2" t="s">
         <v>1197</v>
       </c>
     </row>
-    <row r="733" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O733" s="2"/>
-    </row>
     <row r="734" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A734" s="2" t="s">
-        <v>1198</v>
-      </c>
-      <c r="B734" s="2" t="s">
-        <v>1199</v>
-      </c>
-      <c r="O734" s="2" t="s">
-        <v>1200</v>
-      </c>
+      <c r="O734" s="2"/>
     </row>
     <row r="735" spans="1:15" ht="24.95" customHeight="1">
       <c r="A735" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B735" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="O735" s="2" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="736" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A736" s="2" t="s">
         <v>1201</v>
       </c>
-      <c r="B735" s="2" t="s">
+      <c r="B736" s="2" t="s">
         <v>1202</v>
       </c>
-      <c r="O735" s="2" t="s">
+      <c r="O736" s="2" t="s">
         <v>1203</v>
       </c>
     </row>
-    <row r="736" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O736" s="2"/>
-    </row>
-    <row r="737" spans="1:15" ht="33">
-      <c r="A737" s="2" t="s">
+    <row r="737" spans="1:15" ht="24.95" customHeight="1">
+      <c r="O737" s="2"/>
+    </row>
+    <row r="738" spans="1:15" ht="33">
+      <c r="A738" s="2" t="s">
+        <v>2965</v>
+      </c>
+      <c r="O738" s="3" t="s">
         <v>2966</v>
       </c>
-      <c r="O737" s="3" t="s">
-        <v>2967</v>
-      </c>
-    </row>
-    <row r="738" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O738" s="2"/>
     </row>
     <row r="739" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A739" s="2" t="s">
+      <c r="O739" s="2"/>
+    </row>
+    <row r="740" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A740" s="2" t="s">
         <v>1204</v>
       </c>
-      <c r="O739" s="2" t="s">
+      <c r="O740" s="2" t="s">
         <v>1773</v>
       </c>
     </row>
-    <row r="740" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O740" s="2"/>
-    </row>
     <row r="741" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A741" s="2" t="s">
-        <v>1205</v>
-      </c>
-      <c r="B741" s="2" t="s">
-        <v>1206</v>
-      </c>
-      <c r="O741" s="2" t="s">
-        <v>1207</v>
-      </c>
+      <c r="O741" s="2"/>
     </row>
     <row r="742" spans="1:15" ht="24.95" customHeight="1">
       <c r="A742" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B742" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="O742" s="2" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="743" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A743" s="2" t="s">
         <v>1208</v>
       </c>
-      <c r="B742" s="2" t="s">
+      <c r="B743" s="2" t="s">
         <v>1209</v>
       </c>
-      <c r="O742" s="2" t="s">
+      <c r="O743" s="2" t="s">
         <v>1210</v>
       </c>
     </row>
-    <row r="743" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O743" s="2"/>
-    </row>
     <row r="744" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A744" s="2" t="s">
+      <c r="O744" s="2"/>
+    </row>
+    <row r="745" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A745" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="B744" s="2" t="s">
+      <c r="B745" s="2" t="s">
         <v>1212</v>
       </c>
-      <c r="O744" s="2" t="s">
+      <c r="O745" s="2" t="s">
         <v>1213</v>
       </c>
     </row>
-    <row r="745" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O745" s="2"/>
-    </row>
     <row r="746" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A746" s="2" t="s">
-        <v>1214</v>
-      </c>
-      <c r="B746" s="2" t="s">
-        <v>1215</v>
-      </c>
-      <c r="O746" s="2" t="s">
-        <v>1216</v>
-      </c>
+      <c r="O746" s="2"/>
     </row>
     <row r="747" spans="1:15" ht="24.95" customHeight="1">
       <c r="A747" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B747" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="O747" s="2" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="748" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A748" s="2" t="s">
         <v>1217</v>
       </c>
-      <c r="B747" s="2" t="s">
+      <c r="B748" s="2" t="s">
         <v>1218</v>
       </c>
-      <c r="O747" s="2" t="s">
+      <c r="O748" s="2" t="s">
         <v>1219</v>
       </c>
     </row>
-    <row r="748" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O748" s="2"/>
-    </row>
     <row r="749" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A749" s="2" t="s">
+      <c r="O749" s="2"/>
+    </row>
+    <row r="750" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A750" s="2" t="s">
         <v>1220</v>
       </c>
-      <c r="B749" s="2" t="s">
+      <c r="B750" s="2" t="s">
         <v>1763</v>
       </c>
-      <c r="O749" s="2" t="s">
+      <c r="O750" s="2" t="s">
         <v>1221</v>
       </c>
     </row>
-    <row r="750" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O750" s="2"/>
-    </row>
     <row r="751" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A751" s="2" t="s">
-        <v>3178</v>
-      </c>
-      <c r="O751" s="2" t="s">
-        <v>3180</v>
-      </c>
+      <c r="O751" s="2"/>
     </row>
     <row r="752" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O752" s="2"/>
+      <c r="A752" s="2" t="s">
+        <v>3177</v>
+      </c>
+      <c r="O752" s="2" t="s">
+        <v>3179</v>
+      </c>
     </row>
     <row r="753" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A753" s="2" t="s">
+      <c r="O753" s="2"/>
+    </row>
+    <row r="754" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A754" s="2" t="s">
         <v>1222</v>
       </c>
-      <c r="O753" s="2" t="s">
+      <c r="O754" s="2" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="754" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O754" s="2"/>
-    </row>
     <row r="755" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A755" s="2" t="s">
-        <v>3176</v>
-      </c>
-      <c r="O755" s="2" t="s">
-        <v>3177</v>
-      </c>
+      <c r="O755" s="2"/>
     </row>
     <row r="756" spans="1:15" ht="24.95" customHeight="1">
       <c r="A756" s="2" t="s">
+        <v>3175</v>
+      </c>
+      <c r="O756" s="2" t="s">
+        <v>3176</v>
+      </c>
+    </row>
+    <row r="757" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A757" s="2" t="s">
         <v>1223</v>
       </c>
-      <c r="B756" s="2" t="s">
+      <c r="B757" s="2" t="s">
         <v>1762</v>
       </c>
-      <c r="O756" s="2" t="s">
+      <c r="O757" s="2" t="s">
         <v>1224</v>
       </c>
     </row>
-    <row r="757" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O757" s="2"/>
-    </row>
     <row r="758" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A758" s="2" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B758" s="2" t="s">
-        <v>1226</v>
-      </c>
-      <c r="O758" s="2" t="s">
-        <v>1227</v>
-      </c>
+      <c r="O758" s="2"/>
     </row>
     <row r="759" spans="1:15" ht="24.95" customHeight="1">
       <c r="A759" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B759" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="O759" s="2" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="760" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A760" s="2" t="s">
         <v>1228</v>
       </c>
-      <c r="B759" s="2" t="s">
+      <c r="B760" s="2" t="s">
         <v>1229</v>
       </c>
-      <c r="O759" s="2" t="s">
+      <c r="O760" s="2" t="s">
         <v>1230</v>
       </c>
     </row>
-    <row r="760" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O760" s="2"/>
-    </row>
     <row r="761" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A761" s="2" t="s">
-        <v>1231</v>
-      </c>
-      <c r="B761" s="2" t="s">
-        <v>1232</v>
-      </c>
-      <c r="O761" s="2" t="s">
-        <v>1233</v>
-      </c>
+      <c r="O761" s="2"/>
     </row>
     <row r="762" spans="1:15" ht="24.95" customHeight="1">
       <c r="A762" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B762" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="O762" s="2" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="763" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A763" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="B762" s="2" t="s">
+      <c r="B763" s="2" t="s">
         <v>1235</v>
       </c>
-      <c r="O762" s="2" t="s">
+      <c r="O763" s="2" t="s">
         <v>1236</v>
       </c>
     </row>
-    <row r="763" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O763" s="2"/>
-    </row>
     <row r="764" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A764" s="2" t="s">
-        <v>1237</v>
-      </c>
-      <c r="B764" s="2" t="s">
-        <v>1238</v>
-      </c>
-      <c r="O764" s="2" t="s">
-        <v>1239</v>
-      </c>
+      <c r="O764" s="2"/>
     </row>
     <row r="765" spans="1:15" ht="24.95" customHeight="1">
       <c r="A765" s="2" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="B765" s="2" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="O765" s="2" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="766" spans="1:15" ht="24.95" customHeight="1">
       <c r="A766" s="2" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="B766" s="2" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="O766" s="2" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="767" spans="1:15" ht="24.95" customHeight="1">
       <c r="A767" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B767" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="O767" s="2" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="768" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A768" s="2" t="s">
         <v>1246</v>
       </c>
-      <c r="B767" s="2" t="s">
+      <c r="B768" s="2" t="s">
         <v>1247</v>
       </c>
-      <c r="O767" s="2" t="s">
+      <c r="O768" s="2" t="s">
         <v>1248</v>
       </c>
     </row>
-    <row r="768" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O768" s="2"/>
-    </row>
     <row r="769" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A769" s="2" t="s">
-        <v>1600</v>
-      </c>
-      <c r="O769" s="2" t="s">
-        <v>1602</v>
-      </c>
+      <c r="O769" s="2"/>
     </row>
     <row r="770" spans="1:15" ht="24.95" customHeight="1">
       <c r="A770" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="O770" s="2" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="771" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A771" s="2" t="s">
         <v>1601</v>
       </c>
-      <c r="O770" s="3" t="s">
+      <c r="O771" s="3" t="s">
         <v>1603</v>
       </c>
-    </row>
-    <row r="771" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O771" s="2"/>
     </row>
     <row r="772" spans="1:15" ht="24.95" customHeight="1">
       <c r="O772" s="2"/>
@@ -19758,8 +19779,8 @@
     <row r="867" spans="15:15" ht="24.95" customHeight="1">
       <c r="O867" s="2"/>
     </row>
-    <row r="869" spans="15:15" ht="24.95" customHeight="1">
-      <c r="O869" s="2"/>
+    <row r="868" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O868" s="2"/>
     </row>
     <row r="870" spans="15:15" ht="24.95" customHeight="1">
       <c r="O870" s="2"/>
@@ -20938,23 +20959,23 @@
       <c r="O1261" s="2"/>
     </row>
     <row r="1262" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A1262" s="5"/>
-      <c r="B1262" s="5"/>
-      <c r="D1262" s="5"/>
-      <c r="E1262" s="5"/>
-      <c r="F1262" s="5"/>
-      <c r="G1262" s="5"/>
-      <c r="H1262" s="5"/>
-      <c r="I1262" s="5"/>
-      <c r="J1262" s="5"/>
-      <c r="K1262" s="5"/>
-      <c r="L1262" s="5"/>
-      <c r="M1262" s="5"/>
-      <c r="N1262" s="5"/>
-      <c r="O1262" s="6"/>
+      <c r="O1262" s="2"/>
     </row>
     <row r="1263" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O1263" s="2"/>
+      <c r="A1263" s="5"/>
+      <c r="B1263" s="5"/>
+      <c r="D1263" s="5"/>
+      <c r="E1263" s="5"/>
+      <c r="F1263" s="5"/>
+      <c r="G1263" s="5"/>
+      <c r="H1263" s="5"/>
+      <c r="I1263" s="5"/>
+      <c r="J1263" s="5"/>
+      <c r="K1263" s="5"/>
+      <c r="L1263" s="5"/>
+      <c r="M1263" s="5"/>
+      <c r="N1263" s="5"/>
+      <c r="O1263" s="6"/>
     </row>
     <row r="1264" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1264" s="2"/>
@@ -22468,8 +22489,11 @@
     <row r="1767" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1767" s="2"/>
     </row>
+    <row r="1768" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1768" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="O1:O1470" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="O1:O1471" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -22550,7 +22574,7 @@
         <v>1249</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="54">
@@ -22558,7 +22582,7 @@
         <v>1250</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>2754</v>
@@ -22624,7 +22648,7 @@
         <v>1265</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>2769</v>
@@ -22649,7 +22673,7 @@
         <v>2770</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="45" customHeight="1"/>
@@ -22658,7 +22682,7 @@
         <v>2488</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="45" customHeight="1">
@@ -22674,7 +22698,7 @@
         <v>2491</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="45" customHeight="1">
@@ -22732,7 +22756,7 @@
     <row r="23" spans="1:15" s="2" customFormat="1" ht="24.95" customHeight="1"/>
     <row r="24" spans="1:15" s="2" customFormat="1" ht="24.95" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>106</v>
@@ -22746,18 +22770,18 @@
     </row>
     <row r="25" spans="1:15" ht="24.95" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="24.95" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>1280</v>
@@ -23010,35 +23034,35 @@
     </row>
     <row r="55" spans="1:15" ht="24.95" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="24.95" customHeight="1">
       <c r="A56" s="1" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>2901</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>2902</v>
-      </c>
       <c r="O56" s="1" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="24.95" customHeight="1">
       <c r="A57" s="1" t="s">
+        <v>2898</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>2899</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>2900</v>
-      </c>
       <c r="O57" s="1" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="24.95" customHeight="1">
@@ -23054,34 +23078,34 @@
     </row>
     <row r="59" spans="1:15" ht="24.95" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="24.95" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="24.95" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="24.95" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="24.95" customHeight="1">
@@ -23103,7 +23127,7 @@
         <v>2532</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="24.95" customHeight="1">
@@ -23119,389 +23143,389 @@
     </row>
     <row r="69" spans="1:15" ht="24.95" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="24.95" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="24.95" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="24.95" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="24.95" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="24.95" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="24.95" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="24.95" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="24.95" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="24.95" customHeight="1">
       <c r="A78" s="1" t="s">
+        <v>3001</v>
+      </c>
+      <c r="O78" s="1" t="s">
         <v>3002</v>
-      </c>
-      <c r="O78" s="1" t="s">
-        <v>3003</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="24.95" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="24.95" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="81" spans="1:15" ht="24.95" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="24.95" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="83" spans="1:15" ht="24.95" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="24.95" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="85" spans="1:15" ht="24.95" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
     </row>
     <row r="86" spans="1:15" ht="24.95" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
     </row>
     <row r="87" spans="1:15" ht="24.95" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="24.95" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="24.95" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
     </row>
     <row r="90" spans="1:15" ht="24.95" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="24.95" customHeight="1">
       <c r="A91" s="1" t="s">
+        <v>2956</v>
+      </c>
+      <c r="O91" s="1" t="s">
         <v>2957</v>
-      </c>
-      <c r="O91" s="1" t="s">
-        <v>2958</v>
       </c>
     </row>
     <row r="92" spans="1:15" ht="24.95" customHeight="1">
       <c r="A92" s="1" t="s">
+        <v>2958</v>
+      </c>
+      <c r="O92" s="1" t="s">
         <v>2959</v>
-      </c>
-      <c r="O92" s="1" t="s">
-        <v>2960</v>
       </c>
     </row>
     <row r="93" spans="1:15" ht="24.95" customHeight="1">
       <c r="A93" s="1" t="s">
+        <v>2960</v>
+      </c>
+      <c r="O93" s="1" t="s">
         <v>2961</v>
-      </c>
-      <c r="O93" s="1" t="s">
-        <v>2962</v>
       </c>
     </row>
     <row r="94" spans="1:15" ht="24.95" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
     </row>
     <row r="96" spans="1:15" ht="24.95" customHeight="1">
       <c r="A96" s="1" t="s">
+        <v>3147</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>3146</v>
+      </c>
+      <c r="O96" s="1" t="s">
         <v>3148</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>3147</v>
-      </c>
-      <c r="O96" s="1" t="s">
-        <v>3149</v>
       </c>
     </row>
     <row r="97" spans="1:15" ht="24.95" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="C97" s="1" t="s">
+        <v>3106</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>3107</v>
       </c>
-      <c r="D97" s="1" t="s">
+      <c r="E97" s="1" t="s">
         <v>3108</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="F97" s="1" t="s">
         <v>3109</v>
       </c>
-      <c r="F97" s="1" t="s">
+      <c r="G97" s="1" t="s">
         <v>3110</v>
       </c>
-      <c r="G97" s="1" t="s">
+      <c r="H97" s="1" t="s">
         <v>3111</v>
       </c>
-      <c r="H97" s="1" t="s">
+      <c r="I97" s="1" t="s">
         <v>3112</v>
       </c>
-      <c r="I97" s="1" t="s">
+      <c r="J97" s="1" t="s">
         <v>3113</v>
       </c>
-      <c r="J97" s="1" t="s">
+      <c r="K97" s="1" t="s">
         <v>3114</v>
       </c>
-      <c r="K97" s="1" t="s">
+      <c r="L97" s="1" t="s">
         <v>3115</v>
       </c>
-      <c r="L97" s="1" t="s">
+      <c r="M97" s="1" t="s">
         <v>3116</v>
       </c>
-      <c r="M97" s="1" t="s">
+      <c r="N97" s="1" t="s">
         <v>3117</v>
       </c>
-      <c r="N97" s="1" t="s">
-        <v>3118</v>
-      </c>
       <c r="O97" s="1" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="98" spans="1:15" ht="24.95" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="C98" s="1" t="s">
+        <v>3094</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>3095</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="E98" s="1" t="s">
         <v>3096</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="F98" s="1" t="s">
         <v>3097</v>
       </c>
-      <c r="F98" s="1" t="s">
+      <c r="G98" s="1" t="s">
         <v>3098</v>
       </c>
-      <c r="G98" s="1" t="s">
+      <c r="H98" s="1" t="s">
         <v>3099</v>
       </c>
-      <c r="H98" s="1" t="s">
+      <c r="I98" s="1" t="s">
         <v>3100</v>
       </c>
-      <c r="I98" s="1" t="s">
+      <c r="J98" s="1" t="s">
         <v>3101</v>
       </c>
-      <c r="J98" s="1" t="s">
+      <c r="K98" s="1" t="s">
         <v>3102</v>
       </c>
-      <c r="K98" s="1" t="s">
+      <c r="L98" s="1" t="s">
         <v>3103</v>
       </c>
-      <c r="L98" s="1" t="s">
+      <c r="M98" s="1" t="s">
         <v>3104</v>
       </c>
-      <c r="M98" s="1" t="s">
+      <c r="N98" s="1" t="s">
         <v>3105</v>
       </c>
-      <c r="N98" s="1" t="s">
-        <v>3106</v>
-      </c>
       <c r="O98" s="1" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="99" spans="1:15" ht="24.95" customHeight="1">
       <c r="A99" s="1" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
     </row>
     <row r="100" spans="1:15" ht="24.95" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="101" spans="1:15" ht="24.95" customHeight="1">
       <c r="A101" s="1" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="O101" s="1" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="102" spans="1:15" ht="24.95" customHeight="1">
       <c r="A102" s="1" t="s">
+        <v>3139</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>3140</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="O102" s="1" t="s">
         <v>3141</v>
-      </c>
-      <c r="O102" s="1" t="s">
-        <v>3142</v>
       </c>
     </row>
     <row r="103" spans="1:15" ht="24.95" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="O103" s="1" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
     </row>
     <row r="104" spans="1:15" ht="24.95" customHeight="1">
       <c r="A104" s="1" t="s">
+        <v>3151</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>3152</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>3153</v>
-      </c>
       <c r="O104" s="1" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
     </row>
     <row r="105" spans="1:15" ht="24.95" customHeight="1">
       <c r="A105" s="1" t="s">
+        <v>3158</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>3159</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>3160</v>
       </c>
       <c r="O105" s="1" t="s">
         <v>2546</v>
@@ -23509,10 +23533,10 @@
     </row>
     <row r="106" spans="1:15" ht="24.95" customHeight="1">
       <c r="A106" s="1" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="O106" s="1" t="s">
         <v>1842</v>
@@ -23520,24 +23544,24 @@
     </row>
     <row r="107" spans="1:15" ht="24.95" customHeight="1">
       <c r="A107" s="1" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="B107" s="1" t="s">
+        <v>3165</v>
+      </c>
+      <c r="O107" s="1" t="s">
         <v>3166</v>
-      </c>
-      <c r="O107" s="1" t="s">
-        <v>3167</v>
       </c>
     </row>
     <row r="108" spans="1:15" ht="24.95" customHeight="1">
       <c r="A108" s="1" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="B108" s="1" t="s">
+        <v>3161</v>
+      </c>
+      <c r="O108" s="1" t="s">
         <v>3162</v>
-      </c>
-      <c r="O108" s="1" t="s">
-        <v>3163</v>
       </c>
     </row>
   </sheetData>
@@ -23629,7 +23653,7 @@
         <v>1314</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="16.5">
@@ -23640,7 +23664,7 @@
         <v>1316</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="16.5">
@@ -23651,7 +23675,7 @@
         <v>1318</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="16.5">
@@ -23673,7 +23697,7 @@
         <v>1322</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="16.5">
@@ -23684,7 +23708,7 @@
         <v>1324</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="16.5">
@@ -24070,7 +24094,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:S97"/>
+  <dimension ref="A1:S98"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21.5" style="2" customWidth="1"/>
@@ -24203,10 +24227,10 @@
         <v>1433</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1">
@@ -24445,7 +24469,7 @@
     </row>
     <row r="29" spans="1:15" ht="20.100000000000001" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>1494</v>
@@ -25133,79 +25157,87 @@
     </row>
     <row r="91" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A91" s="2" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>2891</v>
+      </c>
+      <c r="O91" s="2" t="s">
         <v>2892</v>
-      </c>
-      <c r="O91" s="2" t="s">
-        <v>2893</v>
       </c>
     </row>
     <row r="92" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A92" s="2" t="s">
+        <v>3068</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>3069</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="O92" s="2" t="s">
         <v>3070</v>
-      </c>
-      <c r="O92" s="2" t="s">
-        <v>3071</v>
       </c>
     </row>
     <row r="93" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A93" s="2" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="94" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A94" s="2" t="s">
+        <v>3083</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>2891</v>
+      </c>
+      <c r="O94" s="2" t="s">
         <v>3084</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>2892</v>
-      </c>
-      <c r="O94" s="2" t="s">
-        <v>3085</v>
       </c>
     </row>
     <row r="95" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A95" s="2" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>1438</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
     </row>
     <row r="96" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A96" s="2" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>1438</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
     </row>
     <row r="97" spans="1:15" ht="20.100000000000001" customHeight="1">
       <c r="A97" s="2" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>1438</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>3278</v>
+        <v>3277</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" ht="20.100000000000001" customHeight="1">
+      <c r="A98" s="2" t="s">
+        <v>3286</v>
+      </c>
+      <c r="O98" s="2" t="s">
+        <v>3287</v>
       </c>
     </row>
   </sheetData>
@@ -25289,13 +25321,13 @@
     </row>
     <row r="3" spans="1:17" ht="24.95" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>1642</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="24.95" customHeight="1"/>
@@ -25355,29 +25387,29 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="7" t="s">
+        <v>2968</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>2968</v>
+      </c>
+      <c r="O13" s="7" t="s">
         <v>2969</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>2969</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>2970</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="7" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="7" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -26003,56 +26035,56 @@
     </row>
     <row r="109" spans="1:15">
       <c r="A109" s="7" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="O109" s="7" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="110" spans="1:15">
       <c r="A110" s="7" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="O110" s="7" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="111" spans="1:15">
       <c r="A111" s="7" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="O111" s="7" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
     </row>
     <row r="113" spans="1:15">
       <c r="A113" s="7" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O113" s="7" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
     </row>
     <row r="114" spans="1:15">
       <c r="A114" s="7" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="O114" s="7" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
     </row>
     <row r="115" spans="1:15">
       <c r="A115" s="7" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="O115" s="7" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="117" spans="1:15">
@@ -26246,56 +26278,56 @@
     </row>
     <row r="145" spans="1:15">
       <c r="A145" s="7" t="s">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="O145" s="7" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
     </row>
     <row r="146" spans="1:15">
       <c r="A146" s="7" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="O146" s="7" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
     </row>
     <row r="147" spans="1:15">
       <c r="A147" s="7" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="O147" s="7" t="s">
-        <v>2895</v>
+        <v>2894</v>
       </c>
     </row>
     <row r="149" spans="1:15">
       <c r="A149" s="7" t="s">
+        <v>3194</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>3193</v>
+      </c>
+      <c r="O149" s="7" t="s">
         <v>3195</v>
-      </c>
-      <c r="B149" s="7" t="s">
-        <v>3194</v>
-      </c>
-      <c r="O149" s="7" t="s">
-        <v>3196</v>
       </c>
     </row>
     <row r="150" spans="1:15">
       <c r="A150" s="7" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="O150" s="7" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
     </row>
     <row r="151" spans="1:15">
       <c r="A151" s="7" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="O151" s="7" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
     </row>
     <row r="153" spans="1:15">
@@ -26516,29 +26548,29 @@
     </row>
     <row r="185" spans="1:15">
       <c r="A185" s="7" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B185" s="7" t="s">
+        <v>3180</v>
+      </c>
+      <c r="O185" s="7" t="s">
         <v>3181</v>
-      </c>
-      <c r="O185" s="7" t="s">
-        <v>3182</v>
       </c>
     </row>
     <row r="186" spans="1:15">
       <c r="A186" s="7" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="O186" s="7" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
     </row>
     <row r="187" spans="1:15">
       <c r="A187" s="7" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="O187" s="7" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="189" spans="1:15">
@@ -26597,29 +26629,29 @@
     </row>
     <row r="197" spans="1:15">
       <c r="A197" s="7" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="O197" s="7" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
     </row>
     <row r="198" spans="1:15">
       <c r="A198" s="7" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="O198" s="7" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="199" spans="1:15">
       <c r="A199" s="7" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="O199" s="7" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
     </row>
     <row r="201" spans="1:15">
@@ -27380,29 +27412,29 @@
     </row>
     <row r="313" spans="1:15">
       <c r="A313" s="7" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="B313" s="7" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="O313" s="7" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="314" spans="1:15">
       <c r="A314" s="7" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="O314" s="7" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="315" spans="1:15">
       <c r="A315" s="7" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="O315" s="7" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="317" spans="1:15">
@@ -27488,29 +27520,29 @@
     </row>
     <row r="329" spans="1:15">
       <c r="A329" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="B329" s="7" t="s">
+        <v>2974</v>
+      </c>
+      <c r="O329" s="7" t="s">
         <v>2976</v>
-      </c>
-      <c r="B329" s="7" t="s">
-        <v>2975</v>
-      </c>
-      <c r="O329" s="7" t="s">
-        <v>2977</v>
       </c>
     </row>
     <row r="330" spans="1:15">
       <c r="A330" s="7" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="O330" s="7" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
     </row>
     <row r="331" spans="1:15">
       <c r="A331" s="7" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="O331" s="7" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="333" spans="1:15">
@@ -28061,7 +28093,7 @@
         <v>2248</v>
       </c>
       <c r="O413" s="7" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
     </row>
     <row r="414" spans="1:15">
@@ -28163,83 +28195,83 @@
     </row>
     <row r="429" spans="1:15">
       <c r="A429" s="7" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="B429" s="7" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="O429" s="7" t="s">
-        <v>2869</v>
+        <v>2868</v>
       </c>
     </row>
     <row r="430" spans="1:15">
       <c r="A430" s="7" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="O430" s="7" t="s">
-        <v>2870</v>
+        <v>2869</v>
       </c>
     </row>
     <row r="431" spans="1:15">
       <c r="A431" s="7" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="O431" s="7" t="s">
-        <v>2870</v>
+        <v>2869</v>
       </c>
     </row>
     <row r="433" spans="1:15">
       <c r="A433" s="7" t="s">
-        <v>2876</v>
+        <v>2875</v>
       </c>
       <c r="B433" s="7" t="s">
-        <v>2876</v>
+        <v>2875</v>
       </c>
       <c r="O433" s="7" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
     </row>
     <row r="434" spans="1:15">
       <c r="A434" s="7" t="s">
-        <v>2877</v>
+        <v>2876</v>
       </c>
       <c r="O434" s="7" t="s">
-        <v>2880</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="435" spans="1:15">
       <c r="A435" s="7" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
       <c r="O435" s="7" t="s">
-        <v>2880</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="437" spans="1:15">
       <c r="A437" s="7" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="B437" s="7" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="O437" s="7" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
     </row>
     <row r="438" spans="1:15">
       <c r="A438" s="7" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
       <c r="O438" s="7" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="439" spans="1:15">
       <c r="A439" s="7" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
       <c r="O439" s="7" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="441" spans="1:15">
@@ -28399,15 +28431,15 @@
         <v>2314</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>2774</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="60" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="60" customHeight="1">
@@ -28415,7 +28447,7 @@
         <v>2316</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="60" customHeight="1">
@@ -28423,7 +28455,7 @@
         <v>2317</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="60" customHeight="1">
@@ -28431,7 +28463,7 @@
         <v>2318</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="60" customHeight="1">
@@ -28471,7 +28503,7 @@
         <v>2322</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="60" customHeight="1">
@@ -28479,7 +28511,7 @@
         <v>2323</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>2779</v>
+        <v>2778</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="60" customHeight="1">
@@ -28503,7 +28535,7 @@
         <v>2326</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="60" customHeight="1">
@@ -28511,7 +28543,7 @@
         <v>2327</v>
       </c>
       <c r="O16" s="9" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="60" customHeight="1">
@@ -28519,7 +28551,7 @@
         <v>2328</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>2782</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="60" customHeight="1">
@@ -28527,7 +28559,7 @@
         <v>2329</v>
       </c>
       <c r="O18" s="9" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="60" customHeight="1">
@@ -28535,7 +28567,7 @@
         <v>2324</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="60" customHeight="1">
@@ -28543,7 +28575,7 @@
         <v>2330</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>2785</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="60" customHeight="1">
@@ -28559,7 +28591,7 @@
         <v>2332</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="60" customHeight="1">
@@ -28567,7 +28599,7 @@
         <v>2333</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>2786</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="60" customHeight="1">
@@ -28575,7 +28607,7 @@
         <v>2334</v>
       </c>
       <c r="O24" s="9" t="s">
-        <v>2787</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="60" customHeight="1">
@@ -28583,7 +28615,7 @@
         <v>1845</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>2788</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="60" customHeight="1">
@@ -28591,31 +28623,31 @@
         <v>1846</v>
       </c>
       <c r="O26" s="9" t="s">
-        <v>2789</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="60" customHeight="1">
       <c r="A27" s="8" t="s">
+        <v>3076</v>
+      </c>
+      <c r="O27" s="9" t="s">
         <v>3077</v>
-      </c>
-      <c r="O27" s="9" t="s">
-        <v>3078</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="60" customHeight="1">
       <c r="A28" s="8" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="O28" s="9" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="60" customHeight="1">
       <c r="A29" s="8" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="60" customHeight="1">
@@ -28623,7 +28655,7 @@
         <v>1705</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="60" customHeight="1">
@@ -28639,7 +28671,7 @@
         <v>1704</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>2791</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="60" customHeight="1">
@@ -28647,7 +28679,7 @@
         <v>2335</v>
       </c>
       <c r="O34" s="9" t="s">
-        <v>2792</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="60" customHeight="1">
@@ -28663,7 +28695,7 @@
         <v>2337</v>
       </c>
       <c r="O36" s="9" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="60" customHeight="1">
@@ -28671,7 +28703,7 @@
         <v>2338</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>2794</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="60" customHeight="1">
@@ -28679,7 +28711,7 @@
         <v>2339</v>
       </c>
       <c r="O38" s="9" t="s">
-        <v>2795</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="60" customHeight="1">
@@ -28687,7 +28719,7 @@
         <v>2340</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>2796</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="60" customHeight="1">
@@ -28695,7 +28727,7 @@
         <v>2341</v>
       </c>
       <c r="O40" s="9" t="s">
-        <v>2797</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="60" customHeight="1">
@@ -28703,7 +28735,7 @@
         <v>2342</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>2798</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="60" customHeight="1">
@@ -28711,7 +28743,7 @@
         <v>2343</v>
       </c>
       <c r="O42" s="9" t="s">
-        <v>2799</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="60" customHeight="1">
@@ -28719,7 +28751,7 @@
         <v>2344</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="60" customHeight="1">
@@ -28727,7 +28759,7 @@
         <v>2345</v>
       </c>
       <c r="O44" s="9" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="60" customHeight="1">
@@ -28735,7 +28767,7 @@
         <v>2346</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>2801</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="60" customHeight="1">
@@ -28743,7 +28775,7 @@
         <v>2347</v>
       </c>
       <c r="O46" s="9" t="s">
-        <v>2802</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="60" customHeight="1">
@@ -28751,15 +28783,15 @@
         <v>2348</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>2803</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="60" customHeight="1">
       <c r="A48" s="8" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="O48" s="9" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="60" customHeight="1">
@@ -28767,7 +28799,7 @@
         <v>2349</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>2804</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="60" customHeight="1">
@@ -28775,31 +28807,31 @@
         <v>2350</v>
       </c>
       <c r="O50" s="9" t="s">
-        <v>2805</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="60" customHeight="1">
       <c r="A51" s="8" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>2911</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="132.75" customHeight="1">
       <c r="A52" s="8" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="O52" s="9" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="60" customHeight="1">
       <c r="A53" s="8" t="s">
+        <v>3228</v>
+      </c>
+      <c r="O53" s="9" t="s">
         <v>3229</v>
-      </c>
-      <c r="O53" s="9" t="s">
-        <v>3230</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="60" customHeight="1">
@@ -28807,7 +28839,7 @@
         <v>2351</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>2806</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="60" customHeight="1">
@@ -28815,7 +28847,7 @@
         <v>2352</v>
       </c>
       <c r="O56" s="9" t="s">
-        <v>2807</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="60" customHeight="1">
@@ -28831,7 +28863,7 @@
         <v>2354</v>
       </c>
       <c r="O58" s="9" t="s">
-        <v>2808</v>
+        <v>2807</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="60" customHeight="1">
@@ -28839,7 +28871,7 @@
         <v>2355</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="60" customHeight="1">
@@ -28855,7 +28887,7 @@
         <v>2357</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>2810</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="60" customHeight="1">
@@ -28863,7 +28895,7 @@
         <v>2358</v>
       </c>
       <c r="O62" s="9" t="s">
-        <v>2811</v>
+        <v>2810</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="60" customHeight="1">
@@ -28871,7 +28903,7 @@
         <v>2359</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="60" customHeight="1">
@@ -28879,7 +28911,7 @@
         <v>2360</v>
       </c>
       <c r="O64" s="9" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="60" customHeight="1">
@@ -28887,7 +28919,7 @@
         <v>2361</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>2814</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="60" customHeight="1">
@@ -28895,7 +28927,7 @@
         <v>2362</v>
       </c>
       <c r="O66" s="9" t="s">
-        <v>2815</v>
+        <v>2814</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="60" customHeight="1">
@@ -28903,15 +28935,15 @@
         <v>2363</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>2816</v>
+        <v>2815</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="60" customHeight="1">
       <c r="A68" s="8" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="O68" s="9" t="s">
-        <v>2817</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="60" customHeight="1">
@@ -28919,7 +28951,7 @@
         <v>2364</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>2818</v>
+        <v>2817</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="60" customHeight="1">
@@ -28927,7 +28959,7 @@
         <v>2365</v>
       </c>
       <c r="O70" s="9" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="60" customHeight="1">
@@ -28935,7 +28967,7 @@
         <v>2366</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>2819</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="60" customHeight="1">
@@ -28943,7 +28975,7 @@
         <v>2367</v>
       </c>
       <c r="O72" s="9" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="60" customHeight="1">
@@ -28951,7 +28983,7 @@
         <v>2368</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="60" customHeight="1">
@@ -28959,7 +28991,7 @@
         <v>2369</v>
       </c>
       <c r="O74" s="9" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="60" customHeight="1">
@@ -28975,7 +29007,7 @@
         <v>2371</v>
       </c>
       <c r="O76" s="9" t="s">
-        <v>2823</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="60" customHeight="1">
@@ -28983,7 +29015,7 @@
         <v>2372</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="60" customHeight="1">
@@ -28991,7 +29023,7 @@
         <v>2373</v>
       </c>
       <c r="O78" s="9" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="60" customHeight="1">
@@ -28999,7 +29031,7 @@
         <v>2374</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>2826</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="60" customHeight="1">
@@ -29007,7 +29039,7 @@
         <v>1843</v>
       </c>
       <c r="O80" s="9" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="81" spans="1:15" ht="60" customHeight="1">
@@ -29020,10 +29052,10 @@
     </row>
     <row r="82" spans="1:15" ht="60" customHeight="1">
       <c r="A82" s="8" t="s">
+        <v>3079</v>
+      </c>
+      <c r="O82" s="9" t="s">
         <v>3080</v>
-      </c>
-      <c r="O82" s="9" t="s">
-        <v>3081</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="60" customHeight="1">
@@ -29031,7 +29063,7 @@
         <v>2375</v>
       </c>
       <c r="O84" s="9" t="s">
-        <v>2827</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="85" spans="1:15" ht="60" customHeight="1">
@@ -29039,7 +29071,7 @@
         <v>2315</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>2775</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="86" spans="1:15" ht="60" customHeight="1">
@@ -29047,7 +29079,7 @@
         <v>2376</v>
       </c>
       <c r="O86" s="9" t="s">
-        <v>2772</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="87" spans="1:15" ht="60" customHeight="1">
@@ -29055,7 +29087,7 @@
         <v>2377</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="60" customHeight="1">
@@ -29063,15 +29095,15 @@
         <v>2378</v>
       </c>
       <c r="O88" s="9" t="s">
-        <v>2829</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="60" customHeight="1">
       <c r="A89" s="8" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="90" spans="1:15" ht="60" customHeight="1">
@@ -29079,7 +29111,7 @@
         <v>2379</v>
       </c>
       <c r="O90" s="9" t="s">
-        <v>2830</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="60" customHeight="1">
@@ -29087,7 +29119,7 @@
         <v>2380</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="92" spans="1:15" ht="60" customHeight="1">
@@ -29095,7 +29127,7 @@
         <v>2381</v>
       </c>
       <c r="O92" s="9" t="s">
-        <v>2832</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="93" spans="1:15" ht="60" customHeight="1">
@@ -29103,7 +29135,7 @@
         <v>2382</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="94" spans="1:15" ht="60" customHeight="1">
@@ -29111,7 +29143,7 @@
         <v>2383</v>
       </c>
       <c r="O94" s="9" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="95" spans="1:15" ht="60" customHeight="1">
@@ -29119,7 +29151,7 @@
         <v>2384</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="96" spans="1:15" ht="60" customHeight="1">
@@ -29127,7 +29159,7 @@
         <v>2385</v>
       </c>
       <c r="O96" s="9" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="97" spans="1:15" ht="60" customHeight="1">
@@ -29135,7 +29167,7 @@
         <v>2386</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="98" spans="1:15" ht="60" customHeight="1">
@@ -29143,7 +29175,7 @@
         <v>2387</v>
       </c>
       <c r="O98" s="9" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="99" spans="1:15" ht="60" customHeight="1">
@@ -29151,7 +29183,7 @@
         <v>2388</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>2773</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="100" spans="1:15" ht="60" customHeight="1">
@@ -29159,7 +29191,7 @@
         <v>2389</v>
       </c>
       <c r="O100" s="9" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="101" spans="1:15" ht="60" customHeight="1">
@@ -29167,7 +29199,7 @@
         <v>2390</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="102" spans="1:15" ht="60" customHeight="1">
@@ -29175,7 +29207,7 @@
         <v>2391</v>
       </c>
       <c r="O102" s="9" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="103" spans="1:15" ht="60" customHeight="1">
@@ -29183,7 +29215,7 @@
         <v>2392</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="104" spans="1:15" ht="60" customHeight="1">
@@ -29191,7 +29223,7 @@
         <v>2393</v>
       </c>
       <c r="O104" s="9" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
     </row>
     <row r="105" spans="1:15" ht="60" customHeight="1">
@@ -29199,7 +29231,7 @@
         <v>2394</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="106" spans="1:15" ht="60" customHeight="1">
@@ -29207,7 +29239,7 @@
         <v>2395</v>
       </c>
       <c r="O106" s="9" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="107" spans="1:15" ht="60" customHeight="1">
@@ -29215,7 +29247,7 @@
         <v>2396</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="108" spans="1:15" ht="60" customHeight="1">
@@ -29223,7 +29255,7 @@
         <v>2397</v>
       </c>
       <c r="O108" s="9" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
     </row>
     <row r="109" spans="1:15" ht="60" customHeight="1">
@@ -29231,7 +29263,7 @@
         <v>2398</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="110" spans="1:15" ht="60" customHeight="1">
@@ -29239,7 +29271,7 @@
         <v>2399</v>
       </c>
       <c r="O110" s="9" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="111" spans="1:15" ht="60" customHeight="1">
@@ -29247,7 +29279,7 @@
         <v>2400</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="112" spans="1:15" ht="60" customHeight="1">
@@ -29255,31 +29287,31 @@
         <v>2401</v>
       </c>
       <c r="O112" s="9" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
     </row>
     <row r="113" spans="1:15" ht="60" customHeight="1">
       <c r="A113" s="8" t="s">
+        <v>2870</v>
+      </c>
+      <c r="O113" s="9" t="s">
         <v>2871</v>
-      </c>
-      <c r="O113" s="9" t="s">
-        <v>2872</v>
       </c>
     </row>
     <row r="114" spans="1:15" ht="60" customHeight="1">
       <c r="A114" s="8" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="O114" s="9" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="115" spans="1:15" ht="60" customHeight="1">
       <c r="A115" s="8" t="s">
+        <v>3279</v>
+      </c>
+      <c r="O115" s="9" t="s">
         <v>3280</v>
-      </c>
-      <c r="O115" s="9" t="s">
-        <v>3281</v>
       </c>
     </row>
   </sheetData>

--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Among Us code\TheOtherUs\TheOtherUs-Edited-Lite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34EB389-B5AF-49FE-A90B-EF95D6DE9FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A49C2C55-A752-494D-B07D-97715BFAA7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1275" yWindow="1260" windowWidth="25755" windowHeight="14940" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3045" yWindow="1260" windowWidth="25755" windowHeight="14940" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Options" sheetId="3" r:id="rId1"/>
@@ -11698,11 +11698,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>捣蛋鬼可以移动附近的某一具尸体到自己脚下。
-默认范围 x 0.75 (1倍为正常报告范围)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>在会议中可以揭示身份，获得一次在会议中击杀玩家的机会。且无法被猜测
 同时，如果狼之主使用赌怪能力则本轮会议无法揭示身份。
 （猎杀和赌怪一次会议只能用一个能力）</t>
@@ -11734,6 +11729,12 @@
   </si>
   <si>
     <t>错误击杀额外增加的冷却</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>分配阵营：船员
+死亡后有概率成为捣蛋鬼。捣蛋鬼可以移动附近的某一具尸体到自己脚下。
+默认范围 x 0.75 (1倍为正常报告范围)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -15688,7 +15689,7 @@
         <v>627</v>
       </c>
       <c r="O338" s="3" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
     </row>
     <row r="339" spans="1:15" ht="24.95" customHeight="1">
@@ -15715,10 +15716,10 @@
     </row>
     <row r="341" spans="1:15" ht="24.95" customHeight="1">
       <c r="A341" s="2" t="s">
+        <v>3283</v>
+      </c>
+      <c r="O341" s="3" t="s">
         <v>3284</v>
-      </c>
-      <c r="O341" s="3" t="s">
-        <v>3285</v>
       </c>
     </row>
     <row r="343" spans="1:15" ht="24.95" customHeight="1">
@@ -16347,10 +16348,10 @@
     </row>
     <row r="412" spans="1:15" ht="24.95" customHeight="1">
       <c r="A412" s="2" t="s">
+        <v>3281</v>
+      </c>
+      <c r="O412" s="2" t="s">
         <v>3282</v>
-      </c>
-      <c r="O412" s="2" t="s">
-        <v>3283</v>
       </c>
     </row>
     <row r="413" spans="1:15" ht="24.95" customHeight="1">
@@ -25234,10 +25235,10 @@
     </row>
     <row r="98" spans="1:15" ht="20.100000000000001" customHeight="1">
       <c r="A98" s="2" t="s">
+        <v>3285</v>
+      </c>
+      <c r="O98" s="2" t="s">
         <v>3286</v>
-      </c>
-      <c r="O98" s="2" t="s">
-        <v>3287</v>
       </c>
     </row>
   </sheetData>
@@ -28439,7 +28440,7 @@
         <v>2980</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="60" customHeight="1">
@@ -29311,7 +29312,7 @@
         <v>3279</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>3280</v>
+        <v>3288</v>
       </c>
     </row>
   </sheetData>

--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Among Us code\TheOtherUs\TheOtherUs-Edited-Lite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD9A174-6CCE-4C2D-B96C-E81C9F4629DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD5733F-09CA-4A89-9929-D9A267EDF17A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1710" yWindow="1260" windowWidth="25755" windowHeight="14940" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1260" windowWidth="25755" windowHeight="14940" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Options" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Role Description" sheetId="11" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Options!$O$1:$O$1477</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Options!$O$1:$O$1479</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4098" uniqueCount="3833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4104" uniqueCount="3839">
   <si>
     <t>English</t>
   </si>
@@ -14271,14 +14271,6 @@
     <t>正 在 抓 你</t>
   </si>
   <si>
-    <t>HunterInfectedDeath</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>所有感染者已死亡!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>第一轮可以使用技能</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -14435,6 +14427,37 @@
   </si>
   <si>
     <t>在感染者全部死亡后获得的猜测次数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有感染者已死亡 | 剩余猜测次数: {0}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>infectedGuessCount</t>
+  </si>
+  <si>
+    <t>猜测次数（团队共享）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以使用赌怪能力</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>infectedCanUseGuess</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HunterGuesserCount</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>InfectedGuesserCount</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>团队剩余猜测次数: {0}</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -15046,7 +15069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1774"/>
+  <dimension ref="A1:Q1776"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40.375" style="2" customWidth="1"/>
@@ -15471,13 +15494,13 @@
     </row>
     <row r="37" spans="1:15" ht="24.95" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>3802</v>
+        <v>3800</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>3799</v>
+        <v>3797</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>3800</v>
+        <v>3798</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="24.95" customHeight="1">
@@ -15573,13 +15596,13 @@
     </row>
     <row r="47" spans="1:15" ht="24.95" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>3801</v>
+        <v>3799</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>3799</v>
+        <v>3797</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>3800</v>
+        <v>3798</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="24.95" customHeight="1">
@@ -15819,13 +15842,13 @@
     </row>
     <row r="71" spans="1:15" ht="24.95" customHeight="1">
       <c r="A71" s="2" t="s">
+        <v>3791</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>3792</v>
+      </c>
+      <c r="O71" s="3" t="s">
         <v>3793</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>3794</v>
-      </c>
-      <c r="O71" s="3" t="s">
-        <v>3795</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="24.95" customHeight="1">
@@ -15943,7 +15966,7 @@
     </row>
     <row r="83" spans="1:15" ht="24.95" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>3803</v>
+        <v>3801</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>3361</v>
@@ -15954,7 +15977,7 @@
     </row>
     <row r="84" spans="1:15" ht="24.95" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>3804</v>
+        <v>3802</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>3362</v>
@@ -15965,7 +15988,7 @@
     </row>
     <row r="85" spans="1:15" ht="24.95" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>3805</v>
+        <v>3803</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>3363</v>
@@ -15976,7 +15999,7 @@
     </row>
     <row r="86" spans="1:15" ht="24.95" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>3364</v>
@@ -15987,90 +16010,90 @@
     </row>
     <row r="87" spans="1:15" ht="24.95" customHeight="1">
       <c r="A87" s="2" t="s">
+        <v>3822</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>3824</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="O87" s="2" t="s">
         <v>3826</v>
-      </c>
-      <c r="O87" s="2" t="s">
-        <v>3828</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="24.95" customHeight="1">
       <c r="A88" s="2" t="s">
+        <v>3823</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>3825</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="O88" s="2" t="s">
         <v>3827</v>
-      </c>
-      <c r="O88" s="2" t="s">
-        <v>3829</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="24.95" customHeight="1">
       <c r="A89" s="2" t="s">
-        <v>3823</v>
+        <v>3821</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>3807</v>
+        <v>3805</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>3813</v>
+        <v>3811</v>
       </c>
     </row>
     <row r="90" spans="1:15" ht="24.95" customHeight="1">
       <c r="A90" s="2" t="s">
-        <v>3822</v>
+        <v>3820</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>3808</v>
+        <v>3806</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>3814</v>
+        <v>3812</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="24.95" customHeight="1">
       <c r="A91" s="2" t="s">
-        <v>3821</v>
+        <v>3819</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>3809</v>
+        <v>3807</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>3815</v>
+        <v>3813</v>
       </c>
     </row>
     <row r="92" spans="1:15" ht="24.95" customHeight="1">
       <c r="A92" s="2" t="s">
-        <v>3820</v>
+        <v>3818</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>3810</v>
+        <v>3808</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>3816</v>
+        <v>3814</v>
       </c>
     </row>
     <row r="93" spans="1:15" ht="24.95" customHeight="1">
       <c r="A93" s="2" t="s">
-        <v>3819</v>
+        <v>3817</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>3817</v>
+        <v>3815</v>
       </c>
     </row>
     <row r="94" spans="1:15" ht="24.95" customHeight="1">
       <c r="A94" s="2" t="s">
-        <v>3830</v>
+        <v>3828</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>3812</v>
+        <v>3810</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>3818</v>
+        <v>3816</v>
       </c>
     </row>
     <row r="95" spans="1:15" ht="24.95" customHeight="1">
@@ -19126,7 +19149,7 @@
         <v>3517</v>
       </c>
       <c r="O408" s="2" t="s">
-        <v>3796</v>
+        <v>3794</v>
       </c>
     </row>
     <row r="409" spans="1:15" ht="24.95" customHeight="1">
@@ -20272,7 +20295,7 @@
         <v>3667</v>
       </c>
       <c r="O530" s="3" t="s">
-        <v>3798</v>
+        <v>3796</v>
       </c>
     </row>
     <row r="532" spans="1:15" ht="24.95" customHeight="1">
@@ -20283,7 +20306,7 @@
         <v>3668</v>
       </c>
       <c r="O532" s="3" t="s">
-        <v>3797</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="533" spans="1:15" ht="24.95" customHeight="1">
@@ -22559,45 +22582,57 @@
       </c>
     </row>
     <row r="778" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O778" s="2"/>
+      <c r="A778" s="2" t="s">
+        <v>3835</v>
+      </c>
+      <c r="B778" s="3"/>
+      <c r="O778" s="3" t="s">
+        <v>3834</v>
+      </c>
     </row>
     <row r="779" spans="1:15" ht="24.95" customHeight="1">
       <c r="A779" s="2" t="s">
-        <v>3759</v>
-      </c>
-      <c r="O779" s="2" t="s">
-        <v>3766</v>
+        <v>3832</v>
+      </c>
+      <c r="B779" s="3"/>
+      <c r="O779" s="3" t="s">
+        <v>3833</v>
       </c>
     </row>
     <row r="780" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A780" s="2" t="s">
-        <v>3760</v>
-      </c>
-      <c r="O780" s="2" t="s">
-        <v>3765</v>
-      </c>
+      <c r="O780" s="2"/>
     </row>
     <row r="781" spans="1:15" ht="24.95" customHeight="1">
       <c r="A781" s="2" t="s">
-        <v>3777</v>
+        <v>3759</v>
       </c>
       <c r="O781" s="2" t="s">
-        <v>3791</v>
+        <v>3766</v>
       </c>
     </row>
     <row r="782" spans="1:15" ht="24.95" customHeight="1">
       <c r="A782" s="2" t="s">
-        <v>3831</v>
+        <v>3760</v>
       </c>
       <c r="O782" s="2" t="s">
-        <v>3832</v>
+        <v>3765</v>
       </c>
     </row>
     <row r="783" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O783" s="2"/>
+      <c r="A783" s="2" t="s">
+        <v>3777</v>
+      </c>
+      <c r="O783" s="2" t="s">
+        <v>3789</v>
+      </c>
     </row>
     <row r="784" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O784" s="2"/>
+      <c r="A784" s="2" t="s">
+        <v>3829</v>
+      </c>
+      <c r="O784" s="2" t="s">
+        <v>3830</v>
+      </c>
     </row>
     <row r="785" spans="15:15" ht="24.95" customHeight="1">
       <c r="O785" s="2"/>
@@ -22869,12 +22904,12 @@
     <row r="874" spans="15:15" ht="24.95" customHeight="1">
       <c r="O874" s="2"/>
     </row>
+    <row r="875" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O875" s="2"/>
+    </row>
     <row r="876" spans="15:15" ht="24.95" customHeight="1">
       <c r="O876" s="2"/>
     </row>
-    <row r="877" spans="15:15" ht="24.95" customHeight="1">
-      <c r="O877" s="2"/>
-    </row>
     <row r="878" spans="15:15" ht="24.95" customHeight="1">
       <c r="O878" s="2"/>
     </row>
@@ -24049,26 +24084,26 @@
       <c r="O1268" s="2"/>
     </row>
     <row r="1269" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A1269" s="5"/>
-      <c r="B1269" s="5"/>
-      <c r="D1269" s="5"/>
-      <c r="E1269" s="5"/>
-      <c r="F1269" s="5"/>
-      <c r="G1269" s="5"/>
-      <c r="H1269" s="5"/>
-      <c r="I1269" s="5"/>
-      <c r="J1269" s="5"/>
-      <c r="K1269" s="5"/>
-      <c r="L1269" s="5"/>
-      <c r="M1269" s="5"/>
-      <c r="N1269" s="5"/>
-      <c r="O1269" s="6"/>
+      <c r="O1269" s="2"/>
     </row>
     <row r="1270" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1270" s="2"/>
     </row>
     <row r="1271" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O1271" s="2"/>
+      <c r="A1271" s="5"/>
+      <c r="B1271" s="5"/>
+      <c r="D1271" s="5"/>
+      <c r="E1271" s="5"/>
+      <c r="F1271" s="5"/>
+      <c r="G1271" s="5"/>
+      <c r="H1271" s="5"/>
+      <c r="I1271" s="5"/>
+      <c r="J1271" s="5"/>
+      <c r="K1271" s="5"/>
+      <c r="L1271" s="5"/>
+      <c r="M1271" s="5"/>
+      <c r="N1271" s="5"/>
+      <c r="O1271" s="6"/>
     </row>
     <row r="1272" spans="1:15" ht="24.95" customHeight="1">
       <c r="O1272" s="2"/>
@@ -25579,8 +25614,14 @@
     <row r="1774" spans="15:15" ht="24.95" customHeight="1">
       <c r="O1774" s="2"/>
     </row>
+    <row r="1775" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1775" s="2"/>
+    </row>
+    <row r="1776" spans="15:15" ht="24.95" customHeight="1">
+      <c r="O1776" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="O1:O1477" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="O1:O1479" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -25589,7 +25630,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q109"/>
+  <dimension ref="A1:Q110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
@@ -26199,565 +26240,573 @@
     </row>
     <row r="61" spans="1:15" ht="24.95" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>3789</v>
+        <v>3836</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>3790</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A63" s="1" t="s">
-        <v>2777</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>2900</v>
-      </c>
-      <c r="O63" s="1" t="s">
-        <v>2776</v>
+        <v>3831</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A62" s="1" t="s">
+        <v>3837</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>3838</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="24.95" customHeight="1">
       <c r="A64" s="1" t="s">
+        <v>2777</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>2900</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>2776</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A65" s="1" t="s">
         <v>2780</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>2901</v>
       </c>
-      <c r="O64" s="1" t="s">
+      <c r="O65" s="1" t="s">
         <v>2794</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A66" s="1" t="s">
-        <v>2160</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>2161</v>
-      </c>
-      <c r="O66" s="1" t="s">
-        <v>2162</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="24.95" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>2164</v>
+        <v>2160</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>2796</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="24.95" customHeight="1">
       <c r="A68" s="1" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>2163</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>2796</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A69" s="1" t="s">
         <v>2165</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B69" s="1" t="s">
         <v>2902</v>
       </c>
-      <c r="O68" s="1" t="s">
+      <c r="O69" s="1" t="s">
         <v>2166</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A70" s="1" t="s">
-        <v>2520</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>2903</v>
-      </c>
-      <c r="O70" s="1" t="s">
-        <v>2550</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="24.95" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="24.95" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>2786</v>
+        <v>2521</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>2909</v>
+        <v>2904</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>2788</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="24.95" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>2787</v>
+        <v>2786</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>2910</v>
+        <v>2909</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>2789</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="24.95" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>2522</v>
+        <v>2787</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>2905</v>
+        <v>2910</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>2548</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="24.95" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>2911</v>
+        <v>2905</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="24.95" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="24.95" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>2906</v>
+        <v>2912</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="24.95" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>2915</v>
+        <v>2906</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="24.95" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>2602</v>
+        <v>2526</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>2914</v>
+        <v>2915</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>2603</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="24.95" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>2527</v>
+        <v>2602</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>2543</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="81" spans="1:15" ht="24.95" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>2907</v>
+        <v>2913</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>2542</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="24.95" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>2916</v>
+        <v>2907</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>2541</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="83" spans="1:15" ht="24.95" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>3054</v>
+        <v>2916</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>2557</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="24.95" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>2917</v>
+        <v>3054</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="85" spans="1:15" ht="24.95" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>2540</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="86" spans="1:15" ht="24.95" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>2555</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="87" spans="1:15" ht="24.95" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="24.95" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>2935</v>
+        <v>2920</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>2539</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="24.95" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>2975</v>
+        <v>2935</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>2553</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="90" spans="1:15" ht="24.95" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>2921</v>
+        <v>2975</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>2551</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="24.95" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="92" spans="1:15" ht="24.95" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>2558</v>
+        <v>2538</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>2559</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="93" spans="1:15" ht="24.95" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>2560</v>
+        <v>2558</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>2908</v>
+        <v>2923</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>2561</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="94" spans="1:15" ht="24.95" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>2562</v>
+        <v>2560</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>3037</v>
+        <v>2908</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>2563</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="95" spans="1:15" ht="24.95" customHeight="1">
       <c r="A95" s="1" t="s">
+        <v>2562</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>3037</v>
+      </c>
+      <c r="O95" s="1" t="s">
+        <v>2563</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A96" s="1" t="s">
         <v>2779</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B96" s="1" t="s">
         <v>3038</v>
       </c>
-      <c r="O95" s="1" t="s">
+      <c r="O96" s="1" t="s">
         <v>2778</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A97" s="1" t="s">
-        <v>2739</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>2936</v>
-      </c>
-      <c r="O97" s="1" t="s">
-        <v>2740</v>
       </c>
     </row>
     <row r="98" spans="1:15" ht="24.95" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>2758</v>
+        <v>2739</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>2937</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>2703</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>2704</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>2705</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>2706</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>2707</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>2708</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>2709</v>
-      </c>
-      <c r="J98" s="1" t="s">
-        <v>2710</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>2711</v>
-      </c>
-      <c r="L98" s="1" t="s">
-        <v>2712</v>
-      </c>
-      <c r="M98" s="1" t="s">
-        <v>2713</v>
-      </c>
-      <c r="N98" s="1" t="s">
-        <v>2714</v>
+        <v>2936</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>2738</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="99" spans="1:15" ht="24.95" customHeight="1">
       <c r="A99" s="1" t="s">
-        <v>2715</v>
+        <v>2758</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>2737</v>
+        <v>2937</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>2691</v>
+        <v>2703</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>2692</v>
+        <v>2704</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>2693</v>
+        <v>2705</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>2694</v>
+        <v>2706</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>2695</v>
+        <v>2707</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>2696</v>
+        <v>2708</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>2697</v>
+        <v>2709</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>2698</v>
+        <v>2710</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>2699</v>
+        <v>2711</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>2700</v>
+        <v>2712</v>
       </c>
       <c r="M99" s="1" t="s">
-        <v>2701</v>
+        <v>2713</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>2702</v>
+        <v>2714</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>2736</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="100" spans="1:15" ht="24.95" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>2716</v>
+        <v>2715</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>2891</v>
+        <v>2737</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>2691</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>2692</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>2693</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>2694</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>2695</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>2696</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>2697</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>2698</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>2699</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>2700</v>
+      </c>
+      <c r="M100" s="1" t="s">
+        <v>2701</v>
+      </c>
+      <c r="N100" s="1" t="s">
+        <v>2702</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>2761</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="101" spans="1:15" ht="24.95" customHeight="1">
       <c r="A101" s="1" t="s">
-        <v>2759</v>
+        <v>2716</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>2760</v>
+        <v>2891</v>
       </c>
       <c r="O101" s="1" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="102" spans="1:15" ht="24.95" customHeight="1">
       <c r="A102" s="1" t="s">
-        <v>2717</v>
+        <v>2759</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>2690</v>
+        <v>2760</v>
       </c>
       <c r="O102" s="1" t="s">
-        <v>2735</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="103" spans="1:15" ht="24.95" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>2733</v>
+        <v>2717</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>2938</v>
+        <v>2690</v>
       </c>
       <c r="O103" s="1" t="s">
-        <v>2734</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="104" spans="1:15" ht="24.95" customHeight="1">
       <c r="A104" s="1" t="s">
-        <v>2742</v>
+        <v>2733</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>2741</v>
+        <v>2938</v>
       </c>
       <c r="O104" s="1" t="s">
-        <v>2745</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="105" spans="1:15" ht="24.95" customHeight="1">
       <c r="A105" s="1" t="s">
-        <v>2743</v>
+        <v>2742</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>2744</v>
+        <v>2741</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="106" spans="1:15" ht="24.95" customHeight="1">
       <c r="A106" s="1" t="s">
-        <v>2750</v>
+        <v>2743</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>2751</v>
+        <v>2744</v>
       </c>
       <c r="O106" s="1" t="s">
-        <v>2174</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="107" spans="1:15" ht="24.95" customHeight="1">
       <c r="A107" s="1" t="s">
-        <v>2756</v>
+        <v>2750</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>2752</v>
+        <v>2751</v>
       </c>
       <c r="O107" s="1" t="s">
-        <v>1505</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="108" spans="1:15" ht="24.95" customHeight="1">
       <c r="A108" s="1" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>2892</v>
+        <v>2752</v>
       </c>
       <c r="O108" s="1" t="s">
-        <v>2757</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="109" spans="1:15" ht="24.95" customHeight="1">
       <c r="A109" s="1" t="s">
+        <v>2755</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>2892</v>
+      </c>
+      <c r="O109" s="1" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A110" s="1" t="s">
         <v>2733</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B110" s="1" t="s">
         <v>2753</v>
       </c>
-      <c r="O109" s="1" t="s">
+      <c r="O110" s="1" t="s">
         <v>2754</v>
       </c>
     </row>
@@ -28662,7 +28711,7 @@
         <v>1544</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>3792</v>
+        <v>3790</v>
       </c>
       <c r="O19" s="7" t="s">
         <v>2242</v>

--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Among Us code\TheOtherUs\TheOtherUs-Edited-Lite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1513E5-9F26-4898-8C8C-3DB93F722895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA57CAF3-BC31-4291-AF09-54E30622746D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1710" yWindow="1260" windowWidth="25755" windowHeight="14940" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2160" yWindow="900" windowWidth="25755" windowHeight="14940" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Options" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4102" uniqueCount="3837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4121" uniqueCount="3855">
   <si>
     <t>English</t>
   </si>
@@ -14129,9 +14129,6 @@
     <t>hunterMaxCount</t>
   </si>
   <si>
-    <t>hunterCooldown</t>
-  </si>
-  <si>
     <t>infectedActiveLimit</t>
   </si>
   <si>
@@ -14143,10 +14140,6 @@
   </si>
   <si>
     <t>同时存在的感染者数量</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能冷却</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -14185,10 +14178,6 @@
     <t>身份窃贼可以击杀任何带刀职业，并夺取他们的职业。包括跟班、巴甫洛夫等。
 如果目标并非带刀职业则会自杀。
 在赌怪模式中，身份窃贼可以通过猜测带刀的玩家获得身份</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>hunterCanStakeRoundOne</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -14245,10 +14234,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>第一轮可以使用技能</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Change your look to not get caught</t>
   </si>
   <si>
@@ -14394,13 +14379,6 @@
   </si>
   <si>
     <t>PresetCustomMap</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>hunterCanShootNum</t>
-  </si>
-  <si>
-    <t>在感染者全部死亡后获得的猜测次数</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -14447,6 +14425,103 @@
   </si>
   <si>
     <t>击杀可疑的玩家</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jailor</t>
+  </si>
+  <si>
+    <t>JailorIntroDesc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>JailorShortDesc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>典狱长</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>JailorFullDesc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>jailButtonText</t>
+  </si>
+  <si>
+    <t>JAIL</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>监禁</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jailor.YouAreJailed</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你已被监禁</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>YOU ARE JAILED</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jailor.InJail</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> (被监禁)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jailor.JailedChat</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jailor.JailorChat</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>jailorCooldown</t>
+  </si>
+  <si>
+    <t>技能冷却</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>jailorUseCount</t>
+  </si>
+  <si>
+    <t>技能最大使用次数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你可以使用 [/jail text] 指令来与被监禁玩家私聊。
+并且对方本轮会议内只能向你发送消息，其它玩家无法看到。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你已被监禁，本轮会议发送消息只能与典狱长私聊。其他玩家无法看到。
+另外，本轮会议你无法投票，也无法使用任何会议技能。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你可以在行动阶段选择一位玩家监禁，进入会议后会将目标玩家监禁。
+目标在会议中发送的消息只会被典狱长接收，其他玩家无法看到，
+但典狱长可以使用 [/jail text] 指令与被监禁者私聊。
+典狱长可以在会议中处决被监禁玩家，但如果处决了船员，将永久失去技能。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>囚禁可疑的玩家</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>监禁并处决可疑玩家</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -15483,13 +15558,13 @@
     </row>
     <row r="37" spans="1:15" ht="24.95" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>3795</v>
+        <v>3791</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>3792</v>
+        <v>3788</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>3793</v>
+        <v>3789</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="24.95" customHeight="1">
@@ -15585,13 +15660,13 @@
     </row>
     <row r="47" spans="1:15" ht="24.95" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>3794</v>
+        <v>3790</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>3792</v>
+        <v>3788</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>3793</v>
+        <v>3789</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="24.95" customHeight="1">
@@ -15831,13 +15906,13 @@
     </row>
     <row r="71" spans="1:15" ht="24.95" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>3786</v>
+        <v>3782</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>3787</v>
+        <v>3783</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>3788</v>
+        <v>3784</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="24.95" customHeight="1">
@@ -15955,7 +16030,7 @@
     </row>
     <row r="83" spans="1:15" ht="24.95" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>3796</v>
+        <v>3792</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>3360</v>
@@ -15966,7 +16041,7 @@
     </row>
     <row r="84" spans="1:15" ht="24.95" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>3797</v>
+        <v>3793</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>3361</v>
@@ -15977,7 +16052,7 @@
     </row>
     <row r="85" spans="1:15" ht="24.95" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>3798</v>
+        <v>3794</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>3362</v>
@@ -15988,7 +16063,7 @@
     </row>
     <row r="86" spans="1:15" ht="24.95" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>3799</v>
+        <v>3795</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>3363</v>
@@ -15999,90 +16074,90 @@
     </row>
     <row r="87" spans="1:15" ht="24.95" customHeight="1">
       <c r="A87" s="2" t="s">
+        <v>3813</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>3815</v>
+      </c>
+      <c r="O87" s="2" t="s">
         <v>3817</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>3819</v>
-      </c>
-      <c r="O87" s="2" t="s">
-        <v>3821</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="24.95" customHeight="1">
       <c r="A88" s="2" t="s">
+        <v>3814</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>3816</v>
+      </c>
+      <c r="O88" s="2" t="s">
         <v>3818</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>3820</v>
-      </c>
-      <c r="O88" s="2" t="s">
-        <v>3822</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="24.95" customHeight="1">
       <c r="A89" s="2" t="s">
-        <v>3816</v>
+        <v>3812</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>3800</v>
+        <v>3796</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>3806</v>
+        <v>3802</v>
       </c>
     </row>
     <row r="90" spans="1:15" ht="24.95" customHeight="1">
       <c r="A90" s="2" t="s">
-        <v>3815</v>
+        <v>3811</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>3801</v>
+        <v>3797</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>3807</v>
+        <v>3803</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="24.95" customHeight="1">
       <c r="A91" s="2" t="s">
-        <v>3814</v>
+        <v>3810</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>3802</v>
+        <v>3798</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>3808</v>
+        <v>3804</v>
       </c>
     </row>
     <row r="92" spans="1:15" ht="24.95" customHeight="1">
       <c r="A92" s="2" t="s">
-        <v>3813</v>
+        <v>3809</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>3803</v>
+        <v>3799</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>3809</v>
+        <v>3805</v>
       </c>
     </row>
     <row r="93" spans="1:15" ht="24.95" customHeight="1">
       <c r="A93" s="2" t="s">
-        <v>3812</v>
+        <v>3808</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>3804</v>
+        <v>3800</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>3810</v>
+        <v>3806</v>
       </c>
     </row>
     <row r="94" spans="1:15" ht="24.95" customHeight="1">
       <c r="A94" s="2" t="s">
-        <v>3823</v>
+        <v>3819</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>3805</v>
+        <v>3801</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>3811</v>
+        <v>3807</v>
       </c>
     </row>
     <row r="95" spans="1:15" ht="24.95" customHeight="1">
@@ -19138,7 +19213,7 @@
         <v>3516</v>
       </c>
       <c r="O408" s="2" t="s">
-        <v>3789</v>
+        <v>3785</v>
       </c>
     </row>
     <row r="409" spans="1:15" ht="24.95" customHeight="1">
@@ -20284,7 +20359,7 @@
         <v>3666</v>
       </c>
       <c r="O530" s="3" t="s">
-        <v>3791</v>
+        <v>3787</v>
       </c>
     </row>
     <row r="532" spans="1:15" ht="24.95" customHeight="1">
@@ -20295,7 +20370,7 @@
         <v>3667</v>
       </c>
       <c r="O532" s="3" t="s">
-        <v>3790</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="533" spans="1:15" ht="24.95" customHeight="1">
@@ -22554,38 +22629,38 @@
     </row>
     <row r="776" spans="1:15" ht="24.95" customHeight="1">
       <c r="A776" s="2" t="s">
-        <v>3761</v>
+        <v>3760</v>
       </c>
       <c r="B776" s="3"/>
       <c r="O776" s="3" t="s">
-        <v>3762</v>
+        <v>3761</v>
       </c>
     </row>
     <row r="777" spans="1:15" ht="24.95" customHeight="1">
       <c r="A777" s="2" t="s">
-        <v>3760</v>
+        <v>3759</v>
       </c>
       <c r="B777" s="3"/>
       <c r="O777" s="3" t="s">
-        <v>3763</v>
+        <v>3762</v>
       </c>
     </row>
     <row r="778" spans="1:15" ht="24.95" customHeight="1">
       <c r="A778" s="2" t="s">
-        <v>3830</v>
+        <v>3824</v>
       </c>
       <c r="B778" s="3"/>
       <c r="O778" s="3" t="s">
-        <v>3829</v>
+        <v>3823</v>
       </c>
     </row>
     <row r="779" spans="1:15" ht="24.95" customHeight="1">
       <c r="A779" s="2" t="s">
-        <v>3827</v>
+        <v>3821</v>
       </c>
       <c r="B779" s="3"/>
       <c r="O779" s="3" t="s">
-        <v>3828</v>
+        <v>3822</v>
       </c>
     </row>
     <row r="780" spans="1:15" ht="24.95" customHeight="1">
@@ -22596,31 +22671,26 @@
         <v>3758</v>
       </c>
       <c r="O781" s="2" t="s">
-        <v>3765</v>
+        <v>3763</v>
       </c>
     </row>
     <row r="782" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A782" s="2" t="s">
-        <v>3759</v>
-      </c>
-      <c r="O782" s="2" t="s">
-        <v>3764</v>
-      </c>
+      <c r="O782" s="2"/>
     </row>
     <row r="783" spans="1:15" ht="24.95" customHeight="1">
       <c r="A783" s="2" t="s">
-        <v>3774</v>
+        <v>3846</v>
       </c>
       <c r="O783" s="2" t="s">
-        <v>3784</v>
+        <v>3847</v>
       </c>
     </row>
     <row r="784" spans="1:15" ht="24.95" customHeight="1">
       <c r="A784" s="2" t="s">
-        <v>3824</v>
+        <v>3848</v>
       </c>
       <c r="O784" s="2" t="s">
-        <v>3825</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="785" spans="15:15" ht="24.95" customHeight="1">
@@ -25619,7 +25689,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q110"/>
+  <dimension ref="A1:Q115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
@@ -26229,18 +26299,18 @@
     </row>
     <row r="61" spans="1:15" ht="24.95" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>3831</v>
+        <v>3825</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>3826</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="24.95" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>3832</v>
+        <v>3826</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>3833</v>
+        <v>3827</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="24.95" customHeight="1">
@@ -26797,6 +26867,41 @@
       </c>
       <c r="O110" s="1" t="s">
         <v>2753</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A112" s="1" t="s">
+        <v>3839</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>3841</v>
+      </c>
+      <c r="O112" s="1" t="s">
+        <v>3840</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A113" s="1" t="s">
+        <v>3842</v>
+      </c>
+      <c r="O113" s="1" t="s">
+        <v>3843</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A114" s="1" t="s">
+        <v>3844</v>
+      </c>
+      <c r="O114" s="1" t="s">
+        <v>3851</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A115" s="1" t="s">
+        <v>3845</v>
+      </c>
+      <c r="O115" s="1" t="s">
+        <v>3850</v>
       </c>
     </row>
   </sheetData>
@@ -27330,7 +27435,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:S98"/>
+  <dimension ref="A1:S99"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21.5" style="2" customWidth="1"/>
@@ -28479,6 +28584,17 @@
         <v>2869</v>
       </c>
     </row>
+    <row r="99" spans="1:15" ht="20.100000000000001" customHeight="1">
+      <c r="A99" s="2" t="s">
+        <v>3836</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>3837</v>
+      </c>
+      <c r="O99" s="2" t="s">
+        <v>3838</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28488,7 +28604,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:Q447"/>
+  <dimension ref="A1:Q451"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="27.875" style="7" customWidth="1"/>
@@ -28700,7 +28816,7 @@
         <v>1544</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>3785</v>
+        <v>3781</v>
       </c>
       <c r="O19" s="7" t="s">
         <v>2241</v>
@@ -32173,29 +32289,29 @@
     </row>
     <row r="441" spans="1:15">
       <c r="A441" s="7" t="s">
+        <v>3766</v>
+      </c>
+      <c r="B441" s="7" t="s">
+        <v>3767</v>
+      </c>
+      <c r="O441" s="7" t="s">
         <v>3768</v>
-      </c>
-      <c r="B441" s="7" t="s">
-        <v>3769</v>
-      </c>
-      <c r="O441" s="7" t="s">
-        <v>3770</v>
       </c>
     </row>
     <row r="442" spans="1:15">
       <c r="A442" s="7" t="s">
-        <v>3766</v>
+        <v>3764</v>
       </c>
       <c r="O442" s="7" t="s">
-        <v>3775</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="443" spans="1:15">
       <c r="A443" s="7" t="s">
-        <v>3767</v>
+        <v>3765</v>
       </c>
       <c r="O443" s="7" t="s">
-        <v>3776</v>
+        <v>3773</v>
       </c>
     </row>
     <row r="445" spans="1:15">
@@ -32206,7 +32322,7 @@
         <v>1930</v>
       </c>
       <c r="O445" s="7" t="s">
-        <v>3835</v>
+        <v>3829</v>
       </c>
     </row>
     <row r="446" spans="1:15">
@@ -32219,7 +32335,34 @@
         <v>1932</v>
       </c>
       <c r="O447" s="7" t="s">
-        <v>3836</v>
+        <v>3830</v>
+      </c>
+    </row>
+    <row r="449" spans="1:15">
+      <c r="A449" s="7" t="s">
+        <v>3831</v>
+      </c>
+      <c r="B449" s="7" t="s">
+        <v>3831</v>
+      </c>
+      <c r="O449" s="7" t="s">
+        <v>3834</v>
+      </c>
+    </row>
+    <row r="450" spans="1:15">
+      <c r="A450" s="7" t="s">
+        <v>3832</v>
+      </c>
+      <c r="O450" s="7" t="s">
+        <v>3854</v>
+      </c>
+    </row>
+    <row r="451" spans="1:15">
+      <c r="A451" s="7" t="s">
+        <v>3833</v>
+      </c>
+      <c r="O451" s="7" t="s">
+        <v>3853</v>
       </c>
     </row>
   </sheetData>
@@ -32231,7 +32374,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:Q119"/>
+  <dimension ref="A1:Q120"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="60" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.625" style="8" customWidth="1"/>
@@ -32774,7 +32917,7 @@
         <v>3259</v>
       </c>
       <c r="O46" s="9" t="s">
-        <v>3773</v>
+        <v>3771</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="60" customHeight="1">
@@ -32873,7 +33016,7 @@
         <v>3268</v>
       </c>
       <c r="O56" s="9" t="s">
-        <v>3777</v>
+        <v>3774</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="60" customHeight="1">
@@ -32895,7 +33038,7 @@
         <v>3270</v>
       </c>
       <c r="O58" s="9" t="s">
-        <v>3778</v>
+        <v>3775</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="60" customHeight="1">
@@ -32939,7 +33082,7 @@
         <v>3274</v>
       </c>
       <c r="O62" s="9" t="s">
-        <v>3779</v>
+        <v>3776</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="60" customHeight="1">
@@ -32950,7 +33093,7 @@
         <v>3275</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>3780</v>
+        <v>3777</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="60" customHeight="1">
@@ -33005,7 +33148,7 @@
         <v>3280</v>
       </c>
       <c r="O68" s="9" t="s">
-        <v>3781</v>
+        <v>3778</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="60" customHeight="1">
@@ -33027,7 +33170,7 @@
         <v>3210</v>
       </c>
       <c r="O70" s="9" t="s">
-        <v>3782</v>
+        <v>3779</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="60" customHeight="1">
@@ -33126,7 +33269,7 @@
         <v>3289</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>3783</v>
+        <v>3780</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="60" customHeight="1">
@@ -33516,15 +33659,23 @@
     </row>
     <row r="117" spans="1:15" ht="82.5">
       <c r="A117" s="8" t="s">
-        <v>3771</v>
+        <v>3769</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>3834</v>
+        <v>3828</v>
       </c>
     </row>
     <row r="119" spans="1:15" ht="60" customHeight="1">
       <c r="A119" s="8" t="s">
-        <v>3772</v>
+        <v>3770</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" ht="60" customHeight="1">
+      <c r="A120" s="8" t="s">
+        <v>3835</v>
+      </c>
+      <c r="O120" s="9" t="s">
+        <v>3852</v>
       </c>
     </row>
   </sheetData>

--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Among Us code\TheOtherUs\TheOtherUs-Edited-Lite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A50570-98FF-41D7-914D-3E6F4B096992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E922D8A-85FD-4D4E-B562-4B2EB27E8AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3045" yWindow="1260" windowWidth="25755" windowHeight="14940" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2265" yWindow="615" windowWidth="25755" windowHeight="14940" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Options" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4293" uniqueCount="4022">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4299" uniqueCount="4028">
   <si>
     <t>English</t>
   </si>
@@ -15282,7 +15282,30 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>游戏中指令：
+    <t>MessageFromTheHost</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>【 ★ Host message ★ 】</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>【 ★ 房主消息 ★ 】</t>
+  </si>
+  <si>
+    <t>Command.NotInGame</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前并未在游戏内。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Not In Game.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令列表：
 /end ：强制游戏结束
 /mt: 召集/结束会议
 /list : 获取全部玩家的ID
@@ -26265,7 +26288,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q214"/>
+  <dimension ref="A1:Q217"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.125" style="1" bestFit="1" customWidth="1"/>
@@ -26473,7 +26496,7 @@
         <v>4019</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>4021</v>
+        <v>4027</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="189">
@@ -26509,109 +26532,65 @@
         <v>3833</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="24.95" customHeight="1">
+    <row r="19" spans="1:15" ht="15.75">
+      <c r="A19" s="1" t="s">
+        <v>4024</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>4026</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>4025</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15.75">
       <c r="A20" s="1" t="s">
+        <v>4021</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>4022</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>4023</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="15.75"/>
+    <row r="23" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A23" s="1" t="s">
         <v>3838</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>1023</v>
       </c>
-      <c r="O20" s="1" t="s">
+      <c r="O23" s="1" t="s">
         <v>1024</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A21" s="1" t="s">
+    <row r="24" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A24" s="1" t="s">
         <v>3866</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>3868</v>
       </c>
-      <c r="O21" s="15" t="s">
+      <c r="O24" s="15" t="s">
         <v>3871</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A22" s="1" t="s">
+    <row r="25" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A25" s="1" t="s">
         <v>3867</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>3869</v>
       </c>
-      <c r="O22" s="15" t="s">
+      <c r="O25" s="15" t="s">
         <v>3870</v>
       </c>
     </row>
-    <row r="23" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="5"/>
-    </row>
-    <row r="24" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>3815</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A25" s="4" t="s">
-        <v>3816</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>3818</v>
-      </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="5" t="s">
-        <v>3819</v>
-      </c>
-    </row>
     <row r="26" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A26" s="4" t="s">
-        <v>3817</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>3813</v>
-      </c>
+      <c r="A26" s="4"/>
+      <c r="B26" s="5"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -26624,16 +26603,14 @@
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
-      <c r="O26" s="5" t="s">
-        <v>3814</v>
-      </c>
+      <c r="O26" s="5"/>
     </row>
     <row r="27" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>3798</v>
+        <v>3815</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>3800</v>
+        <v>20</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
@@ -26648,15 +26625,15 @@
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
       <c r="O27" s="5" t="s">
-        <v>3799</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>3802</v>
+        <v>3816</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>3812</v>
+        <v>3818</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -26671,15 +26648,15 @@
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
       <c r="O28" s="5" t="s">
-        <v>3808</v>
+        <v>3819</v>
       </c>
     </row>
     <row r="29" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>3803</v>
+        <v>3817</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>3811</v>
+        <v>3813</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -26694,15 +26671,15 @@
       <c r="M29" s="4"/>
       <c r="N29" s="4"/>
       <c r="O29" s="5" t="s">
-        <v>3805</v>
+        <v>3814</v>
       </c>
     </row>
     <row r="30" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A30" s="4" t="s">
-        <v>3804</v>
+        <v>3798</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>3810</v>
+        <v>3800</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
@@ -26717,15 +26694,15 @@
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
       <c r="O30" s="5" t="s">
-        <v>3807</v>
+        <v>3799</v>
       </c>
     </row>
     <row r="31" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>3820</v>
+        <v>3802</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>3809</v>
+        <v>3812</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
@@ -26740,15 +26717,15 @@
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
       <c r="O31" s="5" t="s">
-        <v>3806</v>
+        <v>3808</v>
       </c>
     </row>
     <row r="32" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>3801</v>
+        <v>3803</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>3813</v>
+        <v>3811</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -26763,15 +26740,15 @@
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
       <c r="O32" s="5" t="s">
-        <v>3821</v>
+        <v>3805</v>
       </c>
     </row>
     <row r="33" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>22</v>
+        <v>3804</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>23</v>
+        <v>3810</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -26786,15 +26763,15 @@
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
       <c r="O33" s="5" t="s">
-        <v>24</v>
+        <v>3807</v>
       </c>
     </row>
     <row r="34" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>25</v>
+        <v>3820</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>26</v>
+        <v>3809</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -26809,15 +26786,15 @@
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
       <c r="O34" s="5" t="s">
-        <v>27</v>
+        <v>3806</v>
       </c>
     </row>
     <row r="35" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>28</v>
+        <v>3801</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>29</v>
+        <v>3813</v>
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -26832,15 +26809,15 @@
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
       <c r="O35" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" s="6" customFormat="1" ht="24.75" customHeight="1">
+        <v>3821</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A36" s="4" t="s">
-        <v>2079</v>
+        <v>22</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>3310</v>
+        <v>23</v>
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -26855,15 +26832,15 @@
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
       <c r="O36" s="5" t="s">
-        <v>2080</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" s="6" customFormat="1" ht="24.75" customHeight="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>2166</v>
+        <v>25</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>2167</v>
+        <v>26</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -26878,15 +26855,15 @@
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
       <c r="O37" s="5" t="s">
-        <v>2168</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A38" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -26901,12 +26878,16 @@
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
       <c r="O38" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" s="6" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A39" s="4" t="s">
+        <v>2079</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>3310</v>
+      </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -26919,14 +26900,16 @@
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
-      <c r="O39" s="5"/>
-    </row>
-    <row r="40" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
+      <c r="O39" s="5" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" s="6" customFormat="1" ht="24.75" customHeight="1">
       <c r="A40" s="4" t="s">
-        <v>2056</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>2072</v>
+        <v>2166</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>2167</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -26941,15 +26924,15 @@
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
       <c r="O40" s="5" t="s">
-        <v>2057</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="41" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>2055</v>
+        <v>31</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>2071</v>
+        <v>32</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -26964,16 +26947,12 @@
       <c r="M41" s="4"/>
       <c r="N41" s="4"/>
       <c r="O41" s="5" t="s">
-        <v>2058</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A42" s="4" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2069</v>
-      </c>
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -26986,16 +26965,14 @@
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
-      <c r="O42" s="5" t="s">
-        <v>2070</v>
-      </c>
+      <c r="O42" s="5"/>
     </row>
     <row r="43" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>2075</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2066</v>
+        <v>2056</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>2072</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -27010,15 +26987,15 @@
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
       <c r="O43" s="5" t="s">
-        <v>2064</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="44" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>2554</v>
+        <v>2055</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>2067</v>
+        <v>2071</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -27033,15 +27010,15 @@
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
       <c r="O44" s="5" t="s">
-        <v>2063</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="45" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>2555</v>
+        <v>2068</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>2073</v>
+        <v>2069</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
@@ -27056,15 +27033,15 @@
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
       <c r="O45" s="5" t="s">
-        <v>2062</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="46" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A46" s="4" t="s">
-        <v>2084</v>
+        <v>2075</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
@@ -27079,15 +27056,15 @@
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
       <c r="O46" s="5" t="s">
-        <v>2078</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="47" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>2129</v>
+        <v>2554</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>2130</v>
+        <v>2067</v>
       </c>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
@@ -27102,15 +27079,15 @@
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
       <c r="O47" s="5" t="s">
-        <v>2131</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="48" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A48" s="4" t="s">
-        <v>2085</v>
+        <v>2555</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>2086</v>
+        <v>2073</v>
       </c>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
@@ -27125,15 +27102,15 @@
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
       <c r="O48" s="5" t="s">
-        <v>2087</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="49" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>2359</v>
+        <v>2084</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>3311</v>
+        <v>2065</v>
       </c>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
@@ -27148,15 +27125,15 @@
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
       <c r="O49" s="5" t="s">
-        <v>2360</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="50" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A50" s="4" t="s">
-        <v>2161</v>
+        <v>2129</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>2361</v>
+        <v>2130</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -27171,15 +27148,15 @@
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
       <c r="O50" s="5" t="s">
-        <v>2162</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="51" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>2059</v>
+        <v>2085</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>2074</v>
+        <v>2086</v>
       </c>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -27194,15 +27171,15 @@
       <c r="M51" s="4"/>
       <c r="N51" s="4"/>
       <c r="O51" s="5" t="s">
-        <v>2060</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="52" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A52" s="4" t="s">
-        <v>2061</v>
+        <v>2359</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>2076</v>
+        <v>3311</v>
       </c>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
@@ -27217,15 +27194,15 @@
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
       <c r="O52" s="5" t="s">
-        <v>2077</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="53" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>2081</v>
+        <v>2161</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>2083</v>
+        <v>2361</v>
       </c>
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
@@ -27240,1489 +27217,1558 @@
       <c r="M53" s="4"/>
       <c r="N53" s="4"/>
       <c r="O53" s="5" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A54" s="4" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="5" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A55" s="4" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="5" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A56" s="4" t="s">
+        <v>2081</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2083</v>
+      </c>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="5" t="s">
         <v>2082</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A55" s="1" t="s">
-        <v>1025</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>1026</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A57" s="1" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>2857</v>
-      </c>
-      <c r="O57" s="1" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="24.95" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>2888</v>
+        <v>1026</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A59" s="4"/>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="4"/>
-      <c r="L59" s="4"/>
-      <c r="M59" s="4"/>
-      <c r="N59" s="4"/>
-      <c r="O59" s="4"/>
-    </row>
-    <row r="60" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A60" s="4" t="s">
-        <v>2678</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>2858</v>
-      </c>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="4"/>
-      <c r="L60" s="4"/>
-      <c r="M60" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="N60" s="4"/>
-      <c r="O60" s="4" t="s">
-        <v>101</v>
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A60" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>2857</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>1029</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="24.95" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>2674</v>
+        <v>1030</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>2677</v>
+        <v>2888</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>2676</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A62" s="1" t="s">
-        <v>2675</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>1032</v>
-      </c>
-      <c r="O62" s="1" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A63" s="1" t="s">
-        <v>1034</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>1035</v>
-      </c>
-      <c r="O63" s="1" t="s">
-        <v>1036</v>
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A62" s="4"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
+    </row>
+    <row r="63" spans="1:15" s="6" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A63" s="4" t="s">
+        <v>2678</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>2858</v>
+      </c>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="24.95" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>1037</v>
+        <v>2674</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>1038</v>
+        <v>2677</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>1039</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="24.95" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>1040</v>
+        <v>2675</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>1041</v>
+        <v>1032</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>1042</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="24.95" customHeight="1">
       <c r="A66" s="1" t="s">
-        <v>1043</v>
+        <v>1034</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>1045</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="24.95" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>1046</v>
+        <v>1037</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>1047</v>
+        <v>1038</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>1048</v>
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A68" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>1042</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="24.95" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A71" s="1" t="s">
-        <v>2185</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>2197</v>
-      </c>
-      <c r="O71" s="1" t="s">
-        <v>2196</v>
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A70" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>1048</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="24.95" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>2186</v>
+        <v>1049</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>2198</v>
+        <v>1050</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>2195</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A73" s="1" t="s">
-        <v>2187</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>2199</v>
-      </c>
-      <c r="O73" s="1" t="s">
-        <v>2194</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="24.95" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>2188</v>
+        <v>2185</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>2200</v>
+        <v>2197</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>2193</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" ht="31.5">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" ht="24.95" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>2189</v>
+        <v>2186</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>2201</v>
+        <v>2198</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="24.95" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>2190</v>
+        <v>2187</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>2191</v>
+        <v>2199</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>2043</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" ht="24.95" customHeight="1">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A77" s="1" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>2200</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" ht="31.5">
       <c r="A78" s="1" t="s">
-        <v>2122</v>
+        <v>2189</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>2124</v>
+        <v>2201</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>2123</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="24.95" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>2178</v>
+        <v>2190</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>2889</v>
+        <v>2191</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>2179</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="81" spans="1:15" ht="24.95" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>1429</v>
+        <v>2122</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>3960</v>
+        <v>2124</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>1431</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A83" s="1" t="s">
-        <v>3839</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>3967</v>
-      </c>
-      <c r="O83" s="1" t="s">
-        <v>3840</v>
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A82" s="1" t="s">
+        <v>2178</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>2889</v>
+      </c>
+      <c r="O82" s="1" t="s">
+        <v>2179</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="24.95" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>3841</v>
+        <v>1429</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>3968</v>
+        <v>3960</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>3842</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A85" s="1" t="s">
-        <v>3848</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>3961</v>
-      </c>
-      <c r="O85" s="1" t="s">
-        <v>3851</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="86" spans="1:15" ht="24.95" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>3843</v>
+        <v>3839</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>3962</v>
+        <v>3967</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>3844</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="87" spans="1:15" ht="24.95" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>3845</v>
+        <v>3841</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>3963</v>
+        <v>3968</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>3852</v>
+        <v>3842</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="24.95" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>3846</v>
+        <v>3848</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>3965</v>
+        <v>3961</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>3849</v>
+        <v>3851</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="24.95" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>3847</v>
+        <v>3843</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>3964</v>
+        <v>3962</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>3850</v>
+        <v>3844</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A90" s="1" t="s">
+        <v>3845</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>3963</v>
+      </c>
+      <c r="O90" s="1" t="s">
+        <v>3852</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="24.95" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>3853</v>
+        <v>3846</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>3966</v>
+        <v>3965</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>3854</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="92" spans="1:15" ht="24.95" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>3855</v>
+        <v>3847</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>3975</v>
+        <v>3964</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>3859</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A93" s="1" t="s">
-        <v>3856</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>3969</v>
-      </c>
-      <c r="O93" s="1" t="s">
-        <v>3860</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="94" spans="1:15" ht="24.95" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>3857</v>
+        <v>3853</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>3976</v>
+        <v>3966</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>3861</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="95" spans="1:15" ht="24.95" customHeight="1">
       <c r="A95" s="1" t="s">
+        <v>3855</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>3975</v>
+      </c>
+      <c r="O95" s="1" t="s">
+        <v>3859</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A96" s="1" t="s">
+        <v>3856</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>3969</v>
+      </c>
+      <c r="O96" s="1" t="s">
+        <v>3860</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A97" s="1" t="s">
+        <v>3857</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>3976</v>
+      </c>
+      <c r="O97" s="1" t="s">
+        <v>3861</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A98" s="1" t="s">
         <v>3858</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B98" s="1" t="s">
         <v>3978</v>
       </c>
-      <c r="O95" s="16" t="s">
+      <c r="O98" s="16" t="s">
         <v>3977</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" ht="31.5">
-      <c r="A97" s="1" t="s">
-        <v>3863</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>3979</v>
-      </c>
-      <c r="O97" s="1" t="s">
-        <v>3872</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" ht="31.5">
-      <c r="A98" s="1" t="s">
-        <v>3864</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>3980</v>
-      </c>
-      <c r="O98" s="1" t="s">
-        <v>3873</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" ht="31.5">
-      <c r="A99" s="1" t="s">
-        <v>3865</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>3983</v>
-      </c>
-      <c r="O99" s="1" t="s">
-        <v>3874</v>
       </c>
     </row>
     <row r="100" spans="1:15" ht="31.5">
       <c r="A100" s="1" t="s">
-        <v>3875</v>
+        <v>3863</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>3982</v>
+        <v>3979</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>3878</v>
+        <v>3872</v>
       </c>
     </row>
     <row r="101" spans="1:15" ht="31.5">
       <c r="A101" s="1" t="s">
-        <v>3876</v>
+        <v>3864</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="O101" s="1" t="s">
-        <v>3879</v>
+        <v>3873</v>
       </c>
     </row>
     <row r="102" spans="1:15" ht="31.5">
       <c r="A102" s="1" t="s">
-        <v>3877</v>
+        <v>3865</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>3983</v>
       </c>
       <c r="O102" s="1" t="s">
+        <v>3874</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" ht="31.5">
+      <c r="A103" s="1" t="s">
+        <v>3875</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>3982</v>
+      </c>
+      <c r="O103" s="1" t="s">
+        <v>3878</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" ht="31.5">
+      <c r="A104" s="1" t="s">
+        <v>3876</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>3981</v>
+      </c>
+      <c r="O104" s="1" t="s">
+        <v>3879</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" ht="31.5">
+      <c r="A105" s="1" t="s">
+        <v>3877</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>3983</v>
+      </c>
+      <c r="O105" s="1" t="s">
         <v>3880</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A104" s="1" t="s">
-        <v>3881</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>3984</v>
-      </c>
-      <c r="O104" s="1" t="s">
-        <v>3883</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A105" s="1" t="s">
-        <v>3882</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>3985</v>
-      </c>
-      <c r="O105" s="1" t="s">
-        <v>3884</v>
       </c>
     </row>
     <row r="107" spans="1:15" ht="24.95" customHeight="1">
       <c r="A107" s="1" t="s">
-        <v>3885</v>
+        <v>3881</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>3986</v>
+        <v>3984</v>
       </c>
       <c r="O107" s="1" t="s">
-        <v>3886</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A109" s="1" t="s">
-        <v>3887</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>3988</v>
-      </c>
-      <c r="O109" s="1" t="s">
-        <v>3890</v>
+        <v>3883</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A108" s="1" t="s">
+        <v>3882</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>3985</v>
+      </c>
+      <c r="O108" s="1" t="s">
+        <v>3884</v>
       </c>
     </row>
     <row r="110" spans="1:15" ht="24.95" customHeight="1">
       <c r="A110" s="1" t="s">
-        <v>3888</v>
+        <v>3885</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>3987</v>
+        <v>3986</v>
       </c>
       <c r="O110" s="1" t="s">
-        <v>3889</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="112" spans="1:15" ht="24.95" customHeight="1">
       <c r="A112" s="1" t="s">
-        <v>3783</v>
+        <v>3887</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>3785</v>
+        <v>3988</v>
       </c>
       <c r="O112" s="1" t="s">
-        <v>3784</v>
+        <v>3890</v>
       </c>
     </row>
     <row r="113" spans="1:15" ht="24.95" customHeight="1">
       <c r="A113" s="1" t="s">
-        <v>3892</v>
+        <v>3888</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>3989</v>
+        <v>3987</v>
       </c>
       <c r="O113" s="1" t="s">
-        <v>3786</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15" ht="47.25">
-      <c r="A114" s="1" t="s">
-        <v>3787</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>3990</v>
-      </c>
-      <c r="O114" s="1" t="s">
-        <v>3793</v>
+        <v>3889</v>
       </c>
     </row>
     <row r="115" spans="1:15" ht="24.95" customHeight="1">
       <c r="A115" s="1" t="s">
+        <v>3783</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>3785</v>
+      </c>
+      <c r="O115" s="1" t="s">
+        <v>3784</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A116" s="1" t="s">
+        <v>3892</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>3989</v>
+      </c>
+      <c r="O116" s="1" t="s">
+        <v>3786</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" ht="47.25">
+      <c r="A117" s="1" t="s">
+        <v>3787</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>3990</v>
+      </c>
+      <c r="O117" s="1" t="s">
+        <v>3793</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A118" s="1" t="s">
         <v>3788</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B118" s="1" t="s">
         <v>3991</v>
       </c>
-      <c r="O115" s="1" t="s">
+      <c r="O118" s="1" t="s">
         <v>3891</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15" ht="31.5">
-      <c r="A117" s="1" t="s">
-        <v>3893</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>3995</v>
-      </c>
-      <c r="O117" s="1" t="s">
-        <v>3902</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" ht="31.5">
-      <c r="A118" s="1" t="s">
-        <v>3894</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>3996</v>
-      </c>
-      <c r="O118" s="1" t="s">
-        <v>3903</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15" ht="31.5">
-      <c r="A119" s="1" t="s">
-        <v>3895</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>3997</v>
-      </c>
-      <c r="O119" s="1" t="s">
-        <v>3904</v>
       </c>
     </row>
     <row r="120" spans="1:15" ht="31.5">
       <c r="A120" s="1" t="s">
-        <v>3896</v>
+        <v>3893</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>3998</v>
+        <v>3995</v>
       </c>
       <c r="O120" s="1" t="s">
-        <v>3905</v>
+        <v>3902</v>
       </c>
     </row>
     <row r="121" spans="1:15" ht="31.5">
       <c r="A121" s="1" t="s">
-        <v>3897</v>
+        <v>3894</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>3999</v>
+        <v>3996</v>
       </c>
       <c r="O121" s="1" t="s">
-        <v>3906</v>
+        <v>3903</v>
       </c>
     </row>
     <row r="122" spans="1:15" ht="31.5">
       <c r="A122" s="1" t="s">
-        <v>3898</v>
+        <v>3895</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>4000</v>
+        <v>3997</v>
       </c>
       <c r="O122" s="1" t="s">
-        <v>3907</v>
-      </c>
-    </row>
-    <row r="123" spans="1:15" ht="47.25">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" ht="31.5">
       <c r="A123" s="1" t="s">
-        <v>3899</v>
+        <v>3896</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>4001</v>
+        <v>3998</v>
       </c>
       <c r="O123" s="1" t="s">
-        <v>3908</v>
+        <v>3905</v>
       </c>
     </row>
     <row r="124" spans="1:15" ht="31.5">
       <c r="A124" s="1" t="s">
-        <v>3900</v>
+        <v>3897</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>4002</v>
+        <v>3999</v>
       </c>
       <c r="O124" s="1" t="s">
-        <v>3909</v>
+        <v>3906</v>
       </c>
     </row>
     <row r="125" spans="1:15" ht="31.5">
       <c r="A125" s="1" t="s">
+        <v>3898</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>4000</v>
+      </c>
+      <c r="O125" s="1" t="s">
+        <v>3907</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" ht="47.25">
+      <c r="A126" s="1" t="s">
+        <v>3899</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>4001</v>
+      </c>
+      <c r="O126" s="1" t="s">
+        <v>3908</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" ht="31.5">
+      <c r="A127" s="1" t="s">
+        <v>3900</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>4002</v>
+      </c>
+      <c r="O127" s="1" t="s">
+        <v>3909</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" ht="31.5">
+      <c r="A128" s="1" t="s">
         <v>3901</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B128" s="1" t="s">
         <v>4003</v>
       </c>
-      <c r="O125" s="1" t="s">
+      <c r="O128" s="1" t="s">
         <v>3910</v>
-      </c>
-    </row>
-    <row r="127" spans="1:15" ht="24" customHeight="1">
-      <c r="A127" s="1" t="s">
-        <v>3914</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>3992</v>
-      </c>
-      <c r="O127" s="1" t="s">
-        <v>3915</v>
-      </c>
-    </row>
-    <row r="128" spans="1:15" ht="24" customHeight="1">
-      <c r="A128" s="1" t="s">
-        <v>3911</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>3993</v>
-      </c>
-      <c r="O128" s="1" t="s">
-        <v>3916</v>
-      </c>
-    </row>
-    <row r="129" spans="1:15" ht="24" customHeight="1">
-      <c r="A129" s="1" t="s">
-        <v>3912</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>4004</v>
-      </c>
-      <c r="O129" s="1" t="s">
-        <v>3917</v>
       </c>
     </row>
     <row r="130" spans="1:15" ht="24" customHeight="1">
       <c r="A130" s="1" t="s">
-        <v>3913</v>
+        <v>3914</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>3994</v>
+        <v>3992</v>
       </c>
       <c r="O130" s="1" t="s">
-        <v>3918</v>
-      </c>
-    </row>
-    <row r="131" spans="1:15" ht="24" customHeight="1"/>
+        <v>3915</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" ht="24" customHeight="1">
+      <c r="A131" s="1" t="s">
+        <v>3911</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>3993</v>
+      </c>
+      <c r="O131" s="1" t="s">
+        <v>3916</v>
+      </c>
+    </row>
     <row r="132" spans="1:15" ht="24" customHeight="1">
       <c r="A132" s="1" t="s">
-        <v>3923</v>
+        <v>3912</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="O132" s="1" t="s">
-        <v>3924</v>
-      </c>
-    </row>
-    <row r="133" spans="1:15" ht="24" customHeight="1"/>
-    <row r="134" spans="1:15" ht="24" customHeight="1">
-      <c r="A134" s="1" t="s">
-        <v>3931</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>4006</v>
-      </c>
-      <c r="O134" s="1" t="s">
-        <v>3934</v>
-      </c>
-    </row>
+        <v>3917</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" ht="24" customHeight="1">
+      <c r="A133" s="1" t="s">
+        <v>3913</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>3994</v>
+      </c>
+      <c r="O133" s="1" t="s">
+        <v>3918</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" ht="24" customHeight="1"/>
     <row r="135" spans="1:15" ht="24" customHeight="1">
       <c r="A135" s="1" t="s">
-        <v>3932</v>
+        <v>3923</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>4007</v>
+        <v>4005</v>
       </c>
       <c r="O135" s="1" t="s">
-        <v>3935</v>
-      </c>
-    </row>
-    <row r="136" spans="1:15" ht="24" customHeight="1">
-      <c r="A136" s="1" t="s">
-        <v>3933</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>4017</v>
-      </c>
-      <c r="O136" s="1" t="s">
-        <v>4016</v>
-      </c>
-    </row>
-    <row r="137" spans="1:15" ht="24" customHeight="1"/>
+        <v>3924</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" ht="24" customHeight="1"/>
+    <row r="137" spans="1:15" ht="24" customHeight="1">
+      <c r="A137" s="1" t="s">
+        <v>3931</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>4006</v>
+      </c>
+      <c r="O137" s="1" t="s">
+        <v>3934</v>
+      </c>
+    </row>
     <row r="138" spans="1:15" ht="24" customHeight="1">
       <c r="A138" s="1" t="s">
-        <v>3936</v>
+        <v>3932</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="O138" s="1" t="s">
-        <v>3939</v>
+        <v>3935</v>
       </c>
     </row>
     <row r="139" spans="1:15" ht="24" customHeight="1">
       <c r="A139" s="1" t="s">
+        <v>3933</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>4017</v>
+      </c>
+      <c r="O139" s="1" t="s">
+        <v>4016</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" ht="24" customHeight="1"/>
+    <row r="141" spans="1:15" ht="24" customHeight="1">
+      <c r="A141" s="1" t="s">
+        <v>3936</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>4008</v>
+      </c>
+      <c r="O141" s="1" t="s">
+        <v>3939</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" ht="24" customHeight="1">
+      <c r="A142" s="1" t="s">
         <v>3937</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B142" s="1" t="s">
         <v>4009</v>
       </c>
-      <c r="O139" s="1" t="s">
+      <c r="O142" s="1" t="s">
         <v>3940</v>
       </c>
     </row>
-    <row r="140" spans="1:15" ht="24" customHeight="1">
-      <c r="A140" s="1" t="s">
+    <row r="143" spans="1:15" ht="24" customHeight="1">
+      <c r="A143" s="1" t="s">
         <v>3938</v>
       </c>
-      <c r="B140" s="17" t="s">
+      <c r="B143" s="17" t="s">
         <v>4010</v>
       </c>
-      <c r="O140" s="1" t="s">
+      <c r="O143" s="1" t="s">
         <v>3941</v>
       </c>
     </row>
-    <row r="141" spans="1:15" ht="24" customHeight="1"/>
-    <row r="142" spans="1:15" ht="24" customHeight="1"/>
-    <row r="143" spans="1:15" ht="24" customHeight="1"/>
     <row r="144" spans="1:15" ht="24" customHeight="1"/>
-    <row r="146" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A146" s="1" t="s">
-        <v>3919</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>3921</v>
-      </c>
-      <c r="O146" s="1" t="s">
-        <v>3920</v>
-      </c>
-    </row>
-    <row r="147" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A147" s="1" t="s">
-        <v>3922</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>4012</v>
-      </c>
-      <c r="O147" s="1" t="s">
-        <v>4011</v>
-      </c>
-    </row>
+    <row r="145" spans="1:15" ht="24" customHeight="1"/>
+    <row r="146" spans="1:15" ht="24" customHeight="1"/>
+    <row r="147" spans="1:15" ht="24" customHeight="1"/>
     <row r="149" spans="1:15" ht="24.95" customHeight="1">
       <c r="A149" s="1" t="s">
-        <v>3925</v>
+        <v>3919</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>4014</v>
+        <v>3921</v>
       </c>
       <c r="O149" s="1" t="s">
-        <v>3927</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="150" spans="1:15" ht="24.95" customHeight="1">
       <c r="A150" s="1" t="s">
-        <v>3926</v>
+        <v>3922</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="O150" s="1" t="s">
-        <v>3928</v>
-      </c>
-    </row>
-    <row r="151" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A151" s="1" t="s">
-        <v>3929</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>4015</v>
-      </c>
-      <c r="O151" s="1" t="s">
-        <v>3930</v>
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A152" s="1" t="s">
+        <v>3925</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>4014</v>
+      </c>
+      <c r="O152" s="1" t="s">
+        <v>3927</v>
       </c>
     </row>
     <row r="153" spans="1:15" ht="24.95" customHeight="1">
       <c r="A153" s="1" t="s">
-        <v>1330</v>
+        <v>3926</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>2890</v>
+        <v>4013</v>
       </c>
       <c r="O153" s="1" t="s">
-        <v>1052</v>
+        <v>3928</v>
       </c>
     </row>
     <row r="154" spans="1:15" ht="24.95" customHeight="1">
       <c r="A154" s="1" t="s">
-        <v>1053</v>
+        <v>3929</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>1054</v>
+        <v>4015</v>
       </c>
       <c r="O154" s="1" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="155" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A155" s="1" t="s">
-        <v>1056</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>1057</v>
-      </c>
-      <c r="O155" s="1" t="s">
-        <v>1058</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="156" spans="1:15" ht="24.95" customHeight="1">
       <c r="A156" s="1" t="s">
-        <v>1059</v>
+        <v>1330</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="O156" s="1" t="s">
-        <v>1060</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="157" spans="1:15" ht="24.95" customHeight="1">
       <c r="A157" s="1" t="s">
-        <v>2089</v>
+        <v>1053</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>2892</v>
+        <v>1054</v>
       </c>
       <c r="O157" s="1" t="s">
-        <v>2090</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="158" spans="1:15" ht="24.95" customHeight="1">
       <c r="A158" s="1" t="s">
-        <v>2133</v>
+        <v>1056</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>3174</v>
+        <v>1057</v>
       </c>
       <c r="O158" s="1" t="s">
-        <v>2134</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="159" spans="1:15" ht="24.95" customHeight="1">
       <c r="A159" s="1" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>2893</v>
+        <v>2891</v>
       </c>
       <c r="O159" s="1" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="160" spans="1:15" ht="24.95" customHeight="1">
       <c r="A160" s="1" t="s">
-        <v>2490</v>
+        <v>2089</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>2894</v>
+        <v>2892</v>
       </c>
       <c r="O160" s="1" t="s">
-        <v>2489</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="161" spans="1:15" ht="24.95" customHeight="1">
       <c r="A161" s="1" t="s">
-        <v>2492</v>
+        <v>2133</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>2859</v>
+        <v>3174</v>
       </c>
       <c r="O161" s="1" t="s">
-        <v>2571</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="162" spans="1:15" ht="24.95" customHeight="1">
       <c r="A162" s="1" t="s">
-        <v>2491</v>
+        <v>1061</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>2895</v>
+        <v>2893</v>
       </c>
       <c r="O162" s="1" t="s">
-        <v>2494</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="163" spans="1:15" ht="24.95" customHeight="1">
       <c r="A163" s="1" t="s">
-        <v>2365</v>
+        <v>2490</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>3401</v>
+        <v>2894</v>
       </c>
       <c r="O163" s="1" t="s">
-        <v>2368</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="164" spans="1:15" ht="24.95" customHeight="1">
       <c r="A164" s="1" t="s">
-        <v>2763</v>
+        <v>2492</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="O164" s="1" t="s">
-        <v>2765</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="165" spans="1:15" ht="24.95" customHeight="1">
       <c r="A165" s="1" t="s">
-        <v>2764</v>
+        <v>2491</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>2861</v>
+        <v>2895</v>
       </c>
       <c r="O165" s="1" t="s">
-        <v>2766</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="166" spans="1:15" ht="24.95" customHeight="1">
       <c r="A166" s="1" t="s">
-        <v>3772</v>
+        <v>2365</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>3401</v>
       </c>
       <c r="O166" s="1" t="s">
-        <v>3773</v>
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A167" s="1" t="s">
+        <v>2763</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>2860</v>
+      </c>
+      <c r="O167" s="1" t="s">
+        <v>2765</v>
       </c>
     </row>
     <row r="168" spans="1:15" ht="24.95" customHeight="1">
       <c r="A168" s="1" t="s">
-        <v>2742</v>
+        <v>2764</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
       <c r="O168" s="1" t="s">
-        <v>2741</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="169" spans="1:15" ht="24.95" customHeight="1">
       <c r="A169" s="1" t="s">
-        <v>2745</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>2863</v>
+        <v>3772</v>
       </c>
       <c r="O169" s="1" t="s">
-        <v>2759</v>
+        <v>3773</v>
       </c>
     </row>
     <row r="171" spans="1:15" ht="24.95" customHeight="1">
       <c r="A171" s="1" t="s">
-        <v>2152</v>
+        <v>2742</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>2153</v>
+        <v>2862</v>
       </c>
       <c r="O171" s="1" t="s">
-        <v>2154</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="172" spans="1:15" ht="24.95" customHeight="1">
       <c r="A172" s="1" t="s">
-        <v>2156</v>
+        <v>2745</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>2155</v>
+        <v>2863</v>
       </c>
       <c r="O172" s="1" t="s">
-        <v>2761</v>
-      </c>
-    </row>
-    <row r="173" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A173" s="1" t="s">
-        <v>3862</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>2864</v>
-      </c>
-      <c r="O173" s="1" t="s">
-        <v>2157</v>
+        <v>2759</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A174" s="1" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>2153</v>
+      </c>
+      <c r="O174" s="1" t="s">
+        <v>2154</v>
       </c>
     </row>
     <row r="175" spans="1:15" ht="24.95" customHeight="1">
       <c r="A175" s="1" t="s">
-        <v>2509</v>
+        <v>2156</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>2865</v>
+        <v>2155</v>
       </c>
       <c r="O175" s="1" t="s">
-        <v>2539</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="176" spans="1:15" ht="24.95" customHeight="1">
       <c r="A176" s="1" t="s">
-        <v>2510</v>
+        <v>3862</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>2866</v>
+        <v>2864</v>
       </c>
       <c r="O176" s="1" t="s">
-        <v>2538</v>
-      </c>
-    </row>
-    <row r="177" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A177" s="1" t="s">
-        <v>2751</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>2871</v>
-      </c>
-      <c r="O177" s="1" t="s">
-        <v>2753</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="178" spans="1:15" ht="24.95" customHeight="1">
       <c r="A178" s="1" t="s">
-        <v>2752</v>
+        <v>2509</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>2872</v>
+        <v>2865</v>
       </c>
       <c r="O178" s="1" t="s">
-        <v>2754</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="179" spans="1:15" ht="24.95" customHeight="1">
       <c r="A179" s="1" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="O179" s="1" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="180" spans="1:15" ht="24.95" customHeight="1">
       <c r="A180" s="1" t="s">
-        <v>2512</v>
+        <v>2751</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>2873</v>
+        <v>2871</v>
       </c>
       <c r="O180" s="1" t="s">
-        <v>2536</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="181" spans="1:15" ht="24.95" customHeight="1">
       <c r="A181" s="1" t="s">
-        <v>2513</v>
+        <v>2752</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>2874</v>
+        <v>2872</v>
       </c>
       <c r="O181" s="1" t="s">
-        <v>2535</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="182" spans="1:15" ht="24.95" customHeight="1">
       <c r="A182" s="1" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="O182" s="1" t="s">
-        <v>2534</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="183" spans="1:15" ht="24.95" customHeight="1">
       <c r="A183" s="1" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>2877</v>
+        <v>2873</v>
       </c>
       <c r="O183" s="1" t="s">
-        <v>2533</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="184" spans="1:15" ht="24.95" customHeight="1">
       <c r="A184" s="1" t="s">
-        <v>2591</v>
+        <v>2513</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>2876</v>
+        <v>2874</v>
       </c>
       <c r="O184" s="1" t="s">
-        <v>2592</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="185" spans="1:15" ht="24.95" customHeight="1">
       <c r="A185" s="1" t="s">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>2875</v>
+        <v>2868</v>
       </c>
       <c r="O185" s="1" t="s">
-        <v>2532</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="186" spans="1:15" ht="24.95" customHeight="1">
       <c r="A186" s="1" t="s">
-        <v>2517</v>
+        <v>2515</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>2869</v>
+        <v>2877</v>
       </c>
       <c r="O186" s="1" t="s">
-        <v>2531</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="187" spans="1:15" ht="24.95" customHeight="1">
       <c r="A187" s="1" t="s">
-        <v>2518</v>
+        <v>2591</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>2878</v>
+        <v>2876</v>
       </c>
       <c r="O187" s="1" t="s">
-        <v>2530</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="188" spans="1:15" ht="24.95" customHeight="1">
       <c r="A188" s="1" t="s">
-        <v>2519</v>
+        <v>2516</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>3014</v>
+        <v>2875</v>
       </c>
       <c r="O188" s="1" t="s">
-        <v>2546</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="189" spans="1:15" ht="24.95" customHeight="1">
       <c r="A189" s="1" t="s">
-        <v>2520</v>
+        <v>2517</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>2879</v>
+        <v>2869</v>
       </c>
       <c r="O189" s="1" t="s">
-        <v>2545</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="190" spans="1:15" ht="24.95" customHeight="1">
       <c r="A190" s="1" t="s">
-        <v>2521</v>
+        <v>2518</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>2880</v>
+        <v>2878</v>
       </c>
       <c r="O190" s="1" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="191" spans="1:15" ht="24.95" customHeight="1">
       <c r="A191" s="1" t="s">
-        <v>2522</v>
+        <v>2519</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>2881</v>
+        <v>3014</v>
       </c>
       <c r="O191" s="1" t="s">
-        <v>2544</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="192" spans="1:15" ht="24.95" customHeight="1">
       <c r="A192" s="1" t="s">
-        <v>2523</v>
+        <v>2520</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>2882</v>
+        <v>2879</v>
       </c>
       <c r="O192" s="1" t="s">
-        <v>2543</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="193" spans="1:15" ht="24.95" customHeight="1">
       <c r="A193" s="1" t="s">
-        <v>2524</v>
+        <v>2521</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>2896</v>
+        <v>2880</v>
       </c>
       <c r="O193" s="1" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="194" spans="1:15" ht="24.95" customHeight="1">
       <c r="A194" s="1" t="s">
-        <v>2525</v>
+        <v>2522</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>2935</v>
+        <v>2881</v>
       </c>
       <c r="O194" s="1" t="s">
-        <v>2542</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="195" spans="1:15" ht="24.95" customHeight="1">
       <c r="A195" s="1" t="s">
-        <v>2526</v>
+        <v>2523</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
       <c r="O195" s="1" t="s">
-        <v>2540</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="196" spans="1:15" ht="24.95" customHeight="1">
       <c r="A196" s="1" t="s">
-        <v>2527</v>
+        <v>2524</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>2884</v>
+        <v>2896</v>
       </c>
       <c r="O196" s="1" t="s">
-        <v>2541</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="197" spans="1:15" ht="24.95" customHeight="1">
       <c r="A197" s="1" t="s">
-        <v>2547</v>
+        <v>2525</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>2885</v>
+        <v>2935</v>
       </c>
       <c r="O197" s="1" t="s">
-        <v>2548</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="198" spans="1:15" ht="24.95" customHeight="1">
       <c r="A198" s="1" t="s">
-        <v>2549</v>
+        <v>2526</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>2870</v>
+        <v>2883</v>
       </c>
       <c r="O198" s="1" t="s">
-        <v>2550</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="199" spans="1:15" ht="24.95" customHeight="1">
       <c r="A199" s="1" t="s">
-        <v>2551</v>
+        <v>2527</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>2997</v>
+        <v>2884</v>
       </c>
       <c r="O199" s="1" t="s">
-        <v>2552</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="200" spans="1:15" ht="24.95" customHeight="1">
       <c r="A200" s="1" t="s">
-        <v>2744</v>
+        <v>2547</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>2998</v>
+        <v>2885</v>
       </c>
       <c r="O200" s="1" t="s">
-        <v>2743</v>
+        <v>2548</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A201" s="1" t="s">
+        <v>2549</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>2870</v>
+      </c>
+      <c r="O201" s="1" t="s">
+        <v>2550</v>
       </c>
     </row>
     <row r="202" spans="1:15" ht="24.95" customHeight="1">
       <c r="A202" s="1" t="s">
-        <v>2704</v>
+        <v>2551</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>2897</v>
+        <v>2997</v>
       </c>
       <c r="O202" s="1" t="s">
-        <v>2705</v>
-      </c>
-    </row>
-    <row r="203" spans="1:15" ht="94.5">
+        <v>2552</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" ht="24.95" customHeight="1">
       <c r="A203" s="1" t="s">
-        <v>2723</v>
+        <v>2744</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>2898</v>
+        <v>2998</v>
       </c>
       <c r="O203" s="1" t="s">
-        <v>2703</v>
-      </c>
-    </row>
-    <row r="204" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A204" s="1" t="s">
-        <v>2680</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>2702</v>
-      </c>
-      <c r="O204" s="1" t="s">
-        <v>2701</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="205" spans="1:15" ht="24.95" customHeight="1">
       <c r="A205" s="1" t="s">
-        <v>2681</v>
+        <v>2704</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>2854</v>
+        <v>2897</v>
       </c>
       <c r="O205" s="1" t="s">
-        <v>2726</v>
-      </c>
-    </row>
-    <row r="206" spans="1:15" ht="24.95" customHeight="1">
+        <v>2705</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" ht="94.5">
       <c r="A206" s="1" t="s">
-        <v>2724</v>
+        <v>2723</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>2725</v>
+        <v>2898</v>
       </c>
       <c r="O206" s="1" t="s">
-        <v>2727</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="207" spans="1:15" ht="24.95" customHeight="1">
       <c r="A207" s="1" t="s">
-        <v>2682</v>
+        <v>2680</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>2679</v>
+        <v>2702</v>
       </c>
       <c r="O207" s="1" t="s">
-        <v>2700</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="208" spans="1:15" ht="24.95" customHeight="1">
       <c r="A208" s="1" t="s">
-        <v>2698</v>
+        <v>2681</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>2899</v>
+        <v>2854</v>
       </c>
       <c r="O208" s="1" t="s">
-        <v>2699</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="209" spans="1:15" ht="24.95" customHeight="1">
       <c r="A209" s="1" t="s">
-        <v>2707</v>
+        <v>2724</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>2706</v>
+        <v>2725</v>
       </c>
       <c r="O209" s="1" t="s">
-        <v>2710</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="210" spans="1:15" ht="24.95" customHeight="1">
       <c r="A210" s="1" t="s">
-        <v>2708</v>
+        <v>2682</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>2709</v>
+        <v>2679</v>
       </c>
       <c r="O210" s="1" t="s">
-        <v>2711</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="211" spans="1:15" ht="24.95" customHeight="1">
       <c r="A211" s="1" t="s">
-        <v>2715</v>
+        <v>2698</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>2716</v>
+        <v>2899</v>
       </c>
       <c r="O211" s="1" t="s">
-        <v>2165</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="212" spans="1:15" ht="24.95" customHeight="1">
       <c r="A212" s="1" t="s">
-        <v>2721</v>
+        <v>2707</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>2717</v>
+        <v>2706</v>
       </c>
       <c r="O212" s="1" t="s">
-        <v>1502</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="213" spans="1:15" ht="24.95" customHeight="1">
       <c r="A213" s="1" t="s">
-        <v>2720</v>
+        <v>2708</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>2855</v>
+        <v>2709</v>
       </c>
       <c r="O213" s="1" t="s">
-        <v>2722</v>
+        <v>2711</v>
       </c>
     </row>
     <row r="214" spans="1:15" ht="24.95" customHeight="1">
       <c r="A214" s="1" t="s">
+        <v>2715</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>2716</v>
+      </c>
+      <c r="O214" s="1" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A215" s="1" t="s">
+        <v>2721</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>2717</v>
+      </c>
+      <c r="O215" s="1" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A216" s="1" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>2855</v>
+      </c>
+      <c r="O216" s="1" t="s">
+        <v>2722</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A217" s="1" t="s">
         <v>2698</v>
       </c>
-      <c r="B214" s="1" t="s">
+      <c r="B217" s="1" t="s">
         <v>2718</v>
       </c>
-      <c r="O214" s="1" t="s">
+      <c r="O217" s="1" t="s">
         <v>2719</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19410" windowHeight="11610" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19410" windowHeight="11610" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Options" sheetId="3" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="Role Description" sheetId="11" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Options!$O$1:$O$1490</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Options!$O$1:$O$1491</definedName>
   </definedNames>
   <calcPr calcId="145621"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4544" uniqueCount="4275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4546" uniqueCount="4277">
   <si>
     <t>English</t>
   </si>
@@ -16386,6 +16386,14 @@
   </si>
   <si>
     <t>Change Ability</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>marionetteMonitoringCanMove</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>监视木偶时玩家还可以移动</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -17008,7 +17016,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q1787"/>
+  <dimension ref="A1:Q1788"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40.375" style="2" customWidth="1"/>
@@ -20369,4251 +20377,4256 @@
         <v>4271</v>
       </c>
     </row>
-    <row r="332" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A332" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="B332" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="O332" s="4" t="s">
-        <v>464</v>
+    <row r="331" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A331" s="2" t="s">
+        <v>4275</v>
+      </c>
+      <c r="O331" s="4" t="s">
+        <v>4276</v>
       </c>
     </row>
     <row r="333" spans="1:15" ht="24.95" customHeight="1">
       <c r="A333" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>3262</v>
-      </c>
-      <c r="O333" s="3" t="s">
-        <v>466</v>
+        <v>463</v>
+      </c>
+      <c r="O333" s="4" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="334" spans="1:15" ht="24.95" customHeight="1">
       <c r="A334" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B334" s="2" t="s">
+        <v>3262</v>
+      </c>
+      <c r="O334" s="3" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="335" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A335" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="B334" s="2" t="s">
+      <c r="B335" s="2" t="s">
         <v>3253</v>
       </c>
-      <c r="O334" s="4" t="s">
+      <c r="O335" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="335" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O335" s="2"/>
-    </row>
     <row r="336" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A336" s="2" t="s">
+      <c r="O336" s="2"/>
+    </row>
+    <row r="337" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A337" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="B336" s="2" t="s">
+      <c r="B337" s="2" t="s">
         <v>3254</v>
       </c>
-      <c r="O336" s="3" t="s">
+      <c r="O337" s="3" t="s">
         <v>470</v>
-      </c>
-    </row>
-    <row r="338" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A338" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="B338" s="2" t="s">
-        <v>3263</v>
-      </c>
-      <c r="O338" s="3" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="339" spans="1:15" ht="24.95" customHeight="1">
       <c r="A339" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>3263</v>
+      </c>
+      <c r="O339" s="3" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="340" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A340" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B339" s="2" t="s">
+      <c r="B340" s="2" t="s">
         <v>3256</v>
       </c>
-      <c r="O339" s="3" t="s">
+      <c r="O340" s="3" t="s">
         <v>474</v>
-      </c>
-    </row>
-    <row r="341" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A341" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="B341" s="2" t="s">
-        <v>3258</v>
-      </c>
-      <c r="O341" s="3" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="342" spans="1:15" ht="24.95" customHeight="1">
       <c r="A342" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>3268</v>
+        <v>3258</v>
       </c>
       <c r="O342" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="343" spans="1:15" ht="24.95" customHeight="1">
       <c r="A343" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>3264</v>
+        <v>3268</v>
       </c>
       <c r="O343" s="3" t="s">
-        <v>2691</v>
+        <v>478</v>
       </c>
     </row>
     <row r="344" spans="1:15" ht="24.95" customHeight="1">
       <c r="A344" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="O344" s="3" t="s">
-        <v>481</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="345" spans="1:15" ht="24.95" customHeight="1">
       <c r="A345" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
       <c r="O345" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="346" spans="1:15" ht="24.95" customHeight="1">
       <c r="A346" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>3266</v>
+      </c>
+      <c r="O346" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="347" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A347" s="2" t="s">
         <v>2687</v>
       </c>
-      <c r="B346" s="2" t="s">
+      <c r="B347" s="2" t="s">
         <v>3267</v>
       </c>
-      <c r="O346" s="3" t="s">
+      <c r="O347" s="3" t="s">
         <v>2688</v>
-      </c>
-    </row>
-    <row r="348" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A348" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="B348" s="2" t="s">
-        <v>3273</v>
-      </c>
-      <c r="O348" s="3" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="349" spans="1:15" ht="24.95" customHeight="1">
       <c r="A349" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>3272</v>
+        <v>3273</v>
       </c>
       <c r="O349" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="350" spans="1:15" ht="24.95" customHeight="1">
       <c r="A350" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>3271</v>
-      </c>
-      <c r="O350" s="4" t="s">
-        <v>489</v>
+        <v>3272</v>
+      </c>
+      <c r="O350" s="3" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="351" spans="1:15" ht="24.95" customHeight="1">
       <c r="A351" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>3269</v>
-      </c>
-      <c r="O351" s="2" t="s">
-        <v>491</v>
+        <v>3271</v>
+      </c>
+      <c r="O351" s="4" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="352" spans="1:15" ht="24.95" customHeight="1">
       <c r="A352" s="2" t="s">
-        <v>2002</v>
+        <v>490</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>3255</v>
+        <v>3269</v>
       </c>
       <c r="O352" s="2" t="s">
-        <v>2005</v>
+        <v>491</v>
       </c>
     </row>
     <row r="353" spans="1:15" ht="24.95" customHeight="1">
       <c r="A353" s="2" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>3255</v>
+      </c>
+      <c r="O353" s="2" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="354" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A354" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="B353" s="2" t="s">
+      <c r="B354" s="2" t="s">
         <v>3270</v>
       </c>
-      <c r="O353" s="2" t="s">
+      <c r="O354" s="2" t="s">
         <v>2376</v>
       </c>
     </row>
-    <row r="354" spans="1:15" ht="24.95" customHeight="1">
-      <c r="B354" s="3"/>
-      <c r="M354" s="3"/>
-    </row>
     <row r="355" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A355" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="B355" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="O355" s="2" t="s">
-        <v>495</v>
-      </c>
+      <c r="B355" s="3"/>
+      <c r="M355" s="3"/>
     </row>
     <row r="356" spans="1:15" ht="24.95" customHeight="1">
       <c r="A356" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="B356" s="3" t="s">
-        <v>3274</v>
-      </c>
-      <c r="M356" s="3"/>
-      <c r="O356" s="3" t="s">
-        <v>497</v>
+        <v>493</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="O356" s="2" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="357" spans="1:15" ht="24.95" customHeight="1">
       <c r="A357" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="B357" s="2" t="s">
-        <v>3306</v>
-      </c>
-      <c r="O357" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
+      </c>
+      <c r="B357" s="3" t="s">
+        <v>3274</v>
+      </c>
+      <c r="M357" s="3"/>
+      <c r="O357" s="3" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="358" spans="1:15" ht="24.95" customHeight="1">
       <c r="A358" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>3275</v>
+        <v>3306</v>
       </c>
       <c r="O358" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="359" spans="1:15" ht="24.95" customHeight="1">
       <c r="A359" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>3275</v>
+      </c>
+      <c r="O359" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="360" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A360" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B359" s="2" t="s">
+      <c r="B360" s="2" t="s">
         <v>3307</v>
       </c>
-      <c r="O359" s="2" t="s">
+      <c r="O360" s="2" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="360" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O360" s="2"/>
-    </row>
     <row r="361" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A361" s="2" t="s">
+      <c r="O361" s="2"/>
+    </row>
+    <row r="362" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A362" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="B361" s="2" t="s">
+      <c r="B362" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="O361" s="2" t="s">
+      <c r="O362" s="2" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="362" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O362" s="2"/>
-    </row>
     <row r="363" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A363" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="B363" s="2" t="s">
-        <v>3276</v>
-      </c>
-      <c r="O363" s="2" t="s">
-        <v>508</v>
-      </c>
+      <c r="O363" s="2"/>
     </row>
     <row r="364" spans="1:15" ht="24.95" customHeight="1">
       <c r="A364" s="2" t="s">
-        <v>2080</v>
+        <v>507</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>3308</v>
+        <v>3276</v>
       </c>
       <c r="O364" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="365" spans="1:15" ht="24.95" customHeight="1">
       <c r="A365" s="2" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>3277</v>
-      </c>
-      <c r="O365" s="3" t="s">
-        <v>510</v>
+        <v>3308</v>
+      </c>
+      <c r="O365" s="2" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="366" spans="1:15" ht="24.95" customHeight="1">
       <c r="A366" s="2" t="s">
-        <v>511</v>
+        <v>2079</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="O366" s="2" t="s">
-        <v>513</v>
+        <v>3277</v>
+      </c>
+      <c r="O366" s="3" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="367" spans="1:15" ht="24.95" customHeight="1">
       <c r="A367" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>3278</v>
+        <v>512</v>
       </c>
       <c r="O367" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="368" spans="1:15" ht="24.95" customHeight="1">
       <c r="A368" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>3278</v>
+      </c>
+      <c r="O368" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="369" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A369" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="B368" s="2" t="s">
+      <c r="B369" s="2" t="s">
         <v>3279</v>
       </c>
-      <c r="O368" s="2" t="s">
+      <c r="O369" s="2" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="369" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O369" s="2"/>
-    </row>
     <row r="370" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A370" s="2" t="s">
+      <c r="O370" s="2"/>
+    </row>
+    <row r="371" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A371" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="B370" s="2" t="s">
+      <c r="B371" s="2" t="s">
         <v>3309</v>
       </c>
-      <c r="O370" s="2" t="s">
+      <c r="O371" s="2" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="371" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O371" s="2"/>
-    </row>
     <row r="372" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A372" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="B372" s="2" t="s">
-        <v>3310</v>
-      </c>
-      <c r="O372" s="2" t="s">
-        <v>495</v>
-      </c>
+      <c r="O372" s="2"/>
     </row>
     <row r="373" spans="1:15" ht="24.95" customHeight="1">
       <c r="A373" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>3280</v>
+        <v>3310</v>
       </c>
       <c r="O373" s="2" t="s">
-        <v>521</v>
+        <v>495</v>
       </c>
     </row>
     <row r="374" spans="1:15" ht="24.95" customHeight="1">
       <c r="A374" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>3311</v>
+        <v>3280</v>
       </c>
       <c r="O374" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="375" spans="1:15" ht="24.95" customHeight="1">
       <c r="A375" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>3281</v>
+        <v>3311</v>
       </c>
       <c r="O375" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="376" spans="1:15" ht="24.95" customHeight="1">
       <c r="A376" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>527</v>
+        <v>3281</v>
       </c>
       <c r="O376" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="377" spans="1:15" ht="24.95" customHeight="1">
       <c r="A377" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B377" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="O377" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="378" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A378" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="B377" s="2" t="s">
+      <c r="B378" s="2" t="s">
         <v>3282</v>
       </c>
-      <c r="O377" s="2" t="s">
+      <c r="O378" s="2" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="378" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O378" s="2"/>
-    </row>
     <row r="379" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A379" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="B379" s="2" t="s">
-        <v>3312</v>
-      </c>
-      <c r="O379" s="2" t="s">
-        <v>532</v>
-      </c>
+      <c r="O379" s="2"/>
     </row>
     <row r="380" spans="1:15" ht="24.95" customHeight="1">
       <c r="A380" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>3283</v>
+        <v>3312</v>
       </c>
       <c r="O380" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="381" spans="1:15" ht="24.95" customHeight="1">
       <c r="A381" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="O381" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="382" spans="1:15" ht="24.95" customHeight="1">
       <c r="A382" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>3313</v>
+        <v>3284</v>
       </c>
       <c r="O382" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="383" spans="1:15" ht="24.95" customHeight="1">
       <c r="A383" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="O383" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="384" spans="1:15" ht="24.95" customHeight="1">
       <c r="A384" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
       <c r="O384" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="385" spans="1:15" ht="24.95" customHeight="1">
       <c r="A385" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>3285</v>
+        <v>3315</v>
       </c>
       <c r="O385" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="386" spans="1:15" ht="24.95" customHeight="1">
       <c r="A386" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B386" s="2" t="s">
+        <v>3285</v>
+      </c>
+      <c r="O386" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="387" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A387" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="B386" s="2" t="s">
+      <c r="B387" s="2" t="s">
         <v>3316</v>
       </c>
-      <c r="O386" s="2" t="s">
+      <c r="O387" s="2" t="s">
         <v>546</v>
-      </c>
-    </row>
-    <row r="388" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A388" s="2" t="s">
-        <v>1831</v>
-      </c>
-      <c r="B388" s="2" t="s">
-        <v>3286</v>
-      </c>
-      <c r="O388" s="3" t="s">
-        <v>1836</v>
       </c>
     </row>
     <row r="389" spans="1:15" ht="24.95" customHeight="1">
       <c r="A389" s="2" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>1837</v>
-      </c>
-      <c r="O389" s="2" t="s">
-        <v>1835</v>
+        <v>3286</v>
+      </c>
+      <c r="O389" s="3" t="s">
+        <v>1836</v>
       </c>
     </row>
     <row r="390" spans="1:15" ht="24.95" customHeight="1">
       <c r="A390" s="2" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B390" s="2" t="s">
+        <v>1837</v>
+      </c>
+      <c r="O390" s="2" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="391" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A391" s="2" t="s">
         <v>1833</v>
       </c>
-      <c r="B390" s="2" t="s">
+      <c r="B391" s="2" t="s">
         <v>3287</v>
       </c>
-      <c r="O390" s="2" t="s">
+      <c r="O391" s="2" t="s">
         <v>1834</v>
       </c>
     </row>
-    <row r="391" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O391" s="2"/>
-    </row>
     <row r="392" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A392" s="2" t="s">
-        <v>2098</v>
-      </c>
-      <c r="B392" s="2" t="s">
-        <v>2091</v>
-      </c>
-      <c r="O392" s="2" t="s">
-        <v>2093</v>
-      </c>
+      <c r="O392" s="2"/>
     </row>
     <row r="393" spans="1:15" ht="24.95" customHeight="1">
       <c r="A393" s="2" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>3288</v>
+        <v>2091</v>
       </c>
       <c r="O393" s="2" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="394" spans="1:15" ht="24.95" customHeight="1">
       <c r="A394" s="2" t="s">
-        <v>2090</v>
+        <v>2097</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="O394" s="2" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="395" spans="1:15" ht="24.95" customHeight="1">
       <c r="A395" s="2" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>3317</v>
+        <v>3289</v>
       </c>
       <c r="O395" s="2" t="s">
-        <v>2088</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="396" spans="1:15" ht="24.95" customHeight="1">
       <c r="A396" s="2" t="s">
-        <v>2095</v>
+        <v>2089</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>3291</v>
+        <v>3317</v>
       </c>
       <c r="O396" s="2" t="s">
-        <v>2099</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="397" spans="1:15" ht="24.95" customHeight="1">
       <c r="A397" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="B397" s="2" t="s">
+        <v>3291</v>
+      </c>
+      <c r="O397" s="2" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="398" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A398" s="2" t="s">
         <v>2096</v>
       </c>
-      <c r="B397" s="2" t="s">
+      <c r="B398" s="2" t="s">
         <v>3290</v>
       </c>
-      <c r="O397" s="2" t="s">
+      <c r="O398" s="2" t="s">
         <v>2100</v>
       </c>
     </row>
-    <row r="398" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O398" s="2"/>
-    </row>
     <row r="399" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A399" s="2" t="s">
-        <v>2648</v>
-      </c>
-      <c r="B399" s="2" t="s">
-        <v>3292</v>
-      </c>
-      <c r="O399" s="2" t="s">
-        <v>2650</v>
-      </c>
+      <c r="O399" s="2"/>
     </row>
     <row r="400" spans="1:15" ht="24.95" customHeight="1">
       <c r="A400" s="2" t="s">
+        <v>2648</v>
+      </c>
+      <c r="B400" s="2" t="s">
+        <v>3292</v>
+      </c>
+      <c r="O400" s="2" t="s">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="401" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A401" s="2" t="s">
         <v>2649</v>
       </c>
-      <c r="B400" s="2" t="s">
+      <c r="B401" s="2" t="s">
         <v>3318</v>
       </c>
-      <c r="O400" s="2" t="s">
+      <c r="O401" s="2" t="s">
         <v>2651</v>
-      </c>
-    </row>
-    <row r="402" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A402" s="2" t="s">
-        <v>2664</v>
-      </c>
-      <c r="B402" s="2" t="s">
-        <v>3294</v>
-      </c>
-      <c r="O402" s="2" t="s">
-        <v>2662</v>
       </c>
     </row>
     <row r="403" spans="1:15" ht="24.95" customHeight="1">
       <c r="A403" s="2" t="s">
+        <v>2664</v>
+      </c>
+      <c r="B403" s="2" t="s">
+        <v>3294</v>
+      </c>
+      <c r="O403" s="2" t="s">
+        <v>2662</v>
+      </c>
+    </row>
+    <row r="404" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A404" s="2" t="s">
         <v>2663</v>
       </c>
-      <c r="B403" s="2" t="s">
+      <c r="B404" s="2" t="s">
         <v>3319</v>
       </c>
-      <c r="O403" s="2" t="s">
+      <c r="O404" s="2" t="s">
         <v>2661</v>
       </c>
     </row>
-    <row r="404" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O404" s="2"/>
-    </row>
     <row r="405" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A405" s="2" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B405" s="2" t="s">
-        <v>3320</v>
-      </c>
-      <c r="O405" s="2" t="s">
-        <v>583</v>
-      </c>
+      <c r="O405" s="2"/>
     </row>
     <row r="406" spans="1:15" ht="24.95" customHeight="1">
       <c r="A406" s="2" t="s">
-        <v>2478</v>
+        <v>1826</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="O406" s="2" t="s">
-        <v>1339</v>
+        <v>583</v>
       </c>
     </row>
     <row r="407" spans="1:15" ht="24.95" customHeight="1">
       <c r="A407" s="2" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>3295</v>
+        <v>3321</v>
       </c>
       <c r="O407" s="2" t="s">
-        <v>590</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="408" spans="1:15" ht="24.95" customHeight="1">
       <c r="A408" s="2" t="s">
+        <v>2477</v>
+      </c>
+      <c r="B408" s="2" t="s">
+        <v>3295</v>
+      </c>
+      <c r="O408" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="409" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A409" s="2" t="s">
         <v>2624</v>
       </c>
-      <c r="B408" s="2" t="s">
+      <c r="B409" s="2" t="s">
         <v>1261</v>
       </c>
-      <c r="O408" s="2" t="s">
+      <c r="O409" s="2" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="409" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O409" s="2"/>
-    </row>
     <row r="410" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A410" s="2" t="s">
-        <v>2530</v>
-      </c>
-      <c r="B410" s="2" t="s">
-        <v>3675</v>
-      </c>
-      <c r="O410" s="2" t="s">
-        <v>3578</v>
-      </c>
+      <c r="O410" s="2"/>
     </row>
     <row r="411" spans="1:15" ht="24.95" customHeight="1">
       <c r="A411" s="2" t="s">
-        <v>2451</v>
+        <v>2530</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>3322</v>
+        <v>3675</v>
       </c>
       <c r="O411" s="2" t="s">
-        <v>2452</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="412" spans="1:15" ht="24.95" customHeight="1">
       <c r="A412" s="2" t="s">
-        <v>2464</v>
+        <v>2451</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="O412" s="2" t="s">
-        <v>2466</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="413" spans="1:15" ht="24.95" customHeight="1">
       <c r="A413" s="2" t="s">
+        <v>2464</v>
+      </c>
+      <c r="B413" s="2" t="s">
+        <v>3323</v>
+      </c>
+      <c r="O413" s="2" t="s">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="414" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A414" s="2" t="s">
         <v>2463</v>
       </c>
-      <c r="B413" s="2" t="s">
+      <c r="B414" s="2" t="s">
         <v>3324</v>
       </c>
-      <c r="O413" s="3" t="s">
+      <c r="O414" s="3" t="s">
         <v>2465</v>
       </c>
     </row>
-    <row r="414" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O414" s="2"/>
-    </row>
     <row r="415" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A415" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="B415" s="2" t="s">
-        <v>3296</v>
-      </c>
-      <c r="O415" s="2" t="s">
-        <v>548</v>
-      </c>
+      <c r="O415" s="2"/>
     </row>
     <row r="416" spans="1:15" ht="24.95" customHeight="1">
       <c r="A416" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>550</v>
+        <v>3296</v>
       </c>
       <c r="O416" s="2" t="s">
-        <v>1339</v>
+        <v>548</v>
       </c>
     </row>
     <row r="417" spans="1:15" ht="24.95" customHeight="1">
       <c r="A417" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B417" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="O417" s="2" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="418" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A418" s="2" t="s">
         <v>2685</v>
       </c>
-      <c r="B417" s="2" t="s">
+      <c r="B418" s="2" t="s">
         <v>3297</v>
       </c>
-      <c r="O417" s="2" t="s">
+      <c r="O418" s="2" t="s">
         <v>2686</v>
       </c>
     </row>
-    <row r="418" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O418" s="2"/>
-    </row>
     <row r="419" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A419" s="2" t="s">
-        <v>1293</v>
-      </c>
-      <c r="B419" s="2" t="s">
-        <v>3298</v>
-      </c>
-      <c r="O419" s="2" t="s">
-        <v>1300</v>
-      </c>
+      <c r="O419" s="2"/>
     </row>
     <row r="420" spans="1:15" ht="24.95" customHeight="1">
       <c r="A420" s="2" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>3325</v>
+        <v>3298</v>
       </c>
       <c r="O420" s="2" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="421" spans="1:15" ht="24.95" customHeight="1">
       <c r="A421" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>1273</v>
+        <v>3325</v>
       </c>
       <c r="O421" s="2" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="422" spans="1:15" ht="24.95" customHeight="1">
       <c r="A422" s="2" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="O422" s="2" t="s">
-        <v>1278</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="423" spans="1:15" ht="24.95" customHeight="1">
       <c r="A423" s="2" t="s">
-        <v>1306</v>
+        <v>1296</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>3326</v>
+        <v>1274</v>
       </c>
       <c r="O423" s="2" t="s">
-        <v>1307</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="424" spans="1:15" ht="24.95" customHeight="1">
       <c r="A424" s="2" t="s">
-        <v>1297</v>
+        <v>1306</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="O424" s="2" t="s">
-        <v>1302</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="425" spans="1:15" ht="24.95" customHeight="1">
       <c r="A425" s="2" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>1277</v>
+        <v>3327</v>
       </c>
       <c r="O425" s="2" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="426" spans="1:15" ht="24.95" customHeight="1">
       <c r="A426" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B426" s="2" t="s">
+        <v>1277</v>
+      </c>
+      <c r="O426" s="2" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="427" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A427" s="2" t="s">
         <v>1299</v>
       </c>
-      <c r="B426" s="2" t="s">
+      <c r="B427" s="2" t="s">
         <v>3328</v>
       </c>
-      <c r="O426" s="2" t="s">
+      <c r="O427" s="2" t="s">
         <v>1303</v>
       </c>
     </row>
-    <row r="427" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O427" s="2"/>
-    </row>
     <row r="428" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A428" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="B428" s="2" t="s">
-        <v>3329</v>
-      </c>
-      <c r="O428" s="2" t="s">
-        <v>552</v>
-      </c>
+      <c r="O428" s="2"/>
     </row>
     <row r="429" spans="1:15" ht="24.95" customHeight="1">
       <c r="A429" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B429" s="2" t="s">
+        <v>3329</v>
+      </c>
+      <c r="O429" s="2" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="430" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A430" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="B429" s="2" t="s">
+      <c r="B430" s="2" t="s">
         <v>3330</v>
       </c>
-      <c r="O429" s="2" t="s">
+      <c r="O430" s="2" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="430" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O430" s="2"/>
-    </row>
     <row r="431" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A431" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="B431" s="2" t="s">
-        <v>3331</v>
-      </c>
-      <c r="O431" s="2" t="s">
-        <v>556</v>
-      </c>
+      <c r="O431" s="2"/>
     </row>
     <row r="432" spans="1:15" ht="24.95" customHeight="1">
       <c r="A432" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>3299</v>
+        <v>3331</v>
       </c>
       <c r="O432" s="2" t="s">
-        <v>2334</v>
+        <v>556</v>
       </c>
     </row>
     <row r="433" spans="1:15" ht="24.95" customHeight="1">
       <c r="A433" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="B433" s="2" t="s">
+        <v>3299</v>
+      </c>
+      <c r="O433" s="2" t="s">
+        <v>2334</v>
+      </c>
+    </row>
+    <row r="434" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A434" s="2" t="s">
         <v>2336</v>
       </c>
-      <c r="B433" s="2" t="s">
+      <c r="B434" s="2" t="s">
         <v>3332</v>
       </c>
-      <c r="O433" s="2" t="s">
+      <c r="O434" s="2" t="s">
         <v>2335</v>
       </c>
     </row>
-    <row r="434" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O434" s="2"/>
-    </row>
     <row r="435" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A435" s="2" t="s">
+      <c r="O435" s="2"/>
+    </row>
+    <row r="436" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A436" s="2" t="s">
         <v>3876</v>
       </c>
-      <c r="B435" s="2" t="s">
+      <c r="B436" s="2" t="s">
         <v>3877</v>
       </c>
-      <c r="O435" s="2" t="s">
+      <c r="O436" s="2" t="s">
         <v>3875</v>
       </c>
     </row>
-    <row r="436" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O436" s="2"/>
-    </row>
     <row r="437" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A437" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="B437" s="2" t="s">
-        <v>3333</v>
-      </c>
-      <c r="O437" s="2" t="s">
-        <v>559</v>
-      </c>
+      <c r="O437" s="2"/>
     </row>
     <row r="438" spans="1:15" ht="24.95" customHeight="1">
       <c r="A438" s="2" t="s">
-        <v>1228</v>
+        <v>558</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="O438" s="2" t="s">
-        <v>377</v>
+        <v>559</v>
       </c>
     </row>
     <row r="439" spans="1:15" ht="24.95" customHeight="1">
       <c r="A439" s="2" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="O439" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="440" spans="1:15" ht="24.95" customHeight="1">
       <c r="A440" s="2" t="s">
-        <v>560</v>
+        <v>1229</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>3304</v>
+        <v>3335</v>
       </c>
       <c r="O440" s="2" t="s">
-        <v>561</v>
+        <v>380</v>
       </c>
     </row>
     <row r="441" spans="1:15" ht="24.95" customHeight="1">
       <c r="A441" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>3302</v>
+        <v>3304</v>
       </c>
       <c r="O441" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="442" spans="1:15" ht="24.95" customHeight="1">
       <c r="A442" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>3336</v>
+        <v>3302</v>
       </c>
       <c r="O442" s="2" t="s">
-        <v>1340</v>
+        <v>563</v>
       </c>
     </row>
     <row r="443" spans="1:15" ht="24.95" customHeight="1">
       <c r="A443" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="O443" s="2" t="s">
-        <v>566</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="444" spans="1:15" ht="24.95" customHeight="1">
       <c r="A444" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="O444" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="445" spans="1:15" ht="24.95" customHeight="1">
       <c r="A445" s="2" t="s">
-        <v>1938</v>
+        <v>567</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="O445" s="2" t="s">
-        <v>1939</v>
+        <v>568</v>
       </c>
     </row>
     <row r="446" spans="1:15" ht="24.95" customHeight="1">
       <c r="A446" s="2" t="s">
-        <v>1326</v>
+        <v>1938</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>3303</v>
+        <v>3339</v>
       </c>
       <c r="O446" s="2" t="s">
-        <v>569</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="447" spans="1:15" ht="24.95" customHeight="1">
       <c r="A447" s="2" t="s">
-        <v>570</v>
+        <v>1326</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>571</v>
+        <v>3303</v>
       </c>
       <c r="O447" s="2" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="448" spans="1:15" ht="24.95" customHeight="1">
       <c r="A448" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="O448" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="449" spans="1:15" ht="24.95" customHeight="1">
       <c r="A449" s="2" t="s">
-        <v>1936</v>
+        <v>573</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>3340</v>
+        <v>574</v>
       </c>
       <c r="O449" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="450" spans="1:15" ht="24.95" customHeight="1">
       <c r="A450" s="2" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B450" s="2" t="s">
+        <v>3340</v>
+      </c>
+      <c r="O450" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="451" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A451" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="B450" s="2" t="s">
+      <c r="B451" s="2" t="s">
         <v>3305</v>
       </c>
-      <c r="O450" s="2" t="s">
+      <c r="O451" s="2" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="451" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O451" s="2"/>
-    </row>
     <row r="452" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A452" s="2" t="s">
-        <v>1233</v>
-      </c>
-      <c r="B452" s="2" t="s">
-        <v>3347</v>
-      </c>
-      <c r="O452" s="2" t="s">
-        <v>1253</v>
-      </c>
+      <c r="O452" s="2"/>
     </row>
     <row r="453" spans="1:15" ht="24.95" customHeight="1">
       <c r="A453" s="2" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="O453" s="2" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="454" spans="1:15" ht="24.95" customHeight="1">
       <c r="A454" s="2" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>3342</v>
+        <v>3348</v>
       </c>
       <c r="O454" s="2" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="455" spans="1:15" ht="24.95" customHeight="1">
       <c r="A455" s="2" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="O455" s="2" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="456" spans="1:15" ht="24.95" customHeight="1">
       <c r="A456" s="2" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="O456" s="2" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="457" spans="1:15" ht="24.95" customHeight="1">
       <c r="A457" s="2" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>3349</v>
+        <v>3344</v>
       </c>
       <c r="O457" s="2" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="458" spans="1:15" ht="24.95" customHeight="1">
       <c r="A458" s="2" t="s">
-        <v>1238</v>
-      </c>
-      <c r="B458" s="5" t="s">
-        <v>3350</v>
+        <v>1237</v>
+      </c>
+      <c r="B458" s="2" t="s">
+        <v>3349</v>
       </c>
       <c r="O458" s="2" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="459" spans="1:15" ht="24.95" customHeight="1">
       <c r="A459" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B459" s="5" t="s">
+        <v>3350</v>
+      </c>
+      <c r="O459" s="2" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="460" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A460" s="2" t="s">
         <v>1239</v>
       </c>
-      <c r="B459" s="2" t="s">
+      <c r="B460" s="2" t="s">
         <v>3438</v>
       </c>
-      <c r="O459" s="2" t="s">
+      <c r="O460" s="2" t="s">
         <v>1246</v>
       </c>
     </row>
-    <row r="460" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O460" s="2"/>
-    </row>
     <row r="461" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A461" s="2" t="s">
-        <v>1241</v>
-      </c>
-      <c r="B461" s="2" t="s">
-        <v>3334</v>
-      </c>
-      <c r="O461" s="2" t="s">
-        <v>1245</v>
-      </c>
+      <c r="O461" s="2"/>
     </row>
     <row r="462" spans="1:15" ht="24.95" customHeight="1">
       <c r="A462" s="2" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="O462" s="2" t="s">
-        <v>380</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="463" spans="1:15" ht="24.95" customHeight="1">
       <c r="A463" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B463" s="2" t="s">
+        <v>3335</v>
+      </c>
+      <c r="O463" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="464" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A464" s="2" t="s">
         <v>1824</v>
       </c>
-      <c r="B463" s="2" t="s">
+      <c r="B464" s="2" t="s">
         <v>3351</v>
       </c>
-      <c r="O463" s="2" t="s">
+      <c r="O464" s="2" t="s">
         <v>1825</v>
       </c>
     </row>
-    <row r="464" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O464" s="2"/>
-    </row>
     <row r="465" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A465" s="2" t="s">
-        <v>4202</v>
-      </c>
-      <c r="B465" s="2" t="s">
-        <v>4203</v>
-      </c>
-      <c r="O465" s="2" t="s">
-        <v>4204</v>
-      </c>
+      <c r="O465" s="2"/>
     </row>
     <row r="466" spans="1:15" ht="24.95" customHeight="1">
       <c r="A466" s="2" t="s">
-        <v>598</v>
+        <v>4202</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>599</v>
+        <v>4203</v>
       </c>
       <c r="O466" s="2" t="s">
-        <v>600</v>
+        <v>4204</v>
       </c>
     </row>
     <row r="467" spans="1:15" ht="24.95" customHeight="1">
       <c r="A467" s="2" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="O467" s="2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="468" spans="1:15" ht="24.95" customHeight="1">
       <c r="A468" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="B468" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="O468" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="469" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A469" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="B468" s="2" t="s">
+      <c r="B469" s="2" t="s">
         <v>3439</v>
       </c>
-      <c r="O468" s="2" t="s">
+      <c r="O469" s="2" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="469" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O469" s="2"/>
-    </row>
     <row r="470" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A470" s="2" t="s">
+      <c r="O470" s="2"/>
+    </row>
+    <row r="471" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A471" s="2" t="s">
         <v>1243</v>
       </c>
-      <c r="B470" s="2" t="s">
+      <c r="B471" s="2" t="s">
         <v>3352</v>
       </c>
-      <c r="O470" s="2" t="s">
+      <c r="O471" s="2" t="s">
         <v>1244</v>
       </c>
     </row>
-    <row r="471" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O471" s="2"/>
-    </row>
     <row r="472" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A472" s="2" t="s">
-        <v>2436</v>
-      </c>
-      <c r="B472" s="2" t="s">
-        <v>3440</v>
-      </c>
-      <c r="O472" s="2" t="s">
-        <v>2438</v>
-      </c>
+      <c r="O472" s="2"/>
     </row>
     <row r="473" spans="1:15" ht="24.95" customHeight="1">
       <c r="A473" s="2" t="s">
+        <v>2436</v>
+      </c>
+      <c r="B473" s="2" t="s">
+        <v>3440</v>
+      </c>
+      <c r="O473" s="2" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="474" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A474" s="2" t="s">
         <v>2437</v>
       </c>
-      <c r="B473" s="2" t="s">
+      <c r="B474" s="2" t="s">
         <v>3441</v>
       </c>
-      <c r="O473" s="2" t="s">
+      <c r="O474" s="2" t="s">
         <v>2439</v>
       </c>
     </row>
-    <row r="474" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O474" s="2"/>
-    </row>
     <row r="475" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A475" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="B475" s="2" t="s">
-        <v>3442</v>
-      </c>
-      <c r="O475" s="2" t="s">
-        <v>580</v>
-      </c>
+      <c r="O475" s="2"/>
     </row>
     <row r="476" spans="1:15" ht="24.95" customHeight="1">
       <c r="A476" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="O476" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="477" spans="1:15" ht="24.95" customHeight="1">
       <c r="A477" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B477" s="2" t="s">
+        <v>3443</v>
+      </c>
+      <c r="O477" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="478" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A478" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="B477" s="2" t="s">
+      <c r="B478" s="2" t="s">
         <v>3444</v>
       </c>
-      <c r="O477" s="2" t="s">
+      <c r="O478" s="2" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="478" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O478" s="2"/>
-    </row>
     <row r="479" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A479" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="B479" s="2" t="s">
-        <v>3445</v>
-      </c>
-      <c r="O479" s="2" t="s">
-        <v>586</v>
-      </c>
+      <c r="O479" s="2"/>
     </row>
     <row r="480" spans="1:15" ht="24.95" customHeight="1">
       <c r="A480" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>588</v>
+        <v>3445</v>
       </c>
       <c r="O480" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="481" spans="1:15" ht="24.95" customHeight="1">
       <c r="A481" s="2" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>3446</v>
+        <v>588</v>
       </c>
       <c r="O481" s="2" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="482" spans="1:15" ht="24.95" customHeight="1">
       <c r="A482" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>3356</v>
+        <v>3446</v>
       </c>
       <c r="O482" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="483" spans="1:15" ht="24.95" customHeight="1">
       <c r="A483" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B483" s="2" t="s">
+        <v>3356</v>
+      </c>
+      <c r="O483" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="484" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A484" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="B483" s="2" t="s">
+      <c r="B484" s="2" t="s">
         <v>3447</v>
       </c>
-      <c r="O483" s="2" t="s">
+      <c r="O484" s="2" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="484" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O484" s="2"/>
-    </row>
     <row r="485" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A485" s="2" t="s">
-        <v>1232</v>
-      </c>
-      <c r="B485" s="2" t="s">
-        <v>3448</v>
-      </c>
-      <c r="O485" s="2" t="s">
-        <v>2499</v>
-      </c>
+      <c r="O485" s="2"/>
     </row>
     <row r="486" spans="1:15" ht="24.95" customHeight="1">
       <c r="A486" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B486" s="2" t="s">
+        <v>3448</v>
+      </c>
+      <c r="O486" s="2" t="s">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="487" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A487" s="2" t="s">
         <v>1282</v>
       </c>
-      <c r="B486" s="2" t="s">
+      <c r="B487" s="2" t="s">
         <v>3357</v>
       </c>
-      <c r="O486" s="2" t="s">
+      <c r="O487" s="2" t="s">
         <v>2500</v>
       </c>
     </row>
-    <row r="487" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O487" s="2"/>
-    </row>
     <row r="488" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A488" s="2" t="s">
-        <v>1265</v>
-      </c>
-      <c r="B488" s="2" t="s">
-        <v>3449</v>
-      </c>
-      <c r="O488" s="2" t="s">
-        <v>1266</v>
-      </c>
+      <c r="O488" s="2"/>
     </row>
     <row r="489" spans="1:15" ht="24.95" customHeight="1">
       <c r="A489" s="2" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>1277</v>
+        <v>3449</v>
       </c>
       <c r="O489" s="2" t="s">
-        <v>1304</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="490" spans="1:15" ht="24.95" customHeight="1">
       <c r="A490" s="2" t="s">
-        <v>593</v>
+        <v>1269</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="O490" s="2" t="s">
-        <v>1279</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="491" spans="1:15" ht="24.95" customHeight="1">
       <c r="A491" s="2" t="s">
-        <v>1267</v>
+        <v>593</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>3450</v>
+        <v>1276</v>
       </c>
       <c r="O491" s="2" t="s">
-        <v>1268</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="492" spans="1:15" ht="24.95" customHeight="1">
       <c r="A492" s="2" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>1273</v>
+        <v>3450</v>
       </c>
       <c r="O492" s="2" t="s">
-        <v>1305</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="493" spans="1:15" ht="24.95" customHeight="1">
       <c r="A493" s="2" t="s">
-        <v>1275</v>
+        <v>1270</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="O493" s="2" t="s">
-        <v>1278</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="494" spans="1:15" ht="24.95" customHeight="1">
       <c r="A494" s="2" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>3326</v>
+        <v>1274</v>
       </c>
       <c r="O494" s="2" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="495" spans="1:15" ht="24.95" customHeight="1">
       <c r="A495" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B495" s="2" t="s">
+        <v>3326</v>
+      </c>
+      <c r="O495" s="2" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="496" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A496" s="2" t="s">
         <v>1271</v>
       </c>
-      <c r="B495" s="2" t="s">
+      <c r="B496" s="2" t="s">
         <v>3451</v>
       </c>
-      <c r="O495" s="2" t="s">
+      <c r="O496" s="2" t="s">
         <v>1280</v>
       </c>
     </row>
-    <row r="496" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O496" s="2"/>
-    </row>
     <row r="497" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A497" s="2" t="s">
-        <v>2369</v>
-      </c>
-      <c r="B497" s="2" t="s">
-        <v>3358</v>
-      </c>
-      <c r="O497" s="2" t="s">
-        <v>2374</v>
-      </c>
+      <c r="O497" s="2"/>
     </row>
     <row r="498" spans="1:15" ht="24.95" customHeight="1">
       <c r="A498" s="2" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>3359</v>
+        <v>3358</v>
       </c>
       <c r="O498" s="2" t="s">
-        <v>2372</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="499" spans="1:15" ht="24.95" customHeight="1">
       <c r="A499" s="2" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>3360</v>
-      </c>
-      <c r="O499" s="3" t="s">
-        <v>2373</v>
+        <v>3359</v>
+      </c>
+      <c r="O499" s="2" t="s">
+        <v>2372</v>
       </c>
     </row>
     <row r="500" spans="1:15" ht="24.95" customHeight="1">
       <c r="A500" s="2" t="s">
+        <v>2371</v>
+      </c>
+      <c r="B500" s="2" t="s">
+        <v>3360</v>
+      </c>
+      <c r="O500" s="3" t="s">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="501" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A501" s="2" t="s">
         <v>2425</v>
       </c>
-      <c r="B500" s="2" t="s">
+      <c r="B501" s="2" t="s">
         <v>3452</v>
       </c>
-      <c r="O500" s="3" t="s">
+      <c r="O501" s="3" t="s">
         <v>2450</v>
-      </c>
-    </row>
-    <row r="502" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A502" s="2" t="s">
-        <v>2612</v>
-      </c>
-      <c r="B502" s="2" t="s">
-        <v>3361</v>
-      </c>
-      <c r="O502" s="3" t="s">
-        <v>2615</v>
       </c>
     </row>
     <row r="503" spans="1:15" ht="24.95" customHeight="1">
       <c r="A503" s="2" t="s">
+        <v>2612</v>
+      </c>
+      <c r="B503" s="2" t="s">
+        <v>3361</v>
+      </c>
+      <c r="O503" s="3" t="s">
+        <v>2615</v>
+      </c>
+    </row>
+    <row r="504" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A504" s="2" t="s">
         <v>2613</v>
       </c>
-      <c r="B503" s="2" t="s">
+      <c r="B504" s="2" t="s">
         <v>3453</v>
       </c>
-      <c r="O503" s="3" t="s">
+      <c r="O504" s="3" t="s">
         <v>2614</v>
       </c>
     </row>
-    <row r="504" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O504" s="2"/>
-    </row>
     <row r="505" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A505" s="2" t="s">
-        <v>2000</v>
-      </c>
-      <c r="B505" s="2" t="s">
-        <v>3454</v>
-      </c>
-      <c r="O505" s="3" t="s">
-        <v>2001</v>
-      </c>
+      <c r="O505" s="2"/>
     </row>
     <row r="506" spans="1:15" ht="24.95" customHeight="1">
       <c r="A506" s="2" t="s">
-        <v>1991</v>
+        <v>2000</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>3365</v>
-      </c>
-      <c r="O506" s="2" t="s">
-        <v>1989</v>
+        <v>3454</v>
+      </c>
+      <c r="O506" s="3" t="s">
+        <v>2001</v>
       </c>
     </row>
     <row r="507" spans="1:15" ht="24.95" customHeight="1">
       <c r="A507" s="2" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B507" s="2" t="s">
+        <v>3365</v>
+      </c>
+      <c r="O507" s="2" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="508" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A508" s="2" t="s">
         <v>1992</v>
       </c>
-      <c r="B507" s="2" t="s">
+      <c r="B508" s="2" t="s">
         <v>3366</v>
       </c>
-      <c r="O507" s="2" t="s">
+      <c r="O508" s="2" t="s">
         <v>1990</v>
       </c>
     </row>
-    <row r="508" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O508" s="2"/>
-    </row>
     <row r="509" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A509" s="2" t="s">
-        <v>1230</v>
-      </c>
-      <c r="B509" s="2" t="s">
-        <v>3455</v>
-      </c>
-      <c r="O509" s="2" t="s">
-        <v>1254</v>
-      </c>
+      <c r="O509" s="2"/>
     </row>
     <row r="510" spans="1:15" ht="24.95" customHeight="1">
       <c r="A510" s="2" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>3243</v>
+        <v>3455</v>
       </c>
       <c r="O510" s="2" t="s">
-        <v>1944</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="511" spans="1:15" ht="24.95" customHeight="1">
       <c r="A511" s="2" t="s">
-        <v>1255</v>
+        <v>1231</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>3456</v>
+        <v>3243</v>
       </c>
       <c r="O511" s="2" t="s">
-        <v>1360</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="512" spans="1:15" ht="24.95" customHeight="1">
       <c r="A512" s="2" t="s">
-        <v>719</v>
+        <v>1255</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>3367</v>
+        <v>3456</v>
       </c>
       <c r="O512" s="2" t="s">
-        <v>1945</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="513" spans="1:15" ht="24.95" customHeight="1">
       <c r="A513" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>3457</v>
+        <v>3367</v>
       </c>
       <c r="O513" s="2" t="s">
-        <v>721</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="514" spans="1:15" ht="24.95" customHeight="1">
       <c r="A514" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B514" s="2" t="s">
+        <v>3457</v>
+      </c>
+      <c r="O514" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="515" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A515" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="B514" s="2" t="s">
+      <c r="B515" s="2" t="s">
         <v>3368</v>
       </c>
-      <c r="O514" s="2" t="s">
+      <c r="O515" s="2" t="s">
         <v>1943</v>
       </c>
     </row>
-    <row r="515" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O515" s="2"/>
-    </row>
     <row r="516" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A516" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="B516" s="2" t="s">
-        <v>3369</v>
-      </c>
-      <c r="O516" s="2" t="s">
-        <v>744</v>
-      </c>
+      <c r="O516" s="2"/>
     </row>
     <row r="517" spans="1:15" ht="24.95" customHeight="1">
       <c r="A517" s="2" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>3458</v>
+        <v>3369</v>
       </c>
       <c r="O517" s="2" t="s">
-        <v>2329</v>
+        <v>744</v>
       </c>
     </row>
     <row r="518" spans="1:15" ht="24.95" customHeight="1">
       <c r="A518" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>3370</v>
+        <v>3458</v>
       </c>
       <c r="O518" s="2" t="s">
-        <v>747</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="519" spans="1:15" ht="24.95" customHeight="1">
       <c r="A519" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>3459</v>
+        <v>3370</v>
       </c>
       <c r="O519" s="2" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="520" spans="1:15" ht="24.95" customHeight="1">
       <c r="A520" s="2" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="O520" s="2" t="s">
-        <v>2025</v>
+        <v>749</v>
       </c>
     </row>
     <row r="521" spans="1:15" ht="24.95" customHeight="1">
       <c r="A521" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="B521" s="2" t="s">
+        <v>3460</v>
+      </c>
+      <c r="O521" s="2" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="522" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A522" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="B521" s="2" t="s">
+      <c r="B522" s="2" t="s">
         <v>3371</v>
       </c>
-      <c r="O521" s="2" t="s">
+      <c r="O522" s="2" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="522" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O522" s="2"/>
-    </row>
     <row r="523" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A523" s="2" t="s">
-        <v>2633</v>
-      </c>
-      <c r="B523" s="2" t="s">
-        <v>3372</v>
-      </c>
-      <c r="O523" s="2" t="s">
-        <v>2634</v>
-      </c>
+      <c r="O523" s="2"/>
     </row>
     <row r="524" spans="1:15" ht="24.95" customHeight="1">
       <c r="A524" s="2" t="s">
-        <v>606</v>
+        <v>2633</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>3461</v>
+        <v>3372</v>
       </c>
       <c r="O524" s="2" t="s">
-        <v>1260</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="525" spans="1:15" ht="24.95" customHeight="1">
       <c r="A525" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="O525" s="2" t="s">
-        <v>608</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="526" spans="1:15" ht="24.95" customHeight="1">
       <c r="A526" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B526" s="2" t="s">
+        <v>3462</v>
+      </c>
+      <c r="O526" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="527" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A527" s="2" t="s">
         <v>1259</v>
       </c>
-      <c r="B526" s="2" t="s">
+      <c r="B527" s="2" t="s">
         <v>3463</v>
       </c>
-      <c r="O526" s="3" t="s">
+      <c r="O527" s="3" t="s">
         <v>1258</v>
-      </c>
-    </row>
-    <row r="528" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A528" s="2" t="s">
-        <v>2627</v>
-      </c>
-      <c r="B528" s="2" t="s">
-        <v>3373</v>
-      </c>
-      <c r="O528" s="3" t="s">
-        <v>2630</v>
       </c>
     </row>
     <row r="529" spans="1:15" ht="24.95" customHeight="1">
       <c r="A529" s="2" t="s">
-        <v>4136</v>
+        <v>2627</v>
+      </c>
+      <c r="B529" s="2" t="s">
+        <v>3373</v>
       </c>
       <c r="O529" s="3" t="s">
-        <v>4137</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="530" spans="1:15" ht="24.95" customHeight="1">
       <c r="A530" s="2" t="s">
-        <v>2631</v>
-      </c>
-      <c r="B530" s="2" t="s">
-        <v>3464</v>
+        <v>4136</v>
       </c>
       <c r="O530" s="3" t="s">
-        <v>2632</v>
+        <v>4137</v>
       </c>
     </row>
     <row r="531" spans="1:15" ht="24.95" customHeight="1">
       <c r="A531" s="2" t="s">
-        <v>2625</v>
+        <v>2631</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="O531" s="3" t="s">
-        <v>2628</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="532" spans="1:15" ht="24.95" customHeight="1">
       <c r="A532" s="2" t="s">
+        <v>2625</v>
+      </c>
+      <c r="B532" s="2" t="s">
+        <v>3465</v>
+      </c>
+      <c r="O532" s="3" t="s">
+        <v>2628</v>
+      </c>
+    </row>
+    <row r="533" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A533" s="2" t="s">
         <v>2626</v>
       </c>
-      <c r="B532" s="2" t="s">
+      <c r="B533" s="2" t="s">
         <v>3466</v>
       </c>
-      <c r="O532" s="3" t="s">
+      <c r="O533" s="3" t="s">
         <v>2629</v>
       </c>
     </row>
-    <row r="534" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A534" s="2" t="s">
+    <row r="535" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A535" s="2" t="s">
         <v>2353</v>
       </c>
-      <c r="B534" s="2" t="s">
+      <c r="B535" s="2" t="s">
         <v>3673</v>
       </c>
-      <c r="O534" s="3" t="s">
+      <c r="O535" s="3" t="s">
         <v>3580</v>
-      </c>
-    </row>
-    <row r="536" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A536" s="2" t="s">
-        <v>2675</v>
-      </c>
-      <c r="B536" s="2" t="s">
-        <v>3674</v>
-      </c>
-      <c r="O536" s="3" t="s">
-        <v>3579</v>
       </c>
     </row>
     <row r="537" spans="1:15" ht="24.95" customHeight="1">
       <c r="A537" s="2" t="s">
-        <v>2676</v>
+        <v>2675</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>3374</v>
+        <v>3674</v>
       </c>
       <c r="O537" s="3" t="s">
-        <v>2678</v>
+        <v>3579</v>
       </c>
     </row>
     <row r="538" spans="1:15" ht="24.95" customHeight="1">
       <c r="A538" s="2" t="s">
+        <v>2676</v>
+      </c>
+      <c r="B538" s="2" t="s">
+        <v>3374</v>
+      </c>
+      <c r="O538" s="3" t="s">
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="539" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A539" s="2" t="s">
         <v>2677</v>
       </c>
-      <c r="B538" s="2" t="s">
+      <c r="B539" s="2" t="s">
         <v>3375</v>
       </c>
-      <c r="O538" s="3" t="s">
+      <c r="O539" s="3" t="s">
         <v>2679</v>
-      </c>
-    </row>
-    <row r="540" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A540" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="B540" s="2" t="s">
-        <v>3467</v>
-      </c>
-      <c r="O540" s="2" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="541" spans="1:15" ht="24.95" customHeight="1">
       <c r="A541" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>3376</v>
+        <v>3467</v>
       </c>
       <c r="O541" s="2" t="s">
-        <v>399</v>
+        <v>610</v>
       </c>
     </row>
     <row r="542" spans="1:15" ht="24.95" customHeight="1">
       <c r="A542" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>3468</v>
+        <v>3376</v>
       </c>
       <c r="O542" s="2" t="s">
-        <v>613</v>
+        <v>399</v>
       </c>
     </row>
     <row r="543" spans="1:15" ht="24.95" customHeight="1">
       <c r="A543" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B543" s="2" t="s">
+        <v>3468</v>
+      </c>
+      <c r="O543" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="544" spans="1:15" ht="24.95" customHeight="1">
+      <c r="A544" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B543" s="2" t="s">
+      <c r="B544" s="2" t="s">
         <v>3215</v>
       </c>
-      <c r="O543" s="2" t="s">
+      <c r="O544" s="2" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="544" spans="1:15" ht="24.95" customHeight="1">
-      <c r="O544" s="2"/>
-    </row>
     <row r="545" spans="1:15" ht="24.95" customHeight="1">
-      <c r="A545" s="2" t="s">
-        <v>3879</v>
-      </c>
-      <c r="B545" s="2" t="s">
-        <v>4186</v>
-      </c>
-      <c r="O545" s="2" t="s">
-        <v>3880</v>
-      </c>
+      <c r="O545" s="2"/>
     </row>
     <row r="546" spans="1:15" ht="24.95" customHeight="1">
       <c r="A546" s="2" t="s">
-        <v>3888</v>
+        <v>3879</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>4187</v>
-      </c>
-      <c r="O546" s="3" t="s">
-        <v>3885</v>
+        <v>4186</v>
+      </c>
+      <c r="O546" s="2" t="s">
+        <v>3880</v>
       </c>
     </row>
     <row r="547" spans="1:15" ht="24.95" customHeight="1">
       <c r="A547" s="2" t="s">
-        <v>3881</v>
+        <v>3888</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>4188</v>
-      </c>
-      <c r="O547" s="2" t="s">
-        <v>3883</v>
+        <v>4187</v>
+      </c>
+      <c r="O547" s="3" t="s">
+        <v>3885</v>
       </c>
     </row>
     <row r="548" spans="1:15" ht="24.95" customHeight="1">
       <c r="A548" s="2" t="s">
-        <v>3882</v>
+        <v>3881</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>4189</v>
+        <v>4188</v>
       </c>
       <c r="O548" s="2" t="s">
-        <v>3884</v>
+        <v>3883</v>
       </c>
     </row>
     <row r="549" spans="1:15" ht="24.95" customHeight="1">
       <c r="A549" s="2" t="s">
-        <v>3893</v>
+        <v>3882</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>4190</v>
+        <v>4189</v>
       </c>
       <c r="O549" s="2" t="s">
-        <v>3894</v>
+        <v>3884</v>
       </c>
     </row>
     <row r="550" spans="1:15" ht="24.95" customHeight="1">
       <c r="A550" s="2" t="s">
-        <v>3889</v>
+        <v>3893</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>4191</v>
+        <v>4190</v>
       </c>
       <c r="O550" s="2" t="s">
-        <v>3895</v>
+        <v>3894</v>
       </c>
     </row>
     <row r="551" spans="1:15" ht="24.95" customHeight="1">
       <c r="A551" s="2" t="s">
-        <v>3890</v>
+        <v>3889</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>4192</v>
+        <v>4191</v>
       </c>
       <c r="O551" s="2" t="s">
-        <v>3892</v>
+        <v>3895</v>
       </c>
     </row>
     <row r="552" spans="1:15" ht="24.95" customHeight="1">
       <c r="A552" s="2" t="s">
-        <v>3891</v>
+        <v>3890</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>4193</v>
+        <v>4192</v>
       </c>
       <c r="O552" s="2" t="s">
-        <v>3896</v>
+        <v>3892</v>
       </c>
     </row>
     <row r="553" spans="1:15" ht="24.95" customHeight="1">
       <c r="A553" s="2" t="s">
-        <v>3897</v>
+        <v>3891</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>4194</v>
+        <v>4193</v>
       </c>
       <c r="O553" s="2" t="s">
-        <v>3898</v>
+        <v>3896</v>
       </c>
     </row>
     <row r="554" spans="1:15" ht="24.95" customHeight="1">
       <c 